--- a/Notice.xlsx
+++ b/Notice.xlsx
@@ -5,10 +5,10 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Downloads\New folder (13)\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D92A034C-1795-4C13-9D46-2BD0B3676EE6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{105205DE-FFB3-4376-91BE-8A5F1B9C0663}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -292,9 +292,6 @@
     <t>Total</t>
   </si>
   <si>
-    <t>Notice &amp; Hearing Report Last Updated On : 12-09-2026 09:56:54</t>
-  </si>
-  <si>
     <t>DSE with UP</t>
   </si>
   <si>
@@ -305,6 +302,9 @@
   </si>
   <si>
     <t>No Action Required</t>
+  </si>
+  <si>
+    <t>Notice &amp; Hearing Report Last Updated On : 14-09-2026 07:56:54</t>
   </si>
 </sst>
 </file>
@@ -340,7 +340,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
@@ -682,12 +683,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:S74"/>
+  <dimension ref="A1:S76"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -742,7 +743,7 @@
       <c r="O2" s="1"/>
       <c r="P2" s="1"/>
       <c r="Q2" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="R2" s="1"/>
       <c r="S2" s="1"/>
@@ -784,14 +785,14 @@
       <c r="P3" t="s">
         <v>18</v>
       </c>
-      <c r="Q3" t="s">
+      <c r="Q3" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="R3" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="R3" t="s">
+      <c r="S3" s="2" t="s">
         <v>93</v>
-      </c>
-      <c r="S3" t="s">
-        <v>94</v>
       </c>
     </row>
     <row r="4" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
@@ -843,13 +844,13 @@
       <c r="P4">
         <v>53812</v>
       </c>
-      <c r="Q4">
+      <c r="Q4" s="2">
         <v>12212</v>
       </c>
-      <c r="R4">
-        <v>0</v>
-      </c>
-      <c r="S4">
+      <c r="R4" s="2">
+        <v>0</v>
+      </c>
+      <c r="S4" s="2">
         <v>11</v>
       </c>
     </row>
@@ -902,13 +903,13 @@
       <c r="P5">
         <v>74848</v>
       </c>
-      <c r="Q5">
+      <c r="Q5" s="2">
         <v>16108</v>
       </c>
-      <c r="R5">
-        <v>0</v>
-      </c>
-      <c r="S5">
+      <c r="R5" s="2">
+        <v>0</v>
+      </c>
+      <c r="S5" s="2">
         <v>30</v>
       </c>
     </row>
@@ -941,33 +942,33 @@
         <v>0</v>
       </c>
       <c r="J6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K6">
         <v>0</v>
       </c>
       <c r="L6">
-        <v>6027</v>
+        <v>6035</v>
       </c>
       <c r="M6">
         <v>201</v>
       </c>
       <c r="N6">
-        <v>1804</v>
+        <v>1810</v>
       </c>
       <c r="O6">
-        <v>36928</v>
+        <v>37296</v>
       </c>
       <c r="P6">
         <v>71989</v>
       </c>
-      <c r="Q6">
+      <c r="Q6" s="2">
         <v>17830</v>
       </c>
-      <c r="R6">
-        <v>0</v>
-      </c>
-      <c r="S6">
+      <c r="R6" s="2">
+        <v>0</v>
+      </c>
+      <c r="S6" s="2">
         <v>54</v>
       </c>
     </row>
@@ -1000,13 +1001,13 @@
         <v>0</v>
       </c>
       <c r="J7">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K7">
         <v>0</v>
       </c>
       <c r="L7">
-        <v>5627</v>
+        <v>5681</v>
       </c>
       <c r="M7">
         <v>257</v>
@@ -1020,13 +1021,13 @@
       <c r="P7">
         <v>77581</v>
       </c>
-      <c r="Q7">
+      <c r="Q7" s="2">
         <v>20511</v>
       </c>
-      <c r="R7">
-        <v>0</v>
-      </c>
-      <c r="S7">
+      <c r="R7" s="2">
+        <v>0</v>
+      </c>
+      <c r="S7" s="2">
         <v>8</v>
       </c>
     </row>
@@ -1059,13 +1060,13 @@
         <v>0</v>
       </c>
       <c r="J8">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K8">
         <v>0</v>
       </c>
       <c r="L8">
-        <v>14241</v>
+        <v>14243</v>
       </c>
       <c r="M8">
         <v>164</v>
@@ -1074,18 +1075,18 @@
         <v>1874</v>
       </c>
       <c r="O8">
-        <v>35270</v>
+        <v>37746</v>
       </c>
       <c r="P8">
         <v>73458</v>
       </c>
-      <c r="Q8">
+      <c r="Q8" s="2">
         <v>20788</v>
       </c>
-      <c r="R8">
-        <v>0</v>
-      </c>
-      <c r="S8">
+      <c r="R8" s="2">
+        <v>0</v>
+      </c>
+      <c r="S8" s="2">
         <v>110</v>
       </c>
     </row>
@@ -1138,13 +1139,13 @@
       <c r="P9">
         <v>72913</v>
       </c>
-      <c r="Q9">
+      <c r="Q9" s="2">
         <v>18141</v>
       </c>
-      <c r="R9">
-        <v>0</v>
-      </c>
-      <c r="S9">
+      <c r="R9" s="2">
+        <v>0</v>
+      </c>
+      <c r="S9" s="2">
         <v>110</v>
       </c>
     </row>
@@ -1197,13 +1198,13 @@
       <c r="P10">
         <v>53124</v>
       </c>
-      <c r="Q10">
+      <c r="Q10" s="2">
         <v>9498</v>
       </c>
-      <c r="R10">
-        <v>0</v>
-      </c>
-      <c r="S10">
+      <c r="R10" s="2">
+        <v>0</v>
+      </c>
+      <c r="S10" s="2">
         <v>2</v>
       </c>
     </row>
@@ -1256,13 +1257,13 @@
       <c r="P11">
         <v>84438</v>
       </c>
-      <c r="Q11">
+      <c r="Q11" s="2">
         <v>23477</v>
       </c>
-      <c r="R11">
-        <v>0</v>
-      </c>
-      <c r="S11">
+      <c r="R11" s="2">
+        <v>0</v>
+      </c>
+      <c r="S11" s="2">
         <v>23</v>
       </c>
     </row>
@@ -1295,33 +1296,33 @@
         <v>0</v>
       </c>
       <c r="J12">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="K12">
         <v>0</v>
       </c>
       <c r="L12">
-        <v>9980</v>
+        <v>9993</v>
       </c>
       <c r="M12">
         <v>207</v>
       </c>
       <c r="N12">
-        <v>1062</v>
+        <v>1086</v>
       </c>
       <c r="O12">
-        <v>39510</v>
+        <v>39515</v>
       </c>
       <c r="P12">
         <v>66685</v>
       </c>
-      <c r="Q12">
+      <c r="Q12" s="2">
         <v>17786</v>
       </c>
-      <c r="R12">
-        <v>0</v>
-      </c>
-      <c r="S12">
+      <c r="R12" s="2">
+        <v>0</v>
+      </c>
+      <c r="S12" s="2">
         <v>3</v>
       </c>
     </row>
@@ -1374,13 +1375,13 @@
       <c r="P13">
         <v>56564</v>
       </c>
-      <c r="Q13">
+      <c r="Q13" s="2">
         <v>16237</v>
       </c>
-      <c r="R13">
-        <v>0</v>
-      </c>
-      <c r="S13">
+      <c r="R13" s="2">
+        <v>0</v>
+      </c>
+      <c r="S13" s="2">
         <v>106</v>
       </c>
     </row>
@@ -1413,33 +1414,33 @@
         <v>0</v>
       </c>
       <c r="J14">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="K14">
         <v>0</v>
       </c>
       <c r="L14">
-        <v>15163</v>
+        <v>15241</v>
       </c>
       <c r="M14">
         <v>1456</v>
       </c>
       <c r="N14">
-        <v>5688</v>
+        <v>5844</v>
       </c>
       <c r="O14">
-        <v>41771</v>
+        <v>43034</v>
       </c>
       <c r="P14">
         <v>77955</v>
       </c>
-      <c r="Q14">
+      <c r="Q14" s="2">
         <v>19716</v>
       </c>
-      <c r="R14">
-        <v>0</v>
-      </c>
-      <c r="S14">
+      <c r="R14" s="2">
+        <v>0</v>
+      </c>
+      <c r="S14" s="2">
         <v>174</v>
       </c>
     </row>
@@ -1492,13 +1493,13 @@
       <c r="P15">
         <v>67178</v>
       </c>
-      <c r="Q15">
+      <c r="Q15" s="2">
         <v>4859</v>
       </c>
-      <c r="R15">
-        <v>0</v>
-      </c>
-      <c r="S15">
+      <c r="R15" s="2">
+        <v>0</v>
+      </c>
+      <c r="S15" s="2">
         <v>50</v>
       </c>
     </row>
@@ -1551,13 +1552,13 @@
       <c r="P16">
         <v>71673</v>
       </c>
-      <c r="Q16">
+      <c r="Q16" s="2">
         <v>5197</v>
       </c>
-      <c r="R16">
-        <v>0</v>
-      </c>
-      <c r="S16">
+      <c r="R16" s="2">
+        <v>0</v>
+      </c>
+      <c r="S16" s="2">
         <v>47</v>
       </c>
     </row>
@@ -1610,13 +1611,13 @@
       <c r="P17">
         <v>65457</v>
       </c>
-      <c r="Q17">
+      <c r="Q17" s="2">
         <v>5417</v>
       </c>
-      <c r="R17">
-        <v>0</v>
-      </c>
-      <c r="S17">
+      <c r="R17" s="2">
+        <v>0</v>
+      </c>
+      <c r="S17" s="2">
         <v>105</v>
       </c>
     </row>
@@ -1669,13 +1670,13 @@
       <c r="P18">
         <v>71475</v>
       </c>
-      <c r="Q18">
+      <c r="Q18" s="2">
         <v>6819</v>
       </c>
-      <c r="R18">
-        <v>0</v>
-      </c>
-      <c r="S18">
+      <c r="R18" s="2">
+        <v>0</v>
+      </c>
+      <c r="S18" s="2">
         <v>32</v>
       </c>
     </row>
@@ -1720,21 +1721,21 @@
         <v>1</v>
       </c>
       <c r="N19">
-        <v>910</v>
+        <v>912</v>
       </c>
       <c r="O19">
-        <v>55580</v>
+        <v>55578</v>
       </c>
       <c r="P19">
         <v>106392</v>
       </c>
-      <c r="Q19">
+      <c r="Q19" s="2">
         <v>6135</v>
       </c>
-      <c r="R19">
-        <v>0</v>
-      </c>
-      <c r="S19">
+      <c r="R19" s="2">
+        <v>0</v>
+      </c>
+      <c r="S19" s="2">
         <v>36</v>
       </c>
     </row>
@@ -1787,13 +1788,13 @@
       <c r="P20">
         <v>75812</v>
       </c>
-      <c r="Q20">
+      <c r="Q20" s="2">
         <v>8984</v>
       </c>
-      <c r="R20">
-        <v>0</v>
-      </c>
-      <c r="S20">
+      <c r="R20" s="2">
+        <v>0</v>
+      </c>
+      <c r="S20" s="2">
         <v>71</v>
       </c>
     </row>
@@ -1846,13 +1847,13 @@
       <c r="P21">
         <v>62460</v>
       </c>
-      <c r="Q21">
+      <c r="Q21" s="2">
         <v>3868</v>
       </c>
-      <c r="R21">
-        <v>0</v>
-      </c>
-      <c r="S21">
+      <c r="R21" s="2">
+        <v>0</v>
+      </c>
+      <c r="S21" s="2">
         <v>0</v>
       </c>
     </row>
@@ -1905,13 +1906,13 @@
       <c r="P22">
         <v>64099</v>
       </c>
-      <c r="Q22">
+      <c r="Q22" s="2">
         <v>4848</v>
       </c>
-      <c r="R22">
-        <v>0</v>
-      </c>
-      <c r="S22">
+      <c r="R22" s="2">
+        <v>0</v>
+      </c>
+      <c r="S22" s="2">
         <v>0</v>
       </c>
     </row>
@@ -1964,13 +1965,13 @@
       <c r="P23">
         <v>57094</v>
       </c>
-      <c r="Q23">
+      <c r="Q23" s="2">
         <v>3541</v>
       </c>
-      <c r="R23">
-        <v>0</v>
-      </c>
-      <c r="S23">
+      <c r="R23" s="2">
+        <v>0</v>
+      </c>
+      <c r="S23" s="2">
         <v>28</v>
       </c>
     </row>
@@ -2023,13 +2024,13 @@
       <c r="P24">
         <v>65629</v>
       </c>
-      <c r="Q24">
+      <c r="Q24" s="2">
         <v>3492</v>
       </c>
-      <c r="R24">
-        <v>0</v>
-      </c>
-      <c r="S24">
+      <c r="R24" s="2">
+        <v>0</v>
+      </c>
+      <c r="S24" s="2">
         <v>0</v>
       </c>
     </row>
@@ -2082,13 +2083,13 @@
       <c r="P25">
         <v>57533</v>
       </c>
-      <c r="Q25">
+      <c r="Q25" s="2">
         <v>3231</v>
       </c>
-      <c r="R25">
-        <v>0</v>
-      </c>
-      <c r="S25">
+      <c r="R25" s="2">
+        <v>0</v>
+      </c>
+      <c r="S25" s="2">
         <v>13</v>
       </c>
     </row>
@@ -2141,13 +2142,13 @@
       <c r="P26">
         <v>66594</v>
       </c>
-      <c r="Q26">
+      <c r="Q26" s="2">
         <v>3333</v>
       </c>
-      <c r="R26">
-        <v>0</v>
-      </c>
-      <c r="S26">
+      <c r="R26" s="2">
+        <v>0</v>
+      </c>
+      <c r="S26" s="2">
         <v>2</v>
       </c>
     </row>
@@ -2200,13 +2201,13 @@
       <c r="P27">
         <v>73109</v>
       </c>
-      <c r="Q27">
+      <c r="Q27" s="2">
         <v>12669</v>
       </c>
-      <c r="R27">
-        <v>0</v>
-      </c>
-      <c r="S27">
+      <c r="R27" s="2">
+        <v>0</v>
+      </c>
+      <c r="S27" s="2">
         <v>0</v>
       </c>
     </row>
@@ -2259,13 +2260,13 @@
       <c r="P28">
         <v>80620</v>
       </c>
-      <c r="Q28">
+      <c r="Q28" s="2">
         <v>13995</v>
       </c>
-      <c r="R28">
-        <v>0</v>
-      </c>
-      <c r="S28">
+      <c r="R28" s="2">
+        <v>0</v>
+      </c>
+      <c r="S28" s="2">
         <v>127</v>
       </c>
     </row>
@@ -2318,13 +2319,13 @@
       <c r="P29">
         <v>83836</v>
       </c>
-      <c r="Q29">
+      <c r="Q29" s="2">
         <v>14229</v>
       </c>
-      <c r="R29">
-        <v>0</v>
-      </c>
-      <c r="S29">
+      <c r="R29" s="2">
+        <v>0</v>
+      </c>
+      <c r="S29" s="2">
         <v>22</v>
       </c>
     </row>
@@ -2377,13 +2378,13 @@
       <c r="P30">
         <v>86933</v>
       </c>
-      <c r="Q30">
+      <c r="Q30" s="2">
         <v>12564</v>
       </c>
-      <c r="R30">
-        <v>0</v>
-      </c>
-      <c r="S30">
+      <c r="R30" s="2">
+        <v>0</v>
+      </c>
+      <c r="S30" s="2">
         <v>8</v>
       </c>
     </row>
@@ -2436,13 +2437,13 @@
       <c r="P31">
         <v>81642</v>
       </c>
-      <c r="Q31">
+      <c r="Q31" s="2">
         <v>14581</v>
       </c>
-      <c r="R31">
-        <v>0</v>
-      </c>
-      <c r="S31">
+      <c r="R31" s="2">
+        <v>0</v>
+      </c>
+      <c r="S31" s="2">
         <v>39</v>
       </c>
     </row>
@@ -2495,13 +2496,13 @@
       <c r="P32">
         <v>74810</v>
       </c>
-      <c r="Q32">
+      <c r="Q32" s="2">
         <v>11379</v>
       </c>
-      <c r="R32">
-        <v>0</v>
-      </c>
-      <c r="S32">
+      <c r="R32" s="2">
+        <v>0</v>
+      </c>
+      <c r="S32" s="2">
         <v>0</v>
       </c>
     </row>
@@ -2534,7 +2535,7 @@
         <v>0</v>
       </c>
       <c r="J33">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="K33">
         <v>0</v>
@@ -2546,21 +2547,21 @@
         <v>296</v>
       </c>
       <c r="N33">
-        <v>1240</v>
+        <v>1269</v>
       </c>
       <c r="O33">
-        <v>38838</v>
+        <v>38922</v>
       </c>
       <c r="P33">
         <v>76969</v>
       </c>
-      <c r="Q33">
+      <c r="Q33" s="2">
         <v>6678</v>
       </c>
-      <c r="R33">
-        <v>0</v>
-      </c>
-      <c r="S33">
+      <c r="R33" s="2">
+        <v>0</v>
+      </c>
+      <c r="S33" s="2">
         <v>19</v>
       </c>
     </row>
@@ -2613,13 +2614,13 @@
       <c r="P34">
         <v>74624</v>
       </c>
-      <c r="Q34">
+      <c r="Q34" s="2">
         <v>7137</v>
       </c>
-      <c r="R34">
-        <v>0</v>
-      </c>
-      <c r="S34">
+      <c r="R34" s="2">
+        <v>0</v>
+      </c>
+      <c r="S34" s="2">
         <v>0</v>
       </c>
     </row>
@@ -2672,13 +2673,13 @@
       <c r="P35">
         <v>76465</v>
       </c>
-      <c r="Q35">
+      <c r="Q35" s="2">
         <v>8879</v>
       </c>
-      <c r="R35">
-        <v>0</v>
-      </c>
-      <c r="S35">
+      <c r="R35" s="2">
+        <v>0</v>
+      </c>
+      <c r="S35" s="2">
         <v>35</v>
       </c>
     </row>
@@ -2731,13 +2732,13 @@
       <c r="P36">
         <v>60419</v>
       </c>
-      <c r="Q36">
+      <c r="Q36" s="2">
         <v>3855</v>
       </c>
-      <c r="R36">
-        <v>0</v>
-      </c>
-      <c r="S36">
+      <c r="R36" s="2">
+        <v>0</v>
+      </c>
+      <c r="S36" s="2">
         <v>2</v>
       </c>
     </row>
@@ -2790,13 +2791,13 @@
       <c r="P37">
         <v>57832</v>
       </c>
-      <c r="Q37">
+      <c r="Q37" s="2">
         <v>4036</v>
       </c>
-      <c r="R37">
-        <v>0</v>
-      </c>
-      <c r="S37">
+      <c r="R37" s="2">
+        <v>0</v>
+      </c>
+      <c r="S37" s="2">
         <v>1</v>
       </c>
     </row>
@@ -2849,13 +2850,13 @@
       <c r="P38">
         <v>63038</v>
       </c>
-      <c r="Q38">
+      <c r="Q38" s="2">
         <v>5135</v>
       </c>
-      <c r="R38">
-        <v>0</v>
-      </c>
-      <c r="S38">
+      <c r="R38" s="2">
+        <v>0</v>
+      </c>
+      <c r="S38" s="2">
         <v>0</v>
       </c>
     </row>
@@ -2908,13 +2909,13 @@
       <c r="P39">
         <v>71133</v>
       </c>
-      <c r="Q39">
+      <c r="Q39" s="2">
         <v>5903</v>
       </c>
-      <c r="R39">
-        <v>0</v>
-      </c>
-      <c r="S39">
+      <c r="R39" s="2">
+        <v>0</v>
+      </c>
+      <c r="S39" s="2">
         <v>26</v>
       </c>
     </row>
@@ -2967,13 +2968,13 @@
       <c r="P40">
         <v>73242</v>
       </c>
-      <c r="Q40">
+      <c r="Q40" s="2">
         <v>3824</v>
       </c>
-      <c r="R40">
-        <v>0</v>
-      </c>
-      <c r="S40">
+      <c r="R40" s="2">
+        <v>0</v>
+      </c>
+      <c r="S40" s="2">
         <v>61</v>
       </c>
     </row>
@@ -3026,13 +3027,13 @@
       <c r="P41">
         <v>85251</v>
       </c>
-      <c r="Q41">
+      <c r="Q41" s="2">
         <v>6015</v>
       </c>
-      <c r="R41">
-        <v>0</v>
-      </c>
-      <c r="S41">
+      <c r="R41" s="2">
+        <v>0</v>
+      </c>
+      <c r="S41" s="2">
         <v>27</v>
       </c>
     </row>
@@ -3085,13 +3086,13 @@
       <c r="P42">
         <v>68615</v>
       </c>
-      <c r="Q42">
+      <c r="Q42" s="2">
         <v>4708</v>
       </c>
-      <c r="R42">
-        <v>0</v>
-      </c>
-      <c r="S42">
+      <c r="R42" s="2">
+        <v>0</v>
+      </c>
+      <c r="S42" s="2">
         <v>8</v>
       </c>
     </row>
@@ -3144,13 +3145,13 @@
       <c r="P43">
         <v>63012</v>
       </c>
-      <c r="Q43">
+      <c r="Q43" s="2">
         <v>5219</v>
       </c>
-      <c r="R43">
-        <v>0</v>
-      </c>
-      <c r="S43">
+      <c r="R43" s="2">
+        <v>0</v>
+      </c>
+      <c r="S43" s="2">
         <v>121</v>
       </c>
     </row>
@@ -3203,13 +3204,13 @@
       <c r="P44">
         <v>68393</v>
       </c>
-      <c r="Q44">
+      <c r="Q44" s="2">
         <v>7659</v>
       </c>
-      <c r="R44">
-        <v>0</v>
-      </c>
-      <c r="S44">
+      <c r="R44" s="2">
+        <v>0</v>
+      </c>
+      <c r="S44" s="2">
         <v>20</v>
       </c>
     </row>
@@ -3262,13 +3263,13 @@
       <c r="P45">
         <v>76287</v>
       </c>
-      <c r="Q45">
+      <c r="Q45" s="2">
         <v>6998</v>
       </c>
-      <c r="R45">
-        <v>0</v>
-      </c>
-      <c r="S45">
+      <c r="R45" s="2">
+        <v>0</v>
+      </c>
+      <c r="S45" s="2">
         <v>129</v>
       </c>
     </row>
@@ -3321,13 +3322,13 @@
       <c r="P46">
         <v>64160</v>
       </c>
-      <c r="Q46">
+      <c r="Q46" s="2">
         <v>7548</v>
       </c>
-      <c r="R46">
-        <v>0</v>
-      </c>
-      <c r="S46">
+      <c r="R46" s="2">
+        <v>0</v>
+      </c>
+      <c r="S46" s="2">
         <v>152</v>
       </c>
     </row>
@@ -3380,13 +3381,13 @@
       <c r="P47">
         <v>49875</v>
       </c>
-      <c r="Q47">
+      <c r="Q47" s="2">
         <v>5046</v>
       </c>
-      <c r="R47">
-        <v>0</v>
-      </c>
-      <c r="S47">
+      <c r="R47" s="2">
+        <v>0</v>
+      </c>
+      <c r="S47" s="2">
         <v>0</v>
       </c>
     </row>
@@ -3434,18 +3435,18 @@
         <v>254</v>
       </c>
       <c r="O48">
-        <v>19347</v>
+        <v>19350</v>
       </c>
       <c r="P48">
         <v>54142</v>
       </c>
-      <c r="Q48">
+      <c r="Q48" s="2">
         <v>4623</v>
       </c>
-      <c r="R48">
-        <v>0</v>
-      </c>
-      <c r="S48">
+      <c r="R48" s="2">
+        <v>0</v>
+      </c>
+      <c r="S48" s="2">
         <v>9</v>
       </c>
     </row>
@@ -3498,13 +3499,13 @@
       <c r="P49">
         <v>55376</v>
       </c>
-      <c r="Q49">
+      <c r="Q49" s="2">
         <v>5057</v>
       </c>
-      <c r="R49">
-        <v>0</v>
-      </c>
-      <c r="S49">
+      <c r="R49" s="2">
+        <v>0</v>
+      </c>
+      <c r="S49" s="2">
         <v>4</v>
       </c>
     </row>
@@ -3557,13 +3558,13 @@
       <c r="P50">
         <v>63298</v>
       </c>
-      <c r="Q50">
+      <c r="Q50" s="2">
         <v>7292</v>
       </c>
-      <c r="R50">
-        <v>0</v>
-      </c>
-      <c r="S50">
+      <c r="R50" s="2">
+        <v>0</v>
+      </c>
+      <c r="S50" s="2">
         <v>1</v>
       </c>
     </row>
@@ -3616,13 +3617,13 @@
       <c r="P51">
         <v>71754</v>
       </c>
-      <c r="Q51">
+      <c r="Q51" s="2">
         <v>7715</v>
       </c>
-      <c r="R51">
-        <v>0</v>
-      </c>
-      <c r="S51">
+      <c r="R51" s="2">
+        <v>0</v>
+      </c>
+      <c r="S51" s="2">
         <v>40</v>
       </c>
     </row>
@@ -3675,13 +3676,13 @@
       <c r="P52">
         <v>63987</v>
       </c>
-      <c r="Q52">
+      <c r="Q52" s="2">
         <v>5655</v>
       </c>
-      <c r="R52">
-        <v>0</v>
-      </c>
-      <c r="S52">
+      <c r="R52" s="2">
+        <v>0</v>
+      </c>
+      <c r="S52" s="2">
         <v>2</v>
       </c>
     </row>
@@ -3734,13 +3735,13 @@
       <c r="P53">
         <v>56306</v>
       </c>
-      <c r="Q53">
+      <c r="Q53" s="2">
         <v>6551</v>
       </c>
-      <c r="R53">
-        <v>0</v>
-      </c>
-      <c r="S53">
+      <c r="R53" s="2">
+        <v>0</v>
+      </c>
+      <c r="S53" s="2">
         <v>5</v>
       </c>
     </row>
@@ -3793,13 +3794,13 @@
       <c r="P54">
         <v>58440</v>
       </c>
-      <c r="Q54">
+      <c r="Q54" s="2">
         <v>7347</v>
       </c>
-      <c r="R54">
-        <v>0</v>
-      </c>
-      <c r="S54">
+      <c r="R54" s="2">
+        <v>0</v>
+      </c>
+      <c r="S54" s="2">
         <v>1</v>
       </c>
     </row>
@@ -3852,13 +3853,13 @@
       <c r="P55">
         <v>58215</v>
       </c>
-      <c r="Q55">
+      <c r="Q55" s="2">
         <v>5098</v>
       </c>
-      <c r="R55">
-        <v>0</v>
-      </c>
-      <c r="S55">
+      <c r="R55" s="2">
+        <v>0</v>
+      </c>
+      <c r="S55" s="2">
         <v>0</v>
       </c>
     </row>
@@ -3894,7 +3895,7 @@
         <v>3</v>
       </c>
       <c r="K56">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L56">
         <v>4088</v>
@@ -3911,13 +3912,13 @@
       <c r="P56">
         <v>47621</v>
       </c>
-      <c r="Q56">
+      <c r="Q56" s="2">
         <v>4882</v>
       </c>
-      <c r="R56">
-        <v>0</v>
-      </c>
-      <c r="S56">
+      <c r="R56" s="2">
+        <v>0</v>
+      </c>
+      <c r="S56" s="2">
         <v>30</v>
       </c>
     </row>
@@ -3970,13 +3971,13 @@
       <c r="P57">
         <v>61556</v>
       </c>
-      <c r="Q57">
+      <c r="Q57" s="2">
         <v>6870</v>
       </c>
-      <c r="R57">
-        <v>0</v>
-      </c>
-      <c r="S57">
+      <c r="R57" s="2">
+        <v>0</v>
+      </c>
+      <c r="S57" s="2">
         <v>0</v>
       </c>
     </row>
@@ -4029,13 +4030,13 @@
       <c r="P58">
         <v>57577</v>
       </c>
-      <c r="Q58">
+      <c r="Q58" s="2">
         <v>8884</v>
       </c>
-      <c r="R58">
-        <v>0</v>
-      </c>
-      <c r="S58">
+      <c r="R58" s="2">
+        <v>0</v>
+      </c>
+      <c r="S58" s="2">
         <v>64</v>
       </c>
     </row>
@@ -4088,13 +4089,13 @@
       <c r="P59">
         <v>60495</v>
       </c>
-      <c r="Q59">
+      <c r="Q59" s="2">
         <v>8028</v>
       </c>
-      <c r="R59">
-        <v>0</v>
-      </c>
-      <c r="S59">
+      <c r="R59" s="2">
+        <v>0</v>
+      </c>
+      <c r="S59" s="2">
         <v>27</v>
       </c>
     </row>
@@ -4147,13 +4148,13 @@
       <c r="P60">
         <v>70140</v>
       </c>
-      <c r="Q60">
+      <c r="Q60" s="2">
         <v>7415</v>
       </c>
-      <c r="R60">
-        <v>0</v>
-      </c>
-      <c r="S60">
+      <c r="R60" s="2">
+        <v>0</v>
+      </c>
+      <c r="S60" s="2">
         <v>32</v>
       </c>
     </row>
@@ -4206,13 +4207,13 @@
       <c r="P61">
         <v>55240</v>
       </c>
-      <c r="Q61">
+      <c r="Q61" s="2">
         <v>7927</v>
       </c>
-      <c r="R61">
+      <c r="R61" s="2">
         <v>1</v>
       </c>
-      <c r="S61">
+      <c r="S61" s="2">
         <v>268</v>
       </c>
     </row>
@@ -4265,13 +4266,13 @@
       <c r="P62">
         <v>51334</v>
       </c>
-      <c r="Q62">
+      <c r="Q62" s="2">
         <v>6917</v>
       </c>
-      <c r="R62">
-        <v>0</v>
-      </c>
-      <c r="S62">
+      <c r="R62" s="2">
+        <v>0</v>
+      </c>
+      <c r="S62" s="2">
         <v>100</v>
       </c>
     </row>
@@ -4324,13 +4325,13 @@
       <c r="P63">
         <v>68691</v>
       </c>
-      <c r="Q63">
+      <c r="Q63" s="2">
         <v>9766</v>
       </c>
-      <c r="R63">
-        <v>0</v>
-      </c>
-      <c r="S63">
+      <c r="R63" s="2">
+        <v>0</v>
+      </c>
+      <c r="S63" s="2">
         <v>153</v>
       </c>
     </row>
@@ -4383,13 +4384,13 @@
       <c r="P64">
         <v>60527</v>
       </c>
-      <c r="Q64">
+      <c r="Q64" s="2">
         <v>5985</v>
       </c>
-      <c r="R64">
-        <v>0</v>
-      </c>
-      <c r="S64">
+      <c r="R64" s="2">
+        <v>0</v>
+      </c>
+      <c r="S64" s="2">
         <v>101</v>
       </c>
     </row>
@@ -4442,13 +4443,13 @@
       <c r="P65">
         <v>58527</v>
       </c>
-      <c r="Q65">
+      <c r="Q65" s="2">
         <v>13282</v>
       </c>
-      <c r="R65">
-        <v>0</v>
-      </c>
-      <c r="S65">
+      <c r="R65" s="2">
+        <v>0</v>
+      </c>
+      <c r="S65" s="2">
         <v>138</v>
       </c>
     </row>
@@ -4501,13 +4502,13 @@
       <c r="P66">
         <v>93810</v>
       </c>
-      <c r="Q66">
+      <c r="Q66" s="2">
         <v>17742</v>
       </c>
-      <c r="R66">
-        <v>0</v>
-      </c>
-      <c r="S66">
+      <c r="R66" s="2">
+        <v>0</v>
+      </c>
+      <c r="S66" s="2">
         <v>52</v>
       </c>
     </row>
@@ -4560,13 +4561,13 @@
       <c r="P67">
         <v>78032</v>
       </c>
-      <c r="Q67">
+      <c r="Q67" s="2">
         <v>9807</v>
       </c>
-      <c r="R67">
-        <v>0</v>
-      </c>
-      <c r="S67">
+      <c r="R67" s="2">
+        <v>0</v>
+      </c>
+      <c r="S67" s="2">
         <v>116</v>
       </c>
     </row>
@@ -4619,13 +4620,13 @@
       <c r="P68">
         <v>71325</v>
       </c>
-      <c r="Q68">
+      <c r="Q68" s="2">
         <v>7850</v>
       </c>
-      <c r="R68">
-        <v>0</v>
-      </c>
-      <c r="S68">
+      <c r="R68" s="2">
+        <v>0</v>
+      </c>
+      <c r="S68" s="2">
         <v>26</v>
       </c>
     </row>
@@ -4678,13 +4679,13 @@
       <c r="P69">
         <v>36118</v>
       </c>
-      <c r="Q69">
+      <c r="Q69" s="2">
         <v>6528</v>
       </c>
-      <c r="R69">
-        <v>0</v>
-      </c>
-      <c r="S69">
+      <c r="R69" s="2">
+        <v>0</v>
+      </c>
+      <c r="S69" s="2">
         <v>47</v>
       </c>
     </row>
@@ -4737,13 +4738,13 @@
       <c r="P70">
         <v>42051</v>
       </c>
-      <c r="Q70">
+      <c r="Q70" s="2">
         <v>5798</v>
       </c>
-      <c r="R70">
-        <v>0</v>
-      </c>
-      <c r="S70">
+      <c r="R70" s="2">
+        <v>0</v>
+      </c>
+      <c r="S70" s="2">
         <v>29</v>
       </c>
     </row>
@@ -4796,13 +4797,13 @@
       <c r="P71">
         <v>49140</v>
       </c>
-      <c r="Q71">
+      <c r="Q71" s="2">
         <v>6782</v>
       </c>
-      <c r="R71">
-        <v>0</v>
-      </c>
-      <c r="S71">
+      <c r="R71" s="2">
+        <v>0</v>
+      </c>
+      <c r="S71" s="2">
         <v>235</v>
       </c>
     </row>
@@ -4855,13 +4856,13 @@
       <c r="P72">
         <v>85505</v>
       </c>
-      <c r="Q72">
+      <c r="Q72" s="2">
         <v>12340</v>
       </c>
-      <c r="R72">
-        <v>0</v>
-      </c>
-      <c r="S72">
+      <c r="R72" s="2">
+        <v>0</v>
+      </c>
+      <c r="S72" s="2">
         <v>79</v>
       </c>
     </row>
@@ -4914,13 +4915,13 @@
       <c r="P73">
         <v>67666</v>
       </c>
-      <c r="Q73">
+      <c r="Q73" s="2">
         <v>10010</v>
       </c>
-      <c r="R73">
-        <v>0</v>
-      </c>
-      <c r="S73">
+      <c r="R73" s="2">
+        <v>0</v>
+      </c>
+      <c r="S73" s="2">
         <v>74</v>
       </c>
     </row>
@@ -4951,36 +4952,38 @@
         <v>0</v>
       </c>
       <c r="J74">
-        <v>363</v>
+        <v>304</v>
       </c>
       <c r="K74">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L74">
-        <v>625082</v>
+        <v>625237</v>
       </c>
       <c r="M74">
         <v>8174</v>
       </c>
       <c r="N74">
-        <v>96539</v>
+        <v>96756</v>
       </c>
       <c r="O74">
-        <v>2325834</v>
+        <v>2330031</v>
       </c>
       <c r="P74">
         <v>4701901</v>
       </c>
-      <c r="Q74">
+      <c r="Q74" s="2">
         <v>626236</v>
       </c>
-      <c r="R74">
+      <c r="R74" s="2">
         <v>1</v>
       </c>
-      <c r="S74">
+      <c r="S74" s="2">
         <v>3445</v>
       </c>
     </row>
+    <row r="75" spans="1:19" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="76" spans="1:19" ht="15.75" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="12">
     <mergeCell ref="A74:B74"/>

--- a/Notice.xlsx
+++ b/Notice.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Downloads\New folder (13)\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{105205DE-FFB3-4376-91BE-8A5F1B9C0663}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8D7569F-DAD1-4B43-BCCC-4626D41D38A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -304,7 +304,7 @@
     <t>No Action Required</t>
   </si>
   <si>
-    <t>Notice &amp; Hearing Report Last Updated On : 14-09-2026 07:56:54</t>
+    <t>Notice &amp; Hearing Report Last Updated On : 15-09-2026 13:56:50</t>
   </si>
 </sst>
 </file>
@@ -340,8 +340,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
@@ -683,10 +682,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:S76"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:S74"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>94</v>
       </c>
@@ -707,7 +706,7 @@
       <c r="P1" s="1"/>
       <c r="Q1" s="1"/>
     </row>
-    <row r="2" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -748,7 +747,7 @@
       <c r="R2" s="1"/>
       <c r="S2" s="1"/>
     </row>
-    <row r="3" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A3" s="1"/>
       <c r="B3" s="1"/>
       <c r="C3" s="1"/>
@@ -785,17 +784,17 @@
       <c r="P3" t="s">
         <v>18</v>
       </c>
-      <c r="Q3" s="2" t="s">
+      <c r="Q3" t="s">
         <v>91</v>
       </c>
-      <c r="R3" s="2" t="s">
+      <c r="R3" t="s">
         <v>92</v>
       </c>
-      <c r="S3" s="2" t="s">
+      <c r="S3" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="4" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>1</v>
       </c>
@@ -844,17 +843,17 @@
       <c r="P4">
         <v>53812</v>
       </c>
-      <c r="Q4" s="2">
+      <c r="Q4">
         <v>12212</v>
       </c>
-      <c r="R4" s="2">
-        <v>0</v>
-      </c>
-      <c r="S4" s="2">
+      <c r="R4">
+        <v>0</v>
+      </c>
+      <c r="S4">
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>2</v>
       </c>
@@ -903,17 +902,17 @@
       <c r="P5">
         <v>74848</v>
       </c>
-      <c r="Q5" s="2">
+      <c r="Q5">
         <v>16108</v>
       </c>
-      <c r="R5" s="2">
-        <v>0</v>
-      </c>
-      <c r="S5" s="2">
+      <c r="R5">
+        <v>0</v>
+      </c>
+      <c r="S5">
         <v>30</v>
       </c>
     </row>
-    <row r="6" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>3</v>
       </c>
@@ -942,37 +941,37 @@
         <v>0</v>
       </c>
       <c r="J6">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="K6">
         <v>0</v>
       </c>
       <c r="L6">
-        <v>6035</v>
+        <v>6043</v>
       </c>
       <c r="M6">
         <v>201</v>
       </c>
       <c r="N6">
-        <v>1810</v>
+        <v>1827</v>
       </c>
       <c r="O6">
-        <v>37296</v>
+        <v>37304</v>
       </c>
       <c r="P6">
         <v>71989</v>
       </c>
-      <c r="Q6" s="2">
+      <c r="Q6">
         <v>17830</v>
       </c>
-      <c r="R6" s="2">
-        <v>0</v>
-      </c>
-      <c r="S6" s="2">
+      <c r="R6">
+        <v>0</v>
+      </c>
+      <c r="S6">
         <v>54</v>
       </c>
     </row>
-    <row r="7" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>4</v>
       </c>
@@ -1001,7 +1000,7 @@
         <v>0</v>
       </c>
       <c r="J7">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K7">
         <v>0</v>
@@ -1021,17 +1020,17 @@
       <c r="P7">
         <v>77581</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="Q7">
         <v>20511</v>
       </c>
-      <c r="R7" s="2">
-        <v>0</v>
-      </c>
-      <c r="S7" s="2">
+      <c r="R7">
+        <v>0</v>
+      </c>
+      <c r="S7">
         <v>8</v>
       </c>
     </row>
-    <row r="8" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>5</v>
       </c>
@@ -1075,22 +1074,22 @@
         <v>1874</v>
       </c>
       <c r="O8">
-        <v>37746</v>
+        <v>38041</v>
       </c>
       <c r="P8">
         <v>73458</v>
       </c>
-      <c r="Q8" s="2">
+      <c r="Q8">
         <v>20788</v>
       </c>
-      <c r="R8" s="2">
-        <v>0</v>
-      </c>
-      <c r="S8" s="2">
+      <c r="R8">
+        <v>0</v>
+      </c>
+      <c r="S8">
         <v>110</v>
       </c>
     </row>
-    <row r="9" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>6</v>
       </c>
@@ -1139,17 +1138,17 @@
       <c r="P9">
         <v>72913</v>
       </c>
-      <c r="Q9" s="2">
+      <c r="Q9">
         <v>18141</v>
       </c>
-      <c r="R9" s="2">
-        <v>0</v>
-      </c>
-      <c r="S9" s="2">
+      <c r="R9">
+        <v>0</v>
+      </c>
+      <c r="S9">
         <v>110</v>
       </c>
     </row>
-    <row r="10" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>7</v>
       </c>
@@ -1198,17 +1197,17 @@
       <c r="P10">
         <v>53124</v>
       </c>
-      <c r="Q10" s="2">
+      <c r="Q10">
         <v>9498</v>
       </c>
-      <c r="R10" s="2">
-        <v>0</v>
-      </c>
-      <c r="S10" s="2">
+      <c r="R10">
+        <v>0</v>
+      </c>
+      <c r="S10">
         <v>2</v>
       </c>
     </row>
-    <row r="11" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>8</v>
       </c>
@@ -1257,17 +1256,17 @@
       <c r="P11">
         <v>84438</v>
       </c>
-      <c r="Q11" s="2">
+      <c r="Q11">
         <v>23477</v>
       </c>
-      <c r="R11" s="2">
-        <v>0</v>
-      </c>
-      <c r="S11" s="2">
+      <c r="R11">
+        <v>0</v>
+      </c>
+      <c r="S11">
         <v>23</v>
       </c>
     </row>
-    <row r="12" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>9</v>
       </c>
@@ -1296,37 +1295,37 @@
         <v>0</v>
       </c>
       <c r="J12">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="K12">
         <v>0</v>
       </c>
       <c r="L12">
-        <v>9993</v>
+        <v>10051</v>
       </c>
       <c r="M12">
         <v>207</v>
       </c>
       <c r="N12">
-        <v>1086</v>
+        <v>1133</v>
       </c>
       <c r="O12">
-        <v>39515</v>
+        <v>39527</v>
       </c>
       <c r="P12">
         <v>66685</v>
       </c>
-      <c r="Q12" s="2">
+      <c r="Q12">
         <v>17786</v>
       </c>
-      <c r="R12" s="2">
-        <v>0</v>
-      </c>
-      <c r="S12" s="2">
+      <c r="R12">
+        <v>0</v>
+      </c>
+      <c r="S12">
         <v>3</v>
       </c>
     </row>
-    <row r="13" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>10</v>
       </c>
@@ -1375,17 +1374,17 @@
       <c r="P13">
         <v>56564</v>
       </c>
-      <c r="Q13" s="2">
+      <c r="Q13">
         <v>16237</v>
       </c>
-      <c r="R13" s="2">
-        <v>0</v>
-      </c>
-      <c r="S13" s="2">
+      <c r="R13">
+        <v>0</v>
+      </c>
+      <c r="S13">
         <v>106</v>
       </c>
     </row>
-    <row r="14" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>11</v>
       </c>
@@ -1414,7 +1413,7 @@
         <v>0</v>
       </c>
       <c r="J14">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="K14">
         <v>0</v>
@@ -1429,22 +1428,22 @@
         <v>5844</v>
       </c>
       <c r="O14">
-        <v>43034</v>
+        <v>43059</v>
       </c>
       <c r="P14">
         <v>77955</v>
       </c>
-      <c r="Q14" s="2">
+      <c r="Q14">
         <v>19716</v>
       </c>
-      <c r="R14" s="2">
-        <v>0</v>
-      </c>
-      <c r="S14" s="2">
+      <c r="R14">
+        <v>0</v>
+      </c>
+      <c r="S14">
         <v>174</v>
       </c>
     </row>
-    <row r="15" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>12</v>
       </c>
@@ -1493,17 +1492,17 @@
       <c r="P15">
         <v>67178</v>
       </c>
-      <c r="Q15" s="2">
+      <c r="Q15">
         <v>4859</v>
       </c>
-      <c r="R15" s="2">
-        <v>0</v>
-      </c>
-      <c r="S15" s="2">
+      <c r="R15">
+        <v>0</v>
+      </c>
+      <c r="S15">
         <v>50</v>
       </c>
     </row>
-    <row r="16" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>13</v>
       </c>
@@ -1552,17 +1551,17 @@
       <c r="P16">
         <v>71673</v>
       </c>
-      <c r="Q16" s="2">
+      <c r="Q16">
         <v>5197</v>
       </c>
-      <c r="R16" s="2">
-        <v>0</v>
-      </c>
-      <c r="S16" s="2">
+      <c r="R16">
+        <v>0</v>
+      </c>
+      <c r="S16">
         <v>47</v>
       </c>
     </row>
-    <row r="17" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>14</v>
       </c>
@@ -1611,17 +1610,17 @@
       <c r="P17">
         <v>65457</v>
       </c>
-      <c r="Q17" s="2">
+      <c r="Q17">
         <v>5417</v>
       </c>
-      <c r="R17" s="2">
-        <v>0</v>
-      </c>
-      <c r="S17" s="2">
+      <c r="R17">
+        <v>0</v>
+      </c>
+      <c r="S17">
         <v>105</v>
       </c>
     </row>
-    <row r="18" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>15</v>
       </c>
@@ -1670,17 +1669,17 @@
       <c r="P18">
         <v>71475</v>
       </c>
-      <c r="Q18" s="2">
+      <c r="Q18">
         <v>6819</v>
       </c>
-      <c r="R18" s="2">
-        <v>0</v>
-      </c>
-      <c r="S18" s="2">
+      <c r="R18">
+        <v>0</v>
+      </c>
+      <c r="S18">
         <v>32</v>
       </c>
     </row>
-    <row r="19" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>16</v>
       </c>
@@ -1729,17 +1728,17 @@
       <c r="P19">
         <v>106392</v>
       </c>
-      <c r="Q19" s="2">
+      <c r="Q19">
         <v>6135</v>
       </c>
-      <c r="R19" s="2">
-        <v>0</v>
-      </c>
-      <c r="S19" s="2">
+      <c r="R19">
+        <v>0</v>
+      </c>
+      <c r="S19">
         <v>36</v>
       </c>
     </row>
-    <row r="20" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>17</v>
       </c>
@@ -1788,17 +1787,17 @@
       <c r="P20">
         <v>75812</v>
       </c>
-      <c r="Q20" s="2">
+      <c r="Q20">
         <v>8984</v>
       </c>
-      <c r="R20" s="2">
-        <v>0</v>
-      </c>
-      <c r="S20" s="2">
+      <c r="R20">
+        <v>0</v>
+      </c>
+      <c r="S20">
         <v>71</v>
       </c>
     </row>
-    <row r="21" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>18</v>
       </c>
@@ -1847,17 +1846,17 @@
       <c r="P21">
         <v>62460</v>
       </c>
-      <c r="Q21" s="2">
+      <c r="Q21">
         <v>3868</v>
       </c>
-      <c r="R21" s="2">
-        <v>0</v>
-      </c>
-      <c r="S21" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="R21">
+        <v>0</v>
+      </c>
+      <c r="S21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>19</v>
       </c>
@@ -1906,17 +1905,17 @@
       <c r="P22">
         <v>64099</v>
       </c>
-      <c r="Q22" s="2">
+      <c r="Q22">
         <v>4848</v>
       </c>
-      <c r="R22" s="2">
-        <v>0</v>
-      </c>
-      <c r="S22" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="R22">
+        <v>0</v>
+      </c>
+      <c r="S22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>20</v>
       </c>
@@ -1965,17 +1964,17 @@
       <c r="P23">
         <v>57094</v>
       </c>
-      <c r="Q23" s="2">
+      <c r="Q23">
         <v>3541</v>
       </c>
-      <c r="R23" s="2">
-        <v>0</v>
-      </c>
-      <c r="S23" s="2">
+      <c r="R23">
+        <v>0</v>
+      </c>
+      <c r="S23">
         <v>28</v>
       </c>
     </row>
-    <row r="24" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>21</v>
       </c>
@@ -2024,17 +2023,17 @@
       <c r="P24">
         <v>65629</v>
       </c>
-      <c r="Q24" s="2">
+      <c r="Q24">
         <v>3492</v>
       </c>
-      <c r="R24" s="2">
-        <v>0</v>
-      </c>
-      <c r="S24" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="R24">
+        <v>0</v>
+      </c>
+      <c r="S24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>22</v>
       </c>
@@ -2083,17 +2082,17 @@
       <c r="P25">
         <v>57533</v>
       </c>
-      <c r="Q25" s="2">
+      <c r="Q25">
         <v>3231</v>
       </c>
-      <c r="R25" s="2">
-        <v>0</v>
-      </c>
-      <c r="S25" s="2">
+      <c r="R25">
+        <v>0</v>
+      </c>
+      <c r="S25">
         <v>13</v>
       </c>
     </row>
-    <row r="26" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>23</v>
       </c>
@@ -2142,17 +2141,17 @@
       <c r="P26">
         <v>66594</v>
       </c>
-      <c r="Q26" s="2">
+      <c r="Q26">
         <v>3333</v>
       </c>
-      <c r="R26" s="2">
-        <v>0</v>
-      </c>
-      <c r="S26" s="2">
+      <c r="R26">
+        <v>0</v>
+      </c>
+      <c r="S26">
         <v>2</v>
       </c>
     </row>
-    <row r="27" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>24</v>
       </c>
@@ -2193,25 +2192,25 @@
         <v>215</v>
       </c>
       <c r="N27">
-        <v>3256</v>
+        <v>3278</v>
       </c>
       <c r="O27">
-        <v>41027</v>
+        <v>41008</v>
       </c>
       <c r="P27">
         <v>73109</v>
       </c>
-      <c r="Q27" s="2">
+      <c r="Q27">
         <v>12669</v>
       </c>
-      <c r="R27" s="2">
-        <v>0</v>
-      </c>
-      <c r="S27" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="R27">
+        <v>0</v>
+      </c>
+      <c r="S27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>25</v>
       </c>
@@ -2252,7 +2251,7 @@
         <v>856</v>
       </c>
       <c r="N28">
-        <v>3478</v>
+        <v>3525</v>
       </c>
       <c r="O28">
         <v>50838</v>
@@ -2260,17 +2259,17 @@
       <c r="P28">
         <v>80620</v>
       </c>
-      <c r="Q28" s="2">
+      <c r="Q28">
         <v>13995</v>
       </c>
-      <c r="R28" s="2">
-        <v>0</v>
-      </c>
-      <c r="S28" s="2">
+      <c r="R28">
+        <v>0</v>
+      </c>
+      <c r="S28">
         <v>127</v>
       </c>
     </row>
-    <row r="29" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>26</v>
       </c>
@@ -2319,17 +2318,17 @@
       <c r="P29">
         <v>83836</v>
       </c>
-      <c r="Q29" s="2">
+      <c r="Q29">
         <v>14229</v>
       </c>
-      <c r="R29" s="2">
-        <v>0</v>
-      </c>
-      <c r="S29" s="2">
+      <c r="R29">
+        <v>0</v>
+      </c>
+      <c r="S29">
         <v>22</v>
       </c>
     </row>
-    <row r="30" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>27</v>
       </c>
@@ -2378,17 +2377,17 @@
       <c r="P30">
         <v>86933</v>
       </c>
-      <c r="Q30" s="2">
+      <c r="Q30">
         <v>12564</v>
       </c>
-      <c r="R30" s="2">
-        <v>0</v>
-      </c>
-      <c r="S30" s="2">
+      <c r="R30">
+        <v>0</v>
+      </c>
+      <c r="S30">
         <v>8</v>
       </c>
     </row>
-    <row r="31" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>28</v>
       </c>
@@ -2437,17 +2436,17 @@
       <c r="P31">
         <v>81642</v>
       </c>
-      <c r="Q31" s="2">
+      <c r="Q31">
         <v>14581</v>
       </c>
-      <c r="R31" s="2">
-        <v>0</v>
-      </c>
-      <c r="S31" s="2">
+      <c r="R31">
+        <v>0</v>
+      </c>
+      <c r="S31">
         <v>39</v>
       </c>
     </row>
-    <row r="32" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>29</v>
       </c>
@@ -2488,25 +2487,25 @@
         <v>316</v>
       </c>
       <c r="N32">
-        <v>4377</v>
+        <v>4391</v>
       </c>
       <c r="O32">
-        <v>42336</v>
+        <v>42337</v>
       </c>
       <c r="P32">
         <v>74810</v>
       </c>
-      <c r="Q32" s="2">
+      <c r="Q32">
         <v>11379</v>
       </c>
-      <c r="R32" s="2">
-        <v>0</v>
-      </c>
-      <c r="S32" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="R32">
+        <v>0</v>
+      </c>
+      <c r="S32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>30</v>
       </c>
@@ -2535,37 +2534,37 @@
         <v>0</v>
       </c>
       <c r="J33">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="K33">
         <v>0</v>
       </c>
       <c r="L33">
-        <v>5095</v>
+        <v>5113</v>
       </c>
       <c r="M33">
-        <v>296</v>
+        <v>311</v>
       </c>
       <c r="N33">
-        <v>1269</v>
+        <v>1272</v>
       </c>
       <c r="O33">
-        <v>38922</v>
+        <v>38944</v>
       </c>
       <c r="P33">
         <v>76969</v>
       </c>
-      <c r="Q33" s="2">
+      <c r="Q33">
         <v>6678</v>
       </c>
-      <c r="R33" s="2">
-        <v>0</v>
-      </c>
-      <c r="S33" s="2">
+      <c r="R33">
+        <v>0</v>
+      </c>
+      <c r="S33">
         <v>19</v>
       </c>
     </row>
-    <row r="34" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>31</v>
       </c>
@@ -2594,37 +2593,37 @@
         <v>0</v>
       </c>
       <c r="J34">
-        <v>267</v>
+        <v>0</v>
       </c>
       <c r="K34">
         <v>0</v>
       </c>
       <c r="L34">
-        <v>12300</v>
+        <v>12439</v>
       </c>
       <c r="M34">
-        <v>384</v>
+        <v>513</v>
       </c>
       <c r="N34">
         <v>1363</v>
       </c>
       <c r="O34">
-        <v>34910</v>
+        <v>35181</v>
       </c>
       <c r="P34">
         <v>74624</v>
       </c>
-      <c r="Q34" s="2">
+      <c r="Q34">
         <v>7137</v>
       </c>
-      <c r="R34" s="2">
-        <v>0</v>
-      </c>
-      <c r="S34" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="R34">
+        <v>0</v>
+      </c>
+      <c r="S34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>32</v>
       </c>
@@ -2665,25 +2664,25 @@
         <v>271</v>
       </c>
       <c r="N35">
-        <v>1101</v>
+        <v>1129</v>
       </c>
       <c r="O35">
         <v>32436</v>
       </c>
       <c r="P35">
-        <v>76465</v>
-      </c>
-      <c r="Q35" s="2">
+        <v>76464</v>
+      </c>
+      <c r="Q35">
         <v>8879</v>
       </c>
-      <c r="R35" s="2">
-        <v>0</v>
-      </c>
-      <c r="S35" s="2">
+      <c r="R35">
+        <v>0</v>
+      </c>
+      <c r="S35">
         <v>35</v>
       </c>
     </row>
-    <row r="36" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>33</v>
       </c>
@@ -2732,17 +2731,17 @@
       <c r="P36">
         <v>60419</v>
       </c>
-      <c r="Q36" s="2">
+      <c r="Q36">
         <v>3855</v>
       </c>
-      <c r="R36" s="2">
-        <v>0</v>
-      </c>
-      <c r="S36" s="2">
+      <c r="R36">
+        <v>0</v>
+      </c>
+      <c r="S36">
         <v>2</v>
       </c>
     </row>
-    <row r="37" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>34</v>
       </c>
@@ -2791,17 +2790,17 @@
       <c r="P37">
         <v>57832</v>
       </c>
-      <c r="Q37" s="2">
+      <c r="Q37">
         <v>4036</v>
       </c>
-      <c r="R37" s="2">
-        <v>0</v>
-      </c>
-      <c r="S37" s="2">
+      <c r="R37">
+        <v>0</v>
+      </c>
+      <c r="S37">
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>35</v>
       </c>
@@ -2850,17 +2849,17 @@
       <c r="P38">
         <v>63038</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="Q38">
         <v>5135</v>
       </c>
-      <c r="R38" s="2">
-        <v>0</v>
-      </c>
-      <c r="S38" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="39" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="R38">
+        <v>0</v>
+      </c>
+      <c r="S38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>36</v>
       </c>
@@ -2909,17 +2908,17 @@
       <c r="P39">
         <v>71133</v>
       </c>
-      <c r="Q39" s="2">
+      <c r="Q39">
         <v>5903</v>
       </c>
-      <c r="R39" s="2">
-        <v>0</v>
-      </c>
-      <c r="S39" s="2">
+      <c r="R39">
+        <v>0</v>
+      </c>
+      <c r="S39">
         <v>26</v>
       </c>
     </row>
-    <row r="40" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>37</v>
       </c>
@@ -2968,17 +2967,17 @@
       <c r="P40">
         <v>73242</v>
       </c>
-      <c r="Q40" s="2">
+      <c r="Q40">
         <v>3824</v>
       </c>
-      <c r="R40" s="2">
-        <v>0</v>
-      </c>
-      <c r="S40" s="2">
+      <c r="R40">
+        <v>0</v>
+      </c>
+      <c r="S40">
         <v>61</v>
       </c>
     </row>
-    <row r="41" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>38</v>
       </c>
@@ -3027,17 +3026,17 @@
       <c r="P41">
         <v>85251</v>
       </c>
-      <c r="Q41" s="2">
+      <c r="Q41">
         <v>6015</v>
       </c>
-      <c r="R41" s="2">
-        <v>0</v>
-      </c>
-      <c r="S41" s="2">
+      <c r="R41">
+        <v>0</v>
+      </c>
+      <c r="S41">
         <v>27</v>
       </c>
     </row>
-    <row r="42" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>39</v>
       </c>
@@ -3086,17 +3085,17 @@
       <c r="P42">
         <v>68615</v>
       </c>
-      <c r="Q42" s="2">
+      <c r="Q42">
         <v>4708</v>
       </c>
-      <c r="R42" s="2">
-        <v>0</v>
-      </c>
-      <c r="S42" s="2">
+      <c r="R42">
+        <v>0</v>
+      </c>
+      <c r="S42">
         <v>8</v>
       </c>
     </row>
-    <row r="43" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>40</v>
       </c>
@@ -3145,17 +3144,17 @@
       <c r="P43">
         <v>63012</v>
       </c>
-      <c r="Q43" s="2">
+      <c r="Q43">
         <v>5219</v>
       </c>
-      <c r="R43" s="2">
-        <v>0</v>
-      </c>
-      <c r="S43" s="2">
+      <c r="R43">
+        <v>0</v>
+      </c>
+      <c r="S43">
         <v>121</v>
       </c>
     </row>
-    <row r="44" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A44">
         <v>41</v>
       </c>
@@ -3204,17 +3203,17 @@
       <c r="P44">
         <v>68393</v>
       </c>
-      <c r="Q44" s="2">
+      <c r="Q44">
         <v>7659</v>
       </c>
-      <c r="R44" s="2">
-        <v>0</v>
-      </c>
-      <c r="S44" s="2">
+      <c r="R44">
+        <v>0</v>
+      </c>
+      <c r="S44">
         <v>20</v>
       </c>
     </row>
-    <row r="45" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A45">
         <v>42</v>
       </c>
@@ -3263,17 +3262,17 @@
       <c r="P45">
         <v>76287</v>
       </c>
-      <c r="Q45" s="2">
+      <c r="Q45">
         <v>6998</v>
       </c>
-      <c r="R45" s="2">
-        <v>0</v>
-      </c>
-      <c r="S45" s="2">
+      <c r="R45">
+        <v>0</v>
+      </c>
+      <c r="S45">
         <v>129</v>
       </c>
     </row>
-    <row r="46" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A46">
         <v>43</v>
       </c>
@@ -3322,17 +3321,17 @@
       <c r="P46">
         <v>64160</v>
       </c>
-      <c r="Q46" s="2">
+      <c r="Q46">
         <v>7548</v>
       </c>
-      <c r="R46" s="2">
-        <v>0</v>
-      </c>
-      <c r="S46" s="2">
+      <c r="R46">
+        <v>0</v>
+      </c>
+      <c r="S46">
         <v>152</v>
       </c>
     </row>
-    <row r="47" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A47">
         <v>44</v>
       </c>
@@ -3381,17 +3380,17 @@
       <c r="P47">
         <v>49875</v>
       </c>
-      <c r="Q47" s="2">
+      <c r="Q47">
         <v>5046</v>
       </c>
-      <c r="R47" s="2">
-        <v>0</v>
-      </c>
-      <c r="S47" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="48" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="R47">
+        <v>0</v>
+      </c>
+      <c r="S47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A48">
         <v>45</v>
       </c>
@@ -3440,17 +3439,17 @@
       <c r="P48">
         <v>54142</v>
       </c>
-      <c r="Q48" s="2">
+      <c r="Q48">
         <v>4623</v>
       </c>
-      <c r="R48" s="2">
-        <v>0</v>
-      </c>
-      <c r="S48" s="2">
+      <c r="R48">
+        <v>0</v>
+      </c>
+      <c r="S48">
         <v>9</v>
       </c>
     </row>
-    <row r="49" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A49">
         <v>46</v>
       </c>
@@ -3499,17 +3498,17 @@
       <c r="P49">
         <v>55376</v>
       </c>
-      <c r="Q49" s="2">
+      <c r="Q49">
         <v>5057</v>
       </c>
-      <c r="R49" s="2">
-        <v>0</v>
-      </c>
-      <c r="S49" s="2">
+      <c r="R49">
+        <v>0</v>
+      </c>
+      <c r="S49">
         <v>4</v>
       </c>
     </row>
-    <row r="50" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A50">
         <v>47</v>
       </c>
@@ -3558,17 +3557,17 @@
       <c r="P50">
         <v>63298</v>
       </c>
-      <c r="Q50" s="2">
+      <c r="Q50">
         <v>7292</v>
       </c>
-      <c r="R50" s="2">
-        <v>0</v>
-      </c>
-      <c r="S50" s="2">
+      <c r="R50">
+        <v>0</v>
+      </c>
+      <c r="S50">
         <v>1</v>
       </c>
     </row>
-    <row r="51" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A51">
         <v>48</v>
       </c>
@@ -3617,17 +3616,17 @@
       <c r="P51">
         <v>71754</v>
       </c>
-      <c r="Q51" s="2">
+      <c r="Q51">
         <v>7715</v>
       </c>
-      <c r="R51" s="2">
-        <v>0</v>
-      </c>
-      <c r="S51" s="2">
+      <c r="R51">
+        <v>0</v>
+      </c>
+      <c r="S51">
         <v>40</v>
       </c>
     </row>
-    <row r="52" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A52">
         <v>49</v>
       </c>
@@ -3676,17 +3675,17 @@
       <c r="P52">
         <v>63987</v>
       </c>
-      <c r="Q52" s="2">
+      <c r="Q52">
         <v>5655</v>
       </c>
-      <c r="R52" s="2">
-        <v>0</v>
-      </c>
-      <c r="S52" s="2">
+      <c r="R52">
+        <v>0</v>
+      </c>
+      <c r="S52">
         <v>2</v>
       </c>
     </row>
-    <row r="53" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A53">
         <v>50</v>
       </c>
@@ -3735,17 +3734,17 @@
       <c r="P53">
         <v>56306</v>
       </c>
-      <c r="Q53" s="2">
+      <c r="Q53">
         <v>6551</v>
       </c>
-      <c r="R53" s="2">
-        <v>0</v>
-      </c>
-      <c r="S53" s="2">
+      <c r="R53">
+        <v>0</v>
+      </c>
+      <c r="S53">
         <v>5</v>
       </c>
     </row>
-    <row r="54" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A54">
         <v>51</v>
       </c>
@@ -3794,17 +3793,17 @@
       <c r="P54">
         <v>58440</v>
       </c>
-      <c r="Q54" s="2">
+      <c r="Q54">
         <v>7347</v>
       </c>
-      <c r="R54" s="2">
-        <v>0</v>
-      </c>
-      <c r="S54" s="2">
+      <c r="R54">
+        <v>0</v>
+      </c>
+      <c r="S54">
         <v>1</v>
       </c>
     </row>
-    <row r="55" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A55">
         <v>52</v>
       </c>
@@ -3833,13 +3832,13 @@
         <v>0</v>
       </c>
       <c r="J55">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K55">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L55">
-        <v>2105</v>
+        <v>2106</v>
       </c>
       <c r="M55">
         <v>1</v>
@@ -3848,22 +3847,22 @@
         <v>129</v>
       </c>
       <c r="O55">
-        <v>15889</v>
+        <v>15890</v>
       </c>
       <c r="P55">
         <v>58215</v>
       </c>
-      <c r="Q55" s="2">
+      <c r="Q55">
         <v>5098</v>
       </c>
-      <c r="R55" s="2">
-        <v>0</v>
-      </c>
-      <c r="S55" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="56" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="R55">
+        <v>0</v>
+      </c>
+      <c r="S55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A56">
         <v>53</v>
       </c>
@@ -3892,13 +3891,13 @@
         <v>0</v>
       </c>
       <c r="J56">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K56">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L56">
-        <v>4088</v>
+        <v>4090</v>
       </c>
       <c r="M56">
         <v>3</v>
@@ -3907,22 +3906,22 @@
         <v>444</v>
       </c>
       <c r="O56">
-        <v>18802</v>
+        <v>18804</v>
       </c>
       <c r="P56">
         <v>47621</v>
       </c>
-      <c r="Q56" s="2">
+      <c r="Q56">
         <v>4882</v>
       </c>
-      <c r="R56" s="2">
-        <v>0</v>
-      </c>
-      <c r="S56" s="2">
+      <c r="R56">
+        <v>0</v>
+      </c>
+      <c r="S56">
         <v>30</v>
       </c>
     </row>
-    <row r="57" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A57">
         <v>54</v>
       </c>
@@ -3971,17 +3970,17 @@
       <c r="P57">
         <v>61556</v>
       </c>
-      <c r="Q57" s="2">
+      <c r="Q57">
         <v>6870</v>
       </c>
-      <c r="R57" s="2">
-        <v>0</v>
-      </c>
-      <c r="S57" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="58" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="R57">
+        <v>0</v>
+      </c>
+      <c r="S57">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A58">
         <v>55</v>
       </c>
@@ -4030,17 +4029,17 @@
       <c r="P58">
         <v>57577</v>
       </c>
-      <c r="Q58" s="2">
+      <c r="Q58">
         <v>8884</v>
       </c>
-      <c r="R58" s="2">
-        <v>0</v>
-      </c>
-      <c r="S58" s="2">
+      <c r="R58">
+        <v>0</v>
+      </c>
+      <c r="S58">
         <v>64</v>
       </c>
     </row>
-    <row r="59" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A59">
         <v>56</v>
       </c>
@@ -4069,7 +4068,7 @@
         <v>0</v>
       </c>
       <c r="J59">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K59">
         <v>0</v>
@@ -4089,17 +4088,17 @@
       <c r="P59">
         <v>60495</v>
       </c>
-      <c r="Q59" s="2">
+      <c r="Q59">
         <v>8028</v>
       </c>
-      <c r="R59" s="2">
-        <v>0</v>
-      </c>
-      <c r="S59" s="2">
+      <c r="R59">
+        <v>0</v>
+      </c>
+      <c r="S59">
         <v>27</v>
       </c>
     </row>
-    <row r="60" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A60">
         <v>57</v>
       </c>
@@ -4148,17 +4147,17 @@
       <c r="P60">
         <v>70140</v>
       </c>
-      <c r="Q60" s="2">
+      <c r="Q60">
         <v>7415</v>
       </c>
-      <c r="R60" s="2">
-        <v>0</v>
-      </c>
-      <c r="S60" s="2">
+      <c r="R60">
+        <v>0</v>
+      </c>
+      <c r="S60">
         <v>32</v>
       </c>
     </row>
-    <row r="61" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A61">
         <v>58</v>
       </c>
@@ -4207,17 +4206,17 @@
       <c r="P61">
         <v>55240</v>
       </c>
-      <c r="Q61" s="2">
+      <c r="Q61">
         <v>7927</v>
       </c>
-      <c r="R61" s="2">
+      <c r="R61">
         <v>1</v>
       </c>
-      <c r="S61" s="2">
+      <c r="S61">
         <v>268</v>
       </c>
     </row>
-    <row r="62" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A62">
         <v>59</v>
       </c>
@@ -4266,17 +4265,17 @@
       <c r="P62">
         <v>51334</v>
       </c>
-      <c r="Q62" s="2">
+      <c r="Q62">
         <v>6917</v>
       </c>
-      <c r="R62" s="2">
-        <v>0</v>
-      </c>
-      <c r="S62" s="2">
+      <c r="R62">
+        <v>0</v>
+      </c>
+      <c r="S62">
         <v>100</v>
       </c>
     </row>
-    <row r="63" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A63">
         <v>60</v>
       </c>
@@ -4323,19 +4322,19 @@
         <v>35823</v>
       </c>
       <c r="P63">
-        <v>68691</v>
-      </c>
-      <c r="Q63" s="2">
+        <v>68696</v>
+      </c>
+      <c r="Q63">
         <v>9766</v>
       </c>
-      <c r="R63" s="2">
-        <v>0</v>
-      </c>
-      <c r="S63" s="2">
+      <c r="R63">
+        <v>0</v>
+      </c>
+      <c r="S63">
         <v>153</v>
       </c>
     </row>
-    <row r="64" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A64">
         <v>61</v>
       </c>
@@ -4384,17 +4383,17 @@
       <c r="P64">
         <v>60527</v>
       </c>
-      <c r="Q64" s="2">
+      <c r="Q64">
         <v>5985</v>
       </c>
-      <c r="R64" s="2">
-        <v>0</v>
-      </c>
-      <c r="S64" s="2">
+      <c r="R64">
+        <v>0</v>
+      </c>
+      <c r="S64">
         <v>101</v>
       </c>
     </row>
-    <row r="65" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A65">
         <v>62</v>
       </c>
@@ -4443,17 +4442,17 @@
       <c r="P65">
         <v>58527</v>
       </c>
-      <c r="Q65" s="2">
+      <c r="Q65">
         <v>13282</v>
       </c>
-      <c r="R65" s="2">
-        <v>0</v>
-      </c>
-      <c r="S65" s="2">
+      <c r="R65">
+        <v>0</v>
+      </c>
+      <c r="S65">
         <v>138</v>
       </c>
     </row>
-    <row r="66" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A66">
         <v>63</v>
       </c>
@@ -4502,17 +4501,17 @@
       <c r="P66">
         <v>93810</v>
       </c>
-      <c r="Q66" s="2">
+      <c r="Q66">
         <v>17742</v>
       </c>
-      <c r="R66" s="2">
-        <v>0</v>
-      </c>
-      <c r="S66" s="2">
+      <c r="R66">
+        <v>0</v>
+      </c>
+      <c r="S66">
         <v>52</v>
       </c>
     </row>
-    <row r="67" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A67">
         <v>64</v>
       </c>
@@ -4561,17 +4560,17 @@
       <c r="P67">
         <v>78032</v>
       </c>
-      <c r="Q67" s="2">
+      <c r="Q67">
         <v>9807</v>
       </c>
-      <c r="R67" s="2">
-        <v>0</v>
-      </c>
-      <c r="S67" s="2">
+      <c r="R67">
+        <v>0</v>
+      </c>
+      <c r="S67">
         <v>116</v>
       </c>
     </row>
-    <row r="68" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A68">
         <v>65</v>
       </c>
@@ -4620,17 +4619,17 @@
       <c r="P68">
         <v>71325</v>
       </c>
-      <c r="Q68" s="2">
+      <c r="Q68">
         <v>7850</v>
       </c>
-      <c r="R68" s="2">
-        <v>0</v>
-      </c>
-      <c r="S68" s="2">
+      <c r="R68">
+        <v>0</v>
+      </c>
+      <c r="S68">
         <v>26</v>
       </c>
     </row>
-    <row r="69" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A69">
         <v>66</v>
       </c>
@@ -4679,17 +4678,17 @@
       <c r="P69">
         <v>36118</v>
       </c>
-      <c r="Q69" s="2">
+      <c r="Q69">
         <v>6528</v>
       </c>
-      <c r="R69" s="2">
-        <v>0</v>
-      </c>
-      <c r="S69" s="2">
+      <c r="R69">
+        <v>0</v>
+      </c>
+      <c r="S69">
         <v>47</v>
       </c>
     </row>
-    <row r="70" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A70">
         <v>67</v>
       </c>
@@ -4738,17 +4737,17 @@
       <c r="P70">
         <v>42051</v>
       </c>
-      <c r="Q70" s="2">
+      <c r="Q70">
         <v>5798</v>
       </c>
-      <c r="R70" s="2">
-        <v>0</v>
-      </c>
-      <c r="S70" s="2">
+      <c r="R70">
+        <v>0</v>
+      </c>
+      <c r="S70">
         <v>29</v>
       </c>
     </row>
-    <row r="71" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A71">
         <v>68</v>
       </c>
@@ -4797,17 +4796,17 @@
       <c r="P71">
         <v>49140</v>
       </c>
-      <c r="Q71" s="2">
+      <c r="Q71">
         <v>6782</v>
       </c>
-      <c r="R71" s="2">
-        <v>0</v>
-      </c>
-      <c r="S71" s="2">
+      <c r="R71">
+        <v>0</v>
+      </c>
+      <c r="S71">
         <v>235</v>
       </c>
     </row>
-    <row r="72" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A72">
         <v>69</v>
       </c>
@@ -4856,17 +4855,17 @@
       <c r="P72">
         <v>85505</v>
       </c>
-      <c r="Q72" s="2">
+      <c r="Q72">
         <v>12340</v>
       </c>
-      <c r="R72" s="2">
-        <v>0</v>
-      </c>
-      <c r="S72" s="2">
+      <c r="R72">
+        <v>0</v>
+      </c>
+      <c r="S72">
         <v>79</v>
       </c>
     </row>
-    <row r="73" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A73">
         <v>70</v>
       </c>
@@ -4915,17 +4914,17 @@
       <c r="P73">
         <v>67666</v>
       </c>
-      <c r="Q73" s="2">
+      <c r="Q73">
         <v>10010</v>
       </c>
-      <c r="R73" s="2">
-        <v>0</v>
-      </c>
-      <c r="S73" s="2">
+      <c r="R73">
+        <v>0</v>
+      </c>
+      <c r="S73">
         <v>74</v>
       </c>
     </row>
-    <row r="74" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A74" s="1" t="s">
         <v>89</v>
       </c>
@@ -4952,38 +4951,36 @@
         <v>0</v>
       </c>
       <c r="J74">
-        <v>304</v>
+        <v>40</v>
       </c>
       <c r="K74">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="L74">
-        <v>625237</v>
+        <v>625463</v>
       </c>
       <c r="M74">
-        <v>8174</v>
+        <v>8318</v>
       </c>
       <c r="N74">
-        <v>96756</v>
+        <v>96934</v>
       </c>
       <c r="O74">
-        <v>2330031</v>
+        <v>2330649</v>
       </c>
       <c r="P74">
-        <v>4701901</v>
-      </c>
-      <c r="Q74" s="2">
+        <v>4701905</v>
+      </c>
+      <c r="Q74">
         <v>626236</v>
       </c>
-      <c r="R74" s="2">
+      <c r="R74">
         <v>1</v>
       </c>
-      <c r="S74" s="2">
+      <c r="S74">
         <v>3445</v>
       </c>
     </row>
-    <row r="75" spans="1:19" ht="15.75" x14ac:dyDescent="0.25"/>
-    <row r="76" spans="1:19" ht="15.75" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="12">
     <mergeCell ref="A74:B74"/>

--- a/Notice.xlsx
+++ b/Notice.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Downloads\New folder (13)\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8D7569F-DAD1-4B43-BCCC-4626D41D38A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D092FE4C-B5CD-4A68-925C-7413B6072177}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -304,7 +304,7 @@
     <t>No Action Required</t>
   </si>
   <si>
-    <t>Notice &amp; Hearing Report Last Updated On : 15-09-2026 13:56:50</t>
+    <t>Notice &amp; Hearing Report Last Updated On : 16-09-2026 09:56:49</t>
   </si>
 </sst>
 </file>
@@ -340,7 +340,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
@@ -682,10 +683,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:S74"/>
-  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:S76"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>94</v>
       </c>
@@ -706,7 +707,7 @@
       <c r="P1" s="1"/>
       <c r="Q1" s="1"/>
     </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -747,7 +748,7 @@
       <c r="R2" s="1"/>
       <c r="S2" s="1"/>
     </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3" s="1"/>
       <c r="B3" s="1"/>
       <c r="C3" s="1"/>
@@ -784,17 +785,17 @@
       <c r="P3" t="s">
         <v>18</v>
       </c>
-      <c r="Q3" t="s">
+      <c r="Q3" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="R3" t="s">
+      <c r="R3" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="S3" t="s">
+      <c r="S3" s="2" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>1</v>
       </c>
@@ -843,17 +844,17 @@
       <c r="P4">
         <v>53812</v>
       </c>
-      <c r="Q4">
+      <c r="Q4" s="2">
         <v>12212</v>
       </c>
-      <c r="R4">
-        <v>0</v>
-      </c>
-      <c r="S4">
+      <c r="R4" s="2">
+        <v>0</v>
+      </c>
+      <c r="S4" s="2">
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>2</v>
       </c>
@@ -902,17 +903,17 @@
       <c r="P5">
         <v>74848</v>
       </c>
-      <c r="Q5">
+      <c r="Q5" s="2">
         <v>16108</v>
       </c>
-      <c r="R5">
-        <v>0</v>
-      </c>
-      <c r="S5">
+      <c r="R5" s="2">
+        <v>0</v>
+      </c>
+      <c r="S5" s="2">
         <v>30</v>
       </c>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>3</v>
       </c>
@@ -941,13 +942,13 @@
         <v>0</v>
       </c>
       <c r="J6">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="K6">
         <v>0</v>
       </c>
       <c r="L6">
-        <v>6043</v>
+        <v>6052</v>
       </c>
       <c r="M6">
         <v>201</v>
@@ -956,22 +957,22 @@
         <v>1827</v>
       </c>
       <c r="O6">
-        <v>37304</v>
+        <v>37320</v>
       </c>
       <c r="P6">
         <v>71989</v>
       </c>
-      <c r="Q6">
+      <c r="Q6" s="2">
         <v>17830</v>
       </c>
-      <c r="R6">
-        <v>0</v>
-      </c>
-      <c r="S6">
+      <c r="R6" s="2">
+        <v>0</v>
+      </c>
+      <c r="S6" s="2">
         <v>54</v>
       </c>
     </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>4</v>
       </c>
@@ -1000,13 +1001,13 @@
         <v>0</v>
       </c>
       <c r="J7">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K7">
         <v>0</v>
       </c>
       <c r="L7">
-        <v>5681</v>
+        <v>5683</v>
       </c>
       <c r="M7">
         <v>257</v>
@@ -1020,17 +1021,17 @@
       <c r="P7">
         <v>77581</v>
       </c>
-      <c r="Q7">
+      <c r="Q7" s="2">
         <v>20511</v>
       </c>
-      <c r="R7">
-        <v>0</v>
-      </c>
-      <c r="S7">
+      <c r="R7" s="2">
+        <v>0</v>
+      </c>
+      <c r="S7" s="2">
         <v>8</v>
       </c>
     </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>5</v>
       </c>
@@ -1079,17 +1080,17 @@
       <c r="P8">
         <v>73458</v>
       </c>
-      <c r="Q8">
+      <c r="Q8" s="2">
         <v>20788</v>
       </c>
-      <c r="R8">
-        <v>0</v>
-      </c>
-      <c r="S8">
+      <c r="R8" s="2">
+        <v>0</v>
+      </c>
+      <c r="S8" s="2">
         <v>110</v>
       </c>
     </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>6</v>
       </c>
@@ -1138,17 +1139,17 @@
       <c r="P9">
         <v>72913</v>
       </c>
-      <c r="Q9">
+      <c r="Q9" s="2">
         <v>18141</v>
       </c>
-      <c r="R9">
-        <v>0</v>
-      </c>
-      <c r="S9">
+      <c r="R9" s="2">
+        <v>0</v>
+      </c>
+      <c r="S9" s="2">
         <v>110</v>
       </c>
     </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>7</v>
       </c>
@@ -1197,17 +1198,17 @@
       <c r="P10">
         <v>53124</v>
       </c>
-      <c r="Q10">
+      <c r="Q10" s="2">
         <v>9498</v>
       </c>
-      <c r="R10">
-        <v>0</v>
-      </c>
-      <c r="S10">
+      <c r="R10" s="2">
+        <v>0</v>
+      </c>
+      <c r="S10" s="2">
         <v>2</v>
       </c>
     </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>8</v>
       </c>
@@ -1256,17 +1257,17 @@
       <c r="P11">
         <v>84438</v>
       </c>
-      <c r="Q11">
+      <c r="Q11" s="2">
         <v>23477</v>
       </c>
-      <c r="R11">
-        <v>0</v>
-      </c>
-      <c r="S11">
+      <c r="R11" s="2">
+        <v>0</v>
+      </c>
+      <c r="S11" s="2">
         <v>23</v>
       </c>
     </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>9</v>
       </c>
@@ -1295,13 +1296,13 @@
         <v>0</v>
       </c>
       <c r="J12">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K12">
         <v>0</v>
       </c>
       <c r="L12">
-        <v>10051</v>
+        <v>10054</v>
       </c>
       <c r="M12">
         <v>207</v>
@@ -1315,17 +1316,17 @@
       <c r="P12">
         <v>66685</v>
       </c>
-      <c r="Q12">
+      <c r="Q12" s="2">
         <v>17786</v>
       </c>
-      <c r="R12">
-        <v>0</v>
-      </c>
-      <c r="S12">
+      <c r="R12" s="2">
+        <v>0</v>
+      </c>
+      <c r="S12" s="2">
         <v>3</v>
       </c>
     </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>10</v>
       </c>
@@ -1374,17 +1375,17 @@
       <c r="P13">
         <v>56564</v>
       </c>
-      <c r="Q13">
+      <c r="Q13" s="2">
         <v>16237</v>
       </c>
-      <c r="R13">
-        <v>0</v>
-      </c>
-      <c r="S13">
+      <c r="R13" s="2">
+        <v>0</v>
+      </c>
+      <c r="S13" s="2">
         <v>106</v>
       </c>
     </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>11</v>
       </c>
@@ -1413,13 +1414,13 @@
         <v>0</v>
       </c>
       <c r="J14">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="K14">
         <v>0</v>
       </c>
       <c r="L14">
-        <v>15241</v>
+        <v>15263</v>
       </c>
       <c r="M14">
         <v>1456</v>
@@ -1433,17 +1434,17 @@
       <c r="P14">
         <v>77955</v>
       </c>
-      <c r="Q14">
+      <c r="Q14" s="2">
         <v>19716</v>
       </c>
-      <c r="R14">
-        <v>0</v>
-      </c>
-      <c r="S14">
+      <c r="R14" s="2">
+        <v>0</v>
+      </c>
+      <c r="S14" s="2">
         <v>174</v>
       </c>
     </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>12</v>
       </c>
@@ -1492,17 +1493,17 @@
       <c r="P15">
         <v>67178</v>
       </c>
-      <c r="Q15">
+      <c r="Q15" s="2">
         <v>4859</v>
       </c>
-      <c r="R15">
-        <v>0</v>
-      </c>
-      <c r="S15">
+      <c r="R15" s="2">
+        <v>0</v>
+      </c>
+      <c r="S15" s="2">
         <v>50</v>
       </c>
     </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>13</v>
       </c>
@@ -1551,17 +1552,17 @@
       <c r="P16">
         <v>71673</v>
       </c>
-      <c r="Q16">
+      <c r="Q16" s="2">
         <v>5197</v>
       </c>
-      <c r="R16">
-        <v>0</v>
-      </c>
-      <c r="S16">
+      <c r="R16" s="2">
+        <v>0</v>
+      </c>
+      <c r="S16" s="2">
         <v>47</v>
       </c>
     </row>
-    <row r="17" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>14</v>
       </c>
@@ -1610,17 +1611,17 @@
       <c r="P17">
         <v>65457</v>
       </c>
-      <c r="Q17">
+      <c r="Q17" s="2">
         <v>5417</v>
       </c>
-      <c r="R17">
-        <v>0</v>
-      </c>
-      <c r="S17">
+      <c r="R17" s="2">
+        <v>0</v>
+      </c>
+      <c r="S17" s="2">
         <v>105</v>
       </c>
     </row>
-    <row r="18" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>15</v>
       </c>
@@ -1669,17 +1670,17 @@
       <c r="P18">
         <v>71475</v>
       </c>
-      <c r="Q18">
+      <c r="Q18" s="2">
         <v>6819</v>
       </c>
-      <c r="R18">
-        <v>0</v>
-      </c>
-      <c r="S18">
+      <c r="R18" s="2">
+        <v>0</v>
+      </c>
+      <c r="S18" s="2">
         <v>32</v>
       </c>
     </row>
-    <row r="19" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>16</v>
       </c>
@@ -1728,17 +1729,17 @@
       <c r="P19">
         <v>106392</v>
       </c>
-      <c r="Q19">
+      <c r="Q19" s="2">
         <v>6135</v>
       </c>
-      <c r="R19">
-        <v>0</v>
-      </c>
-      <c r="S19">
+      <c r="R19" s="2">
+        <v>0</v>
+      </c>
+      <c r="S19" s="2">
         <v>36</v>
       </c>
     </row>
-    <row r="20" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>17</v>
       </c>
@@ -1787,17 +1788,17 @@
       <c r="P20">
         <v>75812</v>
       </c>
-      <c r="Q20">
+      <c r="Q20" s="2">
         <v>8984</v>
       </c>
-      <c r="R20">
-        <v>0</v>
-      </c>
-      <c r="S20">
+      <c r="R20" s="2">
+        <v>0</v>
+      </c>
+      <c r="S20" s="2">
         <v>71</v>
       </c>
     </row>
-    <row r="21" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>18</v>
       </c>
@@ -1846,17 +1847,17 @@
       <c r="P21">
         <v>62460</v>
       </c>
-      <c r="Q21">
+      <c r="Q21" s="2">
         <v>3868</v>
       </c>
-      <c r="R21">
-        <v>0</v>
-      </c>
-      <c r="S21">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="R21" s="2">
+        <v>0</v>
+      </c>
+      <c r="S21" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>19</v>
       </c>
@@ -1905,17 +1906,17 @@
       <c r="P22">
         <v>64099</v>
       </c>
-      <c r="Q22">
+      <c r="Q22" s="2">
         <v>4848</v>
       </c>
-      <c r="R22">
-        <v>0</v>
-      </c>
-      <c r="S22">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="R22" s="2">
+        <v>0</v>
+      </c>
+      <c r="S22" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>20</v>
       </c>
@@ -1964,17 +1965,17 @@
       <c r="P23">
         <v>57094</v>
       </c>
-      <c r="Q23">
+      <c r="Q23" s="2">
         <v>3541</v>
       </c>
-      <c r="R23">
-        <v>0</v>
-      </c>
-      <c r="S23">
+      <c r="R23" s="2">
+        <v>0</v>
+      </c>
+      <c r="S23" s="2">
         <v>28</v>
       </c>
     </row>
-    <row r="24" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>21</v>
       </c>
@@ -2023,17 +2024,17 @@
       <c r="P24">
         <v>65629</v>
       </c>
-      <c r="Q24">
+      <c r="Q24" s="2">
         <v>3492</v>
       </c>
-      <c r="R24">
-        <v>0</v>
-      </c>
-      <c r="S24">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="R24" s="2">
+        <v>0</v>
+      </c>
+      <c r="S24" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>22</v>
       </c>
@@ -2082,17 +2083,17 @@
       <c r="P25">
         <v>57533</v>
       </c>
-      <c r="Q25">
+      <c r="Q25" s="2">
         <v>3231</v>
       </c>
-      <c r="R25">
-        <v>0</v>
-      </c>
-      <c r="S25">
+      <c r="R25" s="2">
+        <v>0</v>
+      </c>
+      <c r="S25" s="2">
         <v>13</v>
       </c>
     </row>
-    <row r="26" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>23</v>
       </c>
@@ -2141,17 +2142,17 @@
       <c r="P26">
         <v>66594</v>
       </c>
-      <c r="Q26">
+      <c r="Q26" s="2">
         <v>3333</v>
       </c>
-      <c r="R26">
-        <v>0</v>
-      </c>
-      <c r="S26">
+      <c r="R26" s="2">
+        <v>0</v>
+      </c>
+      <c r="S26" s="2">
         <v>2</v>
       </c>
     </row>
-    <row r="27" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>24</v>
       </c>
@@ -2200,17 +2201,17 @@
       <c r="P27">
         <v>73109</v>
       </c>
-      <c r="Q27">
+      <c r="Q27" s="2">
         <v>12669</v>
       </c>
-      <c r="R27">
-        <v>0</v>
-      </c>
-      <c r="S27">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="R27" s="2">
+        <v>0</v>
+      </c>
+      <c r="S27" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>25</v>
       </c>
@@ -2259,17 +2260,17 @@
       <c r="P28">
         <v>80620</v>
       </c>
-      <c r="Q28">
+      <c r="Q28" s="2">
         <v>13995</v>
       </c>
-      <c r="R28">
-        <v>0</v>
-      </c>
-      <c r="S28">
+      <c r="R28" s="2">
+        <v>0</v>
+      </c>
+      <c r="S28" s="2">
         <v>127</v>
       </c>
     </row>
-    <row r="29" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>26</v>
       </c>
@@ -2318,17 +2319,17 @@
       <c r="P29">
         <v>83836</v>
       </c>
-      <c r="Q29">
+      <c r="Q29" s="2">
         <v>14229</v>
       </c>
-      <c r="R29">
-        <v>0</v>
-      </c>
-      <c r="S29">
+      <c r="R29" s="2">
+        <v>0</v>
+      </c>
+      <c r="S29" s="2">
         <v>22</v>
       </c>
     </row>
-    <row r="30" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>27</v>
       </c>
@@ -2377,17 +2378,17 @@
       <c r="P30">
         <v>86933</v>
       </c>
-      <c r="Q30">
+      <c r="Q30" s="2">
         <v>12564</v>
       </c>
-      <c r="R30">
-        <v>0</v>
-      </c>
-      <c r="S30">
+      <c r="R30" s="2">
+        <v>0</v>
+      </c>
+      <c r="S30" s="2">
         <v>8</v>
       </c>
     </row>
-    <row r="31" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>28</v>
       </c>
@@ -2436,17 +2437,17 @@
       <c r="P31">
         <v>81642</v>
       </c>
-      <c r="Q31">
+      <c r="Q31" s="2">
         <v>14581</v>
       </c>
-      <c r="R31">
-        <v>0</v>
-      </c>
-      <c r="S31">
+      <c r="R31" s="2">
+        <v>0</v>
+      </c>
+      <c r="S31" s="2">
         <v>39</v>
       </c>
     </row>
-    <row r="32" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>29</v>
       </c>
@@ -2495,17 +2496,17 @@
       <c r="P32">
         <v>74810</v>
       </c>
-      <c r="Q32">
+      <c r="Q32" s="2">
         <v>11379</v>
       </c>
-      <c r="R32">
-        <v>0</v>
-      </c>
-      <c r="S32">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="R32" s="2">
+        <v>0</v>
+      </c>
+      <c r="S32" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>30</v>
       </c>
@@ -2546,25 +2547,25 @@
         <v>311</v>
       </c>
       <c r="N33">
-        <v>1272</v>
+        <v>1275</v>
       </c>
       <c r="O33">
-        <v>38944</v>
+        <v>38955</v>
       </c>
       <c r="P33">
         <v>76969</v>
       </c>
-      <c r="Q33">
+      <c r="Q33" s="2">
         <v>6678</v>
       </c>
-      <c r="R33">
-        <v>0</v>
-      </c>
-      <c r="S33">
+      <c r="R33" s="2">
+        <v>0</v>
+      </c>
+      <c r="S33" s="2">
         <v>19</v>
       </c>
     </row>
-    <row r="34" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>31</v>
       </c>
@@ -2613,17 +2614,17 @@
       <c r="P34">
         <v>74624</v>
       </c>
-      <c r="Q34">
+      <c r="Q34" s="2">
         <v>7137</v>
       </c>
-      <c r="R34">
-        <v>0</v>
-      </c>
-      <c r="S34">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="R34" s="2">
+        <v>0</v>
+      </c>
+      <c r="S34" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>32</v>
       </c>
@@ -2672,17 +2673,17 @@
       <c r="P35">
         <v>76464</v>
       </c>
-      <c r="Q35">
+      <c r="Q35" s="2">
         <v>8879</v>
       </c>
-      <c r="R35">
-        <v>0</v>
-      </c>
-      <c r="S35">
+      <c r="R35" s="2">
+        <v>0</v>
+      </c>
+      <c r="S35" s="2">
         <v>35</v>
       </c>
     </row>
-    <row r="36" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>33</v>
       </c>
@@ -2731,17 +2732,17 @@
       <c r="P36">
         <v>60419</v>
       </c>
-      <c r="Q36">
+      <c r="Q36" s="2">
         <v>3855</v>
       </c>
-      <c r="R36">
-        <v>0</v>
-      </c>
-      <c r="S36">
+      <c r="R36" s="2">
+        <v>0</v>
+      </c>
+      <c r="S36" s="2">
         <v>2</v>
       </c>
     </row>
-    <row r="37" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>34</v>
       </c>
@@ -2790,17 +2791,17 @@
       <c r="P37">
         <v>57832</v>
       </c>
-      <c r="Q37">
+      <c r="Q37" s="2">
         <v>4036</v>
       </c>
-      <c r="R37">
-        <v>0</v>
-      </c>
-      <c r="S37">
+      <c r="R37" s="2">
+        <v>0</v>
+      </c>
+      <c r="S37" s="2">
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>35</v>
       </c>
@@ -2849,17 +2850,17 @@
       <c r="P38">
         <v>63038</v>
       </c>
-      <c r="Q38">
+      <c r="Q38" s="2">
         <v>5135</v>
       </c>
-      <c r="R38">
-        <v>0</v>
-      </c>
-      <c r="S38">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="39" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="R38" s="2">
+        <v>0</v>
+      </c>
+      <c r="S38" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>36</v>
       </c>
@@ -2908,17 +2909,17 @@
       <c r="P39">
         <v>71133</v>
       </c>
-      <c r="Q39">
+      <c r="Q39" s="2">
         <v>5903</v>
       </c>
-      <c r="R39">
-        <v>0</v>
-      </c>
-      <c r="S39">
+      <c r="R39" s="2">
+        <v>0</v>
+      </c>
+      <c r="S39" s="2">
         <v>26</v>
       </c>
     </row>
-    <row r="40" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>37</v>
       </c>
@@ -2967,17 +2968,17 @@
       <c r="P40">
         <v>73242</v>
       </c>
-      <c r="Q40">
+      <c r="Q40" s="2">
         <v>3824</v>
       </c>
-      <c r="R40">
-        <v>0</v>
-      </c>
-      <c r="S40">
+      <c r="R40" s="2">
+        <v>0</v>
+      </c>
+      <c r="S40" s="2">
         <v>61</v>
       </c>
     </row>
-    <row r="41" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>38</v>
       </c>
@@ -3026,17 +3027,17 @@
       <c r="P41">
         <v>85251</v>
       </c>
-      <c r="Q41">
+      <c r="Q41" s="2">
         <v>6015</v>
       </c>
-      <c r="R41">
-        <v>0</v>
-      </c>
-      <c r="S41">
+      <c r="R41" s="2">
+        <v>0</v>
+      </c>
+      <c r="S41" s="2">
         <v>27</v>
       </c>
     </row>
-    <row r="42" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>39</v>
       </c>
@@ -3085,17 +3086,17 @@
       <c r="P42">
         <v>68615</v>
       </c>
-      <c r="Q42">
+      <c r="Q42" s="2">
         <v>4708</v>
       </c>
-      <c r="R42">
-        <v>0</v>
-      </c>
-      <c r="S42">
+      <c r="R42" s="2">
+        <v>0</v>
+      </c>
+      <c r="S42" s="2">
         <v>8</v>
       </c>
     </row>
-    <row r="43" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>40</v>
       </c>
@@ -3144,17 +3145,17 @@
       <c r="P43">
         <v>63012</v>
       </c>
-      <c r="Q43">
+      <c r="Q43" s="2">
         <v>5219</v>
       </c>
-      <c r="R43">
-        <v>0</v>
-      </c>
-      <c r="S43">
+      <c r="R43" s="2">
+        <v>0</v>
+      </c>
+      <c r="S43" s="2">
         <v>121</v>
       </c>
     </row>
-    <row r="44" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A44">
         <v>41</v>
       </c>
@@ -3203,17 +3204,17 @@
       <c r="P44">
         <v>68393</v>
       </c>
-      <c r="Q44">
+      <c r="Q44" s="2">
         <v>7659</v>
       </c>
-      <c r="R44">
-        <v>0</v>
-      </c>
-      <c r="S44">
+      <c r="R44" s="2">
+        <v>0</v>
+      </c>
+      <c r="S44" s="2">
         <v>20</v>
       </c>
     </row>
-    <row r="45" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A45">
         <v>42</v>
       </c>
@@ -3262,17 +3263,17 @@
       <c r="P45">
         <v>76287</v>
       </c>
-      <c r="Q45">
+      <c r="Q45" s="2">
         <v>6998</v>
       </c>
-      <c r="R45">
-        <v>0</v>
-      </c>
-      <c r="S45">
+      <c r="R45" s="2">
+        <v>0</v>
+      </c>
+      <c r="S45" s="2">
         <v>129</v>
       </c>
     </row>
-    <row r="46" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A46">
         <v>43</v>
       </c>
@@ -3321,17 +3322,17 @@
       <c r="P46">
         <v>64160</v>
       </c>
-      <c r="Q46">
+      <c r="Q46" s="2">
         <v>7548</v>
       </c>
-      <c r="R46">
-        <v>0</v>
-      </c>
-      <c r="S46">
+      <c r="R46" s="2">
+        <v>0</v>
+      </c>
+      <c r="S46" s="2">
         <v>152</v>
       </c>
     </row>
-    <row r="47" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A47">
         <v>44</v>
       </c>
@@ -3380,17 +3381,17 @@
       <c r="P47">
         <v>49875</v>
       </c>
-      <c r="Q47">
+      <c r="Q47" s="2">
         <v>5046</v>
       </c>
-      <c r="R47">
-        <v>0</v>
-      </c>
-      <c r="S47">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="48" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="R47" s="2">
+        <v>0</v>
+      </c>
+      <c r="S47" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A48">
         <v>45</v>
       </c>
@@ -3439,17 +3440,17 @@
       <c r="P48">
         <v>54142</v>
       </c>
-      <c r="Q48">
+      <c r="Q48" s="2">
         <v>4623</v>
       </c>
-      <c r="R48">
-        <v>0</v>
-      </c>
-      <c r="S48">
+      <c r="R48" s="2">
+        <v>0</v>
+      </c>
+      <c r="S48" s="2">
         <v>9</v>
       </c>
     </row>
-    <row r="49" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A49">
         <v>46</v>
       </c>
@@ -3498,17 +3499,17 @@
       <c r="P49">
         <v>55376</v>
       </c>
-      <c r="Q49">
+      <c r="Q49" s="2">
         <v>5057</v>
       </c>
-      <c r="R49">
-        <v>0</v>
-      </c>
-      <c r="S49">
+      <c r="R49" s="2">
+        <v>0</v>
+      </c>
+      <c r="S49" s="2">
         <v>4</v>
       </c>
     </row>
-    <row r="50" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A50">
         <v>47</v>
       </c>
@@ -3557,17 +3558,17 @@
       <c r="P50">
         <v>63298</v>
       </c>
-      <c r="Q50">
+      <c r="Q50" s="2">
         <v>7292</v>
       </c>
-      <c r="R50">
-        <v>0</v>
-      </c>
-      <c r="S50">
+      <c r="R50" s="2">
+        <v>0</v>
+      </c>
+      <c r="S50" s="2">
         <v>1</v>
       </c>
     </row>
-    <row r="51" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A51">
         <v>48</v>
       </c>
@@ -3616,17 +3617,17 @@
       <c r="P51">
         <v>71754</v>
       </c>
-      <c r="Q51">
+      <c r="Q51" s="2">
         <v>7715</v>
       </c>
-      <c r="R51">
-        <v>0</v>
-      </c>
-      <c r="S51">
+      <c r="R51" s="2">
+        <v>0</v>
+      </c>
+      <c r="S51" s="2">
         <v>40</v>
       </c>
     </row>
-    <row r="52" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A52">
         <v>49</v>
       </c>
@@ -3675,17 +3676,17 @@
       <c r="P52">
         <v>63987</v>
       </c>
-      <c r="Q52">
+      <c r="Q52" s="2">
         <v>5655</v>
       </c>
-      <c r="R52">
-        <v>0</v>
-      </c>
-      <c r="S52">
+      <c r="R52" s="2">
+        <v>0</v>
+      </c>
+      <c r="S52" s="2">
         <v>2</v>
       </c>
     </row>
-    <row r="53" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A53">
         <v>50</v>
       </c>
@@ -3734,17 +3735,17 @@
       <c r="P53">
         <v>56306</v>
       </c>
-      <c r="Q53">
+      <c r="Q53" s="2">
         <v>6551</v>
       </c>
-      <c r="R53">
-        <v>0</v>
-      </c>
-      <c r="S53">
+      <c r="R53" s="2">
+        <v>0</v>
+      </c>
+      <c r="S53" s="2">
         <v>5</v>
       </c>
     </row>
-    <row r="54" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A54">
         <v>51</v>
       </c>
@@ -3793,17 +3794,17 @@
       <c r="P54">
         <v>58440</v>
       </c>
-      <c r="Q54">
+      <c r="Q54" s="2">
         <v>7347</v>
       </c>
-      <c r="R54">
-        <v>0</v>
-      </c>
-      <c r="S54">
+      <c r="R54" s="2">
+        <v>0</v>
+      </c>
+      <c r="S54" s="2">
         <v>1</v>
       </c>
     </row>
-    <row r="55" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A55">
         <v>52</v>
       </c>
@@ -3852,17 +3853,17 @@
       <c r="P55">
         <v>58215</v>
       </c>
-      <c r="Q55">
+      <c r="Q55" s="2">
         <v>5098</v>
       </c>
-      <c r="R55">
-        <v>0</v>
-      </c>
-      <c r="S55">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="56" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="R55" s="2">
+        <v>0</v>
+      </c>
+      <c r="S55" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A56">
         <v>53</v>
       </c>
@@ -3891,37 +3892,37 @@
         <v>0</v>
       </c>
       <c r="J56">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K56">
         <v>0</v>
       </c>
       <c r="L56">
-        <v>4090</v>
+        <v>4091</v>
       </c>
       <c r="M56">
         <v>3</v>
       </c>
       <c r="N56">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="O56">
-        <v>18804</v>
+        <v>18805</v>
       </c>
       <c r="P56">
         <v>47621</v>
       </c>
-      <c r="Q56">
+      <c r="Q56" s="2">
         <v>4882</v>
       </c>
-      <c r="R56">
-        <v>0</v>
-      </c>
-      <c r="S56">
+      <c r="R56" s="2">
+        <v>0</v>
+      </c>
+      <c r="S56" s="2">
         <v>30</v>
       </c>
     </row>
-    <row r="57" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A57">
         <v>54</v>
       </c>
@@ -3970,17 +3971,17 @@
       <c r="P57">
         <v>61556</v>
       </c>
-      <c r="Q57">
+      <c r="Q57" s="2">
         <v>6870</v>
       </c>
-      <c r="R57">
-        <v>0</v>
-      </c>
-      <c r="S57">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="58" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="R57" s="2">
+        <v>0</v>
+      </c>
+      <c r="S57" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A58">
         <v>55</v>
       </c>
@@ -4029,17 +4030,17 @@
       <c r="P58">
         <v>57577</v>
       </c>
-      <c r="Q58">
+      <c r="Q58" s="2">
         <v>8884</v>
       </c>
-      <c r="R58">
-        <v>0</v>
-      </c>
-      <c r="S58">
+      <c r="R58" s="2">
+        <v>0</v>
+      </c>
+      <c r="S58" s="2">
         <v>64</v>
       </c>
     </row>
-    <row r="59" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A59">
         <v>56</v>
       </c>
@@ -4088,17 +4089,17 @@
       <c r="P59">
         <v>60495</v>
       </c>
-      <c r="Q59">
+      <c r="Q59" s="2">
         <v>8028</v>
       </c>
-      <c r="R59">
-        <v>0</v>
-      </c>
-      <c r="S59">
+      <c r="R59" s="2">
+        <v>0</v>
+      </c>
+      <c r="S59" s="2">
         <v>27</v>
       </c>
     </row>
-    <row r="60" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A60">
         <v>57</v>
       </c>
@@ -4147,17 +4148,17 @@
       <c r="P60">
         <v>70140</v>
       </c>
-      <c r="Q60">
+      <c r="Q60" s="2">
         <v>7415</v>
       </c>
-      <c r="R60">
-        <v>0</v>
-      </c>
-      <c r="S60">
+      <c r="R60" s="2">
+        <v>0</v>
+      </c>
+      <c r="S60" s="2">
         <v>32</v>
       </c>
     </row>
-    <row r="61" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A61">
         <v>58</v>
       </c>
@@ -4206,17 +4207,17 @@
       <c r="P61">
         <v>55240</v>
       </c>
-      <c r="Q61">
+      <c r="Q61" s="2">
         <v>7927</v>
       </c>
-      <c r="R61">
+      <c r="R61" s="2">
         <v>1</v>
       </c>
-      <c r="S61">
+      <c r="S61" s="2">
         <v>268</v>
       </c>
     </row>
-    <row r="62" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A62">
         <v>59</v>
       </c>
@@ -4265,17 +4266,17 @@
       <c r="P62">
         <v>51334</v>
       </c>
-      <c r="Q62">
+      <c r="Q62" s="2">
         <v>6917</v>
       </c>
-      <c r="R62">
-        <v>0</v>
-      </c>
-      <c r="S62">
+      <c r="R62" s="2">
+        <v>0</v>
+      </c>
+      <c r="S62" s="2">
         <v>100</v>
       </c>
     </row>
-    <row r="63" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A63">
         <v>60</v>
       </c>
@@ -4324,17 +4325,17 @@
       <c r="P63">
         <v>68696</v>
       </c>
-      <c r="Q63">
+      <c r="Q63" s="2">
         <v>9766</v>
       </c>
-      <c r="R63">
-        <v>0</v>
-      </c>
-      <c r="S63">
+      <c r="R63" s="2">
+        <v>0</v>
+      </c>
+      <c r="S63" s="2">
         <v>153</v>
       </c>
     </row>
-    <row r="64" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A64">
         <v>61</v>
       </c>
@@ -4383,17 +4384,17 @@
       <c r="P64">
         <v>60527</v>
       </c>
-      <c r="Q64">
+      <c r="Q64" s="2">
         <v>5985</v>
       </c>
-      <c r="R64">
-        <v>0</v>
-      </c>
-      <c r="S64">
+      <c r="R64" s="2">
+        <v>0</v>
+      </c>
+      <c r="S64" s="2">
         <v>101</v>
       </c>
     </row>
-    <row r="65" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A65">
         <v>62</v>
       </c>
@@ -4442,17 +4443,17 @@
       <c r="P65">
         <v>58527</v>
       </c>
-      <c r="Q65">
+      <c r="Q65" s="2">
         <v>13282</v>
       </c>
-      <c r="R65">
-        <v>0</v>
-      </c>
-      <c r="S65">
+      <c r="R65" s="2">
+        <v>0</v>
+      </c>
+      <c r="S65" s="2">
         <v>138</v>
       </c>
     </row>
-    <row r="66" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A66">
         <v>63</v>
       </c>
@@ -4501,17 +4502,17 @@
       <c r="P66">
         <v>93810</v>
       </c>
-      <c r="Q66">
+      <c r="Q66" s="2">
         <v>17742</v>
       </c>
-      <c r="R66">
-        <v>0</v>
-      </c>
-      <c r="S66">
+      <c r="R66" s="2">
+        <v>0</v>
+      </c>
+      <c r="S66" s="2">
         <v>52</v>
       </c>
     </row>
-    <row r="67" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A67">
         <v>64</v>
       </c>
@@ -4560,17 +4561,17 @@
       <c r="P67">
         <v>78032</v>
       </c>
-      <c r="Q67">
+      <c r="Q67" s="2">
         <v>9807</v>
       </c>
-      <c r="R67">
-        <v>0</v>
-      </c>
-      <c r="S67">
+      <c r="R67" s="2">
+        <v>0</v>
+      </c>
+      <c r="S67" s="2">
         <v>116</v>
       </c>
     </row>
-    <row r="68" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A68">
         <v>65</v>
       </c>
@@ -4619,17 +4620,17 @@
       <c r="P68">
         <v>71325</v>
       </c>
-      <c r="Q68">
+      <c r="Q68" s="2">
         <v>7850</v>
       </c>
-      <c r="R68">
-        <v>0</v>
-      </c>
-      <c r="S68">
+      <c r="R68" s="2">
+        <v>0</v>
+      </c>
+      <c r="S68" s="2">
         <v>26</v>
       </c>
     </row>
-    <row r="69" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A69">
         <v>66</v>
       </c>
@@ -4678,17 +4679,17 @@
       <c r="P69">
         <v>36118</v>
       </c>
-      <c r="Q69">
+      <c r="Q69" s="2">
         <v>6528</v>
       </c>
-      <c r="R69">
-        <v>0</v>
-      </c>
-      <c r="S69">
+      <c r="R69" s="2">
+        <v>0</v>
+      </c>
+      <c r="S69" s="2">
         <v>47</v>
       </c>
     </row>
-    <row r="70" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A70">
         <v>67</v>
       </c>
@@ -4737,17 +4738,17 @@
       <c r="P70">
         <v>42051</v>
       </c>
-      <c r="Q70">
+      <c r="Q70" s="2">
         <v>5798</v>
       </c>
-      <c r="R70">
-        <v>0</v>
-      </c>
-      <c r="S70">
+      <c r="R70" s="2">
+        <v>0</v>
+      </c>
+      <c r="S70" s="2">
         <v>29</v>
       </c>
     </row>
-    <row r="71" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A71">
         <v>68</v>
       </c>
@@ -4796,17 +4797,17 @@
       <c r="P71">
         <v>49140</v>
       </c>
-      <c r="Q71">
+      <c r="Q71" s="2">
         <v>6782</v>
       </c>
-      <c r="R71">
-        <v>0</v>
-      </c>
-      <c r="S71">
+      <c r="R71" s="2">
+        <v>0</v>
+      </c>
+      <c r="S71" s="2">
         <v>235</v>
       </c>
     </row>
-    <row r="72" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A72">
         <v>69</v>
       </c>
@@ -4855,17 +4856,17 @@
       <c r="P72">
         <v>85505</v>
       </c>
-      <c r="Q72">
+      <c r="Q72" s="2">
         <v>12340</v>
       </c>
-      <c r="R72">
-        <v>0</v>
-      </c>
-      <c r="S72">
+      <c r="R72" s="2">
+        <v>0</v>
+      </c>
+      <c r="S72" s="2">
         <v>79</v>
       </c>
     </row>
-    <row r="73" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A73">
         <v>70</v>
       </c>
@@ -4914,17 +4915,17 @@
       <c r="P73">
         <v>67666</v>
       </c>
-      <c r="Q73">
+      <c r="Q73" s="2">
         <v>10010</v>
       </c>
-      <c r="R73">
-        <v>0</v>
-      </c>
-      <c r="S73">
+      <c r="R73" s="2">
+        <v>0</v>
+      </c>
+      <c r="S73" s="2">
         <v>74</v>
       </c>
     </row>
-    <row r="74" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A74" s="1" t="s">
         <v>89</v>
       </c>
@@ -4951,36 +4952,38 @@
         <v>0</v>
       </c>
       <c r="J74">
-        <v>40</v>
+        <v>5</v>
       </c>
       <c r="K74">
         <v>3</v>
       </c>
       <c r="L74">
-        <v>625463</v>
+        <v>625500</v>
       </c>
       <c r="M74">
         <v>8318</v>
       </c>
       <c r="N74">
-        <v>96934</v>
+        <v>96939</v>
       </c>
       <c r="O74">
-        <v>2330649</v>
+        <v>2330677</v>
       </c>
       <c r="P74">
         <v>4701905</v>
       </c>
-      <c r="Q74">
+      <c r="Q74" s="2">
         <v>626236</v>
       </c>
-      <c r="R74">
+      <c r="R74" s="2">
         <v>1</v>
       </c>
-      <c r="S74">
+      <c r="S74" s="2">
         <v>3445</v>
       </c>
     </row>
+    <row r="75" spans="1:19" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="76" spans="1:19" ht="15.75" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="12">
     <mergeCell ref="A74:B74"/>

--- a/Notice.xlsx
+++ b/Notice.xlsx
@@ -1,317 +1,41 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <workbookPr codeName="ThisWorkbook"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Downloads\New folder (13)\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D092FE4C-B5CD-4A68-925C-7413B6072177}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
-  <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
-  </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="95">
-  <si>
-    <t>S. No.</t>
-  </si>
-  <si>
-    <t>AC No. - AC Name</t>
-  </si>
-  <si>
-    <t>Notice Generated</t>
-  </si>
-  <si>
-    <t>Pending for Notice Generation</t>
-  </si>
-  <si>
-    <t>Notice Delivered</t>
-  </si>
-  <si>
-    <t>Notices pending delivery</t>
-  </si>
-  <si>
-    <t>Hearing</t>
-  </si>
-  <si>
-    <t>DEO Status</t>
-  </si>
-  <si>
-    <t>ERO/AERO Status</t>
-  </si>
-  <si>
-    <t>Hearing Held</t>
-  </si>
-  <si>
-    <t>Hearing Date Lapsed</t>
-  </si>
-  <si>
-    <t>Reschedule Date Lapsed</t>
-  </si>
-  <si>
-    <t>Total Pending</t>
-  </si>
-  <si>
-    <t>Pending &gt; 5 days</t>
-  </si>
-  <si>
-    <t>Verified</t>
-  </si>
-  <si>
-    <t>Not Verified</t>
-  </si>
-  <si>
-    <t>Found Ineligible for Final</t>
-  </si>
-  <si>
-    <t>Parked for Final Publication w.r.t. Notices Generated</t>
-  </si>
-  <si>
-    <t>Parked For Final Publication w.r.t. Others</t>
-  </si>
-  <si>
-    <t>25 - Haridwar</t>
-  </si>
-  <si>
-    <t>26 - BHEL Ranipur</t>
-  </si>
-  <si>
-    <t>27 - Jwalapur</t>
-  </si>
-  <si>
-    <t>28 - Bhagwanpur</t>
-  </si>
-  <si>
-    <t>29 - Jhabrera</t>
-  </si>
-  <si>
-    <t>30 - Piran Kaliyar</t>
-  </si>
-  <si>
-    <t>31 - Roorkee</t>
-  </si>
-  <si>
-    <t>32 - Khanpur</t>
-  </si>
-  <si>
-    <t>33 - Manglore</t>
-  </si>
-  <si>
-    <t>34 - Laksar</t>
-  </si>
-  <si>
-    <t>35 - Haridwar Rural</t>
-  </si>
-  <si>
-    <t>56 - Lalkuan</t>
-  </si>
-  <si>
-    <t>57 - Bhimtal</t>
-  </si>
-  <si>
-    <t>58 - Nainital</t>
-  </si>
-  <si>
-    <t>59 - Haldwani</t>
-  </si>
-  <si>
-    <t>60 - Kaladhungi</t>
-  </si>
-  <si>
-    <t>61 - Ramnagar</t>
-  </si>
-  <si>
-    <t>48 - Dwarahat</t>
-  </si>
-  <si>
-    <t>49 - Salt</t>
-  </si>
-  <si>
-    <t>50 - Ranikhet</t>
-  </si>
-  <si>
-    <t>51 - Someshwar</t>
-  </si>
-  <si>
-    <t>52 - Almora</t>
-  </si>
-  <si>
-    <t>53 - Jageshwar</t>
-  </si>
-  <si>
-    <t>62 - Jaspur</t>
-  </si>
-  <si>
-    <t>63 - Kashipur</t>
-  </si>
-  <si>
-    <t>64 - Bajpur</t>
-  </si>
-  <si>
-    <t>65 - Gadarpur</t>
-  </si>
-  <si>
-    <t>66 - Rudrapur</t>
-  </si>
-  <si>
-    <t>67 - Kichha</t>
-  </si>
-  <si>
-    <t>68 - Sitarganj</t>
-  </si>
-  <si>
-    <t>69 - Nanakmatta</t>
-  </si>
-  <si>
-    <t>70 - Khatima</t>
-  </si>
-  <si>
-    <t>42 - Dharchula</t>
-  </si>
-  <si>
-    <t>43 - Didihat</t>
-  </si>
-  <si>
-    <t>44 - Pithoragarh</t>
-  </si>
-  <si>
-    <t>45 - Gangolihat</t>
-  </si>
-  <si>
-    <t>46 - Kapkot</t>
-  </si>
-  <si>
-    <t>47 - Bageshwar</t>
-  </si>
-  <si>
-    <t>54 - Lohaghat</t>
-  </si>
-  <si>
-    <t>55 - Champawat</t>
-  </si>
-  <si>
-    <t>4 - Badrinath</t>
-  </si>
-  <si>
-    <t>5 - Tharali</t>
-  </si>
-  <si>
-    <t>6 - Karanprayag</t>
-  </si>
-  <si>
-    <t>1 - Purola</t>
-  </si>
-  <si>
-    <t>2 - Yamunotri</t>
-  </si>
-  <si>
-    <t>3 - Gangotri</t>
-  </si>
-  <si>
-    <t>7 - Kedarnath</t>
-  </si>
-  <si>
-    <t>8 - Rudraprayag</t>
-  </si>
-  <si>
-    <t>9 - Ghansali</t>
-  </si>
-  <si>
-    <t>10 - Devprayag</t>
-  </si>
-  <si>
-    <t>11 - Narendranagar</t>
-  </si>
-  <si>
-    <t>12 - Pratapnagar</t>
-  </si>
-  <si>
-    <t>13 - Tehri</t>
-  </si>
-  <si>
-    <t>14 - Dhanolti</t>
-  </si>
-  <si>
-    <t>36 - Yamkeshwar</t>
-  </si>
-  <si>
-    <t>37 - Pauri</t>
-  </si>
-  <si>
-    <t>38 - Srinagar</t>
-  </si>
-  <si>
-    <t>39 - Chaubattakhal</t>
-  </si>
-  <si>
-    <t>40 - Lansdowne</t>
-  </si>
-  <si>
-    <t>41 - Kotdwar</t>
-  </si>
-  <si>
-    <t>15 - Chakrata</t>
-  </si>
-  <si>
-    <t>16 - Vikasnagar</t>
-  </si>
-  <si>
-    <t>17 - Sahaspur</t>
-  </si>
-  <si>
-    <t>18 - Dharmpur</t>
-  </si>
-  <si>
-    <t>19 - Raipur</t>
-  </si>
-  <si>
-    <t>20 - Rajpur Road</t>
-  </si>
-  <si>
-    <t>21 - Dehradun Cantonment</t>
-  </si>
-  <si>
-    <t>22 - Mussoorie</t>
-  </si>
-  <si>
-    <t>23 - Doiwala</t>
-  </si>
-  <si>
-    <t>24 - Rishikesh</t>
-  </si>
-  <si>
-    <t>Total</t>
-  </si>
-  <si>
-    <t>DSE with UP</t>
-  </si>
-  <si>
-    <t>Electors having DSE with UP</t>
-  </si>
-  <si>
-    <t>Form 7 Generated</t>
-  </si>
-  <si>
-    <t>No Action Required</t>
-  </si>
-  <si>
-    <t>Notice &amp; Hearing Report Last Updated On : 16-09-2026 09:56:49</t>
-  </si>
-</sst>
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
+  <numFmts count="1">
+    <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
+  </numFmts>
+  <fonts count="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -340,24 +64,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+  <cellXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
@@ -682,125 +396,81 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:S76"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:P74"/>
   <sheetData>
-    <row r="1" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
-      <c r="H1" s="1"/>
-      <c r="I1" s="1"/>
-      <c r="J1" s="1"/>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
-      <c r="M1" s="1"/>
-      <c r="N1" s="1"/>
-      <c r="O1" s="1"/>
-      <c r="P1" s="1"/>
-      <c r="Q1" s="1"/>
-    </row>
-    <row r="2" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H2" s="1"/>
-      <c r="I2" s="1"/>
-      <c r="J2" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="K2" s="1"/>
-      <c r="L2" s="1"/>
-      <c r="M2" s="1"/>
-      <c r="N2" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="O2" s="1"/>
-      <c r="P2" s="1"/>
-      <c r="Q2" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="R2" s="1"/>
-      <c r="S2" s="1"/>
-    </row>
-    <row r="3" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A3" s="1"/>
-      <c r="B3" s="1"/>
-      <c r="C3" s="1"/>
-      <c r="D3" s="1"/>
-      <c r="E3" s="1"/>
-      <c r="F3" s="1"/>
-      <c r="G3" t="s">
-        <v>9</v>
-      </c>
-      <c r="H3" t="s">
-        <v>10</v>
-      </c>
-      <c r="I3" t="s">
-        <v>11</v>
-      </c>
-      <c r="J3" t="s">
-        <v>12</v>
-      </c>
-      <c r="K3" t="s">
-        <v>13</v>
-      </c>
-      <c r="L3" t="s">
-        <v>14</v>
-      </c>
-      <c r="M3" t="s">
-        <v>15</v>
-      </c>
-      <c r="N3" t="s">
-        <v>16</v>
-      </c>
-      <c r="O3" t="s">
-        <v>17</v>
-      </c>
-      <c r="P3" t="s">
-        <v>18</v>
-      </c>
-      <c r="Q3" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="R3" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="S3" s="2" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="4" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Notice &amp; Hearing Report</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>S. No.</v>
+      </c>
+      <c r="B2" t="str">
+        <v>AC No. - AC Name</v>
+      </c>
+      <c r="C2" t="str">
+        <v>Notice Generated</v>
+      </c>
+      <c r="D2" t="str">
+        <v>Pending for Notice Generation</v>
+      </c>
+      <c r="E2" t="str">
+        <v>Notice Delivered</v>
+      </c>
+      <c r="F2" t="str">
+        <v>Notices pending delivery</v>
+      </c>
+      <c r="G2" t="str">
+        <v>Hearing</v>
+      </c>
+      <c r="J2" t="str">
+        <v>DEO Status</v>
+      </c>
+      <c r="N2" t="str">
+        <v>ERO/AERO Status</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="G3" t="str">
+        <v>Hearing Held</v>
+      </c>
+      <c r="H3" t="str">
+        <v>Hearing Date Lapsed</v>
+      </c>
+      <c r="I3" t="str">
+        <v>Reschedule Date Lapsed</v>
+      </c>
+      <c r="J3" t="str">
+        <v>Total Pending</v>
+      </c>
+      <c r="K3" t="str">
+        <v>Pending &gt; 5 days</v>
+      </c>
+      <c r="L3" t="str">
+        <v>Verified</v>
+      </c>
+      <c r="M3" t="str">
+        <v>Not Verified</v>
+      </c>
+      <c r="N3" t="str">
+        <v>Found Ineligible for Final</v>
+      </c>
+      <c r="O3" t="str">
+        <v>Parked for Final Publication w.r.t. Notices Generated</v>
+      </c>
+      <c r="P3" t="str">
+        <v>Parked For Final Publication w.r.t. Others</v>
+      </c>
+    </row>
+    <row r="4">
       <c r="A4">
         <v>1</v>
       </c>
-      <c r="B4" t="s">
-        <v>19</v>
+      <c r="B4" t="str">
+        <v>25 - Haridwar</v>
       </c>
       <c r="C4">
         <v>51528</v>
@@ -844,22 +514,13 @@
       <c r="P4">
         <v>53812</v>
       </c>
-      <c r="Q4" s="2">
-        <v>12212</v>
-      </c>
-      <c r="R4" s="2">
-        <v>0</v>
-      </c>
-      <c r="S4" s="2">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="5" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="5">
       <c r="A5">
         <v>2</v>
       </c>
-      <c r="B5" t="s">
-        <v>20</v>
+      <c r="B5" t="str">
+        <v>26 - BHEL Ranipur</v>
       </c>
       <c r="C5">
         <v>53911</v>
@@ -903,22 +564,13 @@
       <c r="P5">
         <v>74848</v>
       </c>
-      <c r="Q5" s="2">
-        <v>16108</v>
-      </c>
-      <c r="R5" s="2">
-        <v>0</v>
-      </c>
-      <c r="S5" s="2">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="6" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="6">
       <c r="A6">
         <v>3</v>
       </c>
-      <c r="B6" t="s">
-        <v>21</v>
+      <c r="B6" t="str">
+        <v>27 - Jwalapur</v>
       </c>
       <c r="C6">
         <v>39773</v>
@@ -957,27 +609,18 @@
         <v>1827</v>
       </c>
       <c r="O6">
-        <v>37320</v>
+        <v>37324</v>
       </c>
       <c r="P6">
         <v>71989</v>
       </c>
-      <c r="Q6" s="2">
-        <v>17830</v>
-      </c>
-      <c r="R6" s="2">
-        <v>0</v>
-      </c>
-      <c r="S6" s="2">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="7" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="7">
       <c r="A7">
         <v>4</v>
       </c>
-      <c r="B7" t="s">
-        <v>22</v>
+      <c r="B7" t="str">
+        <v>28 - Bhagwanpur</v>
       </c>
       <c r="C7">
         <v>39463</v>
@@ -1021,22 +664,13 @@
       <c r="P7">
         <v>77581</v>
       </c>
-      <c r="Q7" s="2">
-        <v>20511</v>
-      </c>
-      <c r="R7" s="2">
-        <v>0</v>
-      </c>
-      <c r="S7" s="2">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="8" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="8">
       <c r="A8">
         <v>5</v>
       </c>
-      <c r="B8" t="s">
-        <v>23</v>
+      <c r="B8" t="str">
+        <v>29 - Jhabrera</v>
       </c>
       <c r="C8">
         <v>40552</v>
@@ -1075,27 +709,18 @@
         <v>1874</v>
       </c>
       <c r="O8">
-        <v>38041</v>
+        <v>38046</v>
       </c>
       <c r="P8">
         <v>73458</v>
       </c>
-      <c r="Q8" s="2">
-        <v>20788</v>
-      </c>
-      <c r="R8" s="2">
-        <v>0</v>
-      </c>
-      <c r="S8" s="2">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="9" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="9">
       <c r="A9">
         <v>6</v>
       </c>
-      <c r="B9" t="s">
-        <v>24</v>
+      <c r="B9" t="str">
+        <v>30 - Piran Kaliyar</v>
       </c>
       <c r="C9">
         <v>43273</v>
@@ -1139,22 +764,13 @@
       <c r="P9">
         <v>72913</v>
       </c>
-      <c r="Q9" s="2">
-        <v>18141</v>
-      </c>
-      <c r="R9" s="2">
-        <v>0</v>
-      </c>
-      <c r="S9" s="2">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="10" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="10">
       <c r="A10">
         <v>7</v>
       </c>
-      <c r="B10" t="s">
-        <v>25</v>
+      <c r="B10" t="str">
+        <v>31 - Roorkee</v>
       </c>
       <c r="C10">
         <v>36576</v>
@@ -1198,22 +814,13 @@
       <c r="P10">
         <v>53124</v>
       </c>
-      <c r="Q10" s="2">
-        <v>9498</v>
-      </c>
-      <c r="R10" s="2">
-        <v>0</v>
-      </c>
-      <c r="S10" s="2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="11" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="11">
       <c r="A11">
         <v>8</v>
       </c>
-      <c r="B11" t="s">
-        <v>26</v>
+      <c r="B11" t="str">
+        <v>32 - Khanpur</v>
       </c>
       <c r="C11">
         <v>50998</v>
@@ -1257,22 +864,13 @@
       <c r="P11">
         <v>84438</v>
       </c>
-      <c r="Q11" s="2">
-        <v>23477</v>
-      </c>
-      <c r="R11" s="2">
-        <v>0</v>
-      </c>
-      <c r="S11" s="2">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="12" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="12">
       <c r="A12">
         <v>9</v>
       </c>
-      <c r="B12" t="s">
-        <v>27</v>
+      <c r="B12" t="str">
+        <v>33 - Manglore</v>
       </c>
       <c r="C12">
         <v>40739</v>
@@ -1311,27 +909,18 @@
         <v>1133</v>
       </c>
       <c r="O12">
-        <v>39527</v>
+        <v>39579</v>
       </c>
       <c r="P12">
         <v>66685</v>
       </c>
-      <c r="Q12" s="2">
-        <v>17786</v>
-      </c>
-      <c r="R12" s="2">
-        <v>0</v>
-      </c>
-      <c r="S12" s="2">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="13" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="13">
       <c r="A13">
         <v>10</v>
       </c>
-      <c r="B13" t="s">
-        <v>28</v>
+      <c r="B13" t="str">
+        <v>34 - Laksar</v>
       </c>
       <c r="C13">
         <v>37031</v>
@@ -1375,22 +964,13 @@
       <c r="P13">
         <v>56564</v>
       </c>
-      <c r="Q13" s="2">
-        <v>16237</v>
-      </c>
-      <c r="R13" s="2">
-        <v>0</v>
-      </c>
-      <c r="S13" s="2">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="14" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="14">
       <c r="A14">
         <v>11</v>
       </c>
-      <c r="B14" t="s">
-        <v>29</v>
+      <c r="B14" t="str">
+        <v>35 - Haridwar Rural</v>
       </c>
       <c r="C14">
         <v>48966</v>
@@ -1420,36 +1000,27 @@
         <v>0</v>
       </c>
       <c r="L14">
-        <v>15263</v>
+        <v>15267</v>
       </c>
       <c r="M14">
         <v>1456</v>
       </c>
       <c r="N14">
-        <v>5844</v>
+        <v>5856</v>
       </c>
       <c r="O14">
-        <v>43059</v>
+        <v>43081</v>
       </c>
       <c r="P14">
         <v>77955</v>
       </c>
-      <c r="Q14" s="2">
-        <v>19716</v>
-      </c>
-      <c r="R14" s="2">
-        <v>0</v>
-      </c>
-      <c r="S14" s="2">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="15" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="15">
       <c r="A15">
         <v>12</v>
       </c>
-      <c r="B15" t="s">
-        <v>30</v>
+      <c r="B15" t="str">
+        <v>56 - Lalkuan</v>
       </c>
       <c r="C15">
         <v>42703</v>
@@ -1493,22 +1064,13 @@
       <c r="P15">
         <v>67178</v>
       </c>
-      <c r="Q15" s="2">
-        <v>4859</v>
-      </c>
-      <c r="R15" s="2">
-        <v>0</v>
-      </c>
-      <c r="S15" s="2">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="16" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="16">
       <c r="A16">
         <v>13</v>
       </c>
-      <c r="B16" t="s">
-        <v>31</v>
+      <c r="B16" t="str">
+        <v>57 - Bhimtal</v>
       </c>
       <c r="C16">
         <v>25549</v>
@@ -1552,22 +1114,13 @@
       <c r="P16">
         <v>71673</v>
       </c>
-      <c r="Q16" s="2">
-        <v>5197</v>
-      </c>
-      <c r="R16" s="2">
-        <v>0</v>
-      </c>
-      <c r="S16" s="2">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="17" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="17">
       <c r="A17">
         <v>14</v>
       </c>
-      <c r="B17" t="s">
-        <v>32</v>
+      <c r="B17" t="str">
+        <v>58 - Nainital</v>
       </c>
       <c r="C17">
         <v>27707</v>
@@ -1611,22 +1164,13 @@
       <c r="P17">
         <v>65457</v>
       </c>
-      <c r="Q17" s="2">
-        <v>5417</v>
-      </c>
-      <c r="R17" s="2">
-        <v>0</v>
-      </c>
-      <c r="S17" s="2">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="18" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="18">
       <c r="A18">
         <v>15</v>
       </c>
-      <c r="B18" t="s">
-        <v>33</v>
+      <c r="B18" t="str">
+        <v>59 - Haldwani</v>
       </c>
       <c r="C18">
         <v>47836</v>
@@ -1670,22 +1214,13 @@
       <c r="P18">
         <v>71475</v>
       </c>
-      <c r="Q18" s="2">
-        <v>6819</v>
-      </c>
-      <c r="R18" s="2">
-        <v>0</v>
-      </c>
-      <c r="S18" s="2">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="19" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="19">
       <c r="A19">
         <v>16</v>
       </c>
-      <c r="B19" t="s">
-        <v>34</v>
+      <c r="B19" t="str">
+        <v>60 - Kaladhungi</v>
       </c>
       <c r="C19">
         <v>56490</v>
@@ -1729,22 +1264,13 @@
       <c r="P19">
         <v>106392</v>
       </c>
-      <c r="Q19" s="2">
-        <v>6135</v>
-      </c>
-      <c r="R19" s="2">
-        <v>0</v>
-      </c>
-      <c r="S19" s="2">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="20" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="20">
       <c r="A20">
         <v>17</v>
       </c>
-      <c r="B20" t="s">
-        <v>35</v>
+      <c r="B20" t="str">
+        <v>61 - Ramnagar</v>
       </c>
       <c r="C20">
         <v>35022</v>
@@ -1788,22 +1314,13 @@
       <c r="P20">
         <v>75812</v>
       </c>
-      <c r="Q20" s="2">
-        <v>8984</v>
-      </c>
-      <c r="R20" s="2">
-        <v>0</v>
-      </c>
-      <c r="S20" s="2">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="21" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="21">
       <c r="A21">
         <v>18</v>
       </c>
-      <c r="B21" t="s">
-        <v>36</v>
+      <c r="B21" t="str">
+        <v>48 - Dwarahat</v>
       </c>
       <c r="C21">
         <v>16962</v>
@@ -1847,22 +1364,13 @@
       <c r="P21">
         <v>62460</v>
       </c>
-      <c r="Q21" s="2">
-        <v>3868</v>
-      </c>
-      <c r="R21" s="2">
-        <v>0</v>
-      </c>
-      <c r="S21" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="22">
       <c r="A22">
         <v>19</v>
       </c>
-      <c r="B22" t="s">
-        <v>37</v>
+      <c r="B22" t="str">
+        <v>49 - Salt</v>
       </c>
       <c r="C22">
         <v>18668</v>
@@ -1906,22 +1414,13 @@
       <c r="P22">
         <v>64099</v>
       </c>
-      <c r="Q22" s="2">
-        <v>4848</v>
-      </c>
-      <c r="R22" s="2">
-        <v>0</v>
-      </c>
-      <c r="S22" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="23">
       <c r="A23">
         <v>20</v>
       </c>
-      <c r="B23" t="s">
-        <v>38</v>
+      <c r="B23" t="str">
+        <v>50 - Ranikhet</v>
       </c>
       <c r="C23">
         <v>12020</v>
@@ -1965,22 +1464,13 @@
       <c r="P23">
         <v>57094</v>
       </c>
-      <c r="Q23" s="2">
-        <v>3541</v>
-      </c>
-      <c r="R23" s="2">
-        <v>0</v>
-      </c>
-      <c r="S23" s="2">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="24" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="24">
       <c r="A24">
         <v>21</v>
       </c>
-      <c r="B24" t="s">
-        <v>39</v>
+      <c r="B24" t="str">
+        <v>51 - Someshwar</v>
       </c>
       <c r="C24">
         <v>14056</v>
@@ -2024,22 +1514,13 @@
       <c r="P24">
         <v>65629</v>
       </c>
-      <c r="Q24" s="2">
-        <v>3492</v>
-      </c>
-      <c r="R24" s="2">
-        <v>0</v>
-      </c>
-      <c r="S24" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="25">
       <c r="A25">
         <v>22</v>
       </c>
-      <c r="B25" t="s">
-        <v>40</v>
+      <c r="B25" t="str">
+        <v>52 - Almora</v>
       </c>
       <c r="C25">
         <v>19266</v>
@@ -2083,22 +1564,13 @@
       <c r="P25">
         <v>57533</v>
       </c>
-      <c r="Q25" s="2">
-        <v>3231</v>
-      </c>
-      <c r="R25" s="2">
-        <v>0</v>
-      </c>
-      <c r="S25" s="2">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="26" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="26">
       <c r="A26">
         <v>23</v>
       </c>
-      <c r="B26" t="s">
-        <v>41</v>
+      <c r="B26" t="str">
+        <v>53 - Jageshwar</v>
       </c>
       <c r="C26">
         <v>17557</v>
@@ -2142,22 +1614,13 @@
       <c r="P26">
         <v>66594</v>
       </c>
-      <c r="Q26" s="2">
-        <v>3333</v>
-      </c>
-      <c r="R26" s="2">
-        <v>0</v>
-      </c>
-      <c r="S26" s="2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="27" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="27">
       <c r="A27">
         <v>24</v>
       </c>
-      <c r="B27" t="s">
-        <v>42</v>
+      <c r="B27" t="str">
+        <v>62 - Jaspur</v>
       </c>
       <c r="C27">
         <v>44276</v>
@@ -2193,7 +1656,7 @@
         <v>215</v>
       </c>
       <c r="N27">
-        <v>3278</v>
+        <v>3282</v>
       </c>
       <c r="O27">
         <v>41008</v>
@@ -2201,22 +1664,13 @@
       <c r="P27">
         <v>73109</v>
       </c>
-      <c r="Q27" s="2">
-        <v>12669</v>
-      </c>
-      <c r="R27" s="2">
-        <v>0</v>
-      </c>
-      <c r="S27" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="28">
       <c r="A28">
         <v>25</v>
       </c>
-      <c r="B28" t="s">
-        <v>43</v>
+      <c r="B28" t="str">
+        <v>63 - Kashipur</v>
       </c>
       <c r="C28">
         <v>54349</v>
@@ -2260,22 +1714,13 @@
       <c r="P28">
         <v>80620</v>
       </c>
-      <c r="Q28" s="2">
-        <v>13995</v>
-      </c>
-      <c r="R28" s="2">
-        <v>0</v>
-      </c>
-      <c r="S28" s="2">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="29" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="29">
       <c r="A29">
         <v>26</v>
       </c>
-      <c r="B29" t="s">
-        <v>44</v>
+      <c r="B29" t="str">
+        <v>64 - Bajpur</v>
       </c>
       <c r="C29">
         <v>47111</v>
@@ -2319,22 +1764,13 @@
       <c r="P29">
         <v>83836</v>
       </c>
-      <c r="Q29" s="2">
-        <v>14229</v>
-      </c>
-      <c r="R29" s="2">
-        <v>0</v>
-      </c>
-      <c r="S29" s="2">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="30" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="30">
       <c r="A30">
         <v>27</v>
       </c>
-      <c r="B30" t="s">
-        <v>45</v>
+      <c r="B30" t="str">
+        <v>65 - Gadarpur</v>
       </c>
       <c r="C30">
         <v>52653</v>
@@ -2378,22 +1814,13 @@
       <c r="P30">
         <v>86933</v>
       </c>
-      <c r="Q30" s="2">
-        <v>12564</v>
-      </c>
-      <c r="R30" s="2">
-        <v>0</v>
-      </c>
-      <c r="S30" s="2">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="31" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="31">
       <c r="A31">
         <v>28</v>
       </c>
-      <c r="B31" t="s">
-        <v>46</v>
+      <c r="B31" t="str">
+        <v>66 - Rudrapur</v>
       </c>
       <c r="C31">
         <v>91162</v>
@@ -2437,22 +1864,13 @@
       <c r="P31">
         <v>81642</v>
       </c>
-      <c r="Q31" s="2">
-        <v>14581</v>
-      </c>
-      <c r="R31" s="2">
-        <v>0</v>
-      </c>
-      <c r="S31" s="2">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="32" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="32">
       <c r="A32">
         <v>29</v>
       </c>
-      <c r="B32" t="s">
-        <v>47</v>
+      <c r="B32" t="str">
+        <v>67 - Kichha</v>
       </c>
       <c r="C32">
         <v>46728</v>
@@ -2491,27 +1909,18 @@
         <v>4391</v>
       </c>
       <c r="O32">
-        <v>42337</v>
+        <v>42344</v>
       </c>
       <c r="P32">
         <v>74810</v>
       </c>
-      <c r="Q32" s="2">
-        <v>11379</v>
-      </c>
-      <c r="R32" s="2">
-        <v>0</v>
-      </c>
-      <c r="S32" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="33">
       <c r="A33">
         <v>30</v>
       </c>
-      <c r="B33" t="s">
-        <v>48</v>
+      <c r="B33" t="str">
+        <v>68 - Sitarganj</v>
       </c>
       <c r="C33">
         <v>40230</v>
@@ -2555,22 +1964,13 @@
       <c r="P33">
         <v>76969</v>
       </c>
-      <c r="Q33" s="2">
-        <v>6678</v>
-      </c>
-      <c r="R33" s="2">
-        <v>0</v>
-      </c>
-      <c r="S33" s="2">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="34" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="34">
       <c r="A34">
         <v>31</v>
       </c>
-      <c r="B34" t="s">
-        <v>49</v>
+      <c r="B34" t="str">
+        <v>69 - Nanakmatta</v>
       </c>
       <c r="C34">
         <v>36542</v>
@@ -2614,22 +2014,13 @@
       <c r="P34">
         <v>74624</v>
       </c>
-      <c r="Q34" s="2">
-        <v>7137</v>
-      </c>
-      <c r="R34" s="2">
-        <v>0</v>
-      </c>
-      <c r="S34" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="35">
       <c r="A35">
         <v>32</v>
       </c>
-      <c r="B35" t="s">
-        <v>50</v>
+      <c r="B35" t="str">
+        <v>70 - Khatima</v>
       </c>
       <c r="C35">
         <v>33564</v>
@@ -2673,22 +2064,13 @@
       <c r="P35">
         <v>76464</v>
       </c>
-      <c r="Q35" s="2">
-        <v>8879</v>
-      </c>
-      <c r="R35" s="2">
-        <v>0</v>
-      </c>
-      <c r="S35" s="2">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="36" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="36">
       <c r="A36">
         <v>33</v>
       </c>
-      <c r="B36" t="s">
-        <v>51</v>
+      <c r="B36" t="str">
+        <v>42 - Dharchula</v>
       </c>
       <c r="C36">
         <v>20905</v>
@@ -2732,22 +2114,13 @@
       <c r="P36">
         <v>60419</v>
       </c>
-      <c r="Q36" s="2">
-        <v>3855</v>
-      </c>
-      <c r="R36" s="2">
-        <v>0</v>
-      </c>
-      <c r="S36" s="2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="37" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="37">
       <c r="A37">
         <v>34</v>
       </c>
-      <c r="B37" t="s">
-        <v>52</v>
+      <c r="B37" t="str">
+        <v>43 - Didihat</v>
       </c>
       <c r="C37">
         <v>17692</v>
@@ -2791,22 +2164,13 @@
       <c r="P37">
         <v>57832</v>
       </c>
-      <c r="Q37" s="2">
-        <v>4036</v>
-      </c>
-      <c r="R37" s="2">
-        <v>0</v>
-      </c>
-      <c r="S37" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="38" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="38">
       <c r="A38">
         <v>35</v>
       </c>
-      <c r="B38" t="s">
-        <v>53</v>
+      <c r="B38" t="str">
+        <v>44 - Pithoragarh</v>
       </c>
       <c r="C38">
         <v>29110</v>
@@ -2850,22 +2214,13 @@
       <c r="P38">
         <v>63038</v>
       </c>
-      <c r="Q38" s="2">
-        <v>5135</v>
-      </c>
-      <c r="R38" s="2">
-        <v>0</v>
-      </c>
-      <c r="S38" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="39" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="39">
       <c r="A39">
         <v>36</v>
       </c>
-      <c r="B39" t="s">
-        <v>54</v>
+      <c r="B39" t="str">
+        <v>45 - Gangolihat</v>
       </c>
       <c r="C39">
         <v>21367</v>
@@ -2909,22 +2264,13 @@
       <c r="P39">
         <v>71133</v>
       </c>
-      <c r="Q39" s="2">
-        <v>5903</v>
-      </c>
-      <c r="R39" s="2">
-        <v>0</v>
-      </c>
-      <c r="S39" s="2">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="40" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="40">
       <c r="A40">
         <v>37</v>
       </c>
-      <c r="B40" t="s">
-        <v>55</v>
+      <c r="B40" t="str">
+        <v>46 - Kapkot</v>
       </c>
       <c r="C40">
         <v>18905</v>
@@ -2968,22 +2314,13 @@
       <c r="P40">
         <v>73242</v>
       </c>
-      <c r="Q40" s="2">
-        <v>3824</v>
-      </c>
-      <c r="R40" s="2">
-        <v>0</v>
-      </c>
-      <c r="S40" s="2">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="41" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="41">
       <c r="A41">
         <v>38</v>
       </c>
-      <c r="B41" t="s">
-        <v>56</v>
+      <c r="B41" t="str">
+        <v>47 - Bageshwar</v>
       </c>
       <c r="C41">
         <v>23521</v>
@@ -3027,22 +2364,13 @@
       <c r="P41">
         <v>85251</v>
       </c>
-      <c r="Q41" s="2">
-        <v>6015</v>
-      </c>
-      <c r="R41" s="2">
-        <v>0</v>
-      </c>
-      <c r="S41" s="2">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="42" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="42">
       <c r="A42">
         <v>39</v>
       </c>
-      <c r="B42" t="s">
-        <v>57</v>
+      <c r="B42" t="str">
+        <v>54 - Lohaghat</v>
       </c>
       <c r="C42">
         <v>27565</v>
@@ -3086,22 +2414,13 @@
       <c r="P42">
         <v>68615</v>
       </c>
-      <c r="Q42" s="2">
-        <v>4708</v>
-      </c>
-      <c r="R42" s="2">
-        <v>0</v>
-      </c>
-      <c r="S42" s="2">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="43" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="43">
       <c r="A43">
         <v>40</v>
       </c>
-      <c r="B43" t="s">
-        <v>58</v>
+      <c r="B43" t="str">
+        <v>55 - Champawat</v>
       </c>
       <c r="C43">
         <v>29700</v>
@@ -3145,22 +2464,13 @@
       <c r="P43">
         <v>63012</v>
       </c>
-      <c r="Q43" s="2">
-        <v>5219</v>
-      </c>
-      <c r="R43" s="2">
-        <v>0</v>
-      </c>
-      <c r="S43" s="2">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="44" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="44">
       <c r="A44">
         <v>41</v>
       </c>
-      <c r="B44" t="s">
-        <v>59</v>
+      <c r="B44" t="str">
+        <v>4 - Badrinath</v>
       </c>
       <c r="C44">
         <v>21900</v>
@@ -3204,22 +2514,13 @@
       <c r="P44">
         <v>68393</v>
       </c>
-      <c r="Q44" s="2">
-        <v>7659</v>
-      </c>
-      <c r="R44" s="2">
-        <v>0</v>
-      </c>
-      <c r="S44" s="2">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="45" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="45">
       <c r="A45">
         <v>42</v>
       </c>
-      <c r="B45" t="s">
-        <v>60</v>
+      <c r="B45" t="str">
+        <v>5 - Tharali</v>
       </c>
       <c r="C45">
         <v>19935</v>
@@ -3263,22 +2564,13 @@
       <c r="P45">
         <v>76287</v>
       </c>
-      <c r="Q45" s="2">
-        <v>6998</v>
-      </c>
-      <c r="R45" s="2">
-        <v>0</v>
-      </c>
-      <c r="S45" s="2">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="46" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="46">
       <c r="A46">
         <v>43</v>
       </c>
-      <c r="B46" t="s">
-        <v>61</v>
+      <c r="B46" t="str">
+        <v>6 - Karanprayag</v>
       </c>
       <c r="C46">
         <v>21512</v>
@@ -3322,22 +2614,13 @@
       <c r="P46">
         <v>64160</v>
       </c>
-      <c r="Q46" s="2">
-        <v>7548</v>
-      </c>
-      <c r="R46" s="2">
-        <v>0</v>
-      </c>
-      <c r="S46" s="2">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="47" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="47">
       <c r="A47">
         <v>44</v>
       </c>
-      <c r="B47" t="s">
-        <v>62</v>
+      <c r="B47" t="str">
+        <v>1 - Purola</v>
       </c>
       <c r="C47">
         <v>22426</v>
@@ -3381,22 +2664,13 @@
       <c r="P47">
         <v>49875</v>
       </c>
-      <c r="Q47" s="2">
-        <v>5046</v>
-      </c>
-      <c r="R47" s="2">
-        <v>0</v>
-      </c>
-      <c r="S47" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="48" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="48">
       <c r="A48">
         <v>45</v>
       </c>
-      <c r="B48" t="s">
-        <v>63</v>
+      <c r="B48" t="str">
+        <v>2 - Yamunotri</v>
       </c>
       <c r="C48">
         <v>19641</v>
@@ -3440,22 +2714,13 @@
       <c r="P48">
         <v>54142</v>
       </c>
-      <c r="Q48" s="2">
-        <v>4623</v>
-      </c>
-      <c r="R48" s="2">
-        <v>0</v>
-      </c>
-      <c r="S48" s="2">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="49" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="49">
       <c r="A49">
         <v>46</v>
       </c>
-      <c r="B49" t="s">
-        <v>64</v>
+      <c r="B49" t="str">
+        <v>3 - Gangotri</v>
       </c>
       <c r="C49">
         <v>21651</v>
@@ -3499,22 +2764,13 @@
       <c r="P49">
         <v>55376</v>
       </c>
-      <c r="Q49" s="2">
-        <v>5057</v>
-      </c>
-      <c r="R49" s="2">
-        <v>0</v>
-      </c>
-      <c r="S49" s="2">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="50" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="50">
       <c r="A50">
         <v>47</v>
       </c>
-      <c r="B50" t="s">
-        <v>65</v>
+      <c r="B50" t="str">
+        <v>7 - Kedarnath</v>
       </c>
       <c r="C50">
         <v>21936</v>
@@ -3558,22 +2814,13 @@
       <c r="P50">
         <v>63298</v>
       </c>
-      <c r="Q50" s="2">
-        <v>7292</v>
-      </c>
-      <c r="R50" s="2">
-        <v>0</v>
-      </c>
-      <c r="S50" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="51" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="51">
       <c r="A51">
         <v>48</v>
       </c>
-      <c r="B51" t="s">
-        <v>66</v>
+      <c r="B51" t="str">
+        <v>8 - Rudraprayag</v>
       </c>
       <c r="C51">
         <v>23798</v>
@@ -3617,22 +2864,13 @@
       <c r="P51">
         <v>71754</v>
       </c>
-      <c r="Q51" s="2">
-        <v>7715</v>
-      </c>
-      <c r="R51" s="2">
-        <v>0</v>
-      </c>
-      <c r="S51" s="2">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="52" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="52">
       <c r="A52">
         <v>49</v>
       </c>
-      <c r="B52" t="s">
-        <v>67</v>
+      <c r="B52" t="str">
+        <v>9 - Ghansali</v>
       </c>
       <c r="C52">
         <v>21094</v>
@@ -3676,22 +2914,13 @@
       <c r="P52">
         <v>63987</v>
       </c>
-      <c r="Q52" s="2">
-        <v>5655</v>
-      </c>
-      <c r="R52" s="2">
-        <v>0</v>
-      </c>
-      <c r="S52" s="2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="53" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="53">
       <c r="A53">
         <v>50</v>
       </c>
-      <c r="B53" t="s">
-        <v>68</v>
+      <c r="B53" t="str">
+        <v>10 - Devprayag</v>
       </c>
       <c r="C53">
         <v>19131</v>
@@ -3735,22 +2964,13 @@
       <c r="P53">
         <v>56306</v>
       </c>
-      <c r="Q53" s="2">
-        <v>6551</v>
-      </c>
-      <c r="R53" s="2">
-        <v>0</v>
-      </c>
-      <c r="S53" s="2">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="54" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="54">
       <c r="A54">
         <v>51</v>
       </c>
-      <c r="B54" t="s">
-        <v>69</v>
+      <c r="B54" t="str">
+        <v>11 - Narendranagar</v>
       </c>
       <c r="C54">
         <v>20758</v>
@@ -3794,22 +3014,13 @@
       <c r="P54">
         <v>58440</v>
       </c>
-      <c r="Q54" s="2">
-        <v>7347</v>
-      </c>
-      <c r="R54" s="2">
-        <v>0</v>
-      </c>
-      <c r="S54" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="55" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="55">
       <c r="A55">
         <v>52</v>
       </c>
-      <c r="B55" t="s">
-        <v>70</v>
+      <c r="B55" t="str">
+        <v>12 - Pratapnagar</v>
       </c>
       <c r="C55">
         <v>16022</v>
@@ -3853,22 +3064,13 @@
       <c r="P55">
         <v>58215</v>
       </c>
-      <c r="Q55" s="2">
-        <v>5098</v>
-      </c>
-      <c r="R55" s="2">
-        <v>0</v>
-      </c>
-      <c r="S55" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="56" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="56">
       <c r="A56">
         <v>53</v>
       </c>
-      <c r="B56" t="s">
-        <v>71</v>
+      <c r="B56" t="str">
+        <v>13 - Tehri</v>
       </c>
       <c r="C56">
         <v>19256</v>
@@ -3892,7 +3094,7 @@
         <v>0</v>
       </c>
       <c r="J56">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K56">
         <v>0</v>
@@ -3904,7 +3106,7 @@
         <v>3</v>
       </c>
       <c r="N56">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="O56">
         <v>18805</v>
@@ -3912,22 +3114,13 @@
       <c r="P56">
         <v>47621</v>
       </c>
-      <c r="Q56" s="2">
-        <v>4882</v>
-      </c>
-      <c r="R56" s="2">
-        <v>0</v>
-      </c>
-      <c r="S56" s="2">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="57" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="57">
       <c r="A57">
         <v>54</v>
       </c>
-      <c r="B57" t="s">
-        <v>72</v>
+      <c r="B57" t="str">
+        <v>14 - Dhanolti</v>
       </c>
       <c r="C57">
         <v>21240</v>
@@ -3971,22 +3164,13 @@
       <c r="P57">
         <v>61556</v>
       </c>
-      <c r="Q57" s="2">
-        <v>6870</v>
-      </c>
-      <c r="R57" s="2">
-        <v>0</v>
-      </c>
-      <c r="S57" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="58" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="58">
       <c r="A58">
         <v>55</v>
       </c>
-      <c r="B58" t="s">
-        <v>73</v>
+      <c r="B58" t="str">
+        <v>36 - Yamkeshwar</v>
       </c>
       <c r="C58">
         <v>22819</v>
@@ -4030,22 +3214,13 @@
       <c r="P58">
         <v>57577</v>
       </c>
-      <c r="Q58" s="2">
-        <v>8884</v>
-      </c>
-      <c r="R58" s="2">
-        <v>0</v>
-      </c>
-      <c r="S58" s="2">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="59" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="59">
       <c r="A59">
         <v>56</v>
       </c>
-      <c r="B59" t="s">
-        <v>74</v>
+      <c r="B59" t="str">
+        <v>37 - Pauri</v>
       </c>
       <c r="C59">
         <v>18776</v>
@@ -4089,22 +3264,13 @@
       <c r="P59">
         <v>60495</v>
       </c>
-      <c r="Q59" s="2">
-        <v>8028</v>
-      </c>
-      <c r="R59" s="2">
-        <v>0</v>
-      </c>
-      <c r="S59" s="2">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="60" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="60">
       <c r="A60">
         <v>57</v>
       </c>
-      <c r="B60" t="s">
-        <v>75</v>
+      <c r="B60" t="str">
+        <v>38 - Srinagar</v>
       </c>
       <c r="C60">
         <v>23749</v>
@@ -4148,22 +3314,13 @@
       <c r="P60">
         <v>70140</v>
       </c>
-      <c r="Q60" s="2">
-        <v>7415</v>
-      </c>
-      <c r="R60" s="2">
-        <v>0</v>
-      </c>
-      <c r="S60" s="2">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="61" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="61">
       <c r="A61">
         <v>58</v>
       </c>
-      <c r="B61" t="s">
-        <v>76</v>
+      <c r="B61" t="str">
+        <v>39 - Chaubattakhal</v>
       </c>
       <c r="C61">
         <v>22069</v>
@@ -4207,22 +3364,13 @@
       <c r="P61">
         <v>55240</v>
       </c>
-      <c r="Q61" s="2">
-        <v>7927</v>
-      </c>
-      <c r="R61" s="2">
-        <v>1</v>
-      </c>
-      <c r="S61" s="2">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="62" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="62">
       <c r="A62">
         <v>59</v>
       </c>
-      <c r="B62" t="s">
-        <v>77</v>
+      <c r="B62" t="str">
+        <v>40 - Lansdowne</v>
       </c>
       <c r="C62">
         <v>15800</v>
@@ -4266,22 +3414,13 @@
       <c r="P62">
         <v>51334</v>
       </c>
-      <c r="Q62" s="2">
-        <v>6917</v>
-      </c>
-      <c r="R62" s="2">
-        <v>0</v>
-      </c>
-      <c r="S62" s="2">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="63" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="63">
       <c r="A63">
         <v>60</v>
       </c>
-      <c r="B63" t="s">
-        <v>78</v>
+      <c r="B63" t="str">
+        <v>41 - Kotdwar</v>
       </c>
       <c r="C63">
         <v>36754</v>
@@ -4325,22 +3464,13 @@
       <c r="P63">
         <v>68696</v>
       </c>
-      <c r="Q63" s="2">
-        <v>9766</v>
-      </c>
-      <c r="R63" s="2">
-        <v>0</v>
-      </c>
-      <c r="S63" s="2">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="64" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="64">
       <c r="A64">
         <v>61</v>
       </c>
-      <c r="B64" t="s">
-        <v>79</v>
+      <c r="B64" t="str">
+        <v>15 - Chakrata</v>
       </c>
       <c r="C64">
         <v>42048</v>
@@ -4384,22 +3514,13 @@
       <c r="P64">
         <v>60527</v>
       </c>
-      <c r="Q64" s="2">
-        <v>5985</v>
-      </c>
-      <c r="R64" s="2">
-        <v>0</v>
-      </c>
-      <c r="S64" s="2">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="65" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="65">
       <c r="A65">
         <v>62</v>
       </c>
-      <c r="B65" t="s">
-        <v>80</v>
+      <c r="B65" t="str">
+        <v>16 - Vikasnagar</v>
       </c>
       <c r="C65">
         <v>41389</v>
@@ -4443,22 +3564,13 @@
       <c r="P65">
         <v>58527</v>
       </c>
-      <c r="Q65" s="2">
-        <v>13282</v>
-      </c>
-      <c r="R65" s="2">
-        <v>0</v>
-      </c>
-      <c r="S65" s="2">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="66" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="66">
       <c r="A66">
         <v>63</v>
       </c>
-      <c r="B66" t="s">
-        <v>81</v>
+      <c r="B66" t="str">
+        <v>17 - Sahaspur</v>
       </c>
       <c r="C66">
         <v>67362</v>
@@ -4502,22 +3614,13 @@
       <c r="P66">
         <v>93810</v>
       </c>
-      <c r="Q66" s="2">
-        <v>17742</v>
-      </c>
-      <c r="R66" s="2">
-        <v>0</v>
-      </c>
-      <c r="S66" s="2">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="67" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="67">
       <c r="A67">
         <v>64</v>
       </c>
-      <c r="B67" t="s">
-        <v>82</v>
+      <c r="B67" t="str">
+        <v>18 - Dharmpur</v>
       </c>
       <c r="C67">
         <v>68828</v>
@@ -4561,22 +3664,13 @@
       <c r="P67">
         <v>78032</v>
       </c>
-      <c r="Q67" s="2">
-        <v>9807</v>
-      </c>
-      <c r="R67" s="2">
-        <v>0</v>
-      </c>
-      <c r="S67" s="2">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="68" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="68">
       <c r="A68">
         <v>65</v>
       </c>
-      <c r="B68" t="s">
-        <v>83</v>
+      <c r="B68" t="str">
+        <v>19 - Raipur</v>
       </c>
       <c r="C68">
         <v>65397</v>
@@ -4620,22 +3714,13 @@
       <c r="P68">
         <v>71325</v>
       </c>
-      <c r="Q68" s="2">
-        <v>7850</v>
-      </c>
-      <c r="R68" s="2">
-        <v>0</v>
-      </c>
-      <c r="S68" s="2">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="69" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="69">
       <c r="A69">
         <v>66</v>
       </c>
-      <c r="B69" t="s">
-        <v>84</v>
+      <c r="B69" t="str">
+        <v>20 - Rajpur Road</v>
       </c>
       <c r="C69">
         <v>43938</v>
@@ -4679,22 +3764,13 @@
       <c r="P69">
         <v>36118</v>
       </c>
-      <c r="Q69" s="2">
-        <v>6528</v>
-      </c>
-      <c r="R69" s="2">
-        <v>0</v>
-      </c>
-      <c r="S69" s="2">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="70" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="70">
       <c r="A70">
         <v>67</v>
       </c>
-      <c r="B70" t="s">
-        <v>85</v>
+      <c r="B70" t="str">
+        <v>21 - Dehradun Cantonment</v>
       </c>
       <c r="C70">
         <v>47711</v>
@@ -4738,22 +3814,13 @@
       <c r="P70">
         <v>42051</v>
       </c>
-      <c r="Q70" s="2">
-        <v>5798</v>
-      </c>
-      <c r="R70" s="2">
-        <v>0</v>
-      </c>
-      <c r="S70" s="2">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="71" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="71">
       <c r="A71">
         <v>68</v>
       </c>
-      <c r="B71" t="s">
-        <v>86</v>
+      <c r="B71" t="str">
+        <v>22 - Mussoorie</v>
       </c>
       <c r="C71">
         <v>50963</v>
@@ -4797,22 +3864,13 @@
       <c r="P71">
         <v>49140</v>
       </c>
-      <c r="Q71" s="2">
-        <v>6782</v>
-      </c>
-      <c r="R71" s="2">
-        <v>0</v>
-      </c>
-      <c r="S71" s="2">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="72" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="72">
       <c r="A72">
         <v>69</v>
       </c>
-      <c r="B72" t="s">
-        <v>87</v>
+      <c r="B72" t="str">
+        <v>23 - Doiwala</v>
       </c>
       <c r="C72">
         <v>61543</v>
@@ -4856,22 +3914,13 @@
       <c r="P72">
         <v>85505</v>
       </c>
-      <c r="Q72" s="2">
-        <v>12340</v>
-      </c>
-      <c r="R72" s="2">
-        <v>0</v>
-      </c>
-      <c r="S72" s="2">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="73" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="73">
       <c r="A73">
         <v>70</v>
       </c>
-      <c r="B73" t="s">
-        <v>88</v>
+      <c r="B73" t="str">
+        <v>24 - Rishikesh</v>
       </c>
       <c r="C73">
         <v>58915</v>
@@ -4915,21 +3964,11 @@
       <c r="P73">
         <v>67666</v>
       </c>
-      <c r="Q73" s="2">
-        <v>10010</v>
-      </c>
-      <c r="R73" s="2">
-        <v>0</v>
-      </c>
-      <c r="S73" s="2">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="74" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A74" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="B74" s="1"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="str">
+        <v>Total</v>
+      </c>
       <c r="C74">
         <v>2430387</v>
       </c>
@@ -4952,42 +3991,29 @@
         <v>0</v>
       </c>
       <c r="J74">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K74">
         <v>3</v>
       </c>
       <c r="L74">
-        <v>625500</v>
+        <v>625504</v>
       </c>
       <c r="M74">
         <v>8318</v>
       </c>
       <c r="N74">
-        <v>96939</v>
+        <v>96956</v>
       </c>
       <c r="O74">
-        <v>2330677</v>
+        <v>2330767</v>
       </c>
       <c r="P74">
         <v>4701905</v>
       </c>
-      <c r="Q74" s="2">
-        <v>626236</v>
-      </c>
-      <c r="R74" s="2">
-        <v>1</v>
-      </c>
-      <c r="S74" s="2">
-        <v>3445</v>
-      </c>
-    </row>
-    <row r="75" spans="1:19" ht="15.75" x14ac:dyDescent="0.25"/>
-    <row r="76" spans="1:19" ht="15.75" x14ac:dyDescent="0.25"/>
+    </row>
   </sheetData>
-  <mergeCells count="12">
-    <mergeCell ref="A74:B74"/>
-    <mergeCell ref="Q2:S2"/>
+  <mergeCells count="11">
     <mergeCell ref="A1:Q1"/>
     <mergeCell ref="A2:A3"/>
     <mergeCell ref="B2:B3"/>
@@ -4998,10 +4024,10 @@
     <mergeCell ref="G2:I2"/>
     <mergeCell ref="J2:M2"/>
     <mergeCell ref="N2:P2"/>
+    <mergeCell ref="A74:B74"/>
   </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="A2:P74 B1:P1" numberStoredAsText="1"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:P74"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/Notice.xlsx
+++ b/Notice.xlsx
@@ -1,41 +1,317 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr codeName="ThisWorkbook"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Downloads\New folder (13)\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98CD1CAD-FA1B-40E1-94E9-0E5F615F421D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
-  <metadataTypes count="1">
-    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLDAPR" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
-          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <cellMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </cellMetadata>
-</metadata>
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="95">
+  <si>
+    <t>Notice &amp; Hearing Report</t>
+  </si>
+  <si>
+    <t>S. No.</t>
+  </si>
+  <si>
+    <t>AC No. - AC Name</t>
+  </si>
+  <si>
+    <t>Notice Generated</t>
+  </si>
+  <si>
+    <t>Pending for Notice Generation</t>
+  </si>
+  <si>
+    <t>Notice Delivered</t>
+  </si>
+  <si>
+    <t>Notices pending delivery</t>
+  </si>
+  <si>
+    <t>Hearing</t>
+  </si>
+  <si>
+    <t>DEO Status</t>
+  </si>
+  <si>
+    <t>ERO/AERO Status</t>
+  </si>
+  <si>
+    <t>Hearing Held</t>
+  </si>
+  <si>
+    <t>Hearing Date Lapsed</t>
+  </si>
+  <si>
+    <t>Reschedule Date Lapsed</t>
+  </si>
+  <si>
+    <t>Total Pending</t>
+  </si>
+  <si>
+    <t>Pending &gt; 5 days</t>
+  </si>
+  <si>
+    <t>Verified</t>
+  </si>
+  <si>
+    <t>Not Verified</t>
+  </si>
+  <si>
+    <t>Found Ineligible for Final</t>
+  </si>
+  <si>
+    <t>Parked for Final Publication w.r.t. Notices Generated</t>
+  </si>
+  <si>
+    <t>Parked For Final Publication w.r.t. Others</t>
+  </si>
+  <si>
+    <t>25 - Haridwar</t>
+  </si>
+  <si>
+    <t>26 - BHEL Ranipur</t>
+  </si>
+  <si>
+    <t>27 - Jwalapur</t>
+  </si>
+  <si>
+    <t>28 - Bhagwanpur</t>
+  </si>
+  <si>
+    <t>29 - Jhabrera</t>
+  </si>
+  <si>
+    <t>30 - Piran Kaliyar</t>
+  </si>
+  <si>
+    <t>31 - Roorkee</t>
+  </si>
+  <si>
+    <t>32 - Khanpur</t>
+  </si>
+  <si>
+    <t>33 - Manglore</t>
+  </si>
+  <si>
+    <t>34 - Laksar</t>
+  </si>
+  <si>
+    <t>35 - Haridwar Rural</t>
+  </si>
+  <si>
+    <t>56 - Lalkuan</t>
+  </si>
+  <si>
+    <t>57 - Bhimtal</t>
+  </si>
+  <si>
+    <t>58 - Nainital</t>
+  </si>
+  <si>
+    <t>59 - Haldwani</t>
+  </si>
+  <si>
+    <t>60 - Kaladhungi</t>
+  </si>
+  <si>
+    <t>61 - Ramnagar</t>
+  </si>
+  <si>
+    <t>48 - Dwarahat</t>
+  </si>
+  <si>
+    <t>49 - Salt</t>
+  </si>
+  <si>
+    <t>50 - Ranikhet</t>
+  </si>
+  <si>
+    <t>51 - Someshwar</t>
+  </si>
+  <si>
+    <t>52 - Almora</t>
+  </si>
+  <si>
+    <t>53 - Jageshwar</t>
+  </si>
+  <si>
+    <t>62 - Jaspur</t>
+  </si>
+  <si>
+    <t>63 - Kashipur</t>
+  </si>
+  <si>
+    <t>64 - Bajpur</t>
+  </si>
+  <si>
+    <t>65 - Gadarpur</t>
+  </si>
+  <si>
+    <t>66 - Rudrapur</t>
+  </si>
+  <si>
+    <t>67 - Kichha</t>
+  </si>
+  <si>
+    <t>68 - Sitarganj</t>
+  </si>
+  <si>
+    <t>69 - Nanakmatta</t>
+  </si>
+  <si>
+    <t>70 - Khatima</t>
+  </si>
+  <si>
+    <t>42 - Dharchula</t>
+  </si>
+  <si>
+    <t>43 - Didihat</t>
+  </si>
+  <si>
+    <t>44 - Pithoragarh</t>
+  </si>
+  <si>
+    <t>45 - Gangolihat</t>
+  </si>
+  <si>
+    <t>46 - Kapkot</t>
+  </si>
+  <si>
+    <t>47 - Bageshwar</t>
+  </si>
+  <si>
+    <t>54 - Lohaghat</t>
+  </si>
+  <si>
+    <t>55 - Champawat</t>
+  </si>
+  <si>
+    <t>4 - Badrinath</t>
+  </si>
+  <si>
+    <t>5 - Tharali</t>
+  </si>
+  <si>
+    <t>6 - Karanprayag</t>
+  </si>
+  <si>
+    <t>1 - Purola</t>
+  </si>
+  <si>
+    <t>2 - Yamunotri</t>
+  </si>
+  <si>
+    <t>3 - Gangotri</t>
+  </si>
+  <si>
+    <t>7 - Kedarnath</t>
+  </si>
+  <si>
+    <t>8 - Rudraprayag</t>
+  </si>
+  <si>
+    <t>9 - Ghansali</t>
+  </si>
+  <si>
+    <t>10 - Devprayag</t>
+  </si>
+  <si>
+    <t>11 - Narendranagar</t>
+  </si>
+  <si>
+    <t>12 - Pratapnagar</t>
+  </si>
+  <si>
+    <t>13 - Tehri</t>
+  </si>
+  <si>
+    <t>14 - Dhanolti</t>
+  </si>
+  <si>
+    <t>36 - Yamkeshwar</t>
+  </si>
+  <si>
+    <t>37 - Pauri</t>
+  </si>
+  <si>
+    <t>38 - Srinagar</t>
+  </si>
+  <si>
+    <t>39 - Chaubattakhal</t>
+  </si>
+  <si>
+    <t>40 - Lansdowne</t>
+  </si>
+  <si>
+    <t>41 - Kotdwar</t>
+  </si>
+  <si>
+    <t>15 - Chakrata</t>
+  </si>
+  <si>
+    <t>16 - Vikasnagar</t>
+  </si>
+  <si>
+    <t>17 - Sahaspur</t>
+  </si>
+  <si>
+    <t>18 - Dharmpur</t>
+  </si>
+  <si>
+    <t>19 - Raipur</t>
+  </si>
+  <si>
+    <t>20 - Rajpur Road</t>
+  </si>
+  <si>
+    <t>21 - Dehradun Cantonment</t>
+  </si>
+  <si>
+    <t>22 - Mussoorie</t>
+  </si>
+  <si>
+    <t>23 - Doiwala</t>
+  </si>
+  <si>
+    <t>24 - Rishikesh</t>
+  </si>
+  <si>
+    <t>Total</t>
+  </si>
+  <si>
+    <t>DSE with UP</t>
+  </si>
+  <si>
+    <t>Electors having DSE with UP</t>
+  </si>
+  <si>
+    <t>Form 7 Generated</t>
+  </si>
+  <si>
+    <t>No Action Required</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="1">
-    <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
-  </numFmts>
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -64,14 +340,24 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+  <cellXfs count="3">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -396,81 +682,125 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P74"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:S76"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Notice &amp; Hearing Report</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>S. No.</v>
-      </c>
-      <c r="B2" t="str">
-        <v>AC No. - AC Name</v>
-      </c>
-      <c r="C2" t="str">
-        <v>Notice Generated</v>
-      </c>
-      <c r="D2" t="str">
-        <v>Pending for Notice Generation</v>
-      </c>
-      <c r="E2" t="str">
-        <v>Notice Delivered</v>
-      </c>
-      <c r="F2" t="str">
-        <v>Notices pending delivery</v>
-      </c>
-      <c r="G2" t="str">
-        <v>Hearing</v>
-      </c>
-      <c r="J2" t="str">
-        <v>DEO Status</v>
-      </c>
-      <c r="N2" t="str">
-        <v>ERO/AERO Status</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="G3" t="str">
-        <v>Hearing Held</v>
-      </c>
-      <c r="H3" t="str">
-        <v>Hearing Date Lapsed</v>
-      </c>
-      <c r="I3" t="str">
-        <v>Reschedule Date Lapsed</v>
-      </c>
-      <c r="J3" t="str">
-        <v>Total Pending</v>
-      </c>
-      <c r="K3" t="str">
-        <v>Pending &gt; 5 days</v>
-      </c>
-      <c r="L3" t="str">
-        <v>Verified</v>
-      </c>
-      <c r="M3" t="str">
-        <v>Not Verified</v>
-      </c>
-      <c r="N3" t="str">
-        <v>Found Ineligible for Final</v>
-      </c>
-      <c r="O3" t="str">
-        <v>Parked for Final Publication w.r.t. Notices Generated</v>
-      </c>
-      <c r="P3" t="str">
-        <v>Parked For Final Publication w.r.t. Others</v>
-      </c>
-    </row>
-    <row r="4">
+    <row r="1" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1"/>
+      <c r="I1" s="1"/>
+      <c r="J1" s="1"/>
+      <c r="K1" s="1"/>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1"/>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="K2" s="1"/>
+      <c r="L2" s="1"/>
+      <c r="M2" s="1"/>
+      <c r="N2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="O2" s="1"/>
+      <c r="P2" s="1"/>
+      <c r="Q2" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="R2" s="1"/>
+      <c r="S2" s="1"/>
+    </row>
+    <row r="3" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A3" s="1"/>
+      <c r="B3" s="1"/>
+      <c r="C3" s="1"/>
+      <c r="D3" s="1"/>
+      <c r="E3" s="1"/>
+      <c r="F3" s="1"/>
+      <c r="G3" t="s">
+        <v>10</v>
+      </c>
+      <c r="H3" t="s">
+        <v>11</v>
+      </c>
+      <c r="I3" t="s">
+        <v>12</v>
+      </c>
+      <c r="J3" t="s">
+        <v>13</v>
+      </c>
+      <c r="K3" t="s">
+        <v>14</v>
+      </c>
+      <c r="L3" t="s">
+        <v>15</v>
+      </c>
+      <c r="M3" t="s">
+        <v>16</v>
+      </c>
+      <c r="N3" t="s">
+        <v>17</v>
+      </c>
+      <c r="O3" t="s">
+        <v>18</v>
+      </c>
+      <c r="P3" t="s">
+        <v>19</v>
+      </c>
+      <c r="Q3" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="R3" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="S3" s="2" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>1</v>
       </c>
-      <c r="B4" t="str">
-        <v>25 - Haridwar</v>
+      <c r="B4" t="s">
+        <v>20</v>
       </c>
       <c r="C4">
         <v>51528</v>
@@ -514,13 +844,22 @@
       <c r="P4">
         <v>53812</v>
       </c>
-    </row>
-    <row r="5">
+      <c r="Q4" s="2">
+        <v>12212</v>
+      </c>
+      <c r="R4" s="2">
+        <v>0</v>
+      </c>
+      <c r="S4" s="2">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>2</v>
       </c>
-      <c r="B5" t="str">
-        <v>26 - BHEL Ranipur</v>
+      <c r="B5" t="s">
+        <v>21</v>
       </c>
       <c r="C5">
         <v>53911</v>
@@ -564,13 +903,22 @@
       <c r="P5">
         <v>74848</v>
       </c>
-    </row>
-    <row r="6">
+      <c r="Q5" s="2">
+        <v>16108</v>
+      </c>
+      <c r="R5" s="2">
+        <v>0</v>
+      </c>
+      <c r="S5" s="2">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>3</v>
       </c>
-      <c r="B6" t="str">
-        <v>27 - Jwalapur</v>
+      <c r="B6" t="s">
+        <v>22</v>
       </c>
       <c r="C6">
         <v>39773</v>
@@ -614,13 +962,22 @@
       <c r="P6">
         <v>71989</v>
       </c>
-    </row>
-    <row r="7">
+      <c r="Q6" s="2">
+        <v>17830</v>
+      </c>
+      <c r="R6" s="2">
+        <v>0</v>
+      </c>
+      <c r="S6" s="2">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>4</v>
       </c>
-      <c r="B7" t="str">
-        <v>28 - Bhagwanpur</v>
+      <c r="B7" t="s">
+        <v>23</v>
       </c>
       <c r="C7">
         <v>39463</v>
@@ -664,13 +1021,22 @@
       <c r="P7">
         <v>77581</v>
       </c>
-    </row>
-    <row r="8">
+      <c r="Q7" s="2">
+        <v>20511</v>
+      </c>
+      <c r="R7" s="2">
+        <v>0</v>
+      </c>
+      <c r="S7" s="2">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>5</v>
       </c>
-      <c r="B8" t="str">
-        <v>29 - Jhabrera</v>
+      <c r="B8" t="s">
+        <v>24</v>
       </c>
       <c r="C8">
         <v>40552</v>
@@ -714,13 +1080,22 @@
       <c r="P8">
         <v>73458</v>
       </c>
-    </row>
-    <row r="9">
+      <c r="Q8" s="2">
+        <v>20788</v>
+      </c>
+      <c r="R8" s="2">
+        <v>0</v>
+      </c>
+      <c r="S8" s="2">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>6</v>
       </c>
-      <c r="B9" t="str">
-        <v>30 - Piran Kaliyar</v>
+      <c r="B9" t="s">
+        <v>25</v>
       </c>
       <c r="C9">
         <v>43273</v>
@@ -764,13 +1139,22 @@
       <c r="P9">
         <v>72913</v>
       </c>
-    </row>
-    <row r="10">
+      <c r="Q9" s="2">
+        <v>18141</v>
+      </c>
+      <c r="R9" s="2">
+        <v>0</v>
+      </c>
+      <c r="S9" s="2">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>7</v>
       </c>
-      <c r="B10" t="str">
-        <v>31 - Roorkee</v>
+      <c r="B10" t="s">
+        <v>26</v>
       </c>
       <c r="C10">
         <v>36576</v>
@@ -814,13 +1198,22 @@
       <c r="P10">
         <v>53124</v>
       </c>
-    </row>
-    <row r="11">
+      <c r="Q10" s="2">
+        <v>9498</v>
+      </c>
+      <c r="R10" s="2">
+        <v>0</v>
+      </c>
+      <c r="S10" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>8</v>
       </c>
-      <c r="B11" t="str">
-        <v>32 - Khanpur</v>
+      <c r="B11" t="s">
+        <v>27</v>
       </c>
       <c r="C11">
         <v>50998</v>
@@ -864,13 +1257,22 @@
       <c r="P11">
         <v>84438</v>
       </c>
-    </row>
-    <row r="12">
+      <c r="Q11" s="2">
+        <v>23477</v>
+      </c>
+      <c r="R11" s="2">
+        <v>0</v>
+      </c>
+      <c r="S11" s="2">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="12" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>9</v>
       </c>
-      <c r="B12" t="str">
-        <v>33 - Manglore</v>
+      <c r="B12" t="s">
+        <v>28</v>
       </c>
       <c r="C12">
         <v>40739</v>
@@ -914,13 +1316,22 @@
       <c r="P12">
         <v>66685</v>
       </c>
-    </row>
-    <row r="13">
+      <c r="Q12" s="2">
+        <v>17786</v>
+      </c>
+      <c r="R12" s="2">
+        <v>0</v>
+      </c>
+      <c r="S12" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>10</v>
       </c>
-      <c r="B13" t="str">
-        <v>34 - Laksar</v>
+      <c r="B13" t="s">
+        <v>29</v>
       </c>
       <c r="C13">
         <v>37031</v>
@@ -964,13 +1375,22 @@
       <c r="P13">
         <v>56564</v>
       </c>
-    </row>
-    <row r="14">
+      <c r="Q13" s="2">
+        <v>16237</v>
+      </c>
+      <c r="R13" s="2">
+        <v>0</v>
+      </c>
+      <c r="S13" s="2">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="14" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>11</v>
       </c>
-      <c r="B14" t="str">
-        <v>35 - Haridwar Rural</v>
+      <c r="B14" t="s">
+        <v>30</v>
       </c>
       <c r="C14">
         <v>48966</v>
@@ -1014,13 +1434,22 @@
       <c r="P14">
         <v>77955</v>
       </c>
-    </row>
-    <row r="15">
+      <c r="Q14" s="2">
+        <v>19716</v>
+      </c>
+      <c r="R14" s="2">
+        <v>0</v>
+      </c>
+      <c r="S14" s="2">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="15" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>12</v>
       </c>
-      <c r="B15" t="str">
-        <v>56 - Lalkuan</v>
+      <c r="B15" t="s">
+        <v>31</v>
       </c>
       <c r="C15">
         <v>42703</v>
@@ -1064,13 +1493,22 @@
       <c r="P15">
         <v>67178</v>
       </c>
-    </row>
-    <row r="16">
+      <c r="Q15" s="2">
+        <v>4859</v>
+      </c>
+      <c r="R15" s="2">
+        <v>0</v>
+      </c>
+      <c r="S15" s="2">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="16" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>13</v>
       </c>
-      <c r="B16" t="str">
-        <v>57 - Bhimtal</v>
+      <c r="B16" t="s">
+        <v>32</v>
       </c>
       <c r="C16">
         <v>25549</v>
@@ -1114,13 +1552,22 @@
       <c r="P16">
         <v>71673</v>
       </c>
-    </row>
-    <row r="17">
+      <c r="Q16" s="2">
+        <v>5197</v>
+      </c>
+      <c r="R16" s="2">
+        <v>0</v>
+      </c>
+      <c r="S16" s="2">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="17" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>14</v>
       </c>
-      <c r="B17" t="str">
-        <v>58 - Nainital</v>
+      <c r="B17" t="s">
+        <v>33</v>
       </c>
       <c r="C17">
         <v>27707</v>
@@ -1164,13 +1611,22 @@
       <c r="P17">
         <v>65457</v>
       </c>
-    </row>
-    <row r="18">
+      <c r="Q17" s="2">
+        <v>5417</v>
+      </c>
+      <c r="R17" s="2">
+        <v>0</v>
+      </c>
+      <c r="S17" s="2">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="18" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>15</v>
       </c>
-      <c r="B18" t="str">
-        <v>59 - Haldwani</v>
+      <c r="B18" t="s">
+        <v>34</v>
       </c>
       <c r="C18">
         <v>47836</v>
@@ -1214,13 +1670,22 @@
       <c r="P18">
         <v>71475</v>
       </c>
-    </row>
-    <row r="19">
+      <c r="Q18" s="2">
+        <v>6819</v>
+      </c>
+      <c r="R18" s="2">
+        <v>0</v>
+      </c>
+      <c r="S18" s="2">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="19" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>16</v>
       </c>
-      <c r="B19" t="str">
-        <v>60 - Kaladhungi</v>
+      <c r="B19" t="s">
+        <v>35</v>
       </c>
       <c r="C19">
         <v>56490</v>
@@ -1264,13 +1729,22 @@
       <c r="P19">
         <v>106392</v>
       </c>
-    </row>
-    <row r="20">
+      <c r="Q19" s="2">
+        <v>6135</v>
+      </c>
+      <c r="R19" s="2">
+        <v>0</v>
+      </c>
+      <c r="S19" s="2">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="20" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>17</v>
       </c>
-      <c r="B20" t="str">
-        <v>61 - Ramnagar</v>
+      <c r="B20" t="s">
+        <v>36</v>
       </c>
       <c r="C20">
         <v>35022</v>
@@ -1314,13 +1788,22 @@
       <c r="P20">
         <v>75812</v>
       </c>
-    </row>
-    <row r="21">
+      <c r="Q20" s="2">
+        <v>8984</v>
+      </c>
+      <c r="R20" s="2">
+        <v>0</v>
+      </c>
+      <c r="S20" s="2">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="21" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>18</v>
       </c>
-      <c r="B21" t="str">
-        <v>48 - Dwarahat</v>
+      <c r="B21" t="s">
+        <v>37</v>
       </c>
       <c r="C21">
         <v>16962</v>
@@ -1364,13 +1847,22 @@
       <c r="P21">
         <v>62460</v>
       </c>
-    </row>
-    <row r="22">
+      <c r="Q21" s="2">
+        <v>3868</v>
+      </c>
+      <c r="R21" s="2">
+        <v>0</v>
+      </c>
+      <c r="S21" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>19</v>
       </c>
-      <c r="B22" t="str">
-        <v>49 - Salt</v>
+      <c r="B22" t="s">
+        <v>38</v>
       </c>
       <c r="C22">
         <v>18668</v>
@@ -1414,13 +1906,22 @@
       <c r="P22">
         <v>64099</v>
       </c>
-    </row>
-    <row r="23">
+      <c r="Q22" s="2">
+        <v>4848</v>
+      </c>
+      <c r="R22" s="2">
+        <v>0</v>
+      </c>
+      <c r="S22" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>20</v>
       </c>
-      <c r="B23" t="str">
-        <v>50 - Ranikhet</v>
+      <c r="B23" t="s">
+        <v>39</v>
       </c>
       <c r="C23">
         <v>12020</v>
@@ -1464,13 +1965,22 @@
       <c r="P23">
         <v>57094</v>
       </c>
-    </row>
-    <row r="24">
+      <c r="Q23" s="2">
+        <v>3541</v>
+      </c>
+      <c r="R23" s="2">
+        <v>0</v>
+      </c>
+      <c r="S23" s="2">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="24" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>21</v>
       </c>
-      <c r="B24" t="str">
-        <v>51 - Someshwar</v>
+      <c r="B24" t="s">
+        <v>40</v>
       </c>
       <c r="C24">
         <v>14056</v>
@@ -1514,13 +2024,22 @@
       <c r="P24">
         <v>65629</v>
       </c>
-    </row>
-    <row r="25">
+      <c r="Q24" s="2">
+        <v>3492</v>
+      </c>
+      <c r="R24" s="2">
+        <v>0</v>
+      </c>
+      <c r="S24" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>22</v>
       </c>
-      <c r="B25" t="str">
-        <v>52 - Almora</v>
+      <c r="B25" t="s">
+        <v>41</v>
       </c>
       <c r="C25">
         <v>19266</v>
@@ -1564,13 +2083,22 @@
       <c r="P25">
         <v>57533</v>
       </c>
-    </row>
-    <row r="26">
+      <c r="Q25" s="2">
+        <v>3231</v>
+      </c>
+      <c r="R25" s="2">
+        <v>0</v>
+      </c>
+      <c r="S25" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="26" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>23</v>
       </c>
-      <c r="B26" t="str">
-        <v>53 - Jageshwar</v>
+      <c r="B26" t="s">
+        <v>42</v>
       </c>
       <c r="C26">
         <v>17557</v>
@@ -1614,13 +2142,22 @@
       <c r="P26">
         <v>66594</v>
       </c>
-    </row>
-    <row r="27">
+      <c r="Q26" s="2">
+        <v>3333</v>
+      </c>
+      <c r="R26" s="2">
+        <v>0</v>
+      </c>
+      <c r="S26" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="27" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>24</v>
       </c>
-      <c r="B27" t="str">
-        <v>62 - Jaspur</v>
+      <c r="B27" t="s">
+        <v>43</v>
       </c>
       <c r="C27">
         <v>44276</v>
@@ -1664,13 +2201,22 @@
       <c r="P27">
         <v>73109</v>
       </c>
-    </row>
-    <row r="28">
+      <c r="Q27" s="2">
+        <v>12669</v>
+      </c>
+      <c r="R27" s="2">
+        <v>0</v>
+      </c>
+      <c r="S27" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>25</v>
       </c>
-      <c r="B28" t="str">
-        <v>63 - Kashipur</v>
+      <c r="B28" t="s">
+        <v>44</v>
       </c>
       <c r="C28">
         <v>54349</v>
@@ -1714,13 +2260,22 @@
       <c r="P28">
         <v>80620</v>
       </c>
-    </row>
-    <row r="29">
+      <c r="Q28" s="2">
+        <v>13995</v>
+      </c>
+      <c r="R28" s="2">
+        <v>0</v>
+      </c>
+      <c r="S28" s="2">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="29" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>26</v>
       </c>
-      <c r="B29" t="str">
-        <v>64 - Bajpur</v>
+      <c r="B29" t="s">
+        <v>45</v>
       </c>
       <c r="C29">
         <v>47111</v>
@@ -1764,13 +2319,22 @@
       <c r="P29">
         <v>83836</v>
       </c>
-    </row>
-    <row r="30">
+      <c r="Q29" s="2">
+        <v>14229</v>
+      </c>
+      <c r="R29" s="2">
+        <v>0</v>
+      </c>
+      <c r="S29" s="2">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="30" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>27</v>
       </c>
-      <c r="B30" t="str">
-        <v>65 - Gadarpur</v>
+      <c r="B30" t="s">
+        <v>46</v>
       </c>
       <c r="C30">
         <v>52653</v>
@@ -1814,13 +2378,22 @@
       <c r="P30">
         <v>86933</v>
       </c>
-    </row>
-    <row r="31">
+      <c r="Q30" s="2">
+        <v>12564</v>
+      </c>
+      <c r="R30" s="2">
+        <v>0</v>
+      </c>
+      <c r="S30" s="2">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="31" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>28</v>
       </c>
-      <c r="B31" t="str">
-        <v>66 - Rudrapur</v>
+      <c r="B31" t="s">
+        <v>47</v>
       </c>
       <c r="C31">
         <v>91162</v>
@@ -1864,13 +2437,22 @@
       <c r="P31">
         <v>81642</v>
       </c>
-    </row>
-    <row r="32">
+      <c r="Q31" s="2">
+        <v>14581</v>
+      </c>
+      <c r="R31" s="2">
+        <v>0</v>
+      </c>
+      <c r="S31" s="2">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="32" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>29</v>
       </c>
-      <c r="B32" t="str">
-        <v>67 - Kichha</v>
+      <c r="B32" t="s">
+        <v>48</v>
       </c>
       <c r="C32">
         <v>46728</v>
@@ -1914,13 +2496,22 @@
       <c r="P32">
         <v>74810</v>
       </c>
-    </row>
-    <row r="33">
+      <c r="Q32" s="2">
+        <v>11379</v>
+      </c>
+      <c r="R32" s="2">
+        <v>0</v>
+      </c>
+      <c r="S32" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>30</v>
       </c>
-      <c r="B33" t="str">
-        <v>68 - Sitarganj</v>
+      <c r="B33" t="s">
+        <v>49</v>
       </c>
       <c r="C33">
         <v>40230</v>
@@ -1964,13 +2555,22 @@
       <c r="P33">
         <v>76969</v>
       </c>
-    </row>
-    <row r="34">
+      <c r="Q33" s="2">
+        <v>6678</v>
+      </c>
+      <c r="R33" s="2">
+        <v>0</v>
+      </c>
+      <c r="S33" s="2">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="34" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>31</v>
       </c>
-      <c r="B34" t="str">
-        <v>69 - Nanakmatta</v>
+      <c r="B34" t="s">
+        <v>50</v>
       </c>
       <c r="C34">
         <v>36542</v>
@@ -2014,13 +2614,22 @@
       <c r="P34">
         <v>74624</v>
       </c>
-    </row>
-    <row r="35">
+      <c r="Q34" s="2">
+        <v>7137</v>
+      </c>
+      <c r="R34" s="2">
+        <v>0</v>
+      </c>
+      <c r="S34" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>32</v>
       </c>
-      <c r="B35" t="str">
-        <v>70 - Khatima</v>
+      <c r="B35" t="s">
+        <v>51</v>
       </c>
       <c r="C35">
         <v>33564</v>
@@ -2064,13 +2673,22 @@
       <c r="P35">
         <v>76464</v>
       </c>
-    </row>
-    <row r="36">
+      <c r="Q35" s="2">
+        <v>8879</v>
+      </c>
+      <c r="R35" s="2">
+        <v>0</v>
+      </c>
+      <c r="S35" s="2">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="36" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>33</v>
       </c>
-      <c r="B36" t="str">
-        <v>42 - Dharchula</v>
+      <c r="B36" t="s">
+        <v>52</v>
       </c>
       <c r="C36">
         <v>20905</v>
@@ -2114,13 +2732,22 @@
       <c r="P36">
         <v>60419</v>
       </c>
-    </row>
-    <row r="37">
+      <c r="Q36" s="2">
+        <v>3855</v>
+      </c>
+      <c r="R36" s="2">
+        <v>0</v>
+      </c>
+      <c r="S36" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="37" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>34</v>
       </c>
-      <c r="B37" t="str">
-        <v>43 - Didihat</v>
+      <c r="B37" t="s">
+        <v>53</v>
       </c>
       <c r="C37">
         <v>17692</v>
@@ -2164,13 +2791,22 @@
       <c r="P37">
         <v>57832</v>
       </c>
-    </row>
-    <row r="38">
+      <c r="Q37" s="2">
+        <v>4036</v>
+      </c>
+      <c r="R37" s="2">
+        <v>0</v>
+      </c>
+      <c r="S37" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>35</v>
       </c>
-      <c r="B38" t="str">
-        <v>44 - Pithoragarh</v>
+      <c r="B38" t="s">
+        <v>54</v>
       </c>
       <c r="C38">
         <v>29110</v>
@@ -2214,13 +2850,22 @@
       <c r="P38">
         <v>63038</v>
       </c>
-    </row>
-    <row r="39">
+      <c r="Q38" s="2">
+        <v>5135</v>
+      </c>
+      <c r="R38" s="2">
+        <v>0</v>
+      </c>
+      <c r="S38" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>36</v>
       </c>
-      <c r="B39" t="str">
-        <v>45 - Gangolihat</v>
+      <c r="B39" t="s">
+        <v>55</v>
       </c>
       <c r="C39">
         <v>21367</v>
@@ -2264,13 +2909,22 @@
       <c r="P39">
         <v>71133</v>
       </c>
-    </row>
-    <row r="40">
+      <c r="Q39" s="2">
+        <v>5903</v>
+      </c>
+      <c r="R39" s="2">
+        <v>0</v>
+      </c>
+      <c r="S39" s="2">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="40" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>37</v>
       </c>
-      <c r="B40" t="str">
-        <v>46 - Kapkot</v>
+      <c r="B40" t="s">
+        <v>56</v>
       </c>
       <c r="C40">
         <v>18905</v>
@@ -2314,13 +2968,22 @@
       <c r="P40">
         <v>73242</v>
       </c>
-    </row>
-    <row r="41">
+      <c r="Q40" s="2">
+        <v>3824</v>
+      </c>
+      <c r="R40" s="2">
+        <v>0</v>
+      </c>
+      <c r="S40" s="2">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="41" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>38</v>
       </c>
-      <c r="B41" t="str">
-        <v>47 - Bageshwar</v>
+      <c r="B41" t="s">
+        <v>57</v>
       </c>
       <c r="C41">
         <v>23521</v>
@@ -2364,13 +3027,22 @@
       <c r="P41">
         <v>85251</v>
       </c>
-    </row>
-    <row r="42">
+      <c r="Q41" s="2">
+        <v>6015</v>
+      </c>
+      <c r="R41" s="2">
+        <v>0</v>
+      </c>
+      <c r="S41" s="2">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="42" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>39</v>
       </c>
-      <c r="B42" t="str">
-        <v>54 - Lohaghat</v>
+      <c r="B42" t="s">
+        <v>58</v>
       </c>
       <c r="C42">
         <v>27565</v>
@@ -2414,13 +3086,22 @@
       <c r="P42">
         <v>68615</v>
       </c>
-    </row>
-    <row r="43">
+      <c r="Q42" s="2">
+        <v>4708</v>
+      </c>
+      <c r="R42" s="2">
+        <v>0</v>
+      </c>
+      <c r="S42" s="2">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="43" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>40</v>
       </c>
-      <c r="B43" t="str">
-        <v>55 - Champawat</v>
+      <c r="B43" t="s">
+        <v>59</v>
       </c>
       <c r="C43">
         <v>29700</v>
@@ -2464,13 +3145,22 @@
       <c r="P43">
         <v>63012</v>
       </c>
-    </row>
-    <row r="44">
+      <c r="Q43" s="2">
+        <v>5219</v>
+      </c>
+      <c r="R43" s="2">
+        <v>0</v>
+      </c>
+      <c r="S43" s="2">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="44" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A44">
         <v>41</v>
       </c>
-      <c r="B44" t="str">
-        <v>4 - Badrinath</v>
+      <c r="B44" t="s">
+        <v>60</v>
       </c>
       <c r="C44">
         <v>21900</v>
@@ -2514,13 +3204,22 @@
       <c r="P44">
         <v>68393</v>
       </c>
-    </row>
-    <row r="45">
+      <c r="Q44" s="2">
+        <v>7659</v>
+      </c>
+      <c r="R44" s="2">
+        <v>0</v>
+      </c>
+      <c r="S44" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="45" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A45">
         <v>42</v>
       </c>
-      <c r="B45" t="str">
-        <v>5 - Tharali</v>
+      <c r="B45" t="s">
+        <v>61</v>
       </c>
       <c r="C45">
         <v>19935</v>
@@ -2564,13 +3263,22 @@
       <c r="P45">
         <v>76287</v>
       </c>
-    </row>
-    <row r="46">
+      <c r="Q45" s="2">
+        <v>6998</v>
+      </c>
+      <c r="R45" s="2">
+        <v>0</v>
+      </c>
+      <c r="S45" s="2">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="46" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A46">
         <v>43</v>
       </c>
-      <c r="B46" t="str">
-        <v>6 - Karanprayag</v>
+      <c r="B46" t="s">
+        <v>62</v>
       </c>
       <c r="C46">
         <v>21512</v>
@@ -2614,13 +3322,22 @@
       <c r="P46">
         <v>64160</v>
       </c>
-    </row>
-    <row r="47">
+      <c r="Q46" s="2">
+        <v>7548</v>
+      </c>
+      <c r="R46" s="2">
+        <v>0</v>
+      </c>
+      <c r="S46" s="2">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="47" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A47">
         <v>44</v>
       </c>
-      <c r="B47" t="str">
-        <v>1 - Purola</v>
+      <c r="B47" t="s">
+        <v>63</v>
       </c>
       <c r="C47">
         <v>22426</v>
@@ -2664,13 +3381,22 @@
       <c r="P47">
         <v>49875</v>
       </c>
-    </row>
-    <row r="48">
+      <c r="Q47" s="2">
+        <v>5046</v>
+      </c>
+      <c r="R47" s="2">
+        <v>0</v>
+      </c>
+      <c r="S47" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A48">
         <v>45</v>
       </c>
-      <c r="B48" t="str">
-        <v>2 - Yamunotri</v>
+      <c r="B48" t="s">
+        <v>64</v>
       </c>
       <c r="C48">
         <v>19641</v>
@@ -2714,13 +3440,22 @@
       <c r="P48">
         <v>54142</v>
       </c>
-    </row>
-    <row r="49">
+      <c r="Q48" s="2">
+        <v>4623</v>
+      </c>
+      <c r="R48" s="2">
+        <v>0</v>
+      </c>
+      <c r="S48" s="2">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="49" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A49">
         <v>46</v>
       </c>
-      <c r="B49" t="str">
-        <v>3 - Gangotri</v>
+      <c r="B49" t="s">
+        <v>65</v>
       </c>
       <c r="C49">
         <v>21651</v>
@@ -2764,13 +3499,22 @@
       <c r="P49">
         <v>55376</v>
       </c>
-    </row>
-    <row r="50">
+      <c r="Q49" s="2">
+        <v>5057</v>
+      </c>
+      <c r="R49" s="2">
+        <v>0</v>
+      </c>
+      <c r="S49" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="50" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A50">
         <v>47</v>
       </c>
-      <c r="B50" t="str">
-        <v>7 - Kedarnath</v>
+      <c r="B50" t="s">
+        <v>66</v>
       </c>
       <c r="C50">
         <v>21936</v>
@@ -2814,13 +3558,22 @@
       <c r="P50">
         <v>63298</v>
       </c>
-    </row>
-    <row r="51">
+      <c r="Q50" s="2">
+        <v>7292</v>
+      </c>
+      <c r="R50" s="2">
+        <v>0</v>
+      </c>
+      <c r="S50" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A51">
         <v>48</v>
       </c>
-      <c r="B51" t="str">
-        <v>8 - Rudraprayag</v>
+      <c r="B51" t="s">
+        <v>67</v>
       </c>
       <c r="C51">
         <v>23798</v>
@@ -2864,13 +3617,22 @@
       <c r="P51">
         <v>71754</v>
       </c>
-    </row>
-    <row r="52">
+      <c r="Q51" s="2">
+        <v>7715</v>
+      </c>
+      <c r="R51" s="2">
+        <v>0</v>
+      </c>
+      <c r="S51" s="2">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="52" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A52">
         <v>49</v>
       </c>
-      <c r="B52" t="str">
-        <v>9 - Ghansali</v>
+      <c r="B52" t="s">
+        <v>68</v>
       </c>
       <c r="C52">
         <v>21094</v>
@@ -2914,13 +3676,22 @@
       <c r="P52">
         <v>63987</v>
       </c>
-    </row>
-    <row r="53">
+      <c r="Q52" s="2">
+        <v>5655</v>
+      </c>
+      <c r="R52" s="2">
+        <v>0</v>
+      </c>
+      <c r="S52" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="53" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A53">
         <v>50</v>
       </c>
-      <c r="B53" t="str">
-        <v>10 - Devprayag</v>
+      <c r="B53" t="s">
+        <v>69</v>
       </c>
       <c r="C53">
         <v>19131</v>
@@ -2964,13 +3735,22 @@
       <c r="P53">
         <v>56306</v>
       </c>
-    </row>
-    <row r="54">
+      <c r="Q53" s="2">
+        <v>6551</v>
+      </c>
+      <c r="R53" s="2">
+        <v>0</v>
+      </c>
+      <c r="S53" s="2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="54" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A54">
         <v>51</v>
       </c>
-      <c r="B54" t="str">
-        <v>11 - Narendranagar</v>
+      <c r="B54" t="s">
+        <v>70</v>
       </c>
       <c r="C54">
         <v>20758</v>
@@ -3014,13 +3794,22 @@
       <c r="P54">
         <v>58440</v>
       </c>
-    </row>
-    <row r="55">
+      <c r="Q54" s="2">
+        <v>7347</v>
+      </c>
+      <c r="R54" s="2">
+        <v>0</v>
+      </c>
+      <c r="S54" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A55">
         <v>52</v>
       </c>
-      <c r="B55" t="str">
-        <v>12 - Pratapnagar</v>
+      <c r="B55" t="s">
+        <v>71</v>
       </c>
       <c r="C55">
         <v>16022</v>
@@ -3064,13 +3853,22 @@
       <c r="P55">
         <v>58215</v>
       </c>
-    </row>
-    <row r="56">
+      <c r="Q55" s="2">
+        <v>5098</v>
+      </c>
+      <c r="R55" s="2">
+        <v>0</v>
+      </c>
+      <c r="S55" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A56">
         <v>53</v>
       </c>
-      <c r="B56" t="str">
-        <v>13 - Tehri</v>
+      <c r="B56" t="s">
+        <v>72</v>
       </c>
       <c r="C56">
         <v>19256</v>
@@ -3114,13 +3912,22 @@
       <c r="P56">
         <v>47621</v>
       </c>
-    </row>
-    <row r="57">
+      <c r="Q56" s="2">
+        <v>4882</v>
+      </c>
+      <c r="R56" s="2">
+        <v>0</v>
+      </c>
+      <c r="S56" s="2">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="57" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A57">
         <v>54</v>
       </c>
-      <c r="B57" t="str">
-        <v>14 - Dhanolti</v>
+      <c r="B57" t="s">
+        <v>73</v>
       </c>
       <c r="C57">
         <v>21240</v>
@@ -3164,13 +3971,22 @@
       <c r="P57">
         <v>61556</v>
       </c>
-    </row>
-    <row r="58">
+      <c r="Q57" s="2">
+        <v>6870</v>
+      </c>
+      <c r="R57" s="2">
+        <v>0</v>
+      </c>
+      <c r="S57" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A58">
         <v>55</v>
       </c>
-      <c r="B58" t="str">
-        <v>36 - Yamkeshwar</v>
+      <c r="B58" t="s">
+        <v>74</v>
       </c>
       <c r="C58">
         <v>22819</v>
@@ -3214,13 +4030,22 @@
       <c r="P58">
         <v>57577</v>
       </c>
-    </row>
-    <row r="59">
+      <c r="Q58" s="2">
+        <v>8884</v>
+      </c>
+      <c r="R58" s="2">
+        <v>0</v>
+      </c>
+      <c r="S58" s="2">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="59" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A59">
         <v>56</v>
       </c>
-      <c r="B59" t="str">
-        <v>37 - Pauri</v>
+      <c r="B59" t="s">
+        <v>75</v>
       </c>
       <c r="C59">
         <v>18776</v>
@@ -3264,13 +4089,22 @@
       <c r="P59">
         <v>60495</v>
       </c>
-    </row>
-    <row r="60">
+      <c r="Q59" s="2">
+        <v>8028</v>
+      </c>
+      <c r="R59" s="2">
+        <v>0</v>
+      </c>
+      <c r="S59" s="2">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="60" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A60">
         <v>57</v>
       </c>
-      <c r="B60" t="str">
-        <v>38 - Srinagar</v>
+      <c r="B60" t="s">
+        <v>76</v>
       </c>
       <c r="C60">
         <v>23749</v>
@@ -3314,13 +4148,22 @@
       <c r="P60">
         <v>70140</v>
       </c>
-    </row>
-    <row r="61">
+      <c r="Q60" s="2">
+        <v>7415</v>
+      </c>
+      <c r="R60" s="2">
+        <v>0</v>
+      </c>
+      <c r="S60" s="2">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="61" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A61">
         <v>58</v>
       </c>
-      <c r="B61" t="str">
-        <v>39 - Chaubattakhal</v>
+      <c r="B61" t="s">
+        <v>77</v>
       </c>
       <c r="C61">
         <v>22069</v>
@@ -3364,13 +4207,22 @@
       <c r="P61">
         <v>55240</v>
       </c>
-    </row>
-    <row r="62">
+      <c r="Q61" s="2">
+        <v>7927</v>
+      </c>
+      <c r="R61" s="2">
+        <v>1</v>
+      </c>
+      <c r="S61" s="2">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="62" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A62">
         <v>59</v>
       </c>
-      <c r="B62" t="str">
-        <v>40 - Lansdowne</v>
+      <c r="B62" t="s">
+        <v>78</v>
       </c>
       <c r="C62">
         <v>15800</v>
@@ -3414,13 +4266,22 @@
       <c r="P62">
         <v>51334</v>
       </c>
-    </row>
-    <row r="63">
+      <c r="Q62" s="2">
+        <v>6917</v>
+      </c>
+      <c r="R62" s="2">
+        <v>0</v>
+      </c>
+      <c r="S62" s="2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="63" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A63">
         <v>60</v>
       </c>
-      <c r="B63" t="str">
-        <v>41 - Kotdwar</v>
+      <c r="B63" t="s">
+        <v>79</v>
       </c>
       <c r="C63">
         <v>36754</v>
@@ -3464,13 +4325,22 @@
       <c r="P63">
         <v>68696</v>
       </c>
-    </row>
-    <row r="64">
+      <c r="Q63" s="2">
+        <v>9766</v>
+      </c>
+      <c r="R63" s="2">
+        <v>0</v>
+      </c>
+      <c r="S63" s="2">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="64" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A64">
         <v>61</v>
       </c>
-      <c r="B64" t="str">
-        <v>15 - Chakrata</v>
+      <c r="B64" t="s">
+        <v>80</v>
       </c>
       <c r="C64">
         <v>42048</v>
@@ -3514,13 +4384,22 @@
       <c r="P64">
         <v>60527</v>
       </c>
-    </row>
-    <row r="65">
+      <c r="Q64" s="2">
+        <v>5985</v>
+      </c>
+      <c r="R64" s="2">
+        <v>0</v>
+      </c>
+      <c r="S64" s="2">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="65" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A65">
         <v>62</v>
       </c>
-      <c r="B65" t="str">
-        <v>16 - Vikasnagar</v>
+      <c r="B65" t="s">
+        <v>81</v>
       </c>
       <c r="C65">
         <v>41389</v>
@@ -3564,13 +4443,22 @@
       <c r="P65">
         <v>58527</v>
       </c>
-    </row>
-    <row r="66">
+      <c r="Q65" s="2">
+        <v>13282</v>
+      </c>
+      <c r="R65" s="2">
+        <v>0</v>
+      </c>
+      <c r="S65" s="2">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="66" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A66">
         <v>63</v>
       </c>
-      <c r="B66" t="str">
-        <v>17 - Sahaspur</v>
+      <c r="B66" t="s">
+        <v>82</v>
       </c>
       <c r="C66">
         <v>67362</v>
@@ -3614,13 +4502,22 @@
       <c r="P66">
         <v>93810</v>
       </c>
-    </row>
-    <row r="67">
+      <c r="Q66" s="2">
+        <v>17742</v>
+      </c>
+      <c r="R66" s="2">
+        <v>0</v>
+      </c>
+      <c r="S66" s="2">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="67" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A67">
         <v>64</v>
       </c>
-      <c r="B67" t="str">
-        <v>18 - Dharmpur</v>
+      <c r="B67" t="s">
+        <v>83</v>
       </c>
       <c r="C67">
         <v>68828</v>
@@ -3664,13 +4561,22 @@
       <c r="P67">
         <v>78032</v>
       </c>
-    </row>
-    <row r="68">
+      <c r="Q67" s="2">
+        <v>9807</v>
+      </c>
+      <c r="R67" s="2">
+        <v>0</v>
+      </c>
+      <c r="S67" s="2">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="68" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A68">
         <v>65</v>
       </c>
-      <c r="B68" t="str">
-        <v>19 - Raipur</v>
+      <c r="B68" t="s">
+        <v>84</v>
       </c>
       <c r="C68">
         <v>65397</v>
@@ -3714,13 +4620,22 @@
       <c r="P68">
         <v>71325</v>
       </c>
-    </row>
-    <row r="69">
+      <c r="Q68" s="2">
+        <v>7850</v>
+      </c>
+      <c r="R68" s="2">
+        <v>0</v>
+      </c>
+      <c r="S68" s="2">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="69" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A69">
         <v>66</v>
       </c>
-      <c r="B69" t="str">
-        <v>20 - Rajpur Road</v>
+      <c r="B69" t="s">
+        <v>85</v>
       </c>
       <c r="C69">
         <v>43938</v>
@@ -3764,13 +4679,22 @@
       <c r="P69">
         <v>36118</v>
       </c>
-    </row>
-    <row r="70">
+      <c r="Q69" s="2">
+        <v>6528</v>
+      </c>
+      <c r="R69" s="2">
+        <v>0</v>
+      </c>
+      <c r="S69" s="2">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="70" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A70">
         <v>67</v>
       </c>
-      <c r="B70" t="str">
-        <v>21 - Dehradun Cantonment</v>
+      <c r="B70" t="s">
+        <v>86</v>
       </c>
       <c r="C70">
         <v>47711</v>
@@ -3814,13 +4738,22 @@
       <c r="P70">
         <v>42051</v>
       </c>
-    </row>
-    <row r="71">
+      <c r="Q70" s="2">
+        <v>5798</v>
+      </c>
+      <c r="R70" s="2">
+        <v>0</v>
+      </c>
+      <c r="S70" s="2">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="71" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A71">
         <v>68</v>
       </c>
-      <c r="B71" t="str">
-        <v>22 - Mussoorie</v>
+      <c r="B71" t="s">
+        <v>87</v>
       </c>
       <c r="C71">
         <v>50963</v>
@@ -3864,13 +4797,22 @@
       <c r="P71">
         <v>49140</v>
       </c>
-    </row>
-    <row r="72">
+      <c r="Q71" s="2">
+        <v>6782</v>
+      </c>
+      <c r="R71" s="2">
+        <v>0</v>
+      </c>
+      <c r="S71" s="2">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="72" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A72">
         <v>69</v>
       </c>
-      <c r="B72" t="str">
-        <v>23 - Doiwala</v>
+      <c r="B72" t="s">
+        <v>88</v>
       </c>
       <c r="C72">
         <v>61543</v>
@@ -3914,13 +4856,22 @@
       <c r="P72">
         <v>85505</v>
       </c>
-    </row>
-    <row r="73">
+      <c r="Q72" s="2">
+        <v>12340</v>
+      </c>
+      <c r="R72" s="2">
+        <v>0</v>
+      </c>
+      <c r="S72" s="2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="73" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A73">
         <v>70</v>
       </c>
-      <c r="B73" t="str">
-        <v>24 - Rishikesh</v>
+      <c r="B73" t="s">
+        <v>89</v>
       </c>
       <c r="C73">
         <v>58915</v>
@@ -3964,11 +4915,21 @@
       <c r="P73">
         <v>67666</v>
       </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="str">
-        <v>Total</v>
-      </c>
+      <c r="Q73" s="2">
+        <v>10010</v>
+      </c>
+      <c r="R73" s="2">
+        <v>0</v>
+      </c>
+      <c r="S73" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="74" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A74" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="B74" s="1"/>
       <c r="C74">
         <v>2430387</v>
       </c>
@@ -4011,9 +4972,22 @@
       <c r="P74">
         <v>4701905</v>
       </c>
-    </row>
+      <c r="Q74" s="2">
+        <v>626236</v>
+      </c>
+      <c r="R74" s="2">
+        <v>1</v>
+      </c>
+      <c r="S74" s="2">
+        <v>3445</v>
+      </c>
+    </row>
+    <row r="75" spans="1:19" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="76" spans="1:19" ht="15.75" x14ac:dyDescent="0.25"/>
   </sheetData>
-  <mergeCells count="11">
+  <mergeCells count="12">
+    <mergeCell ref="A74:B74"/>
+    <mergeCell ref="Q2:S2"/>
     <mergeCell ref="A1:Q1"/>
     <mergeCell ref="A2:A3"/>
     <mergeCell ref="B2:B3"/>
@@ -4024,10 +4998,10 @@
     <mergeCell ref="G2:I2"/>
     <mergeCell ref="J2:M2"/>
     <mergeCell ref="N2:P2"/>
-    <mergeCell ref="A74:B74"/>
   </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:P74"/>
+    <ignoredError sqref="A1:P74" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/Notice.xlsx
+++ b/Notice.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Downloads\New folder (13)\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98CD1CAD-FA1B-40E1-94E9-0E5F615F421D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0705883-D56B-4F1E-9E95-1E442E301ED6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,9 +22,6 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="95">
   <si>
-    <t>Notice &amp; Hearing Report</t>
-  </si>
-  <si>
     <t>S. No.</t>
   </si>
   <si>
@@ -305,6 +302,9 @@
   </si>
   <si>
     <t>No Action Required</t>
+  </si>
+  <si>
+    <t>Notice &amp; Hearing Report Last Updated On : 18-09-2026 09:56:47</t>
   </si>
 </sst>
 </file>
@@ -688,7 +688,7 @@
   <sheetData>
     <row r="1" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>0</v>
+        <v>94</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -709,41 +709,41 @@
     </row>
     <row r="2" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="C2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="D2" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="E2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="F2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="G2" s="1" t="s">
         <v>6</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>7</v>
       </c>
       <c r="H2" s="1"/>
       <c r="I2" s="1"/>
       <c r="J2" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K2" s="1"/>
       <c r="L2" s="1"/>
       <c r="M2" s="1"/>
       <c r="N2" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="O2" s="1"/>
       <c r="P2" s="1"/>
       <c r="Q2" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="R2" s="1"/>
       <c r="S2" s="1"/>
@@ -756,43 +756,43 @@
       <c r="E3" s="1"/>
       <c r="F3" s="1"/>
       <c r="G3" t="s">
+        <v>9</v>
+      </c>
+      <c r="H3" t="s">
         <v>10</v>
       </c>
-      <c r="H3" t="s">
+      <c r="I3" t="s">
         <v>11</v>
       </c>
-      <c r="I3" t="s">
+      <c r="J3" t="s">
         <v>12</v>
       </c>
-      <c r="J3" t="s">
+      <c r="K3" t="s">
         <v>13</v>
       </c>
-      <c r="K3" t="s">
+      <c r="L3" t="s">
         <v>14</v>
       </c>
-      <c r="L3" t="s">
+      <c r="M3" t="s">
         <v>15</v>
       </c>
-      <c r="M3" t="s">
+      <c r="N3" t="s">
         <v>16</v>
       </c>
-      <c r="N3" t="s">
+      <c r="O3" t="s">
         <v>17</v>
       </c>
-      <c r="O3" t="s">
+      <c r="P3" t="s">
         <v>18</v>
       </c>
-      <c r="P3" t="s">
-        <v>19</v>
-      </c>
       <c r="Q3" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="R3" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="R3" s="2" t="s">
+      <c r="S3" s="2" t="s">
         <v>93</v>
-      </c>
-      <c r="S3" s="2" t="s">
-        <v>94</v>
       </c>
     </row>
     <row r="4" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
@@ -800,7 +800,7 @@
         <v>1</v>
       </c>
       <c r="B4" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C4">
         <v>51528</v>
@@ -859,7 +859,7 @@
         <v>2</v>
       </c>
       <c r="B5" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C5">
         <v>53911</v>
@@ -918,7 +918,7 @@
         <v>3</v>
       </c>
       <c r="B6" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C6">
         <v>39773</v>
@@ -977,7 +977,7 @@
         <v>4</v>
       </c>
       <c r="B7" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C7">
         <v>39463</v>
@@ -1036,7 +1036,7 @@
         <v>5</v>
       </c>
       <c r="B8" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C8">
         <v>40552</v>
@@ -1095,7 +1095,7 @@
         <v>6</v>
       </c>
       <c r="B9" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C9">
         <v>43273</v>
@@ -1154,7 +1154,7 @@
         <v>7</v>
       </c>
       <c r="B10" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C10">
         <v>36576</v>
@@ -1213,7 +1213,7 @@
         <v>8</v>
       </c>
       <c r="B11" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C11">
         <v>50998</v>
@@ -1272,7 +1272,7 @@
         <v>9</v>
       </c>
       <c r="B12" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C12">
         <v>40739</v>
@@ -1331,7 +1331,7 @@
         <v>10</v>
       </c>
       <c r="B13" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C13">
         <v>37031</v>
@@ -1390,7 +1390,7 @@
         <v>11</v>
       </c>
       <c r="B14" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C14">
         <v>48966</v>
@@ -1449,7 +1449,7 @@
         <v>12</v>
       </c>
       <c r="B15" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C15">
         <v>42703</v>
@@ -1508,7 +1508,7 @@
         <v>13</v>
       </c>
       <c r="B16" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C16">
         <v>25549</v>
@@ -1567,7 +1567,7 @@
         <v>14</v>
       </c>
       <c r="B17" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C17">
         <v>27707</v>
@@ -1626,7 +1626,7 @@
         <v>15</v>
       </c>
       <c r="B18" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C18">
         <v>47836</v>
@@ -1685,7 +1685,7 @@
         <v>16</v>
       </c>
       <c r="B19" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C19">
         <v>56490</v>
@@ -1744,7 +1744,7 @@
         <v>17</v>
       </c>
       <c r="B20" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C20">
         <v>35022</v>
@@ -1803,7 +1803,7 @@
         <v>18</v>
       </c>
       <c r="B21" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C21">
         <v>16962</v>
@@ -1862,7 +1862,7 @@
         <v>19</v>
       </c>
       <c r="B22" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C22">
         <v>18668</v>
@@ -1921,7 +1921,7 @@
         <v>20</v>
       </c>
       <c r="B23" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C23">
         <v>12020</v>
@@ -1980,7 +1980,7 @@
         <v>21</v>
       </c>
       <c r="B24" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C24">
         <v>14056</v>
@@ -2039,7 +2039,7 @@
         <v>22</v>
       </c>
       <c r="B25" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C25">
         <v>19266</v>
@@ -2098,7 +2098,7 @@
         <v>23</v>
       </c>
       <c r="B26" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C26">
         <v>17557</v>
@@ -2157,7 +2157,7 @@
         <v>24</v>
       </c>
       <c r="B27" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C27">
         <v>44276</v>
@@ -2193,7 +2193,7 @@
         <v>215</v>
       </c>
       <c r="N27">
-        <v>3282</v>
+        <v>3284</v>
       </c>
       <c r="O27">
         <v>41008</v>
@@ -2216,7 +2216,7 @@
         <v>25</v>
       </c>
       <c r="B28" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C28">
         <v>54349</v>
@@ -2255,7 +2255,7 @@
         <v>3525</v>
       </c>
       <c r="O28">
-        <v>50838</v>
+        <v>50844</v>
       </c>
       <c r="P28">
         <v>80620</v>
@@ -2275,7 +2275,7 @@
         <v>26</v>
       </c>
       <c r="B29" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C29">
         <v>47111</v>
@@ -2334,7 +2334,7 @@
         <v>27</v>
       </c>
       <c r="B30" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C30">
         <v>52653</v>
@@ -2393,7 +2393,7 @@
         <v>28</v>
       </c>
       <c r="B31" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C31">
         <v>91162</v>
@@ -2452,7 +2452,7 @@
         <v>29</v>
       </c>
       <c r="B32" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C32">
         <v>46728</v>
@@ -2511,7 +2511,7 @@
         <v>30</v>
       </c>
       <c r="B33" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C33">
         <v>40230</v>
@@ -2570,7 +2570,7 @@
         <v>31</v>
       </c>
       <c r="B34" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C34">
         <v>36542</v>
@@ -2629,7 +2629,7 @@
         <v>32</v>
       </c>
       <c r="B35" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C35">
         <v>33564</v>
@@ -2688,7 +2688,7 @@
         <v>33</v>
       </c>
       <c r="B36" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C36">
         <v>20905</v>
@@ -2747,7 +2747,7 @@
         <v>34</v>
       </c>
       <c r="B37" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C37">
         <v>17692</v>
@@ -2806,7 +2806,7 @@
         <v>35</v>
       </c>
       <c r="B38" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C38">
         <v>29110</v>
@@ -2865,7 +2865,7 @@
         <v>36</v>
       </c>
       <c r="B39" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C39">
         <v>21367</v>
@@ -2924,7 +2924,7 @@
         <v>37</v>
       </c>
       <c r="B40" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C40">
         <v>18905</v>
@@ -2983,7 +2983,7 @@
         <v>38</v>
       </c>
       <c r="B41" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C41">
         <v>23521</v>
@@ -3042,7 +3042,7 @@
         <v>39</v>
       </c>
       <c r="B42" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C42">
         <v>27565</v>
@@ -3101,7 +3101,7 @@
         <v>40</v>
       </c>
       <c r="B43" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C43">
         <v>29700</v>
@@ -3160,7 +3160,7 @@
         <v>41</v>
       </c>
       <c r="B44" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C44">
         <v>21900</v>
@@ -3219,7 +3219,7 @@
         <v>42</v>
       </c>
       <c r="B45" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C45">
         <v>19935</v>
@@ -3278,7 +3278,7 @@
         <v>43</v>
       </c>
       <c r="B46" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C46">
         <v>21512</v>
@@ -3337,7 +3337,7 @@
         <v>44</v>
       </c>
       <c r="B47" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C47">
         <v>22426</v>
@@ -3396,7 +3396,7 @@
         <v>45</v>
       </c>
       <c r="B48" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C48">
         <v>19641</v>
@@ -3455,7 +3455,7 @@
         <v>46</v>
       </c>
       <c r="B49" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C49">
         <v>21651</v>
@@ -3514,7 +3514,7 @@
         <v>47</v>
       </c>
       <c r="B50" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C50">
         <v>21936</v>
@@ -3573,7 +3573,7 @@
         <v>48</v>
       </c>
       <c r="B51" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C51">
         <v>23798</v>
@@ -3632,7 +3632,7 @@
         <v>49</v>
       </c>
       <c r="B52" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C52">
         <v>21094</v>
@@ -3691,7 +3691,7 @@
         <v>50</v>
       </c>
       <c r="B53" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C53">
         <v>19131</v>
@@ -3750,7 +3750,7 @@
         <v>51</v>
       </c>
       <c r="B54" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C54">
         <v>20758</v>
@@ -3809,7 +3809,7 @@
         <v>52</v>
       </c>
       <c r="B55" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C55">
         <v>16022</v>
@@ -3833,13 +3833,13 @@
         <v>0</v>
       </c>
       <c r="J55">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K55">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L55">
-        <v>2106</v>
+        <v>2109</v>
       </c>
       <c r="M55">
         <v>1</v>
@@ -3848,7 +3848,7 @@
         <v>129</v>
       </c>
       <c r="O55">
-        <v>15890</v>
+        <v>15893</v>
       </c>
       <c r="P55">
         <v>58215</v>
@@ -3868,7 +3868,7 @@
         <v>53</v>
       </c>
       <c r="B56" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C56">
         <v>19256</v>
@@ -3927,7 +3927,7 @@
         <v>54</v>
       </c>
       <c r="B57" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C57">
         <v>21240</v>
@@ -3986,7 +3986,7 @@
         <v>55</v>
       </c>
       <c r="B58" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C58">
         <v>22819</v>
@@ -4045,7 +4045,7 @@
         <v>56</v>
       </c>
       <c r="B59" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C59">
         <v>18776</v>
@@ -4104,7 +4104,7 @@
         <v>57</v>
       </c>
       <c r="B60" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C60">
         <v>23749</v>
@@ -4163,7 +4163,7 @@
         <v>58</v>
       </c>
       <c r="B61" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C61">
         <v>22069</v>
@@ -4222,7 +4222,7 @@
         <v>59</v>
       </c>
       <c r="B62" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C62">
         <v>15800</v>
@@ -4281,7 +4281,7 @@
         <v>60</v>
       </c>
       <c r="B63" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C63">
         <v>36754</v>
@@ -4340,7 +4340,7 @@
         <v>61</v>
       </c>
       <c r="B64" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C64">
         <v>42048</v>
@@ -4399,7 +4399,7 @@
         <v>62</v>
       </c>
       <c r="B65" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C65">
         <v>41389</v>
@@ -4458,7 +4458,7 @@
         <v>63</v>
       </c>
       <c r="B66" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C66">
         <v>67362</v>
@@ -4517,7 +4517,7 @@
         <v>64</v>
       </c>
       <c r="B67" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C67">
         <v>68828</v>
@@ -4576,7 +4576,7 @@
         <v>65</v>
       </c>
       <c r="B68" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C68">
         <v>65397</v>
@@ -4635,7 +4635,7 @@
         <v>66</v>
       </c>
       <c r="B69" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C69">
         <v>43938</v>
@@ -4694,7 +4694,7 @@
         <v>67</v>
       </c>
       <c r="B70" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C70">
         <v>47711</v>
@@ -4753,7 +4753,7 @@
         <v>68</v>
       </c>
       <c r="B71" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C71">
         <v>50963</v>
@@ -4812,7 +4812,7 @@
         <v>69</v>
       </c>
       <c r="B72" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C72">
         <v>61543</v>
@@ -4871,7 +4871,7 @@
         <v>70</v>
       </c>
       <c r="B73" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C73">
         <v>58915</v>
@@ -4927,7 +4927,7 @@
     </row>
     <row r="74" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A74" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B74" s="1"/>
       <c r="C74">
@@ -4952,22 +4952,22 @@
         <v>0</v>
       </c>
       <c r="J74">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K74">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L74">
-        <v>625504</v>
+        <v>625507</v>
       </c>
       <c r="M74">
         <v>8318</v>
       </c>
       <c r="N74">
-        <v>96956</v>
+        <v>96958</v>
       </c>
       <c r="O74">
-        <v>2330767</v>
+        <v>2330776</v>
       </c>
       <c r="P74">
         <v>4701905</v>
@@ -5001,7 +5001,7 @@
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:P74" numberStoredAsText="1"/>
+    <ignoredError sqref="A2:P74 B1:P1" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/Notice.xlsx
+++ b/Notice.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Downloads\New folder (13)\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0705883-D56B-4F1E-9E95-1E442E301ED6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E59F1867-EE4B-4BD6-B5F5-A914937F9B7E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -292,6 +292,9 @@
     <t>Total</t>
   </si>
   <si>
+    <t>Notice &amp; Hearing Report Last Updated On : 21-09-2026 09:56:45</t>
+  </si>
+  <si>
     <t>DSE with UP</t>
   </si>
   <si>
@@ -302,9 +305,6 @@
   </si>
   <si>
     <t>No Action Required</t>
-  </si>
-  <si>
-    <t>Notice &amp; Hearing Report Last Updated On : 18-09-2026 09:56:47</t>
   </si>
 </sst>
 </file>
@@ -688,7 +688,7 @@
   <sheetData>
     <row r="1" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -743,7 +743,7 @@
       <c r="O2" s="1"/>
       <c r="P2" s="1"/>
       <c r="Q2" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="R2" s="1"/>
       <c r="S2" s="1"/>
@@ -786,13 +786,13 @@
         <v>18</v>
       </c>
       <c r="Q3" s="2" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="R3" s="2" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="S3" s="2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="4" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
@@ -948,16 +948,16 @@
         <v>0</v>
       </c>
       <c r="L6">
-        <v>6052</v>
+        <v>6075</v>
       </c>
       <c r="M6">
         <v>201</v>
       </c>
       <c r="N6">
-        <v>1827</v>
+        <v>1863</v>
       </c>
       <c r="O6">
-        <v>37324</v>
+        <v>37869</v>
       </c>
       <c r="P6">
         <v>71989</v>
@@ -1013,10 +1013,10 @@
         <v>257</v>
       </c>
       <c r="N7">
-        <v>1991</v>
+        <v>1995</v>
       </c>
       <c r="O7">
-        <v>37230</v>
+        <v>37266</v>
       </c>
       <c r="P7">
         <v>77581</v>
@@ -1060,7 +1060,7 @@
         <v>0</v>
       </c>
       <c r="J8">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="K8">
         <v>0</v>
@@ -1311,7 +1311,7 @@
         <v>1133</v>
       </c>
       <c r="O12">
-        <v>39579</v>
+        <v>39588</v>
       </c>
       <c r="P12">
         <v>66685</v>
@@ -1426,10 +1426,10 @@
         <v>1456</v>
       </c>
       <c r="N14">
-        <v>5856</v>
+        <v>5864</v>
       </c>
       <c r="O14">
-        <v>43081</v>
+        <v>43096</v>
       </c>
       <c r="P14">
         <v>77955</v>
@@ -2193,10 +2193,10 @@
         <v>215</v>
       </c>
       <c r="N27">
-        <v>3284</v>
+        <v>3287</v>
       </c>
       <c r="O27">
-        <v>41008</v>
+        <v>41005</v>
       </c>
       <c r="P27">
         <v>73109</v>
@@ -3904,7 +3904,7 @@
         <v>3</v>
       </c>
       <c r="N56">
-        <v>447</v>
+        <v>451</v>
       </c>
       <c r="O56">
         <v>18805</v>
@@ -4069,13 +4069,13 @@
         <v>0</v>
       </c>
       <c r="J59">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K59">
         <v>0</v>
       </c>
       <c r="L59">
-        <v>2504</v>
+        <v>2506</v>
       </c>
       <c r="M59">
         <v>2</v>
@@ -4084,7 +4084,7 @@
         <v>287</v>
       </c>
       <c r="O59">
-        <v>18487</v>
+        <v>18489</v>
       </c>
       <c r="P59">
         <v>60495</v>
@@ -4952,22 +4952,22 @@
         <v>0</v>
       </c>
       <c r="J74">
-        <v>1</v>
+        <v>45</v>
       </c>
       <c r="K74">
         <v>0</v>
       </c>
       <c r="L74">
-        <v>625507</v>
+        <v>625532</v>
       </c>
       <c r="M74">
         <v>8318</v>
       </c>
       <c r="N74">
-        <v>96958</v>
+        <v>97013</v>
       </c>
       <c r="O74">
-        <v>2330776</v>
+        <v>2331380</v>
       </c>
       <c r="P74">
         <v>4701905</v>

--- a/Notice.xlsx
+++ b/Notice.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Downloads\New folder (13)\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E59F1867-EE4B-4BD6-B5F5-A914937F9B7E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CEA3F735-AB82-4299-B470-477DB483A446}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -292,9 +292,6 @@
     <t>Total</t>
   </si>
   <si>
-    <t>Notice &amp; Hearing Report Last Updated On : 21-09-2026 09:56:45</t>
-  </si>
-  <si>
     <t>DSE with UP</t>
   </si>
   <si>
@@ -305,6 +302,9 @@
   </si>
   <si>
     <t>No Action Required</t>
+  </si>
+  <si>
+    <t>Notice &amp; Hearing Report Last Updated On : 22-09-2026 07:56:44</t>
   </si>
 </sst>
 </file>
@@ -340,8 +340,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
@@ -683,12 +682,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:S76"/>
+  <dimension ref="A1:S74"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -743,7 +742,7 @@
       <c r="O2" s="1"/>
       <c r="P2" s="1"/>
       <c r="Q2" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="R2" s="1"/>
       <c r="S2" s="1"/>
@@ -785,14 +784,14 @@
       <c r="P3" t="s">
         <v>18</v>
       </c>
-      <c r="Q3" s="2" t="s">
+      <c r="Q3" t="s">
+        <v>91</v>
+      </c>
+      <c r="R3" t="s">
         <v>92</v>
       </c>
-      <c r="R3" s="2" t="s">
+      <c r="S3" t="s">
         <v>93</v>
-      </c>
-      <c r="S3" s="2" t="s">
-        <v>94</v>
       </c>
     </row>
     <row r="4" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
@@ -844,13 +843,13 @@
       <c r="P4">
         <v>53812</v>
       </c>
-      <c r="Q4" s="2">
+      <c r="Q4">
         <v>12212</v>
       </c>
-      <c r="R4" s="2">
-        <v>0</v>
-      </c>
-      <c r="S4" s="2">
+      <c r="R4">
+        <v>0</v>
+      </c>
+      <c r="S4">
         <v>11</v>
       </c>
     </row>
@@ -903,13 +902,13 @@
       <c r="P5">
         <v>74848</v>
       </c>
-      <c r="Q5" s="2">
+      <c r="Q5">
         <v>16108</v>
       </c>
-      <c r="R5" s="2">
-        <v>0</v>
-      </c>
-      <c r="S5" s="2">
+      <c r="R5">
+        <v>0</v>
+      </c>
+      <c r="S5">
         <v>30</v>
       </c>
     </row>
@@ -962,13 +961,13 @@
       <c r="P6">
         <v>71989</v>
       </c>
-      <c r="Q6" s="2">
+      <c r="Q6">
         <v>17830</v>
       </c>
-      <c r="R6" s="2">
-        <v>0</v>
-      </c>
-      <c r="S6" s="2">
+      <c r="R6">
+        <v>0</v>
+      </c>
+      <c r="S6">
         <v>54</v>
       </c>
     </row>
@@ -1021,13 +1020,13 @@
       <c r="P7">
         <v>77581</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="Q7">
         <v>20511</v>
       </c>
-      <c r="R7" s="2">
-        <v>0</v>
-      </c>
-      <c r="S7" s="2">
+      <c r="R7">
+        <v>0</v>
+      </c>
+      <c r="S7">
         <v>8</v>
       </c>
     </row>
@@ -1060,13 +1059,13 @@
         <v>0</v>
       </c>
       <c r="J8">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="K8">
         <v>0</v>
       </c>
       <c r="L8">
-        <v>14243</v>
+        <v>14288</v>
       </c>
       <c r="M8">
         <v>164</v>
@@ -1080,13 +1079,13 @@
       <c r="P8">
         <v>73458</v>
       </c>
-      <c r="Q8" s="2">
+      <c r="Q8">
         <v>20788</v>
       </c>
-      <c r="R8" s="2">
-        <v>0</v>
-      </c>
-      <c r="S8" s="2">
+      <c r="R8">
+        <v>0</v>
+      </c>
+      <c r="S8">
         <v>110</v>
       </c>
     </row>
@@ -1139,13 +1138,13 @@
       <c r="P9">
         <v>72913</v>
       </c>
-      <c r="Q9" s="2">
+      <c r="Q9">
         <v>18141</v>
       </c>
-      <c r="R9" s="2">
-        <v>0</v>
-      </c>
-      <c r="S9" s="2">
+      <c r="R9">
+        <v>0</v>
+      </c>
+      <c r="S9">
         <v>110</v>
       </c>
     </row>
@@ -1198,13 +1197,13 @@
       <c r="P10">
         <v>53124</v>
       </c>
-      <c r="Q10" s="2">
+      <c r="Q10">
         <v>9498</v>
       </c>
-      <c r="R10" s="2">
-        <v>0</v>
-      </c>
-      <c r="S10" s="2">
+      <c r="R10">
+        <v>0</v>
+      </c>
+      <c r="S10">
         <v>2</v>
       </c>
     </row>
@@ -1257,13 +1256,13 @@
       <c r="P11">
         <v>84438</v>
       </c>
-      <c r="Q11" s="2">
+      <c r="Q11">
         <v>23477</v>
       </c>
-      <c r="R11" s="2">
-        <v>0</v>
-      </c>
-      <c r="S11" s="2">
+      <c r="R11">
+        <v>0</v>
+      </c>
+      <c r="S11">
         <v>23</v>
       </c>
     </row>
@@ -1316,13 +1315,13 @@
       <c r="P12">
         <v>66685</v>
       </c>
-      <c r="Q12" s="2">
+      <c r="Q12">
         <v>17786</v>
       </c>
-      <c r="R12" s="2">
-        <v>0</v>
-      </c>
-      <c r="S12" s="2">
+      <c r="R12">
+        <v>0</v>
+      </c>
+      <c r="S12">
         <v>3</v>
       </c>
     </row>
@@ -1375,13 +1374,13 @@
       <c r="P13">
         <v>56564</v>
       </c>
-      <c r="Q13" s="2">
+      <c r="Q13">
         <v>16237</v>
       </c>
-      <c r="R13" s="2">
-        <v>0</v>
-      </c>
-      <c r="S13" s="2">
+      <c r="R13">
+        <v>0</v>
+      </c>
+      <c r="S13">
         <v>106</v>
       </c>
     </row>
@@ -1434,13 +1433,13 @@
       <c r="P14">
         <v>77955</v>
       </c>
-      <c r="Q14" s="2">
+      <c r="Q14">
         <v>19716</v>
       </c>
-      <c r="R14" s="2">
-        <v>0</v>
-      </c>
-      <c r="S14" s="2">
+      <c r="R14">
+        <v>0</v>
+      </c>
+      <c r="S14">
         <v>174</v>
       </c>
     </row>
@@ -1493,13 +1492,13 @@
       <c r="P15">
         <v>67178</v>
       </c>
-      <c r="Q15" s="2">
+      <c r="Q15">
         <v>4859</v>
       </c>
-      <c r="R15" s="2">
-        <v>0</v>
-      </c>
-      <c r="S15" s="2">
+      <c r="R15">
+        <v>0</v>
+      </c>
+      <c r="S15">
         <v>50</v>
       </c>
     </row>
@@ -1552,13 +1551,13 @@
       <c r="P16">
         <v>71673</v>
       </c>
-      <c r="Q16" s="2">
+      <c r="Q16">
         <v>5197</v>
       </c>
-      <c r="R16" s="2">
-        <v>0</v>
-      </c>
-      <c r="S16" s="2">
+      <c r="R16">
+        <v>0</v>
+      </c>
+      <c r="S16">
         <v>47</v>
       </c>
     </row>
@@ -1611,13 +1610,13 @@
       <c r="P17">
         <v>65457</v>
       </c>
-      <c r="Q17" s="2">
+      <c r="Q17">
         <v>5417</v>
       </c>
-      <c r="R17" s="2">
-        <v>0</v>
-      </c>
-      <c r="S17" s="2">
+      <c r="R17">
+        <v>0</v>
+      </c>
+      <c r="S17">
         <v>105</v>
       </c>
     </row>
@@ -1670,13 +1669,13 @@
       <c r="P18">
         <v>71475</v>
       </c>
-      <c r="Q18" s="2">
+      <c r="Q18">
         <v>6819</v>
       </c>
-      <c r="R18" s="2">
-        <v>0</v>
-      </c>
-      <c r="S18" s="2">
+      <c r="R18">
+        <v>0</v>
+      </c>
+      <c r="S18">
         <v>32</v>
       </c>
     </row>
@@ -1729,13 +1728,13 @@
       <c r="P19">
         <v>106392</v>
       </c>
-      <c r="Q19" s="2">
+      <c r="Q19">
         <v>6135</v>
       </c>
-      <c r="R19" s="2">
-        <v>0</v>
-      </c>
-      <c r="S19" s="2">
+      <c r="R19">
+        <v>0</v>
+      </c>
+      <c r="S19">
         <v>36</v>
       </c>
     </row>
@@ -1788,13 +1787,13 @@
       <c r="P20">
         <v>75812</v>
       </c>
-      <c r="Q20" s="2">
+      <c r="Q20">
         <v>8984</v>
       </c>
-      <c r="R20" s="2">
-        <v>0</v>
-      </c>
-      <c r="S20" s="2">
+      <c r="R20">
+        <v>0</v>
+      </c>
+      <c r="S20">
         <v>71</v>
       </c>
     </row>
@@ -1847,13 +1846,13 @@
       <c r="P21">
         <v>62460</v>
       </c>
-      <c r="Q21" s="2">
+      <c r="Q21">
         <v>3868</v>
       </c>
-      <c r="R21" s="2">
-        <v>0</v>
-      </c>
-      <c r="S21" s="2">
+      <c r="R21">
+        <v>0</v>
+      </c>
+      <c r="S21">
         <v>0</v>
       </c>
     </row>
@@ -1906,13 +1905,13 @@
       <c r="P22">
         <v>64099</v>
       </c>
-      <c r="Q22" s="2">
+      <c r="Q22">
         <v>4848</v>
       </c>
-      <c r="R22" s="2">
-        <v>0</v>
-      </c>
-      <c r="S22" s="2">
+      <c r="R22">
+        <v>0</v>
+      </c>
+      <c r="S22">
         <v>0</v>
       </c>
     </row>
@@ -1965,13 +1964,13 @@
       <c r="P23">
         <v>57094</v>
       </c>
-      <c r="Q23" s="2">
+      <c r="Q23">
         <v>3541</v>
       </c>
-      <c r="R23" s="2">
-        <v>0</v>
-      </c>
-      <c r="S23" s="2">
+      <c r="R23">
+        <v>0</v>
+      </c>
+      <c r="S23">
         <v>28</v>
       </c>
     </row>
@@ -2024,13 +2023,13 @@
       <c r="P24">
         <v>65629</v>
       </c>
-      <c r="Q24" s="2">
+      <c r="Q24">
         <v>3492</v>
       </c>
-      <c r="R24" s="2">
-        <v>0</v>
-      </c>
-      <c r="S24" s="2">
+      <c r="R24">
+        <v>0</v>
+      </c>
+      <c r="S24">
         <v>0</v>
       </c>
     </row>
@@ -2083,13 +2082,13 @@
       <c r="P25">
         <v>57533</v>
       </c>
-      <c r="Q25" s="2">
+      <c r="Q25">
         <v>3231</v>
       </c>
-      <c r="R25" s="2">
-        <v>0</v>
-      </c>
-      <c r="S25" s="2">
+      <c r="R25">
+        <v>0</v>
+      </c>
+      <c r="S25">
         <v>13</v>
       </c>
     </row>
@@ -2142,13 +2141,13 @@
       <c r="P26">
         <v>66594</v>
       </c>
-      <c r="Q26" s="2">
+      <c r="Q26">
         <v>3333</v>
       </c>
-      <c r="R26" s="2">
-        <v>0</v>
-      </c>
-      <c r="S26" s="2">
+      <c r="R26">
+        <v>0</v>
+      </c>
+      <c r="S26">
         <v>2</v>
       </c>
     </row>
@@ -2201,13 +2200,13 @@
       <c r="P27">
         <v>73109</v>
       </c>
-      <c r="Q27" s="2">
+      <c r="Q27">
         <v>12669</v>
       </c>
-      <c r="R27" s="2">
-        <v>0</v>
-      </c>
-      <c r="S27" s="2">
+      <c r="R27">
+        <v>0</v>
+      </c>
+      <c r="S27">
         <v>0</v>
       </c>
     </row>
@@ -2260,13 +2259,13 @@
       <c r="P28">
         <v>80620</v>
       </c>
-      <c r="Q28" s="2">
+      <c r="Q28">
         <v>13995</v>
       </c>
-      <c r="R28" s="2">
-        <v>0</v>
-      </c>
-      <c r="S28" s="2">
+      <c r="R28">
+        <v>0</v>
+      </c>
+      <c r="S28">
         <v>127</v>
       </c>
     </row>
@@ -2319,13 +2318,13 @@
       <c r="P29">
         <v>83836</v>
       </c>
-      <c r="Q29" s="2">
+      <c r="Q29">
         <v>14229</v>
       </c>
-      <c r="R29" s="2">
-        <v>0</v>
-      </c>
-      <c r="S29" s="2">
+      <c r="R29">
+        <v>0</v>
+      </c>
+      <c r="S29">
         <v>22</v>
       </c>
     </row>
@@ -2378,13 +2377,13 @@
       <c r="P30">
         <v>86933</v>
       </c>
-      <c r="Q30" s="2">
+      <c r="Q30">
         <v>12564</v>
       </c>
-      <c r="R30" s="2">
-        <v>0</v>
-      </c>
-      <c r="S30" s="2">
+      <c r="R30">
+        <v>0</v>
+      </c>
+      <c r="S30">
         <v>8</v>
       </c>
     </row>
@@ -2437,13 +2436,13 @@
       <c r="P31">
         <v>81642</v>
       </c>
-      <c r="Q31" s="2">
+      <c r="Q31">
         <v>14581</v>
       </c>
-      <c r="R31" s="2">
-        <v>0</v>
-      </c>
-      <c r="S31" s="2">
+      <c r="R31">
+        <v>0</v>
+      </c>
+      <c r="S31">
         <v>39</v>
       </c>
     </row>
@@ -2496,13 +2495,13 @@
       <c r="P32">
         <v>74810</v>
       </c>
-      <c r="Q32" s="2">
+      <c r="Q32">
         <v>11379</v>
       </c>
-      <c r="R32" s="2">
-        <v>0</v>
-      </c>
-      <c r="S32" s="2">
+      <c r="R32">
+        <v>0</v>
+      </c>
+      <c r="S32">
         <v>0</v>
       </c>
     </row>
@@ -2555,13 +2554,13 @@
       <c r="P33">
         <v>76969</v>
       </c>
-      <c r="Q33" s="2">
+      <c r="Q33">
         <v>6678</v>
       </c>
-      <c r="R33" s="2">
-        <v>0</v>
-      </c>
-      <c r="S33" s="2">
+      <c r="R33">
+        <v>0</v>
+      </c>
+      <c r="S33">
         <v>19</v>
       </c>
     </row>
@@ -2614,13 +2613,13 @@
       <c r="P34">
         <v>74624</v>
       </c>
-      <c r="Q34" s="2">
+      <c r="Q34">
         <v>7137</v>
       </c>
-      <c r="R34" s="2">
-        <v>0</v>
-      </c>
-      <c r="S34" s="2">
+      <c r="R34">
+        <v>0</v>
+      </c>
+      <c r="S34">
         <v>0</v>
       </c>
     </row>
@@ -2673,13 +2672,13 @@
       <c r="P35">
         <v>76464</v>
       </c>
-      <c r="Q35" s="2">
+      <c r="Q35">
         <v>8879</v>
       </c>
-      <c r="R35" s="2">
-        <v>0</v>
-      </c>
-      <c r="S35" s="2">
+      <c r="R35">
+        <v>0</v>
+      </c>
+      <c r="S35">
         <v>35</v>
       </c>
     </row>
@@ -2732,13 +2731,13 @@
       <c r="P36">
         <v>60419</v>
       </c>
-      <c r="Q36" s="2">
+      <c r="Q36">
         <v>3855</v>
       </c>
-      <c r="R36" s="2">
-        <v>0</v>
-      </c>
-      <c r="S36" s="2">
+      <c r="R36">
+        <v>0</v>
+      </c>
+      <c r="S36">
         <v>2</v>
       </c>
     </row>
@@ -2791,13 +2790,13 @@
       <c r="P37">
         <v>57832</v>
       </c>
-      <c r="Q37" s="2">
+      <c r="Q37">
         <v>4036</v>
       </c>
-      <c r="R37" s="2">
-        <v>0</v>
-      </c>
-      <c r="S37" s="2">
+      <c r="R37">
+        <v>0</v>
+      </c>
+      <c r="S37">
         <v>1</v>
       </c>
     </row>
@@ -2850,13 +2849,13 @@
       <c r="P38">
         <v>63038</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="Q38">
         <v>5135</v>
       </c>
-      <c r="R38" s="2">
-        <v>0</v>
-      </c>
-      <c r="S38" s="2">
+      <c r="R38">
+        <v>0</v>
+      </c>
+      <c r="S38">
         <v>0</v>
       </c>
     </row>
@@ -2909,13 +2908,13 @@
       <c r="P39">
         <v>71133</v>
       </c>
-      <c r="Q39" s="2">
+      <c r="Q39">
         <v>5903</v>
       </c>
-      <c r="R39" s="2">
-        <v>0</v>
-      </c>
-      <c r="S39" s="2">
+      <c r="R39">
+        <v>0</v>
+      </c>
+      <c r="S39">
         <v>26</v>
       </c>
     </row>
@@ -2968,13 +2967,13 @@
       <c r="P40">
         <v>73242</v>
       </c>
-      <c r="Q40" s="2">
+      <c r="Q40">
         <v>3824</v>
       </c>
-      <c r="R40" s="2">
-        <v>0</v>
-      </c>
-      <c r="S40" s="2">
+      <c r="R40">
+        <v>0</v>
+      </c>
+      <c r="S40">
         <v>61</v>
       </c>
     </row>
@@ -3027,13 +3026,13 @@
       <c r="P41">
         <v>85251</v>
       </c>
-      <c r="Q41" s="2">
+      <c r="Q41">
         <v>6015</v>
       </c>
-      <c r="R41" s="2">
-        <v>0</v>
-      </c>
-      <c r="S41" s="2">
+      <c r="R41">
+        <v>0</v>
+      </c>
+      <c r="S41">
         <v>27</v>
       </c>
     </row>
@@ -3086,13 +3085,13 @@
       <c r="P42">
         <v>68615</v>
       </c>
-      <c r="Q42" s="2">
+      <c r="Q42">
         <v>4708</v>
       </c>
-      <c r="R42" s="2">
-        <v>0</v>
-      </c>
-      <c r="S42" s="2">
+      <c r="R42">
+        <v>0</v>
+      </c>
+      <c r="S42">
         <v>8</v>
       </c>
     </row>
@@ -3145,13 +3144,13 @@
       <c r="P43">
         <v>63012</v>
       </c>
-      <c r="Q43" s="2">
+      <c r="Q43">
         <v>5219</v>
       </c>
-      <c r="R43" s="2">
-        <v>0</v>
-      </c>
-      <c r="S43" s="2">
+      <c r="R43">
+        <v>0</v>
+      </c>
+      <c r="S43">
         <v>121</v>
       </c>
     </row>
@@ -3204,13 +3203,13 @@
       <c r="P44">
         <v>68393</v>
       </c>
-      <c r="Q44" s="2">
+      <c r="Q44">
         <v>7659</v>
       </c>
-      <c r="R44" s="2">
-        <v>0</v>
-      </c>
-      <c r="S44" s="2">
+      <c r="R44">
+        <v>0</v>
+      </c>
+      <c r="S44">
         <v>20</v>
       </c>
     </row>
@@ -3263,13 +3262,13 @@
       <c r="P45">
         <v>76287</v>
       </c>
-      <c r="Q45" s="2">
+      <c r="Q45">
         <v>6998</v>
       </c>
-      <c r="R45" s="2">
-        <v>0</v>
-      </c>
-      <c r="S45" s="2">
+      <c r="R45">
+        <v>0</v>
+      </c>
+      <c r="S45">
         <v>129</v>
       </c>
     </row>
@@ -3322,13 +3321,13 @@
       <c r="P46">
         <v>64160</v>
       </c>
-      <c r="Q46" s="2">
+      <c r="Q46">
         <v>7548</v>
       </c>
-      <c r="R46" s="2">
-        <v>0</v>
-      </c>
-      <c r="S46" s="2">
+      <c r="R46">
+        <v>0</v>
+      </c>
+      <c r="S46">
         <v>152</v>
       </c>
     </row>
@@ -3381,13 +3380,13 @@
       <c r="P47">
         <v>49875</v>
       </c>
-      <c r="Q47" s="2">
+      <c r="Q47">
         <v>5046</v>
       </c>
-      <c r="R47" s="2">
-        <v>0</v>
-      </c>
-      <c r="S47" s="2">
+      <c r="R47">
+        <v>0</v>
+      </c>
+      <c r="S47">
         <v>0</v>
       </c>
     </row>
@@ -3440,13 +3439,13 @@
       <c r="P48">
         <v>54142</v>
       </c>
-      <c r="Q48" s="2">
+      <c r="Q48">
         <v>4623</v>
       </c>
-      <c r="R48" s="2">
-        <v>0</v>
-      </c>
-      <c r="S48" s="2">
+      <c r="R48">
+        <v>0</v>
+      </c>
+      <c r="S48">
         <v>9</v>
       </c>
     </row>
@@ -3499,13 +3498,13 @@
       <c r="P49">
         <v>55376</v>
       </c>
-      <c r="Q49" s="2">
+      <c r="Q49">
         <v>5057</v>
       </c>
-      <c r="R49" s="2">
-        <v>0</v>
-      </c>
-      <c r="S49" s="2">
+      <c r="R49">
+        <v>0</v>
+      </c>
+      <c r="S49">
         <v>4</v>
       </c>
     </row>
@@ -3558,13 +3557,13 @@
       <c r="P50">
         <v>63298</v>
       </c>
-      <c r="Q50" s="2">
+      <c r="Q50">
         <v>7292</v>
       </c>
-      <c r="R50" s="2">
-        <v>0</v>
-      </c>
-      <c r="S50" s="2">
+      <c r="R50">
+        <v>0</v>
+      </c>
+      <c r="S50">
         <v>1</v>
       </c>
     </row>
@@ -3617,13 +3616,13 @@
       <c r="P51">
         <v>71754</v>
       </c>
-      <c r="Q51" s="2">
+      <c r="Q51">
         <v>7715</v>
       </c>
-      <c r="R51" s="2">
-        <v>0</v>
-      </c>
-      <c r="S51" s="2">
+      <c r="R51">
+        <v>0</v>
+      </c>
+      <c r="S51">
         <v>40</v>
       </c>
     </row>
@@ -3676,13 +3675,13 @@
       <c r="P52">
         <v>63987</v>
       </c>
-      <c r="Q52" s="2">
+      <c r="Q52">
         <v>5655</v>
       </c>
-      <c r="R52" s="2">
-        <v>0</v>
-      </c>
-      <c r="S52" s="2">
+      <c r="R52">
+        <v>0</v>
+      </c>
+      <c r="S52">
         <v>2</v>
       </c>
     </row>
@@ -3735,13 +3734,13 @@
       <c r="P53">
         <v>56306</v>
       </c>
-      <c r="Q53" s="2">
+      <c r="Q53">
         <v>6551</v>
       </c>
-      <c r="R53" s="2">
-        <v>0</v>
-      </c>
-      <c r="S53" s="2">
+      <c r="R53">
+        <v>0</v>
+      </c>
+      <c r="S53">
         <v>5</v>
       </c>
     </row>
@@ -3794,13 +3793,13 @@
       <c r="P54">
         <v>58440</v>
       </c>
-      <c r="Q54" s="2">
+      <c r="Q54">
         <v>7347</v>
       </c>
-      <c r="R54" s="2">
-        <v>0</v>
-      </c>
-      <c r="S54" s="2">
+      <c r="R54">
+        <v>0</v>
+      </c>
+      <c r="S54">
         <v>1</v>
       </c>
     </row>
@@ -3853,13 +3852,13 @@
       <c r="P55">
         <v>58215</v>
       </c>
-      <c r="Q55" s="2">
+      <c r="Q55">
         <v>5098</v>
       </c>
-      <c r="R55" s="2">
-        <v>0</v>
-      </c>
-      <c r="S55" s="2">
+      <c r="R55">
+        <v>0</v>
+      </c>
+      <c r="S55">
         <v>0</v>
       </c>
     </row>
@@ -3912,13 +3911,13 @@
       <c r="P56">
         <v>47621</v>
       </c>
-      <c r="Q56" s="2">
+      <c r="Q56">
         <v>4882</v>
       </c>
-      <c r="R56" s="2">
-        <v>0</v>
-      </c>
-      <c r="S56" s="2">
+      <c r="R56">
+        <v>0</v>
+      </c>
+      <c r="S56">
         <v>30</v>
       </c>
     </row>
@@ -3971,13 +3970,13 @@
       <c r="P57">
         <v>61556</v>
       </c>
-      <c r="Q57" s="2">
+      <c r="Q57">
         <v>6870</v>
       </c>
-      <c r="R57" s="2">
-        <v>0</v>
-      </c>
-      <c r="S57" s="2">
+      <c r="R57">
+        <v>0</v>
+      </c>
+      <c r="S57">
         <v>0</v>
       </c>
     </row>
@@ -4030,13 +4029,13 @@
       <c r="P58">
         <v>57577</v>
       </c>
-      <c r="Q58" s="2">
+      <c r="Q58">
         <v>8884</v>
       </c>
-      <c r="R58" s="2">
-        <v>0</v>
-      </c>
-      <c r="S58" s="2">
+      <c r="R58">
+        <v>0</v>
+      </c>
+      <c r="S58">
         <v>64</v>
       </c>
     </row>
@@ -4089,13 +4088,13 @@
       <c r="P59">
         <v>60495</v>
       </c>
-      <c r="Q59" s="2">
+      <c r="Q59">
         <v>8028</v>
       </c>
-      <c r="R59" s="2">
-        <v>0</v>
-      </c>
-      <c r="S59" s="2">
+      <c r="R59">
+        <v>0</v>
+      </c>
+      <c r="S59">
         <v>27</v>
       </c>
     </row>
@@ -4148,13 +4147,13 @@
       <c r="P60">
         <v>70140</v>
       </c>
-      <c r="Q60" s="2">
+      <c r="Q60">
         <v>7415</v>
       </c>
-      <c r="R60" s="2">
-        <v>0</v>
-      </c>
-      <c r="S60" s="2">
+      <c r="R60">
+        <v>0</v>
+      </c>
+      <c r="S60">
         <v>32</v>
       </c>
     </row>
@@ -4207,13 +4206,13 @@
       <c r="P61">
         <v>55240</v>
       </c>
-      <c r="Q61" s="2">
+      <c r="Q61">
         <v>7927</v>
       </c>
-      <c r="R61" s="2">
+      <c r="R61">
         <v>1</v>
       </c>
-      <c r="S61" s="2">
+      <c r="S61">
         <v>268</v>
       </c>
     </row>
@@ -4266,13 +4265,13 @@
       <c r="P62">
         <v>51334</v>
       </c>
-      <c r="Q62" s="2">
+      <c r="Q62">
         <v>6917</v>
       </c>
-      <c r="R62" s="2">
-        <v>0</v>
-      </c>
-      <c r="S62" s="2">
+      <c r="R62">
+        <v>0</v>
+      </c>
+      <c r="S62">
         <v>100</v>
       </c>
     </row>
@@ -4325,13 +4324,13 @@
       <c r="P63">
         <v>68696</v>
       </c>
-      <c r="Q63" s="2">
+      <c r="Q63">
         <v>9766</v>
       </c>
-      <c r="R63" s="2">
-        <v>0</v>
-      </c>
-      <c r="S63" s="2">
+      <c r="R63">
+        <v>0</v>
+      </c>
+      <c r="S63">
         <v>153</v>
       </c>
     </row>
@@ -4384,13 +4383,13 @@
       <c r="P64">
         <v>60527</v>
       </c>
-      <c r="Q64" s="2">
+      <c r="Q64">
         <v>5985</v>
       </c>
-      <c r="R64" s="2">
-        <v>0</v>
-      </c>
-      <c r="S64" s="2">
+      <c r="R64">
+        <v>0</v>
+      </c>
+      <c r="S64">
         <v>101</v>
       </c>
     </row>
@@ -4443,13 +4442,13 @@
       <c r="P65">
         <v>58527</v>
       </c>
-      <c r="Q65" s="2">
+      <c r="Q65">
         <v>13282</v>
       </c>
-      <c r="R65" s="2">
-        <v>0</v>
-      </c>
-      <c r="S65" s="2">
+      <c r="R65">
+        <v>0</v>
+      </c>
+      <c r="S65">
         <v>138</v>
       </c>
     </row>
@@ -4502,13 +4501,13 @@
       <c r="P66">
         <v>93810</v>
       </c>
-      <c r="Q66" s="2">
+      <c r="Q66">
         <v>17742</v>
       </c>
-      <c r="R66" s="2">
-        <v>0</v>
-      </c>
-      <c r="S66" s="2">
+      <c r="R66">
+        <v>0</v>
+      </c>
+      <c r="S66">
         <v>52</v>
       </c>
     </row>
@@ -4561,13 +4560,13 @@
       <c r="P67">
         <v>78032</v>
       </c>
-      <c r="Q67" s="2">
+      <c r="Q67">
         <v>9807</v>
       </c>
-      <c r="R67" s="2">
-        <v>0</v>
-      </c>
-      <c r="S67" s="2">
+      <c r="R67">
+        <v>0</v>
+      </c>
+      <c r="S67">
         <v>116</v>
       </c>
     </row>
@@ -4620,13 +4619,13 @@
       <c r="P68">
         <v>71325</v>
       </c>
-      <c r="Q68" s="2">
+      <c r="Q68">
         <v>7850</v>
       </c>
-      <c r="R68" s="2">
-        <v>0</v>
-      </c>
-      <c r="S68" s="2">
+      <c r="R68">
+        <v>0</v>
+      </c>
+      <c r="S68">
         <v>26</v>
       </c>
     </row>
@@ -4679,13 +4678,13 @@
       <c r="P69">
         <v>36118</v>
       </c>
-      <c r="Q69" s="2">
+      <c r="Q69">
         <v>6528</v>
       </c>
-      <c r="R69" s="2">
-        <v>0</v>
-      </c>
-      <c r="S69" s="2">
+      <c r="R69">
+        <v>0</v>
+      </c>
+      <c r="S69">
         <v>47</v>
       </c>
     </row>
@@ -4738,13 +4737,13 @@
       <c r="P70">
         <v>42051</v>
       </c>
-      <c r="Q70" s="2">
+      <c r="Q70">
         <v>5798</v>
       </c>
-      <c r="R70" s="2">
-        <v>0</v>
-      </c>
-      <c r="S70" s="2">
+      <c r="R70">
+        <v>0</v>
+      </c>
+      <c r="S70">
         <v>29</v>
       </c>
     </row>
@@ -4789,21 +4788,21 @@
         <v>1</v>
       </c>
       <c r="N71">
-        <v>4442</v>
+        <v>4449</v>
       </c>
       <c r="O71">
-        <v>46521</v>
+        <v>46514</v>
       </c>
       <c r="P71">
         <v>49140</v>
       </c>
-      <c r="Q71" s="2">
+      <c r="Q71">
         <v>6782</v>
       </c>
-      <c r="R71" s="2">
-        <v>0</v>
-      </c>
-      <c r="S71" s="2">
+      <c r="R71">
+        <v>0</v>
+      </c>
+      <c r="S71">
         <v>235</v>
       </c>
     </row>
@@ -4856,13 +4855,13 @@
       <c r="P72">
         <v>85505</v>
       </c>
-      <c r="Q72" s="2">
+      <c r="Q72">
         <v>12340</v>
       </c>
-      <c r="R72" s="2">
-        <v>0</v>
-      </c>
-      <c r="S72" s="2">
+      <c r="R72">
+        <v>0</v>
+      </c>
+      <c r="S72">
         <v>79</v>
       </c>
     </row>
@@ -4915,13 +4914,13 @@
       <c r="P73">
         <v>67666</v>
       </c>
-      <c r="Q73" s="2">
+      <c r="Q73">
         <v>10010</v>
       </c>
-      <c r="R73" s="2">
-        <v>0</v>
-      </c>
-      <c r="S73" s="2">
+      <c r="R73">
+        <v>0</v>
+      </c>
+      <c r="S73">
         <v>74</v>
       </c>
     </row>
@@ -4952,38 +4951,36 @@
         <v>0</v>
       </c>
       <c r="J74">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="K74">
         <v>0</v>
       </c>
       <c r="L74">
-        <v>625532</v>
+        <v>625577</v>
       </c>
       <c r="M74">
         <v>8318</v>
       </c>
       <c r="N74">
-        <v>97013</v>
+        <v>97020</v>
       </c>
       <c r="O74">
-        <v>2331380</v>
+        <v>2331373</v>
       </c>
       <c r="P74">
         <v>4701905</v>
       </c>
-      <c r="Q74" s="2">
+      <c r="Q74">
         <v>626236</v>
       </c>
-      <c r="R74" s="2">
+      <c r="R74">
         <v>1</v>
       </c>
-      <c r="S74" s="2">
+      <c r="S74">
         <v>3445</v>
       </c>
     </row>
-    <row r="75" spans="1:19" ht="15.75" x14ac:dyDescent="0.25"/>
-    <row r="76" spans="1:19" ht="15.75" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="12">
     <mergeCell ref="A74:B74"/>

--- a/Notice.xlsx
+++ b/Notice.xlsx
@@ -1,317 +1,41 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <workbookPr codeName="ThisWorkbook"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Downloads\New folder (13)\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CEA3F735-AB82-4299-B470-477DB483A446}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
-  <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
-  </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="95">
-  <si>
-    <t>S. No.</t>
-  </si>
-  <si>
-    <t>AC No. - AC Name</t>
-  </si>
-  <si>
-    <t>Notice Generated</t>
-  </si>
-  <si>
-    <t>Pending for Notice Generation</t>
-  </si>
-  <si>
-    <t>Notice Delivered</t>
-  </si>
-  <si>
-    <t>Notices pending delivery</t>
-  </si>
-  <si>
-    <t>Hearing</t>
-  </si>
-  <si>
-    <t>DEO Status</t>
-  </si>
-  <si>
-    <t>ERO/AERO Status</t>
-  </si>
-  <si>
-    <t>Hearing Held</t>
-  </si>
-  <si>
-    <t>Hearing Date Lapsed</t>
-  </si>
-  <si>
-    <t>Reschedule Date Lapsed</t>
-  </si>
-  <si>
-    <t>Total Pending</t>
-  </si>
-  <si>
-    <t>Pending &gt; 5 days</t>
-  </si>
-  <si>
-    <t>Verified</t>
-  </si>
-  <si>
-    <t>Not Verified</t>
-  </si>
-  <si>
-    <t>Found Ineligible for Final</t>
-  </si>
-  <si>
-    <t>Parked for Final Publication w.r.t. Notices Generated</t>
-  </si>
-  <si>
-    <t>Parked For Final Publication w.r.t. Others</t>
-  </si>
-  <si>
-    <t>25 - Haridwar</t>
-  </si>
-  <si>
-    <t>26 - BHEL Ranipur</t>
-  </si>
-  <si>
-    <t>27 - Jwalapur</t>
-  </si>
-  <si>
-    <t>28 - Bhagwanpur</t>
-  </si>
-  <si>
-    <t>29 - Jhabrera</t>
-  </si>
-  <si>
-    <t>30 - Piran Kaliyar</t>
-  </si>
-  <si>
-    <t>31 - Roorkee</t>
-  </si>
-  <si>
-    <t>32 - Khanpur</t>
-  </si>
-  <si>
-    <t>33 - Manglore</t>
-  </si>
-  <si>
-    <t>34 - Laksar</t>
-  </si>
-  <si>
-    <t>35 - Haridwar Rural</t>
-  </si>
-  <si>
-    <t>56 - Lalkuan</t>
-  </si>
-  <si>
-    <t>57 - Bhimtal</t>
-  </si>
-  <si>
-    <t>58 - Nainital</t>
-  </si>
-  <si>
-    <t>59 - Haldwani</t>
-  </si>
-  <si>
-    <t>60 - Kaladhungi</t>
-  </si>
-  <si>
-    <t>61 - Ramnagar</t>
-  </si>
-  <si>
-    <t>48 - Dwarahat</t>
-  </si>
-  <si>
-    <t>49 - Salt</t>
-  </si>
-  <si>
-    <t>50 - Ranikhet</t>
-  </si>
-  <si>
-    <t>51 - Someshwar</t>
-  </si>
-  <si>
-    <t>52 - Almora</t>
-  </si>
-  <si>
-    <t>53 - Jageshwar</t>
-  </si>
-  <si>
-    <t>62 - Jaspur</t>
-  </si>
-  <si>
-    <t>63 - Kashipur</t>
-  </si>
-  <si>
-    <t>64 - Bajpur</t>
-  </si>
-  <si>
-    <t>65 - Gadarpur</t>
-  </si>
-  <si>
-    <t>66 - Rudrapur</t>
-  </si>
-  <si>
-    <t>67 - Kichha</t>
-  </si>
-  <si>
-    <t>68 - Sitarganj</t>
-  </si>
-  <si>
-    <t>69 - Nanakmatta</t>
-  </si>
-  <si>
-    <t>70 - Khatima</t>
-  </si>
-  <si>
-    <t>42 - Dharchula</t>
-  </si>
-  <si>
-    <t>43 - Didihat</t>
-  </si>
-  <si>
-    <t>44 - Pithoragarh</t>
-  </si>
-  <si>
-    <t>45 - Gangolihat</t>
-  </si>
-  <si>
-    <t>46 - Kapkot</t>
-  </si>
-  <si>
-    <t>47 - Bageshwar</t>
-  </si>
-  <si>
-    <t>54 - Lohaghat</t>
-  </si>
-  <si>
-    <t>55 - Champawat</t>
-  </si>
-  <si>
-    <t>4 - Badrinath</t>
-  </si>
-  <si>
-    <t>5 - Tharali</t>
-  </si>
-  <si>
-    <t>6 - Karanprayag</t>
-  </si>
-  <si>
-    <t>1 - Purola</t>
-  </si>
-  <si>
-    <t>2 - Yamunotri</t>
-  </si>
-  <si>
-    <t>3 - Gangotri</t>
-  </si>
-  <si>
-    <t>7 - Kedarnath</t>
-  </si>
-  <si>
-    <t>8 - Rudraprayag</t>
-  </si>
-  <si>
-    <t>9 - Ghansali</t>
-  </si>
-  <si>
-    <t>10 - Devprayag</t>
-  </si>
-  <si>
-    <t>11 - Narendranagar</t>
-  </si>
-  <si>
-    <t>12 - Pratapnagar</t>
-  </si>
-  <si>
-    <t>13 - Tehri</t>
-  </si>
-  <si>
-    <t>14 - Dhanolti</t>
-  </si>
-  <si>
-    <t>36 - Yamkeshwar</t>
-  </si>
-  <si>
-    <t>37 - Pauri</t>
-  </si>
-  <si>
-    <t>38 - Srinagar</t>
-  </si>
-  <si>
-    <t>39 - Chaubattakhal</t>
-  </si>
-  <si>
-    <t>40 - Lansdowne</t>
-  </si>
-  <si>
-    <t>41 - Kotdwar</t>
-  </si>
-  <si>
-    <t>15 - Chakrata</t>
-  </si>
-  <si>
-    <t>16 - Vikasnagar</t>
-  </si>
-  <si>
-    <t>17 - Sahaspur</t>
-  </si>
-  <si>
-    <t>18 - Dharmpur</t>
-  </si>
-  <si>
-    <t>19 - Raipur</t>
-  </si>
-  <si>
-    <t>20 - Rajpur Road</t>
-  </si>
-  <si>
-    <t>21 - Dehradun Cantonment</t>
-  </si>
-  <si>
-    <t>22 - Mussoorie</t>
-  </si>
-  <si>
-    <t>23 - Doiwala</t>
-  </si>
-  <si>
-    <t>24 - Rishikesh</t>
-  </si>
-  <si>
-    <t>Total</t>
-  </si>
-  <si>
-    <t>DSE with UP</t>
-  </si>
-  <si>
-    <t>Electors having DSE with UP</t>
-  </si>
-  <si>
-    <t>Form 7 Generated</t>
-  </si>
-  <si>
-    <t>No Action Required</t>
-  </si>
-  <si>
-    <t>Notice &amp; Hearing Report Last Updated On : 22-09-2026 07:56:44</t>
-  </si>
-</sst>
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
+  <numFmts count="1">
+    <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
+  </numFmts>
+  <fonts count="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -340,23 +64,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+  <cellXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
@@ -681,125 +396,84 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:S74"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:Q74"/>
   <sheetData>
-    <row r="1" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
-      <c r="H1" s="1"/>
-      <c r="I1" s="1"/>
-      <c r="J1" s="1"/>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
-      <c r="M1" s="1"/>
-      <c r="N1" s="1"/>
-      <c r="O1" s="1"/>
-      <c r="P1" s="1"/>
-      <c r="Q1" s="1"/>
-    </row>
-    <row r="2" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H2" s="1"/>
-      <c r="I2" s="1"/>
-      <c r="J2" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="K2" s="1"/>
-      <c r="L2" s="1"/>
-      <c r="M2" s="1"/>
-      <c r="N2" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="O2" s="1"/>
-      <c r="P2" s="1"/>
-      <c r="Q2" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="R2" s="1"/>
-      <c r="S2" s="1"/>
-    </row>
-    <row r="3" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A3" s="1"/>
-      <c r="B3" s="1"/>
-      <c r="C3" s="1"/>
-      <c r="D3" s="1"/>
-      <c r="E3" s="1"/>
-      <c r="F3" s="1"/>
-      <c r="G3" t="s">
-        <v>9</v>
-      </c>
-      <c r="H3" t="s">
-        <v>10</v>
-      </c>
-      <c r="I3" t="s">
-        <v>11</v>
-      </c>
-      <c r="J3" t="s">
-        <v>12</v>
-      </c>
-      <c r="K3" t="s">
-        <v>13</v>
-      </c>
-      <c r="L3" t="s">
-        <v>14</v>
-      </c>
-      <c r="M3" t="s">
-        <v>15</v>
-      </c>
-      <c r="N3" t="s">
-        <v>16</v>
-      </c>
-      <c r="O3" t="s">
-        <v>17</v>
-      </c>
-      <c r="P3" t="s">
-        <v>18</v>
-      </c>
-      <c r="Q3" t="s">
-        <v>91</v>
-      </c>
-      <c r="R3" t="s">
-        <v>92</v>
-      </c>
-      <c r="S3" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="4" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Notice &amp; Hearing Report</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>S. No.</v>
+      </c>
+      <c r="B2" t="str">
+        <v>AC No. - AC Name</v>
+      </c>
+      <c r="C2" t="str">
+        <v>Notice Generated</v>
+      </c>
+      <c r="D2" t="str">
+        <v>Pending for Notice Generation</v>
+      </c>
+      <c r="E2" t="str">
+        <v>Form 7/8 (Shifting)</v>
+      </c>
+      <c r="F2" t="str">
+        <v>Notice Delivered</v>
+      </c>
+      <c r="G2" t="str">
+        <v>Notices pending delivery</v>
+      </c>
+      <c r="H2" t="str">
+        <v>Hearing</v>
+      </c>
+      <c r="K2" t="str">
+        <v>DEO Status</v>
+      </c>
+      <c r="O2" t="str">
+        <v>ERO/AERO Status</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="H3" t="str">
+        <v>Hearing Held</v>
+      </c>
+      <c r="I3" t="str">
+        <v>Hearing Date Lapsed</v>
+      </c>
+      <c r="J3" t="str">
+        <v>Reschedule Date Lapsed</v>
+      </c>
+      <c r="K3" t="str">
+        <v>Total Pending</v>
+      </c>
+      <c r="L3" t="str">
+        <v>Pending &gt; 5 days</v>
+      </c>
+      <c r="M3" t="str">
+        <v>Verified</v>
+      </c>
+      <c r="N3" t="str">
+        <v>Not Verified</v>
+      </c>
+      <c r="O3" t="str">
+        <v>Found Ineligible for Final</v>
+      </c>
+      <c r="P3" t="str">
+        <v>Parked for Final Publication w.r.t. Notices Generated</v>
+      </c>
+      <c r="Q3" t="str">
+        <v>Parked For Final Publication w.r.t. Others</v>
+      </c>
+    </row>
+    <row r="4">
       <c r="A4">
         <v>1</v>
       </c>
-      <c r="B4" t="s">
-        <v>19</v>
+      <c r="B4" t="str">
+        <v>25 - Haridwar</v>
       </c>
       <c r="C4">
         <v>51528</v>
@@ -808,17 +482,17 @@
         <v>0</v>
       </c>
       <c r="E4">
+        <v>2</v>
+      </c>
+      <c r="F4">
         <v>51528</v>
       </c>
-      <c r="F4">
-        <v>0</v>
-      </c>
       <c r="G4">
+        <v>0</v>
+      </c>
+      <c r="H4">
         <v>51528</v>
       </c>
-      <c r="H4">
-        <v>0</v>
-      </c>
       <c r="I4">
         <v>0</v>
       </c>
@@ -829,36 +503,30 @@
         <v>0</v>
       </c>
       <c r="L4">
+        <v>0</v>
+      </c>
+      <c r="M4">
         <v>17975</v>
       </c>
-      <c r="M4">
+      <c r="N4">
         <v>967</v>
       </c>
-      <c r="N4">
+      <c r="O4">
         <v>869</v>
       </c>
-      <c r="O4">
+      <c r="P4">
         <v>50659</v>
       </c>
-      <c r="P4">
+      <c r="Q4">
         <v>53812</v>
       </c>
-      <c r="Q4">
-        <v>12212</v>
-      </c>
-      <c r="R4">
-        <v>0</v>
-      </c>
-      <c r="S4">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="5" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="5">
       <c r="A5">
         <v>2</v>
       </c>
-      <c r="B5" t="s">
-        <v>20</v>
+      <c r="B5" t="str">
+        <v>26 - BHEL Ranipur</v>
       </c>
       <c r="C5">
         <v>53911</v>
@@ -867,17 +535,17 @@
         <v>0</v>
       </c>
       <c r="E5">
+        <v>0</v>
+      </c>
+      <c r="F5">
         <v>53911</v>
       </c>
-      <c r="F5">
-        <v>0</v>
-      </c>
       <c r="G5">
+        <v>0</v>
+      </c>
+      <c r="H5">
         <v>53911</v>
       </c>
-      <c r="H5">
-        <v>0</v>
-      </c>
       <c r="I5">
         <v>0</v>
       </c>
@@ -888,36 +556,30 @@
         <v>0</v>
       </c>
       <c r="L5">
+        <v>0</v>
+      </c>
+      <c r="M5">
         <v>11415</v>
       </c>
-      <c r="M5">
+      <c r="N5">
         <v>757</v>
       </c>
-      <c r="N5">
+      <c r="O5">
         <v>877</v>
       </c>
-      <c r="O5">
+      <c r="P5">
         <v>53035</v>
       </c>
-      <c r="P5">
+      <c r="Q5">
         <v>74848</v>
       </c>
-      <c r="Q5">
-        <v>16108</v>
-      </c>
-      <c r="R5">
-        <v>0</v>
-      </c>
-      <c r="S5">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="6" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="6">
       <c r="A6">
         <v>3</v>
       </c>
-      <c r="B6" t="s">
-        <v>21</v>
+      <c r="B6" t="str">
+        <v>27 - Jwalapur</v>
       </c>
       <c r="C6">
         <v>39773</v>
@@ -926,17 +588,17 @@
         <v>0</v>
       </c>
       <c r="E6">
+        <v>0</v>
+      </c>
+      <c r="F6">
         <v>39773</v>
       </c>
-      <c r="F6">
-        <v>0</v>
-      </c>
       <c r="G6">
+        <v>0</v>
+      </c>
+      <c r="H6">
         <v>39773</v>
       </c>
-      <c r="H6">
-        <v>0</v>
-      </c>
       <c r="I6">
         <v>0</v>
       </c>
@@ -947,36 +609,30 @@
         <v>0</v>
       </c>
       <c r="L6">
+        <v>0</v>
+      </c>
+      <c r="M6">
         <v>6075</v>
       </c>
-      <c r="M6">
+      <c r="N6">
         <v>201</v>
       </c>
-      <c r="N6">
+      <c r="O6">
         <v>1863</v>
       </c>
-      <c r="O6">
+      <c r="P6">
         <v>37869</v>
       </c>
-      <c r="P6">
+      <c r="Q6">
         <v>71989</v>
       </c>
-      <c r="Q6">
-        <v>17830</v>
-      </c>
-      <c r="R6">
-        <v>0</v>
-      </c>
-      <c r="S6">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="7" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="7">
       <c r="A7">
         <v>4</v>
       </c>
-      <c r="B7" t="s">
-        <v>22</v>
+      <c r="B7" t="str">
+        <v>28 - Bhagwanpur</v>
       </c>
       <c r="C7">
         <v>39463</v>
@@ -985,17 +641,17 @@
         <v>0</v>
       </c>
       <c r="E7">
+        <v>0</v>
+      </c>
+      <c r="F7">
         <v>39463</v>
       </c>
-      <c r="F7">
-        <v>0</v>
-      </c>
       <c r="G7">
+        <v>0</v>
+      </c>
+      <c r="H7">
         <v>39463</v>
       </c>
-      <c r="H7">
-        <v>0</v>
-      </c>
       <c r="I7">
         <v>0</v>
       </c>
@@ -1006,36 +662,30 @@
         <v>0</v>
       </c>
       <c r="L7">
+        <v>0</v>
+      </c>
+      <c r="M7">
         <v>5683</v>
       </c>
-      <c r="M7">
+      <c r="N7">
         <v>257</v>
       </c>
-      <c r="N7">
+      <c r="O7">
         <v>1995</v>
       </c>
-      <c r="O7">
+      <c r="P7">
         <v>37266</v>
       </c>
-      <c r="P7">
+      <c r="Q7">
         <v>77581</v>
       </c>
-      <c r="Q7">
-        <v>20511</v>
-      </c>
-      <c r="R7">
-        <v>0</v>
-      </c>
-      <c r="S7">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="8" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="8">
       <c r="A8">
         <v>5</v>
       </c>
-      <c r="B8" t="s">
-        <v>23</v>
+      <c r="B8" t="str">
+        <v>29 - Jhabrera</v>
       </c>
       <c r="C8">
         <v>40552</v>
@@ -1044,17 +694,17 @@
         <v>0</v>
       </c>
       <c r="E8">
+        <v>5</v>
+      </c>
+      <c r="F8">
         <v>40552</v>
       </c>
-      <c r="F8">
-        <v>0</v>
-      </c>
       <c r="G8">
+        <v>0</v>
+      </c>
+      <c r="H8">
         <v>40552</v>
       </c>
-      <c r="H8">
-        <v>0</v>
-      </c>
       <c r="I8">
         <v>0</v>
       </c>
@@ -1065,36 +715,30 @@
         <v>0</v>
       </c>
       <c r="L8">
+        <v>0</v>
+      </c>
+      <c r="M8">
         <v>14288</v>
       </c>
-      <c r="M8">
+      <c r="N8">
         <v>164</v>
       </c>
-      <c r="N8">
+      <c r="O8">
         <v>1874</v>
       </c>
-      <c r="O8">
-        <v>38046</v>
-      </c>
       <c r="P8">
+        <v>38055</v>
+      </c>
+      <c r="Q8">
         <v>73458</v>
       </c>
-      <c r="Q8">
-        <v>20788</v>
-      </c>
-      <c r="R8">
-        <v>0</v>
-      </c>
-      <c r="S8">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="9" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="9">
       <c r="A9">
         <v>6</v>
       </c>
-      <c r="B9" t="s">
-        <v>24</v>
+      <c r="B9" t="str">
+        <v>30 - Piran Kaliyar</v>
       </c>
       <c r="C9">
         <v>43273</v>
@@ -1103,17 +747,17 @@
         <v>0</v>
       </c>
       <c r="E9">
+        <v>0</v>
+      </c>
+      <c r="F9">
         <v>43273</v>
       </c>
-      <c r="F9">
-        <v>0</v>
-      </c>
       <c r="G9">
+        <v>0</v>
+      </c>
+      <c r="H9">
         <v>43273</v>
       </c>
-      <c r="H9">
-        <v>0</v>
-      </c>
       <c r="I9">
         <v>0</v>
       </c>
@@ -1124,36 +768,30 @@
         <v>0</v>
       </c>
       <c r="L9">
+        <v>0</v>
+      </c>
+      <c r="M9">
         <v>7759</v>
       </c>
-      <c r="M9">
+      <c r="N9">
         <v>49</v>
       </c>
-      <c r="N9">
+      <c r="O9">
         <v>1350</v>
       </c>
-      <c r="O9">
+      <c r="P9">
         <v>41924</v>
       </c>
-      <c r="P9">
+      <c r="Q9">
         <v>72913</v>
       </c>
-      <c r="Q9">
-        <v>18141</v>
-      </c>
-      <c r="R9">
-        <v>0</v>
-      </c>
-      <c r="S9">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="10" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="10">
       <c r="A10">
         <v>7</v>
       </c>
-      <c r="B10" t="s">
-        <v>25</v>
+      <c r="B10" t="str">
+        <v>31 - Roorkee</v>
       </c>
       <c r="C10">
         <v>36576</v>
@@ -1162,17 +800,17 @@
         <v>0</v>
       </c>
       <c r="E10">
+        <v>0</v>
+      </c>
+      <c r="F10">
         <v>36576</v>
       </c>
-      <c r="F10">
-        <v>0</v>
-      </c>
       <c r="G10">
+        <v>0</v>
+      </c>
+      <c r="H10">
         <v>36576</v>
       </c>
-      <c r="H10">
-        <v>0</v>
-      </c>
       <c r="I10">
         <v>0</v>
       </c>
@@ -1183,36 +821,30 @@
         <v>0</v>
       </c>
       <c r="L10">
+        <v>0</v>
+      </c>
+      <c r="M10">
         <v>10960</v>
       </c>
-      <c r="M10">
+      <c r="N10">
         <v>172</v>
       </c>
-      <c r="N10">
+      <c r="O10">
         <v>815</v>
       </c>
-      <c r="O10">
+      <c r="P10">
         <v>35761</v>
       </c>
-      <c r="P10">
+      <c r="Q10">
         <v>53124</v>
       </c>
-      <c r="Q10">
-        <v>9498</v>
-      </c>
-      <c r="R10">
-        <v>0</v>
-      </c>
-      <c r="S10">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="11" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="11">
       <c r="A11">
         <v>8</v>
       </c>
-      <c r="B11" t="s">
-        <v>26</v>
+      <c r="B11" t="str">
+        <v>32 - Khanpur</v>
       </c>
       <c r="C11">
         <v>50998</v>
@@ -1221,17 +853,17 @@
         <v>0</v>
       </c>
       <c r="E11">
+        <v>0</v>
+      </c>
+      <c r="F11">
         <v>50998</v>
       </c>
-      <c r="F11">
-        <v>0</v>
-      </c>
       <c r="G11">
+        <v>0</v>
+      </c>
+      <c r="H11">
         <v>50998</v>
       </c>
-      <c r="H11">
-        <v>0</v>
-      </c>
       <c r="I11">
         <v>0</v>
       </c>
@@ -1242,36 +874,30 @@
         <v>0</v>
       </c>
       <c r="L11">
+        <v>0</v>
+      </c>
+      <c r="M11">
         <v>9958</v>
       </c>
-      <c r="M11">
+      <c r="N11">
         <v>253</v>
       </c>
-      <c r="N11">
+      <c r="O11">
         <v>1703</v>
       </c>
-      <c r="O11">
+      <c r="P11">
         <v>49300</v>
       </c>
-      <c r="P11">
+      <c r="Q11">
         <v>84438</v>
       </c>
-      <c r="Q11">
-        <v>23477</v>
-      </c>
-      <c r="R11">
-        <v>0</v>
-      </c>
-      <c r="S11">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="12" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="12">
       <c r="A12">
         <v>9</v>
       </c>
-      <c r="B12" t="s">
-        <v>27</v>
+      <c r="B12" t="str">
+        <v>33 - Manglore</v>
       </c>
       <c r="C12">
         <v>40739</v>
@@ -1280,17 +906,17 @@
         <v>0</v>
       </c>
       <c r="E12">
+        <v>0</v>
+      </c>
+      <c r="F12">
         <v>40739</v>
       </c>
-      <c r="F12">
-        <v>0</v>
-      </c>
       <c r="G12">
+        <v>0</v>
+      </c>
+      <c r="H12">
         <v>40739</v>
       </c>
-      <c r="H12">
-        <v>0</v>
-      </c>
       <c r="I12">
         <v>0</v>
       </c>
@@ -1301,36 +927,30 @@
         <v>0</v>
       </c>
       <c r="L12">
+        <v>0</v>
+      </c>
+      <c r="M12">
         <v>10054</v>
       </c>
-      <c r="M12">
+      <c r="N12">
         <v>207</v>
       </c>
-      <c r="N12">
+      <c r="O12">
         <v>1133</v>
       </c>
-      <c r="O12">
+      <c r="P12">
         <v>39588</v>
       </c>
-      <c r="P12">
+      <c r="Q12">
         <v>66685</v>
       </c>
-      <c r="Q12">
-        <v>17786</v>
-      </c>
-      <c r="R12">
-        <v>0</v>
-      </c>
-      <c r="S12">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="13" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="13">
       <c r="A13">
         <v>10</v>
       </c>
-      <c r="B13" t="s">
-        <v>28</v>
+      <c r="B13" t="str">
+        <v>34 - Laksar</v>
       </c>
       <c r="C13">
         <v>37031</v>
@@ -1339,17 +959,17 @@
         <v>0</v>
       </c>
       <c r="E13">
+        <v>0</v>
+      </c>
+      <c r="F13">
         <v>37031</v>
       </c>
-      <c r="F13">
-        <v>0</v>
-      </c>
       <c r="G13">
+        <v>0</v>
+      </c>
+      <c r="H13">
         <v>37031</v>
       </c>
-      <c r="H13">
-        <v>0</v>
-      </c>
       <c r="I13">
         <v>0</v>
       </c>
@@ -1360,36 +980,30 @@
         <v>0</v>
       </c>
       <c r="L13">
+        <v>0</v>
+      </c>
+      <c r="M13">
         <v>7864</v>
       </c>
-      <c r="M13">
+      <c r="N13">
         <v>258</v>
       </c>
-      <c r="N13">
+      <c r="O13">
         <v>3822</v>
       </c>
-      <c r="O13">
+      <c r="P13">
         <v>33195</v>
       </c>
-      <c r="P13">
+      <c r="Q13">
         <v>56564</v>
       </c>
-      <c r="Q13">
-        <v>16237</v>
-      </c>
-      <c r="R13">
-        <v>0</v>
-      </c>
-      <c r="S13">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="14" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="14">
       <c r="A14">
         <v>11</v>
       </c>
-      <c r="B14" t="s">
-        <v>29</v>
+      <c r="B14" t="str">
+        <v>35 - Haridwar Rural</v>
       </c>
       <c r="C14">
         <v>48966</v>
@@ -1398,17 +1012,17 @@
         <v>0</v>
       </c>
       <c r="E14">
+        <v>0</v>
+      </c>
+      <c r="F14">
         <v>48966</v>
       </c>
-      <c r="F14">
-        <v>0</v>
-      </c>
       <c r="G14">
+        <v>0</v>
+      </c>
+      <c r="H14">
         <v>48966</v>
       </c>
-      <c r="H14">
-        <v>0</v>
-      </c>
       <c r="I14">
         <v>0</v>
       </c>
@@ -1419,36 +1033,30 @@
         <v>0</v>
       </c>
       <c r="L14">
+        <v>0</v>
+      </c>
+      <c r="M14">
         <v>15267</v>
       </c>
-      <c r="M14">
+      <c r="N14">
         <v>1456</v>
       </c>
-      <c r="N14">
+      <c r="O14">
         <v>5864</v>
       </c>
-      <c r="O14">
+      <c r="P14">
         <v>43096</v>
       </c>
-      <c r="P14">
+      <c r="Q14">
         <v>77955</v>
       </c>
-      <c r="Q14">
-        <v>19716</v>
-      </c>
-      <c r="R14">
-        <v>0</v>
-      </c>
-      <c r="S14">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="15" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="15">
       <c r="A15">
         <v>12</v>
       </c>
-      <c r="B15" t="s">
-        <v>30</v>
+      <c r="B15" t="str">
+        <v>56 - Lalkuan</v>
       </c>
       <c r="C15">
         <v>42703</v>
@@ -1457,17 +1065,17 @@
         <v>0</v>
       </c>
       <c r="E15">
+        <v>0</v>
+      </c>
+      <c r="F15">
         <v>42703</v>
       </c>
-      <c r="F15">
-        <v>0</v>
-      </c>
       <c r="G15">
+        <v>0</v>
+      </c>
+      <c r="H15">
         <v>42703</v>
       </c>
-      <c r="H15">
-        <v>0</v>
-      </c>
       <c r="I15">
         <v>0</v>
       </c>
@@ -1478,36 +1086,30 @@
         <v>0</v>
       </c>
       <c r="L15">
+        <v>0</v>
+      </c>
+      <c r="M15">
         <v>9192</v>
       </c>
-      <c r="M15">
-        <v>0</v>
-      </c>
       <c r="N15">
+        <v>0</v>
+      </c>
+      <c r="O15">
         <v>2821</v>
       </c>
-      <c r="O15">
+      <c r="P15">
         <v>39882</v>
       </c>
-      <c r="P15">
+      <c r="Q15">
         <v>67178</v>
       </c>
-      <c r="Q15">
-        <v>4859</v>
-      </c>
-      <c r="R15">
-        <v>0</v>
-      </c>
-      <c r="S15">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="16" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="16">
       <c r="A16">
         <v>13</v>
       </c>
-      <c r="B16" t="s">
-        <v>31</v>
+      <c r="B16" t="str">
+        <v>57 - Bhimtal</v>
       </c>
       <c r="C16">
         <v>25549</v>
@@ -1516,17 +1118,17 @@
         <v>0</v>
       </c>
       <c r="E16">
+        <v>0</v>
+      </c>
+      <c r="F16">
         <v>25549</v>
       </c>
-      <c r="F16">
-        <v>0</v>
-      </c>
       <c r="G16">
+        <v>0</v>
+      </c>
+      <c r="H16">
         <v>25547</v>
       </c>
-      <c r="H16">
-        <v>0</v>
-      </c>
       <c r="I16">
         <v>0</v>
       </c>
@@ -1537,36 +1139,30 @@
         <v>0</v>
       </c>
       <c r="L16">
+        <v>0</v>
+      </c>
+      <c r="M16">
         <v>14861</v>
       </c>
-      <c r="M16">
+      <c r="N16">
         <v>1</v>
       </c>
-      <c r="N16">
+      <c r="O16">
         <v>261</v>
       </c>
-      <c r="O16">
+      <c r="P16">
         <v>25288</v>
       </c>
-      <c r="P16">
+      <c r="Q16">
         <v>71673</v>
       </c>
-      <c r="Q16">
-        <v>5197</v>
-      </c>
-      <c r="R16">
-        <v>0</v>
-      </c>
-      <c r="S16">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="17" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="17">
       <c r="A17">
         <v>14</v>
       </c>
-      <c r="B17" t="s">
-        <v>32</v>
+      <c r="B17" t="str">
+        <v>58 - Nainital</v>
       </c>
       <c r="C17">
         <v>27707</v>
@@ -1575,17 +1171,17 @@
         <v>0</v>
       </c>
       <c r="E17">
+        <v>0</v>
+      </c>
+      <c r="F17">
         <v>27707</v>
       </c>
-      <c r="F17">
-        <v>0</v>
-      </c>
       <c r="G17">
+        <v>0</v>
+      </c>
+      <c r="H17">
         <v>27707</v>
       </c>
-      <c r="H17">
-        <v>0</v>
-      </c>
       <c r="I17">
         <v>0</v>
       </c>
@@ -1596,36 +1192,30 @@
         <v>0</v>
       </c>
       <c r="L17">
+        <v>0</v>
+      </c>
+      <c r="M17">
         <v>9287</v>
       </c>
-      <c r="M17">
+      <c r="N17">
         <v>2</v>
       </c>
-      <c r="N17">
+      <c r="O17">
         <v>426</v>
       </c>
-      <c r="O17">
+      <c r="P17">
         <v>27282</v>
       </c>
-      <c r="P17">
+      <c r="Q17">
         <v>65457</v>
       </c>
-      <c r="Q17">
-        <v>5417</v>
-      </c>
-      <c r="R17">
-        <v>0</v>
-      </c>
-      <c r="S17">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="18" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="18">
       <c r="A18">
         <v>15</v>
       </c>
-      <c r="B18" t="s">
-        <v>33</v>
+      <c r="B18" t="str">
+        <v>59 - Haldwani</v>
       </c>
       <c r="C18">
         <v>47836</v>
@@ -1634,17 +1224,17 @@
         <v>0</v>
       </c>
       <c r="E18">
+        <v>0</v>
+      </c>
+      <c r="F18">
         <v>47836</v>
       </c>
-      <c r="F18">
-        <v>0</v>
-      </c>
       <c r="G18">
+        <v>0</v>
+      </c>
+      <c r="H18">
         <v>47836</v>
       </c>
-      <c r="H18">
-        <v>0</v>
-      </c>
       <c r="I18">
         <v>0</v>
       </c>
@@ -1655,36 +1245,30 @@
         <v>0</v>
       </c>
       <c r="L18">
+        <v>0</v>
+      </c>
+      <c r="M18">
         <v>7875</v>
       </c>
-      <c r="M18">
+      <c r="N18">
         <v>3</v>
       </c>
-      <c r="N18">
+      <c r="O18">
         <v>1969</v>
       </c>
-      <c r="O18">
+      <c r="P18">
         <v>45401</v>
       </c>
-      <c r="P18">
+      <c r="Q18">
         <v>71475</v>
       </c>
-      <c r="Q18">
-        <v>6819</v>
-      </c>
-      <c r="R18">
-        <v>0</v>
-      </c>
-      <c r="S18">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="19" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="19">
       <c r="A19">
         <v>16</v>
       </c>
-      <c r="B19" t="s">
-        <v>34</v>
+      <c r="B19" t="str">
+        <v>60 - Kaladhungi</v>
       </c>
       <c r="C19">
         <v>56490</v>
@@ -1693,17 +1277,17 @@
         <v>0</v>
       </c>
       <c r="E19">
+        <v>0</v>
+      </c>
+      <c r="F19">
         <v>56490</v>
       </c>
-      <c r="F19">
-        <v>0</v>
-      </c>
       <c r="G19">
+        <v>0</v>
+      </c>
+      <c r="H19">
         <v>56490</v>
       </c>
-      <c r="H19">
-        <v>0</v>
-      </c>
       <c r="I19">
         <v>0</v>
       </c>
@@ -1714,36 +1298,30 @@
         <v>0</v>
       </c>
       <c r="L19">
+        <v>0</v>
+      </c>
+      <c r="M19">
         <v>15286</v>
       </c>
-      <c r="M19">
+      <c r="N19">
         <v>1</v>
       </c>
-      <c r="N19">
+      <c r="O19">
         <v>912</v>
       </c>
-      <c r="O19">
+      <c r="P19">
         <v>55578</v>
       </c>
-      <c r="P19">
+      <c r="Q19">
         <v>106392</v>
       </c>
-      <c r="Q19">
-        <v>6135</v>
-      </c>
-      <c r="R19">
-        <v>0</v>
-      </c>
-      <c r="S19">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="20" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="20">
       <c r="A20">
         <v>17</v>
       </c>
-      <c r="B20" t="s">
-        <v>35</v>
+      <c r="B20" t="str">
+        <v>61 - Ramnagar</v>
       </c>
       <c r="C20">
         <v>35022</v>
@@ -1752,17 +1330,17 @@
         <v>0</v>
       </c>
       <c r="E20">
+        <v>0</v>
+      </c>
+      <c r="F20">
         <v>35022</v>
       </c>
-      <c r="F20">
-        <v>0</v>
-      </c>
       <c r="G20">
+        <v>0</v>
+      </c>
+      <c r="H20">
         <v>35022</v>
       </c>
-      <c r="H20">
-        <v>0</v>
-      </c>
       <c r="I20">
         <v>0</v>
       </c>
@@ -1773,36 +1351,30 @@
         <v>0</v>
       </c>
       <c r="L20">
+        <v>0</v>
+      </c>
+      <c r="M20">
         <v>6093</v>
       </c>
-      <c r="M20">
+      <c r="N20">
         <v>5</v>
       </c>
-      <c r="N20">
+      <c r="O20">
         <v>546</v>
       </c>
-      <c r="O20">
+      <c r="P20">
         <v>34464</v>
       </c>
-      <c r="P20">
+      <c r="Q20">
         <v>75812</v>
       </c>
-      <c r="Q20">
-        <v>8984</v>
-      </c>
-      <c r="R20">
-        <v>0</v>
-      </c>
-      <c r="S20">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="21" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="21">
       <c r="A21">
         <v>18</v>
       </c>
-      <c r="B21" t="s">
-        <v>36</v>
+      <c r="B21" t="str">
+        <v>48 - Dwarahat</v>
       </c>
       <c r="C21">
         <v>16962</v>
@@ -1811,17 +1383,17 @@
         <v>0</v>
       </c>
       <c r="E21">
+        <v>0</v>
+      </c>
+      <c r="F21">
         <v>16962</v>
       </c>
-      <c r="F21">
-        <v>0</v>
-      </c>
       <c r="G21">
+        <v>0</v>
+      </c>
+      <c r="H21">
         <v>16962</v>
       </c>
-      <c r="H21">
-        <v>0</v>
-      </c>
       <c r="I21">
         <v>0</v>
       </c>
@@ -1832,36 +1404,30 @@
         <v>0</v>
       </c>
       <c r="L21">
+        <v>0</v>
+      </c>
+      <c r="M21">
         <v>4030</v>
       </c>
-      <c r="M21">
+      <c r="N21">
         <v>3</v>
       </c>
-      <c r="N21">
+      <c r="O21">
         <v>171</v>
       </c>
-      <c r="O21">
+      <c r="P21">
         <v>16791</v>
       </c>
-      <c r="P21">
+      <c r="Q21">
         <v>62460</v>
       </c>
-      <c r="Q21">
-        <v>3868</v>
-      </c>
-      <c r="R21">
-        <v>0</v>
-      </c>
-      <c r="S21">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="22">
       <c r="A22">
         <v>19</v>
       </c>
-      <c r="B22" t="s">
-        <v>37</v>
+      <c r="B22" t="str">
+        <v>49 - Salt</v>
       </c>
       <c r="C22">
         <v>18668</v>
@@ -1870,17 +1436,17 @@
         <v>0</v>
       </c>
       <c r="E22">
+        <v>0</v>
+      </c>
+      <c r="F22">
         <v>18668</v>
       </c>
-      <c r="F22">
-        <v>0</v>
-      </c>
       <c r="G22">
+        <v>0</v>
+      </c>
+      <c r="H22">
         <v>18668</v>
       </c>
-      <c r="H22">
-        <v>0</v>
-      </c>
       <c r="I22">
         <v>0</v>
       </c>
@@ -1891,36 +1457,30 @@
         <v>0</v>
       </c>
       <c r="L22">
+        <v>0</v>
+      </c>
+      <c r="M22">
         <v>7665</v>
       </c>
-      <c r="M22">
-        <v>0</v>
-      </c>
       <c r="N22">
+        <v>0</v>
+      </c>
+      <c r="O22">
         <v>302</v>
       </c>
-      <c r="O22">
+      <c r="P22">
         <v>18366</v>
       </c>
-      <c r="P22">
+      <c r="Q22">
         <v>64099</v>
       </c>
-      <c r="Q22">
-        <v>4848</v>
-      </c>
-      <c r="R22">
-        <v>0</v>
-      </c>
-      <c r="S22">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="23">
       <c r="A23">
         <v>20</v>
       </c>
-      <c r="B23" t="s">
-        <v>38</v>
+      <c r="B23" t="str">
+        <v>50 - Ranikhet</v>
       </c>
       <c r="C23">
         <v>12020</v>
@@ -1929,17 +1489,17 @@
         <v>0</v>
       </c>
       <c r="E23">
+        <v>0</v>
+      </c>
+      <c r="F23">
         <v>12020</v>
       </c>
-      <c r="F23">
-        <v>0</v>
-      </c>
       <c r="G23">
+        <v>0</v>
+      </c>
+      <c r="H23">
         <v>12020</v>
       </c>
-      <c r="H23">
-        <v>0</v>
-      </c>
       <c r="I23">
         <v>0</v>
       </c>
@@ -1950,36 +1510,30 @@
         <v>0</v>
       </c>
       <c r="L23">
+        <v>0</v>
+      </c>
+      <c r="M23">
         <v>2113</v>
       </c>
-      <c r="M23">
-        <v>0</v>
-      </c>
       <c r="N23">
+        <v>0</v>
+      </c>
+      <c r="O23">
         <v>108</v>
       </c>
-      <c r="O23">
+      <c r="P23">
         <v>11912</v>
       </c>
-      <c r="P23">
+      <c r="Q23">
         <v>57094</v>
       </c>
-      <c r="Q23">
-        <v>3541</v>
-      </c>
-      <c r="R23">
-        <v>0</v>
-      </c>
-      <c r="S23">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="24" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="24">
       <c r="A24">
         <v>21</v>
       </c>
-      <c r="B24" t="s">
-        <v>39</v>
+      <c r="B24" t="str">
+        <v>51 - Someshwar</v>
       </c>
       <c r="C24">
         <v>14056</v>
@@ -1988,17 +1542,17 @@
         <v>0</v>
       </c>
       <c r="E24">
+        <v>0</v>
+      </c>
+      <c r="F24">
         <v>14056</v>
       </c>
-      <c r="F24">
-        <v>0</v>
-      </c>
       <c r="G24">
+        <v>0</v>
+      </c>
+      <c r="H24">
         <v>14056</v>
       </c>
-      <c r="H24">
-        <v>0</v>
-      </c>
       <c r="I24">
         <v>0</v>
       </c>
@@ -2009,36 +1563,30 @@
         <v>0</v>
       </c>
       <c r="L24">
+        <v>0</v>
+      </c>
+      <c r="M24">
         <v>3482</v>
       </c>
-      <c r="M24">
+      <c r="N24">
         <v>5</v>
       </c>
-      <c r="N24">
+      <c r="O24">
         <v>231</v>
       </c>
-      <c r="O24">
+      <c r="P24">
         <v>13825</v>
       </c>
-      <c r="P24">
+      <c r="Q24">
         <v>65629</v>
       </c>
-      <c r="Q24">
-        <v>3492</v>
-      </c>
-      <c r="R24">
-        <v>0</v>
-      </c>
-      <c r="S24">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="25">
       <c r="A25">
         <v>22</v>
       </c>
-      <c r="B25" t="s">
-        <v>40</v>
+      <c r="B25" t="str">
+        <v>52 - Almora</v>
       </c>
       <c r="C25">
         <v>19266</v>
@@ -2047,17 +1595,17 @@
         <v>0</v>
       </c>
       <c r="E25">
+        <v>0</v>
+      </c>
+      <c r="F25">
         <v>19266</v>
       </c>
-      <c r="F25">
-        <v>0</v>
-      </c>
       <c r="G25">
+        <v>0</v>
+      </c>
+      <c r="H25">
         <v>19266</v>
       </c>
-      <c r="H25">
-        <v>0</v>
-      </c>
       <c r="I25">
         <v>0</v>
       </c>
@@ -2068,36 +1616,30 @@
         <v>0</v>
       </c>
       <c r="L25">
+        <v>0</v>
+      </c>
+      <c r="M25">
         <v>4862</v>
       </c>
-      <c r="M25">
-        <v>0</v>
-      </c>
       <c r="N25">
+        <v>0</v>
+      </c>
+      <c r="O25">
         <v>298</v>
       </c>
-      <c r="O25">
+      <c r="P25">
         <v>18968</v>
       </c>
-      <c r="P25">
+      <c r="Q25">
         <v>57533</v>
       </c>
-      <c r="Q25">
-        <v>3231</v>
-      </c>
-      <c r="R25">
-        <v>0</v>
-      </c>
-      <c r="S25">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="26" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="26">
       <c r="A26">
         <v>23</v>
       </c>
-      <c r="B26" t="s">
-        <v>41</v>
+      <c r="B26" t="str">
+        <v>53 - Jageshwar</v>
       </c>
       <c r="C26">
         <v>17557</v>
@@ -2106,17 +1648,17 @@
         <v>0</v>
       </c>
       <c r="E26">
+        <v>0</v>
+      </c>
+      <c r="F26">
         <v>17557</v>
       </c>
-      <c r="F26">
-        <v>0</v>
-      </c>
       <c r="G26">
+        <v>0</v>
+      </c>
+      <c r="H26">
         <v>17557</v>
       </c>
-      <c r="H26">
-        <v>0</v>
-      </c>
       <c r="I26">
         <v>0</v>
       </c>
@@ -2127,36 +1669,30 @@
         <v>0</v>
       </c>
       <c r="L26">
+        <v>0</v>
+      </c>
+      <c r="M26">
         <v>3741</v>
       </c>
-      <c r="M26">
+      <c r="N26">
         <v>3</v>
       </c>
-      <c r="N26">
+      <c r="O26">
         <v>194</v>
       </c>
-      <c r="O26">
+      <c r="P26">
         <v>17363</v>
       </c>
-      <c r="P26">
+      <c r="Q26">
         <v>66594</v>
       </c>
-      <c r="Q26">
-        <v>3333</v>
-      </c>
-      <c r="R26">
-        <v>0</v>
-      </c>
-      <c r="S26">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="27" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="27">
       <c r="A27">
         <v>24</v>
       </c>
-      <c r="B27" t="s">
-        <v>42</v>
+      <c r="B27" t="str">
+        <v>62 - Jaspur</v>
       </c>
       <c r="C27">
         <v>44276</v>
@@ -2165,17 +1701,17 @@
         <v>0</v>
       </c>
       <c r="E27">
+        <v>0</v>
+      </c>
+      <c r="F27">
         <v>44276</v>
       </c>
-      <c r="F27">
-        <v>0</v>
-      </c>
       <c r="G27">
+        <v>0</v>
+      </c>
+      <c r="H27">
         <v>44276</v>
       </c>
-      <c r="H27">
-        <v>0</v>
-      </c>
       <c r="I27">
         <v>0</v>
       </c>
@@ -2186,36 +1722,30 @@
         <v>0</v>
       </c>
       <c r="L27">
+        <v>0</v>
+      </c>
+      <c r="M27">
         <v>9679</v>
       </c>
-      <c r="M27">
+      <c r="N27">
         <v>215</v>
       </c>
-      <c r="N27">
+      <c r="O27">
         <v>3287</v>
       </c>
-      <c r="O27">
+      <c r="P27">
         <v>41005</v>
       </c>
-      <c r="P27">
+      <c r="Q27">
         <v>73109</v>
       </c>
-      <c r="Q27">
-        <v>12669</v>
-      </c>
-      <c r="R27">
-        <v>0</v>
-      </c>
-      <c r="S27">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="28">
       <c r="A28">
         <v>25</v>
       </c>
-      <c r="B28" t="s">
-        <v>43</v>
+      <c r="B28" t="str">
+        <v>63 - Kashipur</v>
       </c>
       <c r="C28">
         <v>54349</v>
@@ -2224,17 +1754,17 @@
         <v>0</v>
       </c>
       <c r="E28">
+        <v>0</v>
+      </c>
+      <c r="F28">
         <v>54349</v>
       </c>
-      <c r="F28">
-        <v>0</v>
-      </c>
       <c r="G28">
+        <v>0</v>
+      </c>
+      <c r="H28">
         <v>54349</v>
       </c>
-      <c r="H28">
-        <v>0</v>
-      </c>
       <c r="I28">
         <v>0</v>
       </c>
@@ -2245,36 +1775,30 @@
         <v>0</v>
       </c>
       <c r="L28">
+        <v>0</v>
+      </c>
+      <c r="M28">
         <v>8879</v>
       </c>
-      <c r="M28">
+      <c r="N28">
         <v>856</v>
       </c>
-      <c r="N28">
+      <c r="O28">
         <v>3525</v>
       </c>
-      <c r="O28">
+      <c r="P28">
         <v>50844</v>
       </c>
-      <c r="P28">
+      <c r="Q28">
         <v>80620</v>
       </c>
-      <c r="Q28">
-        <v>13995</v>
-      </c>
-      <c r="R28">
-        <v>0</v>
-      </c>
-      <c r="S28">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="29" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="29">
       <c r="A29">
         <v>26</v>
       </c>
-      <c r="B29" t="s">
-        <v>44</v>
+      <c r="B29" t="str">
+        <v>64 - Bajpur</v>
       </c>
       <c r="C29">
         <v>47111</v>
@@ -2283,17 +1807,17 @@
         <v>0</v>
       </c>
       <c r="E29">
+        <v>0</v>
+      </c>
+      <c r="F29">
         <v>47111</v>
       </c>
-      <c r="F29">
-        <v>0</v>
-      </c>
       <c r="G29">
+        <v>0</v>
+      </c>
+      <c r="H29">
         <v>47111</v>
       </c>
-      <c r="H29">
-        <v>0</v>
-      </c>
       <c r="I29">
         <v>0</v>
       </c>
@@ -2304,36 +1828,30 @@
         <v>0</v>
       </c>
       <c r="L29">
+        <v>0</v>
+      </c>
+      <c r="M29">
         <v>8816</v>
       </c>
-      <c r="M29">
+      <c r="N29">
         <v>318</v>
       </c>
-      <c r="N29">
+      <c r="O29">
         <v>4592</v>
       </c>
-      <c r="O29">
+      <c r="P29">
         <v>42520</v>
       </c>
-      <c r="P29">
+      <c r="Q29">
         <v>83836</v>
       </c>
-      <c r="Q29">
-        <v>14229</v>
-      </c>
-      <c r="R29">
-        <v>0</v>
-      </c>
-      <c r="S29">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="30" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="30">
       <c r="A30">
         <v>27</v>
       </c>
-      <c r="B30" t="s">
-        <v>45</v>
+      <c r="B30" t="str">
+        <v>65 - Gadarpur</v>
       </c>
       <c r="C30">
         <v>52653</v>
@@ -2342,17 +1860,17 @@
         <v>0</v>
       </c>
       <c r="E30">
+        <v>0</v>
+      </c>
+      <c r="F30">
         <v>52653</v>
       </c>
-      <c r="F30">
-        <v>0</v>
-      </c>
       <c r="G30">
+        <v>0</v>
+      </c>
+      <c r="H30">
         <v>52653</v>
       </c>
-      <c r="H30">
-        <v>0</v>
-      </c>
       <c r="I30">
         <v>0</v>
       </c>
@@ -2363,36 +1881,30 @@
         <v>0</v>
       </c>
       <c r="L30">
+        <v>0</v>
+      </c>
+      <c r="M30">
         <v>11659</v>
       </c>
-      <c r="M30">
+      <c r="N30">
         <v>411</v>
       </c>
-      <c r="N30">
+      <c r="O30">
         <v>5383</v>
       </c>
-      <c r="O30">
+      <c r="P30">
         <v>47272</v>
       </c>
-      <c r="P30">
+      <c r="Q30">
         <v>86933</v>
       </c>
-      <c r="Q30">
-        <v>12564</v>
-      </c>
-      <c r="R30">
-        <v>0</v>
-      </c>
-      <c r="S30">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="31" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="31">
       <c r="A31">
         <v>28</v>
       </c>
-      <c r="B31" t="s">
-        <v>46</v>
+      <c r="B31" t="str">
+        <v>66 - Rudrapur</v>
       </c>
       <c r="C31">
         <v>91162</v>
@@ -2401,17 +1913,17 @@
         <v>0</v>
       </c>
       <c r="E31">
+        <v>0</v>
+      </c>
+      <c r="F31">
         <v>91162</v>
       </c>
-      <c r="F31">
-        <v>0</v>
-      </c>
       <c r="G31">
+        <v>0</v>
+      </c>
+      <c r="H31">
         <v>91162</v>
       </c>
-      <c r="H31">
-        <v>0</v>
-      </c>
       <c r="I31">
         <v>0</v>
       </c>
@@ -2422,36 +1934,30 @@
         <v>0</v>
       </c>
       <c r="L31">
+        <v>0</v>
+      </c>
+      <c r="M31">
         <v>46718</v>
       </c>
-      <c r="M31">
+      <c r="N31">
         <v>42</v>
       </c>
-      <c r="N31">
+      <c r="O31">
         <v>1899</v>
       </c>
-      <c r="O31">
+      <c r="P31">
         <v>89264</v>
       </c>
-      <c r="P31">
+      <c r="Q31">
         <v>81642</v>
       </c>
-      <c r="Q31">
-        <v>14581</v>
-      </c>
-      <c r="R31">
-        <v>0</v>
-      </c>
-      <c r="S31">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="32" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="32">
       <c r="A32">
         <v>29</v>
       </c>
-      <c r="B32" t="s">
-        <v>47</v>
+      <c r="B32" t="str">
+        <v>67 - Kichha</v>
       </c>
       <c r="C32">
         <v>46728</v>
@@ -2460,17 +1966,17 @@
         <v>0</v>
       </c>
       <c r="E32">
+        <v>0</v>
+      </c>
+      <c r="F32">
         <v>46728</v>
       </c>
-      <c r="F32">
-        <v>0</v>
-      </c>
       <c r="G32">
+        <v>0</v>
+      </c>
+      <c r="H32">
         <v>46728</v>
       </c>
-      <c r="H32">
-        <v>0</v>
-      </c>
       <c r="I32">
         <v>0</v>
       </c>
@@ -2481,36 +1987,30 @@
         <v>0</v>
       </c>
       <c r="L32">
+        <v>0</v>
+      </c>
+      <c r="M32">
         <v>10557</v>
       </c>
-      <c r="M32">
+      <c r="N32">
         <v>316</v>
       </c>
-      <c r="N32">
+      <c r="O32">
         <v>4391</v>
       </c>
-      <c r="O32">
+      <c r="P32">
         <v>42344</v>
       </c>
-      <c r="P32">
+      <c r="Q32">
         <v>74810</v>
       </c>
-      <c r="Q32">
-        <v>11379</v>
-      </c>
-      <c r="R32">
-        <v>0</v>
-      </c>
-      <c r="S32">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="33">
       <c r="A33">
         <v>30</v>
       </c>
-      <c r="B33" t="s">
-        <v>48</v>
+      <c r="B33" t="str">
+        <v>68 - Sitarganj</v>
       </c>
       <c r="C33">
         <v>40230</v>
@@ -2519,17 +2019,17 @@
         <v>0</v>
       </c>
       <c r="E33">
+        <v>0</v>
+      </c>
+      <c r="F33">
         <v>40230</v>
       </c>
-      <c r="F33">
-        <v>0</v>
-      </c>
       <c r="G33">
+        <v>0</v>
+      </c>
+      <c r="H33">
         <v>40230</v>
       </c>
-      <c r="H33">
-        <v>0</v>
-      </c>
       <c r="I33">
         <v>0</v>
       </c>
@@ -2540,36 +2040,30 @@
         <v>0</v>
       </c>
       <c r="L33">
+        <v>0</v>
+      </c>
+      <c r="M33">
         <v>5113</v>
       </c>
-      <c r="M33">
+      <c r="N33">
         <v>311</v>
       </c>
-      <c r="N33">
+      <c r="O33">
         <v>1275</v>
       </c>
-      <c r="O33">
+      <c r="P33">
         <v>38955</v>
       </c>
-      <c r="P33">
+      <c r="Q33">
         <v>76969</v>
       </c>
-      <c r="Q33">
-        <v>6678</v>
-      </c>
-      <c r="R33">
-        <v>0</v>
-      </c>
-      <c r="S33">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="34" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="34">
       <c r="A34">
         <v>31</v>
       </c>
-      <c r="B34" t="s">
-        <v>49</v>
+      <c r="B34" t="str">
+        <v>69 - Nanakmatta</v>
       </c>
       <c r="C34">
         <v>36542</v>
@@ -2578,17 +2072,17 @@
         <v>0</v>
       </c>
       <c r="E34">
+        <v>0</v>
+      </c>
+      <c r="F34">
         <v>36542</v>
       </c>
-      <c r="F34">
-        <v>0</v>
-      </c>
       <c r="G34">
+        <v>0</v>
+      </c>
+      <c r="H34">
         <v>36542</v>
       </c>
-      <c r="H34">
-        <v>0</v>
-      </c>
       <c r="I34">
         <v>0</v>
       </c>
@@ -2599,36 +2093,30 @@
         <v>0</v>
       </c>
       <c r="L34">
+        <v>0</v>
+      </c>
+      <c r="M34">
         <v>12439</v>
       </c>
-      <c r="M34">
+      <c r="N34">
         <v>513</v>
       </c>
-      <c r="N34">
+      <c r="O34">
         <v>1363</v>
       </c>
-      <c r="O34">
+      <c r="P34">
         <v>35181</v>
       </c>
-      <c r="P34">
+      <c r="Q34">
         <v>74624</v>
       </c>
-      <c r="Q34">
-        <v>7137</v>
-      </c>
-      <c r="R34">
-        <v>0</v>
-      </c>
-      <c r="S34">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="35">
       <c r="A35">
         <v>32</v>
       </c>
-      <c r="B35" t="s">
-        <v>50</v>
+      <c r="B35" t="str">
+        <v>70 - Khatima</v>
       </c>
       <c r="C35">
         <v>33564</v>
@@ -2637,17 +2125,17 @@
         <v>0</v>
       </c>
       <c r="E35">
+        <v>0</v>
+      </c>
+      <c r="F35">
         <v>33564</v>
       </c>
-      <c r="F35">
-        <v>0</v>
-      </c>
       <c r="G35">
+        <v>0</v>
+      </c>
+      <c r="H35">
         <v>33564</v>
       </c>
-      <c r="H35">
-        <v>0</v>
-      </c>
       <c r="I35">
         <v>0</v>
       </c>
@@ -2658,36 +2146,30 @@
         <v>0</v>
       </c>
       <c r="L35">
+        <v>0</v>
+      </c>
+      <c r="M35">
         <v>7886</v>
       </c>
-      <c r="M35">
+      <c r="N35">
         <v>271</v>
       </c>
-      <c r="N35">
+      <c r="O35">
         <v>1129</v>
       </c>
-      <c r="O35">
+      <c r="P35">
         <v>32436</v>
       </c>
-      <c r="P35">
+      <c r="Q35">
         <v>76464</v>
       </c>
-      <c r="Q35">
-        <v>8879</v>
-      </c>
-      <c r="R35">
-        <v>0</v>
-      </c>
-      <c r="S35">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="36" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="36">
       <c r="A36">
         <v>33</v>
       </c>
-      <c r="B36" t="s">
-        <v>51</v>
+      <c r="B36" t="str">
+        <v>42 - Dharchula</v>
       </c>
       <c r="C36">
         <v>20905</v>
@@ -2696,17 +2178,17 @@
         <v>0</v>
       </c>
       <c r="E36">
+        <v>0</v>
+      </c>
+      <c r="F36">
         <v>20905</v>
       </c>
-      <c r="F36">
-        <v>0</v>
-      </c>
       <c r="G36">
+        <v>0</v>
+      </c>
+      <c r="H36">
         <v>20905</v>
       </c>
-      <c r="H36">
-        <v>0</v>
-      </c>
       <c r="I36">
         <v>0</v>
       </c>
@@ -2717,36 +2199,30 @@
         <v>0</v>
       </c>
       <c r="L36">
+        <v>0</v>
+      </c>
+      <c r="M36">
         <v>7350</v>
       </c>
-      <c r="M36">
-        <v>0</v>
-      </c>
       <c r="N36">
+        <v>0</v>
+      </c>
+      <c r="O36">
         <v>951</v>
       </c>
-      <c r="O36">
+      <c r="P36">
         <v>19954</v>
       </c>
-      <c r="P36">
+      <c r="Q36">
         <v>60419</v>
       </c>
-      <c r="Q36">
-        <v>3855</v>
-      </c>
-      <c r="R36">
-        <v>0</v>
-      </c>
-      <c r="S36">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="37" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="37">
       <c r="A37">
         <v>34</v>
       </c>
-      <c r="B37" t="s">
-        <v>52</v>
+      <c r="B37" t="str">
+        <v>43 - Didihat</v>
       </c>
       <c r="C37">
         <v>17692</v>
@@ -2755,17 +2231,17 @@
         <v>0</v>
       </c>
       <c r="E37">
+        <v>0</v>
+      </c>
+      <c r="F37">
         <v>17692</v>
       </c>
-      <c r="F37">
-        <v>0</v>
-      </c>
       <c r="G37">
+        <v>0</v>
+      </c>
+      <c r="H37">
         <v>17692</v>
       </c>
-      <c r="H37">
-        <v>0</v>
-      </c>
       <c r="I37">
         <v>0</v>
       </c>
@@ -2776,36 +2252,30 @@
         <v>0</v>
       </c>
       <c r="L37">
+        <v>0</v>
+      </c>
+      <c r="M37">
         <v>2311</v>
       </c>
-      <c r="M37">
-        <v>0</v>
-      </c>
       <c r="N37">
+        <v>0</v>
+      </c>
+      <c r="O37">
         <v>541</v>
       </c>
-      <c r="O37">
+      <c r="P37">
         <v>17151</v>
       </c>
-      <c r="P37">
+      <c r="Q37">
         <v>57832</v>
       </c>
-      <c r="Q37">
-        <v>4036</v>
-      </c>
-      <c r="R37">
-        <v>0</v>
-      </c>
-      <c r="S37">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="38" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="38">
       <c r="A38">
         <v>35</v>
       </c>
-      <c r="B38" t="s">
-        <v>53</v>
+      <c r="B38" t="str">
+        <v>44 - Pithoragarh</v>
       </c>
       <c r="C38">
         <v>29110</v>
@@ -2814,17 +2284,17 @@
         <v>0</v>
       </c>
       <c r="E38">
+        <v>1</v>
+      </c>
+      <c r="F38">
         <v>29110</v>
       </c>
-      <c r="F38">
-        <v>0</v>
-      </c>
       <c r="G38">
+        <v>0</v>
+      </c>
+      <c r="H38">
         <v>29110</v>
       </c>
-      <c r="H38">
-        <v>0</v>
-      </c>
       <c r="I38">
         <v>0</v>
       </c>
@@ -2835,36 +2305,30 @@
         <v>0</v>
       </c>
       <c r="L38">
+        <v>0</v>
+      </c>
+      <c r="M38">
         <v>5386</v>
       </c>
-      <c r="M38">
+      <c r="N38">
         <v>2</v>
       </c>
-      <c r="N38">
+      <c r="O38">
         <v>635</v>
       </c>
-      <c r="O38">
+      <c r="P38">
         <v>28475</v>
       </c>
-      <c r="P38">
+      <c r="Q38">
         <v>63038</v>
       </c>
-      <c r="Q38">
-        <v>5135</v>
-      </c>
-      <c r="R38">
-        <v>0</v>
-      </c>
-      <c r="S38">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="39" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="39">
       <c r="A39">
         <v>36</v>
       </c>
-      <c r="B39" t="s">
-        <v>54</v>
+      <c r="B39" t="str">
+        <v>45 - Gangolihat</v>
       </c>
       <c r="C39">
         <v>21367</v>
@@ -2873,17 +2337,17 @@
         <v>0</v>
       </c>
       <c r="E39">
+        <v>0</v>
+      </c>
+      <c r="F39">
         <v>21367</v>
       </c>
-      <c r="F39">
-        <v>0</v>
-      </c>
       <c r="G39">
+        <v>0</v>
+      </c>
+      <c r="H39">
         <v>21367</v>
       </c>
-      <c r="H39">
-        <v>0</v>
-      </c>
       <c r="I39">
         <v>0</v>
       </c>
@@ -2894,36 +2358,30 @@
         <v>0</v>
       </c>
       <c r="L39">
+        <v>0</v>
+      </c>
+      <c r="M39">
         <v>4529</v>
       </c>
-      <c r="M39">
+      <c r="N39">
         <v>1</v>
       </c>
-      <c r="N39">
+      <c r="O39">
         <v>234</v>
       </c>
-      <c r="O39">
+      <c r="P39">
         <v>21133</v>
       </c>
-      <c r="P39">
+      <c r="Q39">
         <v>71133</v>
       </c>
-      <c r="Q39">
-        <v>5903</v>
-      </c>
-      <c r="R39">
-        <v>0</v>
-      </c>
-      <c r="S39">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="40" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="40">
       <c r="A40">
         <v>37</v>
       </c>
-      <c r="B40" t="s">
-        <v>55</v>
+      <c r="B40" t="str">
+        <v>46 - Kapkot</v>
       </c>
       <c r="C40">
         <v>18905</v>
@@ -2932,17 +2390,17 @@
         <v>0</v>
       </c>
       <c r="E40">
+        <v>0</v>
+      </c>
+      <c r="F40">
         <v>18905</v>
       </c>
-      <c r="F40">
-        <v>0</v>
-      </c>
       <c r="G40">
+        <v>0</v>
+      </c>
+      <c r="H40">
         <v>18905</v>
       </c>
-      <c r="H40">
-        <v>0</v>
-      </c>
       <c r="I40">
         <v>0</v>
       </c>
@@ -2953,36 +2411,30 @@
         <v>0</v>
       </c>
       <c r="L40">
+        <v>0</v>
+      </c>
+      <c r="M40">
         <v>1812</v>
       </c>
-      <c r="M40">
-        <v>0</v>
-      </c>
       <c r="N40">
+        <v>0</v>
+      </c>
+      <c r="O40">
         <v>52</v>
       </c>
-      <c r="O40">
+      <c r="P40">
         <v>18853</v>
       </c>
-      <c r="P40">
+      <c r="Q40">
         <v>73242</v>
       </c>
-      <c r="Q40">
-        <v>3824</v>
-      </c>
-      <c r="R40">
-        <v>0</v>
-      </c>
-      <c r="S40">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="41" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="41">
       <c r="A41">
         <v>38</v>
       </c>
-      <c r="B41" t="s">
-        <v>56</v>
+      <c r="B41" t="str">
+        <v>47 - Bageshwar</v>
       </c>
       <c r="C41">
         <v>23521</v>
@@ -2991,17 +2443,17 @@
         <v>0</v>
       </c>
       <c r="E41">
+        <v>0</v>
+      </c>
+      <c r="F41">
         <v>23521</v>
       </c>
-      <c r="F41">
-        <v>0</v>
-      </c>
       <c r="G41">
+        <v>0</v>
+      </c>
+      <c r="H41">
         <v>23521</v>
       </c>
-      <c r="H41">
-        <v>0</v>
-      </c>
       <c r="I41">
         <v>0</v>
       </c>
@@ -3012,36 +2464,30 @@
         <v>0</v>
       </c>
       <c r="L41">
+        <v>0</v>
+      </c>
+      <c r="M41">
         <v>1499</v>
       </c>
-      <c r="M41">
-        <v>0</v>
-      </c>
       <c r="N41">
+        <v>0</v>
+      </c>
+      <c r="O41">
         <v>92</v>
       </c>
-      <c r="O41">
+      <c r="P41">
         <v>23429</v>
       </c>
-      <c r="P41">
+      <c r="Q41">
         <v>85251</v>
       </c>
-      <c r="Q41">
-        <v>6015</v>
-      </c>
-      <c r="R41">
-        <v>0</v>
-      </c>
-      <c r="S41">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="42" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="42">
       <c r="A42">
         <v>39</v>
       </c>
-      <c r="B42" t="s">
-        <v>57</v>
+      <c r="B42" t="str">
+        <v>54 - Lohaghat</v>
       </c>
       <c r="C42">
         <v>27565</v>
@@ -3050,17 +2496,17 @@
         <v>0</v>
       </c>
       <c r="E42">
+        <v>0</v>
+      </c>
+      <c r="F42">
         <v>27565</v>
       </c>
-      <c r="F42">
-        <v>0</v>
-      </c>
       <c r="G42">
+        <v>0</v>
+      </c>
+      <c r="H42">
         <v>27565</v>
       </c>
-      <c r="H42">
-        <v>0</v>
-      </c>
       <c r="I42">
         <v>0</v>
       </c>
@@ -3071,36 +2517,30 @@
         <v>0</v>
       </c>
       <c r="L42">
+        <v>0</v>
+      </c>
+      <c r="M42">
         <v>6264</v>
       </c>
-      <c r="M42">
-        <v>0</v>
-      </c>
       <c r="N42">
+        <v>0</v>
+      </c>
+      <c r="O42">
         <v>419</v>
       </c>
-      <c r="O42">
+      <c r="P42">
         <v>27147</v>
       </c>
-      <c r="P42">
+      <c r="Q42">
         <v>68615</v>
       </c>
-      <c r="Q42">
-        <v>4708</v>
-      </c>
-      <c r="R42">
-        <v>0</v>
-      </c>
-      <c r="S42">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="43" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="43">
       <c r="A43">
         <v>40</v>
       </c>
-      <c r="B43" t="s">
-        <v>58</v>
+      <c r="B43" t="str">
+        <v>55 - Champawat</v>
       </c>
       <c r="C43">
         <v>29700</v>
@@ -3109,17 +2549,17 @@
         <v>0</v>
       </c>
       <c r="E43">
+        <v>0</v>
+      </c>
+      <c r="F43">
         <v>29700</v>
       </c>
-      <c r="F43">
-        <v>0</v>
-      </c>
       <c r="G43">
+        <v>0</v>
+      </c>
+      <c r="H43">
         <v>29700</v>
       </c>
-      <c r="H43">
-        <v>0</v>
-      </c>
       <c r="I43">
         <v>0</v>
       </c>
@@ -3130,36 +2570,30 @@
         <v>0</v>
       </c>
       <c r="L43">
+        <v>0</v>
+      </c>
+      <c r="M43">
         <v>6804</v>
       </c>
-      <c r="M43">
+      <c r="N43">
         <v>1</v>
       </c>
-      <c r="N43">
+      <c r="O43">
         <v>957</v>
       </c>
-      <c r="O43">
+      <c r="P43">
         <v>28774</v>
       </c>
-      <c r="P43">
+      <c r="Q43">
         <v>63012</v>
       </c>
-      <c r="Q43">
-        <v>5219</v>
-      </c>
-      <c r="R43">
-        <v>0</v>
-      </c>
-      <c r="S43">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="44" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="44">
       <c r="A44">
         <v>41</v>
       </c>
-      <c r="B44" t="s">
-        <v>59</v>
+      <c r="B44" t="str">
+        <v>4 - Badrinath</v>
       </c>
       <c r="C44">
         <v>21900</v>
@@ -3168,17 +2602,17 @@
         <v>0</v>
       </c>
       <c r="E44">
+        <v>0</v>
+      </c>
+      <c r="F44">
         <v>21900</v>
       </c>
-      <c r="F44">
-        <v>0</v>
-      </c>
       <c r="G44">
+        <v>0</v>
+      </c>
+      <c r="H44">
         <v>21900</v>
       </c>
-      <c r="H44">
-        <v>0</v>
-      </c>
       <c r="I44">
         <v>0</v>
       </c>
@@ -3189,36 +2623,30 @@
         <v>0</v>
       </c>
       <c r="L44">
+        <v>0</v>
+      </c>
+      <c r="M44">
         <v>6643</v>
       </c>
-      <c r="M44">
+      <c r="N44">
         <v>24</v>
       </c>
-      <c r="N44">
+      <c r="O44">
         <v>347</v>
       </c>
-      <c r="O44">
+      <c r="P44">
         <v>21553</v>
       </c>
-      <c r="P44">
+      <c r="Q44">
         <v>68393</v>
       </c>
-      <c r="Q44">
-        <v>7659</v>
-      </c>
-      <c r="R44">
-        <v>0</v>
-      </c>
-      <c r="S44">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="45" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="45">
       <c r="A45">
         <v>42</v>
       </c>
-      <c r="B45" t="s">
-        <v>60</v>
+      <c r="B45" t="str">
+        <v>5 - Tharali</v>
       </c>
       <c r="C45">
         <v>19935</v>
@@ -3227,17 +2655,17 @@
         <v>0</v>
       </c>
       <c r="E45">
+        <v>0</v>
+      </c>
+      <c r="F45">
         <v>19935</v>
       </c>
-      <c r="F45">
-        <v>0</v>
-      </c>
       <c r="G45">
+        <v>0</v>
+      </c>
+      <c r="H45">
         <v>19935</v>
       </c>
-      <c r="H45">
-        <v>0</v>
-      </c>
       <c r="I45">
         <v>0</v>
       </c>
@@ -3248,36 +2676,30 @@
         <v>0</v>
       </c>
       <c r="L45">
+        <v>0</v>
+      </c>
+      <c r="M45">
         <v>2254</v>
       </c>
-      <c r="M45">
+      <c r="N45">
         <v>13</v>
       </c>
-      <c r="N45">
+      <c r="O45">
         <v>149</v>
       </c>
-      <c r="O45">
+      <c r="P45">
         <v>19786</v>
       </c>
-      <c r="P45">
+      <c r="Q45">
         <v>76287</v>
       </c>
-      <c r="Q45">
-        <v>6998</v>
-      </c>
-      <c r="R45">
-        <v>0</v>
-      </c>
-      <c r="S45">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="46" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="46">
       <c r="A46">
         <v>43</v>
       </c>
-      <c r="B46" t="s">
-        <v>61</v>
+      <c r="B46" t="str">
+        <v>6 - Karanprayag</v>
       </c>
       <c r="C46">
         <v>21512</v>
@@ -3286,17 +2708,17 @@
         <v>0</v>
       </c>
       <c r="E46">
+        <v>0</v>
+      </c>
+      <c r="F46">
         <v>21512</v>
       </c>
-      <c r="F46">
-        <v>0</v>
-      </c>
       <c r="G46">
+        <v>0</v>
+      </c>
+      <c r="H46">
         <v>21512</v>
       </c>
-      <c r="H46">
-        <v>0</v>
-      </c>
       <c r="I46">
         <v>0</v>
       </c>
@@ -3307,36 +2729,30 @@
         <v>0</v>
       </c>
       <c r="L46">
+        <v>0</v>
+      </c>
+      <c r="M46">
         <v>8303</v>
       </c>
-      <c r="M46">
+      <c r="N46">
         <v>32</v>
       </c>
-      <c r="N46">
+      <c r="O46">
         <v>276</v>
       </c>
-      <c r="O46">
+      <c r="P46">
         <v>21236</v>
       </c>
-      <c r="P46">
+      <c r="Q46">
         <v>64160</v>
       </c>
-      <c r="Q46">
-        <v>7548</v>
-      </c>
-      <c r="R46">
-        <v>0</v>
-      </c>
-      <c r="S46">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="47" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="47">
       <c r="A47">
         <v>44</v>
       </c>
-      <c r="B47" t="s">
-        <v>62</v>
+      <c r="B47" t="str">
+        <v>1 - Purola</v>
       </c>
       <c r="C47">
         <v>22426</v>
@@ -3345,17 +2761,17 @@
         <v>0</v>
       </c>
       <c r="E47">
+        <v>0</v>
+      </c>
+      <c r="F47">
         <v>22426</v>
       </c>
-      <c r="F47">
-        <v>0</v>
-      </c>
       <c r="G47">
+        <v>0</v>
+      </c>
+      <c r="H47">
         <v>22426</v>
       </c>
-      <c r="H47">
-        <v>0</v>
-      </c>
       <c r="I47">
         <v>0</v>
       </c>
@@ -3366,36 +2782,30 @@
         <v>0</v>
       </c>
       <c r="L47">
+        <v>0</v>
+      </c>
+      <c r="M47">
         <v>2595</v>
       </c>
-      <c r="M47">
+      <c r="N47">
         <v>1</v>
       </c>
-      <c r="N47">
+      <c r="O47">
         <v>137</v>
       </c>
-      <c r="O47">
+      <c r="P47">
         <v>21624</v>
       </c>
-      <c r="P47">
+      <c r="Q47">
         <v>49875</v>
       </c>
-      <c r="Q47">
-        <v>5046</v>
-      </c>
-      <c r="R47">
-        <v>0</v>
-      </c>
-      <c r="S47">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="48" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="48">
       <c r="A48">
         <v>45</v>
       </c>
-      <c r="B48" t="s">
-        <v>63</v>
+      <c r="B48" t="str">
+        <v>2 - Yamunotri</v>
       </c>
       <c r="C48">
         <v>19641</v>
@@ -3404,17 +2814,17 @@
         <v>0</v>
       </c>
       <c r="E48">
+        <v>0</v>
+      </c>
+      <c r="F48">
         <v>19641</v>
       </c>
-      <c r="F48">
-        <v>0</v>
-      </c>
       <c r="G48">
+        <v>0</v>
+      </c>
+      <c r="H48">
         <v>19641</v>
       </c>
-      <c r="H48">
-        <v>0</v>
-      </c>
       <c r="I48">
         <v>0</v>
       </c>
@@ -3425,36 +2835,30 @@
         <v>0</v>
       </c>
       <c r="L48">
+        <v>0</v>
+      </c>
+      <c r="M48">
         <v>3799</v>
       </c>
-      <c r="M48">
+      <c r="N48">
         <v>4</v>
       </c>
-      <c r="N48">
+      <c r="O48">
         <v>254</v>
       </c>
-      <c r="O48">
+      <c r="P48">
         <v>19350</v>
       </c>
-      <c r="P48">
+      <c r="Q48">
         <v>54142</v>
       </c>
-      <c r="Q48">
-        <v>4623</v>
-      </c>
-      <c r="R48">
-        <v>0</v>
-      </c>
-      <c r="S48">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="49" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="49">
       <c r="A49">
         <v>46</v>
       </c>
-      <c r="B49" t="s">
-        <v>64</v>
+      <c r="B49" t="str">
+        <v>3 - Gangotri</v>
       </c>
       <c r="C49">
         <v>21651</v>
@@ -3463,17 +2867,17 @@
         <v>0</v>
       </c>
       <c r="E49">
+        <v>0</v>
+      </c>
+      <c r="F49">
         <v>21651</v>
       </c>
-      <c r="F49">
-        <v>0</v>
-      </c>
       <c r="G49">
+        <v>0</v>
+      </c>
+      <c r="H49">
         <v>21651</v>
       </c>
-      <c r="H49">
-        <v>0</v>
-      </c>
       <c r="I49">
         <v>0</v>
       </c>
@@ -3484,36 +2888,30 @@
         <v>0</v>
       </c>
       <c r="L49">
+        <v>0</v>
+      </c>
+      <c r="M49">
         <v>3627</v>
       </c>
-      <c r="M49">
-        <v>0</v>
-      </c>
       <c r="N49">
+        <v>0</v>
+      </c>
+      <c r="O49">
         <v>628</v>
       </c>
-      <c r="O49">
+      <c r="P49">
         <v>21024</v>
       </c>
-      <c r="P49">
+      <c r="Q49">
         <v>55376</v>
       </c>
-      <c r="Q49">
-        <v>5057</v>
-      </c>
-      <c r="R49">
-        <v>0</v>
-      </c>
-      <c r="S49">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="50" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="50">
       <c r="A50">
         <v>47</v>
       </c>
-      <c r="B50" t="s">
-        <v>65</v>
+      <c r="B50" t="str">
+        <v>7 - Kedarnath</v>
       </c>
       <c r="C50">
         <v>21936</v>
@@ -3522,17 +2920,17 @@
         <v>0</v>
       </c>
       <c r="E50">
+        <v>0</v>
+      </c>
+      <c r="F50">
         <v>21936</v>
       </c>
-      <c r="F50">
-        <v>0</v>
-      </c>
       <c r="G50">
+        <v>0</v>
+      </c>
+      <c r="H50">
         <v>21936</v>
       </c>
-      <c r="H50">
-        <v>0</v>
-      </c>
       <c r="I50">
         <v>0</v>
       </c>
@@ -3543,36 +2941,30 @@
         <v>0</v>
       </c>
       <c r="L50">
+        <v>0</v>
+      </c>
+      <c r="M50">
         <v>4160</v>
       </c>
-      <c r="M50">
+      <c r="N50">
         <v>5</v>
       </c>
-      <c r="N50">
+      <c r="O50">
         <v>26</v>
       </c>
-      <c r="O50">
+      <c r="P50">
         <v>21910</v>
       </c>
-      <c r="P50">
+      <c r="Q50">
         <v>63298</v>
       </c>
-      <c r="Q50">
-        <v>7292</v>
-      </c>
-      <c r="R50">
-        <v>0</v>
-      </c>
-      <c r="S50">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="51" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="51">
       <c r="A51">
         <v>48</v>
       </c>
-      <c r="B51" t="s">
-        <v>66</v>
+      <c r="B51" t="str">
+        <v>8 - Rudraprayag</v>
       </c>
       <c r="C51">
         <v>23798</v>
@@ -3581,17 +2973,17 @@
         <v>0</v>
       </c>
       <c r="E51">
+        <v>0</v>
+      </c>
+      <c r="F51">
         <v>23798</v>
       </c>
-      <c r="F51">
-        <v>0</v>
-      </c>
       <c r="G51">
+        <v>0</v>
+      </c>
+      <c r="H51">
         <v>23798</v>
       </c>
-      <c r="H51">
-        <v>0</v>
-      </c>
       <c r="I51">
         <v>0</v>
       </c>
@@ -3602,36 +2994,30 @@
         <v>0</v>
       </c>
       <c r="L51">
+        <v>0</v>
+      </c>
+      <c r="M51">
         <v>4843</v>
       </c>
-      <c r="M51">
+      <c r="N51">
         <v>11</v>
       </c>
-      <c r="N51">
+      <c r="O51">
         <v>75</v>
       </c>
-      <c r="O51">
+      <c r="P51">
         <v>23723</v>
       </c>
-      <c r="P51">
+      <c r="Q51">
         <v>71754</v>
       </c>
-      <c r="Q51">
-        <v>7715</v>
-      </c>
-      <c r="R51">
-        <v>0</v>
-      </c>
-      <c r="S51">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="52" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="52">
       <c r="A52">
         <v>49</v>
       </c>
-      <c r="B52" t="s">
-        <v>67</v>
+      <c r="B52" t="str">
+        <v>9 - Ghansali</v>
       </c>
       <c r="C52">
         <v>21094</v>
@@ -3640,17 +3026,17 @@
         <v>0</v>
       </c>
       <c r="E52">
+        <v>0</v>
+      </c>
+      <c r="F52">
         <v>21094</v>
       </c>
-      <c r="F52">
-        <v>0</v>
-      </c>
       <c r="G52">
+        <v>0</v>
+      </c>
+      <c r="H52">
         <v>21094</v>
       </c>
-      <c r="H52">
-        <v>0</v>
-      </c>
       <c r="I52">
         <v>0</v>
       </c>
@@ -3661,36 +3047,30 @@
         <v>0</v>
       </c>
       <c r="L52">
+        <v>0</v>
+      </c>
+      <c r="M52">
         <v>2942</v>
       </c>
-      <c r="M52">
+      <c r="N52">
         <v>1</v>
       </c>
-      <c r="N52">
+      <c r="O52">
         <v>45</v>
       </c>
-      <c r="O52">
+      <c r="P52">
         <v>21049</v>
       </c>
-      <c r="P52">
+      <c r="Q52">
         <v>63987</v>
       </c>
-      <c r="Q52">
-        <v>5655</v>
-      </c>
-      <c r="R52">
-        <v>0</v>
-      </c>
-      <c r="S52">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="53" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="53">
       <c r="A53">
         <v>50</v>
       </c>
-      <c r="B53" t="s">
-        <v>68</v>
+      <c r="B53" t="str">
+        <v>10 - Devprayag</v>
       </c>
       <c r="C53">
         <v>19131</v>
@@ -3699,17 +3079,17 @@
         <v>0</v>
       </c>
       <c r="E53">
+        <v>0</v>
+      </c>
+      <c r="F53">
         <v>19131</v>
       </c>
-      <c r="F53">
-        <v>0</v>
-      </c>
       <c r="G53">
+        <v>0</v>
+      </c>
+      <c r="H53">
         <v>19131</v>
       </c>
-      <c r="H53">
-        <v>0</v>
-      </c>
       <c r="I53">
         <v>0</v>
       </c>
@@ -3720,36 +3100,30 @@
         <v>0</v>
       </c>
       <c r="L53">
+        <v>0</v>
+      </c>
+      <c r="M53">
         <v>3513</v>
       </c>
-      <c r="M53">
+      <c r="N53">
         <v>1</v>
       </c>
-      <c r="N53">
+      <c r="O53">
         <v>76</v>
       </c>
-      <c r="O53">
+      <c r="P53">
         <v>19055</v>
       </c>
-      <c r="P53">
+      <c r="Q53">
         <v>56306</v>
       </c>
-      <c r="Q53">
-        <v>6551</v>
-      </c>
-      <c r="R53">
-        <v>0</v>
-      </c>
-      <c r="S53">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="54" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="54">
       <c r="A54">
         <v>51</v>
       </c>
-      <c r="B54" t="s">
-        <v>69</v>
+      <c r="B54" t="str">
+        <v>11 - Narendranagar</v>
       </c>
       <c r="C54">
         <v>20758</v>
@@ -3758,17 +3132,17 @@
         <v>0</v>
       </c>
       <c r="E54">
+        <v>0</v>
+      </c>
+      <c r="F54">
         <v>20758</v>
       </c>
-      <c r="F54">
-        <v>0</v>
-      </c>
       <c r="G54">
+        <v>0</v>
+      </c>
+      <c r="H54">
         <v>20758</v>
       </c>
-      <c r="H54">
-        <v>0</v>
-      </c>
       <c r="I54">
         <v>0</v>
       </c>
@@ -3779,36 +3153,30 @@
         <v>0</v>
       </c>
       <c r="L54">
+        <v>0</v>
+      </c>
+      <c r="M54">
         <v>2603</v>
       </c>
-      <c r="M54">
+      <c r="N54">
         <v>5</v>
       </c>
-      <c r="N54">
+      <c r="O54">
         <v>391</v>
       </c>
-      <c r="O54">
+      <c r="P54">
         <v>20367</v>
       </c>
-      <c r="P54">
+      <c r="Q54">
         <v>58440</v>
       </c>
-      <c r="Q54">
-        <v>7347</v>
-      </c>
-      <c r="R54">
-        <v>0</v>
-      </c>
-      <c r="S54">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="55" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="55">
       <c r="A55">
         <v>52</v>
       </c>
-      <c r="B55" t="s">
-        <v>70</v>
+      <c r="B55" t="str">
+        <v>12 - Pratapnagar</v>
       </c>
       <c r="C55">
         <v>16022</v>
@@ -3817,17 +3185,17 @@
         <v>0</v>
       </c>
       <c r="E55">
+        <v>0</v>
+      </c>
+      <c r="F55">
         <v>16022</v>
       </c>
-      <c r="F55">
-        <v>0</v>
-      </c>
       <c r="G55">
+        <v>0</v>
+      </c>
+      <c r="H55">
         <v>16022</v>
       </c>
-      <c r="H55">
-        <v>0</v>
-      </c>
       <c r="I55">
         <v>0</v>
       </c>
@@ -3838,36 +3206,30 @@
         <v>0</v>
       </c>
       <c r="L55">
+        <v>0</v>
+      </c>
+      <c r="M55">
         <v>2109</v>
       </c>
-      <c r="M55">
+      <c r="N55">
         <v>1</v>
       </c>
-      <c r="N55">
+      <c r="O55">
         <v>129</v>
       </c>
-      <c r="O55">
+      <c r="P55">
         <v>15893</v>
       </c>
-      <c r="P55">
+      <c r="Q55">
         <v>58215</v>
       </c>
-      <c r="Q55">
-        <v>5098</v>
-      </c>
-      <c r="R55">
-        <v>0</v>
-      </c>
-      <c r="S55">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="56" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="56">
       <c r="A56">
         <v>53</v>
       </c>
-      <c r="B56" t="s">
-        <v>71</v>
+      <c r="B56" t="str">
+        <v>13 - Tehri</v>
       </c>
       <c r="C56">
         <v>19256</v>
@@ -3876,17 +3238,17 @@
         <v>0</v>
       </c>
       <c r="E56">
+        <v>0</v>
+      </c>
+      <c r="F56">
         <v>19256</v>
       </c>
-      <c r="F56">
-        <v>0</v>
-      </c>
       <c r="G56">
+        <v>0</v>
+      </c>
+      <c r="H56">
         <v>19256</v>
       </c>
-      <c r="H56">
-        <v>0</v>
-      </c>
       <c r="I56">
         <v>0</v>
       </c>
@@ -3897,36 +3259,30 @@
         <v>0</v>
       </c>
       <c r="L56">
+        <v>0</v>
+      </c>
+      <c r="M56">
         <v>4091</v>
       </c>
-      <c r="M56">
+      <c r="N56">
         <v>3</v>
       </c>
-      <c r="N56">
+      <c r="O56">
         <v>451</v>
       </c>
-      <c r="O56">
+      <c r="P56">
         <v>18805</v>
       </c>
-      <c r="P56">
+      <c r="Q56">
         <v>47621</v>
       </c>
-      <c r="Q56">
-        <v>4882</v>
-      </c>
-      <c r="R56">
-        <v>0</v>
-      </c>
-      <c r="S56">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="57" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="57">
       <c r="A57">
         <v>54</v>
       </c>
-      <c r="B57" t="s">
-        <v>72</v>
+      <c r="B57" t="str">
+        <v>14 - Dhanolti</v>
       </c>
       <c r="C57">
         <v>21240</v>
@@ -3935,17 +3291,17 @@
         <v>0</v>
       </c>
       <c r="E57">
+        <v>0</v>
+      </c>
+      <c r="F57">
         <v>21240</v>
       </c>
-      <c r="F57">
-        <v>0</v>
-      </c>
       <c r="G57">
+        <v>0</v>
+      </c>
+      <c r="H57">
         <v>21240</v>
       </c>
-      <c r="H57">
-        <v>0</v>
-      </c>
       <c r="I57">
         <v>0</v>
       </c>
@@ -3956,36 +3312,30 @@
         <v>0</v>
       </c>
       <c r="L57">
+        <v>0</v>
+      </c>
+      <c r="M57">
         <v>1905</v>
       </c>
-      <c r="M57">
+      <c r="N57">
         <v>5</v>
       </c>
-      <c r="N57">
+      <c r="O57">
         <v>39</v>
       </c>
-      <c r="O57">
+      <c r="P57">
         <v>21201</v>
       </c>
-      <c r="P57">
+      <c r="Q57">
         <v>61556</v>
       </c>
-      <c r="Q57">
-        <v>6870</v>
-      </c>
-      <c r="R57">
-        <v>0</v>
-      </c>
-      <c r="S57">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="58" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="58">
       <c r="A58">
         <v>55</v>
       </c>
-      <c r="B58" t="s">
-        <v>73</v>
+      <c r="B58" t="str">
+        <v>36 - Yamkeshwar</v>
       </c>
       <c r="C58">
         <v>22819</v>
@@ -3994,17 +3344,17 @@
         <v>0</v>
       </c>
       <c r="E58">
+        <v>0</v>
+      </c>
+      <c r="F58">
         <v>22819</v>
       </c>
-      <c r="F58">
-        <v>0</v>
-      </c>
       <c r="G58">
+        <v>0</v>
+      </c>
+      <c r="H58">
         <v>22819</v>
       </c>
-      <c r="H58">
-        <v>0</v>
-      </c>
       <c r="I58">
         <v>0</v>
       </c>
@@ -4015,36 +3365,30 @@
         <v>0</v>
       </c>
       <c r="L58">
+        <v>0</v>
+      </c>
+      <c r="M58">
         <v>8123</v>
       </c>
-      <c r="M58">
+      <c r="N58">
         <v>10</v>
       </c>
-      <c r="N58">
+      <c r="O58">
         <v>552</v>
       </c>
-      <c r="O58">
+      <c r="P58">
         <v>22267</v>
       </c>
-      <c r="P58">
+      <c r="Q58">
         <v>57577</v>
       </c>
-      <c r="Q58">
-        <v>8884</v>
-      </c>
-      <c r="R58">
-        <v>0</v>
-      </c>
-      <c r="S58">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="59" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="59">
       <c r="A59">
         <v>56</v>
       </c>
-      <c r="B59" t="s">
-        <v>74</v>
+      <c r="B59" t="str">
+        <v>37 - Pauri</v>
       </c>
       <c r="C59">
         <v>18776</v>
@@ -4053,17 +3397,17 @@
         <v>0</v>
       </c>
       <c r="E59">
+        <v>0</v>
+      </c>
+      <c r="F59">
         <v>18776</v>
       </c>
-      <c r="F59">
-        <v>0</v>
-      </c>
       <c r="G59">
+        <v>0</v>
+      </c>
+      <c r="H59">
         <v>18776</v>
       </c>
-      <c r="H59">
-        <v>0</v>
-      </c>
       <c r="I59">
         <v>0</v>
       </c>
@@ -4074,36 +3418,30 @@
         <v>0</v>
       </c>
       <c r="L59">
+        <v>0</v>
+      </c>
+      <c r="M59">
         <v>2506</v>
       </c>
-      <c r="M59">
+      <c r="N59">
         <v>2</v>
       </c>
-      <c r="N59">
+      <c r="O59">
         <v>287</v>
       </c>
-      <c r="O59">
+      <c r="P59">
         <v>18489</v>
       </c>
-      <c r="P59">
+      <c r="Q59">
         <v>60495</v>
       </c>
-      <c r="Q59">
-        <v>8028</v>
-      </c>
-      <c r="R59">
-        <v>0</v>
-      </c>
-      <c r="S59">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="60" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="60">
       <c r="A60">
         <v>57</v>
       </c>
-      <c r="B60" t="s">
-        <v>75</v>
+      <c r="B60" t="str">
+        <v>38 - Srinagar</v>
       </c>
       <c r="C60">
         <v>23749</v>
@@ -4112,17 +3450,17 @@
         <v>0</v>
       </c>
       <c r="E60">
+        <v>0</v>
+      </c>
+      <c r="F60">
         <v>23749</v>
       </c>
-      <c r="F60">
-        <v>0</v>
-      </c>
       <c r="G60">
+        <v>0</v>
+      </c>
+      <c r="H60">
         <v>23749</v>
       </c>
-      <c r="H60">
-        <v>0</v>
-      </c>
       <c r="I60">
         <v>0</v>
       </c>
@@ -4133,36 +3471,30 @@
         <v>0</v>
       </c>
       <c r="L60">
+        <v>0</v>
+      </c>
+      <c r="M60">
         <v>5815</v>
       </c>
-      <c r="M60">
+      <c r="N60">
         <v>9</v>
       </c>
-      <c r="N60">
+      <c r="O60">
         <v>324</v>
       </c>
-      <c r="O60">
+      <c r="P60">
         <v>23425</v>
       </c>
-      <c r="P60">
+      <c r="Q60">
         <v>70140</v>
       </c>
-      <c r="Q60">
-        <v>7415</v>
-      </c>
-      <c r="R60">
-        <v>0</v>
-      </c>
-      <c r="S60">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="61" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="61">
       <c r="A61">
         <v>58</v>
       </c>
-      <c r="B61" t="s">
-        <v>76</v>
+      <c r="B61" t="str">
+        <v>39 - Chaubattakhal</v>
       </c>
       <c r="C61">
         <v>22069</v>
@@ -4171,17 +3503,17 @@
         <v>0</v>
       </c>
       <c r="E61">
+        <v>0</v>
+      </c>
+      <c r="F61">
         <v>22069</v>
       </c>
-      <c r="F61">
-        <v>0</v>
-      </c>
       <c r="G61">
+        <v>0</v>
+      </c>
+      <c r="H61">
         <v>22069</v>
       </c>
-      <c r="H61">
-        <v>0</v>
-      </c>
       <c r="I61">
         <v>0</v>
       </c>
@@ -4192,36 +3524,30 @@
         <v>0</v>
       </c>
       <c r="L61">
+        <v>0</v>
+      </c>
+      <c r="M61">
         <v>9977</v>
       </c>
-      <c r="M61">
+      <c r="N61">
         <v>37</v>
       </c>
-      <c r="N61">
+      <c r="O61">
         <v>36</v>
       </c>
-      <c r="O61">
+      <c r="P61">
         <v>22033</v>
       </c>
-      <c r="P61">
+      <c r="Q61">
         <v>55240</v>
       </c>
-      <c r="Q61">
-        <v>7927</v>
-      </c>
-      <c r="R61">
-        <v>1</v>
-      </c>
-      <c r="S61">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="62" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="62">
       <c r="A62">
         <v>59</v>
       </c>
-      <c r="B62" t="s">
-        <v>77</v>
+      <c r="B62" t="str">
+        <v>40 - Lansdowne</v>
       </c>
       <c r="C62">
         <v>15800</v>
@@ -4230,17 +3556,17 @@
         <v>0</v>
       </c>
       <c r="E62">
+        <v>0</v>
+      </c>
+      <c r="F62">
         <v>15800</v>
       </c>
-      <c r="F62">
-        <v>0</v>
-      </c>
       <c r="G62">
+        <v>0</v>
+      </c>
+      <c r="H62">
         <v>15800</v>
       </c>
-      <c r="H62">
-        <v>0</v>
-      </c>
       <c r="I62">
         <v>0</v>
       </c>
@@ -4251,36 +3577,30 @@
         <v>0</v>
       </c>
       <c r="L62">
+        <v>0</v>
+      </c>
+      <c r="M62">
         <v>4214</v>
       </c>
-      <c r="M62">
+      <c r="N62">
         <v>19</v>
       </c>
-      <c r="N62">
+      <c r="O62">
         <v>494</v>
       </c>
-      <c r="O62">
+      <c r="P62">
         <v>15306</v>
       </c>
-      <c r="P62">
+      <c r="Q62">
         <v>51334</v>
       </c>
-      <c r="Q62">
-        <v>6917</v>
-      </c>
-      <c r="R62">
-        <v>0</v>
-      </c>
-      <c r="S62">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="63" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="63">
       <c r="A63">
         <v>60</v>
       </c>
-      <c r="B63" t="s">
-        <v>78</v>
+      <c r="B63" t="str">
+        <v>41 - Kotdwar</v>
       </c>
       <c r="C63">
         <v>36754</v>
@@ -4289,17 +3609,17 @@
         <v>0</v>
       </c>
       <c r="E63">
+        <v>0</v>
+      </c>
+      <c r="F63">
         <v>36754</v>
       </c>
-      <c r="F63">
-        <v>0</v>
-      </c>
       <c r="G63">
+        <v>0</v>
+      </c>
+      <c r="H63">
         <v>36754</v>
       </c>
-      <c r="H63">
-        <v>0</v>
-      </c>
       <c r="I63">
         <v>0</v>
       </c>
@@ -4310,36 +3630,30 @@
         <v>0</v>
       </c>
       <c r="L63">
+        <v>0</v>
+      </c>
+      <c r="M63">
         <v>10975</v>
       </c>
-      <c r="M63">
+      <c r="N63">
         <v>68</v>
       </c>
-      <c r="N63">
+      <c r="O63">
         <v>931</v>
       </c>
-      <c r="O63">
+      <c r="P63">
         <v>35823</v>
       </c>
-      <c r="P63">
+      <c r="Q63">
         <v>68696</v>
       </c>
-      <c r="Q63">
-        <v>9766</v>
-      </c>
-      <c r="R63">
-        <v>0</v>
-      </c>
-      <c r="S63">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="64" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="64">
       <c r="A64">
         <v>61</v>
       </c>
-      <c r="B64" t="s">
-        <v>79</v>
+      <c r="B64" t="str">
+        <v>15 - Chakrata</v>
       </c>
       <c r="C64">
         <v>42048</v>
@@ -4348,17 +3662,17 @@
         <v>0</v>
       </c>
       <c r="E64">
+        <v>0</v>
+      </c>
+      <c r="F64">
         <v>42048</v>
       </c>
-      <c r="F64">
-        <v>0</v>
-      </c>
       <c r="G64">
+        <v>0</v>
+      </c>
+      <c r="H64">
         <v>42048</v>
       </c>
-      <c r="H64">
-        <v>0</v>
-      </c>
       <c r="I64">
         <v>0</v>
       </c>
@@ -4369,36 +3683,30 @@
         <v>0</v>
       </c>
       <c r="L64">
+        <v>0</v>
+      </c>
+      <c r="M64">
         <v>9887</v>
       </c>
-      <c r="M64">
+      <c r="N64">
         <v>8</v>
       </c>
-      <c r="N64">
+      <c r="O64">
         <v>493</v>
       </c>
-      <c r="O64">
+      <c r="P64">
         <v>41555</v>
       </c>
-      <c r="P64">
+      <c r="Q64">
         <v>60527</v>
       </c>
-      <c r="Q64">
-        <v>5985</v>
-      </c>
-      <c r="R64">
-        <v>0</v>
-      </c>
-      <c r="S64">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="65" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="65">
       <c r="A65">
         <v>62</v>
       </c>
-      <c r="B65" t="s">
-        <v>80</v>
+      <c r="B65" t="str">
+        <v>16 - Vikasnagar</v>
       </c>
       <c r="C65">
         <v>41389</v>
@@ -4407,17 +3715,17 @@
         <v>0</v>
       </c>
       <c r="E65">
+        <v>0</v>
+      </c>
+      <c r="F65">
         <v>41389</v>
       </c>
-      <c r="F65">
-        <v>0</v>
-      </c>
       <c r="G65">
+        <v>0</v>
+      </c>
+      <c r="H65">
         <v>41389</v>
       </c>
-      <c r="H65">
-        <v>0</v>
-      </c>
       <c r="I65">
         <v>0</v>
       </c>
@@ -4428,36 +3736,30 @@
         <v>0</v>
       </c>
       <c r="L65">
+        <v>0</v>
+      </c>
+      <c r="M65">
         <v>13582</v>
       </c>
-      <c r="M65">
+      <c r="N65">
         <v>2</v>
       </c>
-      <c r="N65">
+      <c r="O65">
         <v>2635</v>
       </c>
-      <c r="O65">
+      <c r="P65">
         <v>38754</v>
       </c>
-      <c r="P65">
+      <c r="Q65">
         <v>58527</v>
       </c>
-      <c r="Q65">
-        <v>13282</v>
-      </c>
-      <c r="R65">
-        <v>0</v>
-      </c>
-      <c r="S65">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="66" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="66">
       <c r="A66">
         <v>63</v>
       </c>
-      <c r="B66" t="s">
-        <v>81</v>
+      <c r="B66" t="str">
+        <v>17 - Sahaspur</v>
       </c>
       <c r="C66">
         <v>67362</v>
@@ -4466,17 +3768,17 @@
         <v>0</v>
       </c>
       <c r="E66">
+        <v>1</v>
+      </c>
+      <c r="F66">
         <v>67362</v>
       </c>
-      <c r="F66">
-        <v>0</v>
-      </c>
       <c r="G66">
+        <v>0</v>
+      </c>
+      <c r="H66">
         <v>67362</v>
       </c>
-      <c r="H66">
-        <v>0</v>
-      </c>
       <c r="I66">
         <v>0</v>
       </c>
@@ -4487,36 +3789,30 @@
         <v>0</v>
       </c>
       <c r="L66">
+        <v>0</v>
+      </c>
+      <c r="M66">
         <v>13733</v>
       </c>
-      <c r="M66">
+      <c r="N66">
         <v>2</v>
       </c>
-      <c r="N66">
+      <c r="O66">
         <v>4022</v>
       </c>
-      <c r="O66">
+      <c r="P66">
         <v>63341</v>
       </c>
-      <c r="P66">
+      <c r="Q66">
         <v>93810</v>
       </c>
-      <c r="Q66">
-        <v>17742</v>
-      </c>
-      <c r="R66">
-        <v>0</v>
-      </c>
-      <c r="S66">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="67" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="67">
       <c r="A67">
         <v>64</v>
       </c>
-      <c r="B67" t="s">
-        <v>82</v>
+      <c r="B67" t="str">
+        <v>18 - Dharmpur</v>
       </c>
       <c r="C67">
         <v>68828</v>
@@ -4525,17 +3821,17 @@
         <v>0</v>
       </c>
       <c r="E67">
+        <v>0</v>
+      </c>
+      <c r="F67">
         <v>68828</v>
       </c>
-      <c r="F67">
-        <v>0</v>
-      </c>
       <c r="G67">
+        <v>0</v>
+      </c>
+      <c r="H67">
         <v>68828</v>
       </c>
-      <c r="H67">
-        <v>0</v>
-      </c>
       <c r="I67">
         <v>0</v>
       </c>
@@ -4546,36 +3842,30 @@
         <v>0</v>
       </c>
       <c r="L67">
+        <v>0</v>
+      </c>
+      <c r="M67">
         <v>19495</v>
       </c>
-      <c r="M67">
+      <c r="N67">
         <v>10</v>
       </c>
-      <c r="N67">
+      <c r="O67">
         <v>3644</v>
       </c>
-      <c r="O67">
+      <c r="P67">
         <v>65185</v>
       </c>
-      <c r="P67">
+      <c r="Q67">
         <v>78032</v>
       </c>
-      <c r="Q67">
-        <v>9807</v>
-      </c>
-      <c r="R67">
-        <v>0</v>
-      </c>
-      <c r="S67">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="68" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="68">
       <c r="A68">
         <v>65</v>
       </c>
-      <c r="B68" t="s">
-        <v>83</v>
+      <c r="B68" t="str">
+        <v>19 - Raipur</v>
       </c>
       <c r="C68">
         <v>65397</v>
@@ -4584,17 +3874,17 @@
         <v>0</v>
       </c>
       <c r="E68">
+        <v>0</v>
+      </c>
+      <c r="F68">
         <v>65397</v>
       </c>
-      <c r="F68">
-        <v>0</v>
-      </c>
       <c r="G68">
+        <v>0</v>
+      </c>
+      <c r="H68">
         <v>65397</v>
       </c>
-      <c r="H68">
-        <v>0</v>
-      </c>
       <c r="I68">
         <v>0</v>
       </c>
@@ -4605,36 +3895,30 @@
         <v>0</v>
       </c>
       <c r="L68">
+        <v>0</v>
+      </c>
+      <c r="M68">
         <v>18679</v>
       </c>
-      <c r="M68">
+      <c r="N68">
         <v>2</v>
       </c>
-      <c r="N68">
+      <c r="O68">
         <v>1603</v>
       </c>
-      <c r="O68">
+      <c r="P68">
         <v>63795</v>
       </c>
-      <c r="P68">
+      <c r="Q68">
         <v>71325</v>
       </c>
-      <c r="Q68">
-        <v>7850</v>
-      </c>
-      <c r="R68">
-        <v>0</v>
-      </c>
-      <c r="S68">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="69" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="69">
       <c r="A69">
         <v>66</v>
       </c>
-      <c r="B69" t="s">
-        <v>84</v>
+      <c r="B69" t="str">
+        <v>20 - Rajpur Road</v>
       </c>
       <c r="C69">
         <v>43938</v>
@@ -4643,17 +3927,17 @@
         <v>0</v>
       </c>
       <c r="E69">
+        <v>0</v>
+      </c>
+      <c r="F69">
         <v>43938</v>
       </c>
-      <c r="F69">
-        <v>0</v>
-      </c>
       <c r="G69">
+        <v>0</v>
+      </c>
+      <c r="H69">
         <v>43938</v>
       </c>
-      <c r="H69">
-        <v>0</v>
-      </c>
       <c r="I69">
         <v>0</v>
       </c>
@@ -4664,36 +3948,30 @@
         <v>0</v>
       </c>
       <c r="L69">
+        <v>0</v>
+      </c>
+      <c r="M69">
         <v>18216</v>
       </c>
-      <c r="M69">
+      <c r="N69">
         <v>2</v>
       </c>
-      <c r="N69">
+      <c r="O69">
         <v>2619</v>
       </c>
-      <c r="O69">
+      <c r="P69">
         <v>41322</v>
       </c>
-      <c r="P69">
+      <c r="Q69">
         <v>36118</v>
       </c>
-      <c r="Q69">
-        <v>6528</v>
-      </c>
-      <c r="R69">
-        <v>0</v>
-      </c>
-      <c r="S69">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="70" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="70">
       <c r="A70">
         <v>67</v>
       </c>
-      <c r="B70" t="s">
-        <v>85</v>
+      <c r="B70" t="str">
+        <v>21 - Dehradun Cantonment</v>
       </c>
       <c r="C70">
         <v>47711</v>
@@ -4702,17 +3980,17 @@
         <v>0</v>
       </c>
       <c r="E70">
+        <v>0</v>
+      </c>
+      <c r="F70">
         <v>47711</v>
       </c>
-      <c r="F70">
-        <v>0</v>
-      </c>
       <c r="G70">
+        <v>0</v>
+      </c>
+      <c r="H70">
         <v>47711</v>
       </c>
-      <c r="H70">
-        <v>0</v>
-      </c>
       <c r="I70">
         <v>0</v>
       </c>
@@ -4723,36 +4001,30 @@
         <v>0</v>
       </c>
       <c r="L70">
+        <v>0</v>
+      </c>
+      <c r="M70">
         <v>18275</v>
       </c>
-      <c r="M70">
+      <c r="N70">
         <v>2</v>
       </c>
-      <c r="N70">
+      <c r="O70">
         <v>3246</v>
       </c>
-      <c r="O70">
+      <c r="P70">
         <v>44466</v>
       </c>
-      <c r="P70">
+      <c r="Q70">
         <v>42051</v>
       </c>
-      <c r="Q70">
-        <v>5798</v>
-      </c>
-      <c r="R70">
-        <v>0</v>
-      </c>
-      <c r="S70">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="71" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="71">
       <c r="A71">
         <v>68</v>
       </c>
-      <c r="B71" t="s">
-        <v>86</v>
+      <c r="B71" t="str">
+        <v>22 - Mussoorie</v>
       </c>
       <c r="C71">
         <v>50963</v>
@@ -4761,17 +4033,17 @@
         <v>0</v>
       </c>
       <c r="E71">
+        <v>0</v>
+      </c>
+      <c r="F71">
         <v>50963</v>
       </c>
-      <c r="F71">
-        <v>0</v>
-      </c>
       <c r="G71">
+        <v>0</v>
+      </c>
+      <c r="H71">
         <v>50963</v>
       </c>
-      <c r="H71">
-        <v>0</v>
-      </c>
       <c r="I71">
         <v>0</v>
       </c>
@@ -4782,36 +4054,30 @@
         <v>0</v>
       </c>
       <c r="L71">
+        <v>0</v>
+      </c>
+      <c r="M71">
         <v>22851</v>
       </c>
-      <c r="M71">
+      <c r="N71">
         <v>1</v>
       </c>
-      <c r="N71">
+      <c r="O71">
         <v>4449</v>
       </c>
-      <c r="O71">
+      <c r="P71">
         <v>46514</v>
       </c>
-      <c r="P71">
+      <c r="Q71">
         <v>49140</v>
       </c>
-      <c r="Q71">
-        <v>6782</v>
-      </c>
-      <c r="R71">
-        <v>0</v>
-      </c>
-      <c r="S71">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="72" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="72">
       <c r="A72">
         <v>69</v>
       </c>
-      <c r="B72" t="s">
-        <v>87</v>
+      <c r="B72" t="str">
+        <v>23 - Doiwala</v>
       </c>
       <c r="C72">
         <v>61543</v>
@@ -4820,17 +4086,17 @@
         <v>0</v>
       </c>
       <c r="E72">
+        <v>0</v>
+      </c>
+      <c r="F72">
         <v>61543</v>
       </c>
-      <c r="F72">
-        <v>0</v>
-      </c>
       <c r="G72">
+        <v>0</v>
+      </c>
+      <c r="H72">
         <v>61543</v>
       </c>
-      <c r="H72">
-        <v>0</v>
-      </c>
       <c r="I72">
         <v>0</v>
       </c>
@@ -4841,36 +4107,30 @@
         <v>0</v>
       </c>
       <c r="L72">
+        <v>0</v>
+      </c>
+      <c r="M72">
         <v>17245</v>
       </c>
-      <c r="M72">
+      <c r="N72">
         <v>9</v>
       </c>
-      <c r="N72">
+      <c r="O72">
         <v>3667</v>
       </c>
-      <c r="O72">
+      <c r="P72">
         <v>57877</v>
       </c>
-      <c r="P72">
+      <c r="Q72">
         <v>85505</v>
       </c>
-      <c r="Q72">
-        <v>12340</v>
-      </c>
-      <c r="R72">
-        <v>0</v>
-      </c>
-      <c r="S72">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="73" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="73">
       <c r="A73">
         <v>70</v>
       </c>
-      <c r="B73" t="s">
-        <v>88</v>
+      <c r="B73" t="str">
+        <v>24 - Rishikesh</v>
       </c>
       <c r="C73">
         <v>58915</v>
@@ -4879,17 +4139,17 @@
         <v>0</v>
       </c>
       <c r="E73">
+        <v>0</v>
+      </c>
+      <c r="F73">
         <v>58915</v>
       </c>
-      <c r="F73">
-        <v>0</v>
-      </c>
       <c r="G73">
+        <v>0</v>
+      </c>
+      <c r="H73">
         <v>58915</v>
       </c>
-      <c r="H73">
-        <v>0</v>
-      </c>
       <c r="I73">
         <v>0</v>
       </c>
@@ -4900,35 +4160,28 @@
         <v>0</v>
       </c>
       <c r="L73">
+        <v>0</v>
+      </c>
+      <c r="M73">
         <v>15131</v>
       </c>
-      <c r="M73">
+      <c r="N73">
         <v>8</v>
       </c>
-      <c r="N73">
+      <c r="O73">
         <v>3866</v>
       </c>
-      <c r="O73">
+      <c r="P73">
         <v>55049</v>
       </c>
-      <c r="P73">
+      <c r="Q73">
         <v>67666</v>
       </c>
-      <c r="Q73">
-        <v>10010</v>
-      </c>
-      <c r="R73">
-        <v>0</v>
-      </c>
-      <c r="S73">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="74" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A74" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="B74" s="1"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="str">
+        <v>Total</v>
+      </c>
       <c r="C74">
         <v>2430387</v>
       </c>
@@ -4936,17 +4189,17 @@
         <v>0</v>
       </c>
       <c r="E74">
+        <v>9</v>
+      </c>
+      <c r="F74">
         <v>2430387</v>
       </c>
-      <c r="F74">
-        <v>0</v>
-      </c>
       <c r="G74">
+        <v>0</v>
+      </c>
+      <c r="H74">
         <v>2430385</v>
       </c>
-      <c r="H74">
-        <v>0</v>
-      </c>
       <c r="I74">
         <v>0</v>
       </c>
@@ -4957,48 +4210,41 @@
         <v>0</v>
       </c>
       <c r="L74">
+        <v>0</v>
+      </c>
+      <c r="M74">
         <v>625577</v>
       </c>
-      <c r="M74">
+      <c r="N74">
         <v>8318</v>
       </c>
-      <c r="N74">
+      <c r="O74">
         <v>97020</v>
       </c>
-      <c r="O74">
-        <v>2331373</v>
-      </c>
       <c r="P74">
+        <v>2331382</v>
+      </c>
+      <c r="Q74">
         <v>4701905</v>
-      </c>
-      <c r="Q74">
-        <v>626236</v>
-      </c>
-      <c r="R74">
-        <v>1</v>
-      </c>
-      <c r="S74">
-        <v>3445</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="A74:B74"/>
-    <mergeCell ref="Q2:S2"/>
-    <mergeCell ref="A1:Q1"/>
+    <mergeCell ref="A1:R1"/>
     <mergeCell ref="A2:A3"/>
     <mergeCell ref="B2:B3"/>
     <mergeCell ref="C2:C3"/>
     <mergeCell ref="D2:D3"/>
     <mergeCell ref="E2:E3"/>
     <mergeCell ref="F2:F3"/>
-    <mergeCell ref="G2:I2"/>
-    <mergeCell ref="J2:M2"/>
-    <mergeCell ref="N2:P2"/>
+    <mergeCell ref="G2:G3"/>
+    <mergeCell ref="H2:J2"/>
+    <mergeCell ref="K2:N2"/>
+    <mergeCell ref="O2:Q2"/>
+    <mergeCell ref="A74:B74"/>
   </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="A2:P74 B1:P1" numberStoredAsText="1"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:Q74"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/Notice.xlsx
+++ b/Notice.xlsx
@@ -1,41 +1,320 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr codeName="ThisWorkbook"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Downloads\New folder (13)\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FEEA8340-4140-452A-82A3-29B51CAA4DF2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
-  <metadataTypes count="1">
-    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLDAPR" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
-          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <cellMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </cellMetadata>
-</metadata>
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="96">
+  <si>
+    <t>S. No.</t>
+  </si>
+  <si>
+    <t>AC No. - AC Name</t>
+  </si>
+  <si>
+    <t>Notice Generated</t>
+  </si>
+  <si>
+    <t>Pending for Notice Generation</t>
+  </si>
+  <si>
+    <t>Form 7/8 (Shifting)</t>
+  </si>
+  <si>
+    <t>Notice Delivered</t>
+  </si>
+  <si>
+    <t>Notices pending delivery</t>
+  </si>
+  <si>
+    <t>Hearing</t>
+  </si>
+  <si>
+    <t>DEO Status</t>
+  </si>
+  <si>
+    <t>ERO/AERO Status</t>
+  </si>
+  <si>
+    <t>Hearing Held</t>
+  </si>
+  <si>
+    <t>Hearing Date Lapsed</t>
+  </si>
+  <si>
+    <t>Reschedule Date Lapsed</t>
+  </si>
+  <si>
+    <t>Total Pending</t>
+  </si>
+  <si>
+    <t>Pending &gt; 5 days</t>
+  </si>
+  <si>
+    <t>Verified</t>
+  </si>
+  <si>
+    <t>Not Verified</t>
+  </si>
+  <si>
+    <t>Found Ineligible for Final</t>
+  </si>
+  <si>
+    <t>Parked for Final Publication w.r.t. Notices Generated</t>
+  </si>
+  <si>
+    <t>Parked For Final Publication w.r.t. Others</t>
+  </si>
+  <si>
+    <t>25 - Haridwar</t>
+  </si>
+  <si>
+    <t>26 - BHEL Ranipur</t>
+  </si>
+  <si>
+    <t>27 - Jwalapur</t>
+  </si>
+  <si>
+    <t>28 - Bhagwanpur</t>
+  </si>
+  <si>
+    <t>29 - Jhabrera</t>
+  </si>
+  <si>
+    <t>30 - Piran Kaliyar</t>
+  </si>
+  <si>
+    <t>31 - Roorkee</t>
+  </si>
+  <si>
+    <t>32 - Khanpur</t>
+  </si>
+  <si>
+    <t>33 - Manglore</t>
+  </si>
+  <si>
+    <t>34 - Laksar</t>
+  </si>
+  <si>
+    <t>35 - Haridwar Rural</t>
+  </si>
+  <si>
+    <t>56 - Lalkuan</t>
+  </si>
+  <si>
+    <t>57 - Bhimtal</t>
+  </si>
+  <si>
+    <t>58 - Nainital</t>
+  </si>
+  <si>
+    <t>59 - Haldwani</t>
+  </si>
+  <si>
+    <t>60 - Kaladhungi</t>
+  </si>
+  <si>
+    <t>61 - Ramnagar</t>
+  </si>
+  <si>
+    <t>48 - Dwarahat</t>
+  </si>
+  <si>
+    <t>49 - Salt</t>
+  </si>
+  <si>
+    <t>50 - Ranikhet</t>
+  </si>
+  <si>
+    <t>51 - Someshwar</t>
+  </si>
+  <si>
+    <t>52 - Almora</t>
+  </si>
+  <si>
+    <t>53 - Jageshwar</t>
+  </si>
+  <si>
+    <t>62 - Jaspur</t>
+  </si>
+  <si>
+    <t>63 - Kashipur</t>
+  </si>
+  <si>
+    <t>64 - Bajpur</t>
+  </si>
+  <si>
+    <t>65 - Gadarpur</t>
+  </si>
+  <si>
+    <t>66 - Rudrapur</t>
+  </si>
+  <si>
+    <t>67 - Kichha</t>
+  </si>
+  <si>
+    <t>68 - Sitarganj</t>
+  </si>
+  <si>
+    <t>69 - Nanakmatta</t>
+  </si>
+  <si>
+    <t>70 - Khatima</t>
+  </si>
+  <si>
+    <t>42 - Dharchula</t>
+  </si>
+  <si>
+    <t>43 - Didihat</t>
+  </si>
+  <si>
+    <t>44 - Pithoragarh</t>
+  </si>
+  <si>
+    <t>45 - Gangolihat</t>
+  </si>
+  <si>
+    <t>46 - Kapkot</t>
+  </si>
+  <si>
+    <t>47 - Bageshwar</t>
+  </si>
+  <si>
+    <t>54 - Lohaghat</t>
+  </si>
+  <si>
+    <t>55 - Champawat</t>
+  </si>
+  <si>
+    <t>4 - Badrinath</t>
+  </si>
+  <si>
+    <t>5 - Tharali</t>
+  </si>
+  <si>
+    <t>6 - Karanprayag</t>
+  </si>
+  <si>
+    <t>1 - Purola</t>
+  </si>
+  <si>
+    <t>2 - Yamunotri</t>
+  </si>
+  <si>
+    <t>3 - Gangotri</t>
+  </si>
+  <si>
+    <t>7 - Kedarnath</t>
+  </si>
+  <si>
+    <t>8 - Rudraprayag</t>
+  </si>
+  <si>
+    <t>9 - Ghansali</t>
+  </si>
+  <si>
+    <t>10 - Devprayag</t>
+  </si>
+  <si>
+    <t>11 - Narendranagar</t>
+  </si>
+  <si>
+    <t>12 - Pratapnagar</t>
+  </si>
+  <si>
+    <t>13 - Tehri</t>
+  </si>
+  <si>
+    <t>14 - Dhanolti</t>
+  </si>
+  <si>
+    <t>36 - Yamkeshwar</t>
+  </si>
+  <si>
+    <t>37 - Pauri</t>
+  </si>
+  <si>
+    <t>38 - Srinagar</t>
+  </si>
+  <si>
+    <t>39 - Chaubattakhal</t>
+  </si>
+  <si>
+    <t>40 - Lansdowne</t>
+  </si>
+  <si>
+    <t>41 - Kotdwar</t>
+  </si>
+  <si>
+    <t>15 - Chakrata</t>
+  </si>
+  <si>
+    <t>16 - Vikasnagar</t>
+  </si>
+  <si>
+    <t>17 - Sahaspur</t>
+  </si>
+  <si>
+    <t>18 - Dharmpur</t>
+  </si>
+  <si>
+    <t>19 - Raipur</t>
+  </si>
+  <si>
+    <t>20 - Rajpur Road</t>
+  </si>
+  <si>
+    <t>21 - Dehradun Cantonment</t>
+  </si>
+  <si>
+    <t>22 - Mussoorie</t>
+  </si>
+  <si>
+    <t>23 - Doiwala</t>
+  </si>
+  <si>
+    <t>24 - Rishikesh</t>
+  </si>
+  <si>
+    <t>Total</t>
+  </si>
+  <si>
+    <t>DSE with UP</t>
+  </si>
+  <si>
+    <t>Electors having DSE with UP</t>
+  </si>
+  <si>
+    <t>Form 7 Generated</t>
+  </si>
+  <si>
+    <t>No Action Required</t>
+  </si>
+  <si>
+    <t>Notice &amp; Hearing Report 23-09-2026 09:56:43</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="1">
-    <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
-  </numFmts>
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -64,14 +343,24 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+  <cellXfs count="3">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -396,84 +685,130 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Q74"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:T76"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Notice &amp; Hearing Report</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>S. No.</v>
-      </c>
-      <c r="B2" t="str">
-        <v>AC No. - AC Name</v>
-      </c>
-      <c r="C2" t="str">
-        <v>Notice Generated</v>
-      </c>
-      <c r="D2" t="str">
-        <v>Pending for Notice Generation</v>
-      </c>
-      <c r="E2" t="str">
-        <v>Form 7/8 (Shifting)</v>
-      </c>
-      <c r="F2" t="str">
-        <v>Notice Delivered</v>
-      </c>
-      <c r="G2" t="str">
-        <v>Notices pending delivery</v>
-      </c>
-      <c r="H2" t="str">
-        <v>Hearing</v>
-      </c>
-      <c r="K2" t="str">
-        <v>DEO Status</v>
-      </c>
-      <c r="O2" t="str">
-        <v>ERO/AERO Status</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="H3" t="str">
-        <v>Hearing Held</v>
-      </c>
-      <c r="I3" t="str">
-        <v>Hearing Date Lapsed</v>
-      </c>
-      <c r="J3" t="str">
-        <v>Reschedule Date Lapsed</v>
-      </c>
-      <c r="K3" t="str">
-        <v>Total Pending</v>
-      </c>
-      <c r="L3" t="str">
-        <v>Pending &gt; 5 days</v>
-      </c>
-      <c r="M3" t="str">
-        <v>Verified</v>
-      </c>
-      <c r="N3" t="str">
-        <v>Not Verified</v>
-      </c>
-      <c r="O3" t="str">
-        <v>Found Ineligible for Final</v>
-      </c>
-      <c r="P3" t="str">
-        <v>Parked for Final Publication w.r.t. Notices Generated</v>
-      </c>
-      <c r="Q3" t="str">
-        <v>Parked For Final Publication w.r.t. Others</v>
-      </c>
-    </row>
-    <row r="4">
+    <row r="1" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1"/>
+      <c r="I1" s="1"/>
+      <c r="J1" s="1"/>
+      <c r="K1" s="1"/>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1"/>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+    </row>
+    <row r="2" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1"/>
+      <c r="K2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="L2" s="1"/>
+      <c r="M2" s="1"/>
+      <c r="N2" s="1"/>
+      <c r="O2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="P2" s="1"/>
+      <c r="Q2" s="1"/>
+      <c r="R2" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="S2" s="1"/>
+      <c r="T2" s="1"/>
+    </row>
+    <row r="3" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A3" s="1"/>
+      <c r="B3" s="1"/>
+      <c r="C3" s="1"/>
+      <c r="D3" s="1"/>
+      <c r="E3" s="1"/>
+      <c r="F3" s="1"/>
+      <c r="G3" s="1"/>
+      <c r="H3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I3" t="s">
+        <v>11</v>
+      </c>
+      <c r="J3" t="s">
+        <v>12</v>
+      </c>
+      <c r="K3" t="s">
+        <v>13</v>
+      </c>
+      <c r="L3" t="s">
+        <v>14</v>
+      </c>
+      <c r="M3" t="s">
+        <v>15</v>
+      </c>
+      <c r="N3" t="s">
+        <v>16</v>
+      </c>
+      <c r="O3" t="s">
+        <v>17</v>
+      </c>
+      <c r="P3" t="s">
+        <v>18</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>19</v>
+      </c>
+      <c r="R3" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="S3" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="T3" s="2" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="4" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>1</v>
       </c>
-      <c r="B4" t="str">
-        <v>25 - Haridwar</v>
+      <c r="B4" t="s">
+        <v>20</v>
       </c>
       <c r="C4">
         <v>51528</v>
@@ -520,13 +855,22 @@
       <c r="Q4">
         <v>53812</v>
       </c>
-    </row>
-    <row r="5">
+      <c r="R4" s="2">
+        <v>12212</v>
+      </c>
+      <c r="S4" s="2">
+        <v>0</v>
+      </c>
+      <c r="T4" s="2">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="5" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>2</v>
       </c>
-      <c r="B5" t="str">
-        <v>26 - BHEL Ranipur</v>
+      <c r="B5" t="s">
+        <v>21</v>
       </c>
       <c r="C5">
         <v>53911</v>
@@ -573,13 +917,22 @@
       <c r="Q5">
         <v>74848</v>
       </c>
-    </row>
-    <row r="6">
+      <c r="R5" s="2">
+        <v>16108</v>
+      </c>
+      <c r="S5" s="2">
+        <v>0</v>
+      </c>
+      <c r="T5" s="2">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="6" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>3</v>
       </c>
-      <c r="B6" t="str">
-        <v>27 - Jwalapur</v>
+      <c r="B6" t="s">
+        <v>22</v>
       </c>
       <c r="C6">
         <v>39773</v>
@@ -626,13 +979,22 @@
       <c r="Q6">
         <v>71989</v>
       </c>
-    </row>
-    <row r="7">
+      <c r="R6" s="2">
+        <v>17830</v>
+      </c>
+      <c r="S6" s="2">
+        <v>0</v>
+      </c>
+      <c r="T6" s="2">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="7" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>4</v>
       </c>
-      <c r="B7" t="str">
-        <v>28 - Bhagwanpur</v>
+      <c r="B7" t="s">
+        <v>23</v>
       </c>
       <c r="C7">
         <v>39463</v>
@@ -679,13 +1041,22 @@
       <c r="Q7">
         <v>77581</v>
       </c>
-    </row>
-    <row r="8">
+      <c r="R7" s="2">
+        <v>20511</v>
+      </c>
+      <c r="S7" s="2">
+        <v>0</v>
+      </c>
+      <c r="T7" s="2">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>5</v>
       </c>
-      <c r="B8" t="str">
-        <v>29 - Jhabrera</v>
+      <c r="B8" t="s">
+        <v>24</v>
       </c>
       <c r="C8">
         <v>40552</v>
@@ -732,13 +1103,22 @@
       <c r="Q8">
         <v>73458</v>
       </c>
-    </row>
-    <row r="9">
+      <c r="R8" s="2">
+        <v>20788</v>
+      </c>
+      <c r="S8" s="2">
+        <v>0</v>
+      </c>
+      <c r="T8" s="2">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="9" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>6</v>
       </c>
-      <c r="B9" t="str">
-        <v>30 - Piran Kaliyar</v>
+      <c r="B9" t="s">
+        <v>25</v>
       </c>
       <c r="C9">
         <v>43273</v>
@@ -785,13 +1165,22 @@
       <c r="Q9">
         <v>72913</v>
       </c>
-    </row>
-    <row r="10">
+      <c r="R9" s="2">
+        <v>18141</v>
+      </c>
+      <c r="S9" s="2">
+        <v>0</v>
+      </c>
+      <c r="T9" s="2">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="10" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>7</v>
       </c>
-      <c r="B10" t="str">
-        <v>31 - Roorkee</v>
+      <c r="B10" t="s">
+        <v>26</v>
       </c>
       <c r="C10">
         <v>36576</v>
@@ -838,13 +1227,22 @@
       <c r="Q10">
         <v>53124</v>
       </c>
-    </row>
-    <row r="11">
+      <c r="R10" s="2">
+        <v>9498</v>
+      </c>
+      <c r="S10" s="2">
+        <v>0</v>
+      </c>
+      <c r="T10" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>8</v>
       </c>
-      <c r="B11" t="str">
-        <v>32 - Khanpur</v>
+      <c r="B11" t="s">
+        <v>27</v>
       </c>
       <c r="C11">
         <v>50998</v>
@@ -891,13 +1289,22 @@
       <c r="Q11">
         <v>84438</v>
       </c>
-    </row>
-    <row r="12">
+      <c r="R11" s="2">
+        <v>23477</v>
+      </c>
+      <c r="S11" s="2">
+        <v>0</v>
+      </c>
+      <c r="T11" s="2">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="12" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>9</v>
       </c>
-      <c r="B12" t="str">
-        <v>33 - Manglore</v>
+      <c r="B12" t="s">
+        <v>28</v>
       </c>
       <c r="C12">
         <v>40739</v>
@@ -944,13 +1351,22 @@
       <c r="Q12">
         <v>66685</v>
       </c>
-    </row>
-    <row r="13">
+      <c r="R12" s="2">
+        <v>17786</v>
+      </c>
+      <c r="S12" s="2">
+        <v>0</v>
+      </c>
+      <c r="T12" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>10</v>
       </c>
-      <c r="B13" t="str">
-        <v>34 - Laksar</v>
+      <c r="B13" t="s">
+        <v>29</v>
       </c>
       <c r="C13">
         <v>37031</v>
@@ -997,13 +1413,22 @@
       <c r="Q13">
         <v>56564</v>
       </c>
-    </row>
-    <row r="14">
+      <c r="R13" s="2">
+        <v>16237</v>
+      </c>
+      <c r="S13" s="2">
+        <v>0</v>
+      </c>
+      <c r="T13" s="2">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="14" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>11</v>
       </c>
-      <c r="B14" t="str">
-        <v>35 - Haridwar Rural</v>
+      <c r="B14" t="s">
+        <v>30</v>
       </c>
       <c r="C14">
         <v>48966</v>
@@ -1050,13 +1475,22 @@
       <c r="Q14">
         <v>77955</v>
       </c>
-    </row>
-    <row r="15">
+      <c r="R14" s="2">
+        <v>19716</v>
+      </c>
+      <c r="S14" s="2">
+        <v>0</v>
+      </c>
+      <c r="T14" s="2">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="15" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>12</v>
       </c>
-      <c r="B15" t="str">
-        <v>56 - Lalkuan</v>
+      <c r="B15" t="s">
+        <v>31</v>
       </c>
       <c r="C15">
         <v>42703</v>
@@ -1103,13 +1537,22 @@
       <c r="Q15">
         <v>67178</v>
       </c>
-    </row>
-    <row r="16">
+      <c r="R15" s="2">
+        <v>4859</v>
+      </c>
+      <c r="S15" s="2">
+        <v>0</v>
+      </c>
+      <c r="T15" s="2">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="16" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>13</v>
       </c>
-      <c r="B16" t="str">
-        <v>57 - Bhimtal</v>
+      <c r="B16" t="s">
+        <v>32</v>
       </c>
       <c r="C16">
         <v>25549</v>
@@ -1156,13 +1599,22 @@
       <c r="Q16">
         <v>71673</v>
       </c>
-    </row>
-    <row r="17">
+      <c r="R16" s="2">
+        <v>5197</v>
+      </c>
+      <c r="S16" s="2">
+        <v>0</v>
+      </c>
+      <c r="T16" s="2">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="17" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>14</v>
       </c>
-      <c r="B17" t="str">
-        <v>58 - Nainital</v>
+      <c r="B17" t="s">
+        <v>33</v>
       </c>
       <c r="C17">
         <v>27707</v>
@@ -1209,13 +1661,22 @@
       <c r="Q17">
         <v>65457</v>
       </c>
-    </row>
-    <row r="18">
+      <c r="R17" s="2">
+        <v>5417</v>
+      </c>
+      <c r="S17" s="2">
+        <v>0</v>
+      </c>
+      <c r="T17" s="2">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="18" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>15</v>
       </c>
-      <c r="B18" t="str">
-        <v>59 - Haldwani</v>
+      <c r="B18" t="s">
+        <v>34</v>
       </c>
       <c r="C18">
         <v>47836</v>
@@ -1262,13 +1723,22 @@
       <c r="Q18">
         <v>71475</v>
       </c>
-    </row>
-    <row r="19">
+      <c r="R18" s="2">
+        <v>6819</v>
+      </c>
+      <c r="S18" s="2">
+        <v>0</v>
+      </c>
+      <c r="T18" s="2">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="19" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>16</v>
       </c>
-      <c r="B19" t="str">
-        <v>60 - Kaladhungi</v>
+      <c r="B19" t="s">
+        <v>35</v>
       </c>
       <c r="C19">
         <v>56490</v>
@@ -1315,13 +1785,22 @@
       <c r="Q19">
         <v>106392</v>
       </c>
-    </row>
-    <row r="20">
+      <c r="R19" s="2">
+        <v>6135</v>
+      </c>
+      <c r="S19" s="2">
+        <v>0</v>
+      </c>
+      <c r="T19" s="2">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="20" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>17</v>
       </c>
-      <c r="B20" t="str">
-        <v>61 - Ramnagar</v>
+      <c r="B20" t="s">
+        <v>36</v>
       </c>
       <c r="C20">
         <v>35022</v>
@@ -1368,13 +1847,22 @@
       <c r="Q20">
         <v>75812</v>
       </c>
-    </row>
-    <row r="21">
+      <c r="R20" s="2">
+        <v>8984</v>
+      </c>
+      <c r="S20" s="2">
+        <v>0</v>
+      </c>
+      <c r="T20" s="2">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="21" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>18</v>
       </c>
-      <c r="B21" t="str">
-        <v>48 - Dwarahat</v>
+      <c r="B21" t="s">
+        <v>37</v>
       </c>
       <c r="C21">
         <v>16962</v>
@@ -1421,13 +1909,22 @@
       <c r="Q21">
         <v>62460</v>
       </c>
-    </row>
-    <row r="22">
+      <c r="R21" s="2">
+        <v>3868</v>
+      </c>
+      <c r="S21" s="2">
+        <v>0</v>
+      </c>
+      <c r="T21" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>19</v>
       </c>
-      <c r="B22" t="str">
-        <v>49 - Salt</v>
+      <c r="B22" t="s">
+        <v>38</v>
       </c>
       <c r="C22">
         <v>18668</v>
@@ -1474,13 +1971,22 @@
       <c r="Q22">
         <v>64099</v>
       </c>
-    </row>
-    <row r="23">
+      <c r="R22" s="2">
+        <v>4848</v>
+      </c>
+      <c r="S22" s="2">
+        <v>0</v>
+      </c>
+      <c r="T22" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>20</v>
       </c>
-      <c r="B23" t="str">
-        <v>50 - Ranikhet</v>
+      <c r="B23" t="s">
+        <v>39</v>
       </c>
       <c r="C23">
         <v>12020</v>
@@ -1527,13 +2033,22 @@
       <c r="Q23">
         <v>57094</v>
       </c>
-    </row>
-    <row r="24">
+      <c r="R23" s="2">
+        <v>3541</v>
+      </c>
+      <c r="S23" s="2">
+        <v>0</v>
+      </c>
+      <c r="T23" s="2">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="24" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>21</v>
       </c>
-      <c r="B24" t="str">
-        <v>51 - Someshwar</v>
+      <c r="B24" t="s">
+        <v>40</v>
       </c>
       <c r="C24">
         <v>14056</v>
@@ -1580,13 +2095,22 @@
       <c r="Q24">
         <v>65629</v>
       </c>
-    </row>
-    <row r="25">
+      <c r="R24" s="2">
+        <v>3492</v>
+      </c>
+      <c r="S24" s="2">
+        <v>0</v>
+      </c>
+      <c r="T24" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>22</v>
       </c>
-      <c r="B25" t="str">
-        <v>52 - Almora</v>
+      <c r="B25" t="s">
+        <v>41</v>
       </c>
       <c r="C25">
         <v>19266</v>
@@ -1633,13 +2157,22 @@
       <c r="Q25">
         <v>57533</v>
       </c>
-    </row>
-    <row r="26">
+      <c r="R25" s="2">
+        <v>3231</v>
+      </c>
+      <c r="S25" s="2">
+        <v>0</v>
+      </c>
+      <c r="T25" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="26" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>23</v>
       </c>
-      <c r="B26" t="str">
-        <v>53 - Jageshwar</v>
+      <c r="B26" t="s">
+        <v>42</v>
       </c>
       <c r="C26">
         <v>17557</v>
@@ -1686,13 +2219,22 @@
       <c r="Q26">
         <v>66594</v>
       </c>
-    </row>
-    <row r="27">
+      <c r="R26" s="2">
+        <v>3333</v>
+      </c>
+      <c r="S26" s="2">
+        <v>0</v>
+      </c>
+      <c r="T26" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="27" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>24</v>
       </c>
-      <c r="B27" t="str">
-        <v>62 - Jaspur</v>
+      <c r="B27" t="s">
+        <v>43</v>
       </c>
       <c r="C27">
         <v>44276</v>
@@ -1739,13 +2281,22 @@
       <c r="Q27">
         <v>73109</v>
       </c>
-    </row>
-    <row r="28">
+      <c r="R27" s="2">
+        <v>12669</v>
+      </c>
+      <c r="S27" s="2">
+        <v>0</v>
+      </c>
+      <c r="T27" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>25</v>
       </c>
-      <c r="B28" t="str">
-        <v>63 - Kashipur</v>
+      <c r="B28" t="s">
+        <v>44</v>
       </c>
       <c r="C28">
         <v>54349</v>
@@ -1792,13 +2343,22 @@
       <c r="Q28">
         <v>80620</v>
       </c>
-    </row>
-    <row r="29">
+      <c r="R28" s="2">
+        <v>13995</v>
+      </c>
+      <c r="S28" s="2">
+        <v>0</v>
+      </c>
+      <c r="T28" s="2">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="29" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>26</v>
       </c>
-      <c r="B29" t="str">
-        <v>64 - Bajpur</v>
+      <c r="B29" t="s">
+        <v>45</v>
       </c>
       <c r="C29">
         <v>47111</v>
@@ -1845,13 +2405,22 @@
       <c r="Q29">
         <v>83836</v>
       </c>
-    </row>
-    <row r="30">
+      <c r="R29" s="2">
+        <v>14229</v>
+      </c>
+      <c r="S29" s="2">
+        <v>0</v>
+      </c>
+      <c r="T29" s="2">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="30" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>27</v>
       </c>
-      <c r="B30" t="str">
-        <v>65 - Gadarpur</v>
+      <c r="B30" t="s">
+        <v>46</v>
       </c>
       <c r="C30">
         <v>52653</v>
@@ -1898,13 +2467,22 @@
       <c r="Q30">
         <v>86933</v>
       </c>
-    </row>
-    <row r="31">
+      <c r="R30" s="2">
+        <v>12564</v>
+      </c>
+      <c r="S30" s="2">
+        <v>0</v>
+      </c>
+      <c r="T30" s="2">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="31" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>28</v>
       </c>
-      <c r="B31" t="str">
-        <v>66 - Rudrapur</v>
+      <c r="B31" t="s">
+        <v>47</v>
       </c>
       <c r="C31">
         <v>91162</v>
@@ -1951,13 +2529,22 @@
       <c r="Q31">
         <v>81642</v>
       </c>
-    </row>
-    <row r="32">
+      <c r="R31" s="2">
+        <v>14581</v>
+      </c>
+      <c r="S31" s="2">
+        <v>0</v>
+      </c>
+      <c r="T31" s="2">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="32" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>29</v>
       </c>
-      <c r="B32" t="str">
-        <v>67 - Kichha</v>
+      <c r="B32" t="s">
+        <v>48</v>
       </c>
       <c r="C32">
         <v>46728</v>
@@ -2004,13 +2591,22 @@
       <c r="Q32">
         <v>74810</v>
       </c>
-    </row>
-    <row r="33">
+      <c r="R32" s="2">
+        <v>11379</v>
+      </c>
+      <c r="S32" s="2">
+        <v>0</v>
+      </c>
+      <c r="T32" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>30</v>
       </c>
-      <c r="B33" t="str">
-        <v>68 - Sitarganj</v>
+      <c r="B33" t="s">
+        <v>49</v>
       </c>
       <c r="C33">
         <v>40230</v>
@@ -2057,13 +2653,22 @@
       <c r="Q33">
         <v>76969</v>
       </c>
-    </row>
-    <row r="34">
+      <c r="R33" s="2">
+        <v>6678</v>
+      </c>
+      <c r="S33" s="2">
+        <v>0</v>
+      </c>
+      <c r="T33" s="2">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="34" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>31</v>
       </c>
-      <c r="B34" t="str">
-        <v>69 - Nanakmatta</v>
+      <c r="B34" t="s">
+        <v>50</v>
       </c>
       <c r="C34">
         <v>36542</v>
@@ -2110,13 +2715,22 @@
       <c r="Q34">
         <v>74624</v>
       </c>
-    </row>
-    <row r="35">
+      <c r="R34" s="2">
+        <v>7137</v>
+      </c>
+      <c r="S34" s="2">
+        <v>0</v>
+      </c>
+      <c r="T34" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>32</v>
       </c>
-      <c r="B35" t="str">
-        <v>70 - Khatima</v>
+      <c r="B35" t="s">
+        <v>51</v>
       </c>
       <c r="C35">
         <v>33564</v>
@@ -2163,13 +2777,22 @@
       <c r="Q35">
         <v>76464</v>
       </c>
-    </row>
-    <row r="36">
+      <c r="R35" s="2">
+        <v>8879</v>
+      </c>
+      <c r="S35" s="2">
+        <v>0</v>
+      </c>
+      <c r="T35" s="2">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="36" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>33</v>
       </c>
-      <c r="B36" t="str">
-        <v>42 - Dharchula</v>
+      <c r="B36" t="s">
+        <v>52</v>
       </c>
       <c r="C36">
         <v>20905</v>
@@ -2216,13 +2839,22 @@
       <c r="Q36">
         <v>60419</v>
       </c>
-    </row>
-    <row r="37">
+      <c r="R36" s="2">
+        <v>3855</v>
+      </c>
+      <c r="S36" s="2">
+        <v>0</v>
+      </c>
+      <c r="T36" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="37" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>34</v>
       </c>
-      <c r="B37" t="str">
-        <v>43 - Didihat</v>
+      <c r="B37" t="s">
+        <v>53</v>
       </c>
       <c r="C37">
         <v>17692</v>
@@ -2269,13 +2901,22 @@
       <c r="Q37">
         <v>57832</v>
       </c>
-    </row>
-    <row r="38">
+      <c r="R37" s="2">
+        <v>4036</v>
+      </c>
+      <c r="S37" s="2">
+        <v>0</v>
+      </c>
+      <c r="T37" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>35</v>
       </c>
-      <c r="B38" t="str">
-        <v>44 - Pithoragarh</v>
+      <c r="B38" t="s">
+        <v>54</v>
       </c>
       <c r="C38">
         <v>29110</v>
@@ -2322,13 +2963,22 @@
       <c r="Q38">
         <v>63038</v>
       </c>
-    </row>
-    <row r="39">
+      <c r="R38" s="2">
+        <v>5135</v>
+      </c>
+      <c r="S38" s="2">
+        <v>0</v>
+      </c>
+      <c r="T38" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>36</v>
       </c>
-      <c r="B39" t="str">
-        <v>45 - Gangolihat</v>
+      <c r="B39" t="s">
+        <v>55</v>
       </c>
       <c r="C39">
         <v>21367</v>
@@ -2375,13 +3025,22 @@
       <c r="Q39">
         <v>71133</v>
       </c>
-    </row>
-    <row r="40">
+      <c r="R39" s="2">
+        <v>5903</v>
+      </c>
+      <c r="S39" s="2">
+        <v>0</v>
+      </c>
+      <c r="T39" s="2">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="40" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>37</v>
       </c>
-      <c r="B40" t="str">
-        <v>46 - Kapkot</v>
+      <c r="B40" t="s">
+        <v>56</v>
       </c>
       <c r="C40">
         <v>18905</v>
@@ -2428,13 +3087,22 @@
       <c r="Q40">
         <v>73242</v>
       </c>
-    </row>
-    <row r="41">
+      <c r="R40" s="2">
+        <v>3824</v>
+      </c>
+      <c r="S40" s="2">
+        <v>0</v>
+      </c>
+      <c r="T40" s="2">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="41" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>38</v>
       </c>
-      <c r="B41" t="str">
-        <v>47 - Bageshwar</v>
+      <c r="B41" t="s">
+        <v>57</v>
       </c>
       <c r="C41">
         <v>23521</v>
@@ -2481,13 +3149,22 @@
       <c r="Q41">
         <v>85251</v>
       </c>
-    </row>
-    <row r="42">
+      <c r="R41" s="2">
+        <v>6015</v>
+      </c>
+      <c r="S41" s="2">
+        <v>0</v>
+      </c>
+      <c r="T41" s="2">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="42" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>39</v>
       </c>
-      <c r="B42" t="str">
-        <v>54 - Lohaghat</v>
+      <c r="B42" t="s">
+        <v>58</v>
       </c>
       <c r="C42">
         <v>27565</v>
@@ -2534,13 +3211,22 @@
       <c r="Q42">
         <v>68615</v>
       </c>
-    </row>
-    <row r="43">
+      <c r="R42" s="2">
+        <v>4708</v>
+      </c>
+      <c r="S42" s="2">
+        <v>0</v>
+      </c>
+      <c r="T42" s="2">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="43" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>40</v>
       </c>
-      <c r="B43" t="str">
-        <v>55 - Champawat</v>
+      <c r="B43" t="s">
+        <v>59</v>
       </c>
       <c r="C43">
         <v>29700</v>
@@ -2587,13 +3273,22 @@
       <c r="Q43">
         <v>63012</v>
       </c>
-    </row>
-    <row r="44">
+      <c r="R43" s="2">
+        <v>5219</v>
+      </c>
+      <c r="S43" s="2">
+        <v>0</v>
+      </c>
+      <c r="T43" s="2">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="44" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A44">
         <v>41</v>
       </c>
-      <c r="B44" t="str">
-        <v>4 - Badrinath</v>
+      <c r="B44" t="s">
+        <v>60</v>
       </c>
       <c r="C44">
         <v>21900</v>
@@ -2640,13 +3335,22 @@
       <c r="Q44">
         <v>68393</v>
       </c>
-    </row>
-    <row r="45">
+      <c r="R44" s="2">
+        <v>7659</v>
+      </c>
+      <c r="S44" s="2">
+        <v>0</v>
+      </c>
+      <c r="T44" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="45" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A45">
         <v>42</v>
       </c>
-      <c r="B45" t="str">
-        <v>5 - Tharali</v>
+      <c r="B45" t="s">
+        <v>61</v>
       </c>
       <c r="C45">
         <v>19935</v>
@@ -2693,13 +3397,22 @@
       <c r="Q45">
         <v>76287</v>
       </c>
-    </row>
-    <row r="46">
+      <c r="R45" s="2">
+        <v>6998</v>
+      </c>
+      <c r="S45" s="2">
+        <v>0</v>
+      </c>
+      <c r="T45" s="2">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="46" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A46">
         <v>43</v>
       </c>
-      <c r="B46" t="str">
-        <v>6 - Karanprayag</v>
+      <c r="B46" t="s">
+        <v>62</v>
       </c>
       <c r="C46">
         <v>21512</v>
@@ -2746,13 +3459,22 @@
       <c r="Q46">
         <v>64160</v>
       </c>
-    </row>
-    <row r="47">
+      <c r="R46" s="2">
+        <v>7548</v>
+      </c>
+      <c r="S46" s="2">
+        <v>0</v>
+      </c>
+      <c r="T46" s="2">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="47" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A47">
         <v>44</v>
       </c>
-      <c r="B47" t="str">
-        <v>1 - Purola</v>
+      <c r="B47" t="s">
+        <v>63</v>
       </c>
       <c r="C47">
         <v>22426</v>
@@ -2799,13 +3521,22 @@
       <c r="Q47">
         <v>49875</v>
       </c>
-    </row>
-    <row r="48">
+      <c r="R47" s="2">
+        <v>5046</v>
+      </c>
+      <c r="S47" s="2">
+        <v>0</v>
+      </c>
+      <c r="T47" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A48">
         <v>45</v>
       </c>
-      <c r="B48" t="str">
-        <v>2 - Yamunotri</v>
+      <c r="B48" t="s">
+        <v>64</v>
       </c>
       <c r="C48">
         <v>19641</v>
@@ -2852,13 +3583,22 @@
       <c r="Q48">
         <v>54142</v>
       </c>
-    </row>
-    <row r="49">
+      <c r="R48" s="2">
+        <v>4623</v>
+      </c>
+      <c r="S48" s="2">
+        <v>0</v>
+      </c>
+      <c r="T48" s="2">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="49" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A49">
         <v>46</v>
       </c>
-      <c r="B49" t="str">
-        <v>3 - Gangotri</v>
+      <c r="B49" t="s">
+        <v>65</v>
       </c>
       <c r="C49">
         <v>21651</v>
@@ -2905,13 +3645,22 @@
       <c r="Q49">
         <v>55376</v>
       </c>
-    </row>
-    <row r="50">
+      <c r="R49" s="2">
+        <v>5057</v>
+      </c>
+      <c r="S49" s="2">
+        <v>0</v>
+      </c>
+      <c r="T49" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="50" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A50">
         <v>47</v>
       </c>
-      <c r="B50" t="str">
-        <v>7 - Kedarnath</v>
+      <c r="B50" t="s">
+        <v>66</v>
       </c>
       <c r="C50">
         <v>21936</v>
@@ -2958,13 +3707,22 @@
       <c r="Q50">
         <v>63298</v>
       </c>
-    </row>
-    <row r="51">
+      <c r="R50" s="2">
+        <v>7292</v>
+      </c>
+      <c r="S50" s="2">
+        <v>0</v>
+      </c>
+      <c r="T50" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A51">
         <v>48</v>
       </c>
-      <c r="B51" t="str">
-        <v>8 - Rudraprayag</v>
+      <c r="B51" t="s">
+        <v>67</v>
       </c>
       <c r="C51">
         <v>23798</v>
@@ -3011,13 +3769,22 @@
       <c r="Q51">
         <v>71754</v>
       </c>
-    </row>
-    <row r="52">
+      <c r="R51" s="2">
+        <v>7715</v>
+      </c>
+      <c r="S51" s="2">
+        <v>0</v>
+      </c>
+      <c r="T51" s="2">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="52" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A52">
         <v>49</v>
       </c>
-      <c r="B52" t="str">
-        <v>9 - Ghansali</v>
+      <c r="B52" t="s">
+        <v>68</v>
       </c>
       <c r="C52">
         <v>21094</v>
@@ -3064,13 +3831,22 @@
       <c r="Q52">
         <v>63987</v>
       </c>
-    </row>
-    <row r="53">
+      <c r="R52" s="2">
+        <v>5655</v>
+      </c>
+      <c r="S52" s="2">
+        <v>0</v>
+      </c>
+      <c r="T52" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="53" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A53">
         <v>50</v>
       </c>
-      <c r="B53" t="str">
-        <v>10 - Devprayag</v>
+      <c r="B53" t="s">
+        <v>69</v>
       </c>
       <c r="C53">
         <v>19131</v>
@@ -3117,13 +3893,22 @@
       <c r="Q53">
         <v>56306</v>
       </c>
-    </row>
-    <row r="54">
+      <c r="R53" s="2">
+        <v>6551</v>
+      </c>
+      <c r="S53" s="2">
+        <v>0</v>
+      </c>
+      <c r="T53" s="2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="54" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A54">
         <v>51</v>
       </c>
-      <c r="B54" t="str">
-        <v>11 - Narendranagar</v>
+      <c r="B54" t="s">
+        <v>70</v>
       </c>
       <c r="C54">
         <v>20758</v>
@@ -3170,13 +3955,22 @@
       <c r="Q54">
         <v>58440</v>
       </c>
-    </row>
-    <row r="55">
+      <c r="R54" s="2">
+        <v>7347</v>
+      </c>
+      <c r="S54" s="2">
+        <v>0</v>
+      </c>
+      <c r="T54" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A55">
         <v>52</v>
       </c>
-      <c r="B55" t="str">
-        <v>12 - Pratapnagar</v>
+      <c r="B55" t="s">
+        <v>71</v>
       </c>
       <c r="C55">
         <v>16022</v>
@@ -3223,13 +4017,22 @@
       <c r="Q55">
         <v>58215</v>
       </c>
-    </row>
-    <row r="56">
+      <c r="R55" s="2">
+        <v>5098</v>
+      </c>
+      <c r="S55" s="2">
+        <v>0</v>
+      </c>
+      <c r="T55" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A56">
         <v>53</v>
       </c>
-      <c r="B56" t="str">
-        <v>13 - Tehri</v>
+      <c r="B56" t="s">
+        <v>72</v>
       </c>
       <c r="C56">
         <v>19256</v>
@@ -3276,13 +4079,22 @@
       <c r="Q56">
         <v>47621</v>
       </c>
-    </row>
-    <row r="57">
+      <c r="R56" s="2">
+        <v>4882</v>
+      </c>
+      <c r="S56" s="2">
+        <v>0</v>
+      </c>
+      <c r="T56" s="2">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="57" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A57">
         <v>54</v>
       </c>
-      <c r="B57" t="str">
-        <v>14 - Dhanolti</v>
+      <c r="B57" t="s">
+        <v>73</v>
       </c>
       <c r="C57">
         <v>21240</v>
@@ -3329,13 +4141,22 @@
       <c r="Q57">
         <v>61556</v>
       </c>
-    </row>
-    <row r="58">
+      <c r="R57" s="2">
+        <v>6870</v>
+      </c>
+      <c r="S57" s="2">
+        <v>0</v>
+      </c>
+      <c r="T57" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A58">
         <v>55</v>
       </c>
-      <c r="B58" t="str">
-        <v>36 - Yamkeshwar</v>
+      <c r="B58" t="s">
+        <v>74</v>
       </c>
       <c r="C58">
         <v>22819</v>
@@ -3382,13 +4203,22 @@
       <c r="Q58">
         <v>57577</v>
       </c>
-    </row>
-    <row r="59">
+      <c r="R58" s="2">
+        <v>8884</v>
+      </c>
+      <c r="S58" s="2">
+        <v>0</v>
+      </c>
+      <c r="T58" s="2">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="59" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A59">
         <v>56</v>
       </c>
-      <c r="B59" t="str">
-        <v>37 - Pauri</v>
+      <c r="B59" t="s">
+        <v>75</v>
       </c>
       <c r="C59">
         <v>18776</v>
@@ -3435,13 +4265,22 @@
       <c r="Q59">
         <v>60495</v>
       </c>
-    </row>
-    <row r="60">
+      <c r="R59" s="2">
+        <v>8028</v>
+      </c>
+      <c r="S59" s="2">
+        <v>0</v>
+      </c>
+      <c r="T59" s="2">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="60" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A60">
         <v>57</v>
       </c>
-      <c r="B60" t="str">
-        <v>38 - Srinagar</v>
+      <c r="B60" t="s">
+        <v>76</v>
       </c>
       <c r="C60">
         <v>23749</v>
@@ -3488,13 +4327,22 @@
       <c r="Q60">
         <v>70140</v>
       </c>
-    </row>
-    <row r="61">
+      <c r="R60" s="2">
+        <v>7415</v>
+      </c>
+      <c r="S60" s="2">
+        <v>0</v>
+      </c>
+      <c r="T60" s="2">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="61" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A61">
         <v>58</v>
       </c>
-      <c r="B61" t="str">
-        <v>39 - Chaubattakhal</v>
+      <c r="B61" t="s">
+        <v>77</v>
       </c>
       <c r="C61">
         <v>22069</v>
@@ -3541,13 +4389,22 @@
       <c r="Q61">
         <v>55240</v>
       </c>
-    </row>
-    <row r="62">
+      <c r="R61" s="2">
+        <v>7927</v>
+      </c>
+      <c r="S61" s="2">
+        <v>1</v>
+      </c>
+      <c r="T61" s="2">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="62" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A62">
         <v>59</v>
       </c>
-      <c r="B62" t="str">
-        <v>40 - Lansdowne</v>
+      <c r="B62" t="s">
+        <v>78</v>
       </c>
       <c r="C62">
         <v>15800</v>
@@ -3594,13 +4451,22 @@
       <c r="Q62">
         <v>51334</v>
       </c>
-    </row>
-    <row r="63">
+      <c r="R62" s="2">
+        <v>6917</v>
+      </c>
+      <c r="S62" s="2">
+        <v>0</v>
+      </c>
+      <c r="T62" s="2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="63" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A63">
         <v>60</v>
       </c>
-      <c r="B63" t="str">
-        <v>41 - Kotdwar</v>
+      <c r="B63" t="s">
+        <v>79</v>
       </c>
       <c r="C63">
         <v>36754</v>
@@ -3647,13 +4513,22 @@
       <c r="Q63">
         <v>68696</v>
       </c>
-    </row>
-    <row r="64">
+      <c r="R63" s="2">
+        <v>9766</v>
+      </c>
+      <c r="S63" s="2">
+        <v>0</v>
+      </c>
+      <c r="T63" s="2">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="64" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A64">
         <v>61</v>
       </c>
-      <c r="B64" t="str">
-        <v>15 - Chakrata</v>
+      <c r="B64" t="s">
+        <v>80</v>
       </c>
       <c r="C64">
         <v>42048</v>
@@ -3700,13 +4575,22 @@
       <c r="Q64">
         <v>60527</v>
       </c>
-    </row>
-    <row r="65">
+      <c r="R64" s="2">
+        <v>5985</v>
+      </c>
+      <c r="S64" s="2">
+        <v>0</v>
+      </c>
+      <c r="T64" s="2">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="65" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A65">
         <v>62</v>
       </c>
-      <c r="B65" t="str">
-        <v>16 - Vikasnagar</v>
+      <c r="B65" t="s">
+        <v>81</v>
       </c>
       <c r="C65">
         <v>41389</v>
@@ -3753,13 +4637,22 @@
       <c r="Q65">
         <v>58527</v>
       </c>
-    </row>
-    <row r="66">
+      <c r="R65" s="2">
+        <v>13282</v>
+      </c>
+      <c r="S65" s="2">
+        <v>0</v>
+      </c>
+      <c r="T65" s="2">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="66" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A66">
         <v>63</v>
       </c>
-      <c r="B66" t="str">
-        <v>17 - Sahaspur</v>
+      <c r="B66" t="s">
+        <v>82</v>
       </c>
       <c r="C66">
         <v>67362</v>
@@ -3806,13 +4699,22 @@
       <c r="Q66">
         <v>93810</v>
       </c>
-    </row>
-    <row r="67">
+      <c r="R66" s="2">
+        <v>17742</v>
+      </c>
+      <c r="S66" s="2">
+        <v>0</v>
+      </c>
+      <c r="T66" s="2">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="67" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A67">
         <v>64</v>
       </c>
-      <c r="B67" t="str">
-        <v>18 - Dharmpur</v>
+      <c r="B67" t="s">
+        <v>83</v>
       </c>
       <c r="C67">
         <v>68828</v>
@@ -3859,13 +4761,22 @@
       <c r="Q67">
         <v>78032</v>
       </c>
-    </row>
-    <row r="68">
+      <c r="R67" s="2">
+        <v>9807</v>
+      </c>
+      <c r="S67" s="2">
+        <v>0</v>
+      </c>
+      <c r="T67" s="2">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="68" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A68">
         <v>65</v>
       </c>
-      <c r="B68" t="str">
-        <v>19 - Raipur</v>
+      <c r="B68" t="s">
+        <v>84</v>
       </c>
       <c r="C68">
         <v>65397</v>
@@ -3912,13 +4823,22 @@
       <c r="Q68">
         <v>71325</v>
       </c>
-    </row>
-    <row r="69">
+      <c r="R68" s="2">
+        <v>7850</v>
+      </c>
+      <c r="S68" s="2">
+        <v>0</v>
+      </c>
+      <c r="T68" s="2">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="69" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A69">
         <v>66</v>
       </c>
-      <c r="B69" t="str">
-        <v>20 - Rajpur Road</v>
+      <c r="B69" t="s">
+        <v>85</v>
       </c>
       <c r="C69">
         <v>43938</v>
@@ -3965,13 +4885,22 @@
       <c r="Q69">
         <v>36118</v>
       </c>
-    </row>
-    <row r="70">
+      <c r="R69" s="2">
+        <v>6528</v>
+      </c>
+      <c r="S69" s="2">
+        <v>0</v>
+      </c>
+      <c r="T69" s="2">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="70" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A70">
         <v>67</v>
       </c>
-      <c r="B70" t="str">
-        <v>21 - Dehradun Cantonment</v>
+      <c r="B70" t="s">
+        <v>86</v>
       </c>
       <c r="C70">
         <v>47711</v>
@@ -4018,13 +4947,22 @@
       <c r="Q70">
         <v>42051</v>
       </c>
-    </row>
-    <row r="71">
+      <c r="R70" s="2">
+        <v>5798</v>
+      </c>
+      <c r="S70" s="2">
+        <v>0</v>
+      </c>
+      <c r="T70" s="2">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="71" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A71">
         <v>68</v>
       </c>
-      <c r="B71" t="str">
-        <v>22 - Mussoorie</v>
+      <c r="B71" t="s">
+        <v>87</v>
       </c>
       <c r="C71">
         <v>50963</v>
@@ -4071,13 +5009,22 @@
       <c r="Q71">
         <v>49140</v>
       </c>
-    </row>
-    <row r="72">
+      <c r="R71" s="2">
+        <v>6782</v>
+      </c>
+      <c r="S71" s="2">
+        <v>0</v>
+      </c>
+      <c r="T71" s="2">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="72" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A72">
         <v>69</v>
       </c>
-      <c r="B72" t="str">
-        <v>23 - Doiwala</v>
+      <c r="B72" t="s">
+        <v>88</v>
       </c>
       <c r="C72">
         <v>61543</v>
@@ -4124,13 +5071,22 @@
       <c r="Q72">
         <v>85505</v>
       </c>
-    </row>
-    <row r="73">
+      <c r="R72" s="2">
+        <v>12340</v>
+      </c>
+      <c r="S72" s="2">
+        <v>0</v>
+      </c>
+      <c r="T72" s="2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="73" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A73">
         <v>70</v>
       </c>
-      <c r="B73" t="str">
-        <v>24 - Rishikesh</v>
+      <c r="B73" t="s">
+        <v>89</v>
       </c>
       <c r="C73">
         <v>58915</v>
@@ -4177,11 +5133,21 @@
       <c r="Q73">
         <v>67666</v>
       </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="str">
-        <v>Total</v>
-      </c>
+      <c r="R73" s="2">
+        <v>10010</v>
+      </c>
+      <c r="S73" s="2">
+        <v>0</v>
+      </c>
+      <c r="T73" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="74" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A74" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="B74" s="1"/>
       <c r="C74">
         <v>2430387</v>
       </c>
@@ -4227,9 +5193,22 @@
       <c r="Q74">
         <v>4701905</v>
       </c>
-    </row>
+      <c r="R74" s="2">
+        <v>626236</v>
+      </c>
+      <c r="S74" s="2">
+        <v>1</v>
+      </c>
+      <c r="T74" s="2">
+        <v>3445</v>
+      </c>
+    </row>
+    <row r="75" spans="1:20" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="76" spans="1:20" ht="15.75" x14ac:dyDescent="0.25"/>
   </sheetData>
-  <mergeCells count="12">
+  <mergeCells count="13">
+    <mergeCell ref="A74:B74"/>
+    <mergeCell ref="R2:T2"/>
     <mergeCell ref="A1:R1"/>
     <mergeCell ref="A2:A3"/>
     <mergeCell ref="B2:B3"/>
@@ -4241,10 +5220,10 @@
     <mergeCell ref="H2:J2"/>
     <mergeCell ref="K2:N2"/>
     <mergeCell ref="O2:Q2"/>
-    <mergeCell ref="A74:B74"/>
   </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:Q74"/>
+    <ignoredError sqref="A2:Q74 B1:Q1" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/Notice.xlsx
+++ b/Notice.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Downloads\New folder (13)\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FEEA8340-4140-452A-82A3-29B51CAA4DF2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1BF1B861-80EF-4E49-88C4-BD7C76C0A793}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="95">
   <si>
     <t>S. No.</t>
   </si>
@@ -32,9 +32,6 @@
   </si>
   <si>
     <t>Pending for Notice Generation</t>
-  </si>
-  <si>
-    <t>Form 7/8 (Shifting)</t>
   </si>
   <si>
     <t>Notice Delivered</t>
@@ -343,10 +340,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -686,12 +689,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:T76"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:S74"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -709,106 +712,101 @@
       <c r="O1" s="1"/>
       <c r="P1" s="1"/>
       <c r="Q1" s="1"/>
-      <c r="R1" s="1"/>
-    </row>
-    <row r="2" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="1" t="s">
+    </row>
+    <row r="2" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A2" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="D2" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="E2" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="F2" s="4" t="s">
         <v>5</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I2" s="1"/>
-      <c r="J2" s="1"/>
-      <c r="K2" s="1" t="s">
-        <v>8</v>
-      </c>
+      <c r="K2" s="1"/>
       <c r="L2" s="1"/>
       <c r="M2" s="1"/>
-      <c r="N2" s="1"/>
-      <c r="O2" s="1" t="s">
+      <c r="N2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="O2" s="1"/>
+      <c r="P2" s="1"/>
+      <c r="Q2" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="R2" s="1"/>
+      <c r="S2" s="1"/>
+    </row>
+    <row r="3" spans="1:19" s="3" customFormat="1" ht="110.25" x14ac:dyDescent="0.25">
+      <c r="A3" s="4"/>
+      <c r="B3" s="4"/>
+      <c r="C3" s="4"/>
+      <c r="D3" s="4"/>
+      <c r="E3" s="4"/>
+      <c r="F3" s="4"/>
+      <c r="G3" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="P2" s="1"/>
-      <c r="Q2" s="1"/>
-      <c r="R2" s="1" t="s">
+      <c r="H3" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I3" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="J3" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="K3" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="L3" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="M3" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="N3" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="O3" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="P3" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="Q3" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="S2" s="1"/>
-      <c r="T2" s="1"/>
-    </row>
-    <row r="3" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A3" s="1"/>
-      <c r="B3" s="1"/>
-      <c r="C3" s="1"/>
-      <c r="D3" s="1"/>
-      <c r="E3" s="1"/>
-      <c r="F3" s="1"/>
-      <c r="G3" s="1"/>
-      <c r="H3" t="s">
-        <v>10</v>
-      </c>
-      <c r="I3" t="s">
-        <v>11</v>
-      </c>
-      <c r="J3" t="s">
-        <v>12</v>
-      </c>
-      <c r="K3" t="s">
-        <v>13</v>
-      </c>
-      <c r="L3" t="s">
-        <v>14</v>
-      </c>
-      <c r="M3" t="s">
-        <v>15</v>
-      </c>
-      <c r="N3" t="s">
-        <v>16</v>
-      </c>
-      <c r="O3" t="s">
-        <v>17</v>
-      </c>
-      <c r="P3" t="s">
-        <v>18</v>
-      </c>
-      <c r="Q3" t="s">
-        <v>19</v>
-      </c>
-      <c r="R3" s="2" t="s">
+      <c r="R3" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="S3" s="2" t="s">
+      <c r="S3" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="T3" s="2" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="4" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="4" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>1</v>
       </c>
       <c r="B4" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C4">
         <v>51528</v>
@@ -817,16 +815,16 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>2</v>
+        <v>51528</v>
       </c>
       <c r="F4">
+        <v>0</v>
+      </c>
+      <c r="G4">
         <v>51528</v>
       </c>
-      <c r="G4">
-        <v>0</v>
-      </c>
       <c r="H4">
-        <v>51528</v>
+        <v>0</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -838,39 +836,36 @@
         <v>0</v>
       </c>
       <c r="L4">
-        <v>0</v>
+        <v>17975</v>
       </c>
       <c r="M4">
-        <v>17975</v>
+        <v>967</v>
       </c>
       <c r="N4">
-        <v>967</v>
+        <v>869</v>
       </c>
       <c r="O4">
-        <v>869</v>
+        <v>50659</v>
       </c>
       <c r="P4">
-        <v>50659</v>
-      </c>
-      <c r="Q4">
         <v>53812</v>
       </c>
+      <c r="Q4" s="2">
+        <v>12212</v>
+      </c>
       <c r="R4" s="2">
-        <v>12212</v>
+        <v>0</v>
       </c>
       <c r="S4" s="2">
-        <v>0</v>
-      </c>
-      <c r="T4" s="2">
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>2</v>
       </c>
       <c r="B5" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C5">
         <v>53911</v>
@@ -879,16 +874,16 @@
         <v>0</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>53911</v>
       </c>
       <c r="F5">
+        <v>0</v>
+      </c>
+      <c r="G5">
         <v>53911</v>
       </c>
-      <c r="G5">
-        <v>0</v>
-      </c>
       <c r="H5">
-        <v>53911</v>
+        <v>0</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -900,39 +895,36 @@
         <v>0</v>
       </c>
       <c r="L5">
-        <v>0</v>
+        <v>11415</v>
       </c>
       <c r="M5">
-        <v>11415</v>
+        <v>757</v>
       </c>
       <c r="N5">
-        <v>757</v>
+        <v>877</v>
       </c>
       <c r="O5">
-        <v>877</v>
+        <v>53035</v>
       </c>
       <c r="P5">
-        <v>53035</v>
-      </c>
-      <c r="Q5">
         <v>74848</v>
       </c>
+      <c r="Q5" s="2">
+        <v>16108</v>
+      </c>
       <c r="R5" s="2">
-        <v>16108</v>
+        <v>0</v>
       </c>
       <c r="S5" s="2">
-        <v>0</v>
-      </c>
-      <c r="T5" s="2">
         <v>30</v>
       </c>
     </row>
-    <row r="6" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>3</v>
       </c>
       <c r="B6" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C6">
         <v>39773</v>
@@ -941,16 +933,16 @@
         <v>0</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>39773</v>
       </c>
       <c r="F6">
+        <v>0</v>
+      </c>
+      <c r="G6">
         <v>39773</v>
       </c>
-      <c r="G6">
-        <v>0</v>
-      </c>
       <c r="H6">
-        <v>39773</v>
+        <v>0</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -962,39 +954,36 @@
         <v>0</v>
       </c>
       <c r="L6">
-        <v>0</v>
+        <v>6075</v>
       </c>
       <c r="M6">
-        <v>6075</v>
+        <v>201</v>
       </c>
       <c r="N6">
-        <v>201</v>
+        <v>1863</v>
       </c>
       <c r="O6">
-        <v>1863</v>
+        <v>37869</v>
       </c>
       <c r="P6">
-        <v>37869</v>
-      </c>
-      <c r="Q6">
         <v>71989</v>
       </c>
+      <c r="Q6" s="2">
+        <v>17830</v>
+      </c>
       <c r="R6" s="2">
-        <v>17830</v>
+        <v>0</v>
       </c>
       <c r="S6" s="2">
-        <v>0</v>
-      </c>
-      <c r="T6" s="2">
         <v>54</v>
       </c>
     </row>
-    <row r="7" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>4</v>
       </c>
       <c r="B7" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C7">
         <v>39463</v>
@@ -1003,16 +992,16 @@
         <v>0</v>
       </c>
       <c r="E7">
-        <v>0</v>
+        <v>39463</v>
       </c>
       <c r="F7">
+        <v>0</v>
+      </c>
+      <c r="G7">
         <v>39463</v>
       </c>
-      <c r="G7">
-        <v>0</v>
-      </c>
       <c r="H7">
-        <v>39463</v>
+        <v>0</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -1024,39 +1013,36 @@
         <v>0</v>
       </c>
       <c r="L7">
-        <v>0</v>
+        <v>5683</v>
       </c>
       <c r="M7">
-        <v>5683</v>
+        <v>257</v>
       </c>
       <c r="N7">
-        <v>257</v>
+        <v>1995</v>
       </c>
       <c r="O7">
-        <v>1995</v>
+        <v>37266</v>
       </c>
       <c r="P7">
-        <v>37266</v>
-      </c>
-      <c r="Q7">
         <v>77581</v>
       </c>
+      <c r="Q7" s="2">
+        <v>20511</v>
+      </c>
       <c r="R7" s="2">
-        <v>20511</v>
+        <v>0</v>
       </c>
       <c r="S7" s="2">
-        <v>0</v>
-      </c>
-      <c r="T7" s="2">
         <v>8</v>
       </c>
     </row>
-    <row r="8" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>5</v>
       </c>
       <c r="B8" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C8">
         <v>40552</v>
@@ -1065,16 +1051,16 @@
         <v>0</v>
       </c>
       <c r="E8">
-        <v>5</v>
+        <v>40552</v>
       </c>
       <c r="F8">
+        <v>0</v>
+      </c>
+      <c r="G8">
         <v>40552</v>
       </c>
-      <c r="G8">
-        <v>0</v>
-      </c>
       <c r="H8">
-        <v>40552</v>
+        <v>0</v>
       </c>
       <c r="I8">
         <v>0</v>
@@ -1086,39 +1072,36 @@
         <v>0</v>
       </c>
       <c r="L8">
-        <v>0</v>
+        <v>14288</v>
       </c>
       <c r="M8">
-        <v>14288</v>
+        <v>164</v>
       </c>
       <c r="N8">
-        <v>164</v>
+        <v>1874</v>
       </c>
       <c r="O8">
-        <v>1874</v>
+        <v>38055</v>
       </c>
       <c r="P8">
-        <v>38055</v>
-      </c>
-      <c r="Q8">
         <v>73458</v>
       </c>
+      <c r="Q8" s="2">
+        <v>20788</v>
+      </c>
       <c r="R8" s="2">
-        <v>20788</v>
+        <v>0</v>
       </c>
       <c r="S8" s="2">
-        <v>0</v>
-      </c>
-      <c r="T8" s="2">
         <v>110</v>
       </c>
     </row>
-    <row r="9" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>6</v>
       </c>
       <c r="B9" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C9">
         <v>43273</v>
@@ -1127,16 +1110,16 @@
         <v>0</v>
       </c>
       <c r="E9">
-        <v>0</v>
+        <v>43273</v>
       </c>
       <c r="F9">
+        <v>0</v>
+      </c>
+      <c r="G9">
         <v>43273</v>
       </c>
-      <c r="G9">
-        <v>0</v>
-      </c>
       <c r="H9">
-        <v>43273</v>
+        <v>0</v>
       </c>
       <c r="I9">
         <v>0</v>
@@ -1148,39 +1131,36 @@
         <v>0</v>
       </c>
       <c r="L9">
-        <v>0</v>
+        <v>7759</v>
       </c>
       <c r="M9">
-        <v>7759</v>
+        <v>49</v>
       </c>
       <c r="N9">
-        <v>49</v>
+        <v>1350</v>
       </c>
       <c r="O9">
-        <v>1350</v>
+        <v>41924</v>
       </c>
       <c r="P9">
-        <v>41924</v>
-      </c>
-      <c r="Q9">
         <v>72913</v>
       </c>
+      <c r="Q9" s="2">
+        <v>18141</v>
+      </c>
       <c r="R9" s="2">
-        <v>18141</v>
+        <v>0</v>
       </c>
       <c r="S9" s="2">
-        <v>0</v>
-      </c>
-      <c r="T9" s="2">
         <v>110</v>
       </c>
     </row>
-    <row r="10" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>7</v>
       </c>
       <c r="B10" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C10">
         <v>36576</v>
@@ -1189,16 +1169,16 @@
         <v>0</v>
       </c>
       <c r="E10">
-        <v>0</v>
+        <v>36576</v>
       </c>
       <c r="F10">
+        <v>0</v>
+      </c>
+      <c r="G10">
         <v>36576</v>
       </c>
-      <c r="G10">
-        <v>0</v>
-      </c>
       <c r="H10">
-        <v>36576</v>
+        <v>0</v>
       </c>
       <c r="I10">
         <v>0</v>
@@ -1210,39 +1190,36 @@
         <v>0</v>
       </c>
       <c r="L10">
-        <v>0</v>
+        <v>10960</v>
       </c>
       <c r="M10">
-        <v>10960</v>
+        <v>172</v>
       </c>
       <c r="N10">
-        <v>172</v>
+        <v>815</v>
       </c>
       <c r="O10">
-        <v>815</v>
+        <v>35761</v>
       </c>
       <c r="P10">
-        <v>35761</v>
-      </c>
-      <c r="Q10">
         <v>53124</v>
       </c>
+      <c r="Q10" s="2">
+        <v>9498</v>
+      </c>
       <c r="R10" s="2">
-        <v>9498</v>
+        <v>0</v>
       </c>
       <c r="S10" s="2">
-        <v>0</v>
-      </c>
-      <c r="T10" s="2">
         <v>2</v>
       </c>
     </row>
-    <row r="11" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>8</v>
       </c>
       <c r="B11" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C11">
         <v>50998</v>
@@ -1251,16 +1228,16 @@
         <v>0</v>
       </c>
       <c r="E11">
-        <v>0</v>
+        <v>50998</v>
       </c>
       <c r="F11">
+        <v>0</v>
+      </c>
+      <c r="G11">
         <v>50998</v>
       </c>
-      <c r="G11">
-        <v>0</v>
-      </c>
       <c r="H11">
-        <v>50998</v>
+        <v>0</v>
       </c>
       <c r="I11">
         <v>0</v>
@@ -1272,39 +1249,36 @@
         <v>0</v>
       </c>
       <c r="L11">
-        <v>0</v>
+        <v>9958</v>
       </c>
       <c r="M11">
-        <v>9958</v>
+        <v>253</v>
       </c>
       <c r="N11">
-        <v>253</v>
+        <v>1703</v>
       </c>
       <c r="O11">
-        <v>1703</v>
+        <v>49300</v>
       </c>
       <c r="P11">
-        <v>49300</v>
-      </c>
-      <c r="Q11">
         <v>84438</v>
       </c>
+      <c r="Q11" s="2">
+        <v>23477</v>
+      </c>
       <c r="R11" s="2">
-        <v>23477</v>
+        <v>0</v>
       </c>
       <c r="S11" s="2">
-        <v>0</v>
-      </c>
-      <c r="T11" s="2">
         <v>23</v>
       </c>
     </row>
-    <row r="12" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>9</v>
       </c>
       <c r="B12" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C12">
         <v>40739</v>
@@ -1313,16 +1287,16 @@
         <v>0</v>
       </c>
       <c r="E12">
-        <v>0</v>
+        <v>40739</v>
       </c>
       <c r="F12">
+        <v>0</v>
+      </c>
+      <c r="G12">
         <v>40739</v>
       </c>
-      <c r="G12">
-        <v>0</v>
-      </c>
       <c r="H12">
-        <v>40739</v>
+        <v>0</v>
       </c>
       <c r="I12">
         <v>0</v>
@@ -1334,39 +1308,36 @@
         <v>0</v>
       </c>
       <c r="L12">
-        <v>0</v>
+        <v>10054</v>
       </c>
       <c r="M12">
-        <v>10054</v>
+        <v>207</v>
       </c>
       <c r="N12">
-        <v>207</v>
+        <v>1133</v>
       </c>
       <c r="O12">
-        <v>1133</v>
+        <v>39588</v>
       </c>
       <c r="P12">
-        <v>39588</v>
-      </c>
-      <c r="Q12">
         <v>66685</v>
       </c>
+      <c r="Q12" s="2">
+        <v>17786</v>
+      </c>
       <c r="R12" s="2">
-        <v>17786</v>
+        <v>0</v>
       </c>
       <c r="S12" s="2">
-        <v>0</v>
-      </c>
-      <c r="T12" s="2">
         <v>3</v>
       </c>
     </row>
-    <row r="13" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>10</v>
       </c>
       <c r="B13" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C13">
         <v>37031</v>
@@ -1375,16 +1346,16 @@
         <v>0</v>
       </c>
       <c r="E13">
-        <v>0</v>
+        <v>37031</v>
       </c>
       <c r="F13">
+        <v>0</v>
+      </c>
+      <c r="G13">
         <v>37031</v>
       </c>
-      <c r="G13">
-        <v>0</v>
-      </c>
       <c r="H13">
-        <v>37031</v>
+        <v>0</v>
       </c>
       <c r="I13">
         <v>0</v>
@@ -1396,39 +1367,36 @@
         <v>0</v>
       </c>
       <c r="L13">
-        <v>0</v>
+        <v>7864</v>
       </c>
       <c r="M13">
-        <v>7864</v>
+        <v>258</v>
       </c>
       <c r="N13">
-        <v>258</v>
+        <v>3822</v>
       </c>
       <c r="O13">
-        <v>3822</v>
+        <v>33195</v>
       </c>
       <c r="P13">
-        <v>33195</v>
-      </c>
-      <c r="Q13">
         <v>56564</v>
       </c>
+      <c r="Q13" s="2">
+        <v>16237</v>
+      </c>
       <c r="R13" s="2">
-        <v>16237</v>
+        <v>0</v>
       </c>
       <c r="S13" s="2">
-        <v>0</v>
-      </c>
-      <c r="T13" s="2">
         <v>106</v>
       </c>
     </row>
-    <row r="14" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>11</v>
       </c>
       <c r="B14" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C14">
         <v>48966</v>
@@ -1437,16 +1405,16 @@
         <v>0</v>
       </c>
       <c r="E14">
-        <v>0</v>
+        <v>48966</v>
       </c>
       <c r="F14">
+        <v>0</v>
+      </c>
+      <c r="G14">
         <v>48966</v>
       </c>
-      <c r="G14">
-        <v>0</v>
-      </c>
       <c r="H14">
-        <v>48966</v>
+        <v>0</v>
       </c>
       <c r="I14">
         <v>0</v>
@@ -1458,39 +1426,36 @@
         <v>0</v>
       </c>
       <c r="L14">
-        <v>0</v>
+        <v>15267</v>
       </c>
       <c r="M14">
-        <v>15267</v>
+        <v>1456</v>
       </c>
       <c r="N14">
-        <v>1456</v>
+        <v>5864</v>
       </c>
       <c r="O14">
-        <v>5864</v>
+        <v>43096</v>
       </c>
       <c r="P14">
-        <v>43096</v>
-      </c>
-      <c r="Q14">
         <v>77955</v>
       </c>
+      <c r="Q14" s="2">
+        <v>19716</v>
+      </c>
       <c r="R14" s="2">
-        <v>19716</v>
+        <v>0</v>
       </c>
       <c r="S14" s="2">
-        <v>0</v>
-      </c>
-      <c r="T14" s="2">
         <v>174</v>
       </c>
     </row>
-    <row r="15" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>12</v>
       </c>
       <c r="B15" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C15">
         <v>42703</v>
@@ -1499,16 +1464,16 @@
         <v>0</v>
       </c>
       <c r="E15">
-        <v>0</v>
+        <v>42703</v>
       </c>
       <c r="F15">
+        <v>0</v>
+      </c>
+      <c r="G15">
         <v>42703</v>
       </c>
-      <c r="G15">
-        <v>0</v>
-      </c>
       <c r="H15">
-        <v>42703</v>
+        <v>0</v>
       </c>
       <c r="I15">
         <v>0</v>
@@ -1520,39 +1485,36 @@
         <v>0</v>
       </c>
       <c r="L15">
-        <v>0</v>
+        <v>9192</v>
       </c>
       <c r="M15">
-        <v>9192</v>
+        <v>0</v>
       </c>
       <c r="N15">
-        <v>0</v>
+        <v>2821</v>
       </c>
       <c r="O15">
-        <v>2821</v>
+        <v>39882</v>
       </c>
       <c r="P15">
-        <v>39882</v>
-      </c>
-      <c r="Q15">
         <v>67178</v>
       </c>
+      <c r="Q15" s="2">
+        <v>4859</v>
+      </c>
       <c r="R15" s="2">
-        <v>4859</v>
+        <v>0</v>
       </c>
       <c r="S15" s="2">
-        <v>0</v>
-      </c>
-      <c r="T15" s="2">
         <v>50</v>
       </c>
     </row>
-    <row r="16" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>13</v>
       </c>
       <c r="B16" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C16">
         <v>25549</v>
@@ -1561,16 +1523,16 @@
         <v>0</v>
       </c>
       <c r="E16">
-        <v>0</v>
+        <v>25549</v>
       </c>
       <c r="F16">
-        <v>25549</v>
+        <v>0</v>
       </c>
       <c r="G16">
-        <v>0</v>
+        <v>25547</v>
       </c>
       <c r="H16">
-        <v>25547</v>
+        <v>0</v>
       </c>
       <c r="I16">
         <v>0</v>
@@ -1582,39 +1544,36 @@
         <v>0</v>
       </c>
       <c r="L16">
-        <v>0</v>
+        <v>14861</v>
       </c>
       <c r="M16">
-        <v>14861</v>
+        <v>1</v>
       </c>
       <c r="N16">
-        <v>1</v>
+        <v>261</v>
       </c>
       <c r="O16">
-        <v>261</v>
+        <v>25288</v>
       </c>
       <c r="P16">
-        <v>25288</v>
-      </c>
-      <c r="Q16">
         <v>71673</v>
       </c>
+      <c r="Q16" s="2">
+        <v>5197</v>
+      </c>
       <c r="R16" s="2">
-        <v>5197</v>
+        <v>0</v>
       </c>
       <c r="S16" s="2">
-        <v>0</v>
-      </c>
-      <c r="T16" s="2">
         <v>47</v>
       </c>
     </row>
-    <row r="17" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>14</v>
       </c>
       <c r="B17" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C17">
         <v>27707</v>
@@ -1623,16 +1582,16 @@
         <v>0</v>
       </c>
       <c r="E17">
-        <v>0</v>
+        <v>27707</v>
       </c>
       <c r="F17">
+        <v>0</v>
+      </c>
+      <c r="G17">
         <v>27707</v>
       </c>
-      <c r="G17">
-        <v>0</v>
-      </c>
       <c r="H17">
-        <v>27707</v>
+        <v>0</v>
       </c>
       <c r="I17">
         <v>0</v>
@@ -1644,39 +1603,36 @@
         <v>0</v>
       </c>
       <c r="L17">
-        <v>0</v>
+        <v>9287</v>
       </c>
       <c r="M17">
-        <v>9287</v>
+        <v>2</v>
       </c>
       <c r="N17">
-        <v>2</v>
+        <v>426</v>
       </c>
       <c r="O17">
-        <v>426</v>
+        <v>27282</v>
       </c>
       <c r="P17">
-        <v>27282</v>
-      </c>
-      <c r="Q17">
         <v>65457</v>
       </c>
+      <c r="Q17" s="2">
+        <v>5417</v>
+      </c>
       <c r="R17" s="2">
-        <v>5417</v>
+        <v>0</v>
       </c>
       <c r="S17" s="2">
-        <v>0</v>
-      </c>
-      <c r="T17" s="2">
         <v>105</v>
       </c>
     </row>
-    <row r="18" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>15</v>
       </c>
       <c r="B18" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C18">
         <v>47836</v>
@@ -1685,16 +1641,16 @@
         <v>0</v>
       </c>
       <c r="E18">
-        <v>0</v>
+        <v>47836</v>
       </c>
       <c r="F18">
+        <v>0</v>
+      </c>
+      <c r="G18">
         <v>47836</v>
       </c>
-      <c r="G18">
-        <v>0</v>
-      </c>
       <c r="H18">
-        <v>47836</v>
+        <v>0</v>
       </c>
       <c r="I18">
         <v>0</v>
@@ -1706,39 +1662,36 @@
         <v>0</v>
       </c>
       <c r="L18">
-        <v>0</v>
+        <v>7875</v>
       </c>
       <c r="M18">
-        <v>7875</v>
+        <v>3</v>
       </c>
       <c r="N18">
-        <v>3</v>
+        <v>1969</v>
       </c>
       <c r="O18">
-        <v>1969</v>
+        <v>45401</v>
       </c>
       <c r="P18">
-        <v>45401</v>
-      </c>
-      <c r="Q18">
         <v>71475</v>
       </c>
+      <c r="Q18" s="2">
+        <v>6819</v>
+      </c>
       <c r="R18" s="2">
-        <v>6819</v>
+        <v>0</v>
       </c>
       <c r="S18" s="2">
-        <v>0</v>
-      </c>
-      <c r="T18" s="2">
         <v>32</v>
       </c>
     </row>
-    <row r="19" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>16</v>
       </c>
       <c r="B19" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C19">
         <v>56490</v>
@@ -1747,16 +1700,16 @@
         <v>0</v>
       </c>
       <c r="E19">
-        <v>0</v>
+        <v>56490</v>
       </c>
       <c r="F19">
+        <v>0</v>
+      </c>
+      <c r="G19">
         <v>56490</v>
       </c>
-      <c r="G19">
-        <v>0</v>
-      </c>
       <c r="H19">
-        <v>56490</v>
+        <v>0</v>
       </c>
       <c r="I19">
         <v>0</v>
@@ -1768,39 +1721,36 @@
         <v>0</v>
       </c>
       <c r="L19">
-        <v>0</v>
+        <v>15286</v>
       </c>
       <c r="M19">
-        <v>15286</v>
+        <v>1</v>
       </c>
       <c r="N19">
-        <v>1</v>
+        <v>912</v>
       </c>
       <c r="O19">
-        <v>912</v>
+        <v>55578</v>
       </c>
       <c r="P19">
-        <v>55578</v>
-      </c>
-      <c r="Q19">
         <v>106392</v>
       </c>
+      <c r="Q19" s="2">
+        <v>6135</v>
+      </c>
       <c r="R19" s="2">
-        <v>6135</v>
+        <v>0</v>
       </c>
       <c r="S19" s="2">
-        <v>0</v>
-      </c>
-      <c r="T19" s="2">
         <v>36</v>
       </c>
     </row>
-    <row r="20" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>17</v>
       </c>
       <c r="B20" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C20">
         <v>35022</v>
@@ -1809,16 +1759,16 @@
         <v>0</v>
       </c>
       <c r="E20">
-        <v>0</v>
+        <v>35022</v>
       </c>
       <c r="F20">
+        <v>0</v>
+      </c>
+      <c r="G20">
         <v>35022</v>
       </c>
-      <c r="G20">
-        <v>0</v>
-      </c>
       <c r="H20">
-        <v>35022</v>
+        <v>0</v>
       </c>
       <c r="I20">
         <v>0</v>
@@ -1830,39 +1780,36 @@
         <v>0</v>
       </c>
       <c r="L20">
-        <v>0</v>
+        <v>6093</v>
       </c>
       <c r="M20">
-        <v>6093</v>
+        <v>5</v>
       </c>
       <c r="N20">
-        <v>5</v>
+        <v>546</v>
       </c>
       <c r="O20">
-        <v>546</v>
+        <v>34464</v>
       </c>
       <c r="P20">
-        <v>34464</v>
-      </c>
-      <c r="Q20">
         <v>75812</v>
       </c>
+      <c r="Q20" s="2">
+        <v>8984</v>
+      </c>
       <c r="R20" s="2">
-        <v>8984</v>
+        <v>0</v>
       </c>
       <c r="S20" s="2">
-        <v>0</v>
-      </c>
-      <c r="T20" s="2">
         <v>71</v>
       </c>
     </row>
-    <row r="21" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>18</v>
       </c>
       <c r="B21" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C21">
         <v>16962</v>
@@ -1871,16 +1818,16 @@
         <v>0</v>
       </c>
       <c r="E21">
-        <v>0</v>
+        <v>16962</v>
       </c>
       <c r="F21">
+        <v>0</v>
+      </c>
+      <c r="G21">
         <v>16962</v>
       </c>
-      <c r="G21">
-        <v>0</v>
-      </c>
       <c r="H21">
-        <v>16962</v>
+        <v>0</v>
       </c>
       <c r="I21">
         <v>0</v>
@@ -1892,39 +1839,36 @@
         <v>0</v>
       </c>
       <c r="L21">
-        <v>0</v>
+        <v>4030</v>
       </c>
       <c r="M21">
-        <v>4030</v>
+        <v>3</v>
       </c>
       <c r="N21">
-        <v>3</v>
+        <v>171</v>
       </c>
       <c r="O21">
-        <v>171</v>
+        <v>16791</v>
       </c>
       <c r="P21">
-        <v>16791</v>
-      </c>
-      <c r="Q21">
         <v>62460</v>
       </c>
+      <c r="Q21" s="2">
+        <v>3868</v>
+      </c>
       <c r="R21" s="2">
-        <v>3868</v>
+        <v>0</v>
       </c>
       <c r="S21" s="2">
         <v>0</v>
       </c>
-      <c r="T21" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="22" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>19</v>
       </c>
       <c r="B22" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C22">
         <v>18668</v>
@@ -1933,16 +1877,16 @@
         <v>0</v>
       </c>
       <c r="E22">
-        <v>0</v>
+        <v>18668</v>
       </c>
       <c r="F22">
+        <v>0</v>
+      </c>
+      <c r="G22">
         <v>18668</v>
       </c>
-      <c r="G22">
-        <v>0</v>
-      </c>
       <c r="H22">
-        <v>18668</v>
+        <v>0</v>
       </c>
       <c r="I22">
         <v>0</v>
@@ -1954,39 +1898,36 @@
         <v>0</v>
       </c>
       <c r="L22">
-        <v>0</v>
+        <v>7665</v>
       </c>
       <c r="M22">
-        <v>7665</v>
+        <v>0</v>
       </c>
       <c r="N22">
-        <v>0</v>
+        <v>302</v>
       </c>
       <c r="O22">
-        <v>302</v>
+        <v>18366</v>
       </c>
       <c r="P22">
-        <v>18366</v>
-      </c>
-      <c r="Q22">
         <v>64099</v>
       </c>
+      <c r="Q22" s="2">
+        <v>4848</v>
+      </c>
       <c r="R22" s="2">
-        <v>4848</v>
+        <v>0</v>
       </c>
       <c r="S22" s="2">
         <v>0</v>
       </c>
-      <c r="T22" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="23" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>20</v>
       </c>
       <c r="B23" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C23">
         <v>12020</v>
@@ -1995,16 +1936,16 @@
         <v>0</v>
       </c>
       <c r="E23">
-        <v>0</v>
+        <v>12020</v>
       </c>
       <c r="F23">
+        <v>0</v>
+      </c>
+      <c r="G23">
         <v>12020</v>
       </c>
-      <c r="G23">
-        <v>0</v>
-      </c>
       <c r="H23">
-        <v>12020</v>
+        <v>0</v>
       </c>
       <c r="I23">
         <v>0</v>
@@ -2016,39 +1957,36 @@
         <v>0</v>
       </c>
       <c r="L23">
-        <v>0</v>
+        <v>2113</v>
       </c>
       <c r="M23">
-        <v>2113</v>
+        <v>0</v>
       </c>
       <c r="N23">
-        <v>0</v>
+        <v>108</v>
       </c>
       <c r="O23">
-        <v>108</v>
+        <v>11912</v>
       </c>
       <c r="P23">
-        <v>11912</v>
-      </c>
-      <c r="Q23">
         <v>57094</v>
       </c>
+      <c r="Q23" s="2">
+        <v>3541</v>
+      </c>
       <c r="R23" s="2">
-        <v>3541</v>
+        <v>0</v>
       </c>
       <c r="S23" s="2">
-        <v>0</v>
-      </c>
-      <c r="T23" s="2">
         <v>28</v>
       </c>
     </row>
-    <row r="24" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>21</v>
       </c>
       <c r="B24" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C24">
         <v>14056</v>
@@ -2057,16 +1995,16 @@
         <v>0</v>
       </c>
       <c r="E24">
-        <v>0</v>
+        <v>14056</v>
       </c>
       <c r="F24">
+        <v>0</v>
+      </c>
+      <c r="G24">
         <v>14056</v>
       </c>
-      <c r="G24">
-        <v>0</v>
-      </c>
       <c r="H24">
-        <v>14056</v>
+        <v>0</v>
       </c>
       <c r="I24">
         <v>0</v>
@@ -2078,39 +2016,36 @@
         <v>0</v>
       </c>
       <c r="L24">
-        <v>0</v>
+        <v>3482</v>
       </c>
       <c r="M24">
-        <v>3482</v>
+        <v>5</v>
       </c>
       <c r="N24">
-        <v>5</v>
+        <v>231</v>
       </c>
       <c r="O24">
-        <v>231</v>
+        <v>13825</v>
       </c>
       <c r="P24">
-        <v>13825</v>
-      </c>
-      <c r="Q24">
         <v>65629</v>
       </c>
+      <c r="Q24" s="2">
+        <v>3492</v>
+      </c>
       <c r="R24" s="2">
-        <v>3492</v>
+        <v>0</v>
       </c>
       <c r="S24" s="2">
         <v>0</v>
       </c>
-      <c r="T24" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="25" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>22</v>
       </c>
       <c r="B25" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C25">
         <v>19266</v>
@@ -2119,16 +2054,16 @@
         <v>0</v>
       </c>
       <c r="E25">
-        <v>0</v>
+        <v>19266</v>
       </c>
       <c r="F25">
+        <v>0</v>
+      </c>
+      <c r="G25">
         <v>19266</v>
       </c>
-      <c r="G25">
-        <v>0</v>
-      </c>
       <c r="H25">
-        <v>19266</v>
+        <v>0</v>
       </c>
       <c r="I25">
         <v>0</v>
@@ -2140,39 +2075,36 @@
         <v>0</v>
       </c>
       <c r="L25">
-        <v>0</v>
+        <v>4862</v>
       </c>
       <c r="M25">
-        <v>4862</v>
+        <v>0</v>
       </c>
       <c r="N25">
-        <v>0</v>
+        <v>298</v>
       </c>
       <c r="O25">
-        <v>298</v>
+        <v>18968</v>
       </c>
       <c r="P25">
-        <v>18968</v>
-      </c>
-      <c r="Q25">
         <v>57533</v>
       </c>
+      <c r="Q25" s="2">
+        <v>3231</v>
+      </c>
       <c r="R25" s="2">
-        <v>3231</v>
+        <v>0</v>
       </c>
       <c r="S25" s="2">
-        <v>0</v>
-      </c>
-      <c r="T25" s="2">
         <v>13</v>
       </c>
     </row>
-    <row r="26" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>23</v>
       </c>
       <c r="B26" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C26">
         <v>17557</v>
@@ -2181,16 +2113,16 @@
         <v>0</v>
       </c>
       <c r="E26">
-        <v>0</v>
+        <v>17557</v>
       </c>
       <c r="F26">
+        <v>0</v>
+      </c>
+      <c r="G26">
         <v>17557</v>
       </c>
-      <c r="G26">
-        <v>0</v>
-      </c>
       <c r="H26">
-        <v>17557</v>
+        <v>0</v>
       </c>
       <c r="I26">
         <v>0</v>
@@ -2202,39 +2134,36 @@
         <v>0</v>
       </c>
       <c r="L26">
-        <v>0</v>
+        <v>3741</v>
       </c>
       <c r="M26">
-        <v>3741</v>
+        <v>3</v>
       </c>
       <c r="N26">
-        <v>3</v>
+        <v>194</v>
       </c>
       <c r="O26">
-        <v>194</v>
+        <v>17363</v>
       </c>
       <c r="P26">
-        <v>17363</v>
-      </c>
-      <c r="Q26">
         <v>66594</v>
       </c>
+      <c r="Q26" s="2">
+        <v>3333</v>
+      </c>
       <c r="R26" s="2">
-        <v>3333</v>
+        <v>0</v>
       </c>
       <c r="S26" s="2">
-        <v>0</v>
-      </c>
-      <c r="T26" s="2">
         <v>2</v>
       </c>
     </row>
-    <row r="27" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>24</v>
       </c>
       <c r="B27" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C27">
         <v>44276</v>
@@ -2243,16 +2172,16 @@
         <v>0</v>
       </c>
       <c r="E27">
-        <v>0</v>
+        <v>44276</v>
       </c>
       <c r="F27">
+        <v>0</v>
+      </c>
+      <c r="G27">
         <v>44276</v>
       </c>
-      <c r="G27">
-        <v>0</v>
-      </c>
       <c r="H27">
-        <v>44276</v>
+        <v>0</v>
       </c>
       <c r="I27">
         <v>0</v>
@@ -2264,39 +2193,36 @@
         <v>0</v>
       </c>
       <c r="L27">
-        <v>0</v>
+        <v>9679</v>
       </c>
       <c r="M27">
-        <v>9679</v>
+        <v>215</v>
       </c>
       <c r="N27">
-        <v>215</v>
+        <v>3287</v>
       </c>
       <c r="O27">
-        <v>3287</v>
+        <v>41005</v>
       </c>
       <c r="P27">
-        <v>41005</v>
-      </c>
-      <c r="Q27">
         <v>73109</v>
       </c>
+      <c r="Q27" s="2">
+        <v>12669</v>
+      </c>
       <c r="R27" s="2">
-        <v>12669</v>
+        <v>0</v>
       </c>
       <c r="S27" s="2">
         <v>0</v>
       </c>
-      <c r="T27" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="28" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>25</v>
       </c>
       <c r="B28" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C28">
         <v>54349</v>
@@ -2305,16 +2231,16 @@
         <v>0</v>
       </c>
       <c r="E28">
-        <v>0</v>
+        <v>54349</v>
       </c>
       <c r="F28">
+        <v>0</v>
+      </c>
+      <c r="G28">
         <v>54349</v>
       </c>
-      <c r="G28">
-        <v>0</v>
-      </c>
       <c r="H28">
-        <v>54349</v>
+        <v>0</v>
       </c>
       <c r="I28">
         <v>0</v>
@@ -2326,39 +2252,36 @@
         <v>0</v>
       </c>
       <c r="L28">
-        <v>0</v>
+        <v>8879</v>
       </c>
       <c r="M28">
-        <v>8879</v>
+        <v>856</v>
       </c>
       <c r="N28">
-        <v>856</v>
+        <v>3525</v>
       </c>
       <c r="O28">
-        <v>3525</v>
+        <v>50844</v>
       </c>
       <c r="P28">
-        <v>50844</v>
-      </c>
-      <c r="Q28">
         <v>80620</v>
       </c>
+      <c r="Q28" s="2">
+        <v>13995</v>
+      </c>
       <c r="R28" s="2">
-        <v>13995</v>
+        <v>0</v>
       </c>
       <c r="S28" s="2">
-        <v>0</v>
-      </c>
-      <c r="T28" s="2">
         <v>127</v>
       </c>
     </row>
-    <row r="29" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>26</v>
       </c>
       <c r="B29" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C29">
         <v>47111</v>
@@ -2367,16 +2290,16 @@
         <v>0</v>
       </c>
       <c r="E29">
-        <v>0</v>
+        <v>47111</v>
       </c>
       <c r="F29">
+        <v>0</v>
+      </c>
+      <c r="G29">
         <v>47111</v>
       </c>
-      <c r="G29">
-        <v>0</v>
-      </c>
       <c r="H29">
-        <v>47111</v>
+        <v>0</v>
       </c>
       <c r="I29">
         <v>0</v>
@@ -2388,39 +2311,36 @@
         <v>0</v>
       </c>
       <c r="L29">
-        <v>0</v>
+        <v>8816</v>
       </c>
       <c r="M29">
-        <v>8816</v>
+        <v>318</v>
       </c>
       <c r="N29">
-        <v>318</v>
+        <v>4592</v>
       </c>
       <c r="O29">
-        <v>4592</v>
+        <v>42520</v>
       </c>
       <c r="P29">
-        <v>42520</v>
-      </c>
-      <c r="Q29">
         <v>83836</v>
       </c>
+      <c r="Q29" s="2">
+        <v>14229</v>
+      </c>
       <c r="R29" s="2">
-        <v>14229</v>
+        <v>0</v>
       </c>
       <c r="S29" s="2">
-        <v>0</v>
-      </c>
-      <c r="T29" s="2">
         <v>22</v>
       </c>
     </row>
-    <row r="30" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>27</v>
       </c>
       <c r="B30" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C30">
         <v>52653</v>
@@ -2429,16 +2349,16 @@
         <v>0</v>
       </c>
       <c r="E30">
-        <v>0</v>
+        <v>52653</v>
       </c>
       <c r="F30">
+        <v>0</v>
+      </c>
+      <c r="G30">
         <v>52653</v>
       </c>
-      <c r="G30">
-        <v>0</v>
-      </c>
       <c r="H30">
-        <v>52653</v>
+        <v>0</v>
       </c>
       <c r="I30">
         <v>0</v>
@@ -2450,39 +2370,36 @@
         <v>0</v>
       </c>
       <c r="L30">
-        <v>0</v>
+        <v>11659</v>
       </c>
       <c r="M30">
-        <v>11659</v>
+        <v>411</v>
       </c>
       <c r="N30">
-        <v>411</v>
+        <v>5383</v>
       </c>
       <c r="O30">
-        <v>5383</v>
+        <v>47272</v>
       </c>
       <c r="P30">
-        <v>47272</v>
-      </c>
-      <c r="Q30">
         <v>86933</v>
       </c>
+      <c r="Q30" s="2">
+        <v>12564</v>
+      </c>
       <c r="R30" s="2">
-        <v>12564</v>
+        <v>0</v>
       </c>
       <c r="S30" s="2">
-        <v>0</v>
-      </c>
-      <c r="T30" s="2">
         <v>8</v>
       </c>
     </row>
-    <row r="31" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>28</v>
       </c>
       <c r="B31" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C31">
         <v>91162</v>
@@ -2491,16 +2408,16 @@
         <v>0</v>
       </c>
       <c r="E31">
-        <v>0</v>
+        <v>91162</v>
       </c>
       <c r="F31">
+        <v>0</v>
+      </c>
+      <c r="G31">
         <v>91162</v>
       </c>
-      <c r="G31">
-        <v>0</v>
-      </c>
       <c r="H31">
-        <v>91162</v>
+        <v>0</v>
       </c>
       <c r="I31">
         <v>0</v>
@@ -2512,39 +2429,36 @@
         <v>0</v>
       </c>
       <c r="L31">
-        <v>0</v>
+        <v>46718</v>
       </c>
       <c r="M31">
-        <v>46718</v>
+        <v>42</v>
       </c>
       <c r="N31">
-        <v>42</v>
+        <v>1899</v>
       </c>
       <c r="O31">
-        <v>1899</v>
+        <v>89264</v>
       </c>
       <c r="P31">
-        <v>89264</v>
-      </c>
-      <c r="Q31">
         <v>81642</v>
       </c>
+      <c r="Q31" s="2">
+        <v>14581</v>
+      </c>
       <c r="R31" s="2">
-        <v>14581</v>
+        <v>0</v>
       </c>
       <c r="S31" s="2">
-        <v>0</v>
-      </c>
-      <c r="T31" s="2">
         <v>39</v>
       </c>
     </row>
-    <row r="32" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>29</v>
       </c>
       <c r="B32" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C32">
         <v>46728</v>
@@ -2553,16 +2467,16 @@
         <v>0</v>
       </c>
       <c r="E32">
-        <v>0</v>
+        <v>46728</v>
       </c>
       <c r="F32">
+        <v>0</v>
+      </c>
+      <c r="G32">
         <v>46728</v>
       </c>
-      <c r="G32">
-        <v>0</v>
-      </c>
       <c r="H32">
-        <v>46728</v>
+        <v>0</v>
       </c>
       <c r="I32">
         <v>0</v>
@@ -2574,39 +2488,36 @@
         <v>0</v>
       </c>
       <c r="L32">
-        <v>0</v>
+        <v>10557</v>
       </c>
       <c r="M32">
-        <v>10557</v>
+        <v>316</v>
       </c>
       <c r="N32">
-        <v>316</v>
+        <v>4391</v>
       </c>
       <c r="O32">
-        <v>4391</v>
+        <v>42344</v>
       </c>
       <c r="P32">
-        <v>42344</v>
-      </c>
-      <c r="Q32">
         <v>74810</v>
       </c>
+      <c r="Q32" s="2">
+        <v>11379</v>
+      </c>
       <c r="R32" s="2">
-        <v>11379</v>
+        <v>0</v>
       </c>
       <c r="S32" s="2">
         <v>0</v>
       </c>
-      <c r="T32" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="33" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>30</v>
       </c>
       <c r="B33" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C33">
         <v>40230</v>
@@ -2615,16 +2526,16 @@
         <v>0</v>
       </c>
       <c r="E33">
-        <v>0</v>
+        <v>40230</v>
       </c>
       <c r="F33">
+        <v>0</v>
+      </c>
+      <c r="G33">
         <v>40230</v>
       </c>
-      <c r="G33">
-        <v>0</v>
-      </c>
       <c r="H33">
-        <v>40230</v>
+        <v>0</v>
       </c>
       <c r="I33">
         <v>0</v>
@@ -2636,39 +2547,36 @@
         <v>0</v>
       </c>
       <c r="L33">
-        <v>0</v>
+        <v>5113</v>
       </c>
       <c r="M33">
-        <v>5113</v>
+        <v>311</v>
       </c>
       <c r="N33">
-        <v>311</v>
+        <v>1275</v>
       </c>
       <c r="O33">
-        <v>1275</v>
+        <v>38955</v>
       </c>
       <c r="P33">
-        <v>38955</v>
-      </c>
-      <c r="Q33">
         <v>76969</v>
       </c>
+      <c r="Q33" s="2">
+        <v>6678</v>
+      </c>
       <c r="R33" s="2">
-        <v>6678</v>
+        <v>0</v>
       </c>
       <c r="S33" s="2">
-        <v>0</v>
-      </c>
-      <c r="T33" s="2">
         <v>19</v>
       </c>
     </row>
-    <row r="34" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>31</v>
       </c>
       <c r="B34" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C34">
         <v>36542</v>
@@ -2677,16 +2585,16 @@
         <v>0</v>
       </c>
       <c r="E34">
-        <v>0</v>
+        <v>36542</v>
       </c>
       <c r="F34">
+        <v>0</v>
+      </c>
+      <c r="G34">
         <v>36542</v>
       </c>
-      <c r="G34">
-        <v>0</v>
-      </c>
       <c r="H34">
-        <v>36542</v>
+        <v>0</v>
       </c>
       <c r="I34">
         <v>0</v>
@@ -2698,39 +2606,36 @@
         <v>0</v>
       </c>
       <c r="L34">
-        <v>0</v>
+        <v>12439</v>
       </c>
       <c r="M34">
-        <v>12439</v>
+        <v>513</v>
       </c>
       <c r="N34">
-        <v>513</v>
+        <v>1363</v>
       </c>
       <c r="O34">
-        <v>1363</v>
+        <v>35181</v>
       </c>
       <c r="P34">
-        <v>35181</v>
-      </c>
-      <c r="Q34">
         <v>74624</v>
       </c>
+      <c r="Q34" s="2">
+        <v>7137</v>
+      </c>
       <c r="R34" s="2">
-        <v>7137</v>
+        <v>0</v>
       </c>
       <c r="S34" s="2">
         <v>0</v>
       </c>
-      <c r="T34" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="35" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>32</v>
       </c>
       <c r="B35" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C35">
         <v>33564</v>
@@ -2739,16 +2644,16 @@
         <v>0</v>
       </c>
       <c r="E35">
-        <v>0</v>
+        <v>33564</v>
       </c>
       <c r="F35">
+        <v>0</v>
+      </c>
+      <c r="G35">
         <v>33564</v>
       </c>
-      <c r="G35">
-        <v>0</v>
-      </c>
       <c r="H35">
-        <v>33564</v>
+        <v>0</v>
       </c>
       <c r="I35">
         <v>0</v>
@@ -2760,39 +2665,36 @@
         <v>0</v>
       </c>
       <c r="L35">
-        <v>0</v>
+        <v>7886</v>
       </c>
       <c r="M35">
-        <v>7886</v>
+        <v>271</v>
       </c>
       <c r="N35">
-        <v>271</v>
+        <v>1129</v>
       </c>
       <c r="O35">
-        <v>1129</v>
+        <v>32436</v>
       </c>
       <c r="P35">
-        <v>32436</v>
-      </c>
-      <c r="Q35">
         <v>76464</v>
       </c>
+      <c r="Q35" s="2">
+        <v>8879</v>
+      </c>
       <c r="R35" s="2">
-        <v>8879</v>
+        <v>0</v>
       </c>
       <c r="S35" s="2">
-        <v>0</v>
-      </c>
-      <c r="T35" s="2">
         <v>35</v>
       </c>
     </row>
-    <row r="36" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>33</v>
       </c>
       <c r="B36" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C36">
         <v>20905</v>
@@ -2801,16 +2703,16 @@
         <v>0</v>
       </c>
       <c r="E36">
-        <v>0</v>
+        <v>20905</v>
       </c>
       <c r="F36">
+        <v>0</v>
+      </c>
+      <c r="G36">
         <v>20905</v>
       </c>
-      <c r="G36">
-        <v>0</v>
-      </c>
       <c r="H36">
-        <v>20905</v>
+        <v>0</v>
       </c>
       <c r="I36">
         <v>0</v>
@@ -2822,39 +2724,36 @@
         <v>0</v>
       </c>
       <c r="L36">
-        <v>0</v>
+        <v>7350</v>
       </c>
       <c r="M36">
-        <v>7350</v>
+        <v>0</v>
       </c>
       <c r="N36">
-        <v>0</v>
+        <v>951</v>
       </c>
       <c r="O36">
-        <v>951</v>
+        <v>19954</v>
       </c>
       <c r="P36">
-        <v>19954</v>
-      </c>
-      <c r="Q36">
         <v>60419</v>
       </c>
+      <c r="Q36" s="2">
+        <v>3855</v>
+      </c>
       <c r="R36" s="2">
-        <v>3855</v>
+        <v>0</v>
       </c>
       <c r="S36" s="2">
-        <v>0</v>
-      </c>
-      <c r="T36" s="2">
         <v>2</v>
       </c>
     </row>
-    <row r="37" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>34</v>
       </c>
       <c r="B37" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C37">
         <v>17692</v>
@@ -2863,16 +2762,16 @@
         <v>0</v>
       </c>
       <c r="E37">
-        <v>0</v>
+        <v>17692</v>
       </c>
       <c r="F37">
+        <v>0</v>
+      </c>
+      <c r="G37">
         <v>17692</v>
       </c>
-      <c r="G37">
-        <v>0</v>
-      </c>
       <c r="H37">
-        <v>17692</v>
+        <v>0</v>
       </c>
       <c r="I37">
         <v>0</v>
@@ -2884,39 +2783,36 @@
         <v>0</v>
       </c>
       <c r="L37">
-        <v>0</v>
+        <v>2311</v>
       </c>
       <c r="M37">
-        <v>2311</v>
+        <v>0</v>
       </c>
       <c r="N37">
-        <v>0</v>
+        <v>541</v>
       </c>
       <c r="O37">
-        <v>541</v>
+        <v>17151</v>
       </c>
       <c r="P37">
-        <v>17151</v>
-      </c>
-      <c r="Q37">
         <v>57832</v>
       </c>
+      <c r="Q37" s="2">
+        <v>4036</v>
+      </c>
       <c r="R37" s="2">
-        <v>4036</v>
+        <v>0</v>
       </c>
       <c r="S37" s="2">
-        <v>0</v>
-      </c>
-      <c r="T37" s="2">
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>35</v>
       </c>
       <c r="B38" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C38">
         <v>29110</v>
@@ -2925,16 +2821,16 @@
         <v>0</v>
       </c>
       <c r="E38">
-        <v>1</v>
+        <v>29110</v>
       </c>
       <c r="F38">
+        <v>0</v>
+      </c>
+      <c r="G38">
         <v>29110</v>
       </c>
-      <c r="G38">
-        <v>0</v>
-      </c>
       <c r="H38">
-        <v>29110</v>
+        <v>0</v>
       </c>
       <c r="I38">
         <v>0</v>
@@ -2946,39 +2842,36 @@
         <v>0</v>
       </c>
       <c r="L38">
-        <v>0</v>
+        <v>5386</v>
       </c>
       <c r="M38">
-        <v>5386</v>
+        <v>2</v>
       </c>
       <c r="N38">
-        <v>2</v>
+        <v>635</v>
       </c>
       <c r="O38">
-        <v>635</v>
+        <v>28475</v>
       </c>
       <c r="P38">
-        <v>28475</v>
-      </c>
-      <c r="Q38">
         <v>63038</v>
       </c>
+      <c r="Q38" s="2">
+        <v>5135</v>
+      </c>
       <c r="R38" s="2">
-        <v>5135</v>
+        <v>0</v>
       </c>
       <c r="S38" s="2">
         <v>0</v>
       </c>
-      <c r="T38" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="39" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="39" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>36</v>
       </c>
       <c r="B39" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C39">
         <v>21367</v>
@@ -2987,16 +2880,16 @@
         <v>0</v>
       </c>
       <c r="E39">
-        <v>0</v>
+        <v>21367</v>
       </c>
       <c r="F39">
+        <v>0</v>
+      </c>
+      <c r="G39">
         <v>21367</v>
       </c>
-      <c r="G39">
-        <v>0</v>
-      </c>
       <c r="H39">
-        <v>21367</v>
+        <v>0</v>
       </c>
       <c r="I39">
         <v>0</v>
@@ -3008,39 +2901,36 @@
         <v>0</v>
       </c>
       <c r="L39">
-        <v>0</v>
+        <v>4529</v>
       </c>
       <c r="M39">
-        <v>4529</v>
+        <v>1</v>
       </c>
       <c r="N39">
-        <v>1</v>
+        <v>234</v>
       </c>
       <c r="O39">
-        <v>234</v>
+        <v>21133</v>
       </c>
       <c r="P39">
-        <v>21133</v>
-      </c>
-      <c r="Q39">
         <v>71133</v>
       </c>
+      <c r="Q39" s="2">
+        <v>5903</v>
+      </c>
       <c r="R39" s="2">
-        <v>5903</v>
+        <v>0</v>
       </c>
       <c r="S39" s="2">
-        <v>0</v>
-      </c>
-      <c r="T39" s="2">
         <v>26</v>
       </c>
     </row>
-    <row r="40" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>37</v>
       </c>
       <c r="B40" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C40">
         <v>18905</v>
@@ -3049,16 +2939,16 @@
         <v>0</v>
       </c>
       <c r="E40">
-        <v>0</v>
+        <v>18905</v>
       </c>
       <c r="F40">
+        <v>0</v>
+      </c>
+      <c r="G40">
         <v>18905</v>
       </c>
-      <c r="G40">
-        <v>0</v>
-      </c>
       <c r="H40">
-        <v>18905</v>
+        <v>0</v>
       </c>
       <c r="I40">
         <v>0</v>
@@ -3070,39 +2960,36 @@
         <v>0</v>
       </c>
       <c r="L40">
-        <v>0</v>
+        <v>1812</v>
       </c>
       <c r="M40">
-        <v>1812</v>
+        <v>0</v>
       </c>
       <c r="N40">
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="O40">
-        <v>52</v>
+        <v>18853</v>
       </c>
       <c r="P40">
-        <v>18853</v>
-      </c>
-      <c r="Q40">
         <v>73242</v>
       </c>
+      <c r="Q40" s="2">
+        <v>3824</v>
+      </c>
       <c r="R40" s="2">
-        <v>3824</v>
+        <v>0</v>
       </c>
       <c r="S40" s="2">
-        <v>0</v>
-      </c>
-      <c r="T40" s="2">
         <v>61</v>
       </c>
     </row>
-    <row r="41" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>38</v>
       </c>
       <c r="B41" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C41">
         <v>23521</v>
@@ -3111,16 +2998,16 @@
         <v>0</v>
       </c>
       <c r="E41">
-        <v>0</v>
+        <v>23521</v>
       </c>
       <c r="F41">
+        <v>0</v>
+      </c>
+      <c r="G41">
         <v>23521</v>
       </c>
-      <c r="G41">
-        <v>0</v>
-      </c>
       <c r="H41">
-        <v>23521</v>
+        <v>0</v>
       </c>
       <c r="I41">
         <v>0</v>
@@ -3132,39 +3019,36 @@
         <v>0</v>
       </c>
       <c r="L41">
-        <v>0</v>
+        <v>1499</v>
       </c>
       <c r="M41">
-        <v>1499</v>
+        <v>0</v>
       </c>
       <c r="N41">
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="O41">
-        <v>92</v>
+        <v>23429</v>
       </c>
       <c r="P41">
-        <v>23429</v>
-      </c>
-      <c r="Q41">
         <v>85251</v>
       </c>
+      <c r="Q41" s="2">
+        <v>6015</v>
+      </c>
       <c r="R41" s="2">
-        <v>6015</v>
+        <v>0</v>
       </c>
       <c r="S41" s="2">
-        <v>0</v>
-      </c>
-      <c r="T41" s="2">
         <v>27</v>
       </c>
     </row>
-    <row r="42" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>39</v>
       </c>
       <c r="B42" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C42">
         <v>27565</v>
@@ -3173,16 +3057,16 @@
         <v>0</v>
       </c>
       <c r="E42">
-        <v>0</v>
+        <v>27565</v>
       </c>
       <c r="F42">
+        <v>0</v>
+      </c>
+      <c r="G42">
         <v>27565</v>
       </c>
-      <c r="G42">
-        <v>0</v>
-      </c>
       <c r="H42">
-        <v>27565</v>
+        <v>0</v>
       </c>
       <c r="I42">
         <v>0</v>
@@ -3194,39 +3078,36 @@
         <v>0</v>
       </c>
       <c r="L42">
-        <v>0</v>
+        <v>6264</v>
       </c>
       <c r="M42">
-        <v>6264</v>
+        <v>0</v>
       </c>
       <c r="N42">
-        <v>0</v>
+        <v>419</v>
       </c>
       <c r="O42">
-        <v>419</v>
+        <v>27147</v>
       </c>
       <c r="P42">
-        <v>27147</v>
-      </c>
-      <c r="Q42">
         <v>68615</v>
       </c>
+      <c r="Q42" s="2">
+        <v>4708</v>
+      </c>
       <c r="R42" s="2">
-        <v>4708</v>
+        <v>0</v>
       </c>
       <c r="S42" s="2">
-        <v>0</v>
-      </c>
-      <c r="T42" s="2">
         <v>8</v>
       </c>
     </row>
-    <row r="43" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>40</v>
       </c>
       <c r="B43" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C43">
         <v>29700</v>
@@ -3235,16 +3116,16 @@
         <v>0</v>
       </c>
       <c r="E43">
-        <v>0</v>
+        <v>29700</v>
       </c>
       <c r="F43">
+        <v>0</v>
+      </c>
+      <c r="G43">
         <v>29700</v>
       </c>
-      <c r="G43">
-        <v>0</v>
-      </c>
       <c r="H43">
-        <v>29700</v>
+        <v>0</v>
       </c>
       <c r="I43">
         <v>0</v>
@@ -3256,39 +3137,36 @@
         <v>0</v>
       </c>
       <c r="L43">
-        <v>0</v>
+        <v>6804</v>
       </c>
       <c r="M43">
-        <v>6804</v>
+        <v>1</v>
       </c>
       <c r="N43">
-        <v>1</v>
+        <v>957</v>
       </c>
       <c r="O43">
-        <v>957</v>
+        <v>28774</v>
       </c>
       <c r="P43">
-        <v>28774</v>
-      </c>
-      <c r="Q43">
         <v>63012</v>
       </c>
+      <c r="Q43" s="2">
+        <v>5219</v>
+      </c>
       <c r="R43" s="2">
-        <v>5219</v>
+        <v>0</v>
       </c>
       <c r="S43" s="2">
-        <v>0</v>
-      </c>
-      <c r="T43" s="2">
         <v>121</v>
       </c>
     </row>
-    <row r="44" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A44">
         <v>41</v>
       </c>
       <c r="B44" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C44">
         <v>21900</v>
@@ -3297,16 +3175,16 @@
         <v>0</v>
       </c>
       <c r="E44">
-        <v>0</v>
+        <v>21900</v>
       </c>
       <c r="F44">
+        <v>0</v>
+      </c>
+      <c r="G44">
         <v>21900</v>
       </c>
-      <c r="G44">
-        <v>0</v>
-      </c>
       <c r="H44">
-        <v>21900</v>
+        <v>0</v>
       </c>
       <c r="I44">
         <v>0</v>
@@ -3318,39 +3196,36 @@
         <v>0</v>
       </c>
       <c r="L44">
-        <v>0</v>
+        <v>6643</v>
       </c>
       <c r="M44">
-        <v>6643</v>
+        <v>24</v>
       </c>
       <c r="N44">
-        <v>24</v>
+        <v>347</v>
       </c>
       <c r="O44">
-        <v>347</v>
+        <v>21553</v>
       </c>
       <c r="P44">
-        <v>21553</v>
-      </c>
-      <c r="Q44">
         <v>68393</v>
       </c>
+      <c r="Q44" s="2">
+        <v>7659</v>
+      </c>
       <c r="R44" s="2">
-        <v>7659</v>
+        <v>0</v>
       </c>
       <c r="S44" s="2">
-        <v>0</v>
-      </c>
-      <c r="T44" s="2">
         <v>20</v>
       </c>
     </row>
-    <row r="45" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A45">
         <v>42</v>
       </c>
       <c r="B45" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C45">
         <v>19935</v>
@@ -3359,16 +3234,16 @@
         <v>0</v>
       </c>
       <c r="E45">
-        <v>0</v>
+        <v>19935</v>
       </c>
       <c r="F45">
+        <v>0</v>
+      </c>
+      <c r="G45">
         <v>19935</v>
       </c>
-      <c r="G45">
-        <v>0</v>
-      </c>
       <c r="H45">
-        <v>19935</v>
+        <v>0</v>
       </c>
       <c r="I45">
         <v>0</v>
@@ -3380,39 +3255,36 @@
         <v>0</v>
       </c>
       <c r="L45">
-        <v>0</v>
+        <v>2254</v>
       </c>
       <c r="M45">
-        <v>2254</v>
+        <v>13</v>
       </c>
       <c r="N45">
-        <v>13</v>
+        <v>149</v>
       </c>
       <c r="O45">
-        <v>149</v>
+        <v>19786</v>
       </c>
       <c r="P45">
-        <v>19786</v>
-      </c>
-      <c r="Q45">
         <v>76287</v>
       </c>
+      <c r="Q45" s="2">
+        <v>6998</v>
+      </c>
       <c r="R45" s="2">
-        <v>6998</v>
+        <v>0</v>
       </c>
       <c r="S45" s="2">
-        <v>0</v>
-      </c>
-      <c r="T45" s="2">
         <v>129</v>
       </c>
     </row>
-    <row r="46" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A46">
         <v>43</v>
       </c>
       <c r="B46" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C46">
         <v>21512</v>
@@ -3421,16 +3293,16 @@
         <v>0</v>
       </c>
       <c r="E46">
-        <v>0</v>
+        <v>21512</v>
       </c>
       <c r="F46">
+        <v>0</v>
+      </c>
+      <c r="G46">
         <v>21512</v>
       </c>
-      <c r="G46">
-        <v>0</v>
-      </c>
       <c r="H46">
-        <v>21512</v>
+        <v>0</v>
       </c>
       <c r="I46">
         <v>0</v>
@@ -3442,39 +3314,36 @@
         <v>0</v>
       </c>
       <c r="L46">
-        <v>0</v>
+        <v>8303</v>
       </c>
       <c r="M46">
-        <v>8303</v>
+        <v>32</v>
       </c>
       <c r="N46">
-        <v>32</v>
+        <v>276</v>
       </c>
       <c r="O46">
-        <v>276</v>
+        <v>21236</v>
       </c>
       <c r="P46">
-        <v>21236</v>
-      </c>
-      <c r="Q46">
         <v>64160</v>
       </c>
+      <c r="Q46" s="2">
+        <v>7548</v>
+      </c>
       <c r="R46" s="2">
-        <v>7548</v>
+        <v>0</v>
       </c>
       <c r="S46" s="2">
-        <v>0</v>
-      </c>
-      <c r="T46" s="2">
         <v>152</v>
       </c>
     </row>
-    <row r="47" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A47">
         <v>44</v>
       </c>
       <c r="B47" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C47">
         <v>22426</v>
@@ -3483,16 +3352,16 @@
         <v>0</v>
       </c>
       <c r="E47">
-        <v>0</v>
+        <v>22426</v>
       </c>
       <c r="F47">
+        <v>0</v>
+      </c>
+      <c r="G47">
         <v>22426</v>
       </c>
-      <c r="G47">
-        <v>0</v>
-      </c>
       <c r="H47">
-        <v>22426</v>
+        <v>0</v>
       </c>
       <c r="I47">
         <v>0</v>
@@ -3504,39 +3373,36 @@
         <v>0</v>
       </c>
       <c r="L47">
-        <v>0</v>
+        <v>2595</v>
       </c>
       <c r="M47">
-        <v>2595</v>
+        <v>1</v>
       </c>
       <c r="N47">
-        <v>1</v>
+        <v>137</v>
       </c>
       <c r="O47">
-        <v>137</v>
+        <v>21624</v>
       </c>
       <c r="P47">
-        <v>21624</v>
-      </c>
-      <c r="Q47">
         <v>49875</v>
       </c>
+      <c r="Q47" s="2">
+        <v>5046</v>
+      </c>
       <c r="R47" s="2">
-        <v>5046</v>
+        <v>0</v>
       </c>
       <c r="S47" s="2">
         <v>0</v>
       </c>
-      <c r="T47" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="48" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="48" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A48">
         <v>45</v>
       </c>
       <c r="B48" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C48">
         <v>19641</v>
@@ -3545,16 +3411,16 @@
         <v>0</v>
       </c>
       <c r="E48">
-        <v>0</v>
+        <v>19641</v>
       </c>
       <c r="F48">
+        <v>0</v>
+      </c>
+      <c r="G48">
         <v>19641</v>
       </c>
-      <c r="G48">
-        <v>0</v>
-      </c>
       <c r="H48">
-        <v>19641</v>
+        <v>0</v>
       </c>
       <c r="I48">
         <v>0</v>
@@ -3566,39 +3432,36 @@
         <v>0</v>
       </c>
       <c r="L48">
-        <v>0</v>
+        <v>3799</v>
       </c>
       <c r="M48">
-        <v>3799</v>
+        <v>4</v>
       </c>
       <c r="N48">
-        <v>4</v>
+        <v>254</v>
       </c>
       <c r="O48">
-        <v>254</v>
+        <v>19350</v>
       </c>
       <c r="P48">
-        <v>19350</v>
-      </c>
-      <c r="Q48">
         <v>54142</v>
       </c>
+      <c r="Q48" s="2">
+        <v>4623</v>
+      </c>
       <c r="R48" s="2">
-        <v>4623</v>
+        <v>0</v>
       </c>
       <c r="S48" s="2">
-        <v>0</v>
-      </c>
-      <c r="T48" s="2">
         <v>9</v>
       </c>
     </row>
-    <row r="49" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A49">
         <v>46</v>
       </c>
       <c r="B49" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C49">
         <v>21651</v>
@@ -3607,16 +3470,16 @@
         <v>0</v>
       </c>
       <c r="E49">
-        <v>0</v>
+        <v>21651</v>
       </c>
       <c r="F49">
+        <v>0</v>
+      </c>
+      <c r="G49">
         <v>21651</v>
       </c>
-      <c r="G49">
-        <v>0</v>
-      </c>
       <c r="H49">
-        <v>21651</v>
+        <v>0</v>
       </c>
       <c r="I49">
         <v>0</v>
@@ -3628,39 +3491,36 @@
         <v>0</v>
       </c>
       <c r="L49">
-        <v>0</v>
+        <v>3627</v>
       </c>
       <c r="M49">
-        <v>3627</v>
+        <v>0</v>
       </c>
       <c r="N49">
-        <v>0</v>
+        <v>628</v>
       </c>
       <c r="O49">
-        <v>628</v>
+        <v>21024</v>
       </c>
       <c r="P49">
-        <v>21024</v>
-      </c>
-      <c r="Q49">
         <v>55376</v>
       </c>
+      <c r="Q49" s="2">
+        <v>5057</v>
+      </c>
       <c r="R49" s="2">
-        <v>5057</v>
+        <v>0</v>
       </c>
       <c r="S49" s="2">
-        <v>0</v>
-      </c>
-      <c r="T49" s="2">
         <v>4</v>
       </c>
     </row>
-    <row r="50" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A50">
         <v>47</v>
       </c>
       <c r="B50" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C50">
         <v>21936</v>
@@ -3669,16 +3529,16 @@
         <v>0</v>
       </c>
       <c r="E50">
-        <v>0</v>
+        <v>21936</v>
       </c>
       <c r="F50">
+        <v>0</v>
+      </c>
+      <c r="G50">
         <v>21936</v>
       </c>
-      <c r="G50">
-        <v>0</v>
-      </c>
       <c r="H50">
-        <v>21936</v>
+        <v>0</v>
       </c>
       <c r="I50">
         <v>0</v>
@@ -3690,39 +3550,36 @@
         <v>0</v>
       </c>
       <c r="L50">
-        <v>0</v>
+        <v>4160</v>
       </c>
       <c r="M50">
-        <v>4160</v>
+        <v>5</v>
       </c>
       <c r="N50">
-        <v>5</v>
+        <v>26</v>
       </c>
       <c r="O50">
-        <v>26</v>
+        <v>21910</v>
       </c>
       <c r="P50">
-        <v>21910</v>
-      </c>
-      <c r="Q50">
         <v>63298</v>
       </c>
+      <c r="Q50" s="2">
+        <v>7292</v>
+      </c>
       <c r="R50" s="2">
-        <v>7292</v>
+        <v>0</v>
       </c>
       <c r="S50" s="2">
-        <v>0</v>
-      </c>
-      <c r="T50" s="2">
         <v>1</v>
       </c>
     </row>
-    <row r="51" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A51">
         <v>48</v>
       </c>
       <c r="B51" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C51">
         <v>23798</v>
@@ -3731,16 +3588,16 @@
         <v>0</v>
       </c>
       <c r="E51">
-        <v>0</v>
+        <v>23798</v>
       </c>
       <c r="F51">
+        <v>0</v>
+      </c>
+      <c r="G51">
         <v>23798</v>
       </c>
-      <c r="G51">
-        <v>0</v>
-      </c>
       <c r="H51">
-        <v>23798</v>
+        <v>0</v>
       </c>
       <c r="I51">
         <v>0</v>
@@ -3752,39 +3609,36 @@
         <v>0</v>
       </c>
       <c r="L51">
-        <v>0</v>
+        <v>4843</v>
       </c>
       <c r="M51">
-        <v>4843</v>
+        <v>11</v>
       </c>
       <c r="N51">
-        <v>11</v>
+        <v>75</v>
       </c>
       <c r="O51">
-        <v>75</v>
+        <v>23723</v>
       </c>
       <c r="P51">
-        <v>23723</v>
-      </c>
-      <c r="Q51">
         <v>71754</v>
       </c>
+      <c r="Q51" s="2">
+        <v>7715</v>
+      </c>
       <c r="R51" s="2">
-        <v>7715</v>
+        <v>0</v>
       </c>
       <c r="S51" s="2">
-        <v>0</v>
-      </c>
-      <c r="T51" s="2">
         <v>40</v>
       </c>
     </row>
-    <row r="52" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A52">
         <v>49</v>
       </c>
       <c r="B52" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C52">
         <v>21094</v>
@@ -3793,16 +3647,16 @@
         <v>0</v>
       </c>
       <c r="E52">
-        <v>0</v>
+        <v>21094</v>
       </c>
       <c r="F52">
+        <v>0</v>
+      </c>
+      <c r="G52">
         <v>21094</v>
       </c>
-      <c r="G52">
-        <v>0</v>
-      </c>
       <c r="H52">
-        <v>21094</v>
+        <v>0</v>
       </c>
       <c r="I52">
         <v>0</v>
@@ -3814,39 +3668,36 @@
         <v>0</v>
       </c>
       <c r="L52">
-        <v>0</v>
+        <v>2942</v>
       </c>
       <c r="M52">
-        <v>2942</v>
+        <v>1</v>
       </c>
       <c r="N52">
-        <v>1</v>
+        <v>45</v>
       </c>
       <c r="O52">
-        <v>45</v>
+        <v>21049</v>
       </c>
       <c r="P52">
-        <v>21049</v>
-      </c>
-      <c r="Q52">
         <v>63987</v>
       </c>
+      <c r="Q52" s="2">
+        <v>5655</v>
+      </c>
       <c r="R52" s="2">
-        <v>5655</v>
+        <v>0</v>
       </c>
       <c r="S52" s="2">
-        <v>0</v>
-      </c>
-      <c r="T52" s="2">
         <v>2</v>
       </c>
     </row>
-    <row r="53" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A53">
         <v>50</v>
       </c>
       <c r="B53" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C53">
         <v>19131</v>
@@ -3855,16 +3706,16 @@
         <v>0</v>
       </c>
       <c r="E53">
-        <v>0</v>
+        <v>19131</v>
       </c>
       <c r="F53">
+        <v>0</v>
+      </c>
+      <c r="G53">
         <v>19131</v>
       </c>
-      <c r="G53">
-        <v>0</v>
-      </c>
       <c r="H53">
-        <v>19131</v>
+        <v>0</v>
       </c>
       <c r="I53">
         <v>0</v>
@@ -3876,39 +3727,36 @@
         <v>0</v>
       </c>
       <c r="L53">
-        <v>0</v>
+        <v>3513</v>
       </c>
       <c r="M53">
-        <v>3513</v>
+        <v>1</v>
       </c>
       <c r="N53">
-        <v>1</v>
+        <v>76</v>
       </c>
       <c r="O53">
-        <v>76</v>
+        <v>19055</v>
       </c>
       <c r="P53">
-        <v>19055</v>
-      </c>
-      <c r="Q53">
         <v>56306</v>
       </c>
+      <c r="Q53" s="2">
+        <v>6551</v>
+      </c>
       <c r="R53" s="2">
-        <v>6551</v>
+        <v>0</v>
       </c>
       <c r="S53" s="2">
-        <v>0</v>
-      </c>
-      <c r="T53" s="2">
         <v>5</v>
       </c>
     </row>
-    <row r="54" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A54">
         <v>51</v>
       </c>
       <c r="B54" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C54">
         <v>20758</v>
@@ -3917,16 +3765,16 @@
         <v>0</v>
       </c>
       <c r="E54">
-        <v>0</v>
+        <v>20758</v>
       </c>
       <c r="F54">
+        <v>0</v>
+      </c>
+      <c r="G54">
         <v>20758</v>
       </c>
-      <c r="G54">
-        <v>0</v>
-      </c>
       <c r="H54">
-        <v>20758</v>
+        <v>0</v>
       </c>
       <c r="I54">
         <v>0</v>
@@ -3938,39 +3786,36 @@
         <v>0</v>
       </c>
       <c r="L54">
-        <v>0</v>
+        <v>2603</v>
       </c>
       <c r="M54">
-        <v>2603</v>
+        <v>5</v>
       </c>
       <c r="N54">
-        <v>5</v>
+        <v>391</v>
       </c>
       <c r="O54">
-        <v>391</v>
+        <v>20367</v>
       </c>
       <c r="P54">
-        <v>20367</v>
-      </c>
-      <c r="Q54">
         <v>58440</v>
       </c>
+      <c r="Q54" s="2">
+        <v>7347</v>
+      </c>
       <c r="R54" s="2">
-        <v>7347</v>
+        <v>0</v>
       </c>
       <c r="S54" s="2">
-        <v>0</v>
-      </c>
-      <c r="T54" s="2">
         <v>1</v>
       </c>
     </row>
-    <row r="55" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A55">
         <v>52</v>
       </c>
       <c r="B55" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C55">
         <v>16022</v>
@@ -3979,16 +3824,16 @@
         <v>0</v>
       </c>
       <c r="E55">
-        <v>0</v>
+        <v>16022</v>
       </c>
       <c r="F55">
+        <v>0</v>
+      </c>
+      <c r="G55">
         <v>16022</v>
       </c>
-      <c r="G55">
-        <v>0</v>
-      </c>
       <c r="H55">
-        <v>16022</v>
+        <v>0</v>
       </c>
       <c r="I55">
         <v>0</v>
@@ -4000,39 +3845,36 @@
         <v>0</v>
       </c>
       <c r="L55">
-        <v>0</v>
+        <v>2109</v>
       </c>
       <c r="M55">
-        <v>2109</v>
+        <v>1</v>
       </c>
       <c r="N55">
-        <v>1</v>
+        <v>129</v>
       </c>
       <c r="O55">
-        <v>129</v>
+        <v>15893</v>
       </c>
       <c r="P55">
-        <v>15893</v>
-      </c>
-      <c r="Q55">
         <v>58215</v>
       </c>
+      <c r="Q55" s="2">
+        <v>5098</v>
+      </c>
       <c r="R55" s="2">
-        <v>5098</v>
+        <v>0</v>
       </c>
       <c r="S55" s="2">
         <v>0</v>
       </c>
-      <c r="T55" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="56" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="56" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A56">
         <v>53</v>
       </c>
       <c r="B56" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C56">
         <v>19256</v>
@@ -4041,16 +3883,16 @@
         <v>0</v>
       </c>
       <c r="E56">
-        <v>0</v>
+        <v>19256</v>
       </c>
       <c r="F56">
+        <v>0</v>
+      </c>
+      <c r="G56">
         <v>19256</v>
       </c>
-      <c r="G56">
-        <v>0</v>
-      </c>
       <c r="H56">
-        <v>19256</v>
+        <v>0</v>
       </c>
       <c r="I56">
         <v>0</v>
@@ -4062,39 +3904,36 @@
         <v>0</v>
       </c>
       <c r="L56">
-        <v>0</v>
+        <v>4091</v>
       </c>
       <c r="M56">
-        <v>4091</v>
+        <v>3</v>
       </c>
       <c r="N56">
-        <v>3</v>
+        <v>451</v>
       </c>
       <c r="O56">
-        <v>451</v>
+        <v>18805</v>
       </c>
       <c r="P56">
-        <v>18805</v>
-      </c>
-      <c r="Q56">
         <v>47621</v>
       </c>
+      <c r="Q56" s="2">
+        <v>4882</v>
+      </c>
       <c r="R56" s="2">
-        <v>4882</v>
+        <v>0</v>
       </c>
       <c r="S56" s="2">
-        <v>0</v>
-      </c>
-      <c r="T56" s="2">
         <v>30</v>
       </c>
     </row>
-    <row r="57" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A57">
         <v>54</v>
       </c>
       <c r="B57" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C57">
         <v>21240</v>
@@ -4103,16 +3942,16 @@
         <v>0</v>
       </c>
       <c r="E57">
-        <v>0</v>
+        <v>21240</v>
       </c>
       <c r="F57">
+        <v>0</v>
+      </c>
+      <c r="G57">
         <v>21240</v>
       </c>
-      <c r="G57">
-        <v>0</v>
-      </c>
       <c r="H57">
-        <v>21240</v>
+        <v>0</v>
       </c>
       <c r="I57">
         <v>0</v>
@@ -4124,39 +3963,36 @@
         <v>0</v>
       </c>
       <c r="L57">
-        <v>0</v>
+        <v>1905</v>
       </c>
       <c r="M57">
-        <v>1905</v>
+        <v>5</v>
       </c>
       <c r="N57">
-        <v>5</v>
+        <v>39</v>
       </c>
       <c r="O57">
-        <v>39</v>
+        <v>21201</v>
       </c>
       <c r="P57">
-        <v>21201</v>
-      </c>
-      <c r="Q57">
         <v>61556</v>
       </c>
+      <c r="Q57" s="2">
+        <v>6870</v>
+      </c>
       <c r="R57" s="2">
-        <v>6870</v>
+        <v>0</v>
       </c>
       <c r="S57" s="2">
         <v>0</v>
       </c>
-      <c r="T57" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="58" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="58" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A58">
         <v>55</v>
       </c>
       <c r="B58" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C58">
         <v>22819</v>
@@ -4165,16 +4001,16 @@
         <v>0</v>
       </c>
       <c r="E58">
-        <v>0</v>
+        <v>22819</v>
       </c>
       <c r="F58">
+        <v>0</v>
+      </c>
+      <c r="G58">
         <v>22819</v>
       </c>
-      <c r="G58">
-        <v>0</v>
-      </c>
       <c r="H58">
-        <v>22819</v>
+        <v>0</v>
       </c>
       <c r="I58">
         <v>0</v>
@@ -4186,39 +4022,36 @@
         <v>0</v>
       </c>
       <c r="L58">
-        <v>0</v>
+        <v>8123</v>
       </c>
       <c r="M58">
-        <v>8123</v>
+        <v>10</v>
       </c>
       <c r="N58">
-        <v>10</v>
+        <v>552</v>
       </c>
       <c r="O58">
-        <v>552</v>
+        <v>22267</v>
       </c>
       <c r="P58">
-        <v>22267</v>
-      </c>
-      <c r="Q58">
         <v>57577</v>
       </c>
+      <c r="Q58" s="2">
+        <v>8884</v>
+      </c>
       <c r="R58" s="2">
-        <v>8884</v>
+        <v>0</v>
       </c>
       <c r="S58" s="2">
-        <v>0</v>
-      </c>
-      <c r="T58" s="2">
         <v>64</v>
       </c>
     </row>
-    <row r="59" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A59">
         <v>56</v>
       </c>
       <c r="B59" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C59">
         <v>18776</v>
@@ -4227,16 +4060,16 @@
         <v>0</v>
       </c>
       <c r="E59">
-        <v>0</v>
+        <v>18776</v>
       </c>
       <c r="F59">
+        <v>0</v>
+      </c>
+      <c r="G59">
         <v>18776</v>
       </c>
-      <c r="G59">
-        <v>0</v>
-      </c>
       <c r="H59">
-        <v>18776</v>
+        <v>0</v>
       </c>
       <c r="I59">
         <v>0</v>
@@ -4248,39 +4081,36 @@
         <v>0</v>
       </c>
       <c r="L59">
-        <v>0</v>
+        <v>2506</v>
       </c>
       <c r="M59">
-        <v>2506</v>
+        <v>2</v>
       </c>
       <c r="N59">
-        <v>2</v>
+        <v>287</v>
       </c>
       <c r="O59">
-        <v>287</v>
+        <v>18489</v>
       </c>
       <c r="P59">
-        <v>18489</v>
-      </c>
-      <c r="Q59">
         <v>60495</v>
       </c>
+      <c r="Q59" s="2">
+        <v>8028</v>
+      </c>
       <c r="R59" s="2">
-        <v>8028</v>
+        <v>0</v>
       </c>
       <c r="S59" s="2">
-        <v>0</v>
-      </c>
-      <c r="T59" s="2">
         <v>27</v>
       </c>
     </row>
-    <row r="60" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A60">
         <v>57</v>
       </c>
       <c r="B60" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C60">
         <v>23749</v>
@@ -4289,16 +4119,16 @@
         <v>0</v>
       </c>
       <c r="E60">
-        <v>0</v>
+        <v>23749</v>
       </c>
       <c r="F60">
+        <v>0</v>
+      </c>
+      <c r="G60">
         <v>23749</v>
       </c>
-      <c r="G60">
-        <v>0</v>
-      </c>
       <c r="H60">
-        <v>23749</v>
+        <v>0</v>
       </c>
       <c r="I60">
         <v>0</v>
@@ -4310,39 +4140,36 @@
         <v>0</v>
       </c>
       <c r="L60">
-        <v>0</v>
+        <v>5815</v>
       </c>
       <c r="M60">
-        <v>5815</v>
+        <v>9</v>
       </c>
       <c r="N60">
-        <v>9</v>
+        <v>324</v>
       </c>
       <c r="O60">
-        <v>324</v>
+        <v>23425</v>
       </c>
       <c r="P60">
-        <v>23425</v>
-      </c>
-      <c r="Q60">
         <v>70140</v>
       </c>
+      <c r="Q60" s="2">
+        <v>7415</v>
+      </c>
       <c r="R60" s="2">
-        <v>7415</v>
+        <v>0</v>
       </c>
       <c r="S60" s="2">
-        <v>0</v>
-      </c>
-      <c r="T60" s="2">
         <v>32</v>
       </c>
     </row>
-    <row r="61" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A61">
         <v>58</v>
       </c>
       <c r="B61" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C61">
         <v>22069</v>
@@ -4351,16 +4178,16 @@
         <v>0</v>
       </c>
       <c r="E61">
-        <v>0</v>
+        <v>22069</v>
       </c>
       <c r="F61">
+        <v>0</v>
+      </c>
+      <c r="G61">
         <v>22069</v>
       </c>
-      <c r="G61">
-        <v>0</v>
-      </c>
       <c r="H61">
-        <v>22069</v>
+        <v>0</v>
       </c>
       <c r="I61">
         <v>0</v>
@@ -4372,39 +4199,36 @@
         <v>0</v>
       </c>
       <c r="L61">
-        <v>0</v>
+        <v>9977</v>
       </c>
       <c r="M61">
-        <v>9977</v>
+        <v>37</v>
       </c>
       <c r="N61">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="O61">
-        <v>36</v>
+        <v>22033</v>
       </c>
       <c r="P61">
-        <v>22033</v>
-      </c>
-      <c r="Q61">
         <v>55240</v>
       </c>
+      <c r="Q61" s="2">
+        <v>7927</v>
+      </c>
       <c r="R61" s="2">
-        <v>7927</v>
+        <v>1</v>
       </c>
       <c r="S61" s="2">
-        <v>1</v>
-      </c>
-      <c r="T61" s="2">
         <v>268</v>
       </c>
     </row>
-    <row r="62" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A62">
         <v>59</v>
       </c>
       <c r="B62" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C62">
         <v>15800</v>
@@ -4413,16 +4237,16 @@
         <v>0</v>
       </c>
       <c r="E62">
-        <v>0</v>
+        <v>15800</v>
       </c>
       <c r="F62">
+        <v>0</v>
+      </c>
+      <c r="G62">
         <v>15800</v>
       </c>
-      <c r="G62">
-        <v>0</v>
-      </c>
       <c r="H62">
-        <v>15800</v>
+        <v>0</v>
       </c>
       <c r="I62">
         <v>0</v>
@@ -4434,39 +4258,36 @@
         <v>0</v>
       </c>
       <c r="L62">
-        <v>0</v>
+        <v>4214</v>
       </c>
       <c r="M62">
-        <v>4214</v>
+        <v>19</v>
       </c>
       <c r="N62">
-        <v>19</v>
+        <v>494</v>
       </c>
       <c r="O62">
-        <v>494</v>
+        <v>15306</v>
       </c>
       <c r="P62">
-        <v>15306</v>
-      </c>
-      <c r="Q62">
         <v>51334</v>
       </c>
+      <c r="Q62" s="2">
+        <v>6917</v>
+      </c>
       <c r="R62" s="2">
-        <v>6917</v>
+        <v>0</v>
       </c>
       <c r="S62" s="2">
-        <v>0</v>
-      </c>
-      <c r="T62" s="2">
         <v>100</v>
       </c>
     </row>
-    <row r="63" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A63">
         <v>60</v>
       </c>
       <c r="B63" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C63">
         <v>36754</v>
@@ -4475,16 +4296,16 @@
         <v>0</v>
       </c>
       <c r="E63">
-        <v>0</v>
+        <v>36754</v>
       </c>
       <c r="F63">
+        <v>0</v>
+      </c>
+      <c r="G63">
         <v>36754</v>
       </c>
-      <c r="G63">
-        <v>0</v>
-      </c>
       <c r="H63">
-        <v>36754</v>
+        <v>0</v>
       </c>
       <c r="I63">
         <v>0</v>
@@ -4496,39 +4317,36 @@
         <v>0</v>
       </c>
       <c r="L63">
-        <v>0</v>
+        <v>10975</v>
       </c>
       <c r="M63">
-        <v>10975</v>
+        <v>68</v>
       </c>
       <c r="N63">
-        <v>68</v>
+        <v>931</v>
       </c>
       <c r="O63">
-        <v>931</v>
+        <v>35823</v>
       </c>
       <c r="P63">
-        <v>35823</v>
-      </c>
-      <c r="Q63">
         <v>68696</v>
       </c>
+      <c r="Q63" s="2">
+        <v>9766</v>
+      </c>
       <c r="R63" s="2">
-        <v>9766</v>
+        <v>0</v>
       </c>
       <c r="S63" s="2">
-        <v>0</v>
-      </c>
-      <c r="T63" s="2">
         <v>153</v>
       </c>
     </row>
-    <row r="64" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A64">
         <v>61</v>
       </c>
       <c r="B64" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C64">
         <v>42048</v>
@@ -4537,16 +4355,16 @@
         <v>0</v>
       </c>
       <c r="E64">
-        <v>0</v>
+        <v>42048</v>
       </c>
       <c r="F64">
+        <v>0</v>
+      </c>
+      <c r="G64">
         <v>42048</v>
       </c>
-      <c r="G64">
-        <v>0</v>
-      </c>
       <c r="H64">
-        <v>42048</v>
+        <v>0</v>
       </c>
       <c r="I64">
         <v>0</v>
@@ -4558,39 +4376,36 @@
         <v>0</v>
       </c>
       <c r="L64">
-        <v>0</v>
+        <v>9887</v>
       </c>
       <c r="M64">
-        <v>9887</v>
+        <v>8</v>
       </c>
       <c r="N64">
-        <v>8</v>
+        <v>493</v>
       </c>
       <c r="O64">
-        <v>493</v>
+        <v>41555</v>
       </c>
       <c r="P64">
-        <v>41555</v>
-      </c>
-      <c r="Q64">
         <v>60527</v>
       </c>
+      <c r="Q64" s="2">
+        <v>5985</v>
+      </c>
       <c r="R64" s="2">
-        <v>5985</v>
+        <v>0</v>
       </c>
       <c r="S64" s="2">
-        <v>0</v>
-      </c>
-      <c r="T64" s="2">
         <v>101</v>
       </c>
     </row>
-    <row r="65" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A65">
         <v>62</v>
       </c>
       <c r="B65" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C65">
         <v>41389</v>
@@ -4599,16 +4414,16 @@
         <v>0</v>
       </c>
       <c r="E65">
-        <v>0</v>
+        <v>41389</v>
       </c>
       <c r="F65">
+        <v>0</v>
+      </c>
+      <c r="G65">
         <v>41389</v>
       </c>
-      <c r="G65">
-        <v>0</v>
-      </c>
       <c r="H65">
-        <v>41389</v>
+        <v>0</v>
       </c>
       <c r="I65">
         <v>0</v>
@@ -4620,39 +4435,36 @@
         <v>0</v>
       </c>
       <c r="L65">
-        <v>0</v>
+        <v>13582</v>
       </c>
       <c r="M65">
-        <v>13582</v>
+        <v>2</v>
       </c>
       <c r="N65">
-        <v>2</v>
+        <v>2635</v>
       </c>
       <c r="O65">
-        <v>2635</v>
+        <v>38754</v>
       </c>
       <c r="P65">
-        <v>38754</v>
-      </c>
-      <c r="Q65">
         <v>58527</v>
       </c>
+      <c r="Q65" s="2">
+        <v>13282</v>
+      </c>
       <c r="R65" s="2">
-        <v>13282</v>
+        <v>0</v>
       </c>
       <c r="S65" s="2">
-        <v>0</v>
-      </c>
-      <c r="T65" s="2">
         <v>138</v>
       </c>
     </row>
-    <row r="66" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A66">
         <v>63</v>
       </c>
       <c r="B66" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C66">
         <v>67362</v>
@@ -4661,16 +4473,16 @@
         <v>0</v>
       </c>
       <c r="E66">
-        <v>1</v>
+        <v>67362</v>
       </c>
       <c r="F66">
+        <v>0</v>
+      </c>
+      <c r="G66">
         <v>67362</v>
       </c>
-      <c r="G66">
-        <v>0</v>
-      </c>
       <c r="H66">
-        <v>67362</v>
+        <v>0</v>
       </c>
       <c r="I66">
         <v>0</v>
@@ -4682,39 +4494,36 @@
         <v>0</v>
       </c>
       <c r="L66">
-        <v>0</v>
+        <v>13733</v>
       </c>
       <c r="M66">
-        <v>13733</v>
+        <v>2</v>
       </c>
       <c r="N66">
-        <v>2</v>
+        <v>4022</v>
       </c>
       <c r="O66">
-        <v>4022</v>
+        <v>63341</v>
       </c>
       <c r="P66">
-        <v>63341</v>
-      </c>
-      <c r="Q66">
         <v>93810</v>
       </c>
+      <c r="Q66" s="2">
+        <v>17742</v>
+      </c>
       <c r="R66" s="2">
-        <v>17742</v>
+        <v>0</v>
       </c>
       <c r="S66" s="2">
-        <v>0</v>
-      </c>
-      <c r="T66" s="2">
         <v>52</v>
       </c>
     </row>
-    <row r="67" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A67">
         <v>64</v>
       </c>
       <c r="B67" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C67">
         <v>68828</v>
@@ -4723,16 +4532,16 @@
         <v>0</v>
       </c>
       <c r="E67">
-        <v>0</v>
+        <v>68828</v>
       </c>
       <c r="F67">
+        <v>0</v>
+      </c>
+      <c r="G67">
         <v>68828</v>
       </c>
-      <c r="G67">
-        <v>0</v>
-      </c>
       <c r="H67">
-        <v>68828</v>
+        <v>0</v>
       </c>
       <c r="I67">
         <v>0</v>
@@ -4744,39 +4553,36 @@
         <v>0</v>
       </c>
       <c r="L67">
-        <v>0</v>
+        <v>19495</v>
       </c>
       <c r="M67">
-        <v>19495</v>
+        <v>10</v>
       </c>
       <c r="N67">
-        <v>10</v>
+        <v>3644</v>
       </c>
       <c r="O67">
-        <v>3644</v>
+        <v>65185</v>
       </c>
       <c r="P67">
-        <v>65185</v>
-      </c>
-      <c r="Q67">
         <v>78032</v>
       </c>
+      <c r="Q67" s="2">
+        <v>9807</v>
+      </c>
       <c r="R67" s="2">
-        <v>9807</v>
+        <v>0</v>
       </c>
       <c r="S67" s="2">
-        <v>0</v>
-      </c>
-      <c r="T67" s="2">
         <v>116</v>
       </c>
     </row>
-    <row r="68" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A68">
         <v>65</v>
       </c>
       <c r="B68" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C68">
         <v>65397</v>
@@ -4785,16 +4591,16 @@
         <v>0</v>
       </c>
       <c r="E68">
-        <v>0</v>
+        <v>65397</v>
       </c>
       <c r="F68">
+        <v>0</v>
+      </c>
+      <c r="G68">
         <v>65397</v>
       </c>
-      <c r="G68">
-        <v>0</v>
-      </c>
       <c r="H68">
-        <v>65397</v>
+        <v>0</v>
       </c>
       <c r="I68">
         <v>0</v>
@@ -4806,39 +4612,36 @@
         <v>0</v>
       </c>
       <c r="L68">
-        <v>0</v>
+        <v>18679</v>
       </c>
       <c r="M68">
-        <v>18679</v>
+        <v>2</v>
       </c>
       <c r="N68">
-        <v>2</v>
+        <v>1603</v>
       </c>
       <c r="O68">
-        <v>1603</v>
+        <v>63795</v>
       </c>
       <c r="P68">
-        <v>63795</v>
-      </c>
-      <c r="Q68">
         <v>71325</v>
       </c>
+      <c r="Q68" s="2">
+        <v>7850</v>
+      </c>
       <c r="R68" s="2">
-        <v>7850</v>
+        <v>0</v>
       </c>
       <c r="S68" s="2">
-        <v>0</v>
-      </c>
-      <c r="T68" s="2">
         <v>26</v>
       </c>
     </row>
-    <row r="69" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A69">
         <v>66</v>
       </c>
       <c r="B69" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C69">
         <v>43938</v>
@@ -4847,16 +4650,16 @@
         <v>0</v>
       </c>
       <c r="E69">
-        <v>0</v>
+        <v>43938</v>
       </c>
       <c r="F69">
+        <v>0</v>
+      </c>
+      <c r="G69">
         <v>43938</v>
       </c>
-      <c r="G69">
-        <v>0</v>
-      </c>
       <c r="H69">
-        <v>43938</v>
+        <v>0</v>
       </c>
       <c r="I69">
         <v>0</v>
@@ -4868,39 +4671,36 @@
         <v>0</v>
       </c>
       <c r="L69">
-        <v>0</v>
+        <v>18216</v>
       </c>
       <c r="M69">
-        <v>18216</v>
+        <v>2</v>
       </c>
       <c r="N69">
-        <v>2</v>
+        <v>2619</v>
       </c>
       <c r="O69">
-        <v>2619</v>
+        <v>41322</v>
       </c>
       <c r="P69">
-        <v>41322</v>
-      </c>
-      <c r="Q69">
         <v>36118</v>
       </c>
+      <c r="Q69" s="2">
+        <v>6528</v>
+      </c>
       <c r="R69" s="2">
-        <v>6528</v>
+        <v>0</v>
       </c>
       <c r="S69" s="2">
-        <v>0</v>
-      </c>
-      <c r="T69" s="2">
         <v>47</v>
       </c>
     </row>
-    <row r="70" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A70">
         <v>67</v>
       </c>
       <c r="B70" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C70">
         <v>47711</v>
@@ -4909,16 +4709,16 @@
         <v>0</v>
       </c>
       <c r="E70">
-        <v>0</v>
+        <v>47711</v>
       </c>
       <c r="F70">
+        <v>0</v>
+      </c>
+      <c r="G70">
         <v>47711</v>
       </c>
-      <c r="G70">
-        <v>0</v>
-      </c>
       <c r="H70">
-        <v>47711</v>
+        <v>0</v>
       </c>
       <c r="I70">
         <v>0</v>
@@ -4930,39 +4730,36 @@
         <v>0</v>
       </c>
       <c r="L70">
-        <v>0</v>
+        <v>18275</v>
       </c>
       <c r="M70">
-        <v>18275</v>
+        <v>2</v>
       </c>
       <c r="N70">
-        <v>2</v>
+        <v>3246</v>
       </c>
       <c r="O70">
-        <v>3246</v>
+        <v>44466</v>
       </c>
       <c r="P70">
-        <v>44466</v>
-      </c>
-      <c r="Q70">
         <v>42051</v>
       </c>
+      <c r="Q70" s="2">
+        <v>5798</v>
+      </c>
       <c r="R70" s="2">
-        <v>5798</v>
+        <v>0</v>
       </c>
       <c r="S70" s="2">
-        <v>0</v>
-      </c>
-      <c r="T70" s="2">
         <v>29</v>
       </c>
     </row>
-    <row r="71" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A71">
         <v>68</v>
       </c>
       <c r="B71" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C71">
         <v>50963</v>
@@ -4971,16 +4768,16 @@
         <v>0</v>
       </c>
       <c r="E71">
-        <v>0</v>
+        <v>50963</v>
       </c>
       <c r="F71">
+        <v>0</v>
+      </c>
+      <c r="G71">
         <v>50963</v>
       </c>
-      <c r="G71">
-        <v>0</v>
-      </c>
       <c r="H71">
-        <v>50963</v>
+        <v>0</v>
       </c>
       <c r="I71">
         <v>0</v>
@@ -4992,39 +4789,36 @@
         <v>0</v>
       </c>
       <c r="L71">
-        <v>0</v>
+        <v>22851</v>
       </c>
       <c r="M71">
-        <v>22851</v>
+        <v>1</v>
       </c>
       <c r="N71">
-        <v>1</v>
+        <v>4449</v>
       </c>
       <c r="O71">
-        <v>4449</v>
+        <v>46514</v>
       </c>
       <c r="P71">
-        <v>46514</v>
-      </c>
-      <c r="Q71">
         <v>49140</v>
       </c>
+      <c r="Q71" s="2">
+        <v>6782</v>
+      </c>
       <c r="R71" s="2">
-        <v>6782</v>
+        <v>0</v>
       </c>
       <c r="S71" s="2">
-        <v>0</v>
-      </c>
-      <c r="T71" s="2">
         <v>235</v>
       </c>
     </row>
-    <row r="72" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A72">
         <v>69</v>
       </c>
       <c r="B72" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C72">
         <v>61543</v>
@@ -5033,16 +4827,16 @@
         <v>0</v>
       </c>
       <c r="E72">
-        <v>0</v>
+        <v>61543</v>
       </c>
       <c r="F72">
+        <v>0</v>
+      </c>
+      <c r="G72">
         <v>61543</v>
       </c>
-      <c r="G72">
-        <v>0</v>
-      </c>
       <c r="H72">
-        <v>61543</v>
+        <v>0</v>
       </c>
       <c r="I72">
         <v>0</v>
@@ -5054,39 +4848,36 @@
         <v>0</v>
       </c>
       <c r="L72">
-        <v>0</v>
+        <v>17245</v>
       </c>
       <c r="M72">
-        <v>17245</v>
+        <v>9</v>
       </c>
       <c r="N72">
-        <v>9</v>
+        <v>3667</v>
       </c>
       <c r="O72">
-        <v>3667</v>
+        <v>57877</v>
       </c>
       <c r="P72">
-        <v>57877</v>
-      </c>
-      <c r="Q72">
         <v>85505</v>
       </c>
+      <c r="Q72" s="2">
+        <v>12340</v>
+      </c>
       <c r="R72" s="2">
-        <v>12340</v>
+        <v>0</v>
       </c>
       <c r="S72" s="2">
-        <v>0</v>
-      </c>
-      <c r="T72" s="2">
         <v>79</v>
       </c>
     </row>
-    <row r="73" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A73">
         <v>70</v>
       </c>
       <c r="B73" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C73">
         <v>58915</v>
@@ -5095,16 +4886,16 @@
         <v>0</v>
       </c>
       <c r="E73">
-        <v>0</v>
+        <v>58915</v>
       </c>
       <c r="F73">
+        <v>0</v>
+      </c>
+      <c r="G73">
         <v>58915</v>
       </c>
-      <c r="G73">
-        <v>0</v>
-      </c>
       <c r="H73">
-        <v>58915</v>
+        <v>0</v>
       </c>
       <c r="I73">
         <v>0</v>
@@ -5116,36 +4907,33 @@
         <v>0</v>
       </c>
       <c r="L73">
-        <v>0</v>
+        <v>15131</v>
       </c>
       <c r="M73">
-        <v>15131</v>
+        <v>8</v>
       </c>
       <c r="N73">
-        <v>8</v>
+        <v>3866</v>
       </c>
       <c r="O73">
-        <v>3866</v>
+        <v>55049</v>
       </c>
       <c r="P73">
-        <v>55049</v>
-      </c>
-      <c r="Q73">
         <v>67666</v>
       </c>
+      <c r="Q73" s="2">
+        <v>10010</v>
+      </c>
       <c r="R73" s="2">
-        <v>10010</v>
+        <v>0</v>
       </c>
       <c r="S73" s="2">
-        <v>0</v>
-      </c>
-      <c r="T73" s="2">
         <v>74</v>
       </c>
     </row>
-    <row r="74" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A74" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B74" s="1"/>
       <c r="C74">
@@ -5155,16 +4943,16 @@
         <v>0</v>
       </c>
       <c r="E74">
-        <v>9</v>
+        <v>2430387</v>
       </c>
       <c r="F74">
-        <v>2430387</v>
+        <v>0</v>
       </c>
       <c r="G74">
-        <v>0</v>
+        <v>2430385</v>
       </c>
       <c r="H74">
-        <v>2430385</v>
+        <v>0</v>
       </c>
       <c r="I74">
         <v>0</v>
@@ -5176,54 +4964,48 @@
         <v>0</v>
       </c>
       <c r="L74">
-        <v>0</v>
+        <v>625577</v>
       </c>
       <c r="M74">
-        <v>625577</v>
+        <v>8318</v>
       </c>
       <c r="N74">
-        <v>8318</v>
+        <v>97020</v>
       </c>
       <c r="O74">
-        <v>97020</v>
+        <v>2331382</v>
       </c>
       <c r="P74">
-        <v>2331382</v>
-      </c>
-      <c r="Q74">
         <v>4701905</v>
       </c>
+      <c r="Q74" s="2">
+        <v>626236</v>
+      </c>
       <c r="R74" s="2">
-        <v>626236</v>
+        <v>1</v>
       </c>
       <c r="S74" s="2">
-        <v>1</v>
-      </c>
-      <c r="T74" s="2">
         <v>3445</v>
       </c>
     </row>
-    <row r="75" spans="1:20" ht="15.75" x14ac:dyDescent="0.25"/>
-    <row r="76" spans="1:20" ht="15.75" x14ac:dyDescent="0.25"/>
   </sheetData>
-  <mergeCells count="13">
+  <mergeCells count="12">
     <mergeCell ref="A74:B74"/>
-    <mergeCell ref="R2:T2"/>
-    <mergeCell ref="A1:R1"/>
+    <mergeCell ref="Q2:S2"/>
+    <mergeCell ref="A1:Q1"/>
     <mergeCell ref="A2:A3"/>
     <mergeCell ref="B2:B3"/>
     <mergeCell ref="C2:C3"/>
     <mergeCell ref="D2:D3"/>
     <mergeCell ref="E2:E3"/>
     <mergeCell ref="F2:F3"/>
-    <mergeCell ref="G2:G3"/>
-    <mergeCell ref="H2:J2"/>
-    <mergeCell ref="K2:N2"/>
-    <mergeCell ref="O2:Q2"/>
+    <mergeCell ref="G2:I2"/>
+    <mergeCell ref="J2:M2"/>
+    <mergeCell ref="N2:P2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="A2:Q74 B1:Q1" numberStoredAsText="1"/>
+    <ignoredError sqref="A2:D74 E1:P74 B1:D1" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/Notice.xlsx
+++ b/Notice.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Downloads\New folder (13)\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1BF1B861-80EF-4E49-88C4-BD7C76C0A793}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5DC66D63-0804-45CF-8723-2DC1A5326DD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -292,6 +292,9 @@
     <t>Total</t>
   </si>
   <si>
+    <t>Notice &amp; Hearing Report Last Updated On : 25-09-2026 09:56:41</t>
+  </si>
+  <si>
     <t>DSE with UP</t>
   </si>
   <si>
@@ -302,9 +305,6 @@
   </si>
   <si>
     <t>No Action Required</t>
-  </si>
-  <si>
-    <t>Notice &amp; Hearing Report 23-09-2026 09:56:43</t>
   </si>
 </sst>
 </file>
@@ -340,13 +340,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -689,12 +686,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:S74"/>
-  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:S76"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -713,23 +710,23 @@
       <c r="P1" s="1"/>
       <c r="Q1" s="1"/>
     </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A2" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="4" t="s">
+    <row r="2" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="C2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="D2" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="E2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F2" s="4" t="s">
+      <c r="F2" s="1" t="s">
         <v>5</v>
       </c>
       <c r="G2" s="1" t="s">
@@ -749,59 +746,59 @@
       <c r="O2" s="1"/>
       <c r="P2" s="1"/>
       <c r="Q2" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="R2" s="1"/>
       <c r="S2" s="1"/>
     </row>
-    <row r="3" spans="1:19" s="3" customFormat="1" ht="110.25" x14ac:dyDescent="0.25">
-      <c r="A3" s="4"/>
-      <c r="B3" s="4"/>
-      <c r="C3" s="4"/>
-      <c r="D3" s="4"/>
-      <c r="E3" s="4"/>
-      <c r="F3" s="4"/>
-      <c r="G3" s="3" t="s">
+    <row r="3" spans="1:19" ht="63" x14ac:dyDescent="0.25">
+      <c r="A3" s="1"/>
+      <c r="B3" s="1"/>
+      <c r="C3" s="1"/>
+      <c r="D3" s="1"/>
+      <c r="E3" s="1"/>
+      <c r="F3" s="1"/>
+      <c r="G3" t="s">
         <v>9</v>
       </c>
-      <c r="H3" s="3" t="s">
+      <c r="H3" t="s">
         <v>10</v>
       </c>
-      <c r="I3" s="3" t="s">
+      <c r="I3" t="s">
         <v>11</v>
       </c>
-      <c r="J3" s="3" t="s">
+      <c r="J3" t="s">
         <v>12</v>
       </c>
-      <c r="K3" s="3" t="s">
+      <c r="K3" t="s">
         <v>13</v>
       </c>
-      <c r="L3" s="3" t="s">
+      <c r="L3" t="s">
         <v>14</v>
       </c>
-      <c r="M3" s="3" t="s">
+      <c r="M3" t="s">
         <v>15</v>
       </c>
-      <c r="N3" s="3" t="s">
+      <c r="N3" t="s">
         <v>16</v>
       </c>
-      <c r="O3" s="3" t="s">
+      <c r="O3" t="s">
         <v>17</v>
       </c>
-      <c r="P3" s="3" t="s">
+      <c r="P3" t="s">
         <v>18</v>
       </c>
       <c r="Q3" s="3" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="R3" s="3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="S3" s="3" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.25">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>1</v>
       </c>
@@ -860,7 +857,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>2</v>
       </c>
@@ -919,7 +916,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>3</v>
       </c>
@@ -978,7 +975,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>4</v>
       </c>
@@ -1007,13 +1004,13 @@
         <v>0</v>
       </c>
       <c r="J7">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="K7">
         <v>0</v>
       </c>
       <c r="L7">
-        <v>5683</v>
+        <v>5690</v>
       </c>
       <c r="M7">
         <v>257</v>
@@ -1022,7 +1019,7 @@
         <v>1995</v>
       </c>
       <c r="O7">
-        <v>37266</v>
+        <v>37425</v>
       </c>
       <c r="P7">
         <v>77581</v>
@@ -1037,7 +1034,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>5</v>
       </c>
@@ -1081,7 +1078,7 @@
         <v>1874</v>
       </c>
       <c r="O8">
-        <v>38055</v>
+        <v>38100</v>
       </c>
       <c r="P8">
         <v>73458</v>
@@ -1096,7 +1093,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>6</v>
       </c>
@@ -1155,7 +1152,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>7</v>
       </c>
@@ -1214,7 +1211,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>8</v>
       </c>
@@ -1273,7 +1270,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>9</v>
       </c>
@@ -1332,7 +1329,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>10</v>
       </c>
@@ -1376,7 +1373,7 @@
         <v>3822</v>
       </c>
       <c r="O13">
-        <v>33195</v>
+        <v>33237</v>
       </c>
       <c r="P13">
         <v>56564</v>
@@ -1391,7 +1388,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>11</v>
       </c>
@@ -1450,7 +1447,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>12</v>
       </c>
@@ -1497,7 +1494,7 @@
         <v>39882</v>
       </c>
       <c r="P15">
-        <v>67178</v>
+        <v>67183</v>
       </c>
       <c r="Q15" s="2">
         <v>4859</v>
@@ -1509,7 +1506,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>13</v>
       </c>
@@ -1553,7 +1550,7 @@
         <v>261</v>
       </c>
       <c r="O16">
-        <v>25288</v>
+        <v>25289</v>
       </c>
       <c r="P16">
         <v>71673</v>
@@ -1568,7 +1565,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="17" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>14</v>
       </c>
@@ -1627,7 +1624,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="18" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>15</v>
       </c>
@@ -1671,10 +1668,10 @@
         <v>1969</v>
       </c>
       <c r="O18">
-        <v>45401</v>
+        <v>45854</v>
       </c>
       <c r="P18">
-        <v>71475</v>
+        <v>71494</v>
       </c>
       <c r="Q18" s="2">
         <v>6819</v>
@@ -1686,7 +1683,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="19" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>16</v>
       </c>
@@ -1745,7 +1742,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="20" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>17</v>
       </c>
@@ -1789,10 +1786,10 @@
         <v>546</v>
       </c>
       <c r="O20">
-        <v>34464</v>
+        <v>34465</v>
       </c>
       <c r="P20">
-        <v>75812</v>
+        <v>75814</v>
       </c>
       <c r="Q20" s="2">
         <v>8984</v>
@@ -1804,7 +1801,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="21" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>18</v>
       </c>
@@ -1863,7 +1860,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>19</v>
       </c>
@@ -1922,7 +1919,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>20</v>
       </c>
@@ -1981,7 +1978,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="24" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>21</v>
       </c>
@@ -2040,7 +2037,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>22</v>
       </c>
@@ -2099,7 +2096,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="26" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>23</v>
       </c>
@@ -2158,7 +2155,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="27" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>24</v>
       </c>
@@ -2217,7 +2214,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>25</v>
       </c>
@@ -2276,7 +2273,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="29" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>26</v>
       </c>
@@ -2335,7 +2332,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="30" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>27</v>
       </c>
@@ -2394,7 +2391,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="31" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>28</v>
       </c>
@@ -2453,7 +2450,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="32" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>29</v>
       </c>
@@ -2512,7 +2509,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>30</v>
       </c>
@@ -2571,7 +2568,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="34" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>31</v>
       </c>
@@ -2630,7 +2627,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>32</v>
       </c>
@@ -2689,7 +2686,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="36" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>33</v>
       </c>
@@ -2748,7 +2745,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="37" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>34</v>
       </c>
@@ -2807,7 +2804,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>35</v>
       </c>
@@ -2866,7 +2863,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>36</v>
       </c>
@@ -2925,7 +2922,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="40" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>37</v>
       </c>
@@ -2984,7 +2981,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="41" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>38</v>
       </c>
@@ -3043,7 +3040,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="42" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>39</v>
       </c>
@@ -3102,7 +3099,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="43" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>40</v>
       </c>
@@ -3161,7 +3158,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="44" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A44">
         <v>41</v>
       </c>
@@ -3220,7 +3217,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="45" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A45">
         <v>42</v>
       </c>
@@ -3279,7 +3276,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="46" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A46">
         <v>43</v>
       </c>
@@ -3338,7 +3335,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="47" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A47">
         <v>44</v>
       </c>
@@ -3382,10 +3379,10 @@
         <v>137</v>
       </c>
       <c r="O47">
-        <v>21624</v>
+        <v>22286</v>
       </c>
       <c r="P47">
-        <v>49875</v>
+        <v>50821</v>
       </c>
       <c r="Q47" s="2">
         <v>5046</v>
@@ -3397,7 +3394,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A48">
         <v>45</v>
       </c>
@@ -3426,7 +3423,7 @@
         <v>0</v>
       </c>
       <c r="J48">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K48">
         <v>0</v>
@@ -3438,13 +3435,13 @@
         <v>4</v>
       </c>
       <c r="N48">
-        <v>254</v>
+        <v>262</v>
       </c>
       <c r="O48">
-        <v>19350</v>
+        <v>19379</v>
       </c>
       <c r="P48">
-        <v>54142</v>
+        <v>54497</v>
       </c>
       <c r="Q48" s="2">
         <v>4623</v>
@@ -3456,7 +3453,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="49" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A49">
         <v>46</v>
       </c>
@@ -3500,7 +3497,7 @@
         <v>628</v>
       </c>
       <c r="O49">
-        <v>21024</v>
+        <v>21027</v>
       </c>
       <c r="P49">
         <v>55376</v>
@@ -3515,7 +3512,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="50" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A50">
         <v>47</v>
       </c>
@@ -3574,7 +3571,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="51" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A51">
         <v>48</v>
       </c>
@@ -3633,7 +3630,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="52" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A52">
         <v>49</v>
       </c>
@@ -3692,7 +3689,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="53" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A53">
         <v>50</v>
       </c>
@@ -3751,7 +3748,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="54" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A54">
         <v>51</v>
       </c>
@@ -3810,7 +3807,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="55" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A55">
         <v>52</v>
       </c>
@@ -3869,7 +3866,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A56">
         <v>53</v>
       </c>
@@ -3928,7 +3925,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="57" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A57">
         <v>54</v>
       </c>
@@ -3975,7 +3972,7 @@
         <v>21201</v>
       </c>
       <c r="P57">
-        <v>61556</v>
+        <v>61557</v>
       </c>
       <c r="Q57" s="2">
         <v>6870</v>
@@ -3987,7 +3984,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A58">
         <v>55</v>
       </c>
@@ -4046,7 +4043,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="59" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A59">
         <v>56</v>
       </c>
@@ -4105,7 +4102,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="60" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A60">
         <v>57</v>
       </c>
@@ -4164,7 +4161,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="61" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A61">
         <v>58</v>
       </c>
@@ -4223,7 +4220,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="62" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A62">
         <v>59</v>
       </c>
@@ -4282,7 +4279,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="63" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A63">
         <v>60</v>
       </c>
@@ -4329,7 +4326,7 @@
         <v>35823</v>
       </c>
       <c r="P63">
-        <v>68696</v>
+        <v>68699</v>
       </c>
       <c r="Q63" s="2">
         <v>9766</v>
@@ -4341,7 +4338,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="64" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A64">
         <v>61</v>
       </c>
@@ -4400,7 +4397,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="65" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A65">
         <v>62</v>
       </c>
@@ -4459,7 +4456,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="66" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A66">
         <v>63</v>
       </c>
@@ -4518,7 +4515,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="67" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A67">
         <v>64</v>
       </c>
@@ -4577,7 +4574,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="68" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A68">
         <v>65</v>
       </c>
@@ -4636,7 +4633,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="69" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A69">
         <v>66</v>
       </c>
@@ -4695,7 +4692,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="70" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A70">
         <v>67</v>
       </c>
@@ -4754,7 +4751,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="71" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A71">
         <v>68</v>
       </c>
@@ -4813,7 +4810,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="72" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A72">
         <v>69</v>
       </c>
@@ -4854,13 +4851,13 @@
         <v>9</v>
       </c>
       <c r="N72">
-        <v>3667</v>
+        <v>3668</v>
       </c>
       <c r="O72">
         <v>57877</v>
       </c>
       <c r="P72">
-        <v>85505</v>
+        <v>85504</v>
       </c>
       <c r="Q72" s="2">
         <v>12340</v>
@@ -4872,7 +4869,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="73" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A73">
         <v>70</v>
       </c>
@@ -4931,7 +4928,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="74" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A74" s="1" t="s">
         <v>89</v>
       </c>
@@ -4958,25 +4955,25 @@
         <v>0</v>
       </c>
       <c r="J74">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="K74">
         <v>0</v>
       </c>
       <c r="L74">
-        <v>625577</v>
+        <v>625584</v>
       </c>
       <c r="M74">
         <v>8318</v>
       </c>
       <c r="N74">
-        <v>97020</v>
+        <v>97029</v>
       </c>
       <c r="O74">
-        <v>2331382</v>
+        <v>2332777</v>
       </c>
       <c r="P74">
-        <v>4701905</v>
+        <v>4703235</v>
       </c>
       <c r="Q74" s="2">
         <v>626236</v>
@@ -4988,6 +4985,8 @@
         <v>3445</v>
       </c>
     </row>
+    <row r="75" spans="1:19" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="76" spans="1:19" ht="15.75" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="12">
     <mergeCell ref="A74:B74"/>

--- a/Notice.xlsx
+++ b/Notice.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Downloads\New folder (13)\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5DC66D63-0804-45CF-8723-2DC1A5326DD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95F9C41C-55FD-4AB9-BA2F-89EB7B848A89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -292,9 +292,6 @@
     <t>Total</t>
   </si>
   <si>
-    <t>Notice &amp; Hearing Report Last Updated On : 25-09-2026 09:56:41</t>
-  </si>
-  <si>
     <t>DSE with UP</t>
   </si>
   <si>
@@ -305,6 +302,9 @@
   </si>
   <si>
     <t>No Action Required</t>
+  </si>
+  <si>
+    <t>Notice &amp; Hearing Report 28-09-2026 09:56:41</t>
   </si>
 </sst>
 </file>
@@ -686,12 +686,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:S76"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:S74"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -710,7 +710,7 @@
       <c r="P1" s="1"/>
       <c r="Q1" s="1"/>
     </row>
-    <row r="2" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -746,7 +746,7 @@
       <c r="O2" s="1"/>
       <c r="P2" s="1"/>
       <c r="Q2" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="R2" s="1"/>
       <c r="S2" s="1"/>
@@ -789,16 +789,16 @@
         <v>18</v>
       </c>
       <c r="Q3" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="R3" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="R3" s="3" t="s">
+      <c r="S3" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="S3" s="3" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="4" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="4" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>1</v>
       </c>
@@ -857,7 +857,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>2</v>
       </c>
@@ -916,7 +916,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="6" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>3</v>
       </c>
@@ -951,16 +951,16 @@
         <v>0</v>
       </c>
       <c r="L6">
-        <v>6075</v>
+        <v>6086</v>
       </c>
       <c r="M6">
         <v>201</v>
       </c>
       <c r="N6">
-        <v>1863</v>
+        <v>1870</v>
       </c>
       <c r="O6">
-        <v>37869</v>
+        <v>37903</v>
       </c>
       <c r="P6">
         <v>71989</v>
@@ -975,7 +975,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="7" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>4</v>
       </c>
@@ -1004,13 +1004,13 @@
         <v>0</v>
       </c>
       <c r="J7">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="K7">
         <v>0</v>
       </c>
       <c r="L7">
-        <v>5690</v>
+        <v>5733</v>
       </c>
       <c r="M7">
         <v>257</v>
@@ -1019,7 +1019,7 @@
         <v>1995</v>
       </c>
       <c r="O7">
-        <v>37425</v>
+        <v>37468</v>
       </c>
       <c r="P7">
         <v>77581</v>
@@ -1034,7 +1034,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="8" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>5</v>
       </c>
@@ -1069,16 +1069,16 @@
         <v>0</v>
       </c>
       <c r="L8">
-        <v>14288</v>
+        <v>14714</v>
       </c>
       <c r="M8">
         <v>164</v>
       </c>
       <c r="N8">
-        <v>1874</v>
+        <v>1981</v>
       </c>
       <c r="O8">
-        <v>38100</v>
+        <v>38571</v>
       </c>
       <c r="P8">
         <v>73458</v>
@@ -1093,7 +1093,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="9" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>6</v>
       </c>
@@ -1152,7 +1152,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="10" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>7</v>
       </c>
@@ -1211,7 +1211,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="11" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>8</v>
       </c>
@@ -1270,7 +1270,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="12" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>9</v>
       </c>
@@ -1311,7 +1311,7 @@
         <v>207</v>
       </c>
       <c r="N12">
-        <v>1133</v>
+        <v>1151</v>
       </c>
       <c r="O12">
         <v>39588</v>
@@ -1329,7 +1329,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="13" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>10</v>
       </c>
@@ -1388,7 +1388,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="14" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>11</v>
       </c>
@@ -1429,10 +1429,10 @@
         <v>1456</v>
       </c>
       <c r="N14">
-        <v>5864</v>
+        <v>5867</v>
       </c>
       <c r="O14">
-        <v>43096</v>
+        <v>43099</v>
       </c>
       <c r="P14">
         <v>77955</v>
@@ -1447,7 +1447,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="15" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>12</v>
       </c>
@@ -1506,7 +1506,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="16" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>13</v>
       </c>
@@ -1565,7 +1565,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="17" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>14</v>
       </c>
@@ -1624,7 +1624,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="18" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>15</v>
       </c>
@@ -1659,19 +1659,19 @@
         <v>0</v>
       </c>
       <c r="L18">
-        <v>7875</v>
+        <v>7876</v>
       </c>
       <c r="M18">
         <v>3</v>
       </c>
       <c r="N18">
-        <v>1969</v>
+        <v>1970</v>
       </c>
       <c r="O18">
-        <v>45854</v>
+        <v>45865</v>
       </c>
       <c r="P18">
-        <v>71494</v>
+        <v>71496</v>
       </c>
       <c r="Q18" s="2">
         <v>6819</v>
@@ -1683,7 +1683,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="19" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>16</v>
       </c>
@@ -1742,7 +1742,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="20" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>17</v>
       </c>
@@ -1786,7 +1786,7 @@
         <v>546</v>
       </c>
       <c r="O20">
-        <v>34465</v>
+        <v>34477</v>
       </c>
       <c r="P20">
         <v>75814</v>
@@ -1801,7 +1801,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="21" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>18</v>
       </c>
@@ -1860,7 +1860,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>19</v>
       </c>
@@ -1919,7 +1919,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>20</v>
       </c>
@@ -1978,7 +1978,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="24" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>21</v>
       </c>
@@ -2037,7 +2037,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>22</v>
       </c>
@@ -2096,7 +2096,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="26" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>23</v>
       </c>
@@ -2155,7 +2155,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="27" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>24</v>
       </c>
@@ -2214,7 +2214,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>25</v>
       </c>
@@ -2273,7 +2273,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="29" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>26</v>
       </c>
@@ -2332,7 +2332,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="30" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>27</v>
       </c>
@@ -2391,7 +2391,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="31" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>28</v>
       </c>
@@ -2450,7 +2450,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="32" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>29</v>
       </c>
@@ -2509,7 +2509,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>30</v>
       </c>
@@ -2568,7 +2568,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="34" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>31</v>
       </c>
@@ -2627,7 +2627,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>32</v>
       </c>
@@ -2668,13 +2668,13 @@
         <v>271</v>
       </c>
       <c r="N35">
-        <v>1129</v>
+        <v>1137</v>
       </c>
       <c r="O35">
-        <v>32436</v>
+        <v>32429</v>
       </c>
       <c r="P35">
-        <v>76464</v>
+        <v>76463</v>
       </c>
       <c r="Q35" s="2">
         <v>8879</v>
@@ -2686,7 +2686,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="36" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>33</v>
       </c>
@@ -2745,7 +2745,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="37" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>34</v>
       </c>
@@ -2804,7 +2804,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>35</v>
       </c>
@@ -2863,7 +2863,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>36</v>
       </c>
@@ -2922,7 +2922,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="40" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>37</v>
       </c>
@@ -2981,7 +2981,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="41" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>38</v>
       </c>
@@ -3040,7 +3040,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="42" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>39</v>
       </c>
@@ -3099,7 +3099,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="43" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>40</v>
       </c>
@@ -3158,7 +3158,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="44" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A44">
         <v>41</v>
       </c>
@@ -3217,7 +3217,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="45" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A45">
         <v>42</v>
       </c>
@@ -3276,7 +3276,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="46" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A46">
         <v>43</v>
       </c>
@@ -3335,7 +3335,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="47" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A47">
         <v>44</v>
       </c>
@@ -3379,7 +3379,7 @@
         <v>137</v>
       </c>
       <c r="O47">
-        <v>22286</v>
+        <v>22289</v>
       </c>
       <c r="P47">
         <v>50821</v>
@@ -3394,7 +3394,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A48">
         <v>45</v>
       </c>
@@ -3423,13 +3423,13 @@
         <v>0</v>
       </c>
       <c r="J48">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K48">
         <v>0</v>
       </c>
       <c r="L48">
-        <v>3799</v>
+        <v>3800</v>
       </c>
       <c r="M48">
         <v>4</v>
@@ -3438,7 +3438,7 @@
         <v>262</v>
       </c>
       <c r="O48">
-        <v>19379</v>
+        <v>19380</v>
       </c>
       <c r="P48">
         <v>54497</v>
@@ -3453,7 +3453,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="49" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A49">
         <v>46</v>
       </c>
@@ -3512,7 +3512,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="50" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A50">
         <v>47</v>
       </c>
@@ -3571,7 +3571,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="51" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A51">
         <v>48</v>
       </c>
@@ -3630,7 +3630,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="52" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A52">
         <v>49</v>
       </c>
@@ -3689,7 +3689,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="53" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A53">
         <v>50</v>
       </c>
@@ -3748,7 +3748,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="54" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A54">
         <v>51</v>
       </c>
@@ -3795,7 +3795,7 @@
         <v>20367</v>
       </c>
       <c r="P54">
-        <v>58440</v>
+        <v>58441</v>
       </c>
       <c r="Q54" s="2">
         <v>7347</v>
@@ -3807,7 +3807,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="55" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A55">
         <v>52</v>
       </c>
@@ -3866,7 +3866,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A56">
         <v>53</v>
       </c>
@@ -3925,7 +3925,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="57" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A57">
         <v>54</v>
       </c>
@@ -3984,7 +3984,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A58">
         <v>55</v>
       </c>
@@ -4043,7 +4043,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="59" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A59">
         <v>56</v>
       </c>
@@ -4102,7 +4102,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="60" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A60">
         <v>57</v>
       </c>
@@ -4161,7 +4161,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="61" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A61">
         <v>58</v>
       </c>
@@ -4220,7 +4220,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="62" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A62">
         <v>59</v>
       </c>
@@ -4279,7 +4279,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="63" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A63">
         <v>60</v>
       </c>
@@ -4338,7 +4338,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="64" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A64">
         <v>61</v>
       </c>
@@ -4397,7 +4397,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="65" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A65">
         <v>62</v>
       </c>
@@ -4456,7 +4456,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="66" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A66">
         <v>63</v>
       </c>
@@ -4515,7 +4515,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="67" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A67">
         <v>64</v>
       </c>
@@ -4574,7 +4574,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="68" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A68">
         <v>65</v>
       </c>
@@ -4618,7 +4618,7 @@
         <v>1603</v>
       </c>
       <c r="O68">
-        <v>63795</v>
+        <v>63796</v>
       </c>
       <c r="P68">
         <v>71325</v>
@@ -4633,7 +4633,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="69" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A69">
         <v>66</v>
       </c>
@@ -4692,7 +4692,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="70" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A70">
         <v>67</v>
       </c>
@@ -4751,7 +4751,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="71" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A71">
         <v>68</v>
       </c>
@@ -4810,7 +4810,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="72" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A72">
         <v>69</v>
       </c>
@@ -4869,7 +4869,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="73" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A73">
         <v>70</v>
       </c>
@@ -4928,7 +4928,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="74" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A74" s="1" t="s">
         <v>89</v>
       </c>
@@ -4955,25 +4955,25 @@
         <v>0</v>
       </c>
       <c r="J74">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="K74">
         <v>0</v>
       </c>
       <c r="L74">
-        <v>625584</v>
+        <v>626066</v>
       </c>
       <c r="M74">
         <v>8318</v>
       </c>
       <c r="N74">
-        <v>97029</v>
+        <v>97173</v>
       </c>
       <c r="O74">
-        <v>2332777</v>
+        <v>2333349</v>
       </c>
       <c r="P74">
-        <v>4703235</v>
+        <v>4703237</v>
       </c>
       <c r="Q74" s="2">
         <v>626236</v>
@@ -4985,8 +4985,6 @@
         <v>3445</v>
       </c>
     </row>
-    <row r="75" spans="1:19" ht="15.75" x14ac:dyDescent="0.25"/>
-    <row r="76" spans="1:19" ht="15.75" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="12">
     <mergeCell ref="A74:B74"/>
@@ -5004,7 +5002,7 @@
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="A2:D74 E1:P74 B1:D1" numberStoredAsText="1"/>
+    <ignoredError sqref="A2:D74 B1:D1 E2:P74 E1:P1" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/Notice.xlsx
+++ b/Notice.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Downloads\New folder (13)\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95F9C41C-55FD-4AB9-BA2F-89EB7B848A89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B91EC026-5DAA-4ACA-B5F9-0BA19E63B64E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="96">
   <si>
     <t>S. No.</t>
   </si>
@@ -34,6 +34,9 @@
     <t>Pending for Notice Generation</t>
   </si>
   <si>
+    <t>Form 7/8 (Shifting)</t>
+  </si>
+  <si>
     <t>Notice Delivered</t>
   </si>
   <si>
@@ -304,7 +307,7 @@
     <t>No Action Required</t>
   </si>
   <si>
-    <t>Notice &amp; Hearing Report 28-09-2026 09:56:41</t>
+    <t>Notice &amp; Hearing Report  29-09-2026 09:56:38</t>
   </si>
 </sst>
 </file>
@@ -340,8 +343,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -686,12 +688,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:S74"/>
-  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:T74"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -709,8 +711,9 @@
       <c r="O1" s="1"/>
       <c r="P1" s="1"/>
       <c r="Q1" s="1"/>
-    </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="R1" s="1"/>
+    </row>
+    <row r="2" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -732,35 +735,36 @@
       <c r="G2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H2" s="1"/>
+      <c r="H2" s="1" t="s">
+        <v>7</v>
+      </c>
       <c r="I2" s="1"/>
-      <c r="J2" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="K2" s="1"/>
+      <c r="J2" s="1"/>
+      <c r="K2" s="1" t="s">
+        <v>8</v>
+      </c>
       <c r="L2" s="1"/>
       <c r="M2" s="1"/>
-      <c r="N2" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="O2" s="1"/>
+      <c r="N2" s="1"/>
+      <c r="O2" s="1" t="s">
+        <v>9</v>
+      </c>
       <c r="P2" s="1"/>
-      <c r="Q2" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="R2" s="1"/>
+      <c r="Q2" s="1"/>
+      <c r="R2" s="1" t="s">
+        <v>91</v>
+      </c>
       <c r="S2" s="1"/>
-    </row>
-    <row r="3" spans="1:19" ht="63" x14ac:dyDescent="0.25">
+      <c r="T2" s="1"/>
+    </row>
+    <row r="3" spans="1:20" ht="63" x14ac:dyDescent="0.25">
       <c r="A3" s="1"/>
       <c r="B3" s="1"/>
       <c r="C3" s="1"/>
       <c r="D3" s="1"/>
       <c r="E3" s="1"/>
       <c r="F3" s="1"/>
-      <c r="G3" t="s">
-        <v>9</v>
-      </c>
+      <c r="G3" s="1"/>
       <c r="H3" t="s">
         <v>10</v>
       </c>
@@ -788,22 +792,25 @@
       <c r="P3" t="s">
         <v>18</v>
       </c>
-      <c r="Q3" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="R3" s="3" t="s">
+      <c r="Q3" t="s">
+        <v>19</v>
+      </c>
+      <c r="R3" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="S3" s="3" t="s">
+      <c r="S3" s="2" t="s">
         <v>93</v>
       </c>
-    </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T3" s="2" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="4" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>1</v>
       </c>
       <c r="B4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C4">
         <v>51528</v>
@@ -812,17 +819,17 @@
         <v>0</v>
       </c>
       <c r="E4">
+        <v>2</v>
+      </c>
+      <c r="F4">
         <v>51528</v>
       </c>
-      <c r="F4">
-        <v>0</v>
-      </c>
       <c r="G4">
+        <v>0</v>
+      </c>
+      <c r="H4">
         <v>51528</v>
       </c>
-      <c r="H4">
-        <v>0</v>
-      </c>
       <c r="I4">
         <v>0</v>
       </c>
@@ -833,36 +840,39 @@
         <v>0</v>
       </c>
       <c r="L4">
+        <v>0</v>
+      </c>
+      <c r="M4">
         <v>17975</v>
       </c>
-      <c r="M4">
+      <c r="N4">
         <v>967</v>
       </c>
-      <c r="N4">
+      <c r="O4">
         <v>869</v>
       </c>
-      <c r="O4">
+      <c r="P4">
         <v>50659</v>
       </c>
-      <c r="P4">
+      <c r="Q4">
         <v>53812</v>
       </c>
-      <c r="Q4" s="2">
+      <c r="R4">
         <v>12212</v>
       </c>
-      <c r="R4" s="2">
-        <v>0</v>
-      </c>
-      <c r="S4" s="2">
+      <c r="S4">
+        <v>0</v>
+      </c>
+      <c r="T4">
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>2</v>
       </c>
       <c r="B5" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C5">
         <v>53911</v>
@@ -871,17 +881,17 @@
         <v>0</v>
       </c>
       <c r="E5">
+        <v>0</v>
+      </c>
+      <c r="F5">
         <v>53911</v>
       </c>
-      <c r="F5">
-        <v>0</v>
-      </c>
       <c r="G5">
+        <v>0</v>
+      </c>
+      <c r="H5">
         <v>53911</v>
       </c>
-      <c r="H5">
-        <v>0</v>
-      </c>
       <c r="I5">
         <v>0</v>
       </c>
@@ -892,36 +902,39 @@
         <v>0</v>
       </c>
       <c r="L5">
+        <v>0</v>
+      </c>
+      <c r="M5">
         <v>11415</v>
       </c>
-      <c r="M5">
+      <c r="N5">
         <v>757</v>
       </c>
-      <c r="N5">
+      <c r="O5">
         <v>877</v>
       </c>
-      <c r="O5">
+      <c r="P5">
         <v>53035</v>
       </c>
-      <c r="P5">
+      <c r="Q5">
         <v>74848</v>
       </c>
-      <c r="Q5" s="2">
+      <c r="R5">
         <v>16108</v>
       </c>
-      <c r="R5" s="2">
-        <v>0</v>
-      </c>
-      <c r="S5" s="2">
+      <c r="S5">
+        <v>0</v>
+      </c>
+      <c r="T5">
         <v>30</v>
       </c>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>3</v>
       </c>
       <c r="B6" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C6">
         <v>39773</v>
@@ -930,17 +943,17 @@
         <v>0</v>
       </c>
       <c r="E6">
+        <v>0</v>
+      </c>
+      <c r="F6">
         <v>39773</v>
       </c>
-      <c r="F6">
-        <v>0</v>
-      </c>
       <c r="G6">
+        <v>0</v>
+      </c>
+      <c r="H6">
         <v>39773</v>
       </c>
-      <c r="H6">
-        <v>0</v>
-      </c>
       <c r="I6">
         <v>0</v>
       </c>
@@ -951,36 +964,39 @@
         <v>0</v>
       </c>
       <c r="L6">
+        <v>0</v>
+      </c>
+      <c r="M6">
         <v>6086</v>
       </c>
-      <c r="M6">
+      <c r="N6">
         <v>201</v>
       </c>
-      <c r="N6">
+      <c r="O6">
         <v>1870</v>
       </c>
-      <c r="O6">
+      <c r="P6">
         <v>37903</v>
       </c>
-      <c r="P6">
+      <c r="Q6">
         <v>71989</v>
       </c>
-      <c r="Q6" s="2">
+      <c r="R6">
         <v>17830</v>
       </c>
-      <c r="R6" s="2">
-        <v>0</v>
-      </c>
-      <c r="S6" s="2">
+      <c r="S6">
+        <v>0</v>
+      </c>
+      <c r="T6">
         <v>54</v>
       </c>
     </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>4</v>
       </c>
       <c r="B7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C7">
         <v>39463</v>
@@ -989,17 +1005,17 @@
         <v>0</v>
       </c>
       <c r="E7">
+        <v>0</v>
+      </c>
+      <c r="F7">
         <v>39463</v>
       </c>
-      <c r="F7">
-        <v>0</v>
-      </c>
       <c r="G7">
+        <v>0</v>
+      </c>
+      <c r="H7">
         <v>39463</v>
       </c>
-      <c r="H7">
-        <v>0</v>
-      </c>
       <c r="I7">
         <v>0</v>
       </c>
@@ -1010,36 +1026,39 @@
         <v>0</v>
       </c>
       <c r="L7">
+        <v>0</v>
+      </c>
+      <c r="M7">
         <v>5733</v>
       </c>
-      <c r="M7">
+      <c r="N7">
         <v>257</v>
       </c>
-      <c r="N7">
+      <c r="O7">
         <v>1995</v>
       </c>
-      <c r="O7">
+      <c r="P7">
         <v>37468</v>
       </c>
-      <c r="P7">
+      <c r="Q7">
         <v>77581</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7">
         <v>20511</v>
       </c>
-      <c r="R7" s="2">
-        <v>0</v>
-      </c>
-      <c r="S7" s="2">
+      <c r="S7">
+        <v>0</v>
+      </c>
+      <c r="T7">
         <v>8</v>
       </c>
     </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>5</v>
       </c>
       <c r="B8" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C8">
         <v>40552</v>
@@ -1048,17 +1067,17 @@
         <v>0</v>
       </c>
       <c r="E8">
+        <v>5</v>
+      </c>
+      <c r="F8">
         <v>40552</v>
       </c>
-      <c r="F8">
-        <v>0</v>
-      </c>
       <c r="G8">
+        <v>0</v>
+      </c>
+      <c r="H8">
         <v>40552</v>
       </c>
-      <c r="H8">
-        <v>0</v>
-      </c>
       <c r="I8">
         <v>0</v>
       </c>
@@ -1069,36 +1088,39 @@
         <v>0</v>
       </c>
       <c r="L8">
+        <v>0</v>
+      </c>
+      <c r="M8">
         <v>14714</v>
       </c>
-      <c r="M8">
+      <c r="N8">
         <v>164</v>
       </c>
-      <c r="N8">
+      <c r="O8">
         <v>1981</v>
       </c>
-      <c r="O8">
+      <c r="P8">
         <v>38571</v>
       </c>
-      <c r="P8">
+      <c r="Q8">
         <v>73458</v>
       </c>
-      <c r="Q8" s="2">
+      <c r="R8">
         <v>20788</v>
       </c>
-      <c r="R8" s="2">
-        <v>0</v>
-      </c>
-      <c r="S8" s="2">
+      <c r="S8">
+        <v>0</v>
+      </c>
+      <c r="T8">
         <v>110</v>
       </c>
     </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>6</v>
       </c>
       <c r="B9" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C9">
         <v>43273</v>
@@ -1107,17 +1129,17 @@
         <v>0</v>
       </c>
       <c r="E9">
+        <v>0</v>
+      </c>
+      <c r="F9">
         <v>43273</v>
       </c>
-      <c r="F9">
-        <v>0</v>
-      </c>
       <c r="G9">
+        <v>0</v>
+      </c>
+      <c r="H9">
         <v>43273</v>
       </c>
-      <c r="H9">
-        <v>0</v>
-      </c>
       <c r="I9">
         <v>0</v>
       </c>
@@ -1128,36 +1150,39 @@
         <v>0</v>
       </c>
       <c r="L9">
+        <v>0</v>
+      </c>
+      <c r="M9">
         <v>7759</v>
       </c>
-      <c r="M9">
+      <c r="N9">
         <v>49</v>
       </c>
-      <c r="N9">
+      <c r="O9">
         <v>1350</v>
       </c>
-      <c r="O9">
+      <c r="P9">
         <v>41924</v>
       </c>
-      <c r="P9">
+      <c r="Q9">
         <v>72913</v>
       </c>
-      <c r="Q9" s="2">
+      <c r="R9">
         <v>18141</v>
       </c>
-      <c r="R9" s="2">
-        <v>0</v>
-      </c>
-      <c r="S9" s="2">
+      <c r="S9">
+        <v>0</v>
+      </c>
+      <c r="T9">
         <v>110</v>
       </c>
     </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>7</v>
       </c>
       <c r="B10" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C10">
         <v>36576</v>
@@ -1166,17 +1191,17 @@
         <v>0</v>
       </c>
       <c r="E10">
+        <v>0</v>
+      </c>
+      <c r="F10">
         <v>36576</v>
       </c>
-      <c r="F10">
-        <v>0</v>
-      </c>
       <c r="G10">
+        <v>0</v>
+      </c>
+      <c r="H10">
         <v>36576</v>
       </c>
-      <c r="H10">
-        <v>0</v>
-      </c>
       <c r="I10">
         <v>0</v>
       </c>
@@ -1187,36 +1212,39 @@
         <v>0</v>
       </c>
       <c r="L10">
+        <v>0</v>
+      </c>
+      <c r="M10">
         <v>10960</v>
       </c>
-      <c r="M10">
+      <c r="N10">
         <v>172</v>
       </c>
-      <c r="N10">
+      <c r="O10">
         <v>815</v>
       </c>
-      <c r="O10">
+      <c r="P10">
         <v>35761</v>
       </c>
-      <c r="P10">
+      <c r="Q10">
         <v>53124</v>
       </c>
-      <c r="Q10" s="2">
+      <c r="R10">
         <v>9498</v>
       </c>
-      <c r="R10" s="2">
-        <v>0</v>
-      </c>
-      <c r="S10" s="2">
+      <c r="S10">
+        <v>0</v>
+      </c>
+      <c r="T10">
         <v>2</v>
       </c>
     </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>8</v>
       </c>
       <c r="B11" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C11">
         <v>50998</v>
@@ -1225,17 +1253,17 @@
         <v>0</v>
       </c>
       <c r="E11">
+        <v>0</v>
+      </c>
+      <c r="F11">
         <v>50998</v>
       </c>
-      <c r="F11">
-        <v>0</v>
-      </c>
       <c r="G11">
+        <v>0</v>
+      </c>
+      <c r="H11">
         <v>50998</v>
       </c>
-      <c r="H11">
-        <v>0</v>
-      </c>
       <c r="I11">
         <v>0</v>
       </c>
@@ -1246,36 +1274,39 @@
         <v>0</v>
       </c>
       <c r="L11">
+        <v>0</v>
+      </c>
+      <c r="M11">
         <v>9958</v>
       </c>
-      <c r="M11">
+      <c r="N11">
         <v>253</v>
       </c>
-      <c r="N11">
+      <c r="O11">
         <v>1703</v>
       </c>
-      <c r="O11">
+      <c r="P11">
         <v>49300</v>
       </c>
-      <c r="P11">
+      <c r="Q11">
         <v>84438</v>
       </c>
-      <c r="Q11" s="2">
+      <c r="R11">
         <v>23477</v>
       </c>
-      <c r="R11" s="2">
-        <v>0</v>
-      </c>
-      <c r="S11" s="2">
+      <c r="S11">
+        <v>0</v>
+      </c>
+      <c r="T11">
         <v>23</v>
       </c>
     </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>9</v>
       </c>
       <c r="B12" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C12">
         <v>40739</v>
@@ -1284,17 +1315,17 @@
         <v>0</v>
       </c>
       <c r="E12">
+        <v>0</v>
+      </c>
+      <c r="F12">
         <v>40739</v>
       </c>
-      <c r="F12">
-        <v>0</v>
-      </c>
       <c r="G12">
+        <v>0</v>
+      </c>
+      <c r="H12">
         <v>40739</v>
       </c>
-      <c r="H12">
-        <v>0</v>
-      </c>
       <c r="I12">
         <v>0</v>
       </c>
@@ -1305,36 +1336,39 @@
         <v>0</v>
       </c>
       <c r="L12">
+        <v>0</v>
+      </c>
+      <c r="M12">
         <v>10054</v>
       </c>
-      <c r="M12">
+      <c r="N12">
         <v>207</v>
       </c>
-      <c r="N12">
+      <c r="O12">
         <v>1151</v>
       </c>
-      <c r="O12">
+      <c r="P12">
         <v>39588</v>
       </c>
-      <c r="P12">
+      <c r="Q12">
         <v>66685</v>
       </c>
-      <c r="Q12" s="2">
+      <c r="R12">
         <v>17786</v>
       </c>
-      <c r="R12" s="2">
-        <v>0</v>
-      </c>
-      <c r="S12" s="2">
+      <c r="S12">
+        <v>0</v>
+      </c>
+      <c r="T12">
         <v>3</v>
       </c>
     </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>10</v>
       </c>
       <c r="B13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C13">
         <v>37031</v>
@@ -1343,17 +1377,17 @@
         <v>0</v>
       </c>
       <c r="E13">
+        <v>0</v>
+      </c>
+      <c r="F13">
         <v>37031</v>
       </c>
-      <c r="F13">
-        <v>0</v>
-      </c>
       <c r="G13">
+        <v>0</v>
+      </c>
+      <c r="H13">
         <v>37031</v>
       </c>
-      <c r="H13">
-        <v>0</v>
-      </c>
       <c r="I13">
         <v>0</v>
       </c>
@@ -1364,36 +1398,39 @@
         <v>0</v>
       </c>
       <c r="L13">
+        <v>0</v>
+      </c>
+      <c r="M13">
         <v>7864</v>
       </c>
-      <c r="M13">
+      <c r="N13">
         <v>258</v>
       </c>
-      <c r="N13">
+      <c r="O13">
         <v>3822</v>
       </c>
-      <c r="O13">
+      <c r="P13">
         <v>33237</v>
       </c>
-      <c r="P13">
+      <c r="Q13">
         <v>56564</v>
       </c>
-      <c r="Q13" s="2">
+      <c r="R13">
         <v>16237</v>
       </c>
-      <c r="R13" s="2">
-        <v>0</v>
-      </c>
-      <c r="S13" s="2">
+      <c r="S13">
+        <v>0</v>
+      </c>
+      <c r="T13">
         <v>106</v>
       </c>
     </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>11</v>
       </c>
       <c r="B14" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C14">
         <v>48966</v>
@@ -1402,17 +1439,17 @@
         <v>0</v>
       </c>
       <c r="E14">
+        <v>0</v>
+      </c>
+      <c r="F14">
         <v>48966</v>
       </c>
-      <c r="F14">
-        <v>0</v>
-      </c>
       <c r="G14">
+        <v>0</v>
+      </c>
+      <c r="H14">
         <v>48966</v>
       </c>
-      <c r="H14">
-        <v>0</v>
-      </c>
       <c r="I14">
         <v>0</v>
       </c>
@@ -1423,36 +1460,39 @@
         <v>0</v>
       </c>
       <c r="L14">
+        <v>0</v>
+      </c>
+      <c r="M14">
         <v>15267</v>
       </c>
-      <c r="M14">
+      <c r="N14">
         <v>1456</v>
       </c>
-      <c r="N14">
+      <c r="O14">
         <v>5867</v>
       </c>
-      <c r="O14">
+      <c r="P14">
         <v>43099</v>
       </c>
-      <c r="P14">
+      <c r="Q14">
         <v>77955</v>
       </c>
-      <c r="Q14" s="2">
+      <c r="R14">
         <v>19716</v>
       </c>
-      <c r="R14" s="2">
-        <v>0</v>
-      </c>
-      <c r="S14" s="2">
+      <c r="S14">
+        <v>0</v>
+      </c>
+      <c r="T14">
         <v>174</v>
       </c>
     </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>12</v>
       </c>
       <c r="B15" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C15">
         <v>42703</v>
@@ -1461,17 +1501,17 @@
         <v>0</v>
       </c>
       <c r="E15">
+        <v>0</v>
+      </c>
+      <c r="F15">
         <v>42703</v>
       </c>
-      <c r="F15">
-        <v>0</v>
-      </c>
       <c r="G15">
+        <v>0</v>
+      </c>
+      <c r="H15">
         <v>42703</v>
       </c>
-      <c r="H15">
-        <v>0</v>
-      </c>
       <c r="I15">
         <v>0</v>
       </c>
@@ -1482,36 +1522,39 @@
         <v>0</v>
       </c>
       <c r="L15">
+        <v>0</v>
+      </c>
+      <c r="M15">
         <v>9192</v>
       </c>
-      <c r="M15">
-        <v>0</v>
-      </c>
       <c r="N15">
+        <v>0</v>
+      </c>
+      <c r="O15">
         <v>2821</v>
       </c>
-      <c r="O15">
+      <c r="P15">
         <v>39882</v>
       </c>
-      <c r="P15">
+      <c r="Q15">
         <v>67183</v>
       </c>
-      <c r="Q15" s="2">
+      <c r="R15">
         <v>4859</v>
       </c>
-      <c r="R15" s="2">
-        <v>0</v>
-      </c>
-      <c r="S15" s="2">
+      <c r="S15">
+        <v>0</v>
+      </c>
+      <c r="T15">
         <v>50</v>
       </c>
     </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>13</v>
       </c>
       <c r="B16" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C16">
         <v>25549</v>
@@ -1520,17 +1563,17 @@
         <v>0</v>
       </c>
       <c r="E16">
+        <v>0</v>
+      </c>
+      <c r="F16">
         <v>25549</v>
       </c>
-      <c r="F16">
-        <v>0</v>
-      </c>
       <c r="G16">
+        <v>0</v>
+      </c>
+      <c r="H16">
         <v>25547</v>
       </c>
-      <c r="H16">
-        <v>0</v>
-      </c>
       <c r="I16">
         <v>0</v>
       </c>
@@ -1541,36 +1584,39 @@
         <v>0</v>
       </c>
       <c r="L16">
+        <v>0</v>
+      </c>
+      <c r="M16">
         <v>14861</v>
       </c>
-      <c r="M16">
+      <c r="N16">
         <v>1</v>
       </c>
-      <c r="N16">
+      <c r="O16">
         <v>261</v>
       </c>
-      <c r="O16">
+      <c r="P16">
         <v>25289</v>
       </c>
-      <c r="P16">
+      <c r="Q16">
         <v>71673</v>
       </c>
-      <c r="Q16" s="2">
+      <c r="R16">
         <v>5197</v>
       </c>
-      <c r="R16" s="2">
-        <v>0</v>
-      </c>
-      <c r="S16" s="2">
+      <c r="S16">
+        <v>0</v>
+      </c>
+      <c r="T16">
         <v>47</v>
       </c>
     </row>
-    <row r="17" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>14</v>
       </c>
       <c r="B17" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C17">
         <v>27707</v>
@@ -1579,17 +1625,17 @@
         <v>0</v>
       </c>
       <c r="E17">
+        <v>0</v>
+      </c>
+      <c r="F17">
         <v>27707</v>
       </c>
-      <c r="F17">
-        <v>0</v>
-      </c>
       <c r="G17">
+        <v>0</v>
+      </c>
+      <c r="H17">
         <v>27707</v>
       </c>
-      <c r="H17">
-        <v>0</v>
-      </c>
       <c r="I17">
         <v>0</v>
       </c>
@@ -1600,36 +1646,39 @@
         <v>0</v>
       </c>
       <c r="L17">
+        <v>0</v>
+      </c>
+      <c r="M17">
         <v>9287</v>
       </c>
-      <c r="M17">
+      <c r="N17">
         <v>2</v>
       </c>
-      <c r="N17">
+      <c r="O17">
         <v>426</v>
       </c>
-      <c r="O17">
+      <c r="P17">
         <v>27282</v>
       </c>
-      <c r="P17">
+      <c r="Q17">
         <v>65457</v>
       </c>
-      <c r="Q17" s="2">
+      <c r="R17">
         <v>5417</v>
       </c>
-      <c r="R17" s="2">
-        <v>0</v>
-      </c>
-      <c r="S17" s="2">
+      <c r="S17">
+        <v>0</v>
+      </c>
+      <c r="T17">
         <v>105</v>
       </c>
     </row>
-    <row r="18" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>15</v>
       </c>
       <c r="B18" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C18">
         <v>47836</v>
@@ -1638,17 +1687,17 @@
         <v>0</v>
       </c>
       <c r="E18">
+        <v>0</v>
+      </c>
+      <c r="F18">
         <v>47836</v>
       </c>
-      <c r="F18">
-        <v>0</v>
-      </c>
       <c r="G18">
+        <v>0</v>
+      </c>
+      <c r="H18">
         <v>47836</v>
       </c>
-      <c r="H18">
-        <v>0</v>
-      </c>
       <c r="I18">
         <v>0</v>
       </c>
@@ -1659,36 +1708,39 @@
         <v>0</v>
       </c>
       <c r="L18">
+        <v>0</v>
+      </c>
+      <c r="M18">
         <v>7876</v>
       </c>
-      <c r="M18">
+      <c r="N18">
         <v>3</v>
       </c>
-      <c r="N18">
+      <c r="O18">
         <v>1970</v>
       </c>
-      <c r="O18">
-        <v>45865</v>
-      </c>
       <c r="P18">
+        <v>45866</v>
+      </c>
+      <c r="Q18">
         <v>71496</v>
       </c>
-      <c r="Q18" s="2">
+      <c r="R18">
         <v>6819</v>
       </c>
-      <c r="R18" s="2">
-        <v>0</v>
-      </c>
-      <c r="S18" s="2">
+      <c r="S18">
+        <v>0</v>
+      </c>
+      <c r="T18">
         <v>32</v>
       </c>
     </row>
-    <row r="19" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>16</v>
       </c>
       <c r="B19" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C19">
         <v>56490</v>
@@ -1697,17 +1749,17 @@
         <v>0</v>
       </c>
       <c r="E19">
+        <v>0</v>
+      </c>
+      <c r="F19">
         <v>56490</v>
       </c>
-      <c r="F19">
-        <v>0</v>
-      </c>
       <c r="G19">
+        <v>0</v>
+      </c>
+      <c r="H19">
         <v>56490</v>
       </c>
-      <c r="H19">
-        <v>0</v>
-      </c>
       <c r="I19">
         <v>0</v>
       </c>
@@ -1718,36 +1770,39 @@
         <v>0</v>
       </c>
       <c r="L19">
+        <v>0</v>
+      </c>
+      <c r="M19">
         <v>15286</v>
       </c>
-      <c r="M19">
+      <c r="N19">
         <v>1</v>
       </c>
-      <c r="N19">
+      <c r="O19">
         <v>912</v>
       </c>
-      <c r="O19">
+      <c r="P19">
         <v>55578</v>
       </c>
-      <c r="P19">
+      <c r="Q19">
         <v>106392</v>
       </c>
-      <c r="Q19" s="2">
+      <c r="R19">
         <v>6135</v>
       </c>
-      <c r="R19" s="2">
-        <v>0</v>
-      </c>
-      <c r="S19" s="2">
+      <c r="S19">
+        <v>0</v>
+      </c>
+      <c r="T19">
         <v>36</v>
       </c>
     </row>
-    <row r="20" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>17</v>
       </c>
       <c r="B20" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C20">
         <v>35022</v>
@@ -1756,17 +1811,17 @@
         <v>0</v>
       </c>
       <c r="E20">
+        <v>0</v>
+      </c>
+      <c r="F20">
         <v>35022</v>
       </c>
-      <c r="F20">
-        <v>0</v>
-      </c>
       <c r="G20">
+        <v>0</v>
+      </c>
+      <c r="H20">
         <v>35022</v>
       </c>
-      <c r="H20">
-        <v>0</v>
-      </c>
       <c r="I20">
         <v>0</v>
       </c>
@@ -1777,36 +1832,39 @@
         <v>0</v>
       </c>
       <c r="L20">
+        <v>0</v>
+      </c>
+      <c r="M20">
         <v>6093</v>
       </c>
-      <c r="M20">
+      <c r="N20">
         <v>5</v>
       </c>
-      <c r="N20">
+      <c r="O20">
         <v>546</v>
       </c>
-      <c r="O20">
+      <c r="P20">
         <v>34477</v>
       </c>
-      <c r="P20">
+      <c r="Q20">
         <v>75814</v>
       </c>
-      <c r="Q20" s="2">
+      <c r="R20">
         <v>8984</v>
       </c>
-      <c r="R20" s="2">
-        <v>0</v>
-      </c>
-      <c r="S20" s="2">
+      <c r="S20">
+        <v>0</v>
+      </c>
+      <c r="T20">
         <v>71</v>
       </c>
     </row>
-    <row r="21" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>18</v>
       </c>
       <c r="B21" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C21">
         <v>16962</v>
@@ -1815,17 +1873,17 @@
         <v>0</v>
       </c>
       <c r="E21">
+        <v>0</v>
+      </c>
+      <c r="F21">
         <v>16962</v>
       </c>
-      <c r="F21">
-        <v>0</v>
-      </c>
       <c r="G21">
+        <v>0</v>
+      </c>
+      <c r="H21">
         <v>16962</v>
       </c>
-      <c r="H21">
-        <v>0</v>
-      </c>
       <c r="I21">
         <v>0</v>
       </c>
@@ -1836,36 +1894,39 @@
         <v>0</v>
       </c>
       <c r="L21">
+        <v>0</v>
+      </c>
+      <c r="M21">
         <v>4030</v>
       </c>
-      <c r="M21">
+      <c r="N21">
         <v>3</v>
       </c>
-      <c r="N21">
+      <c r="O21">
         <v>171</v>
       </c>
-      <c r="O21">
+      <c r="P21">
         <v>16791</v>
       </c>
-      <c r="P21">
+      <c r="Q21">
         <v>62460</v>
       </c>
-      <c r="Q21" s="2">
+      <c r="R21">
         <v>3868</v>
       </c>
-      <c r="R21" s="2">
-        <v>0</v>
-      </c>
-      <c r="S21" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="S21">
+        <v>0</v>
+      </c>
+      <c r="T21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>19</v>
       </c>
       <c r="B22" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C22">
         <v>18668</v>
@@ -1874,17 +1935,17 @@
         <v>0</v>
       </c>
       <c r="E22">
+        <v>0</v>
+      </c>
+      <c r="F22">
         <v>18668</v>
       </c>
-      <c r="F22">
-        <v>0</v>
-      </c>
       <c r="G22">
+        <v>0</v>
+      </c>
+      <c r="H22">
         <v>18668</v>
       </c>
-      <c r="H22">
-        <v>0</v>
-      </c>
       <c r="I22">
         <v>0</v>
       </c>
@@ -1895,36 +1956,39 @@
         <v>0</v>
       </c>
       <c r="L22">
+        <v>0</v>
+      </c>
+      <c r="M22">
         <v>7665</v>
       </c>
-      <c r="M22">
-        <v>0</v>
-      </c>
       <c r="N22">
+        <v>0</v>
+      </c>
+      <c r="O22">
         <v>302</v>
       </c>
-      <c r="O22">
+      <c r="P22">
         <v>18366</v>
       </c>
-      <c r="P22">
+      <c r="Q22">
         <v>64099</v>
       </c>
-      <c r="Q22" s="2">
+      <c r="R22">
         <v>4848</v>
       </c>
-      <c r="R22" s="2">
-        <v>0</v>
-      </c>
-      <c r="S22" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="S22">
+        <v>0</v>
+      </c>
+      <c r="T22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>20</v>
       </c>
       <c r="B23" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C23">
         <v>12020</v>
@@ -1933,17 +1997,17 @@
         <v>0</v>
       </c>
       <c r="E23">
+        <v>0</v>
+      </c>
+      <c r="F23">
         <v>12020</v>
       </c>
-      <c r="F23">
-        <v>0</v>
-      </c>
       <c r="G23">
+        <v>0</v>
+      </c>
+      <c r="H23">
         <v>12020</v>
       </c>
-      <c r="H23">
-        <v>0</v>
-      </c>
       <c r="I23">
         <v>0</v>
       </c>
@@ -1954,36 +2018,39 @@
         <v>0</v>
       </c>
       <c r="L23">
+        <v>0</v>
+      </c>
+      <c r="M23">
         <v>2113</v>
       </c>
-      <c r="M23">
-        <v>0</v>
-      </c>
       <c r="N23">
+        <v>0</v>
+      </c>
+      <c r="O23">
         <v>108</v>
       </c>
-      <c r="O23">
+      <c r="P23">
         <v>11912</v>
       </c>
-      <c r="P23">
+      <c r="Q23">
         <v>57094</v>
       </c>
-      <c r="Q23" s="2">
+      <c r="R23">
         <v>3541</v>
       </c>
-      <c r="R23" s="2">
-        <v>0</v>
-      </c>
-      <c r="S23" s="2">
+      <c r="S23">
+        <v>0</v>
+      </c>
+      <c r="T23">
         <v>28</v>
       </c>
     </row>
-    <row r="24" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>21</v>
       </c>
       <c r="B24" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C24">
         <v>14056</v>
@@ -1992,17 +2059,17 @@
         <v>0</v>
       </c>
       <c r="E24">
+        <v>0</v>
+      </c>
+      <c r="F24">
         <v>14056</v>
       </c>
-      <c r="F24">
-        <v>0</v>
-      </c>
       <c r="G24">
+        <v>0</v>
+      </c>
+      <c r="H24">
         <v>14056</v>
       </c>
-      <c r="H24">
-        <v>0</v>
-      </c>
       <c r="I24">
         <v>0</v>
       </c>
@@ -2013,36 +2080,39 @@
         <v>0</v>
       </c>
       <c r="L24">
+        <v>0</v>
+      </c>
+      <c r="M24">
         <v>3482</v>
       </c>
-      <c r="M24">
+      <c r="N24">
         <v>5</v>
       </c>
-      <c r="N24">
+      <c r="O24">
         <v>231</v>
       </c>
-      <c r="O24">
+      <c r="P24">
         <v>13825</v>
       </c>
-      <c r="P24">
+      <c r="Q24">
         <v>65629</v>
       </c>
-      <c r="Q24" s="2">
+      <c r="R24">
         <v>3492</v>
       </c>
-      <c r="R24" s="2">
-        <v>0</v>
-      </c>
-      <c r="S24" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="S24">
+        <v>0</v>
+      </c>
+      <c r="T24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>22</v>
       </c>
       <c r="B25" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C25">
         <v>19266</v>
@@ -2051,17 +2121,17 @@
         <v>0</v>
       </c>
       <c r="E25">
+        <v>0</v>
+      </c>
+      <c r="F25">
         <v>19266</v>
       </c>
-      <c r="F25">
-        <v>0</v>
-      </c>
       <c r="G25">
+        <v>0</v>
+      </c>
+      <c r="H25">
         <v>19266</v>
       </c>
-      <c r="H25">
-        <v>0</v>
-      </c>
       <c r="I25">
         <v>0</v>
       </c>
@@ -2072,36 +2142,39 @@
         <v>0</v>
       </c>
       <c r="L25">
+        <v>0</v>
+      </c>
+      <c r="M25">
         <v>4862</v>
       </c>
-      <c r="M25">
-        <v>0</v>
-      </c>
       <c r="N25">
+        <v>0</v>
+      </c>
+      <c r="O25">
         <v>298</v>
       </c>
-      <c r="O25">
+      <c r="P25">
         <v>18968</v>
       </c>
-      <c r="P25">
+      <c r="Q25">
         <v>57533</v>
       </c>
-      <c r="Q25" s="2">
+      <c r="R25">
         <v>3231</v>
       </c>
-      <c r="R25" s="2">
-        <v>0</v>
-      </c>
-      <c r="S25" s="2">
+      <c r="S25">
+        <v>0</v>
+      </c>
+      <c r="T25">
         <v>13</v>
       </c>
     </row>
-    <row r="26" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>23</v>
       </c>
       <c r="B26" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C26">
         <v>17557</v>
@@ -2110,17 +2183,17 @@
         <v>0</v>
       </c>
       <c r="E26">
+        <v>0</v>
+      </c>
+      <c r="F26">
         <v>17557</v>
       </c>
-      <c r="F26">
-        <v>0</v>
-      </c>
       <c r="G26">
+        <v>0</v>
+      </c>
+      <c r="H26">
         <v>17557</v>
       </c>
-      <c r="H26">
-        <v>0</v>
-      </c>
       <c r="I26">
         <v>0</v>
       </c>
@@ -2131,36 +2204,39 @@
         <v>0</v>
       </c>
       <c r="L26">
+        <v>0</v>
+      </c>
+      <c r="M26">
         <v>3741</v>
       </c>
-      <c r="M26">
+      <c r="N26">
         <v>3</v>
       </c>
-      <c r="N26">
+      <c r="O26">
         <v>194</v>
       </c>
-      <c r="O26">
+      <c r="P26">
         <v>17363</v>
       </c>
-      <c r="P26">
+      <c r="Q26">
         <v>66594</v>
       </c>
-      <c r="Q26" s="2">
+      <c r="R26">
         <v>3333</v>
       </c>
-      <c r="R26" s="2">
-        <v>0</v>
-      </c>
-      <c r="S26" s="2">
+      <c r="S26">
+        <v>0</v>
+      </c>
+      <c r="T26">
         <v>2</v>
       </c>
     </row>
-    <row r="27" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>24</v>
       </c>
       <c r="B27" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C27">
         <v>44276</v>
@@ -2169,17 +2245,17 @@
         <v>0</v>
       </c>
       <c r="E27">
+        <v>0</v>
+      </c>
+      <c r="F27">
         <v>44276</v>
       </c>
-      <c r="F27">
-        <v>0</v>
-      </c>
       <c r="G27">
+        <v>0</v>
+      </c>
+      <c r="H27">
         <v>44276</v>
       </c>
-      <c r="H27">
-        <v>0</v>
-      </c>
       <c r="I27">
         <v>0</v>
       </c>
@@ -2190,36 +2266,39 @@
         <v>0</v>
       </c>
       <c r="L27">
+        <v>0</v>
+      </c>
+      <c r="M27">
         <v>9679</v>
       </c>
-      <c r="M27">
+      <c r="N27">
         <v>215</v>
       </c>
-      <c r="N27">
+      <c r="O27">
         <v>3287</v>
       </c>
-      <c r="O27">
+      <c r="P27">
         <v>41005</v>
       </c>
-      <c r="P27">
+      <c r="Q27">
         <v>73109</v>
       </c>
-      <c r="Q27" s="2">
+      <c r="R27">
         <v>12669</v>
       </c>
-      <c r="R27" s="2">
-        <v>0</v>
-      </c>
-      <c r="S27" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="S27">
+        <v>0</v>
+      </c>
+      <c r="T27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>25</v>
       </c>
       <c r="B28" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C28">
         <v>54349</v>
@@ -2228,17 +2307,17 @@
         <v>0</v>
       </c>
       <c r="E28">
+        <v>0</v>
+      </c>
+      <c r="F28">
         <v>54349</v>
       </c>
-      <c r="F28">
-        <v>0</v>
-      </c>
       <c r="G28">
+        <v>0</v>
+      </c>
+      <c r="H28">
         <v>54349</v>
       </c>
-      <c r="H28">
-        <v>0</v>
-      </c>
       <c r="I28">
         <v>0</v>
       </c>
@@ -2249,36 +2328,39 @@
         <v>0</v>
       </c>
       <c r="L28">
+        <v>0</v>
+      </c>
+      <c r="M28">
         <v>8879</v>
       </c>
-      <c r="M28">
+      <c r="N28">
         <v>856</v>
       </c>
-      <c r="N28">
+      <c r="O28">
         <v>3525</v>
       </c>
-      <c r="O28">
+      <c r="P28">
         <v>50844</v>
       </c>
-      <c r="P28">
+      <c r="Q28">
         <v>80620</v>
       </c>
-      <c r="Q28" s="2">
+      <c r="R28">
         <v>13995</v>
       </c>
-      <c r="R28" s="2">
-        <v>0</v>
-      </c>
-      <c r="S28" s="2">
+      <c r="S28">
+        <v>0</v>
+      </c>
+      <c r="T28">
         <v>127</v>
       </c>
     </row>
-    <row r="29" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>26</v>
       </c>
       <c r="B29" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C29">
         <v>47111</v>
@@ -2287,17 +2369,17 @@
         <v>0</v>
       </c>
       <c r="E29">
+        <v>0</v>
+      </c>
+      <c r="F29">
         <v>47111</v>
       </c>
-      <c r="F29">
-        <v>0</v>
-      </c>
       <c r="G29">
+        <v>0</v>
+      </c>
+      <c r="H29">
         <v>47111</v>
       </c>
-      <c r="H29">
-        <v>0</v>
-      </c>
       <c r="I29">
         <v>0</v>
       </c>
@@ -2308,36 +2390,39 @@
         <v>0</v>
       </c>
       <c r="L29">
+        <v>0</v>
+      </c>
+      <c r="M29">
         <v>8816</v>
       </c>
-      <c r="M29">
+      <c r="N29">
         <v>318</v>
       </c>
-      <c r="N29">
+      <c r="O29">
         <v>4592</v>
       </c>
-      <c r="O29">
+      <c r="P29">
         <v>42520</v>
       </c>
-      <c r="P29">
+      <c r="Q29">
         <v>83836</v>
       </c>
-      <c r="Q29" s="2">
+      <c r="R29">
         <v>14229</v>
       </c>
-      <c r="R29" s="2">
-        <v>0</v>
-      </c>
-      <c r="S29" s="2">
+      <c r="S29">
+        <v>0</v>
+      </c>
+      <c r="T29">
         <v>22</v>
       </c>
     </row>
-    <row r="30" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>27</v>
       </c>
       <c r="B30" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C30">
         <v>52653</v>
@@ -2346,17 +2431,17 @@
         <v>0</v>
       </c>
       <c r="E30">
+        <v>0</v>
+      </c>
+      <c r="F30">
         <v>52653</v>
       </c>
-      <c r="F30">
-        <v>0</v>
-      </c>
       <c r="G30">
+        <v>0</v>
+      </c>
+      <c r="H30">
         <v>52653</v>
       </c>
-      <c r="H30">
-        <v>0</v>
-      </c>
       <c r="I30">
         <v>0</v>
       </c>
@@ -2367,36 +2452,39 @@
         <v>0</v>
       </c>
       <c r="L30">
+        <v>0</v>
+      </c>
+      <c r="M30">
         <v>11659</v>
       </c>
-      <c r="M30">
+      <c r="N30">
         <v>411</v>
       </c>
-      <c r="N30">
+      <c r="O30">
         <v>5383</v>
       </c>
-      <c r="O30">
+      <c r="P30">
         <v>47272</v>
       </c>
-      <c r="P30">
+      <c r="Q30">
         <v>86933</v>
       </c>
-      <c r="Q30" s="2">
+      <c r="R30">
         <v>12564</v>
       </c>
-      <c r="R30" s="2">
-        <v>0</v>
-      </c>
-      <c r="S30" s="2">
+      <c r="S30">
+        <v>0</v>
+      </c>
+      <c r="T30">
         <v>8</v>
       </c>
     </row>
-    <row r="31" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>28</v>
       </c>
       <c r="B31" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C31">
         <v>91162</v>
@@ -2405,17 +2493,17 @@
         <v>0</v>
       </c>
       <c r="E31">
+        <v>0</v>
+      </c>
+      <c r="F31">
         <v>91162</v>
       </c>
-      <c r="F31">
-        <v>0</v>
-      </c>
       <c r="G31">
+        <v>0</v>
+      </c>
+      <c r="H31">
         <v>91162</v>
       </c>
-      <c r="H31">
-        <v>0</v>
-      </c>
       <c r="I31">
         <v>0</v>
       </c>
@@ -2426,36 +2514,39 @@
         <v>0</v>
       </c>
       <c r="L31">
+        <v>0</v>
+      </c>
+      <c r="M31">
         <v>46718</v>
       </c>
-      <c r="M31">
+      <c r="N31">
         <v>42</v>
       </c>
-      <c r="N31">
+      <c r="O31">
         <v>1899</v>
       </c>
-      <c r="O31">
+      <c r="P31">
         <v>89264</v>
       </c>
-      <c r="P31">
+      <c r="Q31">
         <v>81642</v>
       </c>
-      <c r="Q31" s="2">
+      <c r="R31">
         <v>14581</v>
       </c>
-      <c r="R31" s="2">
-        <v>0</v>
-      </c>
-      <c r="S31" s="2">
+      <c r="S31">
+        <v>0</v>
+      </c>
+      <c r="T31">
         <v>39</v>
       </c>
     </row>
-    <row r="32" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>29</v>
       </c>
       <c r="B32" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C32">
         <v>46728</v>
@@ -2464,17 +2555,17 @@
         <v>0</v>
       </c>
       <c r="E32">
+        <v>0</v>
+      </c>
+      <c r="F32">
         <v>46728</v>
       </c>
-      <c r="F32">
-        <v>0</v>
-      </c>
       <c r="G32">
+        <v>0</v>
+      </c>
+      <c r="H32">
         <v>46728</v>
       </c>
-      <c r="H32">
-        <v>0</v>
-      </c>
       <c r="I32">
         <v>0</v>
       </c>
@@ -2485,36 +2576,39 @@
         <v>0</v>
       </c>
       <c r="L32">
+        <v>0</v>
+      </c>
+      <c r="M32">
         <v>10557</v>
       </c>
-      <c r="M32">
+      <c r="N32">
         <v>316</v>
       </c>
-      <c r="N32">
+      <c r="O32">
         <v>4391</v>
       </c>
-      <c r="O32">
+      <c r="P32">
         <v>42344</v>
       </c>
-      <c r="P32">
+      <c r="Q32">
         <v>74810</v>
       </c>
-      <c r="Q32" s="2">
+      <c r="R32">
         <v>11379</v>
       </c>
-      <c r="R32" s="2">
-        <v>0</v>
-      </c>
-      <c r="S32" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="S32">
+        <v>0</v>
+      </c>
+      <c r="T32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>30</v>
       </c>
       <c r="B33" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C33">
         <v>40230</v>
@@ -2523,17 +2617,17 @@
         <v>0</v>
       </c>
       <c r="E33">
+        <v>0</v>
+      </c>
+      <c r="F33">
         <v>40230</v>
       </c>
-      <c r="F33">
-        <v>0</v>
-      </c>
       <c r="G33">
+        <v>0</v>
+      </c>
+      <c r="H33">
         <v>40230</v>
       </c>
-      <c r="H33">
-        <v>0</v>
-      </c>
       <c r="I33">
         <v>0</v>
       </c>
@@ -2544,36 +2638,39 @@
         <v>0</v>
       </c>
       <c r="L33">
+        <v>0</v>
+      </c>
+      <c r="M33">
         <v>5113</v>
       </c>
-      <c r="M33">
+      <c r="N33">
         <v>311</v>
       </c>
-      <c r="N33">
+      <c r="O33">
         <v>1275</v>
       </c>
-      <c r="O33">
+      <c r="P33">
         <v>38955</v>
       </c>
-      <c r="P33">
+      <c r="Q33">
         <v>76969</v>
       </c>
-      <c r="Q33" s="2">
+      <c r="R33">
         <v>6678</v>
       </c>
-      <c r="R33" s="2">
-        <v>0</v>
-      </c>
-      <c r="S33" s="2">
+      <c r="S33">
+        <v>0</v>
+      </c>
+      <c r="T33">
         <v>19</v>
       </c>
     </row>
-    <row r="34" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>31</v>
       </c>
       <c r="B34" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C34">
         <v>36542</v>
@@ -2582,17 +2679,17 @@
         <v>0</v>
       </c>
       <c r="E34">
+        <v>0</v>
+      </c>
+      <c r="F34">
         <v>36542</v>
       </c>
-      <c r="F34">
-        <v>0</v>
-      </c>
       <c r="G34">
+        <v>0</v>
+      </c>
+      <c r="H34">
         <v>36542</v>
       </c>
-      <c r="H34">
-        <v>0</v>
-      </c>
       <c r="I34">
         <v>0</v>
       </c>
@@ -2603,36 +2700,39 @@
         <v>0</v>
       </c>
       <c r="L34">
+        <v>0</v>
+      </c>
+      <c r="M34">
         <v>12439</v>
       </c>
-      <c r="M34">
+      <c r="N34">
         <v>513</v>
       </c>
-      <c r="N34">
+      <c r="O34">
         <v>1363</v>
       </c>
-      <c r="O34">
+      <c r="P34">
         <v>35181</v>
       </c>
-      <c r="P34">
+      <c r="Q34">
         <v>74624</v>
       </c>
-      <c r="Q34" s="2">
+      <c r="R34">
         <v>7137</v>
       </c>
-      <c r="R34" s="2">
-        <v>0</v>
-      </c>
-      <c r="S34" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="S34">
+        <v>0</v>
+      </c>
+      <c r="T34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>32</v>
       </c>
       <c r="B35" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C35">
         <v>33564</v>
@@ -2641,17 +2741,17 @@
         <v>0</v>
       </c>
       <c r="E35">
+        <v>0</v>
+      </c>
+      <c r="F35">
         <v>33564</v>
       </c>
-      <c r="F35">
-        <v>0</v>
-      </c>
       <c r="G35">
+        <v>0</v>
+      </c>
+      <c r="H35">
         <v>33564</v>
       </c>
-      <c r="H35">
-        <v>0</v>
-      </c>
       <c r="I35">
         <v>0</v>
       </c>
@@ -2662,36 +2762,39 @@
         <v>0</v>
       </c>
       <c r="L35">
+        <v>0</v>
+      </c>
+      <c r="M35">
         <v>7886</v>
       </c>
-      <c r="M35">
+      <c r="N35">
         <v>271</v>
       </c>
-      <c r="N35">
-        <v>1137</v>
-      </c>
       <c r="O35">
-        <v>32429</v>
+        <v>1141</v>
       </c>
       <c r="P35">
-        <v>76463</v>
-      </c>
-      <c r="Q35" s="2">
+        <v>32426</v>
+      </c>
+      <c r="Q35">
+        <v>76462</v>
+      </c>
+      <c r="R35">
         <v>8879</v>
       </c>
-      <c r="R35" s="2">
-        <v>0</v>
-      </c>
-      <c r="S35" s="2">
+      <c r="S35">
+        <v>0</v>
+      </c>
+      <c r="T35">
         <v>35</v>
       </c>
     </row>
-    <row r="36" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>33</v>
       </c>
       <c r="B36" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C36">
         <v>20905</v>
@@ -2700,17 +2803,17 @@
         <v>0</v>
       </c>
       <c r="E36">
+        <v>0</v>
+      </c>
+      <c r="F36">
         <v>20905</v>
       </c>
-      <c r="F36">
-        <v>0</v>
-      </c>
       <c r="G36">
+        <v>0</v>
+      </c>
+      <c r="H36">
         <v>20905</v>
       </c>
-      <c r="H36">
-        <v>0</v>
-      </c>
       <c r="I36">
         <v>0</v>
       </c>
@@ -2721,36 +2824,39 @@
         <v>0</v>
       </c>
       <c r="L36">
+        <v>0</v>
+      </c>
+      <c r="M36">
         <v>7350</v>
       </c>
-      <c r="M36">
-        <v>0</v>
-      </c>
       <c r="N36">
+        <v>0</v>
+      </c>
+      <c r="O36">
         <v>951</v>
       </c>
-      <c r="O36">
+      <c r="P36">
         <v>19954</v>
       </c>
-      <c r="P36">
+      <c r="Q36">
         <v>60419</v>
       </c>
-      <c r="Q36" s="2">
+      <c r="R36">
         <v>3855</v>
       </c>
-      <c r="R36" s="2">
-        <v>0</v>
-      </c>
-      <c r="S36" s="2">
+      <c r="S36">
+        <v>0</v>
+      </c>
+      <c r="T36">
         <v>2</v>
       </c>
     </row>
-    <row r="37" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>34</v>
       </c>
       <c r="B37" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C37">
         <v>17692</v>
@@ -2759,17 +2865,17 @@
         <v>0</v>
       </c>
       <c r="E37">
+        <v>0</v>
+      </c>
+      <c r="F37">
         <v>17692</v>
       </c>
-      <c r="F37">
-        <v>0</v>
-      </c>
       <c r="G37">
+        <v>0</v>
+      </c>
+      <c r="H37">
         <v>17692</v>
       </c>
-      <c r="H37">
-        <v>0</v>
-      </c>
       <c r="I37">
         <v>0</v>
       </c>
@@ -2780,36 +2886,39 @@
         <v>0</v>
       </c>
       <c r="L37">
+        <v>0</v>
+      </c>
+      <c r="M37">
         <v>2311</v>
       </c>
-      <c r="M37">
-        <v>0</v>
-      </c>
       <c r="N37">
+        <v>0</v>
+      </c>
+      <c r="O37">
         <v>541</v>
       </c>
-      <c r="O37">
+      <c r="P37">
         <v>17151</v>
       </c>
-      <c r="P37">
+      <c r="Q37">
         <v>57832</v>
       </c>
-      <c r="Q37" s="2">
+      <c r="R37">
         <v>4036</v>
       </c>
-      <c r="R37" s="2">
-        <v>0</v>
-      </c>
-      <c r="S37" s="2">
+      <c r="S37">
+        <v>0</v>
+      </c>
+      <c r="T37">
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>35</v>
       </c>
       <c r="B38" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C38">
         <v>29110</v>
@@ -2818,17 +2927,17 @@
         <v>0</v>
       </c>
       <c r="E38">
+        <v>1</v>
+      </c>
+      <c r="F38">
         <v>29110</v>
       </c>
-      <c r="F38">
-        <v>0</v>
-      </c>
       <c r="G38">
+        <v>0</v>
+      </c>
+      <c r="H38">
         <v>29110</v>
       </c>
-      <c r="H38">
-        <v>0</v>
-      </c>
       <c r="I38">
         <v>0</v>
       </c>
@@ -2839,36 +2948,39 @@
         <v>0</v>
       </c>
       <c r="L38">
+        <v>0</v>
+      </c>
+      <c r="M38">
         <v>5386</v>
       </c>
-      <c r="M38">
+      <c r="N38">
         <v>2</v>
       </c>
-      <c r="N38">
+      <c r="O38">
         <v>635</v>
       </c>
-      <c r="O38">
+      <c r="P38">
         <v>28475</v>
       </c>
-      <c r="P38">
+      <c r="Q38">
         <v>63038</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38">
         <v>5135</v>
       </c>
-      <c r="R38" s="2">
-        <v>0</v>
-      </c>
-      <c r="S38" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="39" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="S38">
+        <v>0</v>
+      </c>
+      <c r="T38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>36</v>
       </c>
       <c r="B39" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C39">
         <v>21367</v>
@@ -2877,17 +2989,17 @@
         <v>0</v>
       </c>
       <c r="E39">
+        <v>0</v>
+      </c>
+      <c r="F39">
         <v>21367</v>
       </c>
-      <c r="F39">
-        <v>0</v>
-      </c>
       <c r="G39">
+        <v>0</v>
+      </c>
+      <c r="H39">
         <v>21367</v>
       </c>
-      <c r="H39">
-        <v>0</v>
-      </c>
       <c r="I39">
         <v>0</v>
       </c>
@@ -2898,36 +3010,39 @@
         <v>0</v>
       </c>
       <c r="L39">
+        <v>0</v>
+      </c>
+      <c r="M39">
         <v>4529</v>
       </c>
-      <c r="M39">
+      <c r="N39">
         <v>1</v>
       </c>
-      <c r="N39">
+      <c r="O39">
         <v>234</v>
       </c>
-      <c r="O39">
+      <c r="P39">
         <v>21133</v>
       </c>
-      <c r="P39">
+      <c r="Q39">
         <v>71133</v>
       </c>
-      <c r="Q39" s="2">
+      <c r="R39">
         <v>5903</v>
       </c>
-      <c r="R39" s="2">
-        <v>0</v>
-      </c>
-      <c r="S39" s="2">
+      <c r="S39">
+        <v>0</v>
+      </c>
+      <c r="T39">
         <v>26</v>
       </c>
     </row>
-    <row r="40" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>37</v>
       </c>
       <c r="B40" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C40">
         <v>18905</v>
@@ -2936,17 +3051,17 @@
         <v>0</v>
       </c>
       <c r="E40">
+        <v>0</v>
+      </c>
+      <c r="F40">
         <v>18905</v>
       </c>
-      <c r="F40">
-        <v>0</v>
-      </c>
       <c r="G40">
+        <v>0</v>
+      </c>
+      <c r="H40">
         <v>18905</v>
       </c>
-      <c r="H40">
-        <v>0</v>
-      </c>
       <c r="I40">
         <v>0</v>
       </c>
@@ -2957,36 +3072,39 @@
         <v>0</v>
       </c>
       <c r="L40">
+        <v>0</v>
+      </c>
+      <c r="M40">
         <v>1812</v>
       </c>
-      <c r="M40">
-        <v>0</v>
-      </c>
       <c r="N40">
+        <v>0</v>
+      </c>
+      <c r="O40">
         <v>52</v>
       </c>
-      <c r="O40">
+      <c r="P40">
         <v>18853</v>
       </c>
-      <c r="P40">
+      <c r="Q40">
         <v>73242</v>
       </c>
-      <c r="Q40" s="2">
+      <c r="R40">
         <v>3824</v>
       </c>
-      <c r="R40" s="2">
-        <v>0</v>
-      </c>
-      <c r="S40" s="2">
+      <c r="S40">
+        <v>0</v>
+      </c>
+      <c r="T40">
         <v>61</v>
       </c>
     </row>
-    <row r="41" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>38</v>
       </c>
       <c r="B41" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C41">
         <v>23521</v>
@@ -2995,17 +3113,17 @@
         <v>0</v>
       </c>
       <c r="E41">
+        <v>0</v>
+      </c>
+      <c r="F41">
         <v>23521</v>
       </c>
-      <c r="F41">
-        <v>0</v>
-      </c>
       <c r="G41">
+        <v>0</v>
+      </c>
+      <c r="H41">
         <v>23521</v>
       </c>
-      <c r="H41">
-        <v>0</v>
-      </c>
       <c r="I41">
         <v>0</v>
       </c>
@@ -3016,36 +3134,39 @@
         <v>0</v>
       </c>
       <c r="L41">
+        <v>0</v>
+      </c>
+      <c r="M41">
         <v>1499</v>
       </c>
-      <c r="M41">
-        <v>0</v>
-      </c>
       <c r="N41">
+        <v>0</v>
+      </c>
+      <c r="O41">
         <v>92</v>
       </c>
-      <c r="O41">
+      <c r="P41">
         <v>23429</v>
       </c>
-      <c r="P41">
+      <c r="Q41">
         <v>85251</v>
       </c>
-      <c r="Q41" s="2">
+      <c r="R41">
         <v>6015</v>
       </c>
-      <c r="R41" s="2">
-        <v>0</v>
-      </c>
-      <c r="S41" s="2">
+      <c r="S41">
+        <v>0</v>
+      </c>
+      <c r="T41">
         <v>27</v>
       </c>
     </row>
-    <row r="42" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>39</v>
       </c>
       <c r="B42" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C42">
         <v>27565</v>
@@ -3054,17 +3175,17 @@
         <v>0</v>
       </c>
       <c r="E42">
+        <v>0</v>
+      </c>
+      <c r="F42">
         <v>27565</v>
       </c>
-      <c r="F42">
-        <v>0</v>
-      </c>
       <c r="G42">
+        <v>0</v>
+      </c>
+      <c r="H42">
         <v>27565</v>
       </c>
-      <c r="H42">
-        <v>0</v>
-      </c>
       <c r="I42">
         <v>0</v>
       </c>
@@ -3075,36 +3196,39 @@
         <v>0</v>
       </c>
       <c r="L42">
+        <v>0</v>
+      </c>
+      <c r="M42">
         <v>6264</v>
       </c>
-      <c r="M42">
-        <v>0</v>
-      </c>
       <c r="N42">
+        <v>0</v>
+      </c>
+      <c r="O42">
         <v>419</v>
       </c>
-      <c r="O42">
+      <c r="P42">
         <v>27147</v>
       </c>
-      <c r="P42">
+      <c r="Q42">
         <v>68615</v>
       </c>
-      <c r="Q42" s="2">
+      <c r="R42">
         <v>4708</v>
       </c>
-      <c r="R42" s="2">
-        <v>0</v>
-      </c>
-      <c r="S42" s="2">
+      <c r="S42">
+        <v>0</v>
+      </c>
+      <c r="T42">
         <v>8</v>
       </c>
     </row>
-    <row r="43" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>40</v>
       </c>
       <c r="B43" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C43">
         <v>29700</v>
@@ -3113,17 +3237,17 @@
         <v>0</v>
       </c>
       <c r="E43">
+        <v>0</v>
+      </c>
+      <c r="F43">
         <v>29700</v>
       </c>
-      <c r="F43">
-        <v>0</v>
-      </c>
       <c r="G43">
+        <v>0</v>
+      </c>
+      <c r="H43">
         <v>29700</v>
       </c>
-      <c r="H43">
-        <v>0</v>
-      </c>
       <c r="I43">
         <v>0</v>
       </c>
@@ -3134,36 +3258,39 @@
         <v>0</v>
       </c>
       <c r="L43">
+        <v>0</v>
+      </c>
+      <c r="M43">
         <v>6804</v>
       </c>
-      <c r="M43">
+      <c r="N43">
         <v>1</v>
       </c>
-      <c r="N43">
+      <c r="O43">
         <v>957</v>
       </c>
-      <c r="O43">
+      <c r="P43">
         <v>28774</v>
       </c>
-      <c r="P43">
+      <c r="Q43">
         <v>63012</v>
       </c>
-      <c r="Q43" s="2">
+      <c r="R43">
         <v>5219</v>
       </c>
-      <c r="R43" s="2">
-        <v>0</v>
-      </c>
-      <c r="S43" s="2">
+      <c r="S43">
+        <v>0</v>
+      </c>
+      <c r="T43">
         <v>121</v>
       </c>
     </row>
-    <row r="44" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A44">
         <v>41</v>
       </c>
       <c r="B44" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C44">
         <v>21900</v>
@@ -3172,17 +3299,17 @@
         <v>0</v>
       </c>
       <c r="E44">
+        <v>0</v>
+      </c>
+      <c r="F44">
         <v>21900</v>
       </c>
-      <c r="F44">
-        <v>0</v>
-      </c>
       <c r="G44">
+        <v>0</v>
+      </c>
+      <c r="H44">
         <v>21900</v>
       </c>
-      <c r="H44">
-        <v>0</v>
-      </c>
       <c r="I44">
         <v>0</v>
       </c>
@@ -3193,36 +3320,39 @@
         <v>0</v>
       </c>
       <c r="L44">
+        <v>0</v>
+      </c>
+      <c r="M44">
         <v>6643</v>
       </c>
-      <c r="M44">
+      <c r="N44">
         <v>24</v>
       </c>
-      <c r="N44">
+      <c r="O44">
         <v>347</v>
       </c>
-      <c r="O44">
+      <c r="P44">
         <v>21553</v>
       </c>
-      <c r="P44">
+      <c r="Q44">
         <v>68393</v>
       </c>
-      <c r="Q44" s="2">
+      <c r="R44">
         <v>7659</v>
       </c>
-      <c r="R44" s="2">
-        <v>0</v>
-      </c>
-      <c r="S44" s="2">
+      <c r="S44">
+        <v>0</v>
+      </c>
+      <c r="T44">
         <v>20</v>
       </c>
     </row>
-    <row r="45" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A45">
         <v>42</v>
       </c>
       <c r="B45" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C45">
         <v>19935</v>
@@ -3231,17 +3361,17 @@
         <v>0</v>
       </c>
       <c r="E45">
+        <v>0</v>
+      </c>
+      <c r="F45">
         <v>19935</v>
       </c>
-      <c r="F45">
-        <v>0</v>
-      </c>
       <c r="G45">
+        <v>0</v>
+      </c>
+      <c r="H45">
         <v>19935</v>
       </c>
-      <c r="H45">
-        <v>0</v>
-      </c>
       <c r="I45">
         <v>0</v>
       </c>
@@ -3252,36 +3382,39 @@
         <v>0</v>
       </c>
       <c r="L45">
+        <v>0</v>
+      </c>
+      <c r="M45">
         <v>2254</v>
       </c>
-      <c r="M45">
+      <c r="N45">
         <v>13</v>
       </c>
-      <c r="N45">
+      <c r="O45">
         <v>149</v>
       </c>
-      <c r="O45">
+      <c r="P45">
         <v>19786</v>
       </c>
-      <c r="P45">
+      <c r="Q45">
         <v>76287</v>
       </c>
-      <c r="Q45" s="2">
+      <c r="R45">
         <v>6998</v>
       </c>
-      <c r="R45" s="2">
-        <v>0</v>
-      </c>
-      <c r="S45" s="2">
+      <c r="S45">
+        <v>0</v>
+      </c>
+      <c r="T45">
         <v>129</v>
       </c>
     </row>
-    <row r="46" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A46">
         <v>43</v>
       </c>
       <c r="B46" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C46">
         <v>21512</v>
@@ -3290,17 +3423,17 @@
         <v>0</v>
       </c>
       <c r="E46">
+        <v>0</v>
+      </c>
+      <c r="F46">
         <v>21512</v>
       </c>
-      <c r="F46">
-        <v>0</v>
-      </c>
       <c r="G46">
+        <v>0</v>
+      </c>
+      <c r="H46">
         <v>21512</v>
       </c>
-      <c r="H46">
-        <v>0</v>
-      </c>
       <c r="I46">
         <v>0</v>
       </c>
@@ -3311,36 +3444,39 @@
         <v>0</v>
       </c>
       <c r="L46">
+        <v>0</v>
+      </c>
+      <c r="M46">
         <v>8303</v>
       </c>
-      <c r="M46">
+      <c r="N46">
         <v>32</v>
       </c>
-      <c r="N46">
+      <c r="O46">
         <v>276</v>
       </c>
-      <c r="O46">
+      <c r="P46">
         <v>21236</v>
       </c>
-      <c r="P46">
+      <c r="Q46">
         <v>64160</v>
       </c>
-      <c r="Q46" s="2">
+      <c r="R46">
         <v>7548</v>
       </c>
-      <c r="R46" s="2">
-        <v>0</v>
-      </c>
-      <c r="S46" s="2">
+      <c r="S46">
+        <v>0</v>
+      </c>
+      <c r="T46">
         <v>152</v>
       </c>
     </row>
-    <row r="47" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A47">
         <v>44</v>
       </c>
       <c r="B47" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C47">
         <v>22426</v>
@@ -3349,17 +3485,17 @@
         <v>0</v>
       </c>
       <c r="E47">
+        <v>0</v>
+      </c>
+      <c r="F47">
         <v>22426</v>
       </c>
-      <c r="F47">
-        <v>0</v>
-      </c>
       <c r="G47">
+        <v>0</v>
+      </c>
+      <c r="H47">
         <v>22426</v>
       </c>
-      <c r="H47">
-        <v>0</v>
-      </c>
       <c r="I47">
         <v>0</v>
       </c>
@@ -3370,36 +3506,39 @@
         <v>0</v>
       </c>
       <c r="L47">
+        <v>0</v>
+      </c>
+      <c r="M47">
         <v>2595</v>
       </c>
-      <c r="M47">
+      <c r="N47">
         <v>1</v>
       </c>
-      <c r="N47">
-        <v>137</v>
-      </c>
       <c r="O47">
-        <v>22289</v>
+        <v>142</v>
       </c>
       <c r="P47">
+        <v>22284</v>
+      </c>
+      <c r="Q47">
         <v>50821</v>
       </c>
-      <c r="Q47" s="2">
+      <c r="R47">
         <v>5046</v>
       </c>
-      <c r="R47" s="2">
-        <v>0</v>
-      </c>
-      <c r="S47" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="48" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="S47">
+        <v>0</v>
+      </c>
+      <c r="T47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A48">
         <v>45</v>
       </c>
       <c r="B48" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C48">
         <v>19641</v>
@@ -3408,17 +3547,17 @@
         <v>0</v>
       </c>
       <c r="E48">
+        <v>0</v>
+      </c>
+      <c r="F48">
         <v>19641</v>
       </c>
-      <c r="F48">
-        <v>0</v>
-      </c>
       <c r="G48">
+        <v>0</v>
+      </c>
+      <c r="H48">
         <v>19641</v>
       </c>
-      <c r="H48">
-        <v>0</v>
-      </c>
       <c r="I48">
         <v>0</v>
       </c>
@@ -3429,36 +3568,39 @@
         <v>0</v>
       </c>
       <c r="L48">
+        <v>0</v>
+      </c>
+      <c r="M48">
         <v>3800</v>
       </c>
-      <c r="M48">
+      <c r="N48">
         <v>4</v>
       </c>
-      <c r="N48">
-        <v>262</v>
-      </c>
       <c r="O48">
-        <v>19380</v>
+        <v>266</v>
       </c>
       <c r="P48">
+        <v>19376</v>
+      </c>
+      <c r="Q48">
         <v>54497</v>
       </c>
-      <c r="Q48" s="2">
+      <c r="R48">
         <v>4623</v>
       </c>
-      <c r="R48" s="2">
-        <v>0</v>
-      </c>
-      <c r="S48" s="2">
+      <c r="S48">
+        <v>0</v>
+      </c>
+      <c r="T48">
         <v>9</v>
       </c>
     </row>
-    <row r="49" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A49">
         <v>46</v>
       </c>
       <c r="B49" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C49">
         <v>21651</v>
@@ -3467,17 +3609,17 @@
         <v>0</v>
       </c>
       <c r="E49">
+        <v>0</v>
+      </c>
+      <c r="F49">
         <v>21651</v>
       </c>
-      <c r="F49">
-        <v>0</v>
-      </c>
       <c r="G49">
+        <v>0</v>
+      </c>
+      <c r="H49">
         <v>21651</v>
       </c>
-      <c r="H49">
-        <v>0</v>
-      </c>
       <c r="I49">
         <v>0</v>
       </c>
@@ -3488,36 +3630,39 @@
         <v>0</v>
       </c>
       <c r="L49">
+        <v>0</v>
+      </c>
+      <c r="M49">
         <v>3627</v>
       </c>
-      <c r="M49">
-        <v>0</v>
-      </c>
       <c r="N49">
+        <v>0</v>
+      </c>
+      <c r="O49">
         <v>628</v>
       </c>
-      <c r="O49">
+      <c r="P49">
         <v>21027</v>
       </c>
-      <c r="P49">
+      <c r="Q49">
         <v>55376</v>
       </c>
-      <c r="Q49" s="2">
+      <c r="R49">
         <v>5057</v>
       </c>
-      <c r="R49" s="2">
-        <v>0</v>
-      </c>
-      <c r="S49" s="2">
+      <c r="S49">
+        <v>0</v>
+      </c>
+      <c r="T49">
         <v>4</v>
       </c>
     </row>
-    <row r="50" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A50">
         <v>47</v>
       </c>
       <c r="B50" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C50">
         <v>21936</v>
@@ -3526,17 +3671,17 @@
         <v>0</v>
       </c>
       <c r="E50">
+        <v>0</v>
+      </c>
+      <c r="F50">
         <v>21936</v>
       </c>
-      <c r="F50">
-        <v>0</v>
-      </c>
       <c r="G50">
+        <v>0</v>
+      </c>
+      <c r="H50">
         <v>21936</v>
       </c>
-      <c r="H50">
-        <v>0</v>
-      </c>
       <c r="I50">
         <v>0</v>
       </c>
@@ -3547,36 +3692,39 @@
         <v>0</v>
       </c>
       <c r="L50">
+        <v>0</v>
+      </c>
+      <c r="M50">
         <v>4160</v>
       </c>
-      <c r="M50">
+      <c r="N50">
         <v>5</v>
       </c>
-      <c r="N50">
+      <c r="O50">
         <v>26</v>
       </c>
-      <c r="O50">
+      <c r="P50">
         <v>21910</v>
       </c>
-      <c r="P50">
+      <c r="Q50">
         <v>63298</v>
       </c>
-      <c r="Q50" s="2">
+      <c r="R50">
         <v>7292</v>
       </c>
-      <c r="R50" s="2">
-        <v>0</v>
-      </c>
-      <c r="S50" s="2">
+      <c r="S50">
+        <v>0</v>
+      </c>
+      <c r="T50">
         <v>1</v>
       </c>
     </row>
-    <row r="51" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A51">
         <v>48</v>
       </c>
       <c r="B51" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C51">
         <v>23798</v>
@@ -3585,17 +3733,17 @@
         <v>0</v>
       </c>
       <c r="E51">
+        <v>0</v>
+      </c>
+      <c r="F51">
         <v>23798</v>
       </c>
-      <c r="F51">
-        <v>0</v>
-      </c>
       <c r="G51">
+        <v>0</v>
+      </c>
+      <c r="H51">
         <v>23798</v>
       </c>
-      <c r="H51">
-        <v>0</v>
-      </c>
       <c r="I51">
         <v>0</v>
       </c>
@@ -3606,36 +3754,39 @@
         <v>0</v>
       </c>
       <c r="L51">
+        <v>0</v>
+      </c>
+      <c r="M51">
         <v>4843</v>
       </c>
-      <c r="M51">
+      <c r="N51">
         <v>11</v>
       </c>
-      <c r="N51">
+      <c r="O51">
         <v>75</v>
       </c>
-      <c r="O51">
+      <c r="P51">
         <v>23723</v>
       </c>
-      <c r="P51">
+      <c r="Q51">
         <v>71754</v>
       </c>
-      <c r="Q51" s="2">
+      <c r="R51">
         <v>7715</v>
       </c>
-      <c r="R51" s="2">
-        <v>0</v>
-      </c>
-      <c r="S51" s="2">
+      <c r="S51">
+        <v>0</v>
+      </c>
+      <c r="T51">
         <v>40</v>
       </c>
     </row>
-    <row r="52" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A52">
         <v>49</v>
       </c>
       <c r="B52" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C52">
         <v>21094</v>
@@ -3644,17 +3795,17 @@
         <v>0</v>
       </c>
       <c r="E52">
+        <v>0</v>
+      </c>
+      <c r="F52">
         <v>21094</v>
       </c>
-      <c r="F52">
-        <v>0</v>
-      </c>
       <c r="G52">
+        <v>0</v>
+      </c>
+      <c r="H52">
         <v>21094</v>
       </c>
-      <c r="H52">
-        <v>0</v>
-      </c>
       <c r="I52">
         <v>0</v>
       </c>
@@ -3665,36 +3816,39 @@
         <v>0</v>
       </c>
       <c r="L52">
+        <v>0</v>
+      </c>
+      <c r="M52">
         <v>2942</v>
       </c>
-      <c r="M52">
+      <c r="N52">
         <v>1</v>
       </c>
-      <c r="N52">
+      <c r="O52">
         <v>45</v>
       </c>
-      <c r="O52">
+      <c r="P52">
         <v>21049</v>
       </c>
-      <c r="P52">
+      <c r="Q52">
         <v>63987</v>
       </c>
-      <c r="Q52" s="2">
+      <c r="R52">
         <v>5655</v>
       </c>
-      <c r="R52" s="2">
-        <v>0</v>
-      </c>
-      <c r="S52" s="2">
+      <c r="S52">
+        <v>0</v>
+      </c>
+      <c r="T52">
         <v>2</v>
       </c>
     </row>
-    <row r="53" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A53">
         <v>50</v>
       </c>
       <c r="B53" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C53">
         <v>19131</v>
@@ -3703,17 +3857,17 @@
         <v>0</v>
       </c>
       <c r="E53">
+        <v>0</v>
+      </c>
+      <c r="F53">
         <v>19131</v>
       </c>
-      <c r="F53">
-        <v>0</v>
-      </c>
       <c r="G53">
+        <v>0</v>
+      </c>
+      <c r="H53">
         <v>19131</v>
       </c>
-      <c r="H53">
-        <v>0</v>
-      </c>
       <c r="I53">
         <v>0</v>
       </c>
@@ -3724,36 +3878,39 @@
         <v>0</v>
       </c>
       <c r="L53">
+        <v>0</v>
+      </c>
+      <c r="M53">
         <v>3513</v>
       </c>
-      <c r="M53">
+      <c r="N53">
         <v>1</v>
       </c>
-      <c r="N53">
+      <c r="O53">
         <v>76</v>
       </c>
-      <c r="O53">
+      <c r="P53">
         <v>19055</v>
       </c>
-      <c r="P53">
+      <c r="Q53">
         <v>56306</v>
       </c>
-      <c r="Q53" s="2">
+      <c r="R53">
         <v>6551</v>
       </c>
-      <c r="R53" s="2">
-        <v>0</v>
-      </c>
-      <c r="S53" s="2">
+      <c r="S53">
+        <v>0</v>
+      </c>
+      <c r="T53">
         <v>5</v>
       </c>
     </row>
-    <row r="54" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A54">
         <v>51</v>
       </c>
       <c r="B54" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C54">
         <v>20758</v>
@@ -3762,17 +3919,17 @@
         <v>0</v>
       </c>
       <c r="E54">
+        <v>0</v>
+      </c>
+      <c r="F54">
         <v>20758</v>
       </c>
-      <c r="F54">
-        <v>0</v>
-      </c>
       <c r="G54">
+        <v>0</v>
+      </c>
+      <c r="H54">
         <v>20758</v>
       </c>
-      <c r="H54">
-        <v>0</v>
-      </c>
       <c r="I54">
         <v>0</v>
       </c>
@@ -3783,36 +3940,39 @@
         <v>0</v>
       </c>
       <c r="L54">
+        <v>0</v>
+      </c>
+      <c r="M54">
         <v>2603</v>
       </c>
-      <c r="M54">
+      <c r="N54">
         <v>5</v>
       </c>
-      <c r="N54">
+      <c r="O54">
         <v>391</v>
       </c>
-      <c r="O54">
+      <c r="P54">
         <v>20367</v>
       </c>
-      <c r="P54">
+      <c r="Q54">
         <v>58441</v>
       </c>
-      <c r="Q54" s="2">
+      <c r="R54">
         <v>7347</v>
       </c>
-      <c r="R54" s="2">
-        <v>0</v>
-      </c>
-      <c r="S54" s="2">
+      <c r="S54">
+        <v>0</v>
+      </c>
+      <c r="T54">
         <v>1</v>
       </c>
     </row>
-    <row r="55" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A55">
         <v>52</v>
       </c>
       <c r="B55" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C55">
         <v>16022</v>
@@ -3821,17 +3981,17 @@
         <v>0</v>
       </c>
       <c r="E55">
+        <v>0</v>
+      </c>
+      <c r="F55">
         <v>16022</v>
       </c>
-      <c r="F55">
-        <v>0</v>
-      </c>
       <c r="G55">
+        <v>0</v>
+      </c>
+      <c r="H55">
         <v>16022</v>
       </c>
-      <c r="H55">
-        <v>0</v>
-      </c>
       <c r="I55">
         <v>0</v>
       </c>
@@ -3842,36 +4002,39 @@
         <v>0</v>
       </c>
       <c r="L55">
+        <v>0</v>
+      </c>
+      <c r="M55">
         <v>2109</v>
       </c>
-      <c r="M55">
+      <c r="N55">
         <v>1</v>
       </c>
-      <c r="N55">
+      <c r="O55">
         <v>129</v>
       </c>
-      <c r="O55">
+      <c r="P55">
         <v>15893</v>
       </c>
-      <c r="P55">
+      <c r="Q55">
         <v>58215</v>
       </c>
-      <c r="Q55" s="2">
+      <c r="R55">
         <v>5098</v>
       </c>
-      <c r="R55" s="2">
-        <v>0</v>
-      </c>
-      <c r="S55" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="56" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="S55">
+        <v>0</v>
+      </c>
+      <c r="T55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A56">
         <v>53</v>
       </c>
       <c r="B56" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C56">
         <v>19256</v>
@@ -3880,17 +4043,17 @@
         <v>0</v>
       </c>
       <c r="E56">
+        <v>0</v>
+      </c>
+      <c r="F56">
         <v>19256</v>
       </c>
-      <c r="F56">
-        <v>0</v>
-      </c>
       <c r="G56">
+        <v>0</v>
+      </c>
+      <c r="H56">
         <v>19256</v>
       </c>
-      <c r="H56">
-        <v>0</v>
-      </c>
       <c r="I56">
         <v>0</v>
       </c>
@@ -3901,36 +4064,39 @@
         <v>0</v>
       </c>
       <c r="L56">
+        <v>0</v>
+      </c>
+      <c r="M56">
         <v>4091</v>
       </c>
-      <c r="M56">
+      <c r="N56">
         <v>3</v>
       </c>
-      <c r="N56">
+      <c r="O56">
         <v>451</v>
       </c>
-      <c r="O56">
+      <c r="P56">
         <v>18805</v>
       </c>
-      <c r="P56">
+      <c r="Q56">
         <v>47621</v>
       </c>
-      <c r="Q56" s="2">
+      <c r="R56">
         <v>4882</v>
       </c>
-      <c r="R56" s="2">
-        <v>0</v>
-      </c>
-      <c r="S56" s="2">
+      <c r="S56">
+        <v>0</v>
+      </c>
+      <c r="T56">
         <v>30</v>
       </c>
     </row>
-    <row r="57" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A57">
         <v>54</v>
       </c>
       <c r="B57" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C57">
         <v>21240</v>
@@ -3939,17 +4105,17 @@
         <v>0</v>
       </c>
       <c r="E57">
+        <v>0</v>
+      </c>
+      <c r="F57">
         <v>21240</v>
       </c>
-      <c r="F57">
-        <v>0</v>
-      </c>
       <c r="G57">
+        <v>0</v>
+      </c>
+      <c r="H57">
         <v>21240</v>
       </c>
-      <c r="H57">
-        <v>0</v>
-      </c>
       <c r="I57">
         <v>0</v>
       </c>
@@ -3960,36 +4126,39 @@
         <v>0</v>
       </c>
       <c r="L57">
+        <v>0</v>
+      </c>
+      <c r="M57">
         <v>1905</v>
       </c>
-      <c r="M57">
+      <c r="N57">
         <v>5</v>
       </c>
-      <c r="N57">
+      <c r="O57">
         <v>39</v>
       </c>
-      <c r="O57">
+      <c r="P57">
         <v>21201</v>
       </c>
-      <c r="P57">
+      <c r="Q57">
         <v>61557</v>
       </c>
-      <c r="Q57" s="2">
+      <c r="R57">
         <v>6870</v>
       </c>
-      <c r="R57" s="2">
-        <v>0</v>
-      </c>
-      <c r="S57" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="58" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="S57">
+        <v>0</v>
+      </c>
+      <c r="T57">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A58">
         <v>55</v>
       </c>
       <c r="B58" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C58">
         <v>22819</v>
@@ -3998,17 +4167,17 @@
         <v>0</v>
       </c>
       <c r="E58">
+        <v>0</v>
+      </c>
+      <c r="F58">
         <v>22819</v>
       </c>
-      <c r="F58">
-        <v>0</v>
-      </c>
       <c r="G58">
+        <v>0</v>
+      </c>
+      <c r="H58">
         <v>22819</v>
       </c>
-      <c r="H58">
-        <v>0</v>
-      </c>
       <c r="I58">
         <v>0</v>
       </c>
@@ -4019,36 +4188,39 @@
         <v>0</v>
       </c>
       <c r="L58">
+        <v>0</v>
+      </c>
+      <c r="M58">
         <v>8123</v>
       </c>
-      <c r="M58">
+      <c r="N58">
         <v>10</v>
       </c>
-      <c r="N58">
+      <c r="O58">
         <v>552</v>
       </c>
-      <c r="O58">
+      <c r="P58">
         <v>22267</v>
       </c>
-      <c r="P58">
+      <c r="Q58">
         <v>57577</v>
       </c>
-      <c r="Q58" s="2">
+      <c r="R58">
         <v>8884</v>
       </c>
-      <c r="R58" s="2">
-        <v>0</v>
-      </c>
-      <c r="S58" s="2">
+      <c r="S58">
+        <v>0</v>
+      </c>
+      <c r="T58">
         <v>64</v>
       </c>
     </row>
-    <row r="59" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A59">
         <v>56</v>
       </c>
       <c r="B59" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C59">
         <v>18776</v>
@@ -4057,17 +4229,17 @@
         <v>0</v>
       </c>
       <c r="E59">
+        <v>0</v>
+      </c>
+      <c r="F59">
         <v>18776</v>
       </c>
-      <c r="F59">
-        <v>0</v>
-      </c>
       <c r="G59">
+        <v>0</v>
+      </c>
+      <c r="H59">
         <v>18776</v>
       </c>
-      <c r="H59">
-        <v>0</v>
-      </c>
       <c r="I59">
         <v>0</v>
       </c>
@@ -4078,36 +4250,39 @@
         <v>0</v>
       </c>
       <c r="L59">
+        <v>0</v>
+      </c>
+      <c r="M59">
         <v>2506</v>
       </c>
-      <c r="M59">
+      <c r="N59">
         <v>2</v>
       </c>
-      <c r="N59">
+      <c r="O59">
         <v>287</v>
       </c>
-      <c r="O59">
+      <c r="P59">
         <v>18489</v>
       </c>
-      <c r="P59">
+      <c r="Q59">
         <v>60495</v>
       </c>
-      <c r="Q59" s="2">
+      <c r="R59">
         <v>8028</v>
       </c>
-      <c r="R59" s="2">
-        <v>0</v>
-      </c>
-      <c r="S59" s="2">
+      <c r="S59">
+        <v>0</v>
+      </c>
+      <c r="T59">
         <v>27</v>
       </c>
     </row>
-    <row r="60" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A60">
         <v>57</v>
       </c>
       <c r="B60" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C60">
         <v>23749</v>
@@ -4116,17 +4291,17 @@
         <v>0</v>
       </c>
       <c r="E60">
+        <v>0</v>
+      </c>
+      <c r="F60">
         <v>23749</v>
       </c>
-      <c r="F60">
-        <v>0</v>
-      </c>
       <c r="G60">
+        <v>0</v>
+      </c>
+      <c r="H60">
         <v>23749</v>
       </c>
-      <c r="H60">
-        <v>0</v>
-      </c>
       <c r="I60">
         <v>0</v>
       </c>
@@ -4137,36 +4312,39 @@
         <v>0</v>
       </c>
       <c r="L60">
+        <v>0</v>
+      </c>
+      <c r="M60">
         <v>5815</v>
       </c>
-      <c r="M60">
+      <c r="N60">
         <v>9</v>
       </c>
-      <c r="N60">
+      <c r="O60">
         <v>324</v>
       </c>
-      <c r="O60">
+      <c r="P60">
         <v>23425</v>
       </c>
-      <c r="P60">
+      <c r="Q60">
         <v>70140</v>
       </c>
-      <c r="Q60" s="2">
+      <c r="R60">
         <v>7415</v>
       </c>
-      <c r="R60" s="2">
-        <v>0</v>
-      </c>
-      <c r="S60" s="2">
+      <c r="S60">
+        <v>0</v>
+      </c>
+      <c r="T60">
         <v>32</v>
       </c>
     </row>
-    <row r="61" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A61">
         <v>58</v>
       </c>
       <c r="B61" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C61">
         <v>22069</v>
@@ -4175,17 +4353,17 @@
         <v>0</v>
       </c>
       <c r="E61">
+        <v>0</v>
+      </c>
+      <c r="F61">
         <v>22069</v>
       </c>
-      <c r="F61">
-        <v>0</v>
-      </c>
       <c r="G61">
+        <v>0</v>
+      </c>
+      <c r="H61">
         <v>22069</v>
       </c>
-      <c r="H61">
-        <v>0</v>
-      </c>
       <c r="I61">
         <v>0</v>
       </c>
@@ -4196,36 +4374,39 @@
         <v>0</v>
       </c>
       <c r="L61">
+        <v>0</v>
+      </c>
+      <c r="M61">
         <v>9977</v>
       </c>
-      <c r="M61">
+      <c r="N61">
         <v>37</v>
       </c>
-      <c r="N61">
+      <c r="O61">
         <v>36</v>
       </c>
-      <c r="O61">
+      <c r="P61">
         <v>22033</v>
       </c>
-      <c r="P61">
+      <c r="Q61">
         <v>55240</v>
       </c>
-      <c r="Q61" s="2">
+      <c r="R61">
         <v>7927</v>
       </c>
-      <c r="R61" s="2">
+      <c r="S61">
         <v>1</v>
       </c>
-      <c r="S61" s="2">
+      <c r="T61">
         <v>268</v>
       </c>
     </row>
-    <row r="62" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A62">
         <v>59</v>
       </c>
       <c r="B62" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C62">
         <v>15800</v>
@@ -4234,17 +4415,17 @@
         <v>0</v>
       </c>
       <c r="E62">
+        <v>0</v>
+      </c>
+      <c r="F62">
         <v>15800</v>
       </c>
-      <c r="F62">
-        <v>0</v>
-      </c>
       <c r="G62">
+        <v>0</v>
+      </c>
+      <c r="H62">
         <v>15800</v>
       </c>
-      <c r="H62">
-        <v>0</v>
-      </c>
       <c r="I62">
         <v>0</v>
       </c>
@@ -4255,36 +4436,39 @@
         <v>0</v>
       </c>
       <c r="L62">
+        <v>0</v>
+      </c>
+      <c r="M62">
         <v>4214</v>
       </c>
-      <c r="M62">
+      <c r="N62">
         <v>19</v>
       </c>
-      <c r="N62">
+      <c r="O62">
         <v>494</v>
       </c>
-      <c r="O62">
+      <c r="P62">
         <v>15306</v>
       </c>
-      <c r="P62">
+      <c r="Q62">
         <v>51334</v>
       </c>
-      <c r="Q62" s="2">
+      <c r="R62">
         <v>6917</v>
       </c>
-      <c r="R62" s="2">
-        <v>0</v>
-      </c>
-      <c r="S62" s="2">
+      <c r="S62">
+        <v>0</v>
+      </c>
+      <c r="T62">
         <v>100</v>
       </c>
     </row>
-    <row r="63" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A63">
         <v>60</v>
       </c>
       <c r="B63" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C63">
         <v>36754</v>
@@ -4293,17 +4477,17 @@
         <v>0</v>
       </c>
       <c r="E63">
+        <v>0</v>
+      </c>
+      <c r="F63">
         <v>36754</v>
       </c>
-      <c r="F63">
-        <v>0</v>
-      </c>
       <c r="G63">
+        <v>0</v>
+      </c>
+      <c r="H63">
         <v>36754</v>
       </c>
-      <c r="H63">
-        <v>0</v>
-      </c>
       <c r="I63">
         <v>0</v>
       </c>
@@ -4314,36 +4498,39 @@
         <v>0</v>
       </c>
       <c r="L63">
+        <v>0</v>
+      </c>
+      <c r="M63">
         <v>10975</v>
       </c>
-      <c r="M63">
+      <c r="N63">
         <v>68</v>
       </c>
-      <c r="N63">
+      <c r="O63">
         <v>931</v>
       </c>
-      <c r="O63">
+      <c r="P63">
         <v>35823</v>
       </c>
-      <c r="P63">
+      <c r="Q63">
         <v>68699</v>
       </c>
-      <c r="Q63" s="2">
+      <c r="R63">
         <v>9766</v>
       </c>
-      <c r="R63" s="2">
-        <v>0</v>
-      </c>
-      <c r="S63" s="2">
+      <c r="S63">
+        <v>0</v>
+      </c>
+      <c r="T63">
         <v>153</v>
       </c>
     </row>
-    <row r="64" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A64">
         <v>61</v>
       </c>
       <c r="B64" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C64">
         <v>42048</v>
@@ -4352,17 +4539,17 @@
         <v>0</v>
       </c>
       <c r="E64">
+        <v>0</v>
+      </c>
+      <c r="F64">
         <v>42048</v>
       </c>
-      <c r="F64">
-        <v>0</v>
-      </c>
       <c r="G64">
+        <v>0</v>
+      </c>
+      <c r="H64">
         <v>42048</v>
       </c>
-      <c r="H64">
-        <v>0</v>
-      </c>
       <c r="I64">
         <v>0</v>
       </c>
@@ -4373,36 +4560,39 @@
         <v>0</v>
       </c>
       <c r="L64">
+        <v>0</v>
+      </c>
+      <c r="M64">
         <v>9887</v>
       </c>
-      <c r="M64">
+      <c r="N64">
         <v>8</v>
       </c>
-      <c r="N64">
+      <c r="O64">
         <v>493</v>
       </c>
-      <c r="O64">
+      <c r="P64">
         <v>41555</v>
       </c>
-      <c r="P64">
+      <c r="Q64">
         <v>60527</v>
       </c>
-      <c r="Q64" s="2">
+      <c r="R64">
         <v>5985</v>
       </c>
-      <c r="R64" s="2">
-        <v>0</v>
-      </c>
-      <c r="S64" s="2">
+      <c r="S64">
+        <v>0</v>
+      </c>
+      <c r="T64">
         <v>101</v>
       </c>
     </row>
-    <row r="65" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A65">
         <v>62</v>
       </c>
       <c r="B65" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C65">
         <v>41389</v>
@@ -4411,17 +4601,17 @@
         <v>0</v>
       </c>
       <c r="E65">
+        <v>0</v>
+      </c>
+      <c r="F65">
         <v>41389</v>
       </c>
-      <c r="F65">
-        <v>0</v>
-      </c>
       <c r="G65">
+        <v>0</v>
+      </c>
+      <c r="H65">
         <v>41389</v>
       </c>
-      <c r="H65">
-        <v>0</v>
-      </c>
       <c r="I65">
         <v>0</v>
       </c>
@@ -4432,36 +4622,39 @@
         <v>0</v>
       </c>
       <c r="L65">
+        <v>0</v>
+      </c>
+      <c r="M65">
         <v>13582</v>
       </c>
-      <c r="M65">
+      <c r="N65">
         <v>2</v>
       </c>
-      <c r="N65">
+      <c r="O65">
         <v>2635</v>
       </c>
-      <c r="O65">
+      <c r="P65">
         <v>38754</v>
       </c>
-      <c r="P65">
+      <c r="Q65">
         <v>58527</v>
       </c>
-      <c r="Q65" s="2">
+      <c r="R65">
         <v>13282</v>
       </c>
-      <c r="R65" s="2">
-        <v>0</v>
-      </c>
-      <c r="S65" s="2">
+      <c r="S65">
+        <v>0</v>
+      </c>
+      <c r="T65">
         <v>138</v>
       </c>
     </row>
-    <row r="66" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A66">
         <v>63</v>
       </c>
       <c r="B66" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C66">
         <v>67362</v>
@@ -4470,17 +4663,17 @@
         <v>0</v>
       </c>
       <c r="E66">
+        <v>1</v>
+      </c>
+      <c r="F66">
         <v>67362</v>
       </c>
-      <c r="F66">
-        <v>0</v>
-      </c>
       <c r="G66">
+        <v>0</v>
+      </c>
+      <c r="H66">
         <v>67362</v>
       </c>
-      <c r="H66">
-        <v>0</v>
-      </c>
       <c r="I66">
         <v>0</v>
       </c>
@@ -4491,36 +4684,39 @@
         <v>0</v>
       </c>
       <c r="L66">
+        <v>0</v>
+      </c>
+      <c r="M66">
         <v>13733</v>
       </c>
-      <c r="M66">
+      <c r="N66">
         <v>2</v>
       </c>
-      <c r="N66">
+      <c r="O66">
         <v>4022</v>
       </c>
-      <c r="O66">
+      <c r="P66">
         <v>63341</v>
       </c>
-      <c r="P66">
+      <c r="Q66">
         <v>93810</v>
       </c>
-      <c r="Q66" s="2">
+      <c r="R66">
         <v>17742</v>
       </c>
-      <c r="R66" s="2">
-        <v>0</v>
-      </c>
-      <c r="S66" s="2">
+      <c r="S66">
+        <v>0</v>
+      </c>
+      <c r="T66">
         <v>52</v>
       </c>
     </row>
-    <row r="67" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A67">
         <v>64</v>
       </c>
       <c r="B67" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C67">
         <v>68828</v>
@@ -4529,17 +4725,17 @@
         <v>0</v>
       </c>
       <c r="E67">
+        <v>0</v>
+      </c>
+      <c r="F67">
         <v>68828</v>
       </c>
-      <c r="F67">
-        <v>0</v>
-      </c>
       <c r="G67">
+        <v>0</v>
+      </c>
+      <c r="H67">
         <v>68828</v>
       </c>
-      <c r="H67">
-        <v>0</v>
-      </c>
       <c r="I67">
         <v>0</v>
       </c>
@@ -4550,36 +4746,39 @@
         <v>0</v>
       </c>
       <c r="L67">
+        <v>0</v>
+      </c>
+      <c r="M67">
         <v>19495</v>
       </c>
-      <c r="M67">
+      <c r="N67">
         <v>10</v>
       </c>
-      <c r="N67">
+      <c r="O67">
         <v>3644</v>
       </c>
-      <c r="O67">
+      <c r="P67">
         <v>65185</v>
       </c>
-      <c r="P67">
+      <c r="Q67">
         <v>78032</v>
       </c>
-      <c r="Q67" s="2">
+      <c r="R67">
         <v>9807</v>
       </c>
-      <c r="R67" s="2">
-        <v>0</v>
-      </c>
-      <c r="S67" s="2">
+      <c r="S67">
+        <v>0</v>
+      </c>
+      <c r="T67">
         <v>116</v>
       </c>
     </row>
-    <row r="68" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A68">
         <v>65</v>
       </c>
       <c r="B68" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C68">
         <v>65397</v>
@@ -4588,17 +4787,17 @@
         <v>0</v>
       </c>
       <c r="E68">
+        <v>0</v>
+      </c>
+      <c r="F68">
         <v>65397</v>
       </c>
-      <c r="F68">
-        <v>0</v>
-      </c>
       <c r="G68">
+        <v>0</v>
+      </c>
+      <c r="H68">
         <v>65397</v>
       </c>
-      <c r="H68">
-        <v>0</v>
-      </c>
       <c r="I68">
         <v>0</v>
       </c>
@@ -4609,36 +4808,39 @@
         <v>0</v>
       </c>
       <c r="L68">
+        <v>0</v>
+      </c>
+      <c r="M68">
         <v>18679</v>
       </c>
-      <c r="M68">
+      <c r="N68">
         <v>2</v>
       </c>
-      <c r="N68">
+      <c r="O68">
         <v>1603</v>
       </c>
-      <c r="O68">
+      <c r="P68">
         <v>63796</v>
       </c>
-      <c r="P68">
+      <c r="Q68">
         <v>71325</v>
       </c>
-      <c r="Q68" s="2">
+      <c r="R68">
         <v>7850</v>
       </c>
-      <c r="R68" s="2">
-        <v>0</v>
-      </c>
-      <c r="S68" s="2">
+      <c r="S68">
+        <v>0</v>
+      </c>
+      <c r="T68">
         <v>26</v>
       </c>
     </row>
-    <row r="69" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A69">
         <v>66</v>
       </c>
       <c r="B69" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C69">
         <v>43938</v>
@@ -4647,17 +4849,17 @@
         <v>0</v>
       </c>
       <c r="E69">
+        <v>0</v>
+      </c>
+      <c r="F69">
         <v>43938</v>
       </c>
-      <c r="F69">
-        <v>0</v>
-      </c>
       <c r="G69">
+        <v>0</v>
+      </c>
+      <c r="H69">
         <v>43938</v>
       </c>
-      <c r="H69">
-        <v>0</v>
-      </c>
       <c r="I69">
         <v>0</v>
       </c>
@@ -4668,36 +4870,39 @@
         <v>0</v>
       </c>
       <c r="L69">
+        <v>0</v>
+      </c>
+      <c r="M69">
         <v>18216</v>
       </c>
-      <c r="M69">
+      <c r="N69">
         <v>2</v>
       </c>
-      <c r="N69">
+      <c r="O69">
         <v>2619</v>
       </c>
-      <c r="O69">
+      <c r="P69">
         <v>41322</v>
       </c>
-      <c r="P69">
+      <c r="Q69">
         <v>36118</v>
       </c>
-      <c r="Q69" s="2">
+      <c r="R69">
         <v>6528</v>
       </c>
-      <c r="R69" s="2">
-        <v>0</v>
-      </c>
-      <c r="S69" s="2">
+      <c r="S69">
+        <v>0</v>
+      </c>
+      <c r="T69">
         <v>47</v>
       </c>
     </row>
-    <row r="70" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A70">
         <v>67</v>
       </c>
       <c r="B70" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C70">
         <v>47711</v>
@@ -4706,17 +4911,17 @@
         <v>0</v>
       </c>
       <c r="E70">
+        <v>0</v>
+      </c>
+      <c r="F70">
         <v>47711</v>
       </c>
-      <c r="F70">
-        <v>0</v>
-      </c>
       <c r="G70">
+        <v>0</v>
+      </c>
+      <c r="H70">
         <v>47711</v>
       </c>
-      <c r="H70">
-        <v>0</v>
-      </c>
       <c r="I70">
         <v>0</v>
       </c>
@@ -4727,36 +4932,39 @@
         <v>0</v>
       </c>
       <c r="L70">
+        <v>0</v>
+      </c>
+      <c r="M70">
         <v>18275</v>
       </c>
-      <c r="M70">
+      <c r="N70">
         <v>2</v>
       </c>
-      <c r="N70">
+      <c r="O70">
         <v>3246</v>
       </c>
-      <c r="O70">
+      <c r="P70">
         <v>44466</v>
       </c>
-      <c r="P70">
+      <c r="Q70">
         <v>42051</v>
       </c>
-      <c r="Q70" s="2">
+      <c r="R70">
         <v>5798</v>
       </c>
-      <c r="R70" s="2">
-        <v>0</v>
-      </c>
-      <c r="S70" s="2">
+      <c r="S70">
+        <v>0</v>
+      </c>
+      <c r="T70">
         <v>29</v>
       </c>
     </row>
-    <row r="71" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A71">
         <v>68</v>
       </c>
       <c r="B71" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C71">
         <v>50963</v>
@@ -4765,17 +4973,17 @@
         <v>0</v>
       </c>
       <c r="E71">
+        <v>0</v>
+      </c>
+      <c r="F71">
         <v>50963</v>
       </c>
-      <c r="F71">
-        <v>0</v>
-      </c>
       <c r="G71">
+        <v>0</v>
+      </c>
+      <c r="H71">
         <v>50963</v>
       </c>
-      <c r="H71">
-        <v>0</v>
-      </c>
       <c r="I71">
         <v>0</v>
       </c>
@@ -4786,36 +4994,39 @@
         <v>0</v>
       </c>
       <c r="L71">
+        <v>0</v>
+      </c>
+      <c r="M71">
         <v>22851</v>
       </c>
-      <c r="M71">
+      <c r="N71">
         <v>1</v>
       </c>
-      <c r="N71">
+      <c r="O71">
         <v>4449</v>
       </c>
-      <c r="O71">
+      <c r="P71">
         <v>46514</v>
       </c>
-      <c r="P71">
+      <c r="Q71">
         <v>49140</v>
       </c>
-      <c r="Q71" s="2">
+      <c r="R71">
         <v>6782</v>
       </c>
-      <c r="R71" s="2">
-        <v>0</v>
-      </c>
-      <c r="S71" s="2">
+      <c r="S71">
+        <v>0</v>
+      </c>
+      <c r="T71">
         <v>235</v>
       </c>
     </row>
-    <row r="72" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A72">
         <v>69</v>
       </c>
       <c r="B72" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C72">
         <v>61543</v>
@@ -4824,17 +5035,17 @@
         <v>0</v>
       </c>
       <c r="E72">
+        <v>0</v>
+      </c>
+      <c r="F72">
         <v>61543</v>
       </c>
-      <c r="F72">
-        <v>0</v>
-      </c>
       <c r="G72">
+        <v>0</v>
+      </c>
+      <c r="H72">
         <v>61543</v>
       </c>
-      <c r="H72">
-        <v>0</v>
-      </c>
       <c r="I72">
         <v>0</v>
       </c>
@@ -4845,36 +5056,39 @@
         <v>0</v>
       </c>
       <c r="L72">
+        <v>0</v>
+      </c>
+      <c r="M72">
         <v>17245</v>
       </c>
-      <c r="M72">
+      <c r="N72">
         <v>9</v>
       </c>
-      <c r="N72">
+      <c r="O72">
         <v>3668</v>
       </c>
-      <c r="O72">
+      <c r="P72">
         <v>57877</v>
       </c>
-      <c r="P72">
+      <c r="Q72">
         <v>85504</v>
       </c>
-      <c r="Q72" s="2">
+      <c r="R72">
         <v>12340</v>
       </c>
-      <c r="R72" s="2">
-        <v>0</v>
-      </c>
-      <c r="S72" s="2">
+      <c r="S72">
+        <v>0</v>
+      </c>
+      <c r="T72">
         <v>79</v>
       </c>
     </row>
-    <row r="73" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A73">
         <v>70</v>
       </c>
       <c r="B73" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C73">
         <v>58915</v>
@@ -4883,17 +5097,17 @@
         <v>0</v>
       </c>
       <c r="E73">
+        <v>0</v>
+      </c>
+      <c r="F73">
         <v>58915</v>
       </c>
-      <c r="F73">
-        <v>0</v>
-      </c>
       <c r="G73">
+        <v>0</v>
+      </c>
+      <c r="H73">
         <v>58915</v>
       </c>
-      <c r="H73">
-        <v>0</v>
-      </c>
       <c r="I73">
         <v>0</v>
       </c>
@@ -4904,33 +5118,36 @@
         <v>0</v>
       </c>
       <c r="L73">
+        <v>0</v>
+      </c>
+      <c r="M73">
         <v>15131</v>
       </c>
-      <c r="M73">
+      <c r="N73">
         <v>8</v>
       </c>
-      <c r="N73">
+      <c r="O73">
         <v>3866</v>
       </c>
-      <c r="O73">
+      <c r="P73">
         <v>55049</v>
       </c>
-      <c r="P73">
+      <c r="Q73">
         <v>67666</v>
       </c>
-      <c r="Q73" s="2">
+      <c r="R73">
         <v>10010</v>
       </c>
-      <c r="R73" s="2">
-        <v>0</v>
-      </c>
-      <c r="S73" s="2">
+      <c r="S73">
+        <v>0</v>
+      </c>
+      <c r="T73">
         <v>74</v>
       </c>
     </row>
-    <row r="74" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A74" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B74" s="1"/>
       <c r="C74">
@@ -4940,17 +5157,17 @@
         <v>0</v>
       </c>
       <c r="E74">
+        <v>9</v>
+      </c>
+      <c r="F74">
         <v>2430387</v>
       </c>
-      <c r="F74">
-        <v>0</v>
-      </c>
       <c r="G74">
+        <v>0</v>
+      </c>
+      <c r="H74">
         <v>2430385</v>
       </c>
-      <c r="H74">
-        <v>0</v>
-      </c>
       <c r="I74">
         <v>0</v>
       </c>
@@ -4961,48 +5178,52 @@
         <v>0</v>
       </c>
       <c r="L74">
+        <v>0</v>
+      </c>
+      <c r="M74">
         <v>626066</v>
       </c>
-      <c r="M74">
+      <c r="N74">
         <v>8318</v>
       </c>
-      <c r="N74">
-        <v>97173</v>
-      </c>
       <c r="O74">
-        <v>2333349</v>
+        <v>97186</v>
       </c>
       <c r="P74">
-        <v>4703237</v>
-      </c>
-      <c r="Q74" s="2">
+        <v>2333338</v>
+      </c>
+      <c r="Q74">
+        <v>4703236</v>
+      </c>
+      <c r="R74">
         <v>626236</v>
       </c>
-      <c r="R74" s="2">
+      <c r="S74">
         <v>1</v>
       </c>
-      <c r="S74" s="2">
+      <c r="T74">
         <v>3445</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="12">
+  <mergeCells count="13">
     <mergeCell ref="A74:B74"/>
-    <mergeCell ref="Q2:S2"/>
-    <mergeCell ref="A1:Q1"/>
+    <mergeCell ref="R2:T2"/>
+    <mergeCell ref="A1:R1"/>
     <mergeCell ref="A2:A3"/>
     <mergeCell ref="B2:B3"/>
     <mergeCell ref="C2:C3"/>
     <mergeCell ref="D2:D3"/>
     <mergeCell ref="E2:E3"/>
     <mergeCell ref="F2:F3"/>
-    <mergeCell ref="G2:I2"/>
-    <mergeCell ref="J2:M2"/>
-    <mergeCell ref="N2:P2"/>
+    <mergeCell ref="G2:G3"/>
+    <mergeCell ref="H2:J2"/>
+    <mergeCell ref="K2:N2"/>
+    <mergeCell ref="O2:Q2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="A2:D74 B1:D1 E2:P74 E1:P1" numberStoredAsText="1"/>
+    <ignoredError sqref="A2:Q74 B1:Q1" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/Notice.xlsx
+++ b/Notice.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Downloads\New folder (13)\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B91EC026-5DAA-4ACA-B5F9-0BA19E63B64E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6404515-C3D0-492B-88B8-F1CED2705C87}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="95">
   <si>
     <t>S. No.</t>
   </si>
@@ -32,9 +32,6 @@
   </si>
   <si>
     <t>Pending for Notice Generation</t>
-  </si>
-  <si>
-    <t>Form 7/8 (Shifting)</t>
   </si>
   <si>
     <t>Notice Delivered</t>
@@ -688,12 +685,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:T74"/>
+  <dimension ref="A1:S74"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -711,9 +708,8 @@
       <c r="O1" s="1"/>
       <c r="P1" s="1"/>
       <c r="Q1" s="1"/>
-      <c r="R1" s="1"/>
-    </row>
-    <row r="2" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -735,36 +731,35 @@
       <c r="G2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I2" s="1"/>
-      <c r="J2" s="1"/>
-      <c r="K2" s="1" t="s">
-        <v>8</v>
-      </c>
+      <c r="K2" s="1"/>
       <c r="L2" s="1"/>
       <c r="M2" s="1"/>
-      <c r="N2" s="1"/>
-      <c r="O2" s="1" t="s">
-        <v>9</v>
-      </c>
+      <c r="N2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="O2" s="1"/>
       <c r="P2" s="1"/>
-      <c r="Q2" s="1"/>
-      <c r="R2" s="1" t="s">
-        <v>91</v>
-      </c>
+      <c r="Q2" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="R2" s="1"/>
       <c r="S2" s="1"/>
-      <c r="T2" s="1"/>
-    </row>
-    <row r="3" spans="1:20" ht="63" x14ac:dyDescent="0.25">
+    </row>
+    <row r="3" spans="1:19" ht="63" x14ac:dyDescent="0.25">
       <c r="A3" s="1"/>
       <c r="B3" s="1"/>
       <c r="C3" s="1"/>
       <c r="D3" s="1"/>
       <c r="E3" s="1"/>
       <c r="F3" s="1"/>
-      <c r="G3" s="1"/>
+      <c r="G3" t="s">
+        <v>9</v>
+      </c>
       <c r="H3" t="s">
         <v>10</v>
       </c>
@@ -792,8 +787,8 @@
       <c r="P3" t="s">
         <v>18</v>
       </c>
-      <c r="Q3" t="s">
-        <v>19</v>
+      <c r="Q3" s="2" t="s">
+        <v>91</v>
       </c>
       <c r="R3" s="2" t="s">
         <v>92</v>
@@ -801,16 +796,13 @@
       <c r="S3" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="T3" s="2" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="4" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="4" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>1</v>
       </c>
       <c r="B4" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C4">
         <v>51528</v>
@@ -819,16 +811,16 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>2</v>
+        <v>51528</v>
       </c>
       <c r="F4">
+        <v>0</v>
+      </c>
+      <c r="G4">
         <v>51528</v>
       </c>
-      <c r="G4">
-        <v>0</v>
-      </c>
       <c r="H4">
-        <v>51528</v>
+        <v>0</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -840,39 +832,36 @@
         <v>0</v>
       </c>
       <c r="L4">
-        <v>0</v>
+        <v>17975</v>
       </c>
       <c r="M4">
-        <v>17975</v>
+        <v>967</v>
       </c>
       <c r="N4">
-        <v>967</v>
+        <v>869</v>
       </c>
       <c r="O4">
-        <v>869</v>
+        <v>50659</v>
       </c>
       <c r="P4">
-        <v>50659</v>
+        <v>53812</v>
       </c>
       <c r="Q4">
-        <v>53812</v>
+        <v>12212</v>
       </c>
       <c r="R4">
-        <v>12212</v>
+        <v>0</v>
       </c>
       <c r="S4">
-        <v>0</v>
-      </c>
-      <c r="T4">
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>2</v>
       </c>
       <c r="B5" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C5">
         <v>53911</v>
@@ -881,16 +870,16 @@
         <v>0</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>53911</v>
       </c>
       <c r="F5">
+        <v>0</v>
+      </c>
+      <c r="G5">
         <v>53911</v>
       </c>
-      <c r="G5">
-        <v>0</v>
-      </c>
       <c r="H5">
-        <v>53911</v>
+        <v>0</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -902,39 +891,36 @@
         <v>0</v>
       </c>
       <c r="L5">
-        <v>0</v>
+        <v>11415</v>
       </c>
       <c r="M5">
-        <v>11415</v>
+        <v>757</v>
       </c>
       <c r="N5">
-        <v>757</v>
+        <v>877</v>
       </c>
       <c r="O5">
-        <v>877</v>
+        <v>53035</v>
       </c>
       <c r="P5">
-        <v>53035</v>
+        <v>74848</v>
       </c>
       <c r="Q5">
-        <v>74848</v>
+        <v>16108</v>
       </c>
       <c r="R5">
-        <v>16108</v>
+        <v>0</v>
       </c>
       <c r="S5">
-        <v>0</v>
-      </c>
-      <c r="T5">
         <v>30</v>
       </c>
     </row>
-    <row r="6" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>3</v>
       </c>
       <c r="B6" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C6">
         <v>39773</v>
@@ -943,16 +929,16 @@
         <v>0</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>39773</v>
       </c>
       <c r="F6">
+        <v>0</v>
+      </c>
+      <c r="G6">
         <v>39773</v>
       </c>
-      <c r="G6">
-        <v>0</v>
-      </c>
       <c r="H6">
-        <v>39773</v>
+        <v>0</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -964,39 +950,36 @@
         <v>0</v>
       </c>
       <c r="L6">
-        <v>0</v>
+        <v>6086</v>
       </c>
       <c r="M6">
-        <v>6086</v>
+        <v>201</v>
       </c>
       <c r="N6">
-        <v>201</v>
+        <v>1870</v>
       </c>
       <c r="O6">
-        <v>1870</v>
+        <v>37903</v>
       </c>
       <c r="P6">
-        <v>37903</v>
+        <v>71989</v>
       </c>
       <c r="Q6">
-        <v>71989</v>
+        <v>17830</v>
       </c>
       <c r="R6">
-        <v>17830</v>
+        <v>0</v>
       </c>
       <c r="S6">
-        <v>0</v>
-      </c>
-      <c r="T6">
         <v>54</v>
       </c>
     </row>
-    <row r="7" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>4</v>
       </c>
       <c r="B7" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C7">
         <v>39463</v>
@@ -1005,16 +988,16 @@
         <v>0</v>
       </c>
       <c r="E7">
-        <v>0</v>
+        <v>39463</v>
       </c>
       <c r="F7">
+        <v>0</v>
+      </c>
+      <c r="G7">
         <v>39463</v>
       </c>
-      <c r="G7">
-        <v>0</v>
-      </c>
       <c r="H7">
-        <v>39463</v>
+        <v>0</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -1026,39 +1009,36 @@
         <v>0</v>
       </c>
       <c r="L7">
-        <v>0</v>
+        <v>5733</v>
       </c>
       <c r="M7">
-        <v>5733</v>
+        <v>257</v>
       </c>
       <c r="N7">
-        <v>257</v>
+        <v>1995</v>
       </c>
       <c r="O7">
-        <v>1995</v>
+        <v>37468</v>
       </c>
       <c r="P7">
-        <v>37468</v>
+        <v>77581</v>
       </c>
       <c r="Q7">
-        <v>77581</v>
+        <v>20511</v>
       </c>
       <c r="R7">
-        <v>20511</v>
+        <v>0</v>
       </c>
       <c r="S7">
-        <v>0</v>
-      </c>
-      <c r="T7">
         <v>8</v>
       </c>
     </row>
-    <row r="8" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>5</v>
       </c>
       <c r="B8" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C8">
         <v>40552</v>
@@ -1067,16 +1047,16 @@
         <v>0</v>
       </c>
       <c r="E8">
-        <v>5</v>
+        <v>40552</v>
       </c>
       <c r="F8">
+        <v>0</v>
+      </c>
+      <c r="G8">
         <v>40552</v>
       </c>
-      <c r="G8">
-        <v>0</v>
-      </c>
       <c r="H8">
-        <v>40552</v>
+        <v>0</v>
       </c>
       <c r="I8">
         <v>0</v>
@@ -1088,39 +1068,36 @@
         <v>0</v>
       </c>
       <c r="L8">
-        <v>0</v>
+        <v>14714</v>
       </c>
       <c r="M8">
-        <v>14714</v>
+        <v>164</v>
       </c>
       <c r="N8">
-        <v>164</v>
+        <v>1981</v>
       </c>
       <c r="O8">
-        <v>1981</v>
+        <v>38571</v>
       </c>
       <c r="P8">
-        <v>38571</v>
+        <v>73458</v>
       </c>
       <c r="Q8">
-        <v>73458</v>
+        <v>20788</v>
       </c>
       <c r="R8">
-        <v>20788</v>
+        <v>0</v>
       </c>
       <c r="S8">
-        <v>0</v>
-      </c>
-      <c r="T8">
         <v>110</v>
       </c>
     </row>
-    <row r="9" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>6</v>
       </c>
       <c r="B9" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C9">
         <v>43273</v>
@@ -1129,16 +1106,16 @@
         <v>0</v>
       </c>
       <c r="E9">
-        <v>0</v>
+        <v>43273</v>
       </c>
       <c r="F9">
+        <v>0</v>
+      </c>
+      <c r="G9">
         <v>43273</v>
       </c>
-      <c r="G9">
-        <v>0</v>
-      </c>
       <c r="H9">
-        <v>43273</v>
+        <v>0</v>
       </c>
       <c r="I9">
         <v>0</v>
@@ -1150,39 +1127,36 @@
         <v>0</v>
       </c>
       <c r="L9">
-        <v>0</v>
+        <v>7759</v>
       </c>
       <c r="M9">
-        <v>7759</v>
+        <v>49</v>
       </c>
       <c r="N9">
-        <v>49</v>
+        <v>1350</v>
       </c>
       <c r="O9">
-        <v>1350</v>
+        <v>41924</v>
       </c>
       <c r="P9">
-        <v>41924</v>
+        <v>72913</v>
       </c>
       <c r="Q9">
-        <v>72913</v>
+        <v>18141</v>
       </c>
       <c r="R9">
-        <v>18141</v>
+        <v>0</v>
       </c>
       <c r="S9">
-        <v>0</v>
-      </c>
-      <c r="T9">
         <v>110</v>
       </c>
     </row>
-    <row r="10" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>7</v>
       </c>
       <c r="B10" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C10">
         <v>36576</v>
@@ -1191,16 +1165,16 @@
         <v>0</v>
       </c>
       <c r="E10">
-        <v>0</v>
+        <v>36576</v>
       </c>
       <c r="F10">
+        <v>0</v>
+      </c>
+      <c r="G10">
         <v>36576</v>
       </c>
-      <c r="G10">
-        <v>0</v>
-      </c>
       <c r="H10">
-        <v>36576</v>
+        <v>0</v>
       </c>
       <c r="I10">
         <v>0</v>
@@ -1212,39 +1186,36 @@
         <v>0</v>
       </c>
       <c r="L10">
-        <v>0</v>
+        <v>10960</v>
       </c>
       <c r="M10">
-        <v>10960</v>
+        <v>172</v>
       </c>
       <c r="N10">
-        <v>172</v>
+        <v>815</v>
       </c>
       <c r="O10">
-        <v>815</v>
+        <v>35761</v>
       </c>
       <c r="P10">
-        <v>35761</v>
+        <v>53124</v>
       </c>
       <c r="Q10">
-        <v>53124</v>
+        <v>9498</v>
       </c>
       <c r="R10">
-        <v>9498</v>
+        <v>0</v>
       </c>
       <c r="S10">
-        <v>0</v>
-      </c>
-      <c r="T10">
         <v>2</v>
       </c>
     </row>
-    <row r="11" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>8</v>
       </c>
       <c r="B11" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C11">
         <v>50998</v>
@@ -1253,16 +1224,16 @@
         <v>0</v>
       </c>
       <c r="E11">
-        <v>0</v>
+        <v>50998</v>
       </c>
       <c r="F11">
+        <v>0</v>
+      </c>
+      <c r="G11">
         <v>50998</v>
       </c>
-      <c r="G11">
-        <v>0</v>
-      </c>
       <c r="H11">
-        <v>50998</v>
+        <v>0</v>
       </c>
       <c r="I11">
         <v>0</v>
@@ -1274,39 +1245,36 @@
         <v>0</v>
       </c>
       <c r="L11">
-        <v>0</v>
+        <v>9958</v>
       </c>
       <c r="M11">
-        <v>9958</v>
+        <v>253</v>
       </c>
       <c r="N11">
-        <v>253</v>
+        <v>1703</v>
       </c>
       <c r="O11">
-        <v>1703</v>
+        <v>49300</v>
       </c>
       <c r="P11">
-        <v>49300</v>
+        <v>84438</v>
       </c>
       <c r="Q11">
-        <v>84438</v>
+        <v>23477</v>
       </c>
       <c r="R11">
-        <v>23477</v>
+        <v>0</v>
       </c>
       <c r="S11">
-        <v>0</v>
-      </c>
-      <c r="T11">
         <v>23</v>
       </c>
     </row>
-    <row r="12" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>9</v>
       </c>
       <c r="B12" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C12">
         <v>40739</v>
@@ -1315,16 +1283,16 @@
         <v>0</v>
       </c>
       <c r="E12">
-        <v>0</v>
+        <v>40739</v>
       </c>
       <c r="F12">
+        <v>0</v>
+      </c>
+      <c r="G12">
         <v>40739</v>
       </c>
-      <c r="G12">
-        <v>0</v>
-      </c>
       <c r="H12">
-        <v>40739</v>
+        <v>0</v>
       </c>
       <c r="I12">
         <v>0</v>
@@ -1336,39 +1304,36 @@
         <v>0</v>
       </c>
       <c r="L12">
-        <v>0</v>
+        <v>10054</v>
       </c>
       <c r="M12">
-        <v>10054</v>
+        <v>207</v>
       </c>
       <c r="N12">
-        <v>207</v>
+        <v>1151</v>
       </c>
       <c r="O12">
-        <v>1151</v>
+        <v>39588</v>
       </c>
       <c r="P12">
-        <v>39588</v>
+        <v>66685</v>
       </c>
       <c r="Q12">
-        <v>66685</v>
+        <v>17786</v>
       </c>
       <c r="R12">
-        <v>17786</v>
+        <v>0</v>
       </c>
       <c r="S12">
-        <v>0</v>
-      </c>
-      <c r="T12">
         <v>3</v>
       </c>
     </row>
-    <row r="13" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>10</v>
       </c>
       <c r="B13" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C13">
         <v>37031</v>
@@ -1377,16 +1342,16 @@
         <v>0</v>
       </c>
       <c r="E13">
-        <v>0</v>
+        <v>37031</v>
       </c>
       <c r="F13">
+        <v>0</v>
+      </c>
+      <c r="G13">
         <v>37031</v>
       </c>
-      <c r="G13">
-        <v>0</v>
-      </c>
       <c r="H13">
-        <v>37031</v>
+        <v>0</v>
       </c>
       <c r="I13">
         <v>0</v>
@@ -1398,39 +1363,36 @@
         <v>0</v>
       </c>
       <c r="L13">
-        <v>0</v>
+        <v>7864</v>
       </c>
       <c r="M13">
-        <v>7864</v>
+        <v>258</v>
       </c>
       <c r="N13">
-        <v>258</v>
+        <v>3822</v>
       </c>
       <c r="O13">
-        <v>3822</v>
+        <v>33237</v>
       </c>
       <c r="P13">
-        <v>33237</v>
+        <v>56564</v>
       </c>
       <c r="Q13">
-        <v>56564</v>
+        <v>16237</v>
       </c>
       <c r="R13">
-        <v>16237</v>
+        <v>0</v>
       </c>
       <c r="S13">
-        <v>0</v>
-      </c>
-      <c r="T13">
         <v>106</v>
       </c>
     </row>
-    <row r="14" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>11</v>
       </c>
       <c r="B14" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C14">
         <v>48966</v>
@@ -1439,16 +1401,16 @@
         <v>0</v>
       </c>
       <c r="E14">
-        <v>0</v>
+        <v>48966</v>
       </c>
       <c r="F14">
+        <v>0</v>
+      </c>
+      <c r="G14">
         <v>48966</v>
       </c>
-      <c r="G14">
-        <v>0</v>
-      </c>
       <c r="H14">
-        <v>48966</v>
+        <v>0</v>
       </c>
       <c r="I14">
         <v>0</v>
@@ -1460,39 +1422,36 @@
         <v>0</v>
       </c>
       <c r="L14">
-        <v>0</v>
+        <v>15267</v>
       </c>
       <c r="M14">
-        <v>15267</v>
+        <v>1456</v>
       </c>
       <c r="N14">
-        <v>1456</v>
+        <v>5867</v>
       </c>
       <c r="O14">
-        <v>5867</v>
+        <v>43099</v>
       </c>
       <c r="P14">
-        <v>43099</v>
+        <v>77955</v>
       </c>
       <c r="Q14">
-        <v>77955</v>
+        <v>19716</v>
       </c>
       <c r="R14">
-        <v>19716</v>
+        <v>0</v>
       </c>
       <c r="S14">
-        <v>0</v>
-      </c>
-      <c r="T14">
         <v>174</v>
       </c>
     </row>
-    <row r="15" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>12</v>
       </c>
       <c r="B15" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C15">
         <v>42703</v>
@@ -1501,16 +1460,16 @@
         <v>0</v>
       </c>
       <c r="E15">
-        <v>0</v>
+        <v>42703</v>
       </c>
       <c r="F15">
+        <v>0</v>
+      </c>
+      <c r="G15">
         <v>42703</v>
       </c>
-      <c r="G15">
-        <v>0</v>
-      </c>
       <c r="H15">
-        <v>42703</v>
+        <v>0</v>
       </c>
       <c r="I15">
         <v>0</v>
@@ -1522,39 +1481,36 @@
         <v>0</v>
       </c>
       <c r="L15">
-        <v>0</v>
+        <v>9192</v>
       </c>
       <c r="M15">
-        <v>9192</v>
+        <v>0</v>
       </c>
       <c r="N15">
-        <v>0</v>
+        <v>2821</v>
       </c>
       <c r="O15">
-        <v>2821</v>
+        <v>39882</v>
       </c>
       <c r="P15">
-        <v>39882</v>
+        <v>67183</v>
       </c>
       <c r="Q15">
-        <v>67183</v>
+        <v>4859</v>
       </c>
       <c r="R15">
-        <v>4859</v>
+        <v>0</v>
       </c>
       <c r="S15">
-        <v>0</v>
-      </c>
-      <c r="T15">
         <v>50</v>
       </c>
     </row>
-    <row r="16" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>13</v>
       </c>
       <c r="B16" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C16">
         <v>25549</v>
@@ -1563,16 +1519,16 @@
         <v>0</v>
       </c>
       <c r="E16">
-        <v>0</v>
+        <v>25549</v>
       </c>
       <c r="F16">
-        <v>25549</v>
+        <v>0</v>
       </c>
       <c r="G16">
-        <v>0</v>
+        <v>25547</v>
       </c>
       <c r="H16">
-        <v>25547</v>
+        <v>0</v>
       </c>
       <c r="I16">
         <v>0</v>
@@ -1584,39 +1540,36 @@
         <v>0</v>
       </c>
       <c r="L16">
-        <v>0</v>
+        <v>14861</v>
       </c>
       <c r="M16">
-        <v>14861</v>
+        <v>1</v>
       </c>
       <c r="N16">
-        <v>1</v>
+        <v>261</v>
       </c>
       <c r="O16">
-        <v>261</v>
+        <v>25289</v>
       </c>
       <c r="P16">
-        <v>25289</v>
+        <v>71673</v>
       </c>
       <c r="Q16">
-        <v>71673</v>
+        <v>5197</v>
       </c>
       <c r="R16">
-        <v>5197</v>
+        <v>0</v>
       </c>
       <c r="S16">
-        <v>0</v>
-      </c>
-      <c r="T16">
         <v>47</v>
       </c>
     </row>
-    <row r="17" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>14</v>
       </c>
       <c r="B17" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C17">
         <v>27707</v>
@@ -1625,16 +1578,16 @@
         <v>0</v>
       </c>
       <c r="E17">
-        <v>0</v>
+        <v>27707</v>
       </c>
       <c r="F17">
+        <v>0</v>
+      </c>
+      <c r="G17">
         <v>27707</v>
       </c>
-      <c r="G17">
-        <v>0</v>
-      </c>
       <c r="H17">
-        <v>27707</v>
+        <v>0</v>
       </c>
       <c r="I17">
         <v>0</v>
@@ -1646,39 +1599,36 @@
         <v>0</v>
       </c>
       <c r="L17">
-        <v>0</v>
+        <v>9287</v>
       </c>
       <c r="M17">
-        <v>9287</v>
+        <v>2</v>
       </c>
       <c r="N17">
-        <v>2</v>
+        <v>426</v>
       </c>
       <c r="O17">
-        <v>426</v>
+        <v>27282</v>
       </c>
       <c r="P17">
-        <v>27282</v>
+        <v>65457</v>
       </c>
       <c r="Q17">
-        <v>65457</v>
+        <v>5417</v>
       </c>
       <c r="R17">
-        <v>5417</v>
+        <v>0</v>
       </c>
       <c r="S17">
-        <v>0</v>
-      </c>
-      <c r="T17">
         <v>105</v>
       </c>
     </row>
-    <row r="18" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>15</v>
       </c>
       <c r="B18" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C18">
         <v>47836</v>
@@ -1687,16 +1637,16 @@
         <v>0</v>
       </c>
       <c r="E18">
-        <v>0</v>
+        <v>47836</v>
       </c>
       <c r="F18">
+        <v>0</v>
+      </c>
+      <c r="G18">
         <v>47836</v>
       </c>
-      <c r="G18">
-        <v>0</v>
-      </c>
       <c r="H18">
-        <v>47836</v>
+        <v>0</v>
       </c>
       <c r="I18">
         <v>0</v>
@@ -1708,39 +1658,36 @@
         <v>0</v>
       </c>
       <c r="L18">
-        <v>0</v>
+        <v>7876</v>
       </c>
       <c r="M18">
-        <v>7876</v>
+        <v>3</v>
       </c>
       <c r="N18">
-        <v>3</v>
+        <v>1970</v>
       </c>
       <c r="O18">
-        <v>1970</v>
+        <v>45866</v>
       </c>
       <c r="P18">
-        <v>45866</v>
+        <v>71496</v>
       </c>
       <c r="Q18">
-        <v>71496</v>
+        <v>6819</v>
       </c>
       <c r="R18">
-        <v>6819</v>
+        <v>0</v>
       </c>
       <c r="S18">
-        <v>0</v>
-      </c>
-      <c r="T18">
         <v>32</v>
       </c>
     </row>
-    <row r="19" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>16</v>
       </c>
       <c r="B19" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C19">
         <v>56490</v>
@@ -1749,16 +1696,16 @@
         <v>0</v>
       </c>
       <c r="E19">
-        <v>0</v>
+        <v>56490</v>
       </c>
       <c r="F19">
+        <v>0</v>
+      </c>
+      <c r="G19">
         <v>56490</v>
       </c>
-      <c r="G19">
-        <v>0</v>
-      </c>
       <c r="H19">
-        <v>56490</v>
+        <v>0</v>
       </c>
       <c r="I19">
         <v>0</v>
@@ -1770,39 +1717,36 @@
         <v>0</v>
       </c>
       <c r="L19">
-        <v>0</v>
+        <v>15286</v>
       </c>
       <c r="M19">
-        <v>15286</v>
+        <v>1</v>
       </c>
       <c r="N19">
-        <v>1</v>
+        <v>912</v>
       </c>
       <c r="O19">
-        <v>912</v>
+        <v>55578</v>
       </c>
       <c r="P19">
-        <v>55578</v>
+        <v>106392</v>
       </c>
       <c r="Q19">
-        <v>106392</v>
+        <v>6135</v>
       </c>
       <c r="R19">
-        <v>6135</v>
+        <v>0</v>
       </c>
       <c r="S19">
-        <v>0</v>
-      </c>
-      <c r="T19">
         <v>36</v>
       </c>
     </row>
-    <row r="20" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>17</v>
       </c>
       <c r="B20" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C20">
         <v>35022</v>
@@ -1811,16 +1755,16 @@
         <v>0</v>
       </c>
       <c r="E20">
-        <v>0</v>
+        <v>35022</v>
       </c>
       <c r="F20">
+        <v>0</v>
+      </c>
+      <c r="G20">
         <v>35022</v>
       </c>
-      <c r="G20">
-        <v>0</v>
-      </c>
       <c r="H20">
-        <v>35022</v>
+        <v>0</v>
       </c>
       <c r="I20">
         <v>0</v>
@@ -1832,39 +1776,36 @@
         <v>0</v>
       </c>
       <c r="L20">
-        <v>0</v>
+        <v>6093</v>
       </c>
       <c r="M20">
-        <v>6093</v>
+        <v>5</v>
       </c>
       <c r="N20">
-        <v>5</v>
+        <v>546</v>
       </c>
       <c r="O20">
-        <v>546</v>
+        <v>34477</v>
       </c>
       <c r="P20">
-        <v>34477</v>
+        <v>75814</v>
       </c>
       <c r="Q20">
-        <v>75814</v>
+        <v>8984</v>
       </c>
       <c r="R20">
-        <v>8984</v>
+        <v>0</v>
       </c>
       <c r="S20">
-        <v>0</v>
-      </c>
-      <c r="T20">
         <v>71</v>
       </c>
     </row>
-    <row r="21" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>18</v>
       </c>
       <c r="B21" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C21">
         <v>16962</v>
@@ -1873,16 +1814,16 @@
         <v>0</v>
       </c>
       <c r="E21">
-        <v>0</v>
+        <v>16962</v>
       </c>
       <c r="F21">
+        <v>0</v>
+      </c>
+      <c r="G21">
         <v>16962</v>
       </c>
-      <c r="G21">
-        <v>0</v>
-      </c>
       <c r="H21">
-        <v>16962</v>
+        <v>0</v>
       </c>
       <c r="I21">
         <v>0</v>
@@ -1894,39 +1835,36 @@
         <v>0</v>
       </c>
       <c r="L21">
-        <v>0</v>
+        <v>4030</v>
       </c>
       <c r="M21">
-        <v>4030</v>
+        <v>3</v>
       </c>
       <c r="N21">
-        <v>3</v>
+        <v>171</v>
       </c>
       <c r="O21">
-        <v>171</v>
+        <v>16791</v>
       </c>
       <c r="P21">
-        <v>16791</v>
+        <v>62460</v>
       </c>
       <c r="Q21">
-        <v>62460</v>
+        <v>3868</v>
       </c>
       <c r="R21">
-        <v>3868</v>
+        <v>0</v>
       </c>
       <c r="S21">
         <v>0</v>
       </c>
-      <c r="T21">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="22" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>19</v>
       </c>
       <c r="B22" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C22">
         <v>18668</v>
@@ -1935,16 +1873,16 @@
         <v>0</v>
       </c>
       <c r="E22">
-        <v>0</v>
+        <v>18668</v>
       </c>
       <c r="F22">
+        <v>0</v>
+      </c>
+      <c r="G22">
         <v>18668</v>
       </c>
-      <c r="G22">
-        <v>0</v>
-      </c>
       <c r="H22">
-        <v>18668</v>
+        <v>0</v>
       </c>
       <c r="I22">
         <v>0</v>
@@ -1956,39 +1894,36 @@
         <v>0</v>
       </c>
       <c r="L22">
-        <v>0</v>
+        <v>7665</v>
       </c>
       <c r="M22">
-        <v>7665</v>
+        <v>0</v>
       </c>
       <c r="N22">
-        <v>0</v>
+        <v>302</v>
       </c>
       <c r="O22">
-        <v>302</v>
+        <v>18366</v>
       </c>
       <c r="P22">
-        <v>18366</v>
+        <v>64099</v>
       </c>
       <c r="Q22">
-        <v>64099</v>
+        <v>4848</v>
       </c>
       <c r="R22">
-        <v>4848</v>
+        <v>0</v>
       </c>
       <c r="S22">
         <v>0</v>
       </c>
-      <c r="T22">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="23" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>20</v>
       </c>
       <c r="B23" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C23">
         <v>12020</v>
@@ -1997,16 +1932,16 @@
         <v>0</v>
       </c>
       <c r="E23">
-        <v>0</v>
+        <v>12020</v>
       </c>
       <c r="F23">
+        <v>0</v>
+      </c>
+      <c r="G23">
         <v>12020</v>
       </c>
-      <c r="G23">
-        <v>0</v>
-      </c>
       <c r="H23">
-        <v>12020</v>
+        <v>0</v>
       </c>
       <c r="I23">
         <v>0</v>
@@ -2018,39 +1953,36 @@
         <v>0</v>
       </c>
       <c r="L23">
-        <v>0</v>
+        <v>2113</v>
       </c>
       <c r="M23">
-        <v>2113</v>
+        <v>0</v>
       </c>
       <c r="N23">
-        <v>0</v>
+        <v>108</v>
       </c>
       <c r="O23">
-        <v>108</v>
+        <v>11912</v>
       </c>
       <c r="P23">
-        <v>11912</v>
+        <v>57094</v>
       </c>
       <c r="Q23">
-        <v>57094</v>
+        <v>3541</v>
       </c>
       <c r="R23">
-        <v>3541</v>
+        <v>0</v>
       </c>
       <c r="S23">
-        <v>0</v>
-      </c>
-      <c r="T23">
         <v>28</v>
       </c>
     </row>
-    <row r="24" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>21</v>
       </c>
       <c r="B24" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C24">
         <v>14056</v>
@@ -2059,16 +1991,16 @@
         <v>0</v>
       </c>
       <c r="E24">
-        <v>0</v>
+        <v>14056</v>
       </c>
       <c r="F24">
+        <v>0</v>
+      </c>
+      <c r="G24">
         <v>14056</v>
       </c>
-      <c r="G24">
-        <v>0</v>
-      </c>
       <c r="H24">
-        <v>14056</v>
+        <v>0</v>
       </c>
       <c r="I24">
         <v>0</v>
@@ -2080,39 +2012,36 @@
         <v>0</v>
       </c>
       <c r="L24">
-        <v>0</v>
+        <v>3482</v>
       </c>
       <c r="M24">
-        <v>3482</v>
+        <v>5</v>
       </c>
       <c r="N24">
-        <v>5</v>
+        <v>231</v>
       </c>
       <c r="O24">
-        <v>231</v>
+        <v>13825</v>
       </c>
       <c r="P24">
-        <v>13825</v>
+        <v>65629</v>
       </c>
       <c r="Q24">
-        <v>65629</v>
+        <v>3492</v>
       </c>
       <c r="R24">
-        <v>3492</v>
+        <v>0</v>
       </c>
       <c r="S24">
         <v>0</v>
       </c>
-      <c r="T24">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="25" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>22</v>
       </c>
       <c r="B25" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C25">
         <v>19266</v>
@@ -2121,16 +2050,16 @@
         <v>0</v>
       </c>
       <c r="E25">
-        <v>0</v>
+        <v>19266</v>
       </c>
       <c r="F25">
+        <v>0</v>
+      </c>
+      <c r="G25">
         <v>19266</v>
       </c>
-      <c r="G25">
-        <v>0</v>
-      </c>
       <c r="H25">
-        <v>19266</v>
+        <v>0</v>
       </c>
       <c r="I25">
         <v>0</v>
@@ -2142,39 +2071,36 @@
         <v>0</v>
       </c>
       <c r="L25">
-        <v>0</v>
+        <v>4862</v>
       </c>
       <c r="M25">
-        <v>4862</v>
+        <v>0</v>
       </c>
       <c r="N25">
-        <v>0</v>
+        <v>298</v>
       </c>
       <c r="O25">
-        <v>298</v>
+        <v>18968</v>
       </c>
       <c r="P25">
-        <v>18968</v>
+        <v>57533</v>
       </c>
       <c r="Q25">
-        <v>57533</v>
+        <v>3231</v>
       </c>
       <c r="R25">
-        <v>3231</v>
+        <v>0</v>
       </c>
       <c r="S25">
-        <v>0</v>
-      </c>
-      <c r="T25">
         <v>13</v>
       </c>
     </row>
-    <row r="26" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>23</v>
       </c>
       <c r="B26" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C26">
         <v>17557</v>
@@ -2183,16 +2109,16 @@
         <v>0</v>
       </c>
       <c r="E26">
-        <v>0</v>
+        <v>17557</v>
       </c>
       <c r="F26">
+        <v>0</v>
+      </c>
+      <c r="G26">
         <v>17557</v>
       </c>
-      <c r="G26">
-        <v>0</v>
-      </c>
       <c r="H26">
-        <v>17557</v>
+        <v>0</v>
       </c>
       <c r="I26">
         <v>0</v>
@@ -2204,39 +2130,36 @@
         <v>0</v>
       </c>
       <c r="L26">
-        <v>0</v>
+        <v>3741</v>
       </c>
       <c r="M26">
-        <v>3741</v>
+        <v>3</v>
       </c>
       <c r="N26">
-        <v>3</v>
+        <v>194</v>
       </c>
       <c r="O26">
-        <v>194</v>
+        <v>17363</v>
       </c>
       <c r="P26">
-        <v>17363</v>
+        <v>66594</v>
       </c>
       <c r="Q26">
-        <v>66594</v>
+        <v>3333</v>
       </c>
       <c r="R26">
-        <v>3333</v>
+        <v>0</v>
       </c>
       <c r="S26">
-        <v>0</v>
-      </c>
-      <c r="T26">
         <v>2</v>
       </c>
     </row>
-    <row r="27" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>24</v>
       </c>
       <c r="B27" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C27">
         <v>44276</v>
@@ -2245,16 +2168,16 @@
         <v>0</v>
       </c>
       <c r="E27">
-        <v>0</v>
+        <v>44276</v>
       </c>
       <c r="F27">
+        <v>0</v>
+      </c>
+      <c r="G27">
         <v>44276</v>
       </c>
-      <c r="G27">
-        <v>0</v>
-      </c>
       <c r="H27">
-        <v>44276</v>
+        <v>0</v>
       </c>
       <c r="I27">
         <v>0</v>
@@ -2266,39 +2189,36 @@
         <v>0</v>
       </c>
       <c r="L27">
-        <v>0</v>
+        <v>9679</v>
       </c>
       <c r="M27">
-        <v>9679</v>
+        <v>215</v>
       </c>
       <c r="N27">
-        <v>215</v>
+        <v>3287</v>
       </c>
       <c r="O27">
-        <v>3287</v>
+        <v>41005</v>
       </c>
       <c r="P27">
-        <v>41005</v>
+        <v>73109</v>
       </c>
       <c r="Q27">
-        <v>73109</v>
+        <v>12669</v>
       </c>
       <c r="R27">
-        <v>12669</v>
+        <v>0</v>
       </c>
       <c r="S27">
         <v>0</v>
       </c>
-      <c r="T27">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="28" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>25</v>
       </c>
       <c r="B28" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C28">
         <v>54349</v>
@@ -2307,16 +2227,16 @@
         <v>0</v>
       </c>
       <c r="E28">
-        <v>0</v>
+        <v>54349</v>
       </c>
       <c r="F28">
+        <v>0</v>
+      </c>
+      <c r="G28">
         <v>54349</v>
       </c>
-      <c r="G28">
-        <v>0</v>
-      </c>
       <c r="H28">
-        <v>54349</v>
+        <v>0</v>
       </c>
       <c r="I28">
         <v>0</v>
@@ -2328,39 +2248,36 @@
         <v>0</v>
       </c>
       <c r="L28">
-        <v>0</v>
+        <v>8879</v>
       </c>
       <c r="M28">
-        <v>8879</v>
+        <v>856</v>
       </c>
       <c r="N28">
-        <v>856</v>
+        <v>3525</v>
       </c>
       <c r="O28">
-        <v>3525</v>
+        <v>50844</v>
       </c>
       <c r="P28">
-        <v>50844</v>
+        <v>80620</v>
       </c>
       <c r="Q28">
-        <v>80620</v>
+        <v>13995</v>
       </c>
       <c r="R28">
-        <v>13995</v>
+        <v>0</v>
       </c>
       <c r="S28">
-        <v>0</v>
-      </c>
-      <c r="T28">
         <v>127</v>
       </c>
     </row>
-    <row r="29" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>26</v>
       </c>
       <c r="B29" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C29">
         <v>47111</v>
@@ -2369,16 +2286,16 @@
         <v>0</v>
       </c>
       <c r="E29">
-        <v>0</v>
+        <v>47111</v>
       </c>
       <c r="F29">
+        <v>0</v>
+      </c>
+      <c r="G29">
         <v>47111</v>
       </c>
-      <c r="G29">
-        <v>0</v>
-      </c>
       <c r="H29">
-        <v>47111</v>
+        <v>0</v>
       </c>
       <c r="I29">
         <v>0</v>
@@ -2390,39 +2307,36 @@
         <v>0</v>
       </c>
       <c r="L29">
-        <v>0</v>
+        <v>8816</v>
       </c>
       <c r="M29">
-        <v>8816</v>
+        <v>318</v>
       </c>
       <c r="N29">
-        <v>318</v>
+        <v>4592</v>
       </c>
       <c r="O29">
-        <v>4592</v>
+        <v>42520</v>
       </c>
       <c r="P29">
-        <v>42520</v>
+        <v>83836</v>
       </c>
       <c r="Q29">
-        <v>83836</v>
+        <v>14229</v>
       </c>
       <c r="R29">
-        <v>14229</v>
+        <v>0</v>
       </c>
       <c r="S29">
-        <v>0</v>
-      </c>
-      <c r="T29">
         <v>22</v>
       </c>
     </row>
-    <row r="30" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>27</v>
       </c>
       <c r="B30" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C30">
         <v>52653</v>
@@ -2431,16 +2345,16 @@
         <v>0</v>
       </c>
       <c r="E30">
-        <v>0</v>
+        <v>52653</v>
       </c>
       <c r="F30">
+        <v>0</v>
+      </c>
+      <c r="G30">
         <v>52653</v>
       </c>
-      <c r="G30">
-        <v>0</v>
-      </c>
       <c r="H30">
-        <v>52653</v>
+        <v>0</v>
       </c>
       <c r="I30">
         <v>0</v>
@@ -2452,39 +2366,36 @@
         <v>0</v>
       </c>
       <c r="L30">
-        <v>0</v>
+        <v>11659</v>
       </c>
       <c r="M30">
-        <v>11659</v>
+        <v>411</v>
       </c>
       <c r="N30">
-        <v>411</v>
+        <v>5383</v>
       </c>
       <c r="O30">
-        <v>5383</v>
+        <v>47272</v>
       </c>
       <c r="P30">
-        <v>47272</v>
+        <v>86933</v>
       </c>
       <c r="Q30">
-        <v>86933</v>
+        <v>12564</v>
       </c>
       <c r="R30">
-        <v>12564</v>
+        <v>0</v>
       </c>
       <c r="S30">
-        <v>0</v>
-      </c>
-      <c r="T30">
         <v>8</v>
       </c>
     </row>
-    <row r="31" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>28</v>
       </c>
       <c r="B31" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C31">
         <v>91162</v>
@@ -2493,16 +2404,16 @@
         <v>0</v>
       </c>
       <c r="E31">
-        <v>0</v>
+        <v>91162</v>
       </c>
       <c r="F31">
+        <v>0</v>
+      </c>
+      <c r="G31">
         <v>91162</v>
       </c>
-      <c r="G31">
-        <v>0</v>
-      </c>
       <c r="H31">
-        <v>91162</v>
+        <v>0</v>
       </c>
       <c r="I31">
         <v>0</v>
@@ -2514,39 +2425,36 @@
         <v>0</v>
       </c>
       <c r="L31">
-        <v>0</v>
+        <v>46718</v>
       </c>
       <c r="M31">
-        <v>46718</v>
+        <v>42</v>
       </c>
       <c r="N31">
-        <v>42</v>
+        <v>1899</v>
       </c>
       <c r="O31">
-        <v>1899</v>
+        <v>89264</v>
       </c>
       <c r="P31">
-        <v>89264</v>
+        <v>81642</v>
       </c>
       <c r="Q31">
-        <v>81642</v>
+        <v>14581</v>
       </c>
       <c r="R31">
-        <v>14581</v>
+        <v>0</v>
       </c>
       <c r="S31">
-        <v>0</v>
-      </c>
-      <c r="T31">
         <v>39</v>
       </c>
     </row>
-    <row r="32" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>29</v>
       </c>
       <c r="B32" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C32">
         <v>46728</v>
@@ -2555,16 +2463,16 @@
         <v>0</v>
       </c>
       <c r="E32">
-        <v>0</v>
+        <v>46728</v>
       </c>
       <c r="F32">
+        <v>0</v>
+      </c>
+      <c r="G32">
         <v>46728</v>
       </c>
-      <c r="G32">
-        <v>0</v>
-      </c>
       <c r="H32">
-        <v>46728</v>
+        <v>0</v>
       </c>
       <c r="I32">
         <v>0</v>
@@ -2576,39 +2484,36 @@
         <v>0</v>
       </c>
       <c r="L32">
-        <v>0</v>
+        <v>10557</v>
       </c>
       <c r="M32">
-        <v>10557</v>
+        <v>316</v>
       </c>
       <c r="N32">
-        <v>316</v>
+        <v>4391</v>
       </c>
       <c r="O32">
-        <v>4391</v>
+        <v>42344</v>
       </c>
       <c r="P32">
-        <v>42344</v>
+        <v>74810</v>
       </c>
       <c r="Q32">
-        <v>74810</v>
+        <v>11379</v>
       </c>
       <c r="R32">
-        <v>11379</v>
+        <v>0</v>
       </c>
       <c r="S32">
         <v>0</v>
       </c>
-      <c r="T32">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="33" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>30</v>
       </c>
       <c r="B33" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C33">
         <v>40230</v>
@@ -2617,16 +2522,16 @@
         <v>0</v>
       </c>
       <c r="E33">
-        <v>0</v>
+        <v>40230</v>
       </c>
       <c r="F33">
+        <v>0</v>
+      </c>
+      <c r="G33">
         <v>40230</v>
       </c>
-      <c r="G33">
-        <v>0</v>
-      </c>
       <c r="H33">
-        <v>40230</v>
+        <v>0</v>
       </c>
       <c r="I33">
         <v>0</v>
@@ -2638,39 +2543,36 @@
         <v>0</v>
       </c>
       <c r="L33">
-        <v>0</v>
+        <v>5113</v>
       </c>
       <c r="M33">
-        <v>5113</v>
+        <v>311</v>
       </c>
       <c r="N33">
-        <v>311</v>
+        <v>1275</v>
       </c>
       <c r="O33">
-        <v>1275</v>
+        <v>38955</v>
       </c>
       <c r="P33">
-        <v>38955</v>
+        <v>76969</v>
       </c>
       <c r="Q33">
-        <v>76969</v>
+        <v>6678</v>
       </c>
       <c r="R33">
-        <v>6678</v>
+        <v>0</v>
       </c>
       <c r="S33">
-        <v>0</v>
-      </c>
-      <c r="T33">
         <v>19</v>
       </c>
     </row>
-    <row r="34" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>31</v>
       </c>
       <c r="B34" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C34">
         <v>36542</v>
@@ -2679,16 +2581,16 @@
         <v>0</v>
       </c>
       <c r="E34">
-        <v>0</v>
+        <v>36542</v>
       </c>
       <c r="F34">
+        <v>0</v>
+      </c>
+      <c r="G34">
         <v>36542</v>
       </c>
-      <c r="G34">
-        <v>0</v>
-      </c>
       <c r="H34">
-        <v>36542</v>
+        <v>0</v>
       </c>
       <c r="I34">
         <v>0</v>
@@ -2700,39 +2602,36 @@
         <v>0</v>
       </c>
       <c r="L34">
-        <v>0</v>
+        <v>12439</v>
       </c>
       <c r="M34">
-        <v>12439</v>
+        <v>513</v>
       </c>
       <c r="N34">
-        <v>513</v>
+        <v>1363</v>
       </c>
       <c r="O34">
-        <v>1363</v>
+        <v>35181</v>
       </c>
       <c r="P34">
-        <v>35181</v>
+        <v>74624</v>
       </c>
       <c r="Q34">
-        <v>74624</v>
+        <v>7137</v>
       </c>
       <c r="R34">
-        <v>7137</v>
+        <v>0</v>
       </c>
       <c r="S34">
         <v>0</v>
       </c>
-      <c r="T34">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="35" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>32</v>
       </c>
       <c r="B35" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C35">
         <v>33564</v>
@@ -2741,16 +2640,16 @@
         <v>0</v>
       </c>
       <c r="E35">
-        <v>0</v>
+        <v>33564</v>
       </c>
       <c r="F35">
+        <v>0</v>
+      </c>
+      <c r="G35">
         <v>33564</v>
       </c>
-      <c r="G35">
-        <v>0</v>
-      </c>
       <c r="H35">
-        <v>33564</v>
+        <v>0</v>
       </c>
       <c r="I35">
         <v>0</v>
@@ -2762,39 +2661,36 @@
         <v>0</v>
       </c>
       <c r="L35">
-        <v>0</v>
+        <v>7886</v>
       </c>
       <c r="M35">
-        <v>7886</v>
+        <v>271</v>
       </c>
       <c r="N35">
-        <v>271</v>
+        <v>1141</v>
       </c>
       <c r="O35">
-        <v>1141</v>
+        <v>32426</v>
       </c>
       <c r="P35">
-        <v>32426</v>
+        <v>76462</v>
       </c>
       <c r="Q35">
-        <v>76462</v>
+        <v>8879</v>
       </c>
       <c r="R35">
-        <v>8879</v>
+        <v>0</v>
       </c>
       <c r="S35">
-        <v>0</v>
-      </c>
-      <c r="T35">
         <v>35</v>
       </c>
     </row>
-    <row r="36" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>33</v>
       </c>
       <c r="B36" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C36">
         <v>20905</v>
@@ -2803,16 +2699,16 @@
         <v>0</v>
       </c>
       <c r="E36">
-        <v>0</v>
+        <v>20905</v>
       </c>
       <c r="F36">
+        <v>0</v>
+      </c>
+      <c r="G36">
         <v>20905</v>
       </c>
-      <c r="G36">
-        <v>0</v>
-      </c>
       <c r="H36">
-        <v>20905</v>
+        <v>0</v>
       </c>
       <c r="I36">
         <v>0</v>
@@ -2824,39 +2720,36 @@
         <v>0</v>
       </c>
       <c r="L36">
-        <v>0</v>
+        <v>7350</v>
       </c>
       <c r="M36">
-        <v>7350</v>
+        <v>0</v>
       </c>
       <c r="N36">
-        <v>0</v>
+        <v>951</v>
       </c>
       <c r="O36">
-        <v>951</v>
+        <v>19954</v>
       </c>
       <c r="P36">
-        <v>19954</v>
+        <v>60419</v>
       </c>
       <c r="Q36">
-        <v>60419</v>
+        <v>3855</v>
       </c>
       <c r="R36">
-        <v>3855</v>
+        <v>0</v>
       </c>
       <c r="S36">
-        <v>0</v>
-      </c>
-      <c r="T36">
         <v>2</v>
       </c>
     </row>
-    <row r="37" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>34</v>
       </c>
       <c r="B37" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C37">
         <v>17692</v>
@@ -2865,16 +2758,16 @@
         <v>0</v>
       </c>
       <c r="E37">
-        <v>0</v>
+        <v>17692</v>
       </c>
       <c r="F37">
+        <v>0</v>
+      </c>
+      <c r="G37">
         <v>17692</v>
       </c>
-      <c r="G37">
-        <v>0</v>
-      </c>
       <c r="H37">
-        <v>17692</v>
+        <v>0</v>
       </c>
       <c r="I37">
         <v>0</v>
@@ -2886,39 +2779,36 @@
         <v>0</v>
       </c>
       <c r="L37">
-        <v>0</v>
+        <v>2311</v>
       </c>
       <c r="M37">
-        <v>2311</v>
+        <v>0</v>
       </c>
       <c r="N37">
-        <v>0</v>
+        <v>541</v>
       </c>
       <c r="O37">
-        <v>541</v>
+        <v>17151</v>
       </c>
       <c r="P37">
-        <v>17151</v>
+        <v>57832</v>
       </c>
       <c r="Q37">
-        <v>57832</v>
+        <v>4036</v>
       </c>
       <c r="R37">
-        <v>4036</v>
+        <v>0</v>
       </c>
       <c r="S37">
-        <v>0</v>
-      </c>
-      <c r="T37">
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>35</v>
       </c>
       <c r="B38" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C38">
         <v>29110</v>
@@ -2927,16 +2817,16 @@
         <v>0</v>
       </c>
       <c r="E38">
-        <v>1</v>
+        <v>29110</v>
       </c>
       <c r="F38">
+        <v>0</v>
+      </c>
+      <c r="G38">
         <v>29110</v>
       </c>
-      <c r="G38">
-        <v>0</v>
-      </c>
       <c r="H38">
-        <v>29110</v>
+        <v>0</v>
       </c>
       <c r="I38">
         <v>0</v>
@@ -2948,39 +2838,36 @@
         <v>0</v>
       </c>
       <c r="L38">
-        <v>0</v>
+        <v>5386</v>
       </c>
       <c r="M38">
-        <v>5386</v>
+        <v>2</v>
       </c>
       <c r="N38">
-        <v>2</v>
+        <v>635</v>
       </c>
       <c r="O38">
-        <v>635</v>
+        <v>28475</v>
       </c>
       <c r="P38">
-        <v>28475</v>
+        <v>63038</v>
       </c>
       <c r="Q38">
-        <v>63038</v>
+        <v>5135</v>
       </c>
       <c r="R38">
-        <v>5135</v>
+        <v>0</v>
       </c>
       <c r="S38">
         <v>0</v>
       </c>
-      <c r="T38">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="39" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="39" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>36</v>
       </c>
       <c r="B39" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C39">
         <v>21367</v>
@@ -2989,16 +2876,16 @@
         <v>0</v>
       </c>
       <c r="E39">
-        <v>0</v>
+        <v>21367</v>
       </c>
       <c r="F39">
+        <v>0</v>
+      </c>
+      <c r="G39">
         <v>21367</v>
       </c>
-      <c r="G39">
-        <v>0</v>
-      </c>
       <c r="H39">
-        <v>21367</v>
+        <v>0</v>
       </c>
       <c r="I39">
         <v>0</v>
@@ -3010,39 +2897,36 @@
         <v>0</v>
       </c>
       <c r="L39">
-        <v>0</v>
+        <v>4529</v>
       </c>
       <c r="M39">
-        <v>4529</v>
+        <v>1</v>
       </c>
       <c r="N39">
-        <v>1</v>
+        <v>234</v>
       </c>
       <c r="O39">
-        <v>234</v>
+        <v>21133</v>
       </c>
       <c r="P39">
-        <v>21133</v>
+        <v>71133</v>
       </c>
       <c r="Q39">
-        <v>71133</v>
+        <v>5903</v>
       </c>
       <c r="R39">
-        <v>5903</v>
+        <v>0</v>
       </c>
       <c r="S39">
-        <v>0</v>
-      </c>
-      <c r="T39">
         <v>26</v>
       </c>
     </row>
-    <row r="40" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>37</v>
       </c>
       <c r="B40" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C40">
         <v>18905</v>
@@ -3051,16 +2935,16 @@
         <v>0</v>
       </c>
       <c r="E40">
-        <v>0</v>
+        <v>18905</v>
       </c>
       <c r="F40">
+        <v>0</v>
+      </c>
+      <c r="G40">
         <v>18905</v>
       </c>
-      <c r="G40">
-        <v>0</v>
-      </c>
       <c r="H40">
-        <v>18905</v>
+        <v>0</v>
       </c>
       <c r="I40">
         <v>0</v>
@@ -3072,39 +2956,36 @@
         <v>0</v>
       </c>
       <c r="L40">
-        <v>0</v>
+        <v>1812</v>
       </c>
       <c r="M40">
-        <v>1812</v>
+        <v>0</v>
       </c>
       <c r="N40">
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="O40">
-        <v>52</v>
+        <v>18853</v>
       </c>
       <c r="P40">
-        <v>18853</v>
+        <v>73242</v>
       </c>
       <c r="Q40">
-        <v>73242</v>
+        <v>3824</v>
       </c>
       <c r="R40">
-        <v>3824</v>
+        <v>0</v>
       </c>
       <c r="S40">
-        <v>0</v>
-      </c>
-      <c r="T40">
         <v>61</v>
       </c>
     </row>
-    <row r="41" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>38</v>
       </c>
       <c r="B41" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C41">
         <v>23521</v>
@@ -3113,16 +2994,16 @@
         <v>0</v>
       </c>
       <c r="E41">
-        <v>0</v>
+        <v>23521</v>
       </c>
       <c r="F41">
+        <v>0</v>
+      </c>
+      <c r="G41">
         <v>23521</v>
       </c>
-      <c r="G41">
-        <v>0</v>
-      </c>
       <c r="H41">
-        <v>23521</v>
+        <v>0</v>
       </c>
       <c r="I41">
         <v>0</v>
@@ -3134,39 +3015,36 @@
         <v>0</v>
       </c>
       <c r="L41">
-        <v>0</v>
+        <v>1499</v>
       </c>
       <c r="M41">
-        <v>1499</v>
+        <v>0</v>
       </c>
       <c r="N41">
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="O41">
-        <v>92</v>
+        <v>23429</v>
       </c>
       <c r="P41">
-        <v>23429</v>
+        <v>85251</v>
       </c>
       <c r="Q41">
-        <v>85251</v>
+        <v>6015</v>
       </c>
       <c r="R41">
-        <v>6015</v>
+        <v>0</v>
       </c>
       <c r="S41">
-        <v>0</v>
-      </c>
-      <c r="T41">
         <v>27</v>
       </c>
     </row>
-    <row r="42" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>39</v>
       </c>
       <c r="B42" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C42">
         <v>27565</v>
@@ -3175,16 +3053,16 @@
         <v>0</v>
       </c>
       <c r="E42">
-        <v>0</v>
+        <v>27565</v>
       </c>
       <c r="F42">
+        <v>0</v>
+      </c>
+      <c r="G42">
         <v>27565</v>
       </c>
-      <c r="G42">
-        <v>0</v>
-      </c>
       <c r="H42">
-        <v>27565</v>
+        <v>0</v>
       </c>
       <c r="I42">
         <v>0</v>
@@ -3196,39 +3074,36 @@
         <v>0</v>
       </c>
       <c r="L42">
-        <v>0</v>
+        <v>6264</v>
       </c>
       <c r="M42">
-        <v>6264</v>
+        <v>0</v>
       </c>
       <c r="N42">
-        <v>0</v>
+        <v>419</v>
       </c>
       <c r="O42">
-        <v>419</v>
+        <v>27147</v>
       </c>
       <c r="P42">
-        <v>27147</v>
+        <v>68615</v>
       </c>
       <c r="Q42">
-        <v>68615</v>
+        <v>4708</v>
       </c>
       <c r="R42">
-        <v>4708</v>
+        <v>0</v>
       </c>
       <c r="S42">
-        <v>0</v>
-      </c>
-      <c r="T42">
         <v>8</v>
       </c>
     </row>
-    <row r="43" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>40</v>
       </c>
       <c r="B43" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C43">
         <v>29700</v>
@@ -3237,16 +3112,16 @@
         <v>0</v>
       </c>
       <c r="E43">
-        <v>0</v>
+        <v>29700</v>
       </c>
       <c r="F43">
+        <v>0</v>
+      </c>
+      <c r="G43">
         <v>29700</v>
       </c>
-      <c r="G43">
-        <v>0</v>
-      </c>
       <c r="H43">
-        <v>29700</v>
+        <v>0</v>
       </c>
       <c r="I43">
         <v>0</v>
@@ -3258,39 +3133,36 @@
         <v>0</v>
       </c>
       <c r="L43">
-        <v>0</v>
+        <v>6804</v>
       </c>
       <c r="M43">
-        <v>6804</v>
+        <v>1</v>
       </c>
       <c r="N43">
-        <v>1</v>
+        <v>957</v>
       </c>
       <c r="O43">
-        <v>957</v>
+        <v>28774</v>
       </c>
       <c r="P43">
-        <v>28774</v>
+        <v>63012</v>
       </c>
       <c r="Q43">
-        <v>63012</v>
+        <v>5219</v>
       </c>
       <c r="R43">
-        <v>5219</v>
+        <v>0</v>
       </c>
       <c r="S43">
-        <v>0</v>
-      </c>
-      <c r="T43">
         <v>121</v>
       </c>
     </row>
-    <row r="44" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A44">
         <v>41</v>
       </c>
       <c r="B44" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C44">
         <v>21900</v>
@@ -3299,16 +3171,16 @@
         <v>0</v>
       </c>
       <c r="E44">
-        <v>0</v>
+        <v>21900</v>
       </c>
       <c r="F44">
+        <v>0</v>
+      </c>
+      <c r="G44">
         <v>21900</v>
       </c>
-      <c r="G44">
-        <v>0</v>
-      </c>
       <c r="H44">
-        <v>21900</v>
+        <v>0</v>
       </c>
       <c r="I44">
         <v>0</v>
@@ -3320,39 +3192,36 @@
         <v>0</v>
       </c>
       <c r="L44">
-        <v>0</v>
+        <v>6643</v>
       </c>
       <c r="M44">
-        <v>6643</v>
+        <v>24</v>
       </c>
       <c r="N44">
-        <v>24</v>
+        <v>347</v>
       </c>
       <c r="O44">
-        <v>347</v>
+        <v>21553</v>
       </c>
       <c r="P44">
-        <v>21553</v>
+        <v>68393</v>
       </c>
       <c r="Q44">
-        <v>68393</v>
+        <v>7659</v>
       </c>
       <c r="R44">
-        <v>7659</v>
+        <v>0</v>
       </c>
       <c r="S44">
-        <v>0</v>
-      </c>
-      <c r="T44">
         <v>20</v>
       </c>
     </row>
-    <row r="45" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A45">
         <v>42</v>
       </c>
       <c r="B45" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C45">
         <v>19935</v>
@@ -3361,16 +3230,16 @@
         <v>0</v>
       </c>
       <c r="E45">
-        <v>0</v>
+        <v>19935</v>
       </c>
       <c r="F45">
+        <v>0</v>
+      </c>
+      <c r="G45">
         <v>19935</v>
       </c>
-      <c r="G45">
-        <v>0</v>
-      </c>
       <c r="H45">
-        <v>19935</v>
+        <v>0</v>
       </c>
       <c r="I45">
         <v>0</v>
@@ -3382,39 +3251,36 @@
         <v>0</v>
       </c>
       <c r="L45">
-        <v>0</v>
+        <v>2254</v>
       </c>
       <c r="M45">
-        <v>2254</v>
+        <v>13</v>
       </c>
       <c r="N45">
-        <v>13</v>
+        <v>149</v>
       </c>
       <c r="O45">
-        <v>149</v>
+        <v>19786</v>
       </c>
       <c r="P45">
-        <v>19786</v>
+        <v>76287</v>
       </c>
       <c r="Q45">
-        <v>76287</v>
+        <v>6998</v>
       </c>
       <c r="R45">
-        <v>6998</v>
+        <v>0</v>
       </c>
       <c r="S45">
-        <v>0</v>
-      </c>
-      <c r="T45">
         <v>129</v>
       </c>
     </row>
-    <row r="46" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A46">
         <v>43</v>
       </c>
       <c r="B46" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C46">
         <v>21512</v>
@@ -3423,16 +3289,16 @@
         <v>0</v>
       </c>
       <c r="E46">
-        <v>0</v>
+        <v>21512</v>
       </c>
       <c r="F46">
+        <v>0</v>
+      </c>
+      <c r="G46">
         <v>21512</v>
       </c>
-      <c r="G46">
-        <v>0</v>
-      </c>
       <c r="H46">
-        <v>21512</v>
+        <v>0</v>
       </c>
       <c r="I46">
         <v>0</v>
@@ -3444,39 +3310,36 @@
         <v>0</v>
       </c>
       <c r="L46">
-        <v>0</v>
+        <v>8303</v>
       </c>
       <c r="M46">
-        <v>8303</v>
+        <v>32</v>
       </c>
       <c r="N46">
-        <v>32</v>
+        <v>276</v>
       </c>
       <c r="O46">
-        <v>276</v>
+        <v>21236</v>
       </c>
       <c r="P46">
-        <v>21236</v>
+        <v>64160</v>
       </c>
       <c r="Q46">
-        <v>64160</v>
+        <v>7548</v>
       </c>
       <c r="R46">
-        <v>7548</v>
+        <v>0</v>
       </c>
       <c r="S46">
-        <v>0</v>
-      </c>
-      <c r="T46">
         <v>152</v>
       </c>
     </row>
-    <row r="47" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A47">
         <v>44</v>
       </c>
       <c r="B47" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C47">
         <v>22426</v>
@@ -3485,16 +3348,16 @@
         <v>0</v>
       </c>
       <c r="E47">
-        <v>0</v>
+        <v>22426</v>
       </c>
       <c r="F47">
+        <v>0</v>
+      </c>
+      <c r="G47">
         <v>22426</v>
       </c>
-      <c r="G47">
-        <v>0</v>
-      </c>
       <c r="H47">
-        <v>22426</v>
+        <v>0</v>
       </c>
       <c r="I47">
         <v>0</v>
@@ -3506,39 +3369,36 @@
         <v>0</v>
       </c>
       <c r="L47">
-        <v>0</v>
+        <v>2595</v>
       </c>
       <c r="M47">
-        <v>2595</v>
+        <v>1</v>
       </c>
       <c r="N47">
-        <v>1</v>
+        <v>142</v>
       </c>
       <c r="O47">
-        <v>142</v>
+        <v>22284</v>
       </c>
       <c r="P47">
-        <v>22284</v>
+        <v>50821</v>
       </c>
       <c r="Q47">
-        <v>50821</v>
+        <v>5046</v>
       </c>
       <c r="R47">
-        <v>5046</v>
+        <v>0</v>
       </c>
       <c r="S47">
         <v>0</v>
       </c>
-      <c r="T47">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="48" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="48" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A48">
         <v>45</v>
       </c>
       <c r="B48" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C48">
         <v>19641</v>
@@ -3547,16 +3407,16 @@
         <v>0</v>
       </c>
       <c r="E48">
-        <v>0</v>
+        <v>19641</v>
       </c>
       <c r="F48">
+        <v>0</v>
+      </c>
+      <c r="G48">
         <v>19641</v>
       </c>
-      <c r="G48">
-        <v>0</v>
-      </c>
       <c r="H48">
-        <v>19641</v>
+        <v>0</v>
       </c>
       <c r="I48">
         <v>0</v>
@@ -3568,39 +3428,36 @@
         <v>0</v>
       </c>
       <c r="L48">
-        <v>0</v>
+        <v>3800</v>
       </c>
       <c r="M48">
-        <v>3800</v>
+        <v>4</v>
       </c>
       <c r="N48">
-        <v>4</v>
+        <v>266</v>
       </c>
       <c r="O48">
-        <v>266</v>
+        <v>19376</v>
       </c>
       <c r="P48">
-        <v>19376</v>
+        <v>54497</v>
       </c>
       <c r="Q48">
-        <v>54497</v>
+        <v>4623</v>
       </c>
       <c r="R48">
-        <v>4623</v>
+        <v>0</v>
       </c>
       <c r="S48">
-        <v>0</v>
-      </c>
-      <c r="T48">
         <v>9</v>
       </c>
     </row>
-    <row r="49" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A49">
         <v>46</v>
       </c>
       <c r="B49" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C49">
         <v>21651</v>
@@ -3609,16 +3466,16 @@
         <v>0</v>
       </c>
       <c r="E49">
-        <v>0</v>
+        <v>21651</v>
       </c>
       <c r="F49">
+        <v>0</v>
+      </c>
+      <c r="G49">
         <v>21651</v>
       </c>
-      <c r="G49">
-        <v>0</v>
-      </c>
       <c r="H49">
-        <v>21651</v>
+        <v>0</v>
       </c>
       <c r="I49">
         <v>0</v>
@@ -3630,39 +3487,36 @@
         <v>0</v>
       </c>
       <c r="L49">
-        <v>0</v>
+        <v>3627</v>
       </c>
       <c r="M49">
-        <v>3627</v>
+        <v>0</v>
       </c>
       <c r="N49">
-        <v>0</v>
+        <v>628</v>
       </c>
       <c r="O49">
-        <v>628</v>
+        <v>21027</v>
       </c>
       <c r="P49">
-        <v>21027</v>
+        <v>55376</v>
       </c>
       <c r="Q49">
-        <v>55376</v>
+        <v>5057</v>
       </c>
       <c r="R49">
-        <v>5057</v>
+        <v>0</v>
       </c>
       <c r="S49">
-        <v>0</v>
-      </c>
-      <c r="T49">
         <v>4</v>
       </c>
     </row>
-    <row r="50" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A50">
         <v>47</v>
       </c>
       <c r="B50" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C50">
         <v>21936</v>
@@ -3671,16 +3525,16 @@
         <v>0</v>
       </c>
       <c r="E50">
-        <v>0</v>
+        <v>21936</v>
       </c>
       <c r="F50">
+        <v>0</v>
+      </c>
+      <c r="G50">
         <v>21936</v>
       </c>
-      <c r="G50">
-        <v>0</v>
-      </c>
       <c r="H50">
-        <v>21936</v>
+        <v>0</v>
       </c>
       <c r="I50">
         <v>0</v>
@@ -3692,39 +3546,36 @@
         <v>0</v>
       </c>
       <c r="L50">
-        <v>0</v>
+        <v>4160</v>
       </c>
       <c r="M50">
-        <v>4160</v>
+        <v>5</v>
       </c>
       <c r="N50">
-        <v>5</v>
+        <v>26</v>
       </c>
       <c r="O50">
-        <v>26</v>
+        <v>21910</v>
       </c>
       <c r="P50">
-        <v>21910</v>
+        <v>63298</v>
       </c>
       <c r="Q50">
-        <v>63298</v>
+        <v>7292</v>
       </c>
       <c r="R50">
-        <v>7292</v>
+        <v>0</v>
       </c>
       <c r="S50">
-        <v>0</v>
-      </c>
-      <c r="T50">
         <v>1</v>
       </c>
     </row>
-    <row r="51" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A51">
         <v>48</v>
       </c>
       <c r="B51" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C51">
         <v>23798</v>
@@ -3733,16 +3584,16 @@
         <v>0</v>
       </c>
       <c r="E51">
-        <v>0</v>
+        <v>23798</v>
       </c>
       <c r="F51">
+        <v>0</v>
+      </c>
+      <c r="G51">
         <v>23798</v>
       </c>
-      <c r="G51">
-        <v>0</v>
-      </c>
       <c r="H51">
-        <v>23798</v>
+        <v>0</v>
       </c>
       <c r="I51">
         <v>0</v>
@@ -3754,39 +3605,36 @@
         <v>0</v>
       </c>
       <c r="L51">
-        <v>0</v>
+        <v>4843</v>
       </c>
       <c r="M51">
-        <v>4843</v>
+        <v>11</v>
       </c>
       <c r="N51">
-        <v>11</v>
+        <v>75</v>
       </c>
       <c r="O51">
-        <v>75</v>
+        <v>23723</v>
       </c>
       <c r="P51">
-        <v>23723</v>
+        <v>71754</v>
       </c>
       <c r="Q51">
-        <v>71754</v>
+        <v>7715</v>
       </c>
       <c r="R51">
-        <v>7715</v>
+        <v>0</v>
       </c>
       <c r="S51">
-        <v>0</v>
-      </c>
-      <c r="T51">
         <v>40</v>
       </c>
     </row>
-    <row r="52" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A52">
         <v>49</v>
       </c>
       <c r="B52" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C52">
         <v>21094</v>
@@ -3795,16 +3643,16 @@
         <v>0</v>
       </c>
       <c r="E52">
-        <v>0</v>
+        <v>21094</v>
       </c>
       <c r="F52">
+        <v>0</v>
+      </c>
+      <c r="G52">
         <v>21094</v>
       </c>
-      <c r="G52">
-        <v>0</v>
-      </c>
       <c r="H52">
-        <v>21094</v>
+        <v>0</v>
       </c>
       <c r="I52">
         <v>0</v>
@@ -3816,39 +3664,36 @@
         <v>0</v>
       </c>
       <c r="L52">
-        <v>0</v>
+        <v>2942</v>
       </c>
       <c r="M52">
-        <v>2942</v>
+        <v>1</v>
       </c>
       <c r="N52">
-        <v>1</v>
+        <v>45</v>
       </c>
       <c r="O52">
-        <v>45</v>
+        <v>21049</v>
       </c>
       <c r="P52">
-        <v>21049</v>
+        <v>63987</v>
       </c>
       <c r="Q52">
-        <v>63987</v>
+        <v>5655</v>
       </c>
       <c r="R52">
-        <v>5655</v>
+        <v>0</v>
       </c>
       <c r="S52">
-        <v>0</v>
-      </c>
-      <c r="T52">
         <v>2</v>
       </c>
     </row>
-    <row r="53" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A53">
         <v>50</v>
       </c>
       <c r="B53" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C53">
         <v>19131</v>
@@ -3857,16 +3702,16 @@
         <v>0</v>
       </c>
       <c r="E53">
-        <v>0</v>
+        <v>19131</v>
       </c>
       <c r="F53">
+        <v>0</v>
+      </c>
+      <c r="G53">
         <v>19131</v>
       </c>
-      <c r="G53">
-        <v>0</v>
-      </c>
       <c r="H53">
-        <v>19131</v>
+        <v>0</v>
       </c>
       <c r="I53">
         <v>0</v>
@@ -3878,39 +3723,36 @@
         <v>0</v>
       </c>
       <c r="L53">
-        <v>0</v>
+        <v>3513</v>
       </c>
       <c r="M53">
-        <v>3513</v>
+        <v>1</v>
       </c>
       <c r="N53">
-        <v>1</v>
+        <v>76</v>
       </c>
       <c r="O53">
-        <v>76</v>
+        <v>19055</v>
       </c>
       <c r="P53">
-        <v>19055</v>
+        <v>56306</v>
       </c>
       <c r="Q53">
-        <v>56306</v>
+        <v>6551</v>
       </c>
       <c r="R53">
-        <v>6551</v>
+        <v>0</v>
       </c>
       <c r="S53">
-        <v>0</v>
-      </c>
-      <c r="T53">
         <v>5</v>
       </c>
     </row>
-    <row r="54" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A54">
         <v>51</v>
       </c>
       <c r="B54" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C54">
         <v>20758</v>
@@ -3919,16 +3761,16 @@
         <v>0</v>
       </c>
       <c r="E54">
-        <v>0</v>
+        <v>20758</v>
       </c>
       <c r="F54">
+        <v>0</v>
+      </c>
+      <c r="G54">
         <v>20758</v>
       </c>
-      <c r="G54">
-        <v>0</v>
-      </c>
       <c r="H54">
-        <v>20758</v>
+        <v>0</v>
       </c>
       <c r="I54">
         <v>0</v>
@@ -3940,39 +3782,36 @@
         <v>0</v>
       </c>
       <c r="L54">
-        <v>0</v>
+        <v>2603</v>
       </c>
       <c r="M54">
-        <v>2603</v>
+        <v>5</v>
       </c>
       <c r="N54">
-        <v>5</v>
+        <v>391</v>
       </c>
       <c r="O54">
-        <v>391</v>
+        <v>20367</v>
       </c>
       <c r="P54">
-        <v>20367</v>
+        <v>58441</v>
       </c>
       <c r="Q54">
-        <v>58441</v>
+        <v>7347</v>
       </c>
       <c r="R54">
-        <v>7347</v>
+        <v>0</v>
       </c>
       <c r="S54">
-        <v>0</v>
-      </c>
-      <c r="T54">
         <v>1</v>
       </c>
     </row>
-    <row r="55" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A55">
         <v>52</v>
       </c>
       <c r="B55" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C55">
         <v>16022</v>
@@ -3981,16 +3820,16 @@
         <v>0</v>
       </c>
       <c r="E55">
-        <v>0</v>
+        <v>16022</v>
       </c>
       <c r="F55">
+        <v>0</v>
+      </c>
+      <c r="G55">
         <v>16022</v>
       </c>
-      <c r="G55">
-        <v>0</v>
-      </c>
       <c r="H55">
-        <v>16022</v>
+        <v>0</v>
       </c>
       <c r="I55">
         <v>0</v>
@@ -4002,39 +3841,36 @@
         <v>0</v>
       </c>
       <c r="L55">
-        <v>0</v>
+        <v>2109</v>
       </c>
       <c r="M55">
-        <v>2109</v>
+        <v>1</v>
       </c>
       <c r="N55">
-        <v>1</v>
+        <v>129</v>
       </c>
       <c r="O55">
-        <v>129</v>
+        <v>15893</v>
       </c>
       <c r="P55">
-        <v>15893</v>
+        <v>58215</v>
       </c>
       <c r="Q55">
-        <v>58215</v>
+        <v>5098</v>
       </c>
       <c r="R55">
-        <v>5098</v>
+        <v>0</v>
       </c>
       <c r="S55">
         <v>0</v>
       </c>
-      <c r="T55">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="56" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="56" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A56">
         <v>53</v>
       </c>
       <c r="B56" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C56">
         <v>19256</v>
@@ -4043,16 +3879,16 @@
         <v>0</v>
       </c>
       <c r="E56">
-        <v>0</v>
+        <v>19256</v>
       </c>
       <c r="F56">
+        <v>0</v>
+      </c>
+      <c r="G56">
         <v>19256</v>
       </c>
-      <c r="G56">
-        <v>0</v>
-      </c>
       <c r="H56">
-        <v>19256</v>
+        <v>0</v>
       </c>
       <c r="I56">
         <v>0</v>
@@ -4064,39 +3900,36 @@
         <v>0</v>
       </c>
       <c r="L56">
-        <v>0</v>
+        <v>4091</v>
       </c>
       <c r="M56">
-        <v>4091</v>
+        <v>3</v>
       </c>
       <c r="N56">
-        <v>3</v>
+        <v>451</v>
       </c>
       <c r="O56">
-        <v>451</v>
+        <v>18805</v>
       </c>
       <c r="P56">
-        <v>18805</v>
+        <v>47621</v>
       </c>
       <c r="Q56">
-        <v>47621</v>
+        <v>4882</v>
       </c>
       <c r="R56">
-        <v>4882</v>
+        <v>0</v>
       </c>
       <c r="S56">
-        <v>0</v>
-      </c>
-      <c r="T56">
         <v>30</v>
       </c>
     </row>
-    <row r="57" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A57">
         <v>54</v>
       </c>
       <c r="B57" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C57">
         <v>21240</v>
@@ -4105,16 +3938,16 @@
         <v>0</v>
       </c>
       <c r="E57">
-        <v>0</v>
+        <v>21240</v>
       </c>
       <c r="F57">
+        <v>0</v>
+      </c>
+      <c r="G57">
         <v>21240</v>
       </c>
-      <c r="G57">
-        <v>0</v>
-      </c>
       <c r="H57">
-        <v>21240</v>
+        <v>0</v>
       </c>
       <c r="I57">
         <v>0</v>
@@ -4126,39 +3959,36 @@
         <v>0</v>
       </c>
       <c r="L57">
-        <v>0</v>
+        <v>1905</v>
       </c>
       <c r="M57">
-        <v>1905</v>
+        <v>5</v>
       </c>
       <c r="N57">
-        <v>5</v>
+        <v>39</v>
       </c>
       <c r="O57">
-        <v>39</v>
+        <v>21201</v>
       </c>
       <c r="P57">
-        <v>21201</v>
+        <v>61557</v>
       </c>
       <c r="Q57">
-        <v>61557</v>
+        <v>6870</v>
       </c>
       <c r="R57">
-        <v>6870</v>
+        <v>0</v>
       </c>
       <c r="S57">
         <v>0</v>
       </c>
-      <c r="T57">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="58" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="58" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A58">
         <v>55</v>
       </c>
       <c r="B58" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C58">
         <v>22819</v>
@@ -4167,16 +3997,16 @@
         <v>0</v>
       </c>
       <c r="E58">
-        <v>0</v>
+        <v>22819</v>
       </c>
       <c r="F58">
+        <v>0</v>
+      </c>
+      <c r="G58">
         <v>22819</v>
       </c>
-      <c r="G58">
-        <v>0</v>
-      </c>
       <c r="H58">
-        <v>22819</v>
+        <v>0</v>
       </c>
       <c r="I58">
         <v>0</v>
@@ -4188,39 +4018,36 @@
         <v>0</v>
       </c>
       <c r="L58">
-        <v>0</v>
+        <v>8123</v>
       </c>
       <c r="M58">
-        <v>8123</v>
+        <v>10</v>
       </c>
       <c r="N58">
-        <v>10</v>
+        <v>552</v>
       </c>
       <c r="O58">
-        <v>552</v>
+        <v>22267</v>
       </c>
       <c r="P58">
-        <v>22267</v>
+        <v>57577</v>
       </c>
       <c r="Q58">
-        <v>57577</v>
+        <v>8884</v>
       </c>
       <c r="R58">
-        <v>8884</v>
+        <v>0</v>
       </c>
       <c r="S58">
-        <v>0</v>
-      </c>
-      <c r="T58">
         <v>64</v>
       </c>
     </row>
-    <row r="59" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A59">
         <v>56</v>
       </c>
       <c r="B59" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C59">
         <v>18776</v>
@@ -4229,16 +4056,16 @@
         <v>0</v>
       </c>
       <c r="E59">
-        <v>0</v>
+        <v>18776</v>
       </c>
       <c r="F59">
+        <v>0</v>
+      </c>
+      <c r="G59">
         <v>18776</v>
       </c>
-      <c r="G59">
-        <v>0</v>
-      </c>
       <c r="H59">
-        <v>18776</v>
+        <v>0</v>
       </c>
       <c r="I59">
         <v>0</v>
@@ -4250,39 +4077,36 @@
         <v>0</v>
       </c>
       <c r="L59">
-        <v>0</v>
+        <v>2506</v>
       </c>
       <c r="M59">
-        <v>2506</v>
+        <v>2</v>
       </c>
       <c r="N59">
-        <v>2</v>
+        <v>287</v>
       </c>
       <c r="O59">
-        <v>287</v>
+        <v>18489</v>
       </c>
       <c r="P59">
-        <v>18489</v>
+        <v>60495</v>
       </c>
       <c r="Q59">
-        <v>60495</v>
+        <v>8028</v>
       </c>
       <c r="R59">
-        <v>8028</v>
+        <v>0</v>
       </c>
       <c r="S59">
-        <v>0</v>
-      </c>
-      <c r="T59">
         <v>27</v>
       </c>
     </row>
-    <row r="60" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A60">
         <v>57</v>
       </c>
       <c r="B60" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C60">
         <v>23749</v>
@@ -4291,16 +4115,16 @@
         <v>0</v>
       </c>
       <c r="E60">
-        <v>0</v>
+        <v>23749</v>
       </c>
       <c r="F60">
+        <v>0</v>
+      </c>
+      <c r="G60">
         <v>23749</v>
       </c>
-      <c r="G60">
-        <v>0</v>
-      </c>
       <c r="H60">
-        <v>23749</v>
+        <v>0</v>
       </c>
       <c r="I60">
         <v>0</v>
@@ -4312,39 +4136,36 @@
         <v>0</v>
       </c>
       <c r="L60">
-        <v>0</v>
+        <v>5815</v>
       </c>
       <c r="M60">
-        <v>5815</v>
+        <v>9</v>
       </c>
       <c r="N60">
-        <v>9</v>
+        <v>324</v>
       </c>
       <c r="O60">
-        <v>324</v>
+        <v>23425</v>
       </c>
       <c r="P60">
-        <v>23425</v>
+        <v>70140</v>
       </c>
       <c r="Q60">
-        <v>70140</v>
+        <v>7415</v>
       </c>
       <c r="R60">
-        <v>7415</v>
+        <v>0</v>
       </c>
       <c r="S60">
-        <v>0</v>
-      </c>
-      <c r="T60">
         <v>32</v>
       </c>
     </row>
-    <row r="61" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A61">
         <v>58</v>
       </c>
       <c r="B61" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C61">
         <v>22069</v>
@@ -4353,16 +4174,16 @@
         <v>0</v>
       </c>
       <c r="E61">
-        <v>0</v>
+        <v>22069</v>
       </c>
       <c r="F61">
+        <v>0</v>
+      </c>
+      <c r="G61">
         <v>22069</v>
       </c>
-      <c r="G61">
-        <v>0</v>
-      </c>
       <c r="H61">
-        <v>22069</v>
+        <v>0</v>
       </c>
       <c r="I61">
         <v>0</v>
@@ -4374,39 +4195,36 @@
         <v>0</v>
       </c>
       <c r="L61">
-        <v>0</v>
+        <v>9977</v>
       </c>
       <c r="M61">
-        <v>9977</v>
+        <v>37</v>
       </c>
       <c r="N61">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="O61">
-        <v>36</v>
+        <v>22033</v>
       </c>
       <c r="P61">
-        <v>22033</v>
+        <v>55240</v>
       </c>
       <c r="Q61">
-        <v>55240</v>
+        <v>7927</v>
       </c>
       <c r="R61">
-        <v>7927</v>
+        <v>1</v>
       </c>
       <c r="S61">
-        <v>1</v>
-      </c>
-      <c r="T61">
         <v>268</v>
       </c>
     </row>
-    <row r="62" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A62">
         <v>59</v>
       </c>
       <c r="B62" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C62">
         <v>15800</v>
@@ -4415,16 +4233,16 @@
         <v>0</v>
       </c>
       <c r="E62">
-        <v>0</v>
+        <v>15800</v>
       </c>
       <c r="F62">
+        <v>0</v>
+      </c>
+      <c r="G62">
         <v>15800</v>
       </c>
-      <c r="G62">
-        <v>0</v>
-      </c>
       <c r="H62">
-        <v>15800</v>
+        <v>0</v>
       </c>
       <c r="I62">
         <v>0</v>
@@ -4436,39 +4254,36 @@
         <v>0</v>
       </c>
       <c r="L62">
-        <v>0</v>
+        <v>4214</v>
       </c>
       <c r="M62">
-        <v>4214</v>
+        <v>19</v>
       </c>
       <c r="N62">
-        <v>19</v>
+        <v>494</v>
       </c>
       <c r="O62">
-        <v>494</v>
+        <v>15306</v>
       </c>
       <c r="P62">
-        <v>15306</v>
+        <v>51334</v>
       </c>
       <c r="Q62">
-        <v>51334</v>
+        <v>6917</v>
       </c>
       <c r="R62">
-        <v>6917</v>
+        <v>0</v>
       </c>
       <c r="S62">
-        <v>0</v>
-      </c>
-      <c r="T62">
         <v>100</v>
       </c>
     </row>
-    <row r="63" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A63">
         <v>60</v>
       </c>
       <c r="B63" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C63">
         <v>36754</v>
@@ -4477,16 +4292,16 @@
         <v>0</v>
       </c>
       <c r="E63">
-        <v>0</v>
+        <v>36754</v>
       </c>
       <c r="F63">
+        <v>0</v>
+      </c>
+      <c r="G63">
         <v>36754</v>
       </c>
-      <c r="G63">
-        <v>0</v>
-      </c>
       <c r="H63">
-        <v>36754</v>
+        <v>0</v>
       </c>
       <c r="I63">
         <v>0</v>
@@ -4498,39 +4313,36 @@
         <v>0</v>
       </c>
       <c r="L63">
-        <v>0</v>
+        <v>10975</v>
       </c>
       <c r="M63">
-        <v>10975</v>
+        <v>68</v>
       </c>
       <c r="N63">
-        <v>68</v>
+        <v>931</v>
       </c>
       <c r="O63">
-        <v>931</v>
+        <v>35823</v>
       </c>
       <c r="P63">
-        <v>35823</v>
+        <v>68699</v>
       </c>
       <c r="Q63">
-        <v>68699</v>
+        <v>9766</v>
       </c>
       <c r="R63">
-        <v>9766</v>
+        <v>0</v>
       </c>
       <c r="S63">
-        <v>0</v>
-      </c>
-      <c r="T63">
         <v>153</v>
       </c>
     </row>
-    <row r="64" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A64">
         <v>61</v>
       </c>
       <c r="B64" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C64">
         <v>42048</v>
@@ -4539,16 +4351,16 @@
         <v>0</v>
       </c>
       <c r="E64">
-        <v>0</v>
+        <v>42048</v>
       </c>
       <c r="F64">
+        <v>0</v>
+      </c>
+      <c r="G64">
         <v>42048</v>
       </c>
-      <c r="G64">
-        <v>0</v>
-      </c>
       <c r="H64">
-        <v>42048</v>
+        <v>0</v>
       </c>
       <c r="I64">
         <v>0</v>
@@ -4560,39 +4372,36 @@
         <v>0</v>
       </c>
       <c r="L64">
-        <v>0</v>
+        <v>9887</v>
       </c>
       <c r="M64">
-        <v>9887</v>
+        <v>8</v>
       </c>
       <c r="N64">
-        <v>8</v>
+        <v>493</v>
       </c>
       <c r="O64">
-        <v>493</v>
+        <v>41555</v>
       </c>
       <c r="P64">
-        <v>41555</v>
+        <v>60527</v>
       </c>
       <c r="Q64">
-        <v>60527</v>
+        <v>5985</v>
       </c>
       <c r="R64">
-        <v>5985</v>
+        <v>0</v>
       </c>
       <c r="S64">
-        <v>0</v>
-      </c>
-      <c r="T64">
         <v>101</v>
       </c>
     </row>
-    <row r="65" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A65">
         <v>62</v>
       </c>
       <c r="B65" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C65">
         <v>41389</v>
@@ -4601,16 +4410,16 @@
         <v>0</v>
       </c>
       <c r="E65">
-        <v>0</v>
+        <v>41389</v>
       </c>
       <c r="F65">
+        <v>0</v>
+      </c>
+      <c r="G65">
         <v>41389</v>
       </c>
-      <c r="G65">
-        <v>0</v>
-      </c>
       <c r="H65">
-        <v>41389</v>
+        <v>0</v>
       </c>
       <c r="I65">
         <v>0</v>
@@ -4622,39 +4431,36 @@
         <v>0</v>
       </c>
       <c r="L65">
-        <v>0</v>
+        <v>13582</v>
       </c>
       <c r="M65">
-        <v>13582</v>
+        <v>2</v>
       </c>
       <c r="N65">
-        <v>2</v>
+        <v>2635</v>
       </c>
       <c r="O65">
-        <v>2635</v>
+        <v>38754</v>
       </c>
       <c r="P65">
-        <v>38754</v>
+        <v>58527</v>
       </c>
       <c r="Q65">
-        <v>58527</v>
+        <v>13282</v>
       </c>
       <c r="R65">
-        <v>13282</v>
+        <v>0</v>
       </c>
       <c r="S65">
-        <v>0</v>
-      </c>
-      <c r="T65">
         <v>138</v>
       </c>
     </row>
-    <row r="66" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A66">
         <v>63</v>
       </c>
       <c r="B66" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C66">
         <v>67362</v>
@@ -4663,16 +4469,16 @@
         <v>0</v>
       </c>
       <c r="E66">
-        <v>1</v>
+        <v>67362</v>
       </c>
       <c r="F66">
+        <v>0</v>
+      </c>
+      <c r="G66">
         <v>67362</v>
       </c>
-      <c r="G66">
-        <v>0</v>
-      </c>
       <c r="H66">
-        <v>67362</v>
+        <v>0</v>
       </c>
       <c r="I66">
         <v>0</v>
@@ -4684,39 +4490,36 @@
         <v>0</v>
       </c>
       <c r="L66">
-        <v>0</v>
+        <v>13733</v>
       </c>
       <c r="M66">
-        <v>13733</v>
+        <v>2</v>
       </c>
       <c r="N66">
-        <v>2</v>
+        <v>4022</v>
       </c>
       <c r="O66">
-        <v>4022</v>
+        <v>63341</v>
       </c>
       <c r="P66">
-        <v>63341</v>
+        <v>93810</v>
       </c>
       <c r="Q66">
-        <v>93810</v>
+        <v>17742</v>
       </c>
       <c r="R66">
-        <v>17742</v>
+        <v>0</v>
       </c>
       <c r="S66">
-        <v>0</v>
-      </c>
-      <c r="T66">
         <v>52</v>
       </c>
     </row>
-    <row r="67" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A67">
         <v>64</v>
       </c>
       <c r="B67" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C67">
         <v>68828</v>
@@ -4725,16 +4528,16 @@
         <v>0</v>
       </c>
       <c r="E67">
-        <v>0</v>
+        <v>68828</v>
       </c>
       <c r="F67">
+        <v>0</v>
+      </c>
+      <c r="G67">
         <v>68828</v>
       </c>
-      <c r="G67">
-        <v>0</v>
-      </c>
       <c r="H67">
-        <v>68828</v>
+        <v>0</v>
       </c>
       <c r="I67">
         <v>0</v>
@@ -4746,39 +4549,36 @@
         <v>0</v>
       </c>
       <c r="L67">
-        <v>0</v>
+        <v>19495</v>
       </c>
       <c r="M67">
-        <v>19495</v>
+        <v>10</v>
       </c>
       <c r="N67">
-        <v>10</v>
+        <v>3644</v>
       </c>
       <c r="O67">
-        <v>3644</v>
+        <v>65185</v>
       </c>
       <c r="P67">
-        <v>65185</v>
+        <v>78032</v>
       </c>
       <c r="Q67">
-        <v>78032</v>
+        <v>9807</v>
       </c>
       <c r="R67">
-        <v>9807</v>
+        <v>0</v>
       </c>
       <c r="S67">
-        <v>0</v>
-      </c>
-      <c r="T67">
         <v>116</v>
       </c>
     </row>
-    <row r="68" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A68">
         <v>65</v>
       </c>
       <c r="B68" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C68">
         <v>65397</v>
@@ -4787,16 +4587,16 @@
         <v>0</v>
       </c>
       <c r="E68">
-        <v>0</v>
+        <v>65397</v>
       </c>
       <c r="F68">
+        <v>0</v>
+      </c>
+      <c r="G68">
         <v>65397</v>
       </c>
-      <c r="G68">
-        <v>0</v>
-      </c>
       <c r="H68">
-        <v>65397</v>
+        <v>0</v>
       </c>
       <c r="I68">
         <v>0</v>
@@ -4808,39 +4608,36 @@
         <v>0</v>
       </c>
       <c r="L68">
-        <v>0</v>
+        <v>18679</v>
       </c>
       <c r="M68">
-        <v>18679</v>
+        <v>2</v>
       </c>
       <c r="N68">
-        <v>2</v>
+        <v>1603</v>
       </c>
       <c r="O68">
-        <v>1603</v>
+        <v>63796</v>
       </c>
       <c r="P68">
-        <v>63796</v>
+        <v>71325</v>
       </c>
       <c r="Q68">
-        <v>71325</v>
+        <v>7850</v>
       </c>
       <c r="R68">
-        <v>7850</v>
+        <v>0</v>
       </c>
       <c r="S68">
-        <v>0</v>
-      </c>
-      <c r="T68">
         <v>26</v>
       </c>
     </row>
-    <row r="69" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A69">
         <v>66</v>
       </c>
       <c r="B69" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C69">
         <v>43938</v>
@@ -4849,16 +4646,16 @@
         <v>0</v>
       </c>
       <c r="E69">
-        <v>0</v>
+        <v>43938</v>
       </c>
       <c r="F69">
+        <v>0</v>
+      </c>
+      <c r="G69">
         <v>43938</v>
       </c>
-      <c r="G69">
-        <v>0</v>
-      </c>
       <c r="H69">
-        <v>43938</v>
+        <v>0</v>
       </c>
       <c r="I69">
         <v>0</v>
@@ -4870,39 +4667,36 @@
         <v>0</v>
       </c>
       <c r="L69">
-        <v>0</v>
+        <v>18216</v>
       </c>
       <c r="M69">
-        <v>18216</v>
+        <v>2</v>
       </c>
       <c r="N69">
-        <v>2</v>
+        <v>2619</v>
       </c>
       <c r="O69">
-        <v>2619</v>
+        <v>41322</v>
       </c>
       <c r="P69">
-        <v>41322</v>
+        <v>36118</v>
       </c>
       <c r="Q69">
-        <v>36118</v>
+        <v>6528</v>
       </c>
       <c r="R69">
-        <v>6528</v>
+        <v>0</v>
       </c>
       <c r="S69">
-        <v>0</v>
-      </c>
-      <c r="T69">
         <v>47</v>
       </c>
     </row>
-    <row r="70" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A70">
         <v>67</v>
       </c>
       <c r="B70" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C70">
         <v>47711</v>
@@ -4911,16 +4705,16 @@
         <v>0</v>
       </c>
       <c r="E70">
-        <v>0</v>
+        <v>47711</v>
       </c>
       <c r="F70">
+        <v>0</v>
+      </c>
+      <c r="G70">
         <v>47711</v>
       </c>
-      <c r="G70">
-        <v>0</v>
-      </c>
       <c r="H70">
-        <v>47711</v>
+        <v>0</v>
       </c>
       <c r="I70">
         <v>0</v>
@@ -4932,39 +4726,36 @@
         <v>0</v>
       </c>
       <c r="L70">
-        <v>0</v>
+        <v>18275</v>
       </c>
       <c r="M70">
-        <v>18275</v>
+        <v>2</v>
       </c>
       <c r="N70">
-        <v>2</v>
+        <v>3246</v>
       </c>
       <c r="O70">
-        <v>3246</v>
+        <v>44466</v>
       </c>
       <c r="P70">
-        <v>44466</v>
+        <v>42051</v>
       </c>
       <c r="Q70">
-        <v>42051</v>
+        <v>5798</v>
       </c>
       <c r="R70">
-        <v>5798</v>
+        <v>0</v>
       </c>
       <c r="S70">
-        <v>0</v>
-      </c>
-      <c r="T70">
         <v>29</v>
       </c>
     </row>
-    <row r="71" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A71">
         <v>68</v>
       </c>
       <c r="B71" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C71">
         <v>50963</v>
@@ -4973,16 +4764,16 @@
         <v>0</v>
       </c>
       <c r="E71">
-        <v>0</v>
+        <v>50963</v>
       </c>
       <c r="F71">
+        <v>0</v>
+      </c>
+      <c r="G71">
         <v>50963</v>
       </c>
-      <c r="G71">
-        <v>0</v>
-      </c>
       <c r="H71">
-        <v>50963</v>
+        <v>0</v>
       </c>
       <c r="I71">
         <v>0</v>
@@ -4994,39 +4785,36 @@
         <v>0</v>
       </c>
       <c r="L71">
-        <v>0</v>
+        <v>22851</v>
       </c>
       <c r="M71">
-        <v>22851</v>
+        <v>1</v>
       </c>
       <c r="N71">
-        <v>1</v>
+        <v>4449</v>
       </c>
       <c r="O71">
-        <v>4449</v>
+        <v>46514</v>
       </c>
       <c r="P71">
-        <v>46514</v>
+        <v>49140</v>
       </c>
       <c r="Q71">
-        <v>49140</v>
+        <v>6782</v>
       </c>
       <c r="R71">
-        <v>6782</v>
+        <v>0</v>
       </c>
       <c r="S71">
-        <v>0</v>
-      </c>
-      <c r="T71">
         <v>235</v>
       </c>
     </row>
-    <row r="72" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A72">
         <v>69</v>
       </c>
       <c r="B72" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C72">
         <v>61543</v>
@@ -5035,16 +4823,16 @@
         <v>0</v>
       </c>
       <c r="E72">
-        <v>0</v>
+        <v>61543</v>
       </c>
       <c r="F72">
+        <v>0</v>
+      </c>
+      <c r="G72">
         <v>61543</v>
       </c>
-      <c r="G72">
-        <v>0</v>
-      </c>
       <c r="H72">
-        <v>61543</v>
+        <v>0</v>
       </c>
       <c r="I72">
         <v>0</v>
@@ -5056,39 +4844,36 @@
         <v>0</v>
       </c>
       <c r="L72">
-        <v>0</v>
+        <v>17245</v>
       </c>
       <c r="M72">
-        <v>17245</v>
+        <v>9</v>
       </c>
       <c r="N72">
-        <v>9</v>
+        <v>3668</v>
       </c>
       <c r="O72">
-        <v>3668</v>
+        <v>57877</v>
       </c>
       <c r="P72">
-        <v>57877</v>
+        <v>85504</v>
       </c>
       <c r="Q72">
-        <v>85504</v>
+        <v>12340</v>
       </c>
       <c r="R72">
-        <v>12340</v>
+        <v>0</v>
       </c>
       <c r="S72">
-        <v>0</v>
-      </c>
-      <c r="T72">
         <v>79</v>
       </c>
     </row>
-    <row r="73" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A73">
         <v>70</v>
       </c>
       <c r="B73" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C73">
         <v>58915</v>
@@ -5097,16 +4882,16 @@
         <v>0</v>
       </c>
       <c r="E73">
-        <v>0</v>
+        <v>58915</v>
       </c>
       <c r="F73">
+        <v>0</v>
+      </c>
+      <c r="G73">
         <v>58915</v>
       </c>
-      <c r="G73">
-        <v>0</v>
-      </c>
       <c r="H73">
-        <v>58915</v>
+        <v>0</v>
       </c>
       <c r="I73">
         <v>0</v>
@@ -5118,36 +4903,33 @@
         <v>0</v>
       </c>
       <c r="L73">
-        <v>0</v>
+        <v>15131</v>
       </c>
       <c r="M73">
-        <v>15131</v>
+        <v>8</v>
       </c>
       <c r="N73">
-        <v>8</v>
+        <v>3866</v>
       </c>
       <c r="O73">
-        <v>3866</v>
+        <v>55049</v>
       </c>
       <c r="P73">
-        <v>55049</v>
+        <v>67666</v>
       </c>
       <c r="Q73">
-        <v>67666</v>
+        <v>10010</v>
       </c>
       <c r="R73">
-        <v>10010</v>
+        <v>0</v>
       </c>
       <c r="S73">
-        <v>0</v>
-      </c>
-      <c r="T73">
         <v>74</v>
       </c>
     </row>
-    <row r="74" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A74" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B74" s="1"/>
       <c r="C74">
@@ -5157,16 +4939,16 @@
         <v>0</v>
       </c>
       <c r="E74">
-        <v>9</v>
+        <v>2430387</v>
       </c>
       <c r="F74">
-        <v>2430387</v>
+        <v>0</v>
       </c>
       <c r="G74">
-        <v>0</v>
+        <v>2430385</v>
       </c>
       <c r="H74">
-        <v>2430385</v>
+        <v>0</v>
       </c>
       <c r="I74">
         <v>0</v>
@@ -5178,52 +4960,48 @@
         <v>0</v>
       </c>
       <c r="L74">
-        <v>0</v>
+        <v>626066</v>
       </c>
       <c r="M74">
-        <v>626066</v>
+        <v>8318</v>
       </c>
       <c r="N74">
-        <v>8318</v>
+        <v>97186</v>
       </c>
       <c r="O74">
-        <v>97186</v>
+        <v>2333338</v>
       </c>
       <c r="P74">
-        <v>2333338</v>
+        <v>4703236</v>
       </c>
       <c r="Q74">
-        <v>4703236</v>
+        <v>626236</v>
       </c>
       <c r="R74">
-        <v>626236</v>
+        <v>1</v>
       </c>
       <c r="S74">
-        <v>1</v>
-      </c>
-      <c r="T74">
         <v>3445</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="13">
+  <mergeCells count="12">
     <mergeCell ref="A74:B74"/>
-    <mergeCell ref="R2:T2"/>
-    <mergeCell ref="A1:R1"/>
+    <mergeCell ref="Q2:S2"/>
+    <mergeCell ref="A1:Q1"/>
     <mergeCell ref="A2:A3"/>
     <mergeCell ref="B2:B3"/>
     <mergeCell ref="C2:C3"/>
     <mergeCell ref="D2:D3"/>
     <mergeCell ref="E2:E3"/>
     <mergeCell ref="F2:F3"/>
-    <mergeCell ref="G2:G3"/>
-    <mergeCell ref="H2:J2"/>
-    <mergeCell ref="K2:N2"/>
-    <mergeCell ref="O2:Q2"/>
+    <mergeCell ref="G2:I2"/>
+    <mergeCell ref="J2:M2"/>
+    <mergeCell ref="N2:P2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="A2:Q74 B1:Q1" numberStoredAsText="1"/>
+    <ignoredError sqref="A2:D74 B1:D1 E2:P74 E1:P1" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/Notice.xlsx
+++ b/Notice.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Downloads\New folder (13)\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6404515-C3D0-492B-88B8-F1CED2705C87}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53EC95D2-F6FC-4847-B5C3-F75331010C77}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="96">
   <si>
     <t>S. No.</t>
   </si>
@@ -34,6 +34,9 @@
     <t>Pending for Notice Generation</t>
   </si>
   <si>
+    <t>Form 7/8 (Shifting)</t>
+  </si>
+  <si>
     <t>Notice Delivered</t>
   </si>
   <si>
@@ -304,7 +307,7 @@
     <t>No Action Required</t>
   </si>
   <si>
-    <t>Notice &amp; Hearing Report  29-09-2026 09:56:38</t>
+    <t>Notice &amp; Hearing Report 30-09-2026 09:56:37</t>
   </si>
 </sst>
 </file>
@@ -340,7 +343,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -685,12 +689,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:S74"/>
+  <dimension ref="A1:T76"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -708,8 +712,9 @@
       <c r="O1" s="1"/>
       <c r="P1" s="1"/>
       <c r="Q1" s="1"/>
-    </row>
-    <row r="2" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="R1" s="1"/>
+    </row>
+    <row r="2" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -731,35 +736,36 @@
       <c r="G2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H2" s="1"/>
+      <c r="H2" s="1" t="s">
+        <v>7</v>
+      </c>
       <c r="I2" s="1"/>
-      <c r="J2" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="K2" s="1"/>
+      <c r="J2" s="1"/>
+      <c r="K2" s="1" t="s">
+        <v>8</v>
+      </c>
       <c r="L2" s="1"/>
       <c r="M2" s="1"/>
-      <c r="N2" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="O2" s="1"/>
+      <c r="N2" s="1"/>
+      <c r="O2" s="1" t="s">
+        <v>9</v>
+      </c>
       <c r="P2" s="1"/>
-      <c r="Q2" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="R2" s="1"/>
+      <c r="Q2" s="1"/>
+      <c r="R2" s="1" t="s">
+        <v>91</v>
+      </c>
       <c r="S2" s="1"/>
-    </row>
-    <row r="3" spans="1:19" ht="63" x14ac:dyDescent="0.25">
+      <c r="T2" s="1"/>
+    </row>
+    <row r="3" spans="1:20" ht="63" x14ac:dyDescent="0.25">
       <c r="A3" s="1"/>
       <c r="B3" s="1"/>
       <c r="C3" s="1"/>
       <c r="D3" s="1"/>
       <c r="E3" s="1"/>
       <c r="F3" s="1"/>
-      <c r="G3" t="s">
-        <v>9</v>
-      </c>
+      <c r="G3" s="1"/>
       <c r="H3" t="s">
         <v>10</v>
       </c>
@@ -787,22 +793,25 @@
       <c r="P3" t="s">
         <v>18</v>
       </c>
-      <c r="Q3" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="R3" s="2" t="s">
+      <c r="Q3" t="s">
+        <v>19</v>
+      </c>
+      <c r="R3" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="S3" s="2" t="s">
+      <c r="S3" s="3" t="s">
         <v>93</v>
       </c>
-    </row>
-    <row r="4" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="T3" s="3" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="4" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>1</v>
       </c>
       <c r="B4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C4">
         <v>51528</v>
@@ -811,17 +820,17 @@
         <v>0</v>
       </c>
       <c r="E4">
+        <v>2</v>
+      </c>
+      <c r="F4">
         <v>51528</v>
       </c>
-      <c r="F4">
-        <v>0</v>
-      </c>
       <c r="G4">
+        <v>0</v>
+      </c>
+      <c r="H4">
         <v>51528</v>
       </c>
-      <c r="H4">
-        <v>0</v>
-      </c>
       <c r="I4">
         <v>0</v>
       </c>
@@ -832,36 +841,39 @@
         <v>0</v>
       </c>
       <c r="L4">
+        <v>0</v>
+      </c>
+      <c r="M4">
         <v>17975</v>
       </c>
-      <c r="M4">
+      <c r="N4">
         <v>967</v>
       </c>
-      <c r="N4">
+      <c r="O4">
         <v>869</v>
       </c>
-      <c r="O4">
+      <c r="P4">
         <v>50659</v>
       </c>
-      <c r="P4">
+      <c r="Q4">
         <v>53812</v>
       </c>
-      <c r="Q4">
+      <c r="R4" s="2">
         <v>12212</v>
       </c>
-      <c r="R4">
-        <v>0</v>
-      </c>
-      <c r="S4">
+      <c r="S4" s="2">
+        <v>0</v>
+      </c>
+      <c r="T4" s="2">
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>2</v>
       </c>
       <c r="B5" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C5">
         <v>53911</v>
@@ -870,17 +882,17 @@
         <v>0</v>
       </c>
       <c r="E5">
+        <v>0</v>
+      </c>
+      <c r="F5">
         <v>53911</v>
       </c>
-      <c r="F5">
-        <v>0</v>
-      </c>
       <c r="G5">
+        <v>0</v>
+      </c>
+      <c r="H5">
         <v>53911</v>
       </c>
-      <c r="H5">
-        <v>0</v>
-      </c>
       <c r="I5">
         <v>0</v>
       </c>
@@ -891,36 +903,39 @@
         <v>0</v>
       </c>
       <c r="L5">
+        <v>0</v>
+      </c>
+      <c r="M5">
         <v>11415</v>
       </c>
-      <c r="M5">
+      <c r="N5">
         <v>757</v>
       </c>
-      <c r="N5">
+      <c r="O5">
         <v>877</v>
       </c>
-      <c r="O5">
+      <c r="P5">
         <v>53035</v>
       </c>
-      <c r="P5">
+      <c r="Q5">
         <v>74848</v>
       </c>
-      <c r="Q5">
+      <c r="R5" s="2">
         <v>16108</v>
       </c>
-      <c r="R5">
-        <v>0</v>
-      </c>
-      <c r="S5">
+      <c r="S5" s="2">
+        <v>0</v>
+      </c>
+      <c r="T5" s="2">
         <v>30</v>
       </c>
     </row>
-    <row r="6" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>3</v>
       </c>
       <c r="B6" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C6">
         <v>39773</v>
@@ -929,17 +944,17 @@
         <v>0</v>
       </c>
       <c r="E6">
+        <v>0</v>
+      </c>
+      <c r="F6">
         <v>39773</v>
       </c>
-      <c r="F6">
-        <v>0</v>
-      </c>
       <c r="G6">
+        <v>0</v>
+      </c>
+      <c r="H6">
         <v>39773</v>
       </c>
-      <c r="H6">
-        <v>0</v>
-      </c>
       <c r="I6">
         <v>0</v>
       </c>
@@ -950,36 +965,39 @@
         <v>0</v>
       </c>
       <c r="L6">
+        <v>0</v>
+      </c>
+      <c r="M6">
         <v>6086</v>
       </c>
-      <c r="M6">
+      <c r="N6">
         <v>201</v>
       </c>
-      <c r="N6">
+      <c r="O6">
         <v>1870</v>
       </c>
-      <c r="O6">
+      <c r="P6">
         <v>37903</v>
       </c>
-      <c r="P6">
+      <c r="Q6">
         <v>71989</v>
       </c>
-      <c r="Q6">
+      <c r="R6" s="2">
         <v>17830</v>
       </c>
-      <c r="R6">
-        <v>0</v>
-      </c>
-      <c r="S6">
+      <c r="S6" s="2">
+        <v>0</v>
+      </c>
+      <c r="T6" s="2">
         <v>54</v>
       </c>
     </row>
-    <row r="7" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>4</v>
       </c>
       <c r="B7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C7">
         <v>39463</v>
@@ -988,17 +1006,17 @@
         <v>0</v>
       </c>
       <c r="E7">
+        <v>0</v>
+      </c>
+      <c r="F7">
         <v>39463</v>
       </c>
-      <c r="F7">
-        <v>0</v>
-      </c>
       <c r="G7">
+        <v>0</v>
+      </c>
+      <c r="H7">
         <v>39463</v>
       </c>
-      <c r="H7">
-        <v>0</v>
-      </c>
       <c r="I7">
         <v>0</v>
       </c>
@@ -1009,36 +1027,39 @@
         <v>0</v>
       </c>
       <c r="L7">
+        <v>0</v>
+      </c>
+      <c r="M7">
         <v>5733</v>
       </c>
-      <c r="M7">
+      <c r="N7">
         <v>257</v>
       </c>
-      <c r="N7">
+      <c r="O7">
         <v>1995</v>
       </c>
-      <c r="O7">
+      <c r="P7">
         <v>37468</v>
       </c>
-      <c r="P7">
+      <c r="Q7">
         <v>77581</v>
       </c>
-      <c r="Q7">
+      <c r="R7" s="2">
         <v>20511</v>
       </c>
-      <c r="R7">
-        <v>0</v>
-      </c>
-      <c r="S7">
+      <c r="S7" s="2">
+        <v>0</v>
+      </c>
+      <c r="T7" s="2">
         <v>8</v>
       </c>
     </row>
-    <row r="8" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>5</v>
       </c>
       <c r="B8" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C8">
         <v>40552</v>
@@ -1047,17 +1068,17 @@
         <v>0</v>
       </c>
       <c r="E8">
+        <v>5</v>
+      </c>
+      <c r="F8">
         <v>40552</v>
       </c>
-      <c r="F8">
-        <v>0</v>
-      </c>
       <c r="G8">
+        <v>0</v>
+      </c>
+      <c r="H8">
         <v>40552</v>
       </c>
-      <c r="H8">
-        <v>0</v>
-      </c>
       <c r="I8">
         <v>0</v>
       </c>
@@ -1068,36 +1089,39 @@
         <v>0</v>
       </c>
       <c r="L8">
+        <v>0</v>
+      </c>
+      <c r="M8">
         <v>14714</v>
       </c>
-      <c r="M8">
+      <c r="N8">
         <v>164</v>
       </c>
-      <c r="N8">
+      <c r="O8">
         <v>1981</v>
       </c>
-      <c r="O8">
+      <c r="P8">
         <v>38571</v>
       </c>
-      <c r="P8">
+      <c r="Q8">
         <v>73458</v>
       </c>
-      <c r="Q8">
+      <c r="R8" s="2">
         <v>20788</v>
       </c>
-      <c r="R8">
-        <v>0</v>
-      </c>
-      <c r="S8">
+      <c r="S8" s="2">
+        <v>0</v>
+      </c>
+      <c r="T8" s="2">
         <v>110</v>
       </c>
     </row>
-    <row r="9" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>6</v>
       </c>
       <c r="B9" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C9">
         <v>43273</v>
@@ -1106,17 +1130,17 @@
         <v>0</v>
       </c>
       <c r="E9">
+        <v>0</v>
+      </c>
+      <c r="F9">
         <v>43273</v>
       </c>
-      <c r="F9">
-        <v>0</v>
-      </c>
       <c r="G9">
+        <v>0</v>
+      </c>
+      <c r="H9">
         <v>43273</v>
       </c>
-      <c r="H9">
-        <v>0</v>
-      </c>
       <c r="I9">
         <v>0</v>
       </c>
@@ -1127,36 +1151,39 @@
         <v>0</v>
       </c>
       <c r="L9">
+        <v>0</v>
+      </c>
+      <c r="M9">
         <v>7759</v>
       </c>
-      <c r="M9">
+      <c r="N9">
         <v>49</v>
       </c>
-      <c r="N9">
+      <c r="O9">
         <v>1350</v>
       </c>
-      <c r="O9">
+      <c r="P9">
         <v>41924</v>
       </c>
-      <c r="P9">
+      <c r="Q9">
         <v>72913</v>
       </c>
-      <c r="Q9">
+      <c r="R9" s="2">
         <v>18141</v>
       </c>
-      <c r="R9">
-        <v>0</v>
-      </c>
-      <c r="S9">
+      <c r="S9" s="2">
+        <v>0</v>
+      </c>
+      <c r="T9" s="2">
         <v>110</v>
       </c>
     </row>
-    <row r="10" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>7</v>
       </c>
       <c r="B10" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C10">
         <v>36576</v>
@@ -1165,17 +1192,17 @@
         <v>0</v>
       </c>
       <c r="E10">
+        <v>0</v>
+      </c>
+      <c r="F10">
         <v>36576</v>
       </c>
-      <c r="F10">
-        <v>0</v>
-      </c>
       <c r="G10">
+        <v>0</v>
+      </c>
+      <c r="H10">
         <v>36576</v>
       </c>
-      <c r="H10">
-        <v>0</v>
-      </c>
       <c r="I10">
         <v>0</v>
       </c>
@@ -1186,36 +1213,39 @@
         <v>0</v>
       </c>
       <c r="L10">
+        <v>0</v>
+      </c>
+      <c r="M10">
         <v>10960</v>
       </c>
-      <c r="M10">
+      <c r="N10">
         <v>172</v>
       </c>
-      <c r="N10">
+      <c r="O10">
         <v>815</v>
       </c>
-      <c r="O10">
+      <c r="P10">
         <v>35761</v>
       </c>
-      <c r="P10">
+      <c r="Q10">
         <v>53124</v>
       </c>
-      <c r="Q10">
+      <c r="R10" s="2">
         <v>9498</v>
       </c>
-      <c r="R10">
-        <v>0</v>
-      </c>
-      <c r="S10">
+      <c r="S10" s="2">
+        <v>0</v>
+      </c>
+      <c r="T10" s="2">
         <v>2</v>
       </c>
     </row>
-    <row r="11" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>8</v>
       </c>
       <c r="B11" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C11">
         <v>50998</v>
@@ -1224,17 +1254,17 @@
         <v>0</v>
       </c>
       <c r="E11">
+        <v>0</v>
+      </c>
+      <c r="F11">
         <v>50998</v>
       </c>
-      <c r="F11">
-        <v>0</v>
-      </c>
       <c r="G11">
+        <v>0</v>
+      </c>
+      <c r="H11">
         <v>50998</v>
       </c>
-      <c r="H11">
-        <v>0</v>
-      </c>
       <c r="I11">
         <v>0</v>
       </c>
@@ -1245,36 +1275,39 @@
         <v>0</v>
       </c>
       <c r="L11">
+        <v>0</v>
+      </c>
+      <c r="M11">
         <v>9958</v>
       </c>
-      <c r="M11">
+      <c r="N11">
         <v>253</v>
       </c>
-      <c r="N11">
+      <c r="O11">
         <v>1703</v>
       </c>
-      <c r="O11">
+      <c r="P11">
         <v>49300</v>
       </c>
-      <c r="P11">
+      <c r="Q11">
         <v>84438</v>
       </c>
-      <c r="Q11">
+      <c r="R11" s="2">
         <v>23477</v>
       </c>
-      <c r="R11">
-        <v>0</v>
-      </c>
-      <c r="S11">
+      <c r="S11" s="2">
+        <v>0</v>
+      </c>
+      <c r="T11" s="2">
         <v>23</v>
       </c>
     </row>
-    <row r="12" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>9</v>
       </c>
       <c r="B12" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C12">
         <v>40739</v>
@@ -1283,17 +1316,17 @@
         <v>0</v>
       </c>
       <c r="E12">
+        <v>0</v>
+      </c>
+      <c r="F12">
         <v>40739</v>
       </c>
-      <c r="F12">
-        <v>0</v>
-      </c>
       <c r="G12">
+        <v>0</v>
+      </c>
+      <c r="H12">
         <v>40739</v>
       </c>
-      <c r="H12">
-        <v>0</v>
-      </c>
       <c r="I12">
         <v>0</v>
       </c>
@@ -1304,36 +1337,39 @@
         <v>0</v>
       </c>
       <c r="L12">
+        <v>0</v>
+      </c>
+      <c r="M12">
         <v>10054</v>
       </c>
-      <c r="M12">
+      <c r="N12">
         <v>207</v>
       </c>
-      <c r="N12">
+      <c r="O12">
         <v>1151</v>
       </c>
-      <c r="O12">
+      <c r="P12">
         <v>39588</v>
       </c>
-      <c r="P12">
+      <c r="Q12">
         <v>66685</v>
       </c>
-      <c r="Q12">
+      <c r="R12" s="2">
         <v>17786</v>
       </c>
-      <c r="R12">
-        <v>0</v>
-      </c>
-      <c r="S12">
+      <c r="S12" s="2">
+        <v>0</v>
+      </c>
+      <c r="T12" s="2">
         <v>3</v>
       </c>
     </row>
-    <row r="13" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>10</v>
       </c>
       <c r="B13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C13">
         <v>37031</v>
@@ -1342,17 +1378,17 @@
         <v>0</v>
       </c>
       <c r="E13">
+        <v>0</v>
+      </c>
+      <c r="F13">
         <v>37031</v>
       </c>
-      <c r="F13">
-        <v>0</v>
-      </c>
       <c r="G13">
+        <v>0</v>
+      </c>
+      <c r="H13">
         <v>37031</v>
       </c>
-      <c r="H13">
-        <v>0</v>
-      </c>
       <c r="I13">
         <v>0</v>
       </c>
@@ -1363,36 +1399,39 @@
         <v>0</v>
       </c>
       <c r="L13">
+        <v>0</v>
+      </c>
+      <c r="M13">
         <v>7864</v>
       </c>
-      <c r="M13">
+      <c r="N13">
         <v>258</v>
       </c>
-      <c r="N13">
+      <c r="O13">
         <v>3822</v>
       </c>
-      <c r="O13">
+      <c r="P13">
         <v>33237</v>
       </c>
-      <c r="P13">
+      <c r="Q13">
         <v>56564</v>
       </c>
-      <c r="Q13">
+      <c r="R13" s="2">
         <v>16237</v>
       </c>
-      <c r="R13">
-        <v>0</v>
-      </c>
-      <c r="S13">
+      <c r="S13" s="2">
+        <v>0</v>
+      </c>
+      <c r="T13" s="2">
         <v>106</v>
       </c>
     </row>
-    <row r="14" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>11</v>
       </c>
       <c r="B14" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C14">
         <v>48966</v>
@@ -1401,17 +1440,17 @@
         <v>0</v>
       </c>
       <c r="E14">
+        <v>0</v>
+      </c>
+      <c r="F14">
         <v>48966</v>
       </c>
-      <c r="F14">
-        <v>0</v>
-      </c>
       <c r="G14">
+        <v>0</v>
+      </c>
+      <c r="H14">
         <v>48966</v>
       </c>
-      <c r="H14">
-        <v>0</v>
-      </c>
       <c r="I14">
         <v>0</v>
       </c>
@@ -1422,36 +1461,39 @@
         <v>0</v>
       </c>
       <c r="L14">
+        <v>0</v>
+      </c>
+      <c r="M14">
         <v>15267</v>
       </c>
-      <c r="M14">
+      <c r="N14">
         <v>1456</v>
       </c>
-      <c r="N14">
+      <c r="O14">
         <v>5867</v>
       </c>
-      <c r="O14">
+      <c r="P14">
         <v>43099</v>
       </c>
-      <c r="P14">
+      <c r="Q14">
         <v>77955</v>
       </c>
-      <c r="Q14">
+      <c r="R14" s="2">
         <v>19716</v>
       </c>
-      <c r="R14">
-        <v>0</v>
-      </c>
-      <c r="S14">
+      <c r="S14" s="2">
+        <v>0</v>
+      </c>
+      <c r="T14" s="2">
         <v>174</v>
       </c>
     </row>
-    <row r="15" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>12</v>
       </c>
       <c r="B15" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C15">
         <v>42703</v>
@@ -1460,17 +1502,17 @@
         <v>0</v>
       </c>
       <c r="E15">
+        <v>0</v>
+      </c>
+      <c r="F15">
         <v>42703</v>
       </c>
-      <c r="F15">
-        <v>0</v>
-      </c>
       <c r="G15">
+        <v>0</v>
+      </c>
+      <c r="H15">
         <v>42703</v>
       </c>
-      <c r="H15">
-        <v>0</v>
-      </c>
       <c r="I15">
         <v>0</v>
       </c>
@@ -1481,36 +1523,39 @@
         <v>0</v>
       </c>
       <c r="L15">
+        <v>0</v>
+      </c>
+      <c r="M15">
         <v>9192</v>
       </c>
-      <c r="M15">
-        <v>0</v>
-      </c>
       <c r="N15">
+        <v>0</v>
+      </c>
+      <c r="O15">
         <v>2821</v>
       </c>
-      <c r="O15">
+      <c r="P15">
         <v>39882</v>
       </c>
-      <c r="P15">
+      <c r="Q15">
         <v>67183</v>
       </c>
-      <c r="Q15">
+      <c r="R15" s="2">
         <v>4859</v>
       </c>
-      <c r="R15">
-        <v>0</v>
-      </c>
-      <c r="S15">
+      <c r="S15" s="2">
+        <v>0</v>
+      </c>
+      <c r="T15" s="2">
         <v>50</v>
       </c>
     </row>
-    <row r="16" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>13</v>
       </c>
       <c r="B16" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C16">
         <v>25549</v>
@@ -1519,17 +1564,17 @@
         <v>0</v>
       </c>
       <c r="E16">
+        <v>0</v>
+      </c>
+      <c r="F16">
         <v>25549</v>
       </c>
-      <c r="F16">
-        <v>0</v>
-      </c>
       <c r="G16">
+        <v>0</v>
+      </c>
+      <c r="H16">
         <v>25547</v>
       </c>
-      <c r="H16">
-        <v>0</v>
-      </c>
       <c r="I16">
         <v>0</v>
       </c>
@@ -1540,36 +1585,39 @@
         <v>0</v>
       </c>
       <c r="L16">
+        <v>0</v>
+      </c>
+      <c r="M16">
         <v>14861</v>
       </c>
-      <c r="M16">
+      <c r="N16">
         <v>1</v>
       </c>
-      <c r="N16">
+      <c r="O16">
         <v>261</v>
       </c>
-      <c r="O16">
+      <c r="P16">
         <v>25289</v>
       </c>
-      <c r="P16">
+      <c r="Q16">
         <v>71673</v>
       </c>
-      <c r="Q16">
+      <c r="R16" s="2">
         <v>5197</v>
       </c>
-      <c r="R16">
-        <v>0</v>
-      </c>
-      <c r="S16">
+      <c r="S16" s="2">
+        <v>0</v>
+      </c>
+      <c r="T16" s="2">
         <v>47</v>
       </c>
     </row>
-    <row r="17" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>14</v>
       </c>
       <c r="B17" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C17">
         <v>27707</v>
@@ -1578,17 +1626,17 @@
         <v>0</v>
       </c>
       <c r="E17">
+        <v>0</v>
+      </c>
+      <c r="F17">
         <v>27707</v>
       </c>
-      <c r="F17">
-        <v>0</v>
-      </c>
       <c r="G17">
+        <v>0</v>
+      </c>
+      <c r="H17">
         <v>27707</v>
       </c>
-      <c r="H17">
-        <v>0</v>
-      </c>
       <c r="I17">
         <v>0</v>
       </c>
@@ -1599,36 +1647,39 @@
         <v>0</v>
       </c>
       <c r="L17">
+        <v>0</v>
+      </c>
+      <c r="M17">
         <v>9287</v>
       </c>
-      <c r="M17">
+      <c r="N17">
         <v>2</v>
       </c>
-      <c r="N17">
+      <c r="O17">
         <v>426</v>
       </c>
-      <c r="O17">
+      <c r="P17">
         <v>27282</v>
       </c>
-      <c r="P17">
+      <c r="Q17">
         <v>65457</v>
       </c>
-      <c r="Q17">
+      <c r="R17" s="2">
         <v>5417</v>
       </c>
-      <c r="R17">
-        <v>0</v>
-      </c>
-      <c r="S17">
+      <c r="S17" s="2">
+        <v>0</v>
+      </c>
+      <c r="T17" s="2">
         <v>105</v>
       </c>
     </row>
-    <row r="18" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>15</v>
       </c>
       <c r="B18" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C18">
         <v>47836</v>
@@ -1637,17 +1688,17 @@
         <v>0</v>
       </c>
       <c r="E18">
+        <v>0</v>
+      </c>
+      <c r="F18">
         <v>47836</v>
       </c>
-      <c r="F18">
-        <v>0</v>
-      </c>
       <c r="G18">
+        <v>0</v>
+      </c>
+      <c r="H18">
         <v>47836</v>
       </c>
-      <c r="H18">
-        <v>0</v>
-      </c>
       <c r="I18">
         <v>0</v>
       </c>
@@ -1658,36 +1709,39 @@
         <v>0</v>
       </c>
       <c r="L18">
+        <v>0</v>
+      </c>
+      <c r="M18">
         <v>7876</v>
       </c>
-      <c r="M18">
+      <c r="N18">
         <v>3</v>
       </c>
-      <c r="N18">
+      <c r="O18">
         <v>1970</v>
       </c>
-      <c r="O18">
+      <c r="P18">
         <v>45866</v>
       </c>
-      <c r="P18">
+      <c r="Q18">
         <v>71496</v>
       </c>
-      <c r="Q18">
+      <c r="R18" s="2">
         <v>6819</v>
       </c>
-      <c r="R18">
-        <v>0</v>
-      </c>
-      <c r="S18">
+      <c r="S18" s="2">
+        <v>0</v>
+      </c>
+      <c r="T18" s="2">
         <v>32</v>
       </c>
     </row>
-    <row r="19" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>16</v>
       </c>
       <c r="B19" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C19">
         <v>56490</v>
@@ -1696,17 +1750,17 @@
         <v>0</v>
       </c>
       <c r="E19">
+        <v>0</v>
+      </c>
+      <c r="F19">
         <v>56490</v>
       </c>
-      <c r="F19">
-        <v>0</v>
-      </c>
       <c r="G19">
+        <v>0</v>
+      </c>
+      <c r="H19">
         <v>56490</v>
       </c>
-      <c r="H19">
-        <v>0</v>
-      </c>
       <c r="I19">
         <v>0</v>
       </c>
@@ -1717,36 +1771,39 @@
         <v>0</v>
       </c>
       <c r="L19">
+        <v>0</v>
+      </c>
+      <c r="M19">
         <v>15286</v>
       </c>
-      <c r="M19">
+      <c r="N19">
         <v>1</v>
       </c>
-      <c r="N19">
+      <c r="O19">
         <v>912</v>
       </c>
-      <c r="O19">
+      <c r="P19">
         <v>55578</v>
       </c>
-      <c r="P19">
+      <c r="Q19">
         <v>106392</v>
       </c>
-      <c r="Q19">
+      <c r="R19" s="2">
         <v>6135</v>
       </c>
-      <c r="R19">
-        <v>0</v>
-      </c>
-      <c r="S19">
+      <c r="S19" s="2">
+        <v>0</v>
+      </c>
+      <c r="T19" s="2">
         <v>36</v>
       </c>
     </row>
-    <row r="20" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>17</v>
       </c>
       <c r="B20" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C20">
         <v>35022</v>
@@ -1755,17 +1812,17 @@
         <v>0</v>
       </c>
       <c r="E20">
+        <v>0</v>
+      </c>
+      <c r="F20">
         <v>35022</v>
       </c>
-      <c r="F20">
-        <v>0</v>
-      </c>
       <c r="G20">
+        <v>0</v>
+      </c>
+      <c r="H20">
         <v>35022</v>
       </c>
-      <c r="H20">
-        <v>0</v>
-      </c>
       <c r="I20">
         <v>0</v>
       </c>
@@ -1776,36 +1833,39 @@
         <v>0</v>
       </c>
       <c r="L20">
+        <v>0</v>
+      </c>
+      <c r="M20">
         <v>6093</v>
       </c>
-      <c r="M20">
+      <c r="N20">
         <v>5</v>
       </c>
-      <c r="N20">
+      <c r="O20">
         <v>546</v>
       </c>
-      <c r="O20">
+      <c r="P20">
         <v>34477</v>
       </c>
-      <c r="P20">
+      <c r="Q20">
         <v>75814</v>
       </c>
-      <c r="Q20">
+      <c r="R20" s="2">
         <v>8984</v>
       </c>
-      <c r="R20">
-        <v>0</v>
-      </c>
-      <c r="S20">
+      <c r="S20" s="2">
+        <v>0</v>
+      </c>
+      <c r="T20" s="2">
         <v>71</v>
       </c>
     </row>
-    <row r="21" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>18</v>
       </c>
       <c r="B21" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C21">
         <v>16962</v>
@@ -1814,17 +1874,17 @@
         <v>0</v>
       </c>
       <c r="E21">
+        <v>0</v>
+      </c>
+      <c r="F21">
         <v>16962</v>
       </c>
-      <c r="F21">
-        <v>0</v>
-      </c>
       <c r="G21">
+        <v>0</v>
+      </c>
+      <c r="H21">
         <v>16962</v>
       </c>
-      <c r="H21">
-        <v>0</v>
-      </c>
       <c r="I21">
         <v>0</v>
       </c>
@@ -1835,36 +1895,39 @@
         <v>0</v>
       </c>
       <c r="L21">
+        <v>0</v>
+      </c>
+      <c r="M21">
         <v>4030</v>
       </c>
-      <c r="M21">
+      <c r="N21">
         <v>3</v>
       </c>
-      <c r="N21">
+      <c r="O21">
         <v>171</v>
       </c>
-      <c r="O21">
+      <c r="P21">
         <v>16791</v>
       </c>
-      <c r="P21">
+      <c r="Q21">
         <v>62460</v>
       </c>
-      <c r="Q21">
+      <c r="R21" s="2">
         <v>3868</v>
       </c>
-      <c r="R21">
-        <v>0</v>
-      </c>
-      <c r="S21">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="S21" s="2">
+        <v>0</v>
+      </c>
+      <c r="T21" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>19</v>
       </c>
       <c r="B22" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C22">
         <v>18668</v>
@@ -1873,17 +1936,17 @@
         <v>0</v>
       </c>
       <c r="E22">
+        <v>0</v>
+      </c>
+      <c r="F22">
         <v>18668</v>
       </c>
-      <c r="F22">
-        <v>0</v>
-      </c>
       <c r="G22">
+        <v>0</v>
+      </c>
+      <c r="H22">
         <v>18668</v>
       </c>
-      <c r="H22">
-        <v>0</v>
-      </c>
       <c r="I22">
         <v>0</v>
       </c>
@@ -1894,36 +1957,39 @@
         <v>0</v>
       </c>
       <c r="L22">
+        <v>0</v>
+      </c>
+      <c r="M22">
         <v>7665</v>
       </c>
-      <c r="M22">
-        <v>0</v>
-      </c>
       <c r="N22">
+        <v>0</v>
+      </c>
+      <c r="O22">
         <v>302</v>
       </c>
-      <c r="O22">
+      <c r="P22">
         <v>18366</v>
       </c>
-      <c r="P22">
+      <c r="Q22">
         <v>64099</v>
       </c>
-      <c r="Q22">
+      <c r="R22" s="2">
         <v>4848</v>
       </c>
-      <c r="R22">
-        <v>0</v>
-      </c>
-      <c r="S22">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="S22" s="2">
+        <v>0</v>
+      </c>
+      <c r="T22" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>20</v>
       </c>
       <c r="B23" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C23">
         <v>12020</v>
@@ -1932,17 +1998,17 @@
         <v>0</v>
       </c>
       <c r="E23">
+        <v>0</v>
+      </c>
+      <c r="F23">
         <v>12020</v>
       </c>
-      <c r="F23">
-        <v>0</v>
-      </c>
       <c r="G23">
+        <v>0</v>
+      </c>
+      <c r="H23">
         <v>12020</v>
       </c>
-      <c r="H23">
-        <v>0</v>
-      </c>
       <c r="I23">
         <v>0</v>
       </c>
@@ -1953,36 +2019,39 @@
         <v>0</v>
       </c>
       <c r="L23">
+        <v>0</v>
+      </c>
+      <c r="M23">
         <v>2113</v>
       </c>
-      <c r="M23">
-        <v>0</v>
-      </c>
       <c r="N23">
+        <v>0</v>
+      </c>
+      <c r="O23">
         <v>108</v>
       </c>
-      <c r="O23">
+      <c r="P23">
         <v>11912</v>
       </c>
-      <c r="P23">
+      <c r="Q23">
         <v>57094</v>
       </c>
-      <c r="Q23">
+      <c r="R23" s="2">
         <v>3541</v>
       </c>
-      <c r="R23">
-        <v>0</v>
-      </c>
-      <c r="S23">
+      <c r="S23" s="2">
+        <v>0</v>
+      </c>
+      <c r="T23" s="2">
         <v>28</v>
       </c>
     </row>
-    <row r="24" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>21</v>
       </c>
       <c r="B24" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C24">
         <v>14056</v>
@@ -1991,17 +2060,17 @@
         <v>0</v>
       </c>
       <c r="E24">
+        <v>0</v>
+      </c>
+      <c r="F24">
         <v>14056</v>
       </c>
-      <c r="F24">
-        <v>0</v>
-      </c>
       <c r="G24">
+        <v>0</v>
+      </c>
+      <c r="H24">
         <v>14056</v>
       </c>
-      <c r="H24">
-        <v>0</v>
-      </c>
       <c r="I24">
         <v>0</v>
       </c>
@@ -2012,36 +2081,39 @@
         <v>0</v>
       </c>
       <c r="L24">
+        <v>0</v>
+      </c>
+      <c r="M24">
         <v>3482</v>
       </c>
-      <c r="M24">
+      <c r="N24">
         <v>5</v>
       </c>
-      <c r="N24">
+      <c r="O24">
         <v>231</v>
       </c>
-      <c r="O24">
+      <c r="P24">
         <v>13825</v>
       </c>
-      <c r="P24">
+      <c r="Q24">
         <v>65629</v>
       </c>
-      <c r="Q24">
+      <c r="R24" s="2">
         <v>3492</v>
       </c>
-      <c r="R24">
-        <v>0</v>
-      </c>
-      <c r="S24">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="S24" s="2">
+        <v>0</v>
+      </c>
+      <c r="T24" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>22</v>
       </c>
       <c r="B25" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C25">
         <v>19266</v>
@@ -2050,17 +2122,17 @@
         <v>0</v>
       </c>
       <c r="E25">
+        <v>0</v>
+      </c>
+      <c r="F25">
         <v>19266</v>
       </c>
-      <c r="F25">
-        <v>0</v>
-      </c>
       <c r="G25">
+        <v>0</v>
+      </c>
+      <c r="H25">
         <v>19266</v>
       </c>
-      <c r="H25">
-        <v>0</v>
-      </c>
       <c r="I25">
         <v>0</v>
       </c>
@@ -2071,36 +2143,39 @@
         <v>0</v>
       </c>
       <c r="L25">
+        <v>0</v>
+      </c>
+      <c r="M25">
         <v>4862</v>
       </c>
-      <c r="M25">
-        <v>0</v>
-      </c>
       <c r="N25">
+        <v>0</v>
+      </c>
+      <c r="O25">
         <v>298</v>
       </c>
-      <c r="O25">
+      <c r="P25">
         <v>18968</v>
       </c>
-      <c r="P25">
+      <c r="Q25">
         <v>57533</v>
       </c>
-      <c r="Q25">
+      <c r="R25" s="2">
         <v>3231</v>
       </c>
-      <c r="R25">
-        <v>0</v>
-      </c>
-      <c r="S25">
+      <c r="S25" s="2">
+        <v>0</v>
+      </c>
+      <c r="T25" s="2">
         <v>13</v>
       </c>
     </row>
-    <row r="26" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>23</v>
       </c>
       <c r="B26" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C26">
         <v>17557</v>
@@ -2109,17 +2184,17 @@
         <v>0</v>
       </c>
       <c r="E26">
+        <v>0</v>
+      </c>
+      <c r="F26">
         <v>17557</v>
       </c>
-      <c r="F26">
-        <v>0</v>
-      </c>
       <c r="G26">
+        <v>0</v>
+      </c>
+      <c r="H26">
         <v>17557</v>
       </c>
-      <c r="H26">
-        <v>0</v>
-      </c>
       <c r="I26">
         <v>0</v>
       </c>
@@ -2130,36 +2205,39 @@
         <v>0</v>
       </c>
       <c r="L26">
+        <v>0</v>
+      </c>
+      <c r="M26">
         <v>3741</v>
       </c>
-      <c r="M26">
+      <c r="N26">
         <v>3</v>
       </c>
-      <c r="N26">
+      <c r="O26">
         <v>194</v>
       </c>
-      <c r="O26">
+      <c r="P26">
         <v>17363</v>
       </c>
-      <c r="P26">
+      <c r="Q26">
         <v>66594</v>
       </c>
-      <c r="Q26">
+      <c r="R26" s="2">
         <v>3333</v>
       </c>
-      <c r="R26">
-        <v>0</v>
-      </c>
-      <c r="S26">
+      <c r="S26" s="2">
+        <v>0</v>
+      </c>
+      <c r="T26" s="2">
         <v>2</v>
       </c>
     </row>
-    <row r="27" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>24</v>
       </c>
       <c r="B27" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C27">
         <v>44276</v>
@@ -2168,17 +2246,17 @@
         <v>0</v>
       </c>
       <c r="E27">
+        <v>0</v>
+      </c>
+      <c r="F27">
         <v>44276</v>
       </c>
-      <c r="F27">
-        <v>0</v>
-      </c>
       <c r="G27">
+        <v>0</v>
+      </c>
+      <c r="H27">
         <v>44276</v>
       </c>
-      <c r="H27">
-        <v>0</v>
-      </c>
       <c r="I27">
         <v>0</v>
       </c>
@@ -2189,36 +2267,39 @@
         <v>0</v>
       </c>
       <c r="L27">
+        <v>0</v>
+      </c>
+      <c r="M27">
         <v>9679</v>
       </c>
-      <c r="M27">
+      <c r="N27">
         <v>215</v>
       </c>
-      <c r="N27">
+      <c r="O27">
         <v>3287</v>
       </c>
-      <c r="O27">
+      <c r="P27">
         <v>41005</v>
       </c>
-      <c r="P27">
+      <c r="Q27">
         <v>73109</v>
       </c>
-      <c r="Q27">
+      <c r="R27" s="2">
         <v>12669</v>
       </c>
-      <c r="R27">
-        <v>0</v>
-      </c>
-      <c r="S27">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="S27" s="2">
+        <v>0</v>
+      </c>
+      <c r="T27" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>25</v>
       </c>
       <c r="B28" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C28">
         <v>54349</v>
@@ -2227,17 +2308,17 @@
         <v>0</v>
       </c>
       <c r="E28">
+        <v>0</v>
+      </c>
+      <c r="F28">
         <v>54349</v>
       </c>
-      <c r="F28">
-        <v>0</v>
-      </c>
       <c r="G28">
+        <v>0</v>
+      </c>
+      <c r="H28">
         <v>54349</v>
       </c>
-      <c r="H28">
-        <v>0</v>
-      </c>
       <c r="I28">
         <v>0</v>
       </c>
@@ -2248,36 +2329,39 @@
         <v>0</v>
       </c>
       <c r="L28">
+        <v>0</v>
+      </c>
+      <c r="M28">
         <v>8879</v>
       </c>
-      <c r="M28">
+      <c r="N28">
         <v>856</v>
       </c>
-      <c r="N28">
+      <c r="O28">
         <v>3525</v>
       </c>
-      <c r="O28">
+      <c r="P28">
         <v>50844</v>
       </c>
-      <c r="P28">
+      <c r="Q28">
         <v>80620</v>
       </c>
-      <c r="Q28">
+      <c r="R28" s="2">
         <v>13995</v>
       </c>
-      <c r="R28">
-        <v>0</v>
-      </c>
-      <c r="S28">
+      <c r="S28" s="2">
+        <v>0</v>
+      </c>
+      <c r="T28" s="2">
         <v>127</v>
       </c>
     </row>
-    <row r="29" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>26</v>
       </c>
       <c r="B29" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C29">
         <v>47111</v>
@@ -2286,17 +2370,17 @@
         <v>0</v>
       </c>
       <c r="E29">
+        <v>0</v>
+      </c>
+      <c r="F29">
         <v>47111</v>
       </c>
-      <c r="F29">
-        <v>0</v>
-      </c>
       <c r="G29">
+        <v>0</v>
+      </c>
+      <c r="H29">
         <v>47111</v>
       </c>
-      <c r="H29">
-        <v>0</v>
-      </c>
       <c r="I29">
         <v>0</v>
       </c>
@@ -2307,36 +2391,39 @@
         <v>0</v>
       </c>
       <c r="L29">
+        <v>0</v>
+      </c>
+      <c r="M29">
         <v>8816</v>
       </c>
-      <c r="M29">
+      <c r="N29">
         <v>318</v>
       </c>
-      <c r="N29">
+      <c r="O29">
         <v>4592</v>
       </c>
-      <c r="O29">
+      <c r="P29">
         <v>42520</v>
       </c>
-      <c r="P29">
+      <c r="Q29">
         <v>83836</v>
       </c>
-      <c r="Q29">
+      <c r="R29" s="2">
         <v>14229</v>
       </c>
-      <c r="R29">
-        <v>0</v>
-      </c>
-      <c r="S29">
+      <c r="S29" s="2">
+        <v>0</v>
+      </c>
+      <c r="T29" s="2">
         <v>22</v>
       </c>
     </row>
-    <row r="30" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>27</v>
       </c>
       <c r="B30" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C30">
         <v>52653</v>
@@ -2345,17 +2432,17 @@
         <v>0</v>
       </c>
       <c r="E30">
+        <v>0</v>
+      </c>
+      <c r="F30">
         <v>52653</v>
       </c>
-      <c r="F30">
-        <v>0</v>
-      </c>
       <c r="G30">
+        <v>0</v>
+      </c>
+      <c r="H30">
         <v>52653</v>
       </c>
-      <c r="H30">
-        <v>0</v>
-      </c>
       <c r="I30">
         <v>0</v>
       </c>
@@ -2366,36 +2453,39 @@
         <v>0</v>
       </c>
       <c r="L30">
+        <v>0</v>
+      </c>
+      <c r="M30">
         <v>11659</v>
       </c>
-      <c r="M30">
+      <c r="N30">
         <v>411</v>
       </c>
-      <c r="N30">
+      <c r="O30">
         <v>5383</v>
       </c>
-      <c r="O30">
+      <c r="P30">
         <v>47272</v>
       </c>
-      <c r="P30">
+      <c r="Q30">
         <v>86933</v>
       </c>
-      <c r="Q30">
+      <c r="R30" s="2">
         <v>12564</v>
       </c>
-      <c r="R30">
-        <v>0</v>
-      </c>
-      <c r="S30">
+      <c r="S30" s="2">
+        <v>0</v>
+      </c>
+      <c r="T30" s="2">
         <v>8</v>
       </c>
     </row>
-    <row r="31" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>28</v>
       </c>
       <c r="B31" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C31">
         <v>91162</v>
@@ -2404,17 +2494,17 @@
         <v>0</v>
       </c>
       <c r="E31">
+        <v>0</v>
+      </c>
+      <c r="F31">
         <v>91162</v>
       </c>
-      <c r="F31">
-        <v>0</v>
-      </c>
       <c r="G31">
+        <v>0</v>
+      </c>
+      <c r="H31">
         <v>91162</v>
       </c>
-      <c r="H31">
-        <v>0</v>
-      </c>
       <c r="I31">
         <v>0</v>
       </c>
@@ -2425,36 +2515,39 @@
         <v>0</v>
       </c>
       <c r="L31">
+        <v>0</v>
+      </c>
+      <c r="M31">
         <v>46718</v>
       </c>
-      <c r="M31">
+      <c r="N31">
         <v>42</v>
       </c>
-      <c r="N31">
+      <c r="O31">
         <v>1899</v>
       </c>
-      <c r="O31">
+      <c r="P31">
         <v>89264</v>
       </c>
-      <c r="P31">
+      <c r="Q31">
         <v>81642</v>
       </c>
-      <c r="Q31">
+      <c r="R31" s="2">
         <v>14581</v>
       </c>
-      <c r="R31">
-        <v>0</v>
-      </c>
-      <c r="S31">
+      <c r="S31" s="2">
+        <v>0</v>
+      </c>
+      <c r="T31" s="2">
         <v>39</v>
       </c>
     </row>
-    <row r="32" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>29</v>
       </c>
       <c r="B32" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C32">
         <v>46728</v>
@@ -2463,17 +2556,17 @@
         <v>0</v>
       </c>
       <c r="E32">
+        <v>0</v>
+      </c>
+      <c r="F32">
         <v>46728</v>
       </c>
-      <c r="F32">
-        <v>0</v>
-      </c>
       <c r="G32">
+        <v>0</v>
+      </c>
+      <c r="H32">
         <v>46728</v>
       </c>
-      <c r="H32">
-        <v>0</v>
-      </c>
       <c r="I32">
         <v>0</v>
       </c>
@@ -2484,36 +2577,39 @@
         <v>0</v>
       </c>
       <c r="L32">
+        <v>0</v>
+      </c>
+      <c r="M32">
         <v>10557</v>
       </c>
-      <c r="M32">
+      <c r="N32">
         <v>316</v>
       </c>
-      <c r="N32">
+      <c r="O32">
         <v>4391</v>
       </c>
-      <c r="O32">
+      <c r="P32">
         <v>42344</v>
       </c>
-      <c r="P32">
+      <c r="Q32">
         <v>74810</v>
       </c>
-      <c r="Q32">
+      <c r="R32" s="2">
         <v>11379</v>
       </c>
-      <c r="R32">
-        <v>0</v>
-      </c>
-      <c r="S32">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="S32" s="2">
+        <v>0</v>
+      </c>
+      <c r="T32" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>30</v>
       </c>
       <c r="B33" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C33">
         <v>40230</v>
@@ -2522,17 +2618,17 @@
         <v>0</v>
       </c>
       <c r="E33">
+        <v>0</v>
+      </c>
+      <c r="F33">
         <v>40230</v>
       </c>
-      <c r="F33">
-        <v>0</v>
-      </c>
       <c r="G33">
+        <v>0</v>
+      </c>
+      <c r="H33">
         <v>40230</v>
       </c>
-      <c r="H33">
-        <v>0</v>
-      </c>
       <c r="I33">
         <v>0</v>
       </c>
@@ -2543,36 +2639,39 @@
         <v>0</v>
       </c>
       <c r="L33">
+        <v>0</v>
+      </c>
+      <c r="M33">
         <v>5113</v>
       </c>
-      <c r="M33">
+      <c r="N33">
         <v>311</v>
       </c>
-      <c r="N33">
+      <c r="O33">
         <v>1275</v>
       </c>
-      <c r="O33">
+      <c r="P33">
         <v>38955</v>
       </c>
-      <c r="P33">
+      <c r="Q33">
         <v>76969</v>
       </c>
-      <c r="Q33">
+      <c r="R33" s="2">
         <v>6678</v>
       </c>
-      <c r="R33">
-        <v>0</v>
-      </c>
-      <c r="S33">
+      <c r="S33" s="2">
+        <v>0</v>
+      </c>
+      <c r="T33" s="2">
         <v>19</v>
       </c>
     </row>
-    <row r="34" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>31</v>
       </c>
       <c r="B34" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C34">
         <v>36542</v>
@@ -2581,17 +2680,17 @@
         <v>0</v>
       </c>
       <c r="E34">
+        <v>0</v>
+      </c>
+      <c r="F34">
         <v>36542</v>
       </c>
-      <c r="F34">
-        <v>0</v>
-      </c>
       <c r="G34">
+        <v>0</v>
+      </c>
+      <c r="H34">
         <v>36542</v>
       </c>
-      <c r="H34">
-        <v>0</v>
-      </c>
       <c r="I34">
         <v>0</v>
       </c>
@@ -2602,36 +2701,39 @@
         <v>0</v>
       </c>
       <c r="L34">
+        <v>0</v>
+      </c>
+      <c r="M34">
         <v>12439</v>
       </c>
-      <c r="M34">
+      <c r="N34">
         <v>513</v>
       </c>
-      <c r="N34">
+      <c r="O34">
         <v>1363</v>
       </c>
-      <c r="O34">
+      <c r="P34">
         <v>35181</v>
       </c>
-      <c r="P34">
+      <c r="Q34">
         <v>74624</v>
       </c>
-      <c r="Q34">
+      <c r="R34" s="2">
         <v>7137</v>
       </c>
-      <c r="R34">
-        <v>0</v>
-      </c>
-      <c r="S34">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="S34" s="2">
+        <v>0</v>
+      </c>
+      <c r="T34" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>32</v>
       </c>
       <c r="B35" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C35">
         <v>33564</v>
@@ -2640,17 +2742,17 @@
         <v>0</v>
       </c>
       <c r="E35">
+        <v>0</v>
+      </c>
+      <c r="F35">
         <v>33564</v>
       </c>
-      <c r="F35">
-        <v>0</v>
-      </c>
       <c r="G35">
+        <v>0</v>
+      </c>
+      <c r="H35">
         <v>33564</v>
       </c>
-      <c r="H35">
-        <v>0</v>
-      </c>
       <c r="I35">
         <v>0</v>
       </c>
@@ -2661,36 +2763,39 @@
         <v>0</v>
       </c>
       <c r="L35">
+        <v>0</v>
+      </c>
+      <c r="M35">
         <v>7886</v>
       </c>
-      <c r="M35">
+      <c r="N35">
         <v>271</v>
       </c>
-      <c r="N35">
+      <c r="O35">
         <v>1141</v>
       </c>
-      <c r="O35">
+      <c r="P35">
         <v>32426</v>
       </c>
-      <c r="P35">
+      <c r="Q35">
         <v>76462</v>
       </c>
-      <c r="Q35">
+      <c r="R35" s="2">
         <v>8879</v>
       </c>
-      <c r="R35">
-        <v>0</v>
-      </c>
-      <c r="S35">
+      <c r="S35" s="2">
+        <v>0</v>
+      </c>
+      <c r="T35" s="2">
         <v>35</v>
       </c>
     </row>
-    <row r="36" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>33</v>
       </c>
       <c r="B36" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C36">
         <v>20905</v>
@@ -2699,17 +2804,17 @@
         <v>0</v>
       </c>
       <c r="E36">
+        <v>0</v>
+      </c>
+      <c r="F36">
         <v>20905</v>
       </c>
-      <c r="F36">
-        <v>0</v>
-      </c>
       <c r="G36">
+        <v>0</v>
+      </c>
+      <c r="H36">
         <v>20905</v>
       </c>
-      <c r="H36">
-        <v>0</v>
-      </c>
       <c r="I36">
         <v>0</v>
       </c>
@@ -2720,36 +2825,39 @@
         <v>0</v>
       </c>
       <c r="L36">
+        <v>0</v>
+      </c>
+      <c r="M36">
         <v>7350</v>
       </c>
-      <c r="M36">
-        <v>0</v>
-      </c>
       <c r="N36">
+        <v>0</v>
+      </c>
+      <c r="O36">
         <v>951</v>
       </c>
-      <c r="O36">
+      <c r="P36">
         <v>19954</v>
       </c>
-      <c r="P36">
+      <c r="Q36">
         <v>60419</v>
       </c>
-      <c r="Q36">
+      <c r="R36" s="2">
         <v>3855</v>
       </c>
-      <c r="R36">
-        <v>0</v>
-      </c>
-      <c r="S36">
+      <c r="S36" s="2">
+        <v>0</v>
+      </c>
+      <c r="T36" s="2">
         <v>2</v>
       </c>
     </row>
-    <row r="37" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>34</v>
       </c>
       <c r="B37" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C37">
         <v>17692</v>
@@ -2758,17 +2866,17 @@
         <v>0</v>
       </c>
       <c r="E37">
+        <v>0</v>
+      </c>
+      <c r="F37">
         <v>17692</v>
       </c>
-      <c r="F37">
-        <v>0</v>
-      </c>
       <c r="G37">
+        <v>0</v>
+      </c>
+      <c r="H37">
         <v>17692</v>
       </c>
-      <c r="H37">
-        <v>0</v>
-      </c>
       <c r="I37">
         <v>0</v>
       </c>
@@ -2779,36 +2887,39 @@
         <v>0</v>
       </c>
       <c r="L37">
+        <v>0</v>
+      </c>
+      <c r="M37">
         <v>2311</v>
       </c>
-      <c r="M37">
-        <v>0</v>
-      </c>
       <c r="N37">
+        <v>0</v>
+      </c>
+      <c r="O37">
         <v>541</v>
       </c>
-      <c r="O37">
+      <c r="P37">
         <v>17151</v>
       </c>
-      <c r="P37">
+      <c r="Q37">
         <v>57832</v>
       </c>
-      <c r="Q37">
+      <c r="R37" s="2">
         <v>4036</v>
       </c>
-      <c r="R37">
-        <v>0</v>
-      </c>
-      <c r="S37">
+      <c r="S37" s="2">
+        <v>0</v>
+      </c>
+      <c r="T37" s="2">
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>35</v>
       </c>
       <c r="B38" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C38">
         <v>29110</v>
@@ -2817,17 +2928,17 @@
         <v>0</v>
       </c>
       <c r="E38">
+        <v>1</v>
+      </c>
+      <c r="F38">
         <v>29110</v>
       </c>
-      <c r="F38">
-        <v>0</v>
-      </c>
       <c r="G38">
+        <v>0</v>
+      </c>
+      <c r="H38">
         <v>29110</v>
       </c>
-      <c r="H38">
-        <v>0</v>
-      </c>
       <c r="I38">
         <v>0</v>
       </c>
@@ -2838,36 +2949,39 @@
         <v>0</v>
       </c>
       <c r="L38">
+        <v>0</v>
+      </c>
+      <c r="M38">
         <v>5386</v>
       </c>
-      <c r="M38">
+      <c r="N38">
         <v>2</v>
       </c>
-      <c r="N38">
+      <c r="O38">
         <v>635</v>
       </c>
-      <c r="O38">
+      <c r="P38">
         <v>28475</v>
       </c>
-      <c r="P38">
+      <c r="Q38">
         <v>63038</v>
       </c>
-      <c r="Q38">
+      <c r="R38" s="2">
         <v>5135</v>
       </c>
-      <c r="R38">
-        <v>0</v>
-      </c>
-      <c r="S38">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="39" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="S38" s="2">
+        <v>0</v>
+      </c>
+      <c r="T38" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>36</v>
       </c>
       <c r="B39" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C39">
         <v>21367</v>
@@ -2876,17 +2990,17 @@
         <v>0</v>
       </c>
       <c r="E39">
+        <v>0</v>
+      </c>
+      <c r="F39">
         <v>21367</v>
       </c>
-      <c r="F39">
-        <v>0</v>
-      </c>
       <c r="G39">
+        <v>0</v>
+      </c>
+      <c r="H39">
         <v>21367</v>
       </c>
-      <c r="H39">
-        <v>0</v>
-      </c>
       <c r="I39">
         <v>0</v>
       </c>
@@ -2897,36 +3011,39 @@
         <v>0</v>
       </c>
       <c r="L39">
+        <v>0</v>
+      </c>
+      <c r="M39">
         <v>4529</v>
       </c>
-      <c r="M39">
+      <c r="N39">
         <v>1</v>
       </c>
-      <c r="N39">
+      <c r="O39">
         <v>234</v>
       </c>
-      <c r="O39">
+      <c r="P39">
         <v>21133</v>
       </c>
-      <c r="P39">
+      <c r="Q39">
         <v>71133</v>
       </c>
-      <c r="Q39">
+      <c r="R39" s="2">
         <v>5903</v>
       </c>
-      <c r="R39">
-        <v>0</v>
-      </c>
-      <c r="S39">
+      <c r="S39" s="2">
+        <v>0</v>
+      </c>
+      <c r="T39" s="2">
         <v>26</v>
       </c>
     </row>
-    <row r="40" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>37</v>
       </c>
       <c r="B40" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C40">
         <v>18905</v>
@@ -2935,17 +3052,17 @@
         <v>0</v>
       </c>
       <c r="E40">
+        <v>0</v>
+      </c>
+      <c r="F40">
         <v>18905</v>
       </c>
-      <c r="F40">
-        <v>0</v>
-      </c>
       <c r="G40">
+        <v>0</v>
+      </c>
+      <c r="H40">
         <v>18905</v>
       </c>
-      <c r="H40">
-        <v>0</v>
-      </c>
       <c r="I40">
         <v>0</v>
       </c>
@@ -2956,36 +3073,39 @@
         <v>0</v>
       </c>
       <c r="L40">
+        <v>0</v>
+      </c>
+      <c r="M40">
         <v>1812</v>
       </c>
-      <c r="M40">
-        <v>0</v>
-      </c>
       <c r="N40">
+        <v>0</v>
+      </c>
+      <c r="O40">
         <v>52</v>
       </c>
-      <c r="O40">
+      <c r="P40">
         <v>18853</v>
       </c>
-      <c r="P40">
+      <c r="Q40">
         <v>73242</v>
       </c>
-      <c r="Q40">
+      <c r="R40" s="2">
         <v>3824</v>
       </c>
-      <c r="R40">
-        <v>0</v>
-      </c>
-      <c r="S40">
+      <c r="S40" s="2">
+        <v>0</v>
+      </c>
+      <c r="T40" s="2">
         <v>61</v>
       </c>
     </row>
-    <row r="41" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>38</v>
       </c>
       <c r="B41" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C41">
         <v>23521</v>
@@ -2994,17 +3114,17 @@
         <v>0</v>
       </c>
       <c r="E41">
+        <v>0</v>
+      </c>
+      <c r="F41">
         <v>23521</v>
       </c>
-      <c r="F41">
-        <v>0</v>
-      </c>
       <c r="G41">
+        <v>0</v>
+      </c>
+      <c r="H41">
         <v>23521</v>
       </c>
-      <c r="H41">
-        <v>0</v>
-      </c>
       <c r="I41">
         <v>0</v>
       </c>
@@ -3015,36 +3135,39 @@
         <v>0</v>
       </c>
       <c r="L41">
+        <v>0</v>
+      </c>
+      <c r="M41">
         <v>1499</v>
       </c>
-      <c r="M41">
-        <v>0</v>
-      </c>
       <c r="N41">
+        <v>0</v>
+      </c>
+      <c r="O41">
         <v>92</v>
       </c>
-      <c r="O41">
+      <c r="P41">
         <v>23429</v>
       </c>
-      <c r="P41">
+      <c r="Q41">
         <v>85251</v>
       </c>
-      <c r="Q41">
+      <c r="R41" s="2">
         <v>6015</v>
       </c>
-      <c r="R41">
-        <v>0</v>
-      </c>
-      <c r="S41">
+      <c r="S41" s="2">
+        <v>0</v>
+      </c>
+      <c r="T41" s="2">
         <v>27</v>
       </c>
     </row>
-    <row r="42" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>39</v>
       </c>
       <c r="B42" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C42">
         <v>27565</v>
@@ -3053,17 +3176,17 @@
         <v>0</v>
       </c>
       <c r="E42">
+        <v>0</v>
+      </c>
+      <c r="F42">
         <v>27565</v>
       </c>
-      <c r="F42">
-        <v>0</v>
-      </c>
       <c r="G42">
+        <v>0</v>
+      </c>
+      <c r="H42">
         <v>27565</v>
       </c>
-      <c r="H42">
-        <v>0</v>
-      </c>
       <c r="I42">
         <v>0</v>
       </c>
@@ -3074,36 +3197,39 @@
         <v>0</v>
       </c>
       <c r="L42">
+        <v>0</v>
+      </c>
+      <c r="M42">
         <v>6264</v>
       </c>
-      <c r="M42">
-        <v>0</v>
-      </c>
       <c r="N42">
+        <v>0</v>
+      </c>
+      <c r="O42">
         <v>419</v>
       </c>
-      <c r="O42">
+      <c r="P42">
         <v>27147</v>
       </c>
-      <c r="P42">
+      <c r="Q42">
         <v>68615</v>
       </c>
-      <c r="Q42">
+      <c r="R42" s="2">
         <v>4708</v>
       </c>
-      <c r="R42">
-        <v>0</v>
-      </c>
-      <c r="S42">
+      <c r="S42" s="2">
+        <v>0</v>
+      </c>
+      <c r="T42" s="2">
         <v>8</v>
       </c>
     </row>
-    <row r="43" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>40</v>
       </c>
       <c r="B43" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C43">
         <v>29700</v>
@@ -3112,17 +3238,17 @@
         <v>0</v>
       </c>
       <c r="E43">
+        <v>0</v>
+      </c>
+      <c r="F43">
         <v>29700</v>
       </c>
-      <c r="F43">
-        <v>0</v>
-      </c>
       <c r="G43">
+        <v>0</v>
+      </c>
+      <c r="H43">
         <v>29700</v>
       </c>
-      <c r="H43">
-        <v>0</v>
-      </c>
       <c r="I43">
         <v>0</v>
       </c>
@@ -3133,36 +3259,39 @@
         <v>0</v>
       </c>
       <c r="L43">
+        <v>0</v>
+      </c>
+      <c r="M43">
         <v>6804</v>
       </c>
-      <c r="M43">
+      <c r="N43">
         <v>1</v>
       </c>
-      <c r="N43">
+      <c r="O43">
         <v>957</v>
       </c>
-      <c r="O43">
+      <c r="P43">
         <v>28774</v>
       </c>
-      <c r="P43">
+      <c r="Q43">
         <v>63012</v>
       </c>
-      <c r="Q43">
+      <c r="R43" s="2">
         <v>5219</v>
       </c>
-      <c r="R43">
-        <v>0</v>
-      </c>
-      <c r="S43">
+      <c r="S43" s="2">
+        <v>0</v>
+      </c>
+      <c r="T43" s="2">
         <v>121</v>
       </c>
     </row>
-    <row r="44" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A44">
         <v>41</v>
       </c>
       <c r="B44" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C44">
         <v>21900</v>
@@ -3171,17 +3300,17 @@
         <v>0</v>
       </c>
       <c r="E44">
+        <v>0</v>
+      </c>
+      <c r="F44">
         <v>21900</v>
       </c>
-      <c r="F44">
-        <v>0</v>
-      </c>
       <c r="G44">
+        <v>0</v>
+      </c>
+      <c r="H44">
         <v>21900</v>
       </c>
-      <c r="H44">
-        <v>0</v>
-      </c>
       <c r="I44">
         <v>0</v>
       </c>
@@ -3192,36 +3321,39 @@
         <v>0</v>
       </c>
       <c r="L44">
+        <v>0</v>
+      </c>
+      <c r="M44">
         <v>6643</v>
       </c>
-      <c r="M44">
+      <c r="N44">
         <v>24</v>
       </c>
-      <c r="N44">
+      <c r="O44">
         <v>347</v>
       </c>
-      <c r="O44">
+      <c r="P44">
         <v>21553</v>
       </c>
-      <c r="P44">
+      <c r="Q44">
         <v>68393</v>
       </c>
-      <c r="Q44">
+      <c r="R44" s="2">
         <v>7659</v>
       </c>
-      <c r="R44">
-        <v>0</v>
-      </c>
-      <c r="S44">
+      <c r="S44" s="2">
+        <v>0</v>
+      </c>
+      <c r="T44" s="2">
         <v>20</v>
       </c>
     </row>
-    <row r="45" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A45">
         <v>42</v>
       </c>
       <c r="B45" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C45">
         <v>19935</v>
@@ -3230,17 +3362,17 @@
         <v>0</v>
       </c>
       <c r="E45">
+        <v>0</v>
+      </c>
+      <c r="F45">
         <v>19935</v>
       </c>
-      <c r="F45">
-        <v>0</v>
-      </c>
       <c r="G45">
+        <v>0</v>
+      </c>
+      <c r="H45">
         <v>19935</v>
       </c>
-      <c r="H45">
-        <v>0</v>
-      </c>
       <c r="I45">
         <v>0</v>
       </c>
@@ -3251,36 +3383,39 @@
         <v>0</v>
       </c>
       <c r="L45">
+        <v>0</v>
+      </c>
+      <c r="M45">
         <v>2254</v>
       </c>
-      <c r="M45">
+      <c r="N45">
         <v>13</v>
       </c>
-      <c r="N45">
+      <c r="O45">
         <v>149</v>
       </c>
-      <c r="O45">
+      <c r="P45">
         <v>19786</v>
       </c>
-      <c r="P45">
+      <c r="Q45">
         <v>76287</v>
       </c>
-      <c r="Q45">
+      <c r="R45" s="2">
         <v>6998</v>
       </c>
-      <c r="R45">
-        <v>0</v>
-      </c>
-      <c r="S45">
+      <c r="S45" s="2">
+        <v>0</v>
+      </c>
+      <c r="T45" s="2">
         <v>129</v>
       </c>
     </row>
-    <row r="46" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A46">
         <v>43</v>
       </c>
       <c r="B46" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C46">
         <v>21512</v>
@@ -3289,17 +3424,17 @@
         <v>0</v>
       </c>
       <c r="E46">
+        <v>0</v>
+      </c>
+      <c r="F46">
         <v>21512</v>
       </c>
-      <c r="F46">
-        <v>0</v>
-      </c>
       <c r="G46">
+        <v>0</v>
+      </c>
+      <c r="H46">
         <v>21512</v>
       </c>
-      <c r="H46">
-        <v>0</v>
-      </c>
       <c r="I46">
         <v>0</v>
       </c>
@@ -3310,36 +3445,39 @@
         <v>0</v>
       </c>
       <c r="L46">
+        <v>0</v>
+      </c>
+      <c r="M46">
         <v>8303</v>
       </c>
-      <c r="M46">
+      <c r="N46">
         <v>32</v>
       </c>
-      <c r="N46">
+      <c r="O46">
         <v>276</v>
       </c>
-      <c r="O46">
+      <c r="P46">
         <v>21236</v>
       </c>
-      <c r="P46">
+      <c r="Q46">
         <v>64160</v>
       </c>
-      <c r="Q46">
+      <c r="R46" s="2">
         <v>7548</v>
       </c>
-      <c r="R46">
-        <v>0</v>
-      </c>
-      <c r="S46">
+      <c r="S46" s="2">
+        <v>0</v>
+      </c>
+      <c r="T46" s="2">
         <v>152</v>
       </c>
     </row>
-    <row r="47" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A47">
         <v>44</v>
       </c>
       <c r="B47" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C47">
         <v>22426</v>
@@ -3348,17 +3486,17 @@
         <v>0</v>
       </c>
       <c r="E47">
+        <v>0</v>
+      </c>
+      <c r="F47">
         <v>22426</v>
       </c>
-      <c r="F47">
-        <v>0</v>
-      </c>
       <c r="G47">
+        <v>0</v>
+      </c>
+      <c r="H47">
         <v>22426</v>
       </c>
-      <c r="H47">
-        <v>0</v>
-      </c>
       <c r="I47">
         <v>0</v>
       </c>
@@ -3369,36 +3507,39 @@
         <v>0</v>
       </c>
       <c r="L47">
+        <v>0</v>
+      </c>
+      <c r="M47">
         <v>2595</v>
       </c>
-      <c r="M47">
+      <c r="N47">
         <v>1</v>
       </c>
-      <c r="N47">
+      <c r="O47">
         <v>142</v>
       </c>
-      <c r="O47">
+      <c r="P47">
         <v>22284</v>
       </c>
-      <c r="P47">
+      <c r="Q47">
         <v>50821</v>
       </c>
-      <c r="Q47">
+      <c r="R47" s="2">
         <v>5046</v>
       </c>
-      <c r="R47">
-        <v>0</v>
-      </c>
-      <c r="S47">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="48" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="S47" s="2">
+        <v>0</v>
+      </c>
+      <c r="T47" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A48">
         <v>45</v>
       </c>
       <c r="B48" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C48">
         <v>19641</v>
@@ -3407,17 +3548,17 @@
         <v>0</v>
       </c>
       <c r="E48">
+        <v>0</v>
+      </c>
+      <c r="F48">
         <v>19641</v>
       </c>
-      <c r="F48">
-        <v>0</v>
-      </c>
       <c r="G48">
+        <v>0</v>
+      </c>
+      <c r="H48">
         <v>19641</v>
       </c>
-      <c r="H48">
-        <v>0</v>
-      </c>
       <c r="I48">
         <v>0</v>
       </c>
@@ -3428,36 +3569,39 @@
         <v>0</v>
       </c>
       <c r="L48">
+        <v>0</v>
+      </c>
+      <c r="M48">
         <v>3800</v>
       </c>
-      <c r="M48">
+      <c r="N48">
         <v>4</v>
       </c>
-      <c r="N48">
+      <c r="O48">
         <v>266</v>
       </c>
-      <c r="O48">
+      <c r="P48">
         <v>19376</v>
       </c>
-      <c r="P48">
+      <c r="Q48">
         <v>54497</v>
       </c>
-      <c r="Q48">
+      <c r="R48" s="2">
         <v>4623</v>
       </c>
-      <c r="R48">
-        <v>0</v>
-      </c>
-      <c r="S48">
+      <c r="S48" s="2">
+        <v>0</v>
+      </c>
+      <c r="T48" s="2">
         <v>9</v>
       </c>
     </row>
-    <row r="49" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A49">
         <v>46</v>
       </c>
       <c r="B49" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C49">
         <v>21651</v>
@@ -3466,17 +3610,17 @@
         <v>0</v>
       </c>
       <c r="E49">
+        <v>0</v>
+      </c>
+      <c r="F49">
         <v>21651</v>
       </c>
-      <c r="F49">
-        <v>0</v>
-      </c>
       <c r="G49">
+        <v>0</v>
+      </c>
+      <c r="H49">
         <v>21651</v>
       </c>
-      <c r="H49">
-        <v>0</v>
-      </c>
       <c r="I49">
         <v>0</v>
       </c>
@@ -3487,36 +3631,39 @@
         <v>0</v>
       </c>
       <c r="L49">
+        <v>0</v>
+      </c>
+      <c r="M49">
         <v>3627</v>
       </c>
-      <c r="M49">
-        <v>0</v>
-      </c>
       <c r="N49">
+        <v>0</v>
+      </c>
+      <c r="O49">
         <v>628</v>
       </c>
-      <c r="O49">
+      <c r="P49">
         <v>21027</v>
       </c>
-      <c r="P49">
+      <c r="Q49">
         <v>55376</v>
       </c>
-      <c r="Q49">
+      <c r="R49" s="2">
         <v>5057</v>
       </c>
-      <c r="R49">
-        <v>0</v>
-      </c>
-      <c r="S49">
+      <c r="S49" s="2">
+        <v>0</v>
+      </c>
+      <c r="T49" s="2">
         <v>4</v>
       </c>
     </row>
-    <row r="50" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A50">
         <v>47</v>
       </c>
       <c r="B50" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C50">
         <v>21936</v>
@@ -3525,17 +3672,17 @@
         <v>0</v>
       </c>
       <c r="E50">
+        <v>0</v>
+      </c>
+      <c r="F50">
         <v>21936</v>
       </c>
-      <c r="F50">
-        <v>0</v>
-      </c>
       <c r="G50">
+        <v>0</v>
+      </c>
+      <c r="H50">
         <v>21936</v>
       </c>
-      <c r="H50">
-        <v>0</v>
-      </c>
       <c r="I50">
         <v>0</v>
       </c>
@@ -3546,36 +3693,39 @@
         <v>0</v>
       </c>
       <c r="L50">
+        <v>0</v>
+      </c>
+      <c r="M50">
         <v>4160</v>
       </c>
-      <c r="M50">
+      <c r="N50">
         <v>5</v>
       </c>
-      <c r="N50">
+      <c r="O50">
         <v>26</v>
       </c>
-      <c r="O50">
+      <c r="P50">
         <v>21910</v>
       </c>
-      <c r="P50">
+      <c r="Q50">
         <v>63298</v>
       </c>
-      <c r="Q50">
+      <c r="R50" s="2">
         <v>7292</v>
       </c>
-      <c r="R50">
-        <v>0</v>
-      </c>
-      <c r="S50">
+      <c r="S50" s="2">
+        <v>0</v>
+      </c>
+      <c r="T50" s="2">
         <v>1</v>
       </c>
     </row>
-    <row r="51" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A51">
         <v>48</v>
       </c>
       <c r="B51" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C51">
         <v>23798</v>
@@ -3584,17 +3734,17 @@
         <v>0</v>
       </c>
       <c r="E51">
+        <v>0</v>
+      </c>
+      <c r="F51">
         <v>23798</v>
       </c>
-      <c r="F51">
-        <v>0</v>
-      </c>
       <c r="G51">
+        <v>0</v>
+      </c>
+      <c r="H51">
         <v>23798</v>
       </c>
-      <c r="H51">
-        <v>0</v>
-      </c>
       <c r="I51">
         <v>0</v>
       </c>
@@ -3605,36 +3755,39 @@
         <v>0</v>
       </c>
       <c r="L51">
+        <v>0</v>
+      </c>
+      <c r="M51">
         <v>4843</v>
       </c>
-      <c r="M51">
+      <c r="N51">
         <v>11</v>
       </c>
-      <c r="N51">
+      <c r="O51">
         <v>75</v>
       </c>
-      <c r="O51">
+      <c r="P51">
         <v>23723</v>
       </c>
-      <c r="P51">
+      <c r="Q51">
         <v>71754</v>
       </c>
-      <c r="Q51">
+      <c r="R51" s="2">
         <v>7715</v>
       </c>
-      <c r="R51">
-        <v>0</v>
-      </c>
-      <c r="S51">
+      <c r="S51" s="2">
+        <v>0</v>
+      </c>
+      <c r="T51" s="2">
         <v>40</v>
       </c>
     </row>
-    <row r="52" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A52">
         <v>49</v>
       </c>
       <c r="B52" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C52">
         <v>21094</v>
@@ -3643,17 +3796,17 @@
         <v>0</v>
       </c>
       <c r="E52">
+        <v>0</v>
+      </c>
+      <c r="F52">
         <v>21094</v>
       </c>
-      <c r="F52">
-        <v>0</v>
-      </c>
       <c r="G52">
+        <v>0</v>
+      </c>
+      <c r="H52">
         <v>21094</v>
       </c>
-      <c r="H52">
-        <v>0</v>
-      </c>
       <c r="I52">
         <v>0</v>
       </c>
@@ -3664,36 +3817,39 @@
         <v>0</v>
       </c>
       <c r="L52">
+        <v>0</v>
+      </c>
+      <c r="M52">
         <v>2942</v>
       </c>
-      <c r="M52">
+      <c r="N52">
         <v>1</v>
       </c>
-      <c r="N52">
+      <c r="O52">
         <v>45</v>
       </c>
-      <c r="O52">
+      <c r="P52">
         <v>21049</v>
       </c>
-      <c r="P52">
+      <c r="Q52">
         <v>63987</v>
       </c>
-      <c r="Q52">
+      <c r="R52" s="2">
         <v>5655</v>
       </c>
-      <c r="R52">
-        <v>0</v>
-      </c>
-      <c r="S52">
+      <c r="S52" s="2">
+        <v>0</v>
+      </c>
+      <c r="T52" s="2">
         <v>2</v>
       </c>
     </row>
-    <row r="53" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A53">
         <v>50</v>
       </c>
       <c r="B53" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C53">
         <v>19131</v>
@@ -3702,17 +3858,17 @@
         <v>0</v>
       </c>
       <c r="E53">
+        <v>0</v>
+      </c>
+      <c r="F53">
         <v>19131</v>
       </c>
-      <c r="F53">
-        <v>0</v>
-      </c>
       <c r="G53">
+        <v>0</v>
+      </c>
+      <c r="H53">
         <v>19131</v>
       </c>
-      <c r="H53">
-        <v>0</v>
-      </c>
       <c r="I53">
         <v>0</v>
       </c>
@@ -3723,36 +3879,39 @@
         <v>0</v>
       </c>
       <c r="L53">
+        <v>0</v>
+      </c>
+      <c r="M53">
         <v>3513</v>
       </c>
-      <c r="M53">
+      <c r="N53">
         <v>1</v>
       </c>
-      <c r="N53">
+      <c r="O53">
         <v>76</v>
       </c>
-      <c r="O53">
+      <c r="P53">
         <v>19055</v>
       </c>
-      <c r="P53">
+      <c r="Q53">
         <v>56306</v>
       </c>
-      <c r="Q53">
+      <c r="R53" s="2">
         <v>6551</v>
       </c>
-      <c r="R53">
-        <v>0</v>
-      </c>
-      <c r="S53">
+      <c r="S53" s="2">
+        <v>0</v>
+      </c>
+      <c r="T53" s="2">
         <v>5</v>
       </c>
     </row>
-    <row r="54" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A54">
         <v>51</v>
       </c>
       <c r="B54" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C54">
         <v>20758</v>
@@ -3761,17 +3920,17 @@
         <v>0</v>
       </c>
       <c r="E54">
+        <v>0</v>
+      </c>
+      <c r="F54">
         <v>20758</v>
       </c>
-      <c r="F54">
-        <v>0</v>
-      </c>
       <c r="G54">
+        <v>0</v>
+      </c>
+      <c r="H54">
         <v>20758</v>
       </c>
-      <c r="H54">
-        <v>0</v>
-      </c>
       <c r="I54">
         <v>0</v>
       </c>
@@ -3782,36 +3941,39 @@
         <v>0</v>
       </c>
       <c r="L54">
+        <v>0</v>
+      </c>
+      <c r="M54">
         <v>2603</v>
       </c>
-      <c r="M54">
+      <c r="N54">
         <v>5</v>
       </c>
-      <c r="N54">
+      <c r="O54">
         <v>391</v>
       </c>
-      <c r="O54">
+      <c r="P54">
         <v>20367</v>
       </c>
-      <c r="P54">
+      <c r="Q54">
         <v>58441</v>
       </c>
-      <c r="Q54">
+      <c r="R54" s="2">
         <v>7347</v>
       </c>
-      <c r="R54">
-        <v>0</v>
-      </c>
-      <c r="S54">
+      <c r="S54" s="2">
+        <v>0</v>
+      </c>
+      <c r="T54" s="2">
         <v>1</v>
       </c>
     </row>
-    <row r="55" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A55">
         <v>52</v>
       </c>
       <c r="B55" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C55">
         <v>16022</v>
@@ -3820,17 +3982,17 @@
         <v>0</v>
       </c>
       <c r="E55">
+        <v>0</v>
+      </c>
+      <c r="F55">
         <v>16022</v>
       </c>
-      <c r="F55">
-        <v>0</v>
-      </c>
       <c r="G55">
+        <v>0</v>
+      </c>
+      <c r="H55">
         <v>16022</v>
       </c>
-      <c r="H55">
-        <v>0</v>
-      </c>
       <c r="I55">
         <v>0</v>
       </c>
@@ -3841,36 +4003,39 @@
         <v>0</v>
       </c>
       <c r="L55">
+        <v>0</v>
+      </c>
+      <c r="M55">
         <v>2109</v>
       </c>
-      <c r="M55">
+      <c r="N55">
         <v>1</v>
       </c>
-      <c r="N55">
+      <c r="O55">
         <v>129</v>
       </c>
-      <c r="O55">
+      <c r="P55">
         <v>15893</v>
       </c>
-      <c r="P55">
+      <c r="Q55">
         <v>58215</v>
       </c>
-      <c r="Q55">
+      <c r="R55" s="2">
         <v>5098</v>
       </c>
-      <c r="R55">
-        <v>0</v>
-      </c>
-      <c r="S55">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="56" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="S55" s="2">
+        <v>0</v>
+      </c>
+      <c r="T55" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A56">
         <v>53</v>
       </c>
       <c r="B56" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C56">
         <v>19256</v>
@@ -3879,17 +4044,17 @@
         <v>0</v>
       </c>
       <c r="E56">
+        <v>0</v>
+      </c>
+      <c r="F56">
         <v>19256</v>
       </c>
-      <c r="F56">
-        <v>0</v>
-      </c>
       <c r="G56">
+        <v>0</v>
+      </c>
+      <c r="H56">
         <v>19256</v>
       </c>
-      <c r="H56">
-        <v>0</v>
-      </c>
       <c r="I56">
         <v>0</v>
       </c>
@@ -3900,36 +4065,39 @@
         <v>0</v>
       </c>
       <c r="L56">
+        <v>0</v>
+      </c>
+      <c r="M56">
         <v>4091</v>
       </c>
-      <c r="M56">
+      <c r="N56">
         <v>3</v>
       </c>
-      <c r="N56">
+      <c r="O56">
         <v>451</v>
       </c>
-      <c r="O56">
+      <c r="P56">
         <v>18805</v>
       </c>
-      <c r="P56">
+      <c r="Q56">
         <v>47621</v>
       </c>
-      <c r="Q56">
+      <c r="R56" s="2">
         <v>4882</v>
       </c>
-      <c r="R56">
-        <v>0</v>
-      </c>
-      <c r="S56">
+      <c r="S56" s="2">
+        <v>0</v>
+      </c>
+      <c r="T56" s="2">
         <v>30</v>
       </c>
     </row>
-    <row r="57" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A57">
         <v>54</v>
       </c>
       <c r="B57" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C57">
         <v>21240</v>
@@ -3938,17 +4106,17 @@
         <v>0</v>
       </c>
       <c r="E57">
+        <v>0</v>
+      </c>
+      <c r="F57">
         <v>21240</v>
       </c>
-      <c r="F57">
-        <v>0</v>
-      </c>
       <c r="G57">
+        <v>0</v>
+      </c>
+      <c r="H57">
         <v>21240</v>
       </c>
-      <c r="H57">
-        <v>0</v>
-      </c>
       <c r="I57">
         <v>0</v>
       </c>
@@ -3959,36 +4127,39 @@
         <v>0</v>
       </c>
       <c r="L57">
+        <v>0</v>
+      </c>
+      <c r="M57">
         <v>1905</v>
       </c>
-      <c r="M57">
+      <c r="N57">
         <v>5</v>
       </c>
-      <c r="N57">
+      <c r="O57">
         <v>39</v>
       </c>
-      <c r="O57">
+      <c r="P57">
         <v>21201</v>
       </c>
-      <c r="P57">
+      <c r="Q57">
         <v>61557</v>
       </c>
-      <c r="Q57">
+      <c r="R57" s="2">
         <v>6870</v>
       </c>
-      <c r="R57">
-        <v>0</v>
-      </c>
-      <c r="S57">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="58" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="S57" s="2">
+        <v>0</v>
+      </c>
+      <c r="T57" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A58">
         <v>55</v>
       </c>
       <c r="B58" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C58">
         <v>22819</v>
@@ -3997,17 +4168,17 @@
         <v>0</v>
       </c>
       <c r="E58">
+        <v>0</v>
+      </c>
+      <c r="F58">
         <v>22819</v>
       </c>
-      <c r="F58">
-        <v>0</v>
-      </c>
       <c r="G58">
+        <v>0</v>
+      </c>
+      <c r="H58">
         <v>22819</v>
       </c>
-      <c r="H58">
-        <v>0</v>
-      </c>
       <c r="I58">
         <v>0</v>
       </c>
@@ -4018,36 +4189,39 @@
         <v>0</v>
       </c>
       <c r="L58">
+        <v>0</v>
+      </c>
+      <c r="M58">
         <v>8123</v>
       </c>
-      <c r="M58">
+      <c r="N58">
         <v>10</v>
       </c>
-      <c r="N58">
+      <c r="O58">
         <v>552</v>
       </c>
-      <c r="O58">
+      <c r="P58">
         <v>22267</v>
       </c>
-      <c r="P58">
-        <v>57577</v>
-      </c>
       <c r="Q58">
+        <v>57579</v>
+      </c>
+      <c r="R58" s="2">
         <v>8884</v>
       </c>
-      <c r="R58">
-        <v>0</v>
-      </c>
-      <c r="S58">
+      <c r="S58" s="2">
+        <v>0</v>
+      </c>
+      <c r="T58" s="2">
         <v>64</v>
       </c>
     </row>
-    <row r="59" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A59">
         <v>56</v>
       </c>
       <c r="B59" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C59">
         <v>18776</v>
@@ -4056,17 +4230,17 @@
         <v>0</v>
       </c>
       <c r="E59">
+        <v>0</v>
+      </c>
+      <c r="F59">
         <v>18776</v>
       </c>
-      <c r="F59">
-        <v>0</v>
-      </c>
       <c r="G59">
+        <v>0</v>
+      </c>
+      <c r="H59">
         <v>18776</v>
       </c>
-      <c r="H59">
-        <v>0</v>
-      </c>
       <c r="I59">
         <v>0</v>
       </c>
@@ -4077,36 +4251,39 @@
         <v>0</v>
       </c>
       <c r="L59">
+        <v>0</v>
+      </c>
+      <c r="M59">
         <v>2506</v>
       </c>
-      <c r="M59">
+      <c r="N59">
         <v>2</v>
       </c>
-      <c r="N59">
+      <c r="O59">
         <v>287</v>
       </c>
-      <c r="O59">
+      <c r="P59">
         <v>18489</v>
       </c>
-      <c r="P59">
+      <c r="Q59">
         <v>60495</v>
       </c>
-      <c r="Q59">
+      <c r="R59" s="2">
         <v>8028</v>
       </c>
-      <c r="R59">
-        <v>0</v>
-      </c>
-      <c r="S59">
+      <c r="S59" s="2">
+        <v>0</v>
+      </c>
+      <c r="T59" s="2">
         <v>27</v>
       </c>
     </row>
-    <row r="60" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A60">
         <v>57</v>
       </c>
       <c r="B60" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C60">
         <v>23749</v>
@@ -4115,17 +4292,17 @@
         <v>0</v>
       </c>
       <c r="E60">
+        <v>0</v>
+      </c>
+      <c r="F60">
         <v>23749</v>
       </c>
-      <c r="F60">
-        <v>0</v>
-      </c>
       <c r="G60">
+        <v>0</v>
+      </c>
+      <c r="H60">
         <v>23749</v>
       </c>
-      <c r="H60">
-        <v>0</v>
-      </c>
       <c r="I60">
         <v>0</v>
       </c>
@@ -4136,36 +4313,39 @@
         <v>0</v>
       </c>
       <c r="L60">
+        <v>0</v>
+      </c>
+      <c r="M60">
         <v>5815</v>
       </c>
-      <c r="M60">
+      <c r="N60">
         <v>9</v>
       </c>
-      <c r="N60">
+      <c r="O60">
         <v>324</v>
       </c>
-      <c r="O60">
+      <c r="P60">
         <v>23425</v>
       </c>
-      <c r="P60">
-        <v>70140</v>
-      </c>
       <c r="Q60">
+        <v>70153</v>
+      </c>
+      <c r="R60" s="2">
         <v>7415</v>
       </c>
-      <c r="R60">
-        <v>0</v>
-      </c>
-      <c r="S60">
+      <c r="S60" s="2">
+        <v>0</v>
+      </c>
+      <c r="T60" s="2">
         <v>32</v>
       </c>
     </row>
-    <row r="61" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A61">
         <v>58</v>
       </c>
       <c r="B61" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C61">
         <v>22069</v>
@@ -4174,17 +4354,17 @@
         <v>0</v>
       </c>
       <c r="E61">
+        <v>0</v>
+      </c>
+      <c r="F61">
         <v>22069</v>
       </c>
-      <c r="F61">
-        <v>0</v>
-      </c>
       <c r="G61">
+        <v>0</v>
+      </c>
+      <c r="H61">
         <v>22069</v>
       </c>
-      <c r="H61">
-        <v>0</v>
-      </c>
       <c r="I61">
         <v>0</v>
       </c>
@@ -4195,36 +4375,39 @@
         <v>0</v>
       </c>
       <c r="L61">
+        <v>0</v>
+      </c>
+      <c r="M61">
         <v>9977</v>
       </c>
-      <c r="M61">
+      <c r="N61">
         <v>37</v>
       </c>
-      <c r="N61">
+      <c r="O61">
         <v>36</v>
       </c>
-      <c r="O61">
+      <c r="P61">
         <v>22033</v>
       </c>
-      <c r="P61">
-        <v>55240</v>
-      </c>
       <c r="Q61">
+        <v>55241</v>
+      </c>
+      <c r="R61" s="2">
         <v>7927</v>
       </c>
-      <c r="R61">
+      <c r="S61" s="2">
         <v>1</v>
       </c>
-      <c r="S61">
+      <c r="T61" s="2">
         <v>268</v>
       </c>
     </row>
-    <row r="62" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A62">
         <v>59</v>
       </c>
       <c r="B62" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C62">
         <v>15800</v>
@@ -4233,17 +4416,17 @@
         <v>0</v>
       </c>
       <c r="E62">
+        <v>0</v>
+      </c>
+      <c r="F62">
         <v>15800</v>
       </c>
-      <c r="F62">
-        <v>0</v>
-      </c>
       <c r="G62">
+        <v>0</v>
+      </c>
+      <c r="H62">
         <v>15800</v>
       </c>
-      <c r="H62">
-        <v>0</v>
-      </c>
       <c r="I62">
         <v>0</v>
       </c>
@@ -4254,36 +4437,39 @@
         <v>0</v>
       </c>
       <c r="L62">
+        <v>0</v>
+      </c>
+      <c r="M62">
         <v>4214</v>
       </c>
-      <c r="M62">
+      <c r="N62">
         <v>19</v>
       </c>
-      <c r="N62">
+      <c r="O62">
         <v>494</v>
       </c>
-      <c r="O62">
+      <c r="P62">
         <v>15306</v>
       </c>
-      <c r="P62">
+      <c r="Q62">
         <v>51334</v>
       </c>
-      <c r="Q62">
+      <c r="R62" s="2">
         <v>6917</v>
       </c>
-      <c r="R62">
-        <v>0</v>
-      </c>
-      <c r="S62">
+      <c r="S62" s="2">
+        <v>0</v>
+      </c>
+      <c r="T62" s="2">
         <v>100</v>
       </c>
     </row>
-    <row r="63" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A63">
         <v>60</v>
       </c>
       <c r="B63" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C63">
         <v>36754</v>
@@ -4292,17 +4478,17 @@
         <v>0</v>
       </c>
       <c r="E63">
+        <v>0</v>
+      </c>
+      <c r="F63">
         <v>36754</v>
       </c>
-      <c r="F63">
-        <v>0</v>
-      </c>
       <c r="G63">
+        <v>0</v>
+      </c>
+      <c r="H63">
         <v>36754</v>
       </c>
-      <c r="H63">
-        <v>0</v>
-      </c>
       <c r="I63">
         <v>0</v>
       </c>
@@ -4313,36 +4499,39 @@
         <v>0</v>
       </c>
       <c r="L63">
+        <v>0</v>
+      </c>
+      <c r="M63">
         <v>10975</v>
       </c>
-      <c r="M63">
+      <c r="N63">
         <v>68</v>
       </c>
-      <c r="N63">
+      <c r="O63">
         <v>931</v>
       </c>
-      <c r="O63">
+      <c r="P63">
         <v>35823</v>
       </c>
-      <c r="P63">
+      <c r="Q63">
         <v>68699</v>
       </c>
-      <c r="Q63">
+      <c r="R63" s="2">
         <v>9766</v>
       </c>
-      <c r="R63">
-        <v>0</v>
-      </c>
-      <c r="S63">
+      <c r="S63" s="2">
+        <v>0</v>
+      </c>
+      <c r="T63" s="2">
         <v>153</v>
       </c>
     </row>
-    <row r="64" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A64">
         <v>61</v>
       </c>
       <c r="B64" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C64">
         <v>42048</v>
@@ -4351,17 +4540,17 @@
         <v>0</v>
       </c>
       <c r="E64">
+        <v>0</v>
+      </c>
+      <c r="F64">
         <v>42048</v>
       </c>
-      <c r="F64">
-        <v>0</v>
-      </c>
       <c r="G64">
+        <v>0</v>
+      </c>
+      <c r="H64">
         <v>42048</v>
       </c>
-      <c r="H64">
-        <v>0</v>
-      </c>
       <c r="I64">
         <v>0</v>
       </c>
@@ -4372,36 +4561,39 @@
         <v>0</v>
       </c>
       <c r="L64">
+        <v>0</v>
+      </c>
+      <c r="M64">
         <v>9887</v>
       </c>
-      <c r="M64">
+      <c r="N64">
         <v>8</v>
       </c>
-      <c r="N64">
+      <c r="O64">
         <v>493</v>
       </c>
-      <c r="O64">
+      <c r="P64">
         <v>41555</v>
       </c>
-      <c r="P64">
+      <c r="Q64">
         <v>60527</v>
       </c>
-      <c r="Q64">
+      <c r="R64" s="2">
         <v>5985</v>
       </c>
-      <c r="R64">
-        <v>0</v>
-      </c>
-      <c r="S64">
+      <c r="S64" s="2">
+        <v>0</v>
+      </c>
+      <c r="T64" s="2">
         <v>101</v>
       </c>
     </row>
-    <row r="65" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A65">
         <v>62</v>
       </c>
       <c r="B65" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C65">
         <v>41389</v>
@@ -4410,17 +4602,17 @@
         <v>0</v>
       </c>
       <c r="E65">
+        <v>0</v>
+      </c>
+      <c r="F65">
         <v>41389</v>
       </c>
-      <c r="F65">
-        <v>0</v>
-      </c>
       <c r="G65">
+        <v>0</v>
+      </c>
+      <c r="H65">
         <v>41389</v>
       </c>
-      <c r="H65">
-        <v>0</v>
-      </c>
       <c r="I65">
         <v>0</v>
       </c>
@@ -4431,36 +4623,39 @@
         <v>0</v>
       </c>
       <c r="L65">
+        <v>0</v>
+      </c>
+      <c r="M65">
         <v>13582</v>
       </c>
-      <c r="M65">
+      <c r="N65">
         <v>2</v>
       </c>
-      <c r="N65">
+      <c r="O65">
         <v>2635</v>
       </c>
-      <c r="O65">
+      <c r="P65">
         <v>38754</v>
       </c>
-      <c r="P65">
+      <c r="Q65">
         <v>58527</v>
       </c>
-      <c r="Q65">
+      <c r="R65" s="2">
         <v>13282</v>
       </c>
-      <c r="R65">
-        <v>0</v>
-      </c>
-      <c r="S65">
+      <c r="S65" s="2">
+        <v>0</v>
+      </c>
+      <c r="T65" s="2">
         <v>138</v>
       </c>
     </row>
-    <row r="66" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A66">
         <v>63</v>
       </c>
       <c r="B66" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C66">
         <v>67362</v>
@@ -4469,17 +4664,17 @@
         <v>0</v>
       </c>
       <c r="E66">
+        <v>1</v>
+      </c>
+      <c r="F66">
         <v>67362</v>
       </c>
-      <c r="F66">
-        <v>0</v>
-      </c>
       <c r="G66">
+        <v>0</v>
+      </c>
+      <c r="H66">
         <v>67362</v>
       </c>
-      <c r="H66">
-        <v>0</v>
-      </c>
       <c r="I66">
         <v>0</v>
       </c>
@@ -4490,36 +4685,39 @@
         <v>0</v>
       </c>
       <c r="L66">
+        <v>0</v>
+      </c>
+      <c r="M66">
         <v>13733</v>
       </c>
-      <c r="M66">
+      <c r="N66">
         <v>2</v>
       </c>
-      <c r="N66">
+      <c r="O66">
         <v>4022</v>
       </c>
-      <c r="O66">
+      <c r="P66">
         <v>63341</v>
       </c>
-      <c r="P66">
+      <c r="Q66">
         <v>93810</v>
       </c>
-      <c r="Q66">
+      <c r="R66" s="2">
         <v>17742</v>
       </c>
-      <c r="R66">
-        <v>0</v>
-      </c>
-      <c r="S66">
+      <c r="S66" s="2">
+        <v>0</v>
+      </c>
+      <c r="T66" s="2">
         <v>52</v>
       </c>
     </row>
-    <row r="67" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A67">
         <v>64</v>
       </c>
       <c r="B67" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C67">
         <v>68828</v>
@@ -4528,17 +4726,17 @@
         <v>0</v>
       </c>
       <c r="E67">
+        <v>0</v>
+      </c>
+      <c r="F67">
         <v>68828</v>
       </c>
-      <c r="F67">
-        <v>0</v>
-      </c>
       <c r="G67">
+        <v>0</v>
+      </c>
+      <c r="H67">
         <v>68828</v>
       </c>
-      <c r="H67">
-        <v>0</v>
-      </c>
       <c r="I67">
         <v>0</v>
       </c>
@@ -4549,36 +4747,39 @@
         <v>0</v>
       </c>
       <c r="L67">
+        <v>0</v>
+      </c>
+      <c r="M67">
         <v>19495</v>
       </c>
-      <c r="M67">
+      <c r="N67">
         <v>10</v>
       </c>
-      <c r="N67">
+      <c r="O67">
         <v>3644</v>
       </c>
-      <c r="O67">
+      <c r="P67">
         <v>65185</v>
       </c>
-      <c r="P67">
+      <c r="Q67">
         <v>78032</v>
       </c>
-      <c r="Q67">
+      <c r="R67" s="2">
         <v>9807</v>
       </c>
-      <c r="R67">
-        <v>0</v>
-      </c>
-      <c r="S67">
+      <c r="S67" s="2">
+        <v>0</v>
+      </c>
+      <c r="T67" s="2">
         <v>116</v>
       </c>
     </row>
-    <row r="68" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A68">
         <v>65</v>
       </c>
       <c r="B68" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C68">
         <v>65397</v>
@@ -4587,17 +4788,17 @@
         <v>0</v>
       </c>
       <c r="E68">
+        <v>0</v>
+      </c>
+      <c r="F68">
         <v>65397</v>
       </c>
-      <c r="F68">
-        <v>0</v>
-      </c>
       <c r="G68">
+        <v>0</v>
+      </c>
+      <c r="H68">
         <v>65397</v>
       </c>
-      <c r="H68">
-        <v>0</v>
-      </c>
       <c r="I68">
         <v>0</v>
       </c>
@@ -4608,36 +4809,39 @@
         <v>0</v>
       </c>
       <c r="L68">
+        <v>0</v>
+      </c>
+      <c r="M68">
         <v>18679</v>
       </c>
-      <c r="M68">
+      <c r="N68">
         <v>2</v>
       </c>
-      <c r="N68">
+      <c r="O68">
         <v>1603</v>
       </c>
-      <c r="O68">
+      <c r="P68">
         <v>63796</v>
       </c>
-      <c r="P68">
+      <c r="Q68">
         <v>71325</v>
       </c>
-      <c r="Q68">
+      <c r="R68" s="2">
         <v>7850</v>
       </c>
-      <c r="R68">
-        <v>0</v>
-      </c>
-      <c r="S68">
+      <c r="S68" s="2">
+        <v>0</v>
+      </c>
+      <c r="T68" s="2">
         <v>26</v>
       </c>
     </row>
-    <row r="69" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A69">
         <v>66</v>
       </c>
       <c r="B69" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C69">
         <v>43938</v>
@@ -4646,17 +4850,17 @@
         <v>0</v>
       </c>
       <c r="E69">
+        <v>0</v>
+      </c>
+      <c r="F69">
         <v>43938</v>
       </c>
-      <c r="F69">
-        <v>0</v>
-      </c>
       <c r="G69">
+        <v>0</v>
+      </c>
+      <c r="H69">
         <v>43938</v>
       </c>
-      <c r="H69">
-        <v>0</v>
-      </c>
       <c r="I69">
         <v>0</v>
       </c>
@@ -4667,36 +4871,39 @@
         <v>0</v>
       </c>
       <c r="L69">
+        <v>0</v>
+      </c>
+      <c r="M69">
         <v>18216</v>
       </c>
-      <c r="M69">
+      <c r="N69">
         <v>2</v>
       </c>
-      <c r="N69">
+      <c r="O69">
         <v>2619</v>
       </c>
-      <c r="O69">
+      <c r="P69">
         <v>41322</v>
       </c>
-      <c r="P69">
+      <c r="Q69">
         <v>36118</v>
       </c>
-      <c r="Q69">
+      <c r="R69" s="2">
         <v>6528</v>
       </c>
-      <c r="R69">
-        <v>0</v>
-      </c>
-      <c r="S69">
+      <c r="S69" s="2">
+        <v>0</v>
+      </c>
+      <c r="T69" s="2">
         <v>47</v>
       </c>
     </row>
-    <row r="70" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A70">
         <v>67</v>
       </c>
       <c r="B70" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C70">
         <v>47711</v>
@@ -4705,17 +4912,17 @@
         <v>0</v>
       </c>
       <c r="E70">
+        <v>0</v>
+      </c>
+      <c r="F70">
         <v>47711</v>
       </c>
-      <c r="F70">
-        <v>0</v>
-      </c>
       <c r="G70">
+        <v>0</v>
+      </c>
+      <c r="H70">
         <v>47711</v>
       </c>
-      <c r="H70">
-        <v>0</v>
-      </c>
       <c r="I70">
         <v>0</v>
       </c>
@@ -4726,36 +4933,39 @@
         <v>0</v>
       </c>
       <c r="L70">
+        <v>0</v>
+      </c>
+      <c r="M70">
         <v>18275</v>
       </c>
-      <c r="M70">
+      <c r="N70">
         <v>2</v>
       </c>
-      <c r="N70">
+      <c r="O70">
         <v>3246</v>
       </c>
-      <c r="O70">
+      <c r="P70">
         <v>44466</v>
       </c>
-      <c r="P70">
+      <c r="Q70">
         <v>42051</v>
       </c>
-      <c r="Q70">
+      <c r="R70" s="2">
         <v>5798</v>
       </c>
-      <c r="R70">
-        <v>0</v>
-      </c>
-      <c r="S70">
+      <c r="S70" s="2">
+        <v>0</v>
+      </c>
+      <c r="T70" s="2">
         <v>29</v>
       </c>
     </row>
-    <row r="71" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A71">
         <v>68</v>
       </c>
       <c r="B71" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C71">
         <v>50963</v>
@@ -4764,17 +4974,17 @@
         <v>0</v>
       </c>
       <c r="E71">
+        <v>0</v>
+      </c>
+      <c r="F71">
         <v>50963</v>
       </c>
-      <c r="F71">
-        <v>0</v>
-      </c>
       <c r="G71">
+        <v>0</v>
+      </c>
+      <c r="H71">
         <v>50963</v>
       </c>
-      <c r="H71">
-        <v>0</v>
-      </c>
       <c r="I71">
         <v>0</v>
       </c>
@@ -4785,36 +4995,39 @@
         <v>0</v>
       </c>
       <c r="L71">
+        <v>0</v>
+      </c>
+      <c r="M71">
         <v>22851</v>
       </c>
-      <c r="M71">
+      <c r="N71">
         <v>1</v>
       </c>
-      <c r="N71">
+      <c r="O71">
         <v>4449</v>
       </c>
-      <c r="O71">
+      <c r="P71">
         <v>46514</v>
       </c>
-      <c r="P71">
+      <c r="Q71">
         <v>49140</v>
       </c>
-      <c r="Q71">
+      <c r="R71" s="2">
         <v>6782</v>
       </c>
-      <c r="R71">
-        <v>0</v>
-      </c>
-      <c r="S71">
+      <c r="S71" s="2">
+        <v>0</v>
+      </c>
+      <c r="T71" s="2">
         <v>235</v>
       </c>
     </row>
-    <row r="72" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A72">
         <v>69</v>
       </c>
       <c r="B72" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C72">
         <v>61543</v>
@@ -4823,17 +5036,17 @@
         <v>0</v>
       </c>
       <c r="E72">
+        <v>0</v>
+      </c>
+      <c r="F72">
         <v>61543</v>
       </c>
-      <c r="F72">
-        <v>0</v>
-      </c>
       <c r="G72">
+        <v>0</v>
+      </c>
+      <c r="H72">
         <v>61543</v>
       </c>
-      <c r="H72">
-        <v>0</v>
-      </c>
       <c r="I72">
         <v>0</v>
       </c>
@@ -4844,36 +5057,39 @@
         <v>0</v>
       </c>
       <c r="L72">
+        <v>0</v>
+      </c>
+      <c r="M72">
         <v>17245</v>
       </c>
-      <c r="M72">
+      <c r="N72">
         <v>9</v>
       </c>
-      <c r="N72">
+      <c r="O72">
         <v>3668</v>
       </c>
-      <c r="O72">
+      <c r="P72">
         <v>57877</v>
       </c>
-      <c r="P72">
+      <c r="Q72">
         <v>85504</v>
       </c>
-      <c r="Q72">
+      <c r="R72" s="2">
         <v>12340</v>
       </c>
-      <c r="R72">
-        <v>0</v>
-      </c>
-      <c r="S72">
+      <c r="S72" s="2">
+        <v>0</v>
+      </c>
+      <c r="T72" s="2">
         <v>79</v>
       </c>
     </row>
-    <row r="73" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A73">
         <v>70</v>
       </c>
       <c r="B73" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C73">
         <v>58915</v>
@@ -4882,17 +5098,17 @@
         <v>0</v>
       </c>
       <c r="E73">
+        <v>0</v>
+      </c>
+      <c r="F73">
         <v>58915</v>
       </c>
-      <c r="F73">
-        <v>0</v>
-      </c>
       <c r="G73">
+        <v>0</v>
+      </c>
+      <c r="H73">
         <v>58915</v>
       </c>
-      <c r="H73">
-        <v>0</v>
-      </c>
       <c r="I73">
         <v>0</v>
       </c>
@@ -4903,33 +5119,36 @@
         <v>0</v>
       </c>
       <c r="L73">
+        <v>0</v>
+      </c>
+      <c r="M73">
         <v>15131</v>
       </c>
-      <c r="M73">
+      <c r="N73">
         <v>8</v>
       </c>
-      <c r="N73">
+      <c r="O73">
         <v>3866</v>
       </c>
-      <c r="O73">
+      <c r="P73">
         <v>55049</v>
       </c>
-      <c r="P73">
+      <c r="Q73">
         <v>67666</v>
       </c>
-      <c r="Q73">
+      <c r="R73" s="2">
         <v>10010</v>
       </c>
-      <c r="R73">
-        <v>0</v>
-      </c>
-      <c r="S73">
+      <c r="S73" s="2">
+        <v>0</v>
+      </c>
+      <c r="T73" s="2">
         <v>74</v>
       </c>
     </row>
-    <row r="74" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A74" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B74" s="1"/>
       <c r="C74">
@@ -4939,17 +5158,17 @@
         <v>0</v>
       </c>
       <c r="E74">
+        <v>9</v>
+      </c>
+      <c r="F74">
         <v>2430387</v>
       </c>
-      <c r="F74">
-        <v>0</v>
-      </c>
       <c r="G74">
+        <v>0</v>
+      </c>
+      <c r="H74">
         <v>2430385</v>
       </c>
-      <c r="H74">
-        <v>0</v>
-      </c>
       <c r="I74">
         <v>0</v>
       </c>
@@ -4960,48 +5179,54 @@
         <v>0</v>
       </c>
       <c r="L74">
+        <v>0</v>
+      </c>
+      <c r="M74">
         <v>626066</v>
       </c>
-      <c r="M74">
+      <c r="N74">
         <v>8318</v>
       </c>
-      <c r="N74">
+      <c r="O74">
         <v>97186</v>
       </c>
-      <c r="O74">
+      <c r="P74">
         <v>2333338</v>
       </c>
-      <c r="P74">
-        <v>4703236</v>
-      </c>
       <c r="Q74">
+        <v>4703252</v>
+      </c>
+      <c r="R74" s="2">
         <v>626236</v>
       </c>
-      <c r="R74">
+      <c r="S74" s="2">
         <v>1</v>
       </c>
-      <c r="S74">
+      <c r="T74" s="2">
         <v>3445</v>
       </c>
     </row>
+    <row r="75" spans="1:20" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="76" spans="1:20" ht="15.75" x14ac:dyDescent="0.25"/>
   </sheetData>
-  <mergeCells count="12">
+  <mergeCells count="13">
     <mergeCell ref="A74:B74"/>
-    <mergeCell ref="Q2:S2"/>
-    <mergeCell ref="A1:Q1"/>
+    <mergeCell ref="R2:T2"/>
+    <mergeCell ref="A1:R1"/>
     <mergeCell ref="A2:A3"/>
     <mergeCell ref="B2:B3"/>
     <mergeCell ref="C2:C3"/>
     <mergeCell ref="D2:D3"/>
     <mergeCell ref="E2:E3"/>
     <mergeCell ref="F2:F3"/>
-    <mergeCell ref="G2:I2"/>
-    <mergeCell ref="J2:M2"/>
-    <mergeCell ref="N2:P2"/>
+    <mergeCell ref="G2:G3"/>
+    <mergeCell ref="H2:J2"/>
+    <mergeCell ref="K2:N2"/>
+    <mergeCell ref="O2:Q2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="A2:D74 B1:D1 E2:P74 E1:P1" numberStoredAsText="1"/>
+    <ignoredError sqref="A2:Q74 B1:Q1" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/Notice.xlsx
+++ b/Notice.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Downloads\New folder (13)\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53EC95D2-F6FC-4847-B5C3-F75331010C77}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1E098ED-8EF4-47E7-B3EB-1054B085FB10}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="95">
   <si>
     <t>S. No.</t>
   </si>
@@ -32,9 +32,6 @@
   </si>
   <si>
     <t>Pending for Notice Generation</t>
-  </si>
-  <si>
-    <t>Form 7/8 (Shifting)</t>
   </si>
   <si>
     <t>Notice Delivered</t>
@@ -343,13 +340,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -689,83 +685,81 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:T76"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:S74"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
-      <c r="H1" s="1"/>
-      <c r="I1" s="1"/>
-      <c r="J1" s="1"/>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
-      <c r="M1" s="1"/>
-      <c r="N1" s="1"/>
-      <c r="O1" s="1"/>
-      <c r="P1" s="1"/>
-      <c r="Q1" s="1"/>
-      <c r="R1" s="1"/>
-    </row>
-    <row r="2" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="1" t="s">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="2"/>
+      <c r="H1" s="2"/>
+      <c r="I1" s="2"/>
+      <c r="J1" s="2"/>
+      <c r="K1" s="2"/>
+      <c r="L1" s="2"/>
+      <c r="M1" s="2"/>
+      <c r="N1" s="2"/>
+      <c r="O1" s="2"/>
+      <c r="P1" s="2"/>
+      <c r="Q1" s="2"/>
+    </row>
+    <row r="2" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="D2" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="E2" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="F2" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="G2" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="H2" s="2"/>
+      <c r="I2" s="2"/>
+      <c r="J2" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I2" s="1"/>
-      <c r="J2" s="1"/>
-      <c r="K2" s="1" t="s">
+      <c r="K2" s="2"/>
+      <c r="L2" s="2"/>
+      <c r="M2" s="2"/>
+      <c r="N2" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="L2" s="1"/>
-      <c r="M2" s="1"/>
-      <c r="N2" s="1"/>
-      <c r="O2" s="1" t="s">
+      <c r="O2" s="2"/>
+      <c r="P2" s="2"/>
+      <c r="Q2" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="R2" s="2"/>
+      <c r="S2" s="2"/>
+    </row>
+    <row r="3" spans="1:19" ht="63" x14ac:dyDescent="0.25">
+      <c r="A3" s="2"/>
+      <c r="B3" s="2"/>
+      <c r="C3" s="2"/>
+      <c r="D3" s="2"/>
+      <c r="E3" s="2"/>
+      <c r="F3" s="2"/>
+      <c r="G3" t="s">
         <v>9</v>
       </c>
-      <c r="P2" s="1"/>
-      <c r="Q2" s="1"/>
-      <c r="R2" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="S2" s="1"/>
-      <c r="T2" s="1"/>
-    </row>
-    <row r="3" spans="1:20" ht="63" x14ac:dyDescent="0.25">
-      <c r="A3" s="1"/>
-      <c r="B3" s="1"/>
-      <c r="C3" s="1"/>
-      <c r="D3" s="1"/>
-      <c r="E3" s="1"/>
-      <c r="F3" s="1"/>
-      <c r="G3" s="1"/>
       <c r="H3" t="s">
         <v>10</v>
       </c>
@@ -793,25 +787,22 @@
       <c r="P3" t="s">
         <v>18</v>
       </c>
-      <c r="Q3" t="s">
-        <v>19</v>
-      </c>
-      <c r="R3" s="3" t="s">
+      <c r="Q3" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="R3" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="S3" s="3" t="s">
+      <c r="S3" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="T3" s="3" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="4" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="4" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>1</v>
       </c>
       <c r="B4" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C4">
         <v>51528</v>
@@ -820,16 +811,16 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>2</v>
+        <v>51528</v>
       </c>
       <c r="F4">
+        <v>0</v>
+      </c>
+      <c r="G4">
         <v>51528</v>
       </c>
-      <c r="G4">
-        <v>0</v>
-      </c>
       <c r="H4">
-        <v>51528</v>
+        <v>0</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -841,39 +832,36 @@
         <v>0</v>
       </c>
       <c r="L4">
-        <v>0</v>
+        <v>17975</v>
       </c>
       <c r="M4">
-        <v>17975</v>
+        <v>967</v>
       </c>
       <c r="N4">
-        <v>967</v>
+        <v>869</v>
       </c>
       <c r="O4">
-        <v>869</v>
+        <v>50659</v>
       </c>
       <c r="P4">
-        <v>50659</v>
+        <v>53812</v>
       </c>
       <c r="Q4">
-        <v>53812</v>
-      </c>
-      <c r="R4" s="2">
         <v>12212</v>
       </c>
-      <c r="S4" s="2">
-        <v>0</v>
-      </c>
-      <c r="T4" s="2">
+      <c r="R4">
+        <v>0</v>
+      </c>
+      <c r="S4">
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>2</v>
       </c>
       <c r="B5" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C5">
         <v>53911</v>
@@ -882,16 +870,16 @@
         <v>0</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>53911</v>
       </c>
       <c r="F5">
+        <v>0</v>
+      </c>
+      <c r="G5">
         <v>53911</v>
       </c>
-      <c r="G5">
-        <v>0</v>
-      </c>
       <c r="H5">
-        <v>53911</v>
+        <v>0</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -903,39 +891,36 @@
         <v>0</v>
       </c>
       <c r="L5">
-        <v>0</v>
+        <v>11415</v>
       </c>
       <c r="M5">
-        <v>11415</v>
+        <v>757</v>
       </c>
       <c r="N5">
-        <v>757</v>
+        <v>877</v>
       </c>
       <c r="O5">
-        <v>877</v>
+        <v>53035</v>
       </c>
       <c r="P5">
-        <v>53035</v>
+        <v>74848</v>
       </c>
       <c r="Q5">
-        <v>74848</v>
-      </c>
-      <c r="R5" s="2">
         <v>16108</v>
       </c>
-      <c r="S5" s="2">
-        <v>0</v>
-      </c>
-      <c r="T5" s="2">
+      <c r="R5">
+        <v>0</v>
+      </c>
+      <c r="S5">
         <v>30</v>
       </c>
     </row>
-    <row r="6" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>3</v>
       </c>
       <c r="B6" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C6">
         <v>39773</v>
@@ -944,16 +929,16 @@
         <v>0</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>39773</v>
       </c>
       <c r="F6">
+        <v>0</v>
+      </c>
+      <c r="G6">
         <v>39773</v>
       </c>
-      <c r="G6">
-        <v>0</v>
-      </c>
       <c r="H6">
-        <v>39773</v>
+        <v>0</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -965,39 +950,36 @@
         <v>0</v>
       </c>
       <c r="L6">
-        <v>0</v>
+        <v>6086</v>
       </c>
       <c r="M6">
-        <v>6086</v>
+        <v>201</v>
       </c>
       <c r="N6">
-        <v>201</v>
+        <v>1870</v>
       </c>
       <c r="O6">
-        <v>1870</v>
+        <v>37903</v>
       </c>
       <c r="P6">
-        <v>37903</v>
+        <v>71989</v>
       </c>
       <c r="Q6">
-        <v>71989</v>
-      </c>
-      <c r="R6" s="2">
         <v>17830</v>
       </c>
-      <c r="S6" s="2">
-        <v>0</v>
-      </c>
-      <c r="T6" s="2">
+      <c r="R6">
+        <v>0</v>
+      </c>
+      <c r="S6">
         <v>54</v>
       </c>
     </row>
-    <row r="7" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>4</v>
       </c>
       <c r="B7" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C7">
         <v>39463</v>
@@ -1006,16 +988,16 @@
         <v>0</v>
       </c>
       <c r="E7">
-        <v>0</v>
+        <v>39463</v>
       </c>
       <c r="F7">
+        <v>0</v>
+      </c>
+      <c r="G7">
         <v>39463</v>
       </c>
-      <c r="G7">
-        <v>0</v>
-      </c>
       <c r="H7">
-        <v>39463</v>
+        <v>0</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -1027,39 +1009,36 @@
         <v>0</v>
       </c>
       <c r="L7">
-        <v>0</v>
+        <v>5733</v>
       </c>
       <c r="M7">
-        <v>5733</v>
+        <v>257</v>
       </c>
       <c r="N7">
-        <v>257</v>
+        <v>1995</v>
       </c>
       <c r="O7">
-        <v>1995</v>
+        <v>37468</v>
       </c>
       <c r="P7">
-        <v>37468</v>
+        <v>77581</v>
       </c>
       <c r="Q7">
-        <v>77581</v>
-      </c>
-      <c r="R7" s="2">
         <v>20511</v>
       </c>
-      <c r="S7" s="2">
-        <v>0</v>
-      </c>
-      <c r="T7" s="2">
+      <c r="R7">
+        <v>0</v>
+      </c>
+      <c r="S7">
         <v>8</v>
       </c>
     </row>
-    <row r="8" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>5</v>
       </c>
       <c r="B8" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C8">
         <v>40552</v>
@@ -1068,16 +1047,16 @@
         <v>0</v>
       </c>
       <c r="E8">
-        <v>5</v>
+        <v>40552</v>
       </c>
       <c r="F8">
+        <v>0</v>
+      </c>
+      <c r="G8">
         <v>40552</v>
       </c>
-      <c r="G8">
-        <v>0</v>
-      </c>
       <c r="H8">
-        <v>40552</v>
+        <v>0</v>
       </c>
       <c r="I8">
         <v>0</v>
@@ -1089,39 +1068,36 @@
         <v>0</v>
       </c>
       <c r="L8">
-        <v>0</v>
+        <v>14714</v>
       </c>
       <c r="M8">
-        <v>14714</v>
+        <v>164</v>
       </c>
       <c r="N8">
-        <v>164</v>
+        <v>1981</v>
       </c>
       <c r="O8">
-        <v>1981</v>
+        <v>38571</v>
       </c>
       <c r="P8">
-        <v>38571</v>
+        <v>73458</v>
       </c>
       <c r="Q8">
-        <v>73458</v>
-      </c>
-      <c r="R8" s="2">
         <v>20788</v>
       </c>
-      <c r="S8" s="2">
-        <v>0</v>
-      </c>
-      <c r="T8" s="2">
+      <c r="R8">
+        <v>0</v>
+      </c>
+      <c r="S8">
         <v>110</v>
       </c>
     </row>
-    <row r="9" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>6</v>
       </c>
       <c r="B9" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C9">
         <v>43273</v>
@@ -1130,16 +1106,16 @@
         <v>0</v>
       </c>
       <c r="E9">
-        <v>0</v>
+        <v>43273</v>
       </c>
       <c r="F9">
+        <v>0</v>
+      </c>
+      <c r="G9">
         <v>43273</v>
       </c>
-      <c r="G9">
-        <v>0</v>
-      </c>
       <c r="H9">
-        <v>43273</v>
+        <v>0</v>
       </c>
       <c r="I9">
         <v>0</v>
@@ -1151,39 +1127,36 @@
         <v>0</v>
       </c>
       <c r="L9">
-        <v>0</v>
+        <v>7759</v>
       </c>
       <c r="M9">
-        <v>7759</v>
+        <v>49</v>
       </c>
       <c r="N9">
-        <v>49</v>
+        <v>1350</v>
       </c>
       <c r="O9">
-        <v>1350</v>
+        <v>41924</v>
       </c>
       <c r="P9">
-        <v>41924</v>
+        <v>72913</v>
       </c>
       <c r="Q9">
-        <v>72913</v>
-      </c>
-      <c r="R9" s="2">
         <v>18141</v>
       </c>
-      <c r="S9" s="2">
-        <v>0</v>
-      </c>
-      <c r="T9" s="2">
+      <c r="R9">
+        <v>0</v>
+      </c>
+      <c r="S9">
         <v>110</v>
       </c>
     </row>
-    <row r="10" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>7</v>
       </c>
       <c r="B10" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C10">
         <v>36576</v>
@@ -1192,16 +1165,16 @@
         <v>0</v>
       </c>
       <c r="E10">
-        <v>0</v>
+        <v>36576</v>
       </c>
       <c r="F10">
+        <v>0</v>
+      </c>
+      <c r="G10">
         <v>36576</v>
       </c>
-      <c r="G10">
-        <v>0</v>
-      </c>
       <c r="H10">
-        <v>36576</v>
+        <v>0</v>
       </c>
       <c r="I10">
         <v>0</v>
@@ -1213,39 +1186,36 @@
         <v>0</v>
       </c>
       <c r="L10">
-        <v>0</v>
+        <v>10960</v>
       </c>
       <c r="M10">
-        <v>10960</v>
+        <v>172</v>
       </c>
       <c r="N10">
-        <v>172</v>
+        <v>815</v>
       </c>
       <c r="O10">
-        <v>815</v>
+        <v>35761</v>
       </c>
       <c r="P10">
-        <v>35761</v>
+        <v>53124</v>
       </c>
       <c r="Q10">
-        <v>53124</v>
-      </c>
-      <c r="R10" s="2">
         <v>9498</v>
       </c>
-      <c r="S10" s="2">
-        <v>0</v>
-      </c>
-      <c r="T10" s="2">
+      <c r="R10">
+        <v>0</v>
+      </c>
+      <c r="S10">
         <v>2</v>
       </c>
     </row>
-    <row r="11" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>8</v>
       </c>
       <c r="B11" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C11">
         <v>50998</v>
@@ -1254,16 +1224,16 @@
         <v>0</v>
       </c>
       <c r="E11">
-        <v>0</v>
+        <v>50998</v>
       </c>
       <c r="F11">
+        <v>0</v>
+      </c>
+      <c r="G11">
         <v>50998</v>
       </c>
-      <c r="G11">
-        <v>0</v>
-      </c>
       <c r="H11">
-        <v>50998</v>
+        <v>0</v>
       </c>
       <c r="I11">
         <v>0</v>
@@ -1275,39 +1245,36 @@
         <v>0</v>
       </c>
       <c r="L11">
-        <v>0</v>
+        <v>9958</v>
       </c>
       <c r="M11">
-        <v>9958</v>
+        <v>253</v>
       </c>
       <c r="N11">
-        <v>253</v>
+        <v>1703</v>
       </c>
       <c r="O11">
-        <v>1703</v>
+        <v>49300</v>
       </c>
       <c r="P11">
-        <v>49300</v>
+        <v>84438</v>
       </c>
       <c r="Q11">
-        <v>84438</v>
-      </c>
-      <c r="R11" s="2">
         <v>23477</v>
       </c>
-      <c r="S11" s="2">
-        <v>0</v>
-      </c>
-      <c r="T11" s="2">
+      <c r="R11">
+        <v>0</v>
+      </c>
+      <c r="S11">
         <v>23</v>
       </c>
     </row>
-    <row r="12" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>9</v>
       </c>
       <c r="B12" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C12">
         <v>40739</v>
@@ -1316,16 +1283,16 @@
         <v>0</v>
       </c>
       <c r="E12">
-        <v>0</v>
+        <v>40739</v>
       </c>
       <c r="F12">
+        <v>0</v>
+      </c>
+      <c r="G12">
         <v>40739</v>
       </c>
-      <c r="G12">
-        <v>0</v>
-      </c>
       <c r="H12">
-        <v>40739</v>
+        <v>0</v>
       </c>
       <c r="I12">
         <v>0</v>
@@ -1337,39 +1304,36 @@
         <v>0</v>
       </c>
       <c r="L12">
-        <v>0</v>
+        <v>10054</v>
       </c>
       <c r="M12">
-        <v>10054</v>
+        <v>207</v>
       </c>
       <c r="N12">
-        <v>207</v>
+        <v>1151</v>
       </c>
       <c r="O12">
-        <v>1151</v>
+        <v>39588</v>
       </c>
       <c r="P12">
-        <v>39588</v>
+        <v>66685</v>
       </c>
       <c r="Q12">
-        <v>66685</v>
-      </c>
-      <c r="R12" s="2">
         <v>17786</v>
       </c>
-      <c r="S12" s="2">
-        <v>0</v>
-      </c>
-      <c r="T12" s="2">
+      <c r="R12">
+        <v>0</v>
+      </c>
+      <c r="S12">
         <v>3</v>
       </c>
     </row>
-    <row r="13" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>10</v>
       </c>
       <c r="B13" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C13">
         <v>37031</v>
@@ -1378,16 +1342,16 @@
         <v>0</v>
       </c>
       <c r="E13">
-        <v>0</v>
+        <v>37031</v>
       </c>
       <c r="F13">
+        <v>0</v>
+      </c>
+      <c r="G13">
         <v>37031</v>
       </c>
-      <c r="G13">
-        <v>0</v>
-      </c>
       <c r="H13">
-        <v>37031</v>
+        <v>0</v>
       </c>
       <c r="I13">
         <v>0</v>
@@ -1399,39 +1363,36 @@
         <v>0</v>
       </c>
       <c r="L13">
-        <v>0</v>
+        <v>7864</v>
       </c>
       <c r="M13">
-        <v>7864</v>
+        <v>258</v>
       </c>
       <c r="N13">
-        <v>258</v>
+        <v>3822</v>
       </c>
       <c r="O13">
-        <v>3822</v>
+        <v>33237</v>
       </c>
       <c r="P13">
-        <v>33237</v>
+        <v>56564</v>
       </c>
       <c r="Q13">
-        <v>56564</v>
-      </c>
-      <c r="R13" s="2">
         <v>16237</v>
       </c>
-      <c r="S13" s="2">
-        <v>0</v>
-      </c>
-      <c r="T13" s="2">
+      <c r="R13">
+        <v>0</v>
+      </c>
+      <c r="S13">
         <v>106</v>
       </c>
     </row>
-    <row r="14" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>11</v>
       </c>
       <c r="B14" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C14">
         <v>48966</v>
@@ -1440,16 +1401,16 @@
         <v>0</v>
       </c>
       <c r="E14">
-        <v>0</v>
+        <v>48966</v>
       </c>
       <c r="F14">
+        <v>0</v>
+      </c>
+      <c r="G14">
         <v>48966</v>
       </c>
-      <c r="G14">
-        <v>0</v>
-      </c>
       <c r="H14">
-        <v>48966</v>
+        <v>0</v>
       </c>
       <c r="I14">
         <v>0</v>
@@ -1461,39 +1422,36 @@
         <v>0</v>
       </c>
       <c r="L14">
-        <v>0</v>
+        <v>15267</v>
       </c>
       <c r="M14">
-        <v>15267</v>
+        <v>1456</v>
       </c>
       <c r="N14">
-        <v>1456</v>
+        <v>5867</v>
       </c>
       <c r="O14">
-        <v>5867</v>
+        <v>43099</v>
       </c>
       <c r="P14">
-        <v>43099</v>
+        <v>77955</v>
       </c>
       <c r="Q14">
-        <v>77955</v>
-      </c>
-      <c r="R14" s="2">
         <v>19716</v>
       </c>
-      <c r="S14" s="2">
-        <v>0</v>
-      </c>
-      <c r="T14" s="2">
+      <c r="R14">
+        <v>0</v>
+      </c>
+      <c r="S14">
         <v>174</v>
       </c>
     </row>
-    <row r="15" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>12</v>
       </c>
       <c r="B15" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C15">
         <v>42703</v>
@@ -1502,16 +1460,16 @@
         <v>0</v>
       </c>
       <c r="E15">
-        <v>0</v>
+        <v>42703</v>
       </c>
       <c r="F15">
+        <v>0</v>
+      </c>
+      <c r="G15">
         <v>42703</v>
       </c>
-      <c r="G15">
-        <v>0</v>
-      </c>
       <c r="H15">
-        <v>42703</v>
+        <v>0</v>
       </c>
       <c r="I15">
         <v>0</v>
@@ -1523,39 +1481,36 @@
         <v>0</v>
       </c>
       <c r="L15">
-        <v>0</v>
+        <v>9192</v>
       </c>
       <c r="M15">
-        <v>9192</v>
+        <v>0</v>
       </c>
       <c r="N15">
-        <v>0</v>
+        <v>2821</v>
       </c>
       <c r="O15">
-        <v>2821</v>
+        <v>39882</v>
       </c>
       <c r="P15">
-        <v>39882</v>
+        <v>67183</v>
       </c>
       <c r="Q15">
-        <v>67183</v>
-      </c>
-      <c r="R15" s="2">
         <v>4859</v>
       </c>
-      <c r="S15" s="2">
-        <v>0</v>
-      </c>
-      <c r="T15" s="2">
+      <c r="R15">
+        <v>0</v>
+      </c>
+      <c r="S15">
         <v>50</v>
       </c>
     </row>
-    <row r="16" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>13</v>
       </c>
       <c r="B16" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C16">
         <v>25549</v>
@@ -1564,16 +1519,16 @@
         <v>0</v>
       </c>
       <c r="E16">
-        <v>0</v>
+        <v>25549</v>
       </c>
       <c r="F16">
-        <v>25549</v>
+        <v>0</v>
       </c>
       <c r="G16">
-        <v>0</v>
+        <v>25547</v>
       </c>
       <c r="H16">
-        <v>25547</v>
+        <v>0</v>
       </c>
       <c r="I16">
         <v>0</v>
@@ -1585,39 +1540,36 @@
         <v>0</v>
       </c>
       <c r="L16">
-        <v>0</v>
+        <v>14861</v>
       </c>
       <c r="M16">
-        <v>14861</v>
+        <v>1</v>
       </c>
       <c r="N16">
-        <v>1</v>
+        <v>261</v>
       </c>
       <c r="O16">
-        <v>261</v>
+        <v>25289</v>
       </c>
       <c r="P16">
-        <v>25289</v>
+        <v>71673</v>
       </c>
       <c r="Q16">
-        <v>71673</v>
-      </c>
-      <c r="R16" s="2">
         <v>5197</v>
       </c>
-      <c r="S16" s="2">
-        <v>0</v>
-      </c>
-      <c r="T16" s="2">
+      <c r="R16">
+        <v>0</v>
+      </c>
+      <c r="S16">
         <v>47</v>
       </c>
     </row>
-    <row r="17" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>14</v>
       </c>
       <c r="B17" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C17">
         <v>27707</v>
@@ -1626,16 +1578,16 @@
         <v>0</v>
       </c>
       <c r="E17">
-        <v>0</v>
+        <v>27707</v>
       </c>
       <c r="F17">
+        <v>0</v>
+      </c>
+      <c r="G17">
         <v>27707</v>
       </c>
-      <c r="G17">
-        <v>0</v>
-      </c>
       <c r="H17">
-        <v>27707</v>
+        <v>0</v>
       </c>
       <c r="I17">
         <v>0</v>
@@ -1647,39 +1599,36 @@
         <v>0</v>
       </c>
       <c r="L17">
-        <v>0</v>
+        <v>9287</v>
       </c>
       <c r="M17">
-        <v>9287</v>
+        <v>2</v>
       </c>
       <c r="N17">
-        <v>2</v>
+        <v>426</v>
       </c>
       <c r="O17">
-        <v>426</v>
+        <v>27282</v>
       </c>
       <c r="P17">
-        <v>27282</v>
+        <v>65457</v>
       </c>
       <c r="Q17">
-        <v>65457</v>
-      </c>
-      <c r="R17" s="2">
         <v>5417</v>
       </c>
-      <c r="S17" s="2">
-        <v>0</v>
-      </c>
-      <c r="T17" s="2">
+      <c r="R17">
+        <v>0</v>
+      </c>
+      <c r="S17">
         <v>105</v>
       </c>
     </row>
-    <row r="18" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>15</v>
       </c>
       <c r="B18" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C18">
         <v>47836</v>
@@ -1688,16 +1637,16 @@
         <v>0</v>
       </c>
       <c r="E18">
-        <v>0</v>
+        <v>47836</v>
       </c>
       <c r="F18">
+        <v>0</v>
+      </c>
+      <c r="G18">
         <v>47836</v>
       </c>
-      <c r="G18">
-        <v>0</v>
-      </c>
       <c r="H18">
-        <v>47836</v>
+        <v>0</v>
       </c>
       <c r="I18">
         <v>0</v>
@@ -1709,39 +1658,36 @@
         <v>0</v>
       </c>
       <c r="L18">
-        <v>0</v>
+        <v>7876</v>
       </c>
       <c r="M18">
-        <v>7876</v>
+        <v>3</v>
       </c>
       <c r="N18">
-        <v>3</v>
+        <v>1970</v>
       </c>
       <c r="O18">
-        <v>1970</v>
+        <v>45866</v>
       </c>
       <c r="P18">
-        <v>45866</v>
+        <v>71496</v>
       </c>
       <c r="Q18">
-        <v>71496</v>
-      </c>
-      <c r="R18" s="2">
         <v>6819</v>
       </c>
-      <c r="S18" s="2">
-        <v>0</v>
-      </c>
-      <c r="T18" s="2">
+      <c r="R18">
+        <v>0</v>
+      </c>
+      <c r="S18">
         <v>32</v>
       </c>
     </row>
-    <row r="19" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>16</v>
       </c>
       <c r="B19" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C19">
         <v>56490</v>
@@ -1750,16 +1696,16 @@
         <v>0</v>
       </c>
       <c r="E19">
-        <v>0</v>
+        <v>56490</v>
       </c>
       <c r="F19">
+        <v>0</v>
+      </c>
+      <c r="G19">
         <v>56490</v>
       </c>
-      <c r="G19">
-        <v>0</v>
-      </c>
       <c r="H19">
-        <v>56490</v>
+        <v>0</v>
       </c>
       <c r="I19">
         <v>0</v>
@@ -1771,39 +1717,36 @@
         <v>0</v>
       </c>
       <c r="L19">
-        <v>0</v>
+        <v>15286</v>
       </c>
       <c r="M19">
-        <v>15286</v>
+        <v>1</v>
       </c>
       <c r="N19">
-        <v>1</v>
+        <v>912</v>
       </c>
       <c r="O19">
-        <v>912</v>
+        <v>55578</v>
       </c>
       <c r="P19">
-        <v>55578</v>
+        <v>106392</v>
       </c>
       <c r="Q19">
-        <v>106392</v>
-      </c>
-      <c r="R19" s="2">
         <v>6135</v>
       </c>
-      <c r="S19" s="2">
-        <v>0</v>
-      </c>
-      <c r="T19" s="2">
+      <c r="R19">
+        <v>0</v>
+      </c>
+      <c r="S19">
         <v>36</v>
       </c>
     </row>
-    <row r="20" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>17</v>
       </c>
       <c r="B20" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C20">
         <v>35022</v>
@@ -1812,16 +1755,16 @@
         <v>0</v>
       </c>
       <c r="E20">
-        <v>0</v>
+        <v>35022</v>
       </c>
       <c r="F20">
+        <v>0</v>
+      </c>
+      <c r="G20">
         <v>35022</v>
       </c>
-      <c r="G20">
-        <v>0</v>
-      </c>
       <c r="H20">
-        <v>35022</v>
+        <v>0</v>
       </c>
       <c r="I20">
         <v>0</v>
@@ -1833,39 +1776,36 @@
         <v>0</v>
       </c>
       <c r="L20">
-        <v>0</v>
+        <v>6093</v>
       </c>
       <c r="M20">
-        <v>6093</v>
+        <v>5</v>
       </c>
       <c r="N20">
-        <v>5</v>
+        <v>546</v>
       </c>
       <c r="O20">
-        <v>546</v>
+        <v>34477</v>
       </c>
       <c r="P20">
-        <v>34477</v>
+        <v>75814</v>
       </c>
       <c r="Q20">
-        <v>75814</v>
-      </c>
-      <c r="R20" s="2">
         <v>8984</v>
       </c>
-      <c r="S20" s="2">
-        <v>0</v>
-      </c>
-      <c r="T20" s="2">
+      <c r="R20">
+        <v>0</v>
+      </c>
+      <c r="S20">
         <v>71</v>
       </c>
     </row>
-    <row r="21" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>18</v>
       </c>
       <c r="B21" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C21">
         <v>16962</v>
@@ -1874,16 +1814,16 @@
         <v>0</v>
       </c>
       <c r="E21">
-        <v>0</v>
+        <v>16962</v>
       </c>
       <c r="F21">
+        <v>0</v>
+      </c>
+      <c r="G21">
         <v>16962</v>
       </c>
-      <c r="G21">
-        <v>0</v>
-      </c>
       <c r="H21">
-        <v>16962</v>
+        <v>0</v>
       </c>
       <c r="I21">
         <v>0</v>
@@ -1895,39 +1835,36 @@
         <v>0</v>
       </c>
       <c r="L21">
-        <v>0</v>
+        <v>4030</v>
       </c>
       <c r="M21">
-        <v>4030</v>
+        <v>3</v>
       </c>
       <c r="N21">
-        <v>3</v>
+        <v>171</v>
       </c>
       <c r="O21">
-        <v>171</v>
+        <v>16791</v>
       </c>
       <c r="P21">
-        <v>16791</v>
+        <v>62460</v>
       </c>
       <c r="Q21">
-        <v>62460</v>
-      </c>
-      <c r="R21" s="2">
         <v>3868</v>
       </c>
-      <c r="S21" s="2">
-        <v>0</v>
-      </c>
-      <c r="T21" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="R21">
+        <v>0</v>
+      </c>
+      <c r="S21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>19</v>
       </c>
       <c r="B22" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C22">
         <v>18668</v>
@@ -1936,16 +1873,16 @@
         <v>0</v>
       </c>
       <c r="E22">
-        <v>0</v>
+        <v>18668</v>
       </c>
       <c r="F22">
+        <v>0</v>
+      </c>
+      <c r="G22">
         <v>18668</v>
       </c>
-      <c r="G22">
-        <v>0</v>
-      </c>
       <c r="H22">
-        <v>18668</v>
+        <v>0</v>
       </c>
       <c r="I22">
         <v>0</v>
@@ -1957,39 +1894,36 @@
         <v>0</v>
       </c>
       <c r="L22">
-        <v>0</v>
+        <v>7665</v>
       </c>
       <c r="M22">
-        <v>7665</v>
+        <v>0</v>
       </c>
       <c r="N22">
-        <v>0</v>
+        <v>302</v>
       </c>
       <c r="O22">
-        <v>302</v>
+        <v>18366</v>
       </c>
       <c r="P22">
-        <v>18366</v>
+        <v>64099</v>
       </c>
       <c r="Q22">
-        <v>64099</v>
-      </c>
-      <c r="R22" s="2">
         <v>4848</v>
       </c>
-      <c r="S22" s="2">
-        <v>0</v>
-      </c>
-      <c r="T22" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="R22">
+        <v>0</v>
+      </c>
+      <c r="S22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>20</v>
       </c>
       <c r="B23" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C23">
         <v>12020</v>
@@ -1998,16 +1932,16 @@
         <v>0</v>
       </c>
       <c r="E23">
-        <v>0</v>
+        <v>12020</v>
       </c>
       <c r="F23">
+        <v>0</v>
+      </c>
+      <c r="G23">
         <v>12020</v>
       </c>
-      <c r="G23">
-        <v>0</v>
-      </c>
       <c r="H23">
-        <v>12020</v>
+        <v>0</v>
       </c>
       <c r="I23">
         <v>0</v>
@@ -2019,39 +1953,36 @@
         <v>0</v>
       </c>
       <c r="L23">
-        <v>0</v>
+        <v>2113</v>
       </c>
       <c r="M23">
-        <v>2113</v>
+        <v>0</v>
       </c>
       <c r="N23">
-        <v>0</v>
+        <v>108</v>
       </c>
       <c r="O23">
-        <v>108</v>
+        <v>11912</v>
       </c>
       <c r="P23">
-        <v>11912</v>
+        <v>57094</v>
       </c>
       <c r="Q23">
-        <v>57094</v>
-      </c>
-      <c r="R23" s="2">
         <v>3541</v>
       </c>
-      <c r="S23" s="2">
-        <v>0</v>
-      </c>
-      <c r="T23" s="2">
+      <c r="R23">
+        <v>0</v>
+      </c>
+      <c r="S23">
         <v>28</v>
       </c>
     </row>
-    <row r="24" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>21</v>
       </c>
       <c r="B24" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C24">
         <v>14056</v>
@@ -2060,16 +1991,16 @@
         <v>0</v>
       </c>
       <c r="E24">
-        <v>0</v>
+        <v>14056</v>
       </c>
       <c r="F24">
+        <v>0</v>
+      </c>
+      <c r="G24">
         <v>14056</v>
       </c>
-      <c r="G24">
-        <v>0</v>
-      </c>
       <c r="H24">
-        <v>14056</v>
+        <v>0</v>
       </c>
       <c r="I24">
         <v>0</v>
@@ -2081,39 +2012,36 @@
         <v>0</v>
       </c>
       <c r="L24">
-        <v>0</v>
+        <v>3482</v>
       </c>
       <c r="M24">
-        <v>3482</v>
+        <v>5</v>
       </c>
       <c r="N24">
-        <v>5</v>
+        <v>231</v>
       </c>
       <c r="O24">
-        <v>231</v>
+        <v>13825</v>
       </c>
       <c r="P24">
-        <v>13825</v>
+        <v>65629</v>
       </c>
       <c r="Q24">
-        <v>65629</v>
-      </c>
-      <c r="R24" s="2">
         <v>3492</v>
       </c>
-      <c r="S24" s="2">
-        <v>0</v>
-      </c>
-      <c r="T24" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="R24">
+        <v>0</v>
+      </c>
+      <c r="S24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>22</v>
       </c>
       <c r="B25" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C25">
         <v>19266</v>
@@ -2122,16 +2050,16 @@
         <v>0</v>
       </c>
       <c r="E25">
-        <v>0</v>
+        <v>19266</v>
       </c>
       <c r="F25">
+        <v>0</v>
+      </c>
+      <c r="G25">
         <v>19266</v>
       </c>
-      <c r="G25">
-        <v>0</v>
-      </c>
       <c r="H25">
-        <v>19266</v>
+        <v>0</v>
       </c>
       <c r="I25">
         <v>0</v>
@@ -2143,39 +2071,36 @@
         <v>0</v>
       </c>
       <c r="L25">
-        <v>0</v>
+        <v>4862</v>
       </c>
       <c r="M25">
-        <v>4862</v>
+        <v>0</v>
       </c>
       <c r="N25">
-        <v>0</v>
+        <v>298</v>
       </c>
       <c r="O25">
-        <v>298</v>
+        <v>18968</v>
       </c>
       <c r="P25">
-        <v>18968</v>
+        <v>57533</v>
       </c>
       <c r="Q25">
-        <v>57533</v>
-      </c>
-      <c r="R25" s="2">
         <v>3231</v>
       </c>
-      <c r="S25" s="2">
-        <v>0</v>
-      </c>
-      <c r="T25" s="2">
+      <c r="R25">
+        <v>0</v>
+      </c>
+      <c r="S25">
         <v>13</v>
       </c>
     </row>
-    <row r="26" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>23</v>
       </c>
       <c r="B26" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C26">
         <v>17557</v>
@@ -2184,16 +2109,16 @@
         <v>0</v>
       </c>
       <c r="E26">
-        <v>0</v>
+        <v>17557</v>
       </c>
       <c r="F26">
+        <v>0</v>
+      </c>
+      <c r="G26">
         <v>17557</v>
       </c>
-      <c r="G26">
-        <v>0</v>
-      </c>
       <c r="H26">
-        <v>17557</v>
+        <v>0</v>
       </c>
       <c r="I26">
         <v>0</v>
@@ -2205,39 +2130,36 @@
         <v>0</v>
       </c>
       <c r="L26">
-        <v>0</v>
+        <v>3741</v>
       </c>
       <c r="M26">
-        <v>3741</v>
+        <v>3</v>
       </c>
       <c r="N26">
-        <v>3</v>
+        <v>194</v>
       </c>
       <c r="O26">
-        <v>194</v>
+        <v>17363</v>
       </c>
       <c r="P26">
-        <v>17363</v>
+        <v>66594</v>
       </c>
       <c r="Q26">
-        <v>66594</v>
-      </c>
-      <c r="R26" s="2">
         <v>3333</v>
       </c>
-      <c r="S26" s="2">
-        <v>0</v>
-      </c>
-      <c r="T26" s="2">
+      <c r="R26">
+        <v>0</v>
+      </c>
+      <c r="S26">
         <v>2</v>
       </c>
     </row>
-    <row r="27" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>24</v>
       </c>
       <c r="B27" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C27">
         <v>44276</v>
@@ -2246,16 +2168,16 @@
         <v>0</v>
       </c>
       <c r="E27">
-        <v>0</v>
+        <v>44276</v>
       </c>
       <c r="F27">
+        <v>0</v>
+      </c>
+      <c r="G27">
         <v>44276</v>
       </c>
-      <c r="G27">
-        <v>0</v>
-      </c>
       <c r="H27">
-        <v>44276</v>
+        <v>0</v>
       </c>
       <c r="I27">
         <v>0</v>
@@ -2267,39 +2189,36 @@
         <v>0</v>
       </c>
       <c r="L27">
-        <v>0</v>
+        <v>9679</v>
       </c>
       <c r="M27">
-        <v>9679</v>
+        <v>215</v>
       </c>
       <c r="N27">
-        <v>215</v>
+        <v>3287</v>
       </c>
       <c r="O27">
-        <v>3287</v>
+        <v>41005</v>
       </c>
       <c r="P27">
-        <v>41005</v>
+        <v>73109</v>
       </c>
       <c r="Q27">
-        <v>73109</v>
-      </c>
-      <c r="R27" s="2">
         <v>12669</v>
       </c>
-      <c r="S27" s="2">
-        <v>0</v>
-      </c>
-      <c r="T27" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="R27">
+        <v>0</v>
+      </c>
+      <c r="S27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>25</v>
       </c>
       <c r="B28" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C28">
         <v>54349</v>
@@ -2308,16 +2227,16 @@
         <v>0</v>
       </c>
       <c r="E28">
-        <v>0</v>
+        <v>54349</v>
       </c>
       <c r="F28">
+        <v>0</v>
+      </c>
+      <c r="G28">
         <v>54349</v>
       </c>
-      <c r="G28">
-        <v>0</v>
-      </c>
       <c r="H28">
-        <v>54349</v>
+        <v>0</v>
       </c>
       <c r="I28">
         <v>0</v>
@@ -2329,39 +2248,36 @@
         <v>0</v>
       </c>
       <c r="L28">
-        <v>0</v>
+        <v>8879</v>
       </c>
       <c r="M28">
-        <v>8879</v>
+        <v>856</v>
       </c>
       <c r="N28">
-        <v>856</v>
+        <v>3525</v>
       </c>
       <c r="O28">
-        <v>3525</v>
+        <v>50844</v>
       </c>
       <c r="P28">
-        <v>50844</v>
+        <v>80620</v>
       </c>
       <c r="Q28">
-        <v>80620</v>
-      </c>
-      <c r="R28" s="2">
         <v>13995</v>
       </c>
-      <c r="S28" s="2">
-        <v>0</v>
-      </c>
-      <c r="T28" s="2">
+      <c r="R28">
+        <v>0</v>
+      </c>
+      <c r="S28">
         <v>127</v>
       </c>
     </row>
-    <row r="29" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>26</v>
       </c>
       <c r="B29" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C29">
         <v>47111</v>
@@ -2370,16 +2286,16 @@
         <v>0</v>
       </c>
       <c r="E29">
-        <v>0</v>
+        <v>47111</v>
       </c>
       <c r="F29">
+        <v>0</v>
+      </c>
+      <c r="G29">
         <v>47111</v>
       </c>
-      <c r="G29">
-        <v>0</v>
-      </c>
       <c r="H29">
-        <v>47111</v>
+        <v>0</v>
       </c>
       <c r="I29">
         <v>0</v>
@@ -2391,39 +2307,36 @@
         <v>0</v>
       </c>
       <c r="L29">
-        <v>0</v>
+        <v>8816</v>
       </c>
       <c r="M29">
-        <v>8816</v>
+        <v>318</v>
       </c>
       <c r="N29">
-        <v>318</v>
+        <v>4592</v>
       </c>
       <c r="O29">
-        <v>4592</v>
+        <v>42520</v>
       </c>
       <c r="P29">
-        <v>42520</v>
+        <v>83836</v>
       </c>
       <c r="Q29">
-        <v>83836</v>
-      </c>
-      <c r="R29" s="2">
         <v>14229</v>
       </c>
-      <c r="S29" s="2">
-        <v>0</v>
-      </c>
-      <c r="T29" s="2">
+      <c r="R29">
+        <v>0</v>
+      </c>
+      <c r="S29">
         <v>22</v>
       </c>
     </row>
-    <row r="30" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>27</v>
       </c>
       <c r="B30" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C30">
         <v>52653</v>
@@ -2432,16 +2345,16 @@
         <v>0</v>
       </c>
       <c r="E30">
-        <v>0</v>
+        <v>52653</v>
       </c>
       <c r="F30">
+        <v>0</v>
+      </c>
+      <c r="G30">
         <v>52653</v>
       </c>
-      <c r="G30">
-        <v>0</v>
-      </c>
       <c r="H30">
-        <v>52653</v>
+        <v>0</v>
       </c>
       <c r="I30">
         <v>0</v>
@@ -2453,39 +2366,36 @@
         <v>0</v>
       </c>
       <c r="L30">
-        <v>0</v>
+        <v>11659</v>
       </c>
       <c r="M30">
-        <v>11659</v>
+        <v>411</v>
       </c>
       <c r="N30">
-        <v>411</v>
+        <v>5383</v>
       </c>
       <c r="O30">
-        <v>5383</v>
+        <v>47272</v>
       </c>
       <c r="P30">
-        <v>47272</v>
+        <v>86933</v>
       </c>
       <c r="Q30">
-        <v>86933</v>
-      </c>
-      <c r="R30" s="2">
         <v>12564</v>
       </c>
-      <c r="S30" s="2">
-        <v>0</v>
-      </c>
-      <c r="T30" s="2">
+      <c r="R30">
+        <v>0</v>
+      </c>
+      <c r="S30">
         <v>8</v>
       </c>
     </row>
-    <row r="31" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>28</v>
       </c>
       <c r="B31" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C31">
         <v>91162</v>
@@ -2494,16 +2404,16 @@
         <v>0</v>
       </c>
       <c r="E31">
-        <v>0</v>
+        <v>91162</v>
       </c>
       <c r="F31">
+        <v>0</v>
+      </c>
+      <c r="G31">
         <v>91162</v>
       </c>
-      <c r="G31">
-        <v>0</v>
-      </c>
       <c r="H31">
-        <v>91162</v>
+        <v>0</v>
       </c>
       <c r="I31">
         <v>0</v>
@@ -2515,39 +2425,36 @@
         <v>0</v>
       </c>
       <c r="L31">
-        <v>0</v>
+        <v>46718</v>
       </c>
       <c r="M31">
-        <v>46718</v>
+        <v>42</v>
       </c>
       <c r="N31">
-        <v>42</v>
+        <v>1899</v>
       </c>
       <c r="O31">
-        <v>1899</v>
+        <v>89264</v>
       </c>
       <c r="P31">
-        <v>89264</v>
+        <v>81642</v>
       </c>
       <c r="Q31">
-        <v>81642</v>
-      </c>
-      <c r="R31" s="2">
         <v>14581</v>
       </c>
-      <c r="S31" s="2">
-        <v>0</v>
-      </c>
-      <c r="T31" s="2">
+      <c r="R31">
+        <v>0</v>
+      </c>
+      <c r="S31">
         <v>39</v>
       </c>
     </row>
-    <row r="32" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>29</v>
       </c>
       <c r="B32" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C32">
         <v>46728</v>
@@ -2556,16 +2463,16 @@
         <v>0</v>
       </c>
       <c r="E32">
-        <v>0</v>
+        <v>46728</v>
       </c>
       <c r="F32">
+        <v>0</v>
+      </c>
+      <c r="G32">
         <v>46728</v>
       </c>
-      <c r="G32">
-        <v>0</v>
-      </c>
       <c r="H32">
-        <v>46728</v>
+        <v>0</v>
       </c>
       <c r="I32">
         <v>0</v>
@@ -2577,39 +2484,36 @@
         <v>0</v>
       </c>
       <c r="L32">
-        <v>0</v>
+        <v>10557</v>
       </c>
       <c r="M32">
-        <v>10557</v>
+        <v>316</v>
       </c>
       <c r="N32">
-        <v>316</v>
+        <v>4391</v>
       </c>
       <c r="O32">
-        <v>4391</v>
+        <v>42344</v>
       </c>
       <c r="P32">
-        <v>42344</v>
+        <v>74810</v>
       </c>
       <c r="Q32">
-        <v>74810</v>
-      </c>
-      <c r="R32" s="2">
         <v>11379</v>
       </c>
-      <c r="S32" s="2">
-        <v>0</v>
-      </c>
-      <c r="T32" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="R32">
+        <v>0</v>
+      </c>
+      <c r="S32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>30</v>
       </c>
       <c r="B33" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C33">
         <v>40230</v>
@@ -2618,16 +2522,16 @@
         <v>0</v>
       </c>
       <c r="E33">
-        <v>0</v>
+        <v>40230</v>
       </c>
       <c r="F33">
+        <v>0</v>
+      </c>
+      <c r="G33">
         <v>40230</v>
       </c>
-      <c r="G33">
-        <v>0</v>
-      </c>
       <c r="H33">
-        <v>40230</v>
+        <v>0</v>
       </c>
       <c r="I33">
         <v>0</v>
@@ -2639,39 +2543,36 @@
         <v>0</v>
       </c>
       <c r="L33">
-        <v>0</v>
+        <v>5113</v>
       </c>
       <c r="M33">
-        <v>5113</v>
+        <v>311</v>
       </c>
       <c r="N33">
-        <v>311</v>
+        <v>1275</v>
       </c>
       <c r="O33">
-        <v>1275</v>
+        <v>38955</v>
       </c>
       <c r="P33">
-        <v>38955</v>
+        <v>76969</v>
       </c>
       <c r="Q33">
-        <v>76969</v>
-      </c>
-      <c r="R33" s="2">
         <v>6678</v>
       </c>
-      <c r="S33" s="2">
-        <v>0</v>
-      </c>
-      <c r="T33" s="2">
+      <c r="R33">
+        <v>0</v>
+      </c>
+      <c r="S33">
         <v>19</v>
       </c>
     </row>
-    <row r="34" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>31</v>
       </c>
       <c r="B34" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C34">
         <v>36542</v>
@@ -2680,16 +2581,16 @@
         <v>0</v>
       </c>
       <c r="E34">
-        <v>0</v>
+        <v>36542</v>
       </c>
       <c r="F34">
+        <v>0</v>
+      </c>
+      <c r="G34">
         <v>36542</v>
       </c>
-      <c r="G34">
-        <v>0</v>
-      </c>
       <c r="H34">
-        <v>36542</v>
+        <v>0</v>
       </c>
       <c r="I34">
         <v>0</v>
@@ -2701,39 +2602,36 @@
         <v>0</v>
       </c>
       <c r="L34">
-        <v>0</v>
+        <v>12439</v>
       </c>
       <c r="M34">
-        <v>12439</v>
+        <v>513</v>
       </c>
       <c r="N34">
-        <v>513</v>
+        <v>1363</v>
       </c>
       <c r="O34">
-        <v>1363</v>
+        <v>35181</v>
       </c>
       <c r="P34">
-        <v>35181</v>
+        <v>74624</v>
       </c>
       <c r="Q34">
-        <v>74624</v>
-      </c>
-      <c r="R34" s="2">
         <v>7137</v>
       </c>
-      <c r="S34" s="2">
-        <v>0</v>
-      </c>
-      <c r="T34" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="R34">
+        <v>0</v>
+      </c>
+      <c r="S34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>32</v>
       </c>
       <c r="B35" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C35">
         <v>33564</v>
@@ -2742,16 +2640,16 @@
         <v>0</v>
       </c>
       <c r="E35">
-        <v>0</v>
+        <v>33564</v>
       </c>
       <c r="F35">
+        <v>0</v>
+      </c>
+      <c r="G35">
         <v>33564</v>
       </c>
-      <c r="G35">
-        <v>0</v>
-      </c>
       <c r="H35">
-        <v>33564</v>
+        <v>0</v>
       </c>
       <c r="I35">
         <v>0</v>
@@ -2763,39 +2661,36 @@
         <v>0</v>
       </c>
       <c r="L35">
-        <v>0</v>
+        <v>7886</v>
       </c>
       <c r="M35">
-        <v>7886</v>
+        <v>271</v>
       </c>
       <c r="N35">
-        <v>271</v>
+        <v>1141</v>
       </c>
       <c r="O35">
-        <v>1141</v>
+        <v>32426</v>
       </c>
       <c r="P35">
-        <v>32426</v>
+        <v>76462</v>
       </c>
       <c r="Q35">
-        <v>76462</v>
-      </c>
-      <c r="R35" s="2">
         <v>8879</v>
       </c>
-      <c r="S35" s="2">
-        <v>0</v>
-      </c>
-      <c r="T35" s="2">
+      <c r="R35">
+        <v>0</v>
+      </c>
+      <c r="S35">
         <v>35</v>
       </c>
     </row>
-    <row r="36" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>33</v>
       </c>
       <c r="B36" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C36">
         <v>20905</v>
@@ -2804,16 +2699,16 @@
         <v>0</v>
       </c>
       <c r="E36">
-        <v>0</v>
+        <v>20905</v>
       </c>
       <c r="F36">
+        <v>0</v>
+      </c>
+      <c r="G36">
         <v>20905</v>
       </c>
-      <c r="G36">
-        <v>0</v>
-      </c>
       <c r="H36">
-        <v>20905</v>
+        <v>0</v>
       </c>
       <c r="I36">
         <v>0</v>
@@ -2825,39 +2720,36 @@
         <v>0</v>
       </c>
       <c r="L36">
-        <v>0</v>
+        <v>7350</v>
       </c>
       <c r="M36">
-        <v>7350</v>
+        <v>0</v>
       </c>
       <c r="N36">
-        <v>0</v>
+        <v>951</v>
       </c>
       <c r="O36">
-        <v>951</v>
+        <v>19954</v>
       </c>
       <c r="P36">
-        <v>19954</v>
+        <v>60419</v>
       </c>
       <c r="Q36">
-        <v>60419</v>
-      </c>
-      <c r="R36" s="2">
         <v>3855</v>
       </c>
-      <c r="S36" s="2">
-        <v>0</v>
-      </c>
-      <c r="T36" s="2">
+      <c r="R36">
+        <v>0</v>
+      </c>
+      <c r="S36">
         <v>2</v>
       </c>
     </row>
-    <row r="37" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>34</v>
       </c>
       <c r="B37" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C37">
         <v>17692</v>
@@ -2866,16 +2758,16 @@
         <v>0</v>
       </c>
       <c r="E37">
-        <v>0</v>
+        <v>17692</v>
       </c>
       <c r="F37">
+        <v>0</v>
+      </c>
+      <c r="G37">
         <v>17692</v>
       </c>
-      <c r="G37">
-        <v>0</v>
-      </c>
       <c r="H37">
-        <v>17692</v>
+        <v>0</v>
       </c>
       <c r="I37">
         <v>0</v>
@@ -2887,39 +2779,36 @@
         <v>0</v>
       </c>
       <c r="L37">
-        <v>0</v>
+        <v>2311</v>
       </c>
       <c r="M37">
-        <v>2311</v>
+        <v>0</v>
       </c>
       <c r="N37">
-        <v>0</v>
+        <v>541</v>
       </c>
       <c r="O37">
-        <v>541</v>
+        <v>17151</v>
       </c>
       <c r="P37">
-        <v>17151</v>
+        <v>57832</v>
       </c>
       <c r="Q37">
-        <v>57832</v>
-      </c>
-      <c r="R37" s="2">
         <v>4036</v>
       </c>
-      <c r="S37" s="2">
-        <v>0</v>
-      </c>
-      <c r="T37" s="2">
+      <c r="R37">
+        <v>0</v>
+      </c>
+      <c r="S37">
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>35</v>
       </c>
       <c r="B38" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C38">
         <v>29110</v>
@@ -2928,16 +2817,16 @@
         <v>0</v>
       </c>
       <c r="E38">
-        <v>1</v>
+        <v>29110</v>
       </c>
       <c r="F38">
+        <v>0</v>
+      </c>
+      <c r="G38">
         <v>29110</v>
       </c>
-      <c r="G38">
-        <v>0</v>
-      </c>
       <c r="H38">
-        <v>29110</v>
+        <v>0</v>
       </c>
       <c r="I38">
         <v>0</v>
@@ -2949,39 +2838,36 @@
         <v>0</v>
       </c>
       <c r="L38">
-        <v>0</v>
+        <v>5386</v>
       </c>
       <c r="M38">
-        <v>5386</v>
+        <v>2</v>
       </c>
       <c r="N38">
-        <v>2</v>
+        <v>635</v>
       </c>
       <c r="O38">
-        <v>635</v>
+        <v>28475</v>
       </c>
       <c r="P38">
-        <v>28475</v>
+        <v>63038</v>
       </c>
       <c r="Q38">
-        <v>63038</v>
-      </c>
-      <c r="R38" s="2">
         <v>5135</v>
       </c>
-      <c r="S38" s="2">
-        <v>0</v>
-      </c>
-      <c r="T38" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="39" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="R38">
+        <v>0</v>
+      </c>
+      <c r="S38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>36</v>
       </c>
       <c r="B39" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C39">
         <v>21367</v>
@@ -2990,16 +2876,16 @@
         <v>0</v>
       </c>
       <c r="E39">
-        <v>0</v>
+        <v>21367</v>
       </c>
       <c r="F39">
+        <v>0</v>
+      </c>
+      <c r="G39">
         <v>21367</v>
       </c>
-      <c r="G39">
-        <v>0</v>
-      </c>
       <c r="H39">
-        <v>21367</v>
+        <v>0</v>
       </c>
       <c r="I39">
         <v>0</v>
@@ -3011,39 +2897,36 @@
         <v>0</v>
       </c>
       <c r="L39">
-        <v>0</v>
+        <v>4529</v>
       </c>
       <c r="M39">
-        <v>4529</v>
+        <v>1</v>
       </c>
       <c r="N39">
-        <v>1</v>
+        <v>234</v>
       </c>
       <c r="O39">
-        <v>234</v>
+        <v>21133</v>
       </c>
       <c r="P39">
-        <v>21133</v>
+        <v>71133</v>
       </c>
       <c r="Q39">
-        <v>71133</v>
-      </c>
-      <c r="R39" s="2">
         <v>5903</v>
       </c>
-      <c r="S39" s="2">
-        <v>0</v>
-      </c>
-      <c r="T39" s="2">
+      <c r="R39">
+        <v>0</v>
+      </c>
+      <c r="S39">
         <v>26</v>
       </c>
     </row>
-    <row r="40" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>37</v>
       </c>
       <c r="B40" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C40">
         <v>18905</v>
@@ -3052,16 +2935,16 @@
         <v>0</v>
       </c>
       <c r="E40">
-        <v>0</v>
+        <v>18905</v>
       </c>
       <c r="F40">
+        <v>0</v>
+      </c>
+      <c r="G40">
         <v>18905</v>
       </c>
-      <c r="G40">
-        <v>0</v>
-      </c>
       <c r="H40">
-        <v>18905</v>
+        <v>0</v>
       </c>
       <c r="I40">
         <v>0</v>
@@ -3073,39 +2956,36 @@
         <v>0</v>
       </c>
       <c r="L40">
-        <v>0</v>
+        <v>1812</v>
       </c>
       <c r="M40">
-        <v>1812</v>
+        <v>0</v>
       </c>
       <c r="N40">
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="O40">
-        <v>52</v>
+        <v>18853</v>
       </c>
       <c r="P40">
-        <v>18853</v>
+        <v>73242</v>
       </c>
       <c r="Q40">
-        <v>73242</v>
-      </c>
-      <c r="R40" s="2">
         <v>3824</v>
       </c>
-      <c r="S40" s="2">
-        <v>0</v>
-      </c>
-      <c r="T40" s="2">
+      <c r="R40">
+        <v>0</v>
+      </c>
+      <c r="S40">
         <v>61</v>
       </c>
     </row>
-    <row r="41" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>38</v>
       </c>
       <c r="B41" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C41">
         <v>23521</v>
@@ -3114,16 +2994,16 @@
         <v>0</v>
       </c>
       <c r="E41">
-        <v>0</v>
+        <v>23521</v>
       </c>
       <c r="F41">
+        <v>0</v>
+      </c>
+      <c r="G41">
         <v>23521</v>
       </c>
-      <c r="G41">
-        <v>0</v>
-      </c>
       <c r="H41">
-        <v>23521</v>
+        <v>0</v>
       </c>
       <c r="I41">
         <v>0</v>
@@ -3135,39 +3015,36 @@
         <v>0</v>
       </c>
       <c r="L41">
-        <v>0</v>
+        <v>1499</v>
       </c>
       <c r="M41">
-        <v>1499</v>
+        <v>0</v>
       </c>
       <c r="N41">
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="O41">
-        <v>92</v>
+        <v>23429</v>
       </c>
       <c r="P41">
-        <v>23429</v>
+        <v>85251</v>
       </c>
       <c r="Q41">
-        <v>85251</v>
-      </c>
-      <c r="R41" s="2">
         <v>6015</v>
       </c>
-      <c r="S41" s="2">
-        <v>0</v>
-      </c>
-      <c r="T41" s="2">
+      <c r="R41">
+        <v>0</v>
+      </c>
+      <c r="S41">
         <v>27</v>
       </c>
     </row>
-    <row r="42" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>39</v>
       </c>
       <c r="B42" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C42">
         <v>27565</v>
@@ -3176,16 +3053,16 @@
         <v>0</v>
       </c>
       <c r="E42">
-        <v>0</v>
+        <v>27565</v>
       </c>
       <c r="F42">
+        <v>0</v>
+      </c>
+      <c r="G42">
         <v>27565</v>
       </c>
-      <c r="G42">
-        <v>0</v>
-      </c>
       <c r="H42">
-        <v>27565</v>
+        <v>0</v>
       </c>
       <c r="I42">
         <v>0</v>
@@ -3197,39 +3074,36 @@
         <v>0</v>
       </c>
       <c r="L42">
-        <v>0</v>
+        <v>6264</v>
       </c>
       <c r="M42">
-        <v>6264</v>
+        <v>0</v>
       </c>
       <c r="N42">
-        <v>0</v>
+        <v>419</v>
       </c>
       <c r="O42">
-        <v>419</v>
+        <v>27147</v>
       </c>
       <c r="P42">
-        <v>27147</v>
+        <v>68615</v>
       </c>
       <c r="Q42">
-        <v>68615</v>
-      </c>
-      <c r="R42" s="2">
         <v>4708</v>
       </c>
-      <c r="S42" s="2">
-        <v>0</v>
-      </c>
-      <c r="T42" s="2">
+      <c r="R42">
+        <v>0</v>
+      </c>
+      <c r="S42">
         <v>8</v>
       </c>
     </row>
-    <row r="43" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>40</v>
       </c>
       <c r="B43" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C43">
         <v>29700</v>
@@ -3238,16 +3112,16 @@
         <v>0</v>
       </c>
       <c r="E43">
-        <v>0</v>
+        <v>29700</v>
       </c>
       <c r="F43">
+        <v>0</v>
+      </c>
+      <c r="G43">
         <v>29700</v>
       </c>
-      <c r="G43">
-        <v>0</v>
-      </c>
       <c r="H43">
-        <v>29700</v>
+        <v>0</v>
       </c>
       <c r="I43">
         <v>0</v>
@@ -3259,39 +3133,36 @@
         <v>0</v>
       </c>
       <c r="L43">
-        <v>0</v>
+        <v>6804</v>
       </c>
       <c r="M43">
-        <v>6804</v>
+        <v>1</v>
       </c>
       <c r="N43">
-        <v>1</v>
+        <v>957</v>
       </c>
       <c r="O43">
-        <v>957</v>
+        <v>28774</v>
       </c>
       <c r="P43">
-        <v>28774</v>
+        <v>63012</v>
       </c>
       <c r="Q43">
-        <v>63012</v>
-      </c>
-      <c r="R43" s="2">
         <v>5219</v>
       </c>
-      <c r="S43" s="2">
-        <v>0</v>
-      </c>
-      <c r="T43" s="2">
+      <c r="R43">
+        <v>0</v>
+      </c>
+      <c r="S43">
         <v>121</v>
       </c>
     </row>
-    <row r="44" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A44">
         <v>41</v>
       </c>
       <c r="B44" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C44">
         <v>21900</v>
@@ -3300,16 +3171,16 @@
         <v>0</v>
       </c>
       <c r="E44">
-        <v>0</v>
+        <v>21900</v>
       </c>
       <c r="F44">
+        <v>0</v>
+      </c>
+      <c r="G44">
         <v>21900</v>
       </c>
-      <c r="G44">
-        <v>0</v>
-      </c>
       <c r="H44">
-        <v>21900</v>
+        <v>0</v>
       </c>
       <c r="I44">
         <v>0</v>
@@ -3321,39 +3192,36 @@
         <v>0</v>
       </c>
       <c r="L44">
-        <v>0</v>
+        <v>6643</v>
       </c>
       <c r="M44">
-        <v>6643</v>
+        <v>24</v>
       </c>
       <c r="N44">
-        <v>24</v>
+        <v>347</v>
       </c>
       <c r="O44">
-        <v>347</v>
+        <v>21553</v>
       </c>
       <c r="P44">
-        <v>21553</v>
+        <v>68393</v>
       </c>
       <c r="Q44">
-        <v>68393</v>
-      </c>
-      <c r="R44" s="2">
         <v>7659</v>
       </c>
-      <c r="S44" s="2">
-        <v>0</v>
-      </c>
-      <c r="T44" s="2">
+      <c r="R44">
+        <v>0</v>
+      </c>
+      <c r="S44">
         <v>20</v>
       </c>
     </row>
-    <row r="45" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A45">
         <v>42</v>
       </c>
       <c r="B45" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C45">
         <v>19935</v>
@@ -3362,16 +3230,16 @@
         <v>0</v>
       </c>
       <c r="E45">
-        <v>0</v>
+        <v>19935</v>
       </c>
       <c r="F45">
+        <v>0</v>
+      </c>
+      <c r="G45">
         <v>19935</v>
       </c>
-      <c r="G45">
-        <v>0</v>
-      </c>
       <c r="H45">
-        <v>19935</v>
+        <v>0</v>
       </c>
       <c r="I45">
         <v>0</v>
@@ -3383,39 +3251,36 @@
         <v>0</v>
       </c>
       <c r="L45">
-        <v>0</v>
+        <v>2254</v>
       </c>
       <c r="M45">
-        <v>2254</v>
+        <v>13</v>
       </c>
       <c r="N45">
-        <v>13</v>
+        <v>149</v>
       </c>
       <c r="O45">
-        <v>149</v>
+        <v>19786</v>
       </c>
       <c r="P45">
-        <v>19786</v>
+        <v>76287</v>
       </c>
       <c r="Q45">
-        <v>76287</v>
-      </c>
-      <c r="R45" s="2">
         <v>6998</v>
       </c>
-      <c r="S45" s="2">
-        <v>0</v>
-      </c>
-      <c r="T45" s="2">
+      <c r="R45">
+        <v>0</v>
+      </c>
+      <c r="S45">
         <v>129</v>
       </c>
     </row>
-    <row r="46" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A46">
         <v>43</v>
       </c>
       <c r="B46" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C46">
         <v>21512</v>
@@ -3424,16 +3289,16 @@
         <v>0</v>
       </c>
       <c r="E46">
-        <v>0</v>
+        <v>21512</v>
       </c>
       <c r="F46">
+        <v>0</v>
+      </c>
+      <c r="G46">
         <v>21512</v>
       </c>
-      <c r="G46">
-        <v>0</v>
-      </c>
       <c r="H46">
-        <v>21512</v>
+        <v>0</v>
       </c>
       <c r="I46">
         <v>0</v>
@@ -3445,39 +3310,36 @@
         <v>0</v>
       </c>
       <c r="L46">
-        <v>0</v>
+        <v>8303</v>
       </c>
       <c r="M46">
-        <v>8303</v>
+        <v>32</v>
       </c>
       <c r="N46">
-        <v>32</v>
+        <v>276</v>
       </c>
       <c r="O46">
-        <v>276</v>
+        <v>21236</v>
       </c>
       <c r="P46">
-        <v>21236</v>
+        <v>64160</v>
       </c>
       <c r="Q46">
-        <v>64160</v>
-      </c>
-      <c r="R46" s="2">
         <v>7548</v>
       </c>
-      <c r="S46" s="2">
-        <v>0</v>
-      </c>
-      <c r="T46" s="2">
+      <c r="R46">
+        <v>0</v>
+      </c>
+      <c r="S46">
         <v>152</v>
       </c>
     </row>
-    <row r="47" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A47">
         <v>44</v>
       </c>
       <c r="B47" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C47">
         <v>22426</v>
@@ -3486,16 +3348,16 @@
         <v>0</v>
       </c>
       <c r="E47">
-        <v>0</v>
+        <v>22426</v>
       </c>
       <c r="F47">
+        <v>0</v>
+      </c>
+      <c r="G47">
         <v>22426</v>
       </c>
-      <c r="G47">
-        <v>0</v>
-      </c>
       <c r="H47">
-        <v>22426</v>
+        <v>0</v>
       </c>
       <c r="I47">
         <v>0</v>
@@ -3507,39 +3369,36 @@
         <v>0</v>
       </c>
       <c r="L47">
-        <v>0</v>
+        <v>2595</v>
       </c>
       <c r="M47">
-        <v>2595</v>
+        <v>1</v>
       </c>
       <c r="N47">
-        <v>1</v>
+        <v>142</v>
       </c>
       <c r="O47">
-        <v>142</v>
+        <v>22284</v>
       </c>
       <c r="P47">
-        <v>22284</v>
+        <v>50821</v>
       </c>
       <c r="Q47">
-        <v>50821</v>
-      </c>
-      <c r="R47" s="2">
         <v>5046</v>
       </c>
-      <c r="S47" s="2">
-        <v>0</v>
-      </c>
-      <c r="T47" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="48" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="R47">
+        <v>0</v>
+      </c>
+      <c r="S47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A48">
         <v>45</v>
       </c>
       <c r="B48" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C48">
         <v>19641</v>
@@ -3548,16 +3407,16 @@
         <v>0</v>
       </c>
       <c r="E48">
-        <v>0</v>
+        <v>19641</v>
       </c>
       <c r="F48">
+        <v>0</v>
+      </c>
+      <c r="G48">
         <v>19641</v>
       </c>
-      <c r="G48">
-        <v>0</v>
-      </c>
       <c r="H48">
-        <v>19641</v>
+        <v>0</v>
       </c>
       <c r="I48">
         <v>0</v>
@@ -3569,39 +3428,36 @@
         <v>0</v>
       </c>
       <c r="L48">
-        <v>0</v>
+        <v>3800</v>
       </c>
       <c r="M48">
-        <v>3800</v>
+        <v>4</v>
       </c>
       <c r="N48">
-        <v>4</v>
+        <v>266</v>
       </c>
       <c r="O48">
-        <v>266</v>
+        <v>19376</v>
       </c>
       <c r="P48">
-        <v>19376</v>
+        <v>54497</v>
       </c>
       <c r="Q48">
-        <v>54497</v>
-      </c>
-      <c r="R48" s="2">
         <v>4623</v>
       </c>
-      <c r="S48" s="2">
-        <v>0</v>
-      </c>
-      <c r="T48" s="2">
+      <c r="R48">
+        <v>0</v>
+      </c>
+      <c r="S48">
         <v>9</v>
       </c>
     </row>
-    <row r="49" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A49">
         <v>46</v>
       </c>
       <c r="B49" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C49">
         <v>21651</v>
@@ -3610,16 +3466,16 @@
         <v>0</v>
       </c>
       <c r="E49">
-        <v>0</v>
+        <v>21651</v>
       </c>
       <c r="F49">
+        <v>0</v>
+      </c>
+      <c r="G49">
         <v>21651</v>
       </c>
-      <c r="G49">
-        <v>0</v>
-      </c>
       <c r="H49">
-        <v>21651</v>
+        <v>0</v>
       </c>
       <c r="I49">
         <v>0</v>
@@ -3631,39 +3487,36 @@
         <v>0</v>
       </c>
       <c r="L49">
-        <v>0</v>
+        <v>3627</v>
       </c>
       <c r="M49">
-        <v>3627</v>
+        <v>0</v>
       </c>
       <c r="N49">
-        <v>0</v>
+        <v>628</v>
       </c>
       <c r="O49">
-        <v>628</v>
+        <v>21027</v>
       </c>
       <c r="P49">
-        <v>21027</v>
+        <v>55376</v>
       </c>
       <c r="Q49">
-        <v>55376</v>
-      </c>
-      <c r="R49" s="2">
         <v>5057</v>
       </c>
-      <c r="S49" s="2">
-        <v>0</v>
-      </c>
-      <c r="T49" s="2">
+      <c r="R49">
+        <v>0</v>
+      </c>
+      <c r="S49">
         <v>4</v>
       </c>
     </row>
-    <row r="50" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A50">
         <v>47</v>
       </c>
       <c r="B50" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C50">
         <v>21936</v>
@@ -3672,16 +3525,16 @@
         <v>0</v>
       </c>
       <c r="E50">
-        <v>0</v>
+        <v>21936</v>
       </c>
       <c r="F50">
+        <v>0</v>
+      </c>
+      <c r="G50">
         <v>21936</v>
       </c>
-      <c r="G50">
-        <v>0</v>
-      </c>
       <c r="H50">
-        <v>21936</v>
+        <v>0</v>
       </c>
       <c r="I50">
         <v>0</v>
@@ -3693,39 +3546,36 @@
         <v>0</v>
       </c>
       <c r="L50">
-        <v>0</v>
+        <v>4160</v>
       </c>
       <c r="M50">
-        <v>4160</v>
+        <v>5</v>
       </c>
       <c r="N50">
-        <v>5</v>
+        <v>26</v>
       </c>
       <c r="O50">
-        <v>26</v>
+        <v>21910</v>
       </c>
       <c r="P50">
-        <v>21910</v>
+        <v>63298</v>
       </c>
       <c r="Q50">
-        <v>63298</v>
-      </c>
-      <c r="R50" s="2">
         <v>7292</v>
       </c>
-      <c r="S50" s="2">
-        <v>0</v>
-      </c>
-      <c r="T50" s="2">
+      <c r="R50">
+        <v>0</v>
+      </c>
+      <c r="S50">
         <v>1</v>
       </c>
     </row>
-    <row r="51" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A51">
         <v>48</v>
       </c>
       <c r="B51" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C51">
         <v>23798</v>
@@ -3734,16 +3584,16 @@
         <v>0</v>
       </c>
       <c r="E51">
-        <v>0</v>
+        <v>23798</v>
       </c>
       <c r="F51">
+        <v>0</v>
+      </c>
+      <c r="G51">
         <v>23798</v>
       </c>
-      <c r="G51">
-        <v>0</v>
-      </c>
       <c r="H51">
-        <v>23798</v>
+        <v>0</v>
       </c>
       <c r="I51">
         <v>0</v>
@@ -3755,39 +3605,36 @@
         <v>0</v>
       </c>
       <c r="L51">
-        <v>0</v>
+        <v>4843</v>
       </c>
       <c r="M51">
-        <v>4843</v>
+        <v>11</v>
       </c>
       <c r="N51">
-        <v>11</v>
+        <v>75</v>
       </c>
       <c r="O51">
-        <v>75</v>
+        <v>23723</v>
       </c>
       <c r="P51">
-        <v>23723</v>
+        <v>71754</v>
       </c>
       <c r="Q51">
-        <v>71754</v>
-      </c>
-      <c r="R51" s="2">
         <v>7715</v>
       </c>
-      <c r="S51" s="2">
-        <v>0</v>
-      </c>
-      <c r="T51" s="2">
+      <c r="R51">
+        <v>0</v>
+      </c>
+      <c r="S51">
         <v>40</v>
       </c>
     </row>
-    <row r="52" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A52">
         <v>49</v>
       </c>
       <c r="B52" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C52">
         <v>21094</v>
@@ -3796,16 +3643,16 @@
         <v>0</v>
       </c>
       <c r="E52">
-        <v>0</v>
+        <v>21094</v>
       </c>
       <c r="F52">
+        <v>0</v>
+      </c>
+      <c r="G52">
         <v>21094</v>
       </c>
-      <c r="G52">
-        <v>0</v>
-      </c>
       <c r="H52">
-        <v>21094</v>
+        <v>0</v>
       </c>
       <c r="I52">
         <v>0</v>
@@ -3817,39 +3664,36 @@
         <v>0</v>
       </c>
       <c r="L52">
-        <v>0</v>
+        <v>2942</v>
       </c>
       <c r="M52">
-        <v>2942</v>
+        <v>1</v>
       </c>
       <c r="N52">
-        <v>1</v>
+        <v>45</v>
       </c>
       <c r="O52">
-        <v>45</v>
+        <v>21049</v>
       </c>
       <c r="P52">
-        <v>21049</v>
+        <v>63987</v>
       </c>
       <c r="Q52">
-        <v>63987</v>
-      </c>
-      <c r="R52" s="2">
         <v>5655</v>
       </c>
-      <c r="S52" s="2">
-        <v>0</v>
-      </c>
-      <c r="T52" s="2">
+      <c r="R52">
+        <v>0</v>
+      </c>
+      <c r="S52">
         <v>2</v>
       </c>
     </row>
-    <row r="53" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A53">
         <v>50</v>
       </c>
       <c r="B53" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C53">
         <v>19131</v>
@@ -3858,16 +3702,16 @@
         <v>0</v>
       </c>
       <c r="E53">
-        <v>0</v>
+        <v>19131</v>
       </c>
       <c r="F53">
+        <v>0</v>
+      </c>
+      <c r="G53">
         <v>19131</v>
       </c>
-      <c r="G53">
-        <v>0</v>
-      </c>
       <c r="H53">
-        <v>19131</v>
+        <v>0</v>
       </c>
       <c r="I53">
         <v>0</v>
@@ -3879,39 +3723,36 @@
         <v>0</v>
       </c>
       <c r="L53">
-        <v>0</v>
+        <v>3513</v>
       </c>
       <c r="M53">
-        <v>3513</v>
+        <v>1</v>
       </c>
       <c r="N53">
-        <v>1</v>
+        <v>76</v>
       </c>
       <c r="O53">
-        <v>76</v>
+        <v>19055</v>
       </c>
       <c r="P53">
-        <v>19055</v>
+        <v>56306</v>
       </c>
       <c r="Q53">
-        <v>56306</v>
-      </c>
-      <c r="R53" s="2">
         <v>6551</v>
       </c>
-      <c r="S53" s="2">
-        <v>0</v>
-      </c>
-      <c r="T53" s="2">
+      <c r="R53">
+        <v>0</v>
+      </c>
+      <c r="S53">
         <v>5</v>
       </c>
     </row>
-    <row r="54" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A54">
         <v>51</v>
       </c>
       <c r="B54" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C54">
         <v>20758</v>
@@ -3920,16 +3761,16 @@
         <v>0</v>
       </c>
       <c r="E54">
-        <v>0</v>
+        <v>20758</v>
       </c>
       <c r="F54">
+        <v>0</v>
+      </c>
+      <c r="G54">
         <v>20758</v>
       </c>
-      <c r="G54">
-        <v>0</v>
-      </c>
       <c r="H54">
-        <v>20758</v>
+        <v>0</v>
       </c>
       <c r="I54">
         <v>0</v>
@@ -3941,39 +3782,36 @@
         <v>0</v>
       </c>
       <c r="L54">
-        <v>0</v>
+        <v>2603</v>
       </c>
       <c r="M54">
-        <v>2603</v>
+        <v>5</v>
       </c>
       <c r="N54">
-        <v>5</v>
+        <v>391</v>
       </c>
       <c r="O54">
-        <v>391</v>
+        <v>20367</v>
       </c>
       <c r="P54">
-        <v>20367</v>
+        <v>58441</v>
       </c>
       <c r="Q54">
-        <v>58441</v>
-      </c>
-      <c r="R54" s="2">
         <v>7347</v>
       </c>
-      <c r="S54" s="2">
-        <v>0</v>
-      </c>
-      <c r="T54" s="2">
+      <c r="R54">
+        <v>0</v>
+      </c>
+      <c r="S54">
         <v>1</v>
       </c>
     </row>
-    <row r="55" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A55">
         <v>52</v>
       </c>
       <c r="B55" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C55">
         <v>16022</v>
@@ -3982,16 +3820,16 @@
         <v>0</v>
       </c>
       <c r="E55">
-        <v>0</v>
+        <v>16022</v>
       </c>
       <c r="F55">
+        <v>0</v>
+      </c>
+      <c r="G55">
         <v>16022</v>
       </c>
-      <c r="G55">
-        <v>0</v>
-      </c>
       <c r="H55">
-        <v>16022</v>
+        <v>0</v>
       </c>
       <c r="I55">
         <v>0</v>
@@ -4003,39 +3841,36 @@
         <v>0</v>
       </c>
       <c r="L55">
-        <v>0</v>
+        <v>2109</v>
       </c>
       <c r="M55">
-        <v>2109</v>
+        <v>1</v>
       </c>
       <c r="N55">
-        <v>1</v>
+        <v>129</v>
       </c>
       <c r="O55">
-        <v>129</v>
+        <v>15893</v>
       </c>
       <c r="P55">
-        <v>15893</v>
+        <v>58215</v>
       </c>
       <c r="Q55">
-        <v>58215</v>
-      </c>
-      <c r="R55" s="2">
         <v>5098</v>
       </c>
-      <c r="S55" s="2">
-        <v>0</v>
-      </c>
-      <c r="T55" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="56" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="R55">
+        <v>0</v>
+      </c>
+      <c r="S55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A56">
         <v>53</v>
       </c>
       <c r="B56" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C56">
         <v>19256</v>
@@ -4044,16 +3879,16 @@
         <v>0</v>
       </c>
       <c r="E56">
-        <v>0</v>
+        <v>19256</v>
       </c>
       <c r="F56">
+        <v>0</v>
+      </c>
+      <c r="G56">
         <v>19256</v>
       </c>
-      <c r="G56">
-        <v>0</v>
-      </c>
       <c r="H56">
-        <v>19256</v>
+        <v>0</v>
       </c>
       <c r="I56">
         <v>0</v>
@@ -4065,39 +3900,36 @@
         <v>0</v>
       </c>
       <c r="L56">
-        <v>0</v>
+        <v>4091</v>
       </c>
       <c r="M56">
-        <v>4091</v>
+        <v>3</v>
       </c>
       <c r="N56">
-        <v>3</v>
+        <v>451</v>
       </c>
       <c r="O56">
-        <v>451</v>
+        <v>18805</v>
       </c>
       <c r="P56">
-        <v>18805</v>
+        <v>47621</v>
       </c>
       <c r="Q56">
-        <v>47621</v>
-      </c>
-      <c r="R56" s="2">
         <v>4882</v>
       </c>
-      <c r="S56" s="2">
-        <v>0</v>
-      </c>
-      <c r="T56" s="2">
+      <c r="R56">
+        <v>0</v>
+      </c>
+      <c r="S56">
         <v>30</v>
       </c>
     </row>
-    <row r="57" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A57">
         <v>54</v>
       </c>
       <c r="B57" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C57">
         <v>21240</v>
@@ -4106,16 +3938,16 @@
         <v>0</v>
       </c>
       <c r="E57">
-        <v>0</v>
+        <v>21240</v>
       </c>
       <c r="F57">
+        <v>0</v>
+      </c>
+      <c r="G57">
         <v>21240</v>
       </c>
-      <c r="G57">
-        <v>0</v>
-      </c>
       <c r="H57">
-        <v>21240</v>
+        <v>0</v>
       </c>
       <c r="I57">
         <v>0</v>
@@ -4127,39 +3959,36 @@
         <v>0</v>
       </c>
       <c r="L57">
-        <v>0</v>
+        <v>1905</v>
       </c>
       <c r="M57">
-        <v>1905</v>
+        <v>5</v>
       </c>
       <c r="N57">
-        <v>5</v>
+        <v>39</v>
       </c>
       <c r="O57">
-        <v>39</v>
+        <v>21201</v>
       </c>
       <c r="P57">
-        <v>21201</v>
+        <v>61557</v>
       </c>
       <c r="Q57">
-        <v>61557</v>
-      </c>
-      <c r="R57" s="2">
         <v>6870</v>
       </c>
-      <c r="S57" s="2">
-        <v>0</v>
-      </c>
-      <c r="T57" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="58" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="R57">
+        <v>0</v>
+      </c>
+      <c r="S57">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A58">
         <v>55</v>
       </c>
       <c r="B58" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C58">
         <v>22819</v>
@@ -4168,16 +3997,16 @@
         <v>0</v>
       </c>
       <c r="E58">
-        <v>0</v>
+        <v>22819</v>
       </c>
       <c r="F58">
+        <v>0</v>
+      </c>
+      <c r="G58">
         <v>22819</v>
       </c>
-      <c r="G58">
-        <v>0</v>
-      </c>
       <c r="H58">
-        <v>22819</v>
+        <v>0</v>
       </c>
       <c r="I58">
         <v>0</v>
@@ -4189,39 +4018,36 @@
         <v>0</v>
       </c>
       <c r="L58">
-        <v>0</v>
+        <v>8123</v>
       </c>
       <c r="M58">
-        <v>8123</v>
+        <v>10</v>
       </c>
       <c r="N58">
-        <v>10</v>
+        <v>552</v>
       </c>
       <c r="O58">
-        <v>552</v>
+        <v>22267</v>
       </c>
       <c r="P58">
-        <v>22267</v>
+        <v>57579</v>
       </c>
       <c r="Q58">
-        <v>57579</v>
-      </c>
-      <c r="R58" s="2">
         <v>8884</v>
       </c>
-      <c r="S58" s="2">
-        <v>0</v>
-      </c>
-      <c r="T58" s="2">
+      <c r="R58">
+        <v>0</v>
+      </c>
+      <c r="S58">
         <v>64</v>
       </c>
     </row>
-    <row r="59" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A59">
         <v>56</v>
       </c>
       <c r="B59" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C59">
         <v>18776</v>
@@ -4230,16 +4056,16 @@
         <v>0</v>
       </c>
       <c r="E59">
-        <v>0</v>
+        <v>18776</v>
       </c>
       <c r="F59">
+        <v>0</v>
+      </c>
+      <c r="G59">
         <v>18776</v>
       </c>
-      <c r="G59">
-        <v>0</v>
-      </c>
       <c r="H59">
-        <v>18776</v>
+        <v>0</v>
       </c>
       <c r="I59">
         <v>0</v>
@@ -4251,39 +4077,36 @@
         <v>0</v>
       </c>
       <c r="L59">
-        <v>0</v>
+        <v>2506</v>
       </c>
       <c r="M59">
-        <v>2506</v>
+        <v>2</v>
       </c>
       <c r="N59">
-        <v>2</v>
+        <v>287</v>
       </c>
       <c r="O59">
-        <v>287</v>
+        <v>18489</v>
       </c>
       <c r="P59">
-        <v>18489</v>
+        <v>60495</v>
       </c>
       <c r="Q59">
-        <v>60495</v>
-      </c>
-      <c r="R59" s="2">
         <v>8028</v>
       </c>
-      <c r="S59" s="2">
-        <v>0</v>
-      </c>
-      <c r="T59" s="2">
+      <c r="R59">
+        <v>0</v>
+      </c>
+      <c r="S59">
         <v>27</v>
       </c>
     </row>
-    <row r="60" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A60">
         <v>57</v>
       </c>
       <c r="B60" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C60">
         <v>23749</v>
@@ -4292,16 +4115,16 @@
         <v>0</v>
       </c>
       <c r="E60">
-        <v>0</v>
+        <v>23749</v>
       </c>
       <c r="F60">
+        <v>0</v>
+      </c>
+      <c r="G60">
         <v>23749</v>
       </c>
-      <c r="G60">
-        <v>0</v>
-      </c>
       <c r="H60">
-        <v>23749</v>
+        <v>0</v>
       </c>
       <c r="I60">
         <v>0</v>
@@ -4313,39 +4136,36 @@
         <v>0</v>
       </c>
       <c r="L60">
-        <v>0</v>
+        <v>5815</v>
       </c>
       <c r="M60">
-        <v>5815</v>
+        <v>9</v>
       </c>
       <c r="N60">
-        <v>9</v>
+        <v>324</v>
       </c>
       <c r="O60">
-        <v>324</v>
+        <v>23425</v>
       </c>
       <c r="P60">
-        <v>23425</v>
+        <v>70153</v>
       </c>
       <c r="Q60">
-        <v>70153</v>
-      </c>
-      <c r="R60" s="2">
         <v>7415</v>
       </c>
-      <c r="S60" s="2">
-        <v>0</v>
-      </c>
-      <c r="T60" s="2">
+      <c r="R60">
+        <v>0</v>
+      </c>
+      <c r="S60">
         <v>32</v>
       </c>
     </row>
-    <row r="61" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A61">
         <v>58</v>
       </c>
       <c r="B61" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C61">
         <v>22069</v>
@@ -4354,16 +4174,16 @@
         <v>0</v>
       </c>
       <c r="E61">
-        <v>0</v>
+        <v>22069</v>
       </c>
       <c r="F61">
+        <v>0</v>
+      </c>
+      <c r="G61">
         <v>22069</v>
       </c>
-      <c r="G61">
-        <v>0</v>
-      </c>
       <c r="H61">
-        <v>22069</v>
+        <v>0</v>
       </c>
       <c r="I61">
         <v>0</v>
@@ -4375,39 +4195,36 @@
         <v>0</v>
       </c>
       <c r="L61">
-        <v>0</v>
+        <v>9977</v>
       </c>
       <c r="M61">
-        <v>9977</v>
+        <v>37</v>
       </c>
       <c r="N61">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="O61">
-        <v>36</v>
+        <v>22033</v>
       </c>
       <c r="P61">
-        <v>22033</v>
+        <v>55241</v>
       </c>
       <c r="Q61">
-        <v>55241</v>
-      </c>
-      <c r="R61" s="2">
         <v>7927</v>
       </c>
-      <c r="S61" s="2">
+      <c r="R61">
         <v>1</v>
       </c>
-      <c r="T61" s="2">
+      <c r="S61">
         <v>268</v>
       </c>
     </row>
-    <row r="62" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A62">
         <v>59</v>
       </c>
       <c r="B62" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C62">
         <v>15800</v>
@@ -4416,16 +4233,16 @@
         <v>0</v>
       </c>
       <c r="E62">
-        <v>0</v>
+        <v>15800</v>
       </c>
       <c r="F62">
+        <v>0</v>
+      </c>
+      <c r="G62">
         <v>15800</v>
       </c>
-      <c r="G62">
-        <v>0</v>
-      </c>
       <c r="H62">
-        <v>15800</v>
+        <v>0</v>
       </c>
       <c r="I62">
         <v>0</v>
@@ -4437,39 +4254,36 @@
         <v>0</v>
       </c>
       <c r="L62">
-        <v>0</v>
+        <v>4214</v>
       </c>
       <c r="M62">
-        <v>4214</v>
+        <v>19</v>
       </c>
       <c r="N62">
-        <v>19</v>
+        <v>494</v>
       </c>
       <c r="O62">
-        <v>494</v>
+        <v>15306</v>
       </c>
       <c r="P62">
-        <v>15306</v>
+        <v>51334</v>
       </c>
       <c r="Q62">
-        <v>51334</v>
-      </c>
-      <c r="R62" s="2">
         <v>6917</v>
       </c>
-      <c r="S62" s="2">
-        <v>0</v>
-      </c>
-      <c r="T62" s="2">
+      <c r="R62">
+        <v>0</v>
+      </c>
+      <c r="S62">
         <v>100</v>
       </c>
     </row>
-    <row r="63" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A63">
         <v>60</v>
       </c>
       <c r="B63" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C63">
         <v>36754</v>
@@ -4478,16 +4292,16 @@
         <v>0</v>
       </c>
       <c r="E63">
-        <v>0</v>
+        <v>36754</v>
       </c>
       <c r="F63">
+        <v>0</v>
+      </c>
+      <c r="G63">
         <v>36754</v>
       </c>
-      <c r="G63">
-        <v>0</v>
-      </c>
       <c r="H63">
-        <v>36754</v>
+        <v>0</v>
       </c>
       <c r="I63">
         <v>0</v>
@@ -4499,39 +4313,36 @@
         <v>0</v>
       </c>
       <c r="L63">
-        <v>0</v>
+        <v>10975</v>
       </c>
       <c r="M63">
-        <v>10975</v>
+        <v>68</v>
       </c>
       <c r="N63">
-        <v>68</v>
+        <v>931</v>
       </c>
       <c r="O63">
-        <v>931</v>
+        <v>35823</v>
       </c>
       <c r="P63">
-        <v>35823</v>
+        <v>68699</v>
       </c>
       <c r="Q63">
-        <v>68699</v>
-      </c>
-      <c r="R63" s="2">
         <v>9766</v>
       </c>
-      <c r="S63" s="2">
-        <v>0</v>
-      </c>
-      <c r="T63" s="2">
+      <c r="R63">
+        <v>0</v>
+      </c>
+      <c r="S63">
         <v>153</v>
       </c>
     </row>
-    <row r="64" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A64">
         <v>61</v>
       </c>
       <c r="B64" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C64">
         <v>42048</v>
@@ -4540,16 +4351,16 @@
         <v>0</v>
       </c>
       <c r="E64">
-        <v>0</v>
+        <v>42048</v>
       </c>
       <c r="F64">
+        <v>0</v>
+      </c>
+      <c r="G64">
         <v>42048</v>
       </c>
-      <c r="G64">
-        <v>0</v>
-      </c>
       <c r="H64">
-        <v>42048</v>
+        <v>0</v>
       </c>
       <c r="I64">
         <v>0</v>
@@ -4561,39 +4372,36 @@
         <v>0</v>
       </c>
       <c r="L64">
-        <v>0</v>
+        <v>9887</v>
       </c>
       <c r="M64">
-        <v>9887</v>
+        <v>8</v>
       </c>
       <c r="N64">
-        <v>8</v>
+        <v>493</v>
       </c>
       <c r="O64">
-        <v>493</v>
+        <v>41555</v>
       </c>
       <c r="P64">
-        <v>41555</v>
+        <v>60527</v>
       </c>
       <c r="Q64">
-        <v>60527</v>
-      </c>
-      <c r="R64" s="2">
         <v>5985</v>
       </c>
-      <c r="S64" s="2">
-        <v>0</v>
-      </c>
-      <c r="T64" s="2">
+      <c r="R64">
+        <v>0</v>
+      </c>
+      <c r="S64">
         <v>101</v>
       </c>
     </row>
-    <row r="65" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A65">
         <v>62</v>
       </c>
       <c r="B65" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C65">
         <v>41389</v>
@@ -4602,16 +4410,16 @@
         <v>0</v>
       </c>
       <c r="E65">
-        <v>0</v>
+        <v>41389</v>
       </c>
       <c r="F65">
+        <v>0</v>
+      </c>
+      <c r="G65">
         <v>41389</v>
       </c>
-      <c r="G65">
-        <v>0</v>
-      </c>
       <c r="H65">
-        <v>41389</v>
+        <v>0</v>
       </c>
       <c r="I65">
         <v>0</v>
@@ -4623,39 +4431,36 @@
         <v>0</v>
       </c>
       <c r="L65">
-        <v>0</v>
+        <v>13582</v>
       </c>
       <c r="M65">
-        <v>13582</v>
+        <v>2</v>
       </c>
       <c r="N65">
-        <v>2</v>
+        <v>2635</v>
       </c>
       <c r="O65">
-        <v>2635</v>
+        <v>38754</v>
       </c>
       <c r="P65">
-        <v>38754</v>
+        <v>58527</v>
       </c>
       <c r="Q65">
-        <v>58527</v>
-      </c>
-      <c r="R65" s="2">
         <v>13282</v>
       </c>
-      <c r="S65" s="2">
-        <v>0</v>
-      </c>
-      <c r="T65" s="2">
+      <c r="R65">
+        <v>0</v>
+      </c>
+      <c r="S65">
         <v>138</v>
       </c>
     </row>
-    <row r="66" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A66">
         <v>63</v>
       </c>
       <c r="B66" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C66">
         <v>67362</v>
@@ -4664,16 +4469,16 @@
         <v>0</v>
       </c>
       <c r="E66">
-        <v>1</v>
+        <v>67362</v>
       </c>
       <c r="F66">
+        <v>0</v>
+      </c>
+      <c r="G66">
         <v>67362</v>
       </c>
-      <c r="G66">
-        <v>0</v>
-      </c>
       <c r="H66">
-        <v>67362</v>
+        <v>0</v>
       </c>
       <c r="I66">
         <v>0</v>
@@ -4685,39 +4490,36 @@
         <v>0</v>
       </c>
       <c r="L66">
-        <v>0</v>
+        <v>13733</v>
       </c>
       <c r="M66">
-        <v>13733</v>
+        <v>2</v>
       </c>
       <c r="N66">
-        <v>2</v>
+        <v>4022</v>
       </c>
       <c r="O66">
-        <v>4022</v>
+        <v>63341</v>
       </c>
       <c r="P66">
-        <v>63341</v>
+        <v>93810</v>
       </c>
       <c r="Q66">
-        <v>93810</v>
-      </c>
-      <c r="R66" s="2">
         <v>17742</v>
       </c>
-      <c r="S66" s="2">
-        <v>0</v>
-      </c>
-      <c r="T66" s="2">
+      <c r="R66">
+        <v>0</v>
+      </c>
+      <c r="S66">
         <v>52</v>
       </c>
     </row>
-    <row r="67" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A67">
         <v>64</v>
       </c>
       <c r="B67" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C67">
         <v>68828</v>
@@ -4726,16 +4528,16 @@
         <v>0</v>
       </c>
       <c r="E67">
-        <v>0</v>
+        <v>68828</v>
       </c>
       <c r="F67">
+        <v>0</v>
+      </c>
+      <c r="G67">
         <v>68828</v>
       </c>
-      <c r="G67">
-        <v>0</v>
-      </c>
       <c r="H67">
-        <v>68828</v>
+        <v>0</v>
       </c>
       <c r="I67">
         <v>0</v>
@@ -4747,39 +4549,36 @@
         <v>0</v>
       </c>
       <c r="L67">
-        <v>0</v>
+        <v>19495</v>
       </c>
       <c r="M67">
-        <v>19495</v>
+        <v>10</v>
       </c>
       <c r="N67">
-        <v>10</v>
+        <v>3644</v>
       </c>
       <c r="O67">
-        <v>3644</v>
+        <v>65185</v>
       </c>
       <c r="P67">
-        <v>65185</v>
+        <v>78032</v>
       </c>
       <c r="Q67">
-        <v>78032</v>
-      </c>
-      <c r="R67" s="2">
         <v>9807</v>
       </c>
-      <c r="S67" s="2">
-        <v>0</v>
-      </c>
-      <c r="T67" s="2">
+      <c r="R67">
+        <v>0</v>
+      </c>
+      <c r="S67">
         <v>116</v>
       </c>
     </row>
-    <row r="68" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A68">
         <v>65</v>
       </c>
       <c r="B68" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C68">
         <v>65397</v>
@@ -4788,16 +4587,16 @@
         <v>0</v>
       </c>
       <c r="E68">
-        <v>0</v>
+        <v>65397</v>
       </c>
       <c r="F68">
+        <v>0</v>
+      </c>
+      <c r="G68">
         <v>65397</v>
       </c>
-      <c r="G68">
-        <v>0</v>
-      </c>
       <c r="H68">
-        <v>65397</v>
+        <v>0</v>
       </c>
       <c r="I68">
         <v>0</v>
@@ -4809,39 +4608,36 @@
         <v>0</v>
       </c>
       <c r="L68">
-        <v>0</v>
+        <v>18679</v>
       </c>
       <c r="M68">
-        <v>18679</v>
+        <v>2</v>
       </c>
       <c r="N68">
-        <v>2</v>
+        <v>1603</v>
       </c>
       <c r="O68">
-        <v>1603</v>
+        <v>63796</v>
       </c>
       <c r="P68">
-        <v>63796</v>
+        <v>71325</v>
       </c>
       <c r="Q68">
-        <v>71325</v>
-      </c>
-      <c r="R68" s="2">
         <v>7850</v>
       </c>
-      <c r="S68" s="2">
-        <v>0</v>
-      </c>
-      <c r="T68" s="2">
+      <c r="R68">
+        <v>0</v>
+      </c>
+      <c r="S68">
         <v>26</v>
       </c>
     </row>
-    <row r="69" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A69">
         <v>66</v>
       </c>
       <c r="B69" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C69">
         <v>43938</v>
@@ -4850,16 +4646,16 @@
         <v>0</v>
       </c>
       <c r="E69">
-        <v>0</v>
+        <v>43938</v>
       </c>
       <c r="F69">
+        <v>0</v>
+      </c>
+      <c r="G69">
         <v>43938</v>
       </c>
-      <c r="G69">
-        <v>0</v>
-      </c>
       <c r="H69">
-        <v>43938</v>
+        <v>0</v>
       </c>
       <c r="I69">
         <v>0</v>
@@ -4871,39 +4667,36 @@
         <v>0</v>
       </c>
       <c r="L69">
-        <v>0</v>
+        <v>18216</v>
       </c>
       <c r="M69">
-        <v>18216</v>
+        <v>2</v>
       </c>
       <c r="N69">
-        <v>2</v>
+        <v>2619</v>
       </c>
       <c r="O69">
-        <v>2619</v>
+        <v>41322</v>
       </c>
       <c r="P69">
-        <v>41322</v>
+        <v>36118</v>
       </c>
       <c r="Q69">
-        <v>36118</v>
-      </c>
-      <c r="R69" s="2">
         <v>6528</v>
       </c>
-      <c r="S69" s="2">
-        <v>0</v>
-      </c>
-      <c r="T69" s="2">
+      <c r="R69">
+        <v>0</v>
+      </c>
+      <c r="S69">
         <v>47</v>
       </c>
     </row>
-    <row r="70" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A70">
         <v>67</v>
       </c>
       <c r="B70" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C70">
         <v>47711</v>
@@ -4912,16 +4705,16 @@
         <v>0</v>
       </c>
       <c r="E70">
-        <v>0</v>
+        <v>47711</v>
       </c>
       <c r="F70">
+        <v>0</v>
+      </c>
+      <c r="G70">
         <v>47711</v>
       </c>
-      <c r="G70">
-        <v>0</v>
-      </c>
       <c r="H70">
-        <v>47711</v>
+        <v>0</v>
       </c>
       <c r="I70">
         <v>0</v>
@@ -4933,39 +4726,36 @@
         <v>0</v>
       </c>
       <c r="L70">
-        <v>0</v>
+        <v>18275</v>
       </c>
       <c r="M70">
-        <v>18275</v>
+        <v>2</v>
       </c>
       <c r="N70">
-        <v>2</v>
+        <v>3246</v>
       </c>
       <c r="O70">
-        <v>3246</v>
+        <v>44466</v>
       </c>
       <c r="P70">
-        <v>44466</v>
+        <v>42051</v>
       </c>
       <c r="Q70">
-        <v>42051</v>
-      </c>
-      <c r="R70" s="2">
         <v>5798</v>
       </c>
-      <c r="S70" s="2">
-        <v>0</v>
-      </c>
-      <c r="T70" s="2">
+      <c r="R70">
+        <v>0</v>
+      </c>
+      <c r="S70">
         <v>29</v>
       </c>
     </row>
-    <row r="71" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A71">
         <v>68</v>
       </c>
       <c r="B71" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C71">
         <v>50963</v>
@@ -4974,16 +4764,16 @@
         <v>0</v>
       </c>
       <c r="E71">
-        <v>0</v>
+        <v>50963</v>
       </c>
       <c r="F71">
+        <v>0</v>
+      </c>
+      <c r="G71">
         <v>50963</v>
       </c>
-      <c r="G71">
-        <v>0</v>
-      </c>
       <c r="H71">
-        <v>50963</v>
+        <v>0</v>
       </c>
       <c r="I71">
         <v>0</v>
@@ -4995,39 +4785,36 @@
         <v>0</v>
       </c>
       <c r="L71">
-        <v>0</v>
+        <v>22851</v>
       </c>
       <c r="M71">
-        <v>22851</v>
+        <v>1</v>
       </c>
       <c r="N71">
-        <v>1</v>
+        <v>4449</v>
       </c>
       <c r="O71">
-        <v>4449</v>
+        <v>46514</v>
       </c>
       <c r="P71">
-        <v>46514</v>
+        <v>49140</v>
       </c>
       <c r="Q71">
-        <v>49140</v>
-      </c>
-      <c r="R71" s="2">
         <v>6782</v>
       </c>
-      <c r="S71" s="2">
-        <v>0</v>
-      </c>
-      <c r="T71" s="2">
+      <c r="R71">
+        <v>0</v>
+      </c>
+      <c r="S71">
         <v>235</v>
       </c>
     </row>
-    <row r="72" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A72">
         <v>69</v>
       </c>
       <c r="B72" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C72">
         <v>61543</v>
@@ -5036,16 +4823,16 @@
         <v>0</v>
       </c>
       <c r="E72">
-        <v>0</v>
+        <v>61543</v>
       </c>
       <c r="F72">
+        <v>0</v>
+      </c>
+      <c r="G72">
         <v>61543</v>
       </c>
-      <c r="G72">
-        <v>0</v>
-      </c>
       <c r="H72">
-        <v>61543</v>
+        <v>0</v>
       </c>
       <c r="I72">
         <v>0</v>
@@ -5057,39 +4844,36 @@
         <v>0</v>
       </c>
       <c r="L72">
-        <v>0</v>
+        <v>17245</v>
       </c>
       <c r="M72">
-        <v>17245</v>
+        <v>9</v>
       </c>
       <c r="N72">
-        <v>9</v>
+        <v>3668</v>
       </c>
       <c r="O72">
-        <v>3668</v>
+        <v>57877</v>
       </c>
       <c r="P72">
-        <v>57877</v>
+        <v>85504</v>
       </c>
       <c r="Q72">
-        <v>85504</v>
-      </c>
-      <c r="R72" s="2">
         <v>12340</v>
       </c>
-      <c r="S72" s="2">
-        <v>0</v>
-      </c>
-      <c r="T72" s="2">
+      <c r="R72">
+        <v>0</v>
+      </c>
+      <c r="S72">
         <v>79</v>
       </c>
     </row>
-    <row r="73" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A73">
         <v>70</v>
       </c>
       <c r="B73" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C73">
         <v>58915</v>
@@ -5098,16 +4882,16 @@
         <v>0</v>
       </c>
       <c r="E73">
-        <v>0</v>
+        <v>58915</v>
       </c>
       <c r="F73">
+        <v>0</v>
+      </c>
+      <c r="G73">
         <v>58915</v>
       </c>
-      <c r="G73">
-        <v>0</v>
-      </c>
       <c r="H73">
-        <v>58915</v>
+        <v>0</v>
       </c>
       <c r="I73">
         <v>0</v>
@@ -5119,38 +4903,35 @@
         <v>0</v>
       </c>
       <c r="L73">
-        <v>0</v>
+        <v>15131</v>
       </c>
       <c r="M73">
-        <v>15131</v>
+        <v>8</v>
       </c>
       <c r="N73">
-        <v>8</v>
+        <v>3866</v>
       </c>
       <c r="O73">
-        <v>3866</v>
+        <v>55049</v>
       </c>
       <c r="P73">
-        <v>55049</v>
+        <v>67666</v>
       </c>
       <c r="Q73">
-        <v>67666</v>
-      </c>
-      <c r="R73" s="2">
         <v>10010</v>
       </c>
-      <c r="S73" s="2">
-        <v>0</v>
-      </c>
-      <c r="T73" s="2">
+      <c r="R73">
+        <v>0</v>
+      </c>
+      <c r="S73">
         <v>74</v>
       </c>
     </row>
-    <row r="74" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A74" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="B74" s="1"/>
+    <row r="74" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A74" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="B74" s="2"/>
       <c r="C74">
         <v>2430387</v>
       </c>
@@ -5158,16 +4939,16 @@
         <v>0</v>
       </c>
       <c r="E74">
-        <v>9</v>
+        <v>2430387</v>
       </c>
       <c r="F74">
-        <v>2430387</v>
+        <v>0</v>
       </c>
       <c r="G74">
-        <v>0</v>
+        <v>2430385</v>
       </c>
       <c r="H74">
-        <v>2430385</v>
+        <v>0</v>
       </c>
       <c r="I74">
         <v>0</v>
@@ -5179,54 +4960,48 @@
         <v>0</v>
       </c>
       <c r="L74">
-        <v>0</v>
+        <v>626066</v>
       </c>
       <c r="M74">
-        <v>626066</v>
+        <v>8318</v>
       </c>
       <c r="N74">
-        <v>8318</v>
+        <v>97186</v>
       </c>
       <c r="O74">
-        <v>97186</v>
+        <v>2333338</v>
       </c>
       <c r="P74">
-        <v>2333338</v>
+        <v>4703252</v>
       </c>
       <c r="Q74">
-        <v>4703252</v>
-      </c>
-      <c r="R74" s="2">
         <v>626236</v>
       </c>
-      <c r="S74" s="2">
+      <c r="R74">
         <v>1</v>
       </c>
-      <c r="T74" s="2">
+      <c r="S74">
         <v>3445</v>
       </c>
     </row>
-    <row r="75" spans="1:20" ht="15.75" x14ac:dyDescent="0.25"/>
-    <row r="76" spans="1:20" ht="15.75" x14ac:dyDescent="0.25"/>
   </sheetData>
-  <mergeCells count="13">
+  <mergeCells count="12">
     <mergeCell ref="A74:B74"/>
-    <mergeCell ref="R2:T2"/>
-    <mergeCell ref="A1:R1"/>
+    <mergeCell ref="Q2:S2"/>
+    <mergeCell ref="A1:Q1"/>
     <mergeCell ref="A2:A3"/>
     <mergeCell ref="B2:B3"/>
     <mergeCell ref="C2:C3"/>
     <mergeCell ref="D2:D3"/>
     <mergeCell ref="E2:E3"/>
     <mergeCell ref="F2:F3"/>
-    <mergeCell ref="G2:G3"/>
-    <mergeCell ref="H2:J2"/>
-    <mergeCell ref="K2:N2"/>
-    <mergeCell ref="O2:Q2"/>
+    <mergeCell ref="G2:I2"/>
+    <mergeCell ref="J2:M2"/>
+    <mergeCell ref="N2:P2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="A2:Q74 B1:Q1" numberStoredAsText="1"/>
+    <ignoredError sqref="A2:D74 B1:D1 E2:P74 E1:P1" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>